--- a/eval/learning-curve/results/statistical_tests_full150.xlsx
+++ b/eval/learning-curve/results/statistical_tests_full150.xlsx
@@ -675,7 +675,7 @@
         <v>0.111</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0954</v>
+        <v>0.0956</v>
       </c>
       <c r="J2" t="n">
         <v>0.853</v>
@@ -690,7 +690,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="O2" t="n">
         <v>0.767</v>
@@ -738,7 +738,7 @@
         <v>0.907</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.873</v>
+        <v>0.88</v>
       </c>
       <c r="AE2" t="n">
         <v>0.873</v>
@@ -811,7 +811,7 @@
         <v>0.111</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0954</v>
+        <v>0.0956</v>
       </c>
       <c r="J3" t="n">
         <v>0.853</v>
@@ -826,7 +826,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="O3" t="n">
         <v>0.767</v>
@@ -874,7 +874,7 @@
         <v>0.907</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.873</v>
+        <v>0.88</v>
       </c>
       <c r="AE3" t="n">
         <v>0.873</v>
@@ -910,7 +910,7 @@
         <v>0.68</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.222</v>
+        <v>0.232</v>
       </c>
     </row>
     <row r="4">
@@ -941,13 +941,13 @@
         <v>0.823</v>
       </c>
       <c r="G4" t="n">
-        <v>0.843</v>
+        <v>0.844</v>
       </c>
       <c r="H4" t="n">
         <v>0.111</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0835</v>
       </c>
       <c r="J4" t="n">
         <v>0.853</v>
@@ -962,7 +962,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="O4" t="n">
         <v>0.767</v>
@@ -1010,7 +1010,7 @@
         <v>0.92</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.833</v>
+        <v>0.84</v>
       </c>
       <c r="AE4" t="n">
         <v>0.867</v>
@@ -1046,7 +1046,7 @@
         <v>0.707</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.284</v>
+        <v>0.273</v>
       </c>
     </row>
     <row r="5">
@@ -1077,13 +1077,13 @@
         <v>0.823</v>
       </c>
       <c r="G5" t="n">
-        <v>0.843</v>
+        <v>0.844</v>
       </c>
       <c r="H5" t="n">
         <v>0.111</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0835</v>
       </c>
       <c r="J5" t="n">
         <v>0.853</v>
@@ -1098,7 +1098,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="O5" t="n">
         <v>0.767</v>
@@ -1146,7 +1146,7 @@
         <v>0.92</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.833</v>
+        <v>0.84</v>
       </c>
       <c r="AE5" t="n">
         <v>0.867</v>
@@ -1213,13 +1213,13 @@
         <v>0.823</v>
       </c>
       <c r="G6" t="n">
-        <v>0.839</v>
+        <v>0.84</v>
       </c>
       <c r="H6" t="n">
         <v>0.111</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.0965</v>
       </c>
       <c r="J6" t="n">
         <v>0.853</v>
@@ -1234,7 +1234,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="O6" t="n">
         <v>0.767</v>
@@ -1282,7 +1282,7 @@
         <v>0.953</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AE6" t="n">
         <v>0.84</v>
@@ -1343,19 +1343,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.351</v>
+        <v>0.365</v>
       </c>
       <c r="F7" t="n">
         <v>0.823</v>
       </c>
       <c r="G7" t="n">
-        <v>0.839</v>
+        <v>0.84</v>
       </c>
       <c r="H7" t="n">
         <v>0.111</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.0965</v>
       </c>
       <c r="J7" t="n">
         <v>0.853</v>
@@ -1370,7 +1370,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="O7" t="n">
         <v>0.767</v>
@@ -1418,7 +1418,7 @@
         <v>0.953</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AE7" t="n">
         <v>0.84</v>
@@ -1454,7 +1454,7 @@
         <v>0.6870000000000001</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.351</v>
+        <v>0.365</v>
       </c>
     </row>
     <row r="8">
@@ -1491,7 +1491,7 @@
         <v>0.111</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0849</v>
+        <v>0.0847</v>
       </c>
       <c r="J8" t="n">
         <v>0.853</v>
@@ -1506,7 +1506,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="O8" t="n">
         <v>0.767</v>
@@ -1554,7 +1554,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AE8" t="n">
         <v>0.867</v>
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.111</v>
+        <v>0.117</v>
       </c>
       <c r="F9" t="n">
         <v>0.823</v>
@@ -1627,7 +1627,7 @@
         <v>0.111</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0849</v>
+        <v>0.0847</v>
       </c>
       <c r="J9" t="n">
         <v>0.853</v>
@@ -1642,7 +1642,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="O9" t="n">
         <v>0.767</v>
@@ -1690,7 +1690,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AE9" t="n">
         <v>0.867</v>
@@ -1726,7 +1726,7 @@
         <v>0.72</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.222</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="10">
@@ -1763,7 +1763,7 @@
         <v>0.111</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0698</v>
+        <v>0.0693</v>
       </c>
       <c r="J10" t="n">
         <v>0.853</v>
@@ -1778,7 +1778,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="O10" t="n">
         <v>0.767</v>
@@ -1826,7 +1826,7 @@
         <v>0.96</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="AE10" t="n">
         <v>0.887</v>
@@ -1899,7 +1899,7 @@
         <v>0.111</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0698</v>
+        <v>0.0693</v>
       </c>
       <c r="J11" t="n">
         <v>0.853</v>
@@ -1914,7 +1914,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="O11" t="n">
         <v>0.767</v>
@@ -1962,7 +1962,7 @@
         <v>0.96</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="AE11" t="n">
         <v>0.887</v>
@@ -2295,13 +2295,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.145</v>
+        <v>0.134</v>
       </c>
       <c r="F14" t="n">
         <v>0.796</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>0.152</v>
@@ -2370,7 +2370,7 @@
         <v>0.987</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.78</v>
+        <v>0.787</v>
       </c>
       <c r="AE14" t="n">
         <v>0.847</v>
@@ -2406,7 +2406,7 @@
         <v>0.38</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.242</v>
+        <v>0.223</v>
       </c>
     </row>
     <row r="15">
@@ -2431,13 +2431,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.186</v>
+        <v>0.178</v>
       </c>
       <c r="F15" t="n">
         <v>0.796</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H15" t="n">
         <v>0.152</v>
@@ -2506,7 +2506,7 @@
         <v>0.987</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.78</v>
+        <v>0.787</v>
       </c>
       <c r="AE15" t="n">
         <v>0.847</v>
@@ -2542,7 +2542,7 @@
         <v>0.38</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.31</v>
+        <v>0.297</v>
       </c>
     </row>
     <row r="16">
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.227</v>
+        <v>0.211</v>
       </c>
       <c r="F16" t="n">
         <v>0.796</v>
@@ -2642,7 +2642,7 @@
         <v>0.987</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.747</v>
+        <v>0.753</v>
       </c>
       <c r="AE16" t="n">
         <v>0.86</v>
@@ -2678,7 +2678,7 @@
         <v>0.367</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.284</v>
+        <v>0.273</v>
       </c>
     </row>
     <row r="17">
@@ -2778,7 +2778,7 @@
         <v>0.987</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.747</v>
+        <v>0.753</v>
       </c>
       <c r="AE17" t="n">
         <v>0.86</v>
@@ -3111,19 +3111,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="F20" t="n">
         <v>0.796</v>
       </c>
       <c r="G20" t="n">
-        <v>0.849</v>
+        <v>0.85</v>
       </c>
       <c r="H20" t="n">
         <v>0.152</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0914</v>
+        <v>0.0911</v>
       </c>
       <c r="J20" t="n">
         <v>0.773</v>
@@ -3186,7 +3186,7 @@
         <v>0.98</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.78</v>
+        <v>0.787</v>
       </c>
       <c r="AE20" t="n">
         <v>0.853</v>
@@ -3222,7 +3222,7 @@
         <v>0.7</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -3247,19 +3247,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.00257</v>
+        <v>0.00232</v>
       </c>
       <c r="F21" t="n">
         <v>0.796</v>
       </c>
       <c r="G21" t="n">
-        <v>0.849</v>
+        <v>0.85</v>
       </c>
       <c r="H21" t="n">
         <v>0.152</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0914</v>
+        <v>0.0911</v>
       </c>
       <c r="J21" t="n">
         <v>0.773</v>
@@ -3322,7 +3322,7 @@
         <v>0.98</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.78</v>
+        <v>0.787</v>
       </c>
       <c r="AE21" t="n">
         <v>0.853</v>
@@ -3358,7 +3358,7 @@
         <v>0.7</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.0128</v>
+        <v>0.0116</v>
       </c>
     </row>
     <row r="22">
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.679</v>
+        <v>0.678</v>
       </c>
       <c r="F22" t="n">
         <v>0.834</v>
@@ -3494,7 +3494,7 @@
         <v>0.552</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.884</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="23">
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.789</v>
+        <v>0.788</v>
       </c>
       <c r="F24" t="n">
         <v>0.834</v>
@@ -3667,7 +3667,7 @@
         <v>0.161</v>
       </c>
       <c r="I24" t="n">
-        <v>0.142</v>
+        <v>0.143</v>
       </c>
       <c r="J24" t="n">
         <v>0.917</v>
@@ -3766,7 +3766,7 @@
         <v>0.59</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.884</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="25">
@@ -3803,7 +3803,7 @@
         <v>0.161</v>
       </c>
       <c r="I25" t="n">
-        <v>0.142</v>
+        <v>0.143</v>
       </c>
       <c r="J25" t="n">
         <v>0.917</v>
@@ -4002,7 +4002,7 @@
         <v>0.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.962</v>
+        <v>0.963</v>
       </c>
       <c r="AE26" t="n">
         <v>0.886</v>
@@ -4038,7 +4038,7 @@
         <v>0.556</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.884</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="27">
@@ -4138,7 +4138,7 @@
         <v>0.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.962</v>
+        <v>0.963</v>
       </c>
       <c r="AE27" t="n">
         <v>0.886</v>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.884</v>
+        <v>0.883</v>
       </c>
       <c r="F28" t="n">
         <v>0.834</v>
@@ -4310,7 +4310,7 @@
         <v>0.594</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.884</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="29">
@@ -4546,7 +4546,7 @@
         <v>0.833</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.95</v>
+        <v>0.951</v>
       </c>
       <c r="AE30" t="n">
         <v>0.921</v>
@@ -4682,7 +4682,7 @@
         <v>0.833</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.95</v>
+        <v>0.951</v>
       </c>
       <c r="AE31" t="n">
         <v>0.921</v>
@@ -4854,7 +4854,7 @@
         <v>0.339</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.884</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="33">
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="F34" t="n">
         <v>0.793</v>
@@ -5090,7 +5090,7 @@
         <v>0.955</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.895</v>
+        <v>0.897</v>
       </c>
       <c r="AE34" t="n">
         <v>0.863</v>
@@ -5126,7 +5126,7 @@
         <v>0.347</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.884</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="35">
@@ -5226,7 +5226,7 @@
         <v>0.955</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.895</v>
+        <v>0.897</v>
       </c>
       <c r="AE35" t="n">
         <v>0.863</v>
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.681</v>
+        <v>0.677</v>
       </c>
       <c r="F36" t="n">
         <v>0.793</v>
@@ -5362,7 +5362,7 @@
         <v>1</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.88</v>
+        <v>0.881</v>
       </c>
       <c r="AE36" t="n">
         <v>0.899</v>
@@ -5398,7 +5398,7 @@
         <v>0.333</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.884</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="37">
@@ -5498,7 +5498,7 @@
         <v>1</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.88</v>
+        <v>0.881</v>
       </c>
       <c r="AE37" t="n">
         <v>0.899</v>
@@ -5670,7 +5670,7 @@
         <v>0.315</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.884</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="39">
@@ -6106,10 +6106,10 @@
         <v>0.128</v>
       </c>
       <c r="F42" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="G42" t="n">
-        <v>0.8</v>
+        <v>0.801</v>
       </c>
       <c r="H42" t="n">
         <v>0.152</v>
@@ -6130,7 +6130,7 @@
         <v>0.955</v>
       </c>
       <c r="N42" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="O42" t="n">
         <v>0.674</v>
@@ -6178,7 +6178,7 @@
         <v>0.955</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.822</v>
+        <v>0.832</v>
       </c>
       <c r="AE42" t="n">
         <v>0.88</v>
@@ -6242,10 +6242,10 @@
         <v>0.0464</v>
       </c>
       <c r="F43" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8</v>
+        <v>0.801</v>
       </c>
       <c r="H43" t="n">
         <v>0.152</v>
@@ -6266,7 +6266,7 @@
         <v>0.955</v>
       </c>
       <c r="N43" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="O43" t="n">
         <v>0.674</v>
@@ -6314,7 +6314,7 @@
         <v>0.955</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.822</v>
+        <v>0.832</v>
       </c>
       <c r="AE43" t="n">
         <v>0.88</v>
@@ -6378,10 +6378,10 @@
         <v>0.634</v>
       </c>
       <c r="F44" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="G44" t="n">
-        <v>0.774</v>
+        <v>0.775</v>
       </c>
       <c r="H44" t="n">
         <v>0.152</v>
@@ -6402,7 +6402,7 @@
         <v>0.955</v>
       </c>
       <c r="N44" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="O44" t="n">
         <v>0.674</v>
@@ -6450,7 +6450,7 @@
         <v>0.909</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.772</v>
+        <v>0.782</v>
       </c>
       <c r="AE44" t="n">
         <v>0.891</v>
@@ -6514,10 +6514,10 @@
         <v>0.82</v>
       </c>
       <c r="F45" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="G45" t="n">
-        <v>0.774</v>
+        <v>0.775</v>
       </c>
       <c r="H45" t="n">
         <v>0.152</v>
@@ -6538,7 +6538,7 @@
         <v>0.955</v>
       </c>
       <c r="N45" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="O45" t="n">
         <v>0.674</v>
@@ -6586,7 +6586,7 @@
         <v>0.909</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.772</v>
+        <v>0.782</v>
       </c>
       <c r="AE45" t="n">
         <v>0.891</v>
@@ -6650,7 +6650,7 @@
         <v>0.83</v>
       </c>
       <c r="F46" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="G46" t="n">
         <v>0.768</v>
@@ -6674,7 +6674,7 @@
         <v>0.955</v>
       </c>
       <c r="N46" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="O46" t="n">
         <v>0.674</v>
@@ -6722,7 +6722,7 @@
         <v>0.909</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.752</v>
+        <v>0.762</v>
       </c>
       <c r="AE46" t="n">
         <v>0.848</v>
@@ -6786,7 +6786,7 @@
         <v>0.979</v>
       </c>
       <c r="F47" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="G47" t="n">
         <v>0.768</v>
@@ -6810,7 +6810,7 @@
         <v>0.955</v>
       </c>
       <c r="N47" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="O47" t="n">
         <v>0.674</v>
@@ -6858,7 +6858,7 @@
         <v>0.909</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.752</v>
+        <v>0.762</v>
       </c>
       <c r="AE47" t="n">
         <v>0.848</v>
@@ -6922,7 +6922,7 @@
         <v>0.0799</v>
       </c>
       <c r="F48" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="G48" t="n">
         <v>0.8080000000000001</v>
@@ -6946,7 +6946,7 @@
         <v>0.955</v>
       </c>
       <c r="N48" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="O48" t="n">
         <v>0.674</v>
@@ -6994,7 +6994,7 @@
         <v>0.955</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="AE48" t="n">
         <v>0.88</v>
@@ -7030,7 +7030,7 @@
         <v>0.745</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.131</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="49">
@@ -7058,7 +7058,7 @@
         <v>0.0844</v>
       </c>
       <c r="F49" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="G49" t="n">
         <v>0.8080000000000001</v>
@@ -7082,7 +7082,7 @@
         <v>0.955</v>
       </c>
       <c r="N49" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="O49" t="n">
         <v>0.674</v>
@@ -7130,7 +7130,7 @@
         <v>0.955</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="AE49" t="n">
         <v>0.88</v>
@@ -7194,10 +7194,10 @@
         <v>0.00988</v>
       </c>
       <c r="F50" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="G50" t="n">
-        <v>0.841</v>
+        <v>0.842</v>
       </c>
       <c r="H50" t="n">
         <v>0.152</v>
@@ -7218,7 +7218,7 @@
         <v>0.955</v>
       </c>
       <c r="N50" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="O50" t="n">
         <v>0.674</v>
@@ -7266,7 +7266,7 @@
         <v>0.909</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.752</v>
+        <v>0.762</v>
       </c>
       <c r="AE50" t="n">
         <v>0.891</v>
@@ -7330,10 +7330,10 @@
         <v>0.0132</v>
       </c>
       <c r="F51" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="G51" t="n">
-        <v>0.841</v>
+        <v>0.842</v>
       </c>
       <c r="H51" t="n">
         <v>0.152</v>
@@ -7354,7 +7354,7 @@
         <v>0.955</v>
       </c>
       <c r="N51" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="O51" t="n">
         <v>0.674</v>
@@ -7402,7 +7402,7 @@
         <v>0.909</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.752</v>
+        <v>0.762</v>
       </c>
       <c r="AE51" t="n">
         <v>0.891</v>
@@ -7735,13 +7735,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.0031</v>
+        <v>0.00278</v>
       </c>
       <c r="F54" t="n">
         <v>0.756</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H54" t="n">
         <v>0.182</v>
@@ -7810,7 +7810,7 @@
         <v>0.955</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.762</v>
+        <v>0.772</v>
       </c>
       <c r="AE54" t="n">
         <v>0.891</v>
@@ -7846,7 +7846,7 @@
         <v>0.782</v>
       </c>
       <c r="AP54" t="n">
-        <v>0.031</v>
+        <v>0.0278</v>
       </c>
     </row>
     <row r="55">
@@ -7871,13 +7871,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.00521</v>
+        <v>0.00429</v>
       </c>
       <c r="F55" t="n">
         <v>0.756</v>
       </c>
       <c r="G55" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H55" t="n">
         <v>0.182</v>
@@ -7946,7 +7946,7 @@
         <v>0.955</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.762</v>
+        <v>0.772</v>
       </c>
       <c r="AE55" t="n">
         <v>0.891</v>
@@ -7982,7 +7982,7 @@
         <v>0.782</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.044</v>
+        <v>0.0429</v>
       </c>
     </row>
     <row r="56">
@@ -8007,13 +8007,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.0174</v>
+        <v>0.0155</v>
       </c>
       <c r="F56" t="n">
         <v>0.756</v>
       </c>
       <c r="G56" t="n">
-        <v>0.804</v>
+        <v>0.805</v>
       </c>
       <c r="H56" t="n">
         <v>0.182</v>
@@ -8082,7 +8082,7 @@
         <v>0.909</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.723</v>
+        <v>0.733</v>
       </c>
       <c r="AE56" t="n">
         <v>0.87</v>
@@ -8118,7 +8118,7 @@
         <v>0.727</v>
       </c>
       <c r="AP56" t="n">
-        <v>0.0435</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="57">
@@ -8149,7 +8149,7 @@
         <v>0.756</v>
       </c>
       <c r="G57" t="n">
-        <v>0.804</v>
+        <v>0.805</v>
       </c>
       <c r="H57" t="n">
         <v>0.182</v>
@@ -8218,7 +8218,7 @@
         <v>0.909</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.723</v>
+        <v>0.733</v>
       </c>
       <c r="AE57" t="n">
         <v>0.87</v>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.092</v>
+        <v>0.0951</v>
       </c>
       <c r="F60" t="n">
         <v>0.756</v>
@@ -8626,7 +8626,7 @@
         <v>0.864</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.673</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AE60" t="n">
         <v>0.793</v>
@@ -8662,7 +8662,7 @@
         <v>0.4</v>
       </c>
       <c r="AP60" t="n">
-        <v>0.131</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="61">
@@ -8762,7 +8762,7 @@
         <v>0.864</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.673</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AE61" t="n">
         <v>0.793</v>
@@ -9227,13 +9227,13 @@
         <v>0.728</v>
       </c>
       <c r="U2" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="V2" t="n">
-        <v>0.873</v>
+        <v>0.88</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0877</v>
+        <v>0.0825</v>
       </c>
       <c r="X2" t="n">
         <v>0.437</v>
@@ -9655,13 +9655,13 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="V4" t="n">
-        <v>0.822</v>
+        <v>0.832</v>
       </c>
       <c r="W4" t="n">
-        <v>0.233</v>
+        <v>0.225</v>
       </c>
       <c r="X4" t="n">
         <v>0.85</v>
@@ -9869,16 +9869,16 @@
         <v>0.989</v>
       </c>
       <c r="U5" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="V5" t="n">
-        <v>0.833</v>
+        <v>0.84</v>
       </c>
       <c r="W5" t="n">
-        <v>0.459</v>
+        <v>0.453</v>
       </c>
       <c r="X5" t="n">
-        <v>0.734</v>
+        <v>0.724</v>
       </c>
       <c r="Y5" t="n">
         <v>0.767</v>
@@ -10297,13 +10297,13 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="V7" t="n">
-        <v>0.772</v>
+        <v>0.782</v>
       </c>
       <c r="W7" t="n">
-        <v>0.743</v>
+        <v>0.739</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
@@ -10511,13 +10511,13 @@
         <v>0.888</v>
       </c>
       <c r="U8" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="W8" t="n">
-        <v>0.772</v>
+        <v>0.769</v>
       </c>
       <c r="X8" t="n">
         <v>0.888</v>
@@ -10728,10 +10728,10 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0.962</v>
+        <v>0.963</v>
       </c>
       <c r="W9" t="n">
-        <v>0.719</v>
+        <v>0.72</v>
       </c>
       <c r="X9" t="n">
         <v>1</v>
@@ -10939,10 +10939,10 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="V10" t="n">
-        <v>0.752</v>
+        <v>0.762</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
@@ -11153,13 +11153,13 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="W11" t="n">
-        <v>0.772</v>
+        <v>0.769</v>
       </c>
       <c r="X11" t="n">
         <v>1</v>
@@ -11581,10 +11581,10 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="V13" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
@@ -11795,13 +11795,13 @@
         <v>0.67</v>
       </c>
       <c r="U14" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0.885</v>
+        <v>0.884</v>
       </c>
       <c r="X14" t="n">
         <v>1</v>
@@ -12012,7 +12012,7 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>0.95</v>
+        <v>0.951</v>
       </c>
       <c r="W15" t="n">
         <v>1</v>
@@ -12223,10 +12223,10 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="V16" t="n">
-        <v>0.752</v>
+        <v>0.762</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
@@ -13040,7 +13040,7 @@
         <v>0.188</v>
       </c>
       <c r="H20" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="I20" t="n">
         <v>0.947</v>
@@ -13052,7 +13052,7 @@
         <v>0.785</v>
       </c>
       <c r="L20" t="n">
-        <v>0.88</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="M20" t="n">
         <v>0.92</v>
@@ -13064,7 +13064,7 @@
         <v>0.825</v>
       </c>
       <c r="P20" t="n">
-        <v>0.88</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="Q20" t="n">
         <v>0.98</v>
@@ -13082,13 +13082,13 @@
         <v>0.8</v>
       </c>
       <c r="V20" t="n">
-        <v>0.78</v>
+        <v>0.787</v>
       </c>
       <c r="W20" t="n">
-        <v>0.777</v>
+        <v>0.887</v>
       </c>
       <c r="X20" t="n">
-        <v>0.88</v>
+        <v>0.946</v>
       </c>
       <c r="Y20" t="n">
         <v>0.787</v>
@@ -13100,7 +13100,7 @@
         <v>0.232</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="AC20" t="n">
         <v>0.8129999999999999</v>
@@ -13112,7 +13112,7 @@
         <v>0.762</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.88</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="AG20" t="n">
         <v>0.9330000000000001</v>
@@ -13124,7 +13124,7 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.88</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="AK20" t="n">
         <v>0.673</v>
@@ -13148,7 +13148,7 @@
         <v>0.135</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="AS20" t="n">
         <v>0.793</v>
@@ -13160,7 +13160,7 @@
         <v>0.779</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.88</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="AW20" t="n">
         <v>0.833</v>
@@ -13172,7 +13172,7 @@
         <v>0.518</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.88</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="BA20" t="n">
         <v>0.973</v>
@@ -13184,7 +13184,7 @@
         <v>0.541</v>
       </c>
       <c r="BD20" t="n">
-        <v>0.88</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="BE20" t="n">
         <v>0.78</v>
@@ -13196,7 +13196,7 @@
         <v>0.5659999999999999</v>
       </c>
       <c r="BH20" t="n">
-        <v>0.88</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="BI20" t="n">
         <v>0.52</v>
@@ -13208,7 +13208,7 @@
         <v>0.419</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.88</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="BM20" t="n">
         <v>0.433</v>
@@ -13220,7 +13220,7 @@
         <v>0.411</v>
       </c>
       <c r="BP20" t="n">
-        <v>0.88</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -13296,10 +13296,10 @@
         <v>0.949</v>
       </c>
       <c r="V21" t="n">
-        <v>0.895</v>
+        <v>0.897</v>
       </c>
       <c r="W21" t="n">
-        <v>0.253</v>
+        <v>0.255</v>
       </c>
       <c r="X21" t="n">
         <v>1</v>
@@ -13510,10 +13510,10 @@
         <v>0.743</v>
       </c>
       <c r="V22" t="n">
-        <v>0.762</v>
+        <v>0.772</v>
       </c>
       <c r="W22" t="n">
-        <v>0.871</v>
+        <v>0.743</v>
       </c>
       <c r="X22" t="n">
         <v>1</v>
@@ -13724,10 +13724,10 @@
         <v>0.8</v>
       </c>
       <c r="V23" t="n">
-        <v>0.747</v>
+        <v>0.753</v>
       </c>
       <c r="W23" t="n">
-        <v>0.334</v>
+        <v>0.406</v>
       </c>
       <c r="X23" t="n">
         <v>0.78</v>
@@ -13938,10 +13938,10 @@
         <v>0.949</v>
       </c>
       <c r="V24" t="n">
-        <v>0.88</v>
+        <v>0.881</v>
       </c>
       <c r="W24" t="n">
-        <v>0.162</v>
+        <v>0.163</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
@@ -14152,10 +14152,10 @@
         <v>0.743</v>
       </c>
       <c r="V25" t="n">
-        <v>0.723</v>
+        <v>0.733</v>
       </c>
       <c r="W25" t="n">
-        <v>0.874</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
@@ -15008,10 +15008,10 @@
         <v>0.8</v>
       </c>
       <c r="V29" t="n">
-        <v>0.78</v>
+        <v>0.787</v>
       </c>
       <c r="W29" t="n">
-        <v>0.777</v>
+        <v>0.887</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
@@ -15225,7 +15225,7 @@
         <v>1</v>
       </c>
       <c r="W30" t="n">
-        <v>0.124</v>
+        <v>0.123</v>
       </c>
       <c r="X30" t="n">
         <v>0.248</v>
@@ -15436,13 +15436,13 @@
         <v>0.743</v>
       </c>
       <c r="V31" t="n">
-        <v>0.673</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="W31" t="n">
-        <v>0.353</v>
+        <v>0.437</v>
       </c>
       <c r="X31" t="n">
-        <v>0.707</v>
+        <v>0.794</v>
       </c>
       <c r="Y31" t="n">
         <v>0.761</v>
@@ -15514,7 +15514,7 @@
         <v>0.318</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.707</v>
+        <v>0.727</v>
       </c>
       <c r="AW31" t="n">
         <v>0.6889999999999999</v>

--- a/eval/learning-curve/results/statistical_tests_full150.xlsx
+++ b/eval/learning-curve/results/statistical_tests_full150.xlsx
@@ -503,22 +503,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0853</v>
+        <v>0.0552</v>
       </c>
       <c r="F2" t="n">
-        <v>0.823</v>
+        <v>0.831</v>
       </c>
       <c r="G2" t="n">
-        <v>0.85</v>
+        <v>0.862</v>
       </c>
       <c r="H2" t="n">
-        <v>0.111</v>
+        <v>0.109</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.0881</v>
       </c>
       <c r="J2" t="n">
-        <v>0.171</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="3">
@@ -543,22 +543,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.0926</v>
+        <v>0.0701</v>
       </c>
       <c r="F3" t="n">
-        <v>0.823</v>
+        <v>0.831</v>
       </c>
       <c r="G3" t="n">
-        <v>0.85</v>
+        <v>0.862</v>
       </c>
       <c r="H3" t="n">
-        <v>0.111</v>
+        <v>0.109</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.0881</v>
       </c>
       <c r="J3" t="n">
-        <v>0.232</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="4">
@@ -583,22 +583,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.219</v>
+        <v>0.162</v>
       </c>
       <c r="F4" t="n">
-        <v>0.823</v>
+        <v>0.831</v>
       </c>
       <c r="G4" t="n">
-        <v>0.844</v>
+        <v>0.855</v>
       </c>
       <c r="H4" t="n">
-        <v>0.111</v>
+        <v>0.109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0835</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.274</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="5">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.278</v>
+        <v>0.201</v>
       </c>
       <c r="F5" t="n">
-        <v>0.823</v>
+        <v>0.831</v>
       </c>
       <c r="G5" t="n">
-        <v>0.844</v>
+        <v>0.855</v>
       </c>
       <c r="H5" t="n">
-        <v>0.111</v>
+        <v>0.109</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0835</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.334</v>
+        <v>0.304</v>
       </c>
     </row>
     <row r="6">
@@ -666,19 +666,19 @@
         <v>0.26</v>
       </c>
       <c r="F6" t="n">
-        <v>0.823</v>
+        <v>0.831</v>
       </c>
       <c r="G6" t="n">
-        <v>0.84</v>
+        <v>0.848</v>
       </c>
       <c r="H6" t="n">
-        <v>0.111</v>
+        <v>0.109</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0958</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.289</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="7">
@@ -703,22 +703,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.365</v>
+        <v>0.334</v>
       </c>
       <c r="F7" t="n">
-        <v>0.823</v>
+        <v>0.831</v>
       </c>
       <c r="G7" t="n">
-        <v>0.84</v>
+        <v>0.848</v>
       </c>
       <c r="H7" t="n">
-        <v>0.111</v>
+        <v>0.109</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0958</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.365</v>
+        <v>0.334</v>
       </c>
     </row>
     <row r="8">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.0808</v>
+        <v>0.0281</v>
       </c>
       <c r="F8" t="n">
-        <v>0.823</v>
+        <v>0.831</v>
       </c>
       <c r="G8" t="n">
-        <v>0.853</v>
+        <v>0.869</v>
       </c>
       <c r="H8" t="n">
-        <v>0.111</v>
+        <v>0.109</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.0709</v>
       </c>
       <c r="J8" t="n">
-        <v>0.171</v>
+        <v>0.09370000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.117</v>
+        <v>0.0689</v>
       </c>
       <c r="F9" t="n">
-        <v>0.823</v>
+        <v>0.831</v>
       </c>
       <c r="G9" t="n">
-        <v>0.853</v>
+        <v>0.869</v>
       </c>
       <c r="H9" t="n">
-        <v>0.111</v>
+        <v>0.109</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.0709</v>
       </c>
       <c r="J9" t="n">
-        <v>0.234</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="10">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.00037</v>
+        <v>0.000781</v>
       </c>
       <c r="F10" t="n">
-        <v>0.823</v>
+        <v>0.831</v>
       </c>
       <c r="G10" t="n">
-        <v>0.893</v>
+        <v>0.898</v>
       </c>
       <c r="H10" t="n">
-        <v>0.111</v>
+        <v>0.109</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0687</v>
+        <v>0.0654</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0037</v>
+        <v>0.00781</v>
       </c>
     </row>
     <row r="11">
@@ -863,22 +863,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.000973</v>
+        <v>0.0009790000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.823</v>
+        <v>0.831</v>
       </c>
       <c r="G11" t="n">
-        <v>0.893</v>
+        <v>0.898</v>
       </c>
       <c r="H11" t="n">
-        <v>0.111</v>
+        <v>0.109</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0687</v>
+        <v>0.0654</v>
       </c>
       <c r="J11" t="n">
-        <v>0.009350000000000001</v>
+        <v>0.00979</v>
       </c>
     </row>
     <row r="12">
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.0249</v>
+        <v>0.0493</v>
       </c>
       <c r="F12" t="n">
-        <v>0.796</v>
+        <v>0.801</v>
       </c>
       <c r="G12" t="n">
-        <v>0.821</v>
+        <v>0.823</v>
       </c>
       <c r="H12" t="n">
-        <v>0.152</v>
+        <v>0.148</v>
       </c>
       <c r="I12" t="n">
-        <v>0.16</v>
+        <v>0.161</v>
       </c>
       <c r="J12" t="n">
-        <v>0.083</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="13">
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.0466</v>
+        <v>0.0495</v>
       </c>
       <c r="F13" t="n">
-        <v>0.796</v>
+        <v>0.801</v>
       </c>
       <c r="G13" t="n">
-        <v>0.821</v>
+        <v>0.823</v>
       </c>
       <c r="H13" t="n">
-        <v>0.152</v>
+        <v>0.148</v>
       </c>
       <c r="I13" t="n">
-        <v>0.16</v>
+        <v>0.161</v>
       </c>
       <c r="J13" t="n">
-        <v>0.155</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="14">
@@ -983,22 +983,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.134</v>
+        <v>0.218</v>
       </c>
       <c r="F14" t="n">
-        <v>0.796</v>
+        <v>0.801</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>0.152</v>
+        <v>0.148</v>
       </c>
       <c r="I14" t="n">
         <v>0.168</v>
       </c>
       <c r="J14" t="n">
-        <v>0.223</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="15">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.17</v>
+        <v>0.213</v>
       </c>
       <c r="F15" t="n">
-        <v>0.796</v>
+        <v>0.801</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>0.152</v>
+        <v>0.148</v>
       </c>
       <c r="I15" t="n">
         <v>0.168</v>
       </c>
       <c r="J15" t="n">
-        <v>0.283</v>
+        <v>0.304</v>
       </c>
     </row>
     <row r="16">
@@ -1063,22 +1063,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.214</v>
+        <v>0.302</v>
       </c>
       <c r="F16" t="n">
-        <v>0.796</v>
+        <v>0.801</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.152</v>
+        <v>0.148</v>
       </c>
       <c r="I16" t="n">
         <v>0.17</v>
       </c>
       <c r="J16" t="n">
-        <v>0.274</v>
+        <v>0.336</v>
       </c>
     </row>
     <row r="17">
@@ -1103,16 +1103,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.286</v>
+        <v>0.3</v>
       </c>
       <c r="F17" t="n">
-        <v>0.796</v>
+        <v>0.801</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.152</v>
+        <v>0.148</v>
       </c>
       <c r="I17" t="n">
         <v>0.17</v>
@@ -1143,22 +1143,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.326</v>
+        <v>0.418</v>
       </c>
       <c r="F18" t="n">
-        <v>0.796</v>
+        <v>0.801</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.152</v>
+        <v>0.148</v>
       </c>
       <c r="I18" t="n">
-        <v>0.183</v>
+        <v>0.184</v>
       </c>
       <c r="J18" t="n">
-        <v>0.326</v>
+        <v>0.418</v>
       </c>
     </row>
     <row r="19">
@@ -1183,19 +1183,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.301</v>
+        <v>0.325</v>
       </c>
       <c r="F19" t="n">
-        <v>0.796</v>
+        <v>0.801</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.152</v>
+        <v>0.148</v>
       </c>
       <c r="I19" t="n">
-        <v>0.183</v>
+        <v>0.184</v>
       </c>
       <c r="J19" t="n">
         <v>0.334</v>
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0145</v>
+        <v>0.0137</v>
       </c>
       <c r="F20" t="n">
-        <v>0.796</v>
+        <v>0.801</v>
       </c>
       <c r="G20" t="n">
-        <v>0.849</v>
+        <v>0.851</v>
       </c>
       <c r="H20" t="n">
-        <v>0.152</v>
+        <v>0.148</v>
       </c>
       <c r="I20" t="n">
         <v>0.0917</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0725</v>
+        <v>0.06850000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1263,22 +1263,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.00187</v>
+        <v>0.0023</v>
       </c>
       <c r="F21" t="n">
-        <v>0.796</v>
+        <v>0.801</v>
       </c>
       <c r="G21" t="n">
-        <v>0.849</v>
+        <v>0.851</v>
       </c>
       <c r="H21" t="n">
-        <v>0.152</v>
+        <v>0.148</v>
       </c>
       <c r="I21" t="n">
         <v>0.0917</v>
       </c>
       <c r="J21" t="n">
-        <v>0.009350000000000001</v>
+        <v>0.0115</v>
       </c>
     </row>
     <row r="22">
@@ -1303,22 +1303,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.852</v>
       </c>
       <c r="F22" t="n">
-        <v>0.833</v>
+        <v>0.843</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.836</v>
       </c>
       <c r="H22" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="I22" t="n">
-        <v>0.142</v>
+        <v>0.134</v>
       </c>
       <c r="J22" t="n">
-        <v>0.886</v>
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1343,22 +1343,22 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.274</v>
+        <v>0.597</v>
       </c>
       <c r="F23" t="n">
-        <v>0.833</v>
+        <v>0.843</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.836</v>
       </c>
       <c r="H23" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.142</v>
+        <v>0.134</v>
       </c>
       <c r="J23" t="n">
-        <v>0.803</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1383,22 +1383,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.794</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.833</v>
+        <v>0.843</v>
       </c>
       <c r="G24" t="n">
-        <v>0.822</v>
+        <v>0.84</v>
       </c>
       <c r="H24" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="I24" t="n">
-        <v>0.142</v>
+        <v>0.137</v>
       </c>
       <c r="J24" t="n">
-        <v>0.886</v>
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.528</v>
+        <v>0.632</v>
       </c>
       <c r="F25" t="n">
-        <v>0.833</v>
+        <v>0.843</v>
       </c>
       <c r="G25" t="n">
-        <v>0.822</v>
+        <v>0.84</v>
       </c>
       <c r="H25" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="I25" t="n">
-        <v>0.142</v>
+        <v>0.137</v>
       </c>
       <c r="J25" t="n">
-        <v>0.803</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1463,22 +1463,22 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.398</v>
+        <v>0.38</v>
       </c>
       <c r="F26" t="n">
-        <v>0.833</v>
+        <v>0.843</v>
       </c>
       <c r="G26" t="n">
-        <v>0.857</v>
+        <v>0.867</v>
       </c>
       <c r="H26" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="I26" t="n">
-        <v>0.114</v>
+        <v>0.116</v>
       </c>
       <c r="J26" t="n">
-        <v>0.886</v>
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1503,22 +1503,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.821</v>
+        <v>0.632</v>
       </c>
       <c r="F27" t="n">
-        <v>0.833</v>
+        <v>0.843</v>
       </c>
       <c r="G27" t="n">
-        <v>0.857</v>
+        <v>0.867</v>
       </c>
       <c r="H27" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.114</v>
+        <v>0.116</v>
       </c>
       <c r="J27" t="n">
-        <v>0.821</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1543,22 +1543,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.886</v>
+        <v>0.711</v>
       </c>
       <c r="F28" t="n">
-        <v>0.833</v>
+        <v>0.843</v>
       </c>
       <c r="G28" t="n">
-        <v>0.828</v>
+        <v>0.854</v>
       </c>
       <c r="H28" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="I28" t="n">
-        <v>0.114</v>
+        <v>0.104</v>
       </c>
       <c r="J28" t="n">
-        <v>0.886</v>
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1583,22 +1583,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.532</v>
+        <v>0.91</v>
       </c>
       <c r="F29" t="n">
-        <v>0.833</v>
+        <v>0.843</v>
       </c>
       <c r="G29" t="n">
-        <v>0.828</v>
+        <v>0.854</v>
       </c>
       <c r="H29" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="I29" t="n">
-        <v>0.114</v>
+        <v>0.104</v>
       </c>
       <c r="J29" t="n">
-        <v>0.803</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="30">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.0401</v>
+        <v>0.0588</v>
       </c>
       <c r="F30" t="n">
-        <v>0.833</v>
+        <v>0.843</v>
       </c>
       <c r="G30" t="n">
-        <v>0.902</v>
+        <v>0.907</v>
       </c>
       <c r="H30" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="I30" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2</v>
+        <v>0.294</v>
       </c>
     </row>
     <row r="31">
@@ -1663,22 +1663,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.0535</v>
+        <v>0.112</v>
       </c>
       <c r="F31" t="n">
-        <v>0.833</v>
+        <v>0.843</v>
       </c>
       <c r="G31" t="n">
-        <v>0.902</v>
+        <v>0.907</v>
       </c>
       <c r="H31" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="I31" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>0.268</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1703,22 +1703,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.344</v>
+        <v>0.471</v>
       </c>
       <c r="F32" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="G32" t="n">
-        <v>0.8</v>
+        <v>0.801</v>
       </c>
       <c r="H32" t="n">
-        <v>0.204</v>
+        <v>0.202</v>
       </c>
       <c r="I32" t="n">
         <v>0.194</v>
       </c>
       <c r="J32" t="n">
-        <v>0.886</v>
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1743,22 +1743,22 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.394</v>
+        <v>0.46</v>
       </c>
       <c r="F33" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8</v>
+        <v>0.801</v>
       </c>
       <c r="H33" t="n">
-        <v>0.204</v>
+        <v>0.202</v>
       </c>
       <c r="I33" t="n">
         <v>0.194</v>
       </c>
       <c r="J33" t="n">
-        <v>0.803</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1783,22 +1783,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.892</v>
       </c>
       <c r="F34" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="G34" t="n">
         <v>0.796</v>
       </c>
       <c r="H34" t="n">
-        <v>0.204</v>
+        <v>0.202</v>
       </c>
       <c r="I34" t="n">
         <v>0.179</v>
       </c>
       <c r="J34" t="n">
-        <v>0.886</v>
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1823,22 +1823,22 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.782</v>
+        <v>0.744</v>
       </c>
       <c r="F35" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="G35" t="n">
         <v>0.796</v>
       </c>
       <c r="H35" t="n">
-        <v>0.204</v>
+        <v>0.202</v>
       </c>
       <c r="I35" t="n">
         <v>0.179</v>
       </c>
       <c r="J35" t="n">
-        <v>0.821</v>
+        <v>0.827</v>
       </c>
     </row>
     <row r="36">
@@ -1863,22 +1863,22 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.68</v>
+        <v>0.758</v>
       </c>
       <c r="F36" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="G36" t="n">
-        <v>0.798</v>
+        <v>0.799</v>
       </c>
       <c r="H36" t="n">
-        <v>0.204</v>
+        <v>0.202</v>
       </c>
       <c r="I36" t="n">
         <v>0.187</v>
       </c>
       <c r="J36" t="n">
-        <v>0.886</v>
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1903,22 +1903,22 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="F37" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="G37" t="n">
-        <v>0.798</v>
+        <v>0.799</v>
       </c>
       <c r="H37" t="n">
-        <v>0.204</v>
+        <v>0.202</v>
       </c>
       <c r="I37" t="n">
         <v>0.187</v>
       </c>
       <c r="J37" t="n">
-        <v>0.821</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.663</v>
+        <v>0.738</v>
       </c>
       <c r="F38" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="G38" t="n">
-        <v>0.799</v>
+        <v>0.8</v>
       </c>
       <c r="H38" t="n">
-        <v>0.204</v>
+        <v>0.202</v>
       </c>
       <c r="I38" t="n">
-        <v>0.191</v>
+        <v>0.192</v>
       </c>
       <c r="J38" t="n">
-        <v>0.886</v>
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -1983,22 +1983,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.597</v>
       </c>
       <c r="F39" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="G39" t="n">
-        <v>0.799</v>
+        <v>0.8</v>
       </c>
       <c r="H39" t="n">
-        <v>0.204</v>
+        <v>0.202</v>
       </c>
       <c r="I39" t="n">
-        <v>0.191</v>
+        <v>0.192</v>
       </c>
       <c r="J39" t="n">
-        <v>0.803</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -2023,22 +2023,22 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.000685</v>
+        <v>0.00072</v>
       </c>
       <c r="F40" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="G40" t="n">
         <v>0.912</v>
       </c>
       <c r="H40" t="n">
-        <v>0.204</v>
+        <v>0.202</v>
       </c>
       <c r="I40" t="n">
         <v>0.103</v>
       </c>
       <c r="J40" t="n">
-        <v>0.00685</v>
+        <v>0.0072</v>
       </c>
     </row>
     <row r="41">
@@ -2066,13 +2066,13 @@
         <v>0.000987</v>
       </c>
       <c r="F41" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="G41" t="n">
         <v>0.912</v>
       </c>
       <c r="H41" t="n">
-        <v>0.204</v>
+        <v>0.202</v>
       </c>
       <c r="I41" t="n">
         <v>0.103</v>
@@ -2103,22 +2103,22 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.131</v>
+        <v>0.18</v>
       </c>
       <c r="F42" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G42" t="n">
-        <v>0.801</v>
+        <v>0.805</v>
       </c>
       <c r="H42" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="I42" t="n">
-        <v>0.172</v>
+        <v>0.169</v>
       </c>
       <c r="J42" t="n">
-        <v>0.164</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="43">
@@ -2143,22 +2143,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.0546</v>
+        <v>0.133</v>
       </c>
       <c r="F43" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G43" t="n">
-        <v>0.801</v>
+        <v>0.805</v>
       </c>
       <c r="H43" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="I43" t="n">
-        <v>0.172</v>
+        <v>0.169</v>
       </c>
       <c r="J43" t="n">
-        <v>0.091</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="44">
@@ -2183,22 +2183,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.626</v>
+        <v>0.728</v>
       </c>
       <c r="F44" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G44" t="n">
-        <v>0.775</v>
+        <v>0.779</v>
       </c>
       <c r="H44" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="I44" t="n">
-        <v>0.133</v>
+        <v>0.131</v>
       </c>
       <c r="J44" t="n">
-        <v>0.696</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -2223,22 +2223,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="F45" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G45" t="n">
-        <v>0.775</v>
+        <v>0.779</v>
       </c>
       <c r="H45" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="I45" t="n">
-        <v>0.133</v>
+        <v>0.131</v>
       </c>
       <c r="J45" t="n">
-        <v>0.911</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="46">
@@ -2263,22 +2263,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.79</v>
+        <v>0.882</v>
       </c>
       <c r="F46" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G46" t="n">
-        <v>0.77</v>
+        <v>0.774</v>
       </c>
       <c r="H46" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="I46" t="n">
-        <v>0.126</v>
+        <v>0.124</v>
       </c>
       <c r="J46" t="n">
-        <v>0.79</v>
+        <v>0.882</v>
       </c>
     </row>
     <row r="47">
@@ -2303,22 +2303,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.897</v>
       </c>
       <c r="F47" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G47" t="n">
-        <v>0.77</v>
+        <v>0.774</v>
       </c>
       <c r="H47" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="I47" t="n">
-        <v>0.126</v>
+        <v>0.124</v>
       </c>
       <c r="J47" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="48">
@@ -2343,22 +2343,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.0828</v>
+        <v>0.123</v>
       </c>
       <c r="F48" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G48" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="I48" t="n">
-        <v>0.13</v>
+        <v>0.127</v>
       </c>
       <c r="J48" t="n">
-        <v>0.13</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="49">
@@ -2383,22 +2383,22 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.0844</v>
+        <v>0.116</v>
       </c>
       <c r="F49" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G49" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="I49" t="n">
-        <v>0.13</v>
+        <v>0.127</v>
       </c>
       <c r="J49" t="n">
-        <v>0.121</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="50">
@@ -2423,22 +2423,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.00988</v>
+        <v>0.0138</v>
       </c>
       <c r="F50" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G50" t="n">
-        <v>0.842</v>
+        <v>0.848</v>
       </c>
       <c r="H50" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="I50" t="n">
-        <v>0.128</v>
+        <v>0.127</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0329</v>
+        <v>0.0407</v>
       </c>
     </row>
     <row r="51">
@@ -2463,22 +2463,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.0132</v>
+        <v>0.0186</v>
       </c>
       <c r="F51" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G51" t="n">
-        <v>0.842</v>
+        <v>0.848</v>
       </c>
       <c r="H51" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="I51" t="n">
-        <v>0.128</v>
+        <v>0.127</v>
       </c>
       <c r="J51" t="n">
-        <v>0.044</v>
+        <v>0.0465</v>
       </c>
     </row>
     <row r="52">
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.0224</v>
+        <v>0.0253</v>
       </c>
       <c r="F52" t="n">
-        <v>0.756</v>
+        <v>0.762</v>
       </c>
       <c r="G52" t="n">
-        <v>0.8</v>
+        <v>0.804</v>
       </c>
       <c r="H52" t="n">
-        <v>0.182</v>
+        <v>0.178</v>
       </c>
       <c r="I52" t="n">
-        <v>0.174</v>
+        <v>0.173</v>
       </c>
       <c r="J52" t="n">
-        <v>0.0448</v>
+        <v>0.0506</v>
       </c>
     </row>
     <row r="53">
@@ -2543,22 +2543,22 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.0303</v>
+        <v>0.0356</v>
       </c>
       <c r="F53" t="n">
-        <v>0.756</v>
+        <v>0.762</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8</v>
+        <v>0.804</v>
       </c>
       <c r="H53" t="n">
-        <v>0.182</v>
+        <v>0.178</v>
       </c>
       <c r="I53" t="n">
-        <v>0.174</v>
+        <v>0.173</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0606</v>
+        <v>0.0712</v>
       </c>
     </row>
     <row r="54">
@@ -2583,22 +2583,22 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.00251</v>
+        <v>0.00231</v>
       </c>
       <c r="F54" t="n">
-        <v>0.756</v>
+        <v>0.762</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="H54" t="n">
-        <v>0.182</v>
+        <v>0.178</v>
       </c>
       <c r="I54" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0251</v>
+        <v>0.0231</v>
       </c>
     </row>
     <row r="55">
@@ -2623,22 +2623,22 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.00429</v>
+        <v>0.00521</v>
       </c>
       <c r="F55" t="n">
-        <v>0.756</v>
+        <v>0.762</v>
       </c>
       <c r="G55" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="H55" t="n">
-        <v>0.182</v>
+        <v>0.178</v>
       </c>
       <c r="I55" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="J55" t="n">
-        <v>0.0429</v>
+        <v>0.0314</v>
       </c>
     </row>
     <row r="56">
@@ -2663,22 +2663,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.0153</v>
+        <v>0.0163</v>
       </c>
       <c r="F56" t="n">
-        <v>0.756</v>
+        <v>0.762</v>
       </c>
       <c r="G56" t="n">
-        <v>0.805</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="H56" t="n">
-        <v>0.182</v>
+        <v>0.178</v>
       </c>
       <c r="I56" t="n">
-        <v>0.15</v>
+        <v>0.149</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0382</v>
+        <v>0.0407</v>
       </c>
     </row>
     <row r="57">
@@ -2703,22 +2703,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.0231</v>
+        <v>0.0182</v>
       </c>
       <c r="F57" t="n">
-        <v>0.756</v>
+        <v>0.762</v>
       </c>
       <c r="G57" t="n">
-        <v>0.805</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>0.182</v>
+        <v>0.178</v>
       </c>
       <c r="I57" t="n">
-        <v>0.15</v>
+        <v>0.149</v>
       </c>
       <c r="J57" t="n">
-        <v>0.0577</v>
+        <v>0.0465</v>
       </c>
     </row>
     <row r="58">
@@ -2743,22 +2743,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.00899</v>
+        <v>0.00933</v>
       </c>
       <c r="F58" t="n">
-        <v>0.756</v>
+        <v>0.762</v>
       </c>
       <c r="G58" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>0.182</v>
+        <v>0.178</v>
       </c>
       <c r="I58" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="J58" t="n">
-        <v>0.0329</v>
+        <v>0.0407</v>
       </c>
     </row>
     <row r="59">
@@ -2783,22 +2783,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.0125</v>
+        <v>0.00629</v>
       </c>
       <c r="F59" t="n">
-        <v>0.756</v>
+        <v>0.762</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>0.182</v>
+        <v>0.178</v>
       </c>
       <c r="I59" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="J59" t="n">
-        <v>0.044</v>
+        <v>0.0314</v>
       </c>
     </row>
     <row r="60">
@@ -2823,22 +2823,22 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.0912</v>
+        <v>0.0853</v>
       </c>
       <c r="F60" t="n">
-        <v>0.756</v>
+        <v>0.762</v>
       </c>
       <c r="G60" t="n">
-        <v>0.697</v>
+        <v>0.701</v>
       </c>
       <c r="H60" t="n">
-        <v>0.182</v>
+        <v>0.178</v>
       </c>
       <c r="I60" t="n">
-        <v>0.158</v>
+        <v>0.159</v>
       </c>
       <c r="J60" t="n">
-        <v>0.13</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="61">
@@ -2863,22 +2863,22 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.156</v>
+        <v>0.14</v>
       </c>
       <c r="F61" t="n">
-        <v>0.756</v>
+        <v>0.762</v>
       </c>
       <c r="G61" t="n">
-        <v>0.697</v>
+        <v>0.701</v>
       </c>
       <c r="H61" t="n">
-        <v>0.182</v>
+        <v>0.178</v>
       </c>
       <c r="I61" t="n">
-        <v>0.158</v>
+        <v>0.159</v>
       </c>
       <c r="J61" t="n">
-        <v>0.195</v>
+        <v>0.175</v>
       </c>
     </row>
   </sheetData>
@@ -3078,16 +3078,16 @@
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.947</v>
       </c>
       <c r="G5" t="n">
-        <v>0.907</v>
+        <v>0.927</v>
       </c>
       <c r="H5" t="n">
-        <v>0.524</v>
+        <v>0.637</v>
       </c>
       <c r="I5" t="n">
-        <v>0.771</v>
+        <v>0.783</v>
       </c>
     </row>
     <row r="6">
@@ -3152,16 +3152,16 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.767</v>
+        <v>0.793</v>
       </c>
       <c r="G7" t="n">
-        <v>0.873</v>
+        <v>0.887</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0236</v>
+        <v>0.0398</v>
       </c>
       <c r="I7" t="n">
-        <v>0.189</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="8">
@@ -3189,16 +3189,16 @@
         <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>0.827</v>
+        <v>0.847</v>
       </c>
       <c r="G8" t="n">
-        <v>0.853</v>
+        <v>0.887</v>
       </c>
       <c r="H8" t="n">
-        <v>0.637</v>
+        <v>0.396</v>
       </c>
       <c r="I8" t="n">
-        <v>0.771</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="9">
@@ -3235,7 +3235,7 @@
         <v>0.572</v>
       </c>
       <c r="I9" t="n">
-        <v>0.771</v>
+        <v>0.783</v>
       </c>
     </row>
     <row r="10">
@@ -3266,13 +3266,13 @@
         <v>0.6870000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.713</v>
+        <v>0.707</v>
       </c>
       <c r="H10" t="n">
-        <v>0.706</v>
+        <v>0.802</v>
       </c>
       <c r="I10" t="n">
-        <v>0.771</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="11">
@@ -3300,16 +3300,16 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8</v>
+        <v>0.847</v>
       </c>
       <c r="G11" t="n">
-        <v>0.74</v>
+        <v>0.793</v>
       </c>
       <c r="H11" t="n">
-        <v>0.272</v>
+        <v>0.293</v>
       </c>
       <c r="I11" t="n">
-        <v>0.622</v>
+        <v>0.521</v>
       </c>
     </row>
     <row r="12">
@@ -3337,16 +3337,16 @@
         <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.707</v>
       </c>
       <c r="G12" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="H12" t="n">
-        <v>0.244</v>
+        <v>0.186</v>
       </c>
       <c r="I12" t="n">
-        <v>0.622</v>
+        <v>0.496</v>
       </c>
     </row>
     <row r="13">
@@ -3420,7 +3420,7 @@
         <v>0.723</v>
       </c>
       <c r="I14" t="n">
-        <v>0.771</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="15">
@@ -3457,7 +3457,7 @@
         <v>0.618</v>
       </c>
       <c r="I15" t="n">
-        <v>0.771</v>
+        <v>0.783</v>
       </c>
     </row>
     <row r="16">
@@ -3485,16 +3485,16 @@
         <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>0.673</v>
+        <v>0.68</v>
       </c>
       <c r="G16" t="n">
-        <v>0.727</v>
+        <v>0.747</v>
       </c>
       <c r="H16" t="n">
-        <v>0.378</v>
+        <v>0.25</v>
       </c>
       <c r="I16" t="n">
-        <v>0.756</v>
+        <v>0.501</v>
       </c>
     </row>
     <row r="17">
@@ -3522,16 +3522,16 @@
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>0.633</v>
+        <v>0.64</v>
       </c>
       <c r="G17" t="n">
-        <v>0.68</v>
+        <v>0.713</v>
       </c>
       <c r="H17" t="n">
-        <v>0.466</v>
+        <v>0.217</v>
       </c>
       <c r="I17" t="n">
-        <v>0.771</v>
+        <v>0.496</v>
       </c>
     </row>
     <row r="18">
@@ -3568,7 +3568,7 @@
         <v>0.213</v>
       </c>
       <c r="I18" t="n">
-        <v>0.679</v>
+        <v>0.681</v>
       </c>
     </row>
     <row r="19">
@@ -3670,16 +3670,16 @@
         <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="G21" t="n">
-        <v>0.618</v>
+        <v>0.677</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6</v>
+        <v>0.578</v>
       </c>
       <c r="I21" t="n">
-        <v>0.801</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="22">
@@ -3744,16 +3744,16 @@
         <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>0.925</v>
+        <v>0.969</v>
       </c>
       <c r="G23" t="n">
-        <v>0.91</v>
+        <v>0.931</v>
       </c>
       <c r="H23" t="n">
-        <v>0.779</v>
+        <v>0.467</v>
       </c>
       <c r="I23" t="n">
-        <v>0.837</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="24">
@@ -3781,16 +3781,16 @@
         <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>0.904</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>0.862</v>
+        <v>0.915</v>
       </c>
       <c r="H24" t="n">
-        <v>0.469</v>
+        <v>0.548</v>
       </c>
       <c r="I24" t="n">
-        <v>0.801</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="25">
@@ -3827,7 +3827,7 @@
         <v>0.545</v>
       </c>
       <c r="I25" t="n">
-        <v>0.801</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="26">
@@ -3892,16 +3892,16 @@
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>0.903</v>
+        <v>0.913</v>
       </c>
       <c r="G27" t="n">
-        <v>0.825</v>
+        <v>0.902</v>
       </c>
       <c r="H27" t="n">
-        <v>0.297</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0.679</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -3929,16 +3929,16 @@
         <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>0.869</v>
+        <v>0.873</v>
       </c>
       <c r="G28" t="n">
-        <v>0.899</v>
+        <v>0.914</v>
       </c>
       <c r="H28" t="n">
-        <v>0.784</v>
+        <v>0.574</v>
       </c>
       <c r="I28" t="n">
-        <v>0.837</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="29">
@@ -3975,7 +3975,7 @@
         <v>0.285</v>
       </c>
       <c r="I29" t="n">
-        <v>0.679</v>
+        <v>0.698</v>
       </c>
     </row>
     <row r="30">
@@ -4012,7 +4012,7 @@
         <v>0.704</v>
       </c>
       <c r="I30" t="n">
-        <v>0.837</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="31">
@@ -4077,16 +4077,16 @@
         <v>15</v>
       </c>
       <c r="F32" t="n">
-        <v>0.61</v>
+        <v>0.617</v>
       </c>
       <c r="G32" t="n">
-        <v>0.676</v>
+        <v>0.704</v>
       </c>
       <c r="H32" t="n">
-        <v>0.409</v>
+        <v>0.305</v>
       </c>
       <c r="I32" t="n">
-        <v>0.801</v>
+        <v>0.698</v>
       </c>
     </row>
     <row r="33">
@@ -4114,16 +4114,16 @@
         <v>16</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5</v>
+        <v>0.509</v>
       </c>
       <c r="G33" t="n">
-        <v>0.552</v>
+        <v>0.594</v>
       </c>
       <c r="H33" t="n">
-        <v>0.593</v>
+        <v>0.366</v>
       </c>
       <c r="I33" t="n">
-        <v>0.801</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="34">
@@ -4160,7 +4160,7 @@
         <v>0.515</v>
       </c>
       <c r="I34" t="n">
-        <v>0.85</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="35">
@@ -4234,7 +4234,7 @@
         <v>0.491</v>
       </c>
       <c r="I36" t="n">
-        <v>0.85</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="37">
@@ -4308,7 +4308,7 @@
         <v>0.225</v>
       </c>
       <c r="I38" t="n">
-        <v>0.719</v>
+        <v>0.599</v>
       </c>
     </row>
     <row r="39">
@@ -4336,16 +4336,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.674</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G39" t="n">
         <v>0.88</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00125</v>
+        <v>0.00212</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0199</v>
+        <v>0.0339</v>
       </c>
     </row>
     <row r="40">
@@ -4382,7 +4382,7 @@
         <v>0.102</v>
       </c>
       <c r="I40" t="n">
-        <v>0.719</v>
+        <v>0.599</v>
       </c>
     </row>
     <row r="41">
@@ -4419,7 +4419,7 @@
         <v>0.637</v>
       </c>
       <c r="I41" t="n">
-        <v>0.85</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="42">
@@ -4450,13 +4450,13 @@
         <v>0.635</v>
       </c>
       <c r="G42" t="n">
-        <v>0.675</v>
+        <v>0.667</v>
       </c>
       <c r="H42" t="n">
-        <v>0.596</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>0.85</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="43">
@@ -4484,16 +4484,16 @@
         <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7</v>
+        <v>0.787</v>
       </c>
       <c r="G43" t="n">
-        <v>0.65</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>0.613</v>
+        <v>0.208</v>
       </c>
       <c r="I43" t="n">
-        <v>0.85</v>
+        <v>0.599</v>
       </c>
     </row>
     <row r="44">
@@ -4521,16 +4521,16 @@
         <v>11</v>
       </c>
       <c r="F44" t="n">
-        <v>0.582</v>
+        <v>0.604</v>
       </c>
       <c r="G44" t="n">
-        <v>0.681</v>
+        <v>0.703</v>
       </c>
       <c r="H44" t="n">
-        <v>0.219</v>
+        <v>0.212</v>
       </c>
       <c r="I44" t="n">
-        <v>0.719</v>
+        <v>0.599</v>
       </c>
     </row>
     <row r="45">
@@ -4567,7 +4567,7 @@
         <v>0.383</v>
       </c>
       <c r="I45" t="n">
-        <v>0.85</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="46">
@@ -4641,7 +4641,7 @@
         <v>0.539</v>
       </c>
       <c r="I47" t="n">
-        <v>0.85</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="48">
@@ -4709,13 +4709,13 @@
         <v>0.527</v>
       </c>
       <c r="G49" t="n">
-        <v>0.673</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>0.173</v>
+        <v>0.118</v>
       </c>
       <c r="I49" t="n">
-        <v>0.719</v>
+        <v>0.599</v>
       </c>
     </row>
     <row r="50">
@@ -4854,16 +4854,16 @@
         <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.947</v>
       </c>
       <c r="G53" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>0.825</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.989</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -4928,16 +4928,16 @@
         <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>0.767</v>
+        <v>0.793</v>
       </c>
       <c r="G55" t="n">
-        <v>0.867</v>
+        <v>0.887</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0361</v>
+        <v>0.0398</v>
       </c>
       <c r="I55" t="n">
-        <v>0.192</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="56">
@@ -4965,16 +4965,16 @@
         <v>7</v>
       </c>
       <c r="F56" t="n">
-        <v>0.827</v>
+        <v>0.847</v>
       </c>
       <c r="G56" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0.871</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="57">
@@ -5048,7 +5048,7 @@
         <v>0.197</v>
       </c>
       <c r="I58" t="n">
-        <v>0.439</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="59">
@@ -5076,16 +5076,16 @@
         <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8</v>
+        <v>0.847</v>
       </c>
       <c r="G59" t="n">
-        <v>0.727</v>
+        <v>0.78</v>
       </c>
       <c r="H59" t="n">
-        <v>0.174</v>
+        <v>0.182</v>
       </c>
       <c r="I59" t="n">
-        <v>0.439</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="60">
@@ -5113,16 +5113,16 @@
         <v>11</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.707</v>
       </c>
       <c r="G60" t="n">
-        <v>0.78</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>0.115</v>
+        <v>0.0592</v>
       </c>
       <c r="I60" t="n">
-        <v>0.439</v>
+        <v>0.237</v>
       </c>
     </row>
     <row r="61">
@@ -5233,7 +5233,7 @@
         <v>0.865</v>
       </c>
       <c r="I63" t="n">
-        <v>0.989</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="64">
@@ -5261,16 +5261,16 @@
         <v>15</v>
       </c>
       <c r="F64" t="n">
-        <v>0.673</v>
+        <v>0.68</v>
       </c>
       <c r="G64" t="n">
         <v>0.747</v>
       </c>
       <c r="H64" t="n">
-        <v>0.203</v>
+        <v>0.25</v>
       </c>
       <c r="I64" t="n">
-        <v>0.439</v>
+        <v>0.501</v>
       </c>
     </row>
     <row r="65">
@@ -5298,16 +5298,16 @@
         <v>16</v>
       </c>
       <c r="F65" t="n">
-        <v>0.633</v>
+        <v>0.64</v>
       </c>
       <c r="G65" t="n">
-        <v>0.707</v>
+        <v>0.727</v>
       </c>
       <c r="H65" t="n">
-        <v>0.219</v>
+        <v>0.136</v>
       </c>
       <c r="I65" t="n">
-        <v>0.439</v>
+        <v>0.436</v>
       </c>
     </row>
     <row r="66">
@@ -5446,10 +5446,10 @@
         <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="G69" t="n">
-        <v>0.667</v>
+        <v>0.741</v>
       </c>
       <c r="H69" t="n">
         <v>1</v>
@@ -5520,16 +5520,16 @@
         <v>6</v>
       </c>
       <c r="F71" t="n">
-        <v>0.925</v>
+        <v>0.969</v>
       </c>
       <c r="G71" t="n">
-        <v>0.891</v>
+        <v>0.921</v>
       </c>
       <c r="H71" t="n">
-        <v>0.587</v>
+        <v>0.304</v>
       </c>
       <c r="I71" t="n">
-        <v>0.783</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="72">
@@ -5557,16 +5557,16 @@
         <v>7</v>
       </c>
       <c r="F72" t="n">
-        <v>0.904</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>0.837</v>
+        <v>0.9</v>
       </c>
       <c r="H72" t="n">
-        <v>0.247</v>
+        <v>0.381</v>
       </c>
       <c r="I72" t="n">
-        <v>0.658</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="73">
@@ -5603,7 +5603,7 @@
         <v>0.5590000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>0.783</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="74">
@@ -5668,16 +5668,16 @@
         <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>0.903</v>
+        <v>0.913</v>
       </c>
       <c r="G75" t="n">
-        <v>0.8</v>
+        <v>0.885</v>
       </c>
       <c r="H75" t="n">
-        <v>0.136</v>
+        <v>0.771</v>
       </c>
       <c r="I75" t="n">
-        <v>0.504</v>
+        <v>0.915</v>
       </c>
     </row>
     <row r="76">
@@ -5705,16 +5705,16 @@
         <v>11</v>
       </c>
       <c r="F76" t="n">
-        <v>0.869</v>
+        <v>0.873</v>
       </c>
       <c r="G76" t="n">
-        <v>0.882</v>
+        <v>0.887</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>0.801</v>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>0.915</v>
       </c>
     </row>
     <row r="77">
@@ -5751,7 +5751,7 @@
         <v>0.679</v>
       </c>
       <c r="I77" t="n">
-        <v>0.836</v>
+        <v>0.906</v>
       </c>
     </row>
     <row r="78">
@@ -5853,16 +5853,16 @@
         <v>15</v>
       </c>
       <c r="F80" t="n">
-        <v>0.61</v>
+        <v>0.617</v>
       </c>
       <c r="G80" t="n">
         <v>0.73</v>
       </c>
       <c r="H80" t="n">
-        <v>0.157</v>
+        <v>0.212</v>
       </c>
       <c r="I80" t="n">
-        <v>0.504</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="81">
@@ -5890,16 +5890,16 @@
         <v>16</v>
       </c>
       <c r="F81" t="n">
-        <v>0.5</v>
+        <v>0.509</v>
       </c>
       <c r="G81" t="n">
-        <v>0.59</v>
+        <v>0.621</v>
       </c>
       <c r="H81" t="n">
-        <v>0.36</v>
+        <v>0.262</v>
       </c>
       <c r="I81" t="n">
-        <v>0.708</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="82">
@@ -5936,7 +5936,7 @@
         <v>0.0352</v>
       </c>
       <c r="I82" t="n">
-        <v>0.222</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="83">
@@ -5973,7 +5973,7 @@
         <v>0.236</v>
       </c>
       <c r="I83" t="n">
-        <v>0.652</v>
+        <v>0.5590000000000001</v>
       </c>
     </row>
     <row r="84">
@@ -6112,16 +6112,16 @@
         <v>6</v>
       </c>
       <c r="F87" t="n">
-        <v>0.674</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G87" t="n">
         <v>0.891</v>
       </c>
       <c r="H87" t="n">
-        <v>0.000568</v>
+        <v>0.0009940000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>0.00908</v>
+        <v>0.0159</v>
       </c>
     </row>
     <row r="88">
@@ -6158,7 +6158,7 @@
         <v>0.327</v>
       </c>
       <c r="I88" t="n">
-        <v>0.747</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="89">
@@ -6232,7 +6232,7 @@
         <v>0.136</v>
       </c>
       <c r="I90" t="n">
-        <v>0.545</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="91">
@@ -6260,16 +6260,16 @@
         <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>0.7</v>
+        <v>0.787</v>
       </c>
       <c r="G91" t="n">
-        <v>0.65</v>
+        <v>0.675</v>
       </c>
       <c r="H91" t="n">
-        <v>0.613</v>
+        <v>0.153</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="92">
@@ -6297,16 +6297,16 @@
         <v>11</v>
       </c>
       <c r="F92" t="n">
-        <v>0.582</v>
+        <v>0.604</v>
       </c>
       <c r="G92" t="n">
-        <v>0.736</v>
+        <v>0.78</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0416</v>
+        <v>0.0156</v>
       </c>
       <c r="I92" t="n">
-        <v>0.222</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="93">
@@ -6491,7 +6491,7 @@
         <v>0.244</v>
       </c>
       <c r="I97" t="n">
-        <v>0.652</v>
+        <v>0.5590000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -6630,16 +6630,16 @@
         <v>4</v>
       </c>
       <c r="F101" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.947</v>
       </c>
       <c r="G101" t="n">
         <v>0.953</v>
       </c>
       <c r="H101" t="n">
-        <v>0.619</v>
+        <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>0.888</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -6676,7 +6676,7 @@
         <v>0.769</v>
       </c>
       <c r="I102" t="n">
-        <v>0.888</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -6704,16 +6704,16 @@
         <v>6</v>
       </c>
       <c r="F103" t="n">
-        <v>0.767</v>
+        <v>0.793</v>
       </c>
       <c r="G103" t="n">
         <v>0.84</v>
       </c>
       <c r="H103" t="n">
-        <v>0.146</v>
+        <v>0.371</v>
       </c>
       <c r="I103" t="n">
-        <v>0.616</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -6741,16 +6741,16 @@
         <v>7</v>
       </c>
       <c r="F104" t="n">
-        <v>0.827</v>
+        <v>0.847</v>
       </c>
       <c r="G104" t="n">
-        <v>0.793</v>
+        <v>0.82</v>
       </c>
       <c r="H104" t="n">
-        <v>0.556</v>
+        <v>0.642</v>
       </c>
       <c r="I104" t="n">
-        <v>0.888</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -6852,16 +6852,16 @@
         <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>0.8</v>
+        <v>0.847</v>
       </c>
       <c r="G107" t="n">
-        <v>0.78</v>
+        <v>0.847</v>
       </c>
       <c r="H107" t="n">
-        <v>0.777</v>
+        <v>1</v>
       </c>
       <c r="I107" t="n">
-        <v>0.888</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -6889,16 +6889,16 @@
         <v>11</v>
       </c>
       <c r="F108" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.707</v>
       </c>
       <c r="G108" t="n">
-        <v>0.76</v>
+        <v>0.793</v>
       </c>
       <c r="H108" t="n">
-        <v>0.244</v>
+        <v>0.109</v>
       </c>
       <c r="I108" t="n">
-        <v>0.779</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="109">
@@ -6935,7 +6935,7 @@
         <v>0.611</v>
       </c>
       <c r="I109" t="n">
-        <v>0.888</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -6972,7 +6972,7 @@
         <v>0.723</v>
       </c>
       <c r="I110" t="n">
-        <v>0.888</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -7009,7 +7009,7 @@
         <v>0.51</v>
       </c>
       <c r="I111" t="n">
-        <v>0.888</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -7037,16 +7037,16 @@
         <v>15</v>
       </c>
       <c r="F112" t="n">
-        <v>0.673</v>
+        <v>0.68</v>
       </c>
       <c r="G112" t="n">
-        <v>0.733</v>
+        <v>0.727</v>
       </c>
       <c r="H112" t="n">
-        <v>0.312</v>
+        <v>0.448</v>
       </c>
       <c r="I112" t="n">
-        <v>0.832</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -7074,16 +7074,16 @@
         <v>16</v>
       </c>
       <c r="F113" t="n">
-        <v>0.633</v>
+        <v>0.64</v>
       </c>
       <c r="G113" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H113" t="n">
-        <v>0.394</v>
+        <v>0.391</v>
       </c>
       <c r="I113" t="n">
-        <v>0.888</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -7120,7 +7120,7 @@
         <v>0.0829</v>
       </c>
       <c r="I114" t="n">
-        <v>0.663</v>
+        <v>0.442</v>
       </c>
     </row>
     <row r="115">
@@ -7222,13 +7222,13 @@
         <v>4</v>
       </c>
       <c r="F117" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="G117" t="n">
         <v>0.8</v>
       </c>
       <c r="H117" t="n">
-        <v>0.537</v>
+        <v>0.75</v>
       </c>
       <c r="I117" t="n">
         <v>1</v>
@@ -7296,16 +7296,16 @@
         <v>6</v>
       </c>
       <c r="F119" t="n">
-        <v>0.925</v>
+        <v>0.969</v>
       </c>
       <c r="G119" t="n">
         <v>0.886</v>
       </c>
       <c r="H119" t="n">
-        <v>0.585</v>
+        <v>0.0723</v>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>0.442</v>
       </c>
     </row>
     <row r="120">
@@ -7333,16 +7333,16 @@
         <v>7</v>
       </c>
       <c r="F120" t="n">
-        <v>0.904</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="G120" t="n">
-        <v>0.821</v>
+        <v>0.863</v>
       </c>
       <c r="H120" t="n">
-        <v>0.169</v>
+        <v>0.171</v>
       </c>
       <c r="I120" t="n">
-        <v>0.902</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="121">
@@ -7444,16 +7444,16 @@
         <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>0.903</v>
+        <v>0.913</v>
       </c>
       <c r="G123" t="n">
-        <v>0.841</v>
+        <v>0.952</v>
       </c>
       <c r="H123" t="n">
-        <v>0.312</v>
+        <v>0.497</v>
       </c>
       <c r="I123" t="n">
-        <v>0.998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -7481,13 +7481,13 @@
         <v>11</v>
       </c>
       <c r="F124" t="n">
-        <v>0.869</v>
+        <v>0.873</v>
       </c>
       <c r="G124" t="n">
-        <v>0.877</v>
+        <v>0.895</v>
       </c>
       <c r="H124" t="n">
-        <v>1</v>
+        <v>0.792</v>
       </c>
       <c r="I124" t="n">
         <v>1</v>
@@ -7601,7 +7601,7 @@
         <v>0.273</v>
       </c>
       <c r="I127" t="n">
-        <v>0.998</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="128">
@@ -7629,13 +7629,13 @@
         <v>15</v>
       </c>
       <c r="F128" t="n">
-        <v>0.61</v>
+        <v>0.617</v>
       </c>
       <c r="G128" t="n">
-        <v>0.667</v>
+        <v>0.659</v>
       </c>
       <c r="H128" t="n">
-        <v>0.515</v>
+        <v>0.627</v>
       </c>
       <c r="I128" t="n">
         <v>1</v>
@@ -7666,13 +7666,13 @@
         <v>16</v>
       </c>
       <c r="F129" t="n">
-        <v>0.5</v>
+        <v>0.509</v>
       </c>
       <c r="G129" t="n">
-        <v>0.556</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H129" t="n">
-        <v>0.597</v>
+        <v>0.594</v>
       </c>
       <c r="I129" t="n">
         <v>1</v>
@@ -7888,16 +7888,16 @@
         <v>6</v>
       </c>
       <c r="F135" t="n">
-        <v>0.674</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G135" t="n">
         <v>0.848</v>
       </c>
       <c r="H135" t="n">
-        <v>0.00906</v>
+        <v>0.0141</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0725</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="136">
@@ -8036,13 +8036,13 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>0.7</v>
+        <v>0.787</v>
       </c>
       <c r="G139" t="n">
-        <v>0.725</v>
+        <v>0.75</v>
       </c>
       <c r="H139" t="n">
-        <v>0.861</v>
+        <v>0.708</v>
       </c>
       <c r="I139" t="n">
         <v>1</v>
@@ -8073,16 +8073,16 @@
         <v>11</v>
       </c>
       <c r="F140" t="n">
-        <v>0.582</v>
+        <v>0.604</v>
       </c>
       <c r="G140" t="n">
-        <v>0.703</v>
+        <v>0.747</v>
       </c>
       <c r="H140" t="n">
-        <v>0.122</v>
+        <v>0.0569</v>
       </c>
       <c r="I140" t="n">
-        <v>0.436</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="141">
@@ -8267,7 +8267,7 @@
         <v>0.048</v>
       </c>
       <c r="I145" t="n">
-        <v>0.256</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="146">
@@ -8304,7 +8304,7 @@
         <v>0.868</v>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>0.992</v>
       </c>
     </row>
     <row r="147">
@@ -8406,10 +8406,10 @@
         <v>4</v>
       </c>
       <c r="F149" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.947</v>
       </c>
       <c r="G149" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.953</v>
       </c>
       <c r="H149" t="n">
         <v>1</v>
@@ -8446,13 +8446,13 @@
         <v>0.8</v>
       </c>
       <c r="G150" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="H150" t="n">
-        <v>0.769</v>
+        <v>0.657</v>
       </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>0.992</v>
       </c>
     </row>
     <row r="151">
@@ -8480,16 +8480,16 @@
         <v>6</v>
       </c>
       <c r="F151" t="n">
-        <v>0.767</v>
+        <v>0.793</v>
       </c>
       <c r="G151" t="n">
-        <v>0.867</v>
+        <v>0.887</v>
       </c>
       <c r="H151" t="n">
-        <v>0.0361</v>
+        <v>0.0398</v>
       </c>
       <c r="I151" t="n">
-        <v>0.26</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="152">
@@ -8517,16 +8517,16 @@
         <v>7</v>
       </c>
       <c r="F152" t="n">
-        <v>0.827</v>
+        <v>0.847</v>
       </c>
       <c r="G152" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="H152" t="n">
-        <v>0.877</v>
+        <v>0.502</v>
       </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>0.892</v>
       </c>
     </row>
     <row r="153">
@@ -8563,7 +8563,7 @@
         <v>0.77</v>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>0.992</v>
       </c>
     </row>
     <row r="154">
@@ -8594,13 +8594,13 @@
         <v>0.6870000000000001</v>
       </c>
       <c r="G154" t="n">
-        <v>0.787</v>
+        <v>0.793</v>
       </c>
       <c r="H154" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.0479</v>
       </c>
       <c r="I154" t="n">
-        <v>0.26</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="155">
@@ -8628,16 +8628,16 @@
         <v>10</v>
       </c>
       <c r="F155" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="G155" t="n">
         <v>0.8</v>
       </c>
-      <c r="G155" t="n">
-        <v>0.707</v>
-      </c>
       <c r="H155" t="n">
-        <v>0.0813</v>
+        <v>0.364</v>
       </c>
       <c r="I155" t="n">
-        <v>0.26</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="156">
@@ -8665,16 +8665,16 @@
         <v>11</v>
       </c>
       <c r="F156" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.707</v>
       </c>
       <c r="G156" t="n">
-        <v>0.767</v>
+        <v>0.787</v>
       </c>
       <c r="H156" t="n">
-        <v>0.193</v>
+        <v>0.144</v>
       </c>
       <c r="I156" t="n">
-        <v>0.387</v>
+        <v>0.384</v>
       </c>
     </row>
     <row r="157">
@@ -8711,7 +8711,7 @@
         <v>0.862</v>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>0.992</v>
       </c>
     </row>
     <row r="158">
@@ -8785,7 +8785,7 @@
         <v>0.737</v>
       </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>0.992</v>
       </c>
     </row>
     <row r="160">
@@ -8813,16 +8813,16 @@
         <v>15</v>
       </c>
       <c r="F160" t="n">
-        <v>0.673</v>
+        <v>0.68</v>
       </c>
       <c r="G160" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="H160" t="n">
-        <v>0.0516</v>
+        <v>0.0249</v>
       </c>
       <c r="I160" t="n">
-        <v>0.26</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="161">
@@ -8850,16 +8850,16 @@
         <v>16</v>
       </c>
       <c r="F161" t="n">
-        <v>0.633</v>
+        <v>0.64</v>
       </c>
       <c r="G161" t="n">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="H161" t="n">
-        <v>0.138</v>
+        <v>0.0319</v>
       </c>
       <c r="I161" t="n">
-        <v>0.369</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="162">
@@ -8896,7 +8896,7 @@
         <v>0.0381</v>
       </c>
       <c r="I162" t="n">
-        <v>0.203</v>
+        <v>0.305</v>
       </c>
     </row>
     <row r="163">
@@ -8970,7 +8970,7 @@
         <v>0.256</v>
       </c>
       <c r="I164" t="n">
-        <v>0.584</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="165">
@@ -8998,10 +8998,10 @@
         <v>4</v>
       </c>
       <c r="F165" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="G165" t="n">
-        <v>0.724</v>
+        <v>0.778</v>
       </c>
       <c r="H165" t="n">
         <v>1</v>
@@ -9038,13 +9038,13 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="G166" t="n">
-        <v>0.974</v>
+        <v>0.987</v>
       </c>
       <c r="H166" t="n">
-        <v>0.443</v>
+        <v>0.211</v>
       </c>
       <c r="I166" t="n">
-        <v>0.788</v>
+        <v>0.481</v>
       </c>
     </row>
     <row r="167">
@@ -9072,16 +9072,16 @@
         <v>6</v>
       </c>
       <c r="F167" t="n">
-        <v>0.925</v>
+        <v>0.969</v>
       </c>
       <c r="G167" t="n">
-        <v>0.9</v>
+        <v>0.931</v>
       </c>
       <c r="H167" t="n">
-        <v>0.778</v>
+        <v>0.467</v>
       </c>
       <c r="I167" t="n">
-        <v>1</v>
+        <v>0.831</v>
       </c>
     </row>
     <row r="168">
@@ -9109,16 +9109,16 @@
         <v>7</v>
       </c>
       <c r="F168" t="n">
-        <v>0.904</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="G168" t="n">
-        <v>0.867</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="H168" t="n">
-        <v>0.617</v>
+        <v>1</v>
       </c>
       <c r="I168" t="n">
-        <v>0.915</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -9186,13 +9186,13 @@
         <v>0.988</v>
       </c>
       <c r="G170" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="H170" t="n">
-        <v>0.629</v>
+        <v>1</v>
       </c>
       <c r="I170" t="n">
-        <v>0.915</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -9220,16 +9220,16 @@
         <v>10</v>
       </c>
       <c r="F171" t="n">
-        <v>0.903</v>
+        <v>0.913</v>
       </c>
       <c r="G171" t="n">
-        <v>0.737</v>
+        <v>0.879</v>
       </c>
       <c r="H171" t="n">
-        <v>0.0158</v>
+        <v>0.58</v>
       </c>
       <c r="I171" t="n">
-        <v>0.126</v>
+        <v>0.929</v>
       </c>
     </row>
     <row r="172">
@@ -9257,10 +9257,10 @@
         <v>11</v>
       </c>
       <c r="F172" t="n">
-        <v>0.869</v>
+        <v>0.873</v>
       </c>
       <c r="G172" t="n">
-        <v>0.868</v>
+        <v>0.883</v>
       </c>
       <c r="H172" t="n">
         <v>1</v>
@@ -9377,7 +9377,7 @@
         <v>0.0648</v>
       </c>
       <c r="I175" t="n">
-        <v>0.259</v>
+        <v>0.345</v>
       </c>
     </row>
     <row r="176">
@@ -9405,16 +9405,16 @@
         <v>15</v>
       </c>
       <c r="F176" t="n">
-        <v>0.61</v>
+        <v>0.617</v>
       </c>
       <c r="G176" t="n">
-        <v>0.718</v>
+        <v>0.747</v>
       </c>
       <c r="H176" t="n">
-        <v>0.181</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="I176" t="n">
-        <v>0.484</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="177">
@@ -9442,16 +9442,16 @@
         <v>16</v>
       </c>
       <c r="F177" t="n">
-        <v>0.5</v>
+        <v>0.509</v>
       </c>
       <c r="G177" t="n">
-        <v>0.594</v>
+        <v>0.651</v>
       </c>
       <c r="H177" t="n">
-        <v>0.371</v>
+        <v>0.139</v>
       </c>
       <c r="I177" t="n">
-        <v>0.741</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="178">
@@ -9488,7 +9488,7 @@
         <v>0.447</v>
       </c>
       <c r="I178" t="n">
-        <v>0.959</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="179">
@@ -9562,7 +9562,7 @@
         <v>0.669</v>
       </c>
       <c r="I180" t="n">
-        <v>1</v>
+        <v>0.974</v>
       </c>
     </row>
     <row r="181">
@@ -9664,16 +9664,16 @@
         <v>6</v>
       </c>
       <c r="F183" t="n">
-        <v>0.674</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G183" t="n">
         <v>0.88</v>
       </c>
       <c r="H183" t="n">
-        <v>0.00125</v>
+        <v>0.00212</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0199</v>
+        <v>0.0339</v>
       </c>
     </row>
     <row r="184">
@@ -9710,7 +9710,7 @@
         <v>0.327</v>
       </c>
       <c r="I184" t="n">
-        <v>0.871</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="185">
@@ -9812,16 +9812,16 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>0.7</v>
+        <v>0.787</v>
       </c>
       <c r="G187" t="n">
-        <v>0.7</v>
+        <v>0.725</v>
       </c>
       <c r="H187" t="n">
-        <v>1</v>
+        <v>0.462</v>
       </c>
       <c r="I187" t="n">
-        <v>1</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="188">
@@ -9849,16 +9849,16 @@
         <v>11</v>
       </c>
       <c r="F188" t="n">
-        <v>0.582</v>
+        <v>0.604</v>
       </c>
       <c r="G188" t="n">
-        <v>0.725</v>
+        <v>0.747</v>
       </c>
       <c r="H188" t="n">
-        <v>0.0611</v>
+        <v>0.0569</v>
       </c>
       <c r="I188" t="n">
-        <v>0.244</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="189">
@@ -9895,7 +9895,7 @@
         <v>0.519</v>
       </c>
       <c r="I189" t="n">
-        <v>0.959</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="190">
@@ -9969,7 +9969,7 @@
         <v>0.539</v>
       </c>
       <c r="I191" t="n">
-        <v>0.959</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="192">
@@ -10006,7 +10006,7 @@
         <v>0.288</v>
       </c>
       <c r="I192" t="n">
-        <v>0.871</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="193">
@@ -10154,7 +10154,7 @@
         <v>0.6840000000000001</v>
       </c>
       <c r="I196" t="n">
-        <v>0.842</v>
+        <v>0.898</v>
       </c>
     </row>
     <row r="197">
@@ -10182,16 +10182,16 @@
         <v>4</v>
       </c>
       <c r="F197" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.947</v>
       </c>
       <c r="G197" t="n">
         <v>0.96</v>
       </c>
       <c r="H197" t="n">
-        <v>0.442</v>
+        <v>0.785</v>
       </c>
       <c r="I197" t="n">
-        <v>0.67</v>
+        <v>0.898</v>
       </c>
     </row>
     <row r="198">
@@ -10222,13 +10222,13 @@
         <v>0.8</v>
       </c>
       <c r="G198" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="H198" t="n">
-        <v>0.884</v>
+        <v>0.769</v>
       </c>
       <c r="I198" t="n">
-        <v>1</v>
+        <v>0.898</v>
       </c>
     </row>
     <row r="199">
@@ -10256,16 +10256,16 @@
         <v>6</v>
       </c>
       <c r="F199" t="n">
-        <v>0.767</v>
+        <v>0.793</v>
       </c>
       <c r="G199" t="n">
-        <v>0.887</v>
+        <v>0.907</v>
       </c>
       <c r="H199" t="n">
-        <v>0.00906</v>
+        <v>0.00911</v>
       </c>
       <c r="I199" t="n">
-        <v>0.029</v>
+        <v>0.0292</v>
       </c>
     </row>
     <row r="200">
@@ -10293,16 +10293,16 @@
         <v>7</v>
       </c>
       <c r="F200" t="n">
-        <v>0.827</v>
+        <v>0.847</v>
       </c>
       <c r="G200" t="n">
-        <v>0.887</v>
+        <v>0.893</v>
       </c>
       <c r="H200" t="n">
-        <v>0.187</v>
+        <v>0.303</v>
       </c>
       <c r="I200" t="n">
-        <v>0.393</v>
+        <v>0.606</v>
       </c>
     </row>
     <row r="201">
@@ -10376,7 +10376,7 @@
         <v>0.197</v>
       </c>
       <c r="I202" t="n">
-        <v>0.393</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="203">
@@ -10404,16 +10404,16 @@
         <v>10</v>
       </c>
       <c r="F203" t="n">
-        <v>0.8</v>
+        <v>0.847</v>
       </c>
       <c r="G203" t="n">
-        <v>0.853</v>
+        <v>0.867</v>
       </c>
       <c r="H203" t="n">
-        <v>0.286</v>
+        <v>0.742</v>
       </c>
       <c r="I203" t="n">
-        <v>0.508</v>
+        <v>0.898</v>
       </c>
     </row>
     <row r="204">
@@ -10441,16 +10441,16 @@
         <v>11</v>
       </c>
       <c r="F204" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.707</v>
       </c>
       <c r="G204" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="H204" t="n">
-        <v>0.00395</v>
+        <v>0.0019</v>
       </c>
       <c r="I204" t="n">
-        <v>0.0158</v>
+        <v>0.00761</v>
       </c>
     </row>
     <row r="205">
@@ -10487,7 +10487,7 @@
         <v>0.575</v>
       </c>
       <c r="I205" t="n">
-        <v>0.767</v>
+        <v>0.898</v>
       </c>
     </row>
     <row r="206">
@@ -10561,7 +10561,7 @@
         <v>0.461</v>
       </c>
       <c r="I207" t="n">
-        <v>0.67</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="208">
@@ -10589,16 +10589,16 @@
         <v>15</v>
       </c>
       <c r="F208" t="n">
-        <v>0.673</v>
+        <v>0.68</v>
       </c>
       <c r="G208" t="n">
-        <v>0.847</v>
+        <v>0.853</v>
       </c>
       <c r="H208" t="n">
-        <v>0.000662</v>
+        <v>0.0005820000000000001</v>
       </c>
       <c r="I208" t="n">
-        <v>0.00529</v>
+        <v>0.00356</v>
       </c>
     </row>
     <row r="209">
@@ -10626,16 +10626,16 @@
         <v>16</v>
       </c>
       <c r="F209" t="n">
-        <v>0.633</v>
+        <v>0.64</v>
       </c>
       <c r="G209" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="H209" t="n">
-        <v>0.00123</v>
+        <v>0.000668</v>
       </c>
       <c r="I209" t="n">
-        <v>0.00657</v>
+        <v>0.00356</v>
       </c>
     </row>
     <row r="210">
@@ -10672,7 +10672,7 @@
         <v>0.585</v>
       </c>
       <c r="I210" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.926</v>
       </c>
     </row>
     <row r="211">
@@ -10746,7 +10746,7 @@
         <v>0.491</v>
       </c>
       <c r="I212" t="n">
-        <v>0.873</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="213">
@@ -10774,16 +10774,16 @@
         <v>4</v>
       </c>
       <c r="F213" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="G213" t="n">
         <v>0.833</v>
       </c>
       <c r="H213" t="n">
-        <v>0.343</v>
+        <v>0.516</v>
       </c>
       <c r="I213" t="n">
-        <v>0.784</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="214">
@@ -10814,13 +10814,13 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="G214" t="n">
-        <v>0.951</v>
+        <v>0.963</v>
       </c>
       <c r="H214" t="n">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="I214" t="n">
-        <v>1</v>
+        <v>0.926</v>
       </c>
     </row>
     <row r="215">
@@ -10848,16 +10848,16 @@
         <v>6</v>
       </c>
       <c r="F215" t="n">
-        <v>0.925</v>
+        <v>0.969</v>
       </c>
       <c r="G215" t="n">
-        <v>0.921</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="H215" t="n">
-        <v>1</v>
+        <v>0.699</v>
       </c>
       <c r="I215" t="n">
-        <v>1</v>
+        <v>0.926</v>
       </c>
     </row>
     <row r="216">
@@ -10885,16 +10885,16 @@
         <v>7</v>
       </c>
       <c r="F216" t="n">
-        <v>0.904</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="G216" t="n">
-        <v>0.915</v>
+        <v>0.926</v>
       </c>
       <c r="H216" t="n">
-        <v>1</v>
+        <v>0.752</v>
       </c>
       <c r="I216" t="n">
-        <v>1</v>
+        <v>0.926</v>
       </c>
     </row>
     <row r="217">
@@ -10996,10 +10996,10 @@
         <v>10</v>
       </c>
       <c r="F219" t="n">
-        <v>0.903</v>
+        <v>0.913</v>
       </c>
       <c r="G219" t="n">
-        <v>0.914</v>
+        <v>0.917</v>
       </c>
       <c r="H219" t="n">
         <v>1</v>
@@ -11033,16 +11033,16 @@
         <v>11</v>
       </c>
       <c r="F220" t="n">
-        <v>0.869</v>
+        <v>0.873</v>
       </c>
       <c r="G220" t="n">
-        <v>0.924</v>
+        <v>0.927</v>
       </c>
       <c r="H220" t="n">
-        <v>0.395</v>
+        <v>0.396</v>
       </c>
       <c r="I220" t="n">
-        <v>0.79</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="221">
@@ -11181,16 +11181,16 @@
         <v>15</v>
       </c>
       <c r="F224" t="n">
-        <v>0.61</v>
+        <v>0.617</v>
       </c>
       <c r="G224" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.826</v>
       </c>
       <c r="H224" t="n">
-        <v>0.00738</v>
+        <v>0.00635</v>
       </c>
       <c r="I224" t="n">
-        <v>0.059</v>
+        <v>0.0508</v>
       </c>
     </row>
     <row r="225">
@@ -11218,16 +11218,16 @@
         <v>16</v>
       </c>
       <c r="F225" t="n">
-        <v>0.5</v>
+        <v>0.509</v>
       </c>
       <c r="G225" t="n">
-        <v>0.717</v>
+        <v>0.733</v>
       </c>
       <c r="H225" t="n">
-        <v>0.0231</v>
+        <v>0.0139</v>
       </c>
       <c r="I225" t="n">
-        <v>0.123</v>
+        <v>0.0743</v>
       </c>
     </row>
     <row r="226">
@@ -11301,7 +11301,7 @@
         <v>0.491</v>
       </c>
       <c r="I227" t="n">
-        <v>0.714</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="228">
@@ -11440,16 +11440,16 @@
         <v>6</v>
       </c>
       <c r="F231" t="n">
-        <v>0.674</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G231" t="n">
-        <v>0.891</v>
+        <v>0.902</v>
       </c>
       <c r="H231" t="n">
-        <v>0.000568</v>
+        <v>0.000433</v>
       </c>
       <c r="I231" t="n">
-        <v>0.00908</v>
+        <v>0.0069</v>
       </c>
     </row>
     <row r="232">
@@ -11588,16 +11588,16 @@
         <v>10</v>
       </c>
       <c r="F235" t="n">
-        <v>0.7</v>
+        <v>0.787</v>
       </c>
       <c r="G235" t="n">
-        <v>0.8</v>
+        <v>0.825</v>
       </c>
       <c r="H235" t="n">
-        <v>0.201</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I235" t="n">
-        <v>0.321</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
@@ -11625,16 +11625,16 @@
         <v>11</v>
       </c>
       <c r="F236" t="n">
-        <v>0.582</v>
+        <v>0.604</v>
       </c>
       <c r="G236" t="n">
-        <v>0.802</v>
+        <v>0.835</v>
       </c>
       <c r="H236" t="n">
-        <v>0.00213</v>
+        <v>0.0008630000000000001</v>
       </c>
       <c r="I236" t="n">
-        <v>0.017</v>
+        <v>0.0069</v>
       </c>
     </row>
     <row r="237">
@@ -11782,7 +11782,7 @@
         <v>0.196</v>
       </c>
       <c r="I240" t="n">
-        <v>0.321</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="241">
@@ -11813,13 +11813,13 @@
         <v>0.527</v>
       </c>
       <c r="G241" t="n">
-        <v>0.782</v>
+        <v>0.8</v>
       </c>
       <c r="H241" t="n">
-        <v>0.008710000000000001</v>
+        <v>0.00439</v>
       </c>
       <c r="I241" t="n">
-        <v>0.0464</v>
+        <v>0.0234</v>
       </c>
     </row>
     <row r="242">
@@ -11995,13 +11995,13 @@
         <v>5</v>
       </c>
       <c r="F246" t="n">
-        <v>0.8</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G246" t="n">
         <v>0.82</v>
       </c>
       <c r="H246" t="n">
-        <v>0.769</v>
+        <v>0.882</v>
       </c>
       <c r="I246" t="n">
         <v>1</v>
@@ -12146,10 +12146,10 @@
         <v>0.68</v>
       </c>
       <c r="G250" t="n">
-        <v>0.787</v>
+        <v>0.78</v>
       </c>
       <c r="H250" t="n">
-        <v>0.0498</v>
+        <v>0.0683</v>
       </c>
       <c r="I250" t="n">
         <v>0.703</v>
@@ -12180,13 +12180,13 @@
         <v>10</v>
       </c>
       <c r="F251" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="G251" t="n">
-        <v>0.86</v>
+        <v>0.893</v>
       </c>
       <c r="H251" t="n">
-        <v>0.0977</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="I251" t="n">
         <v>0.703</v>
@@ -12220,10 +12220,10 @@
         <v>0.787</v>
       </c>
       <c r="G252" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="H252" t="n">
-        <v>1</v>
+        <v>0.887</v>
       </c>
       <c r="I252" t="n">
         <v>1</v>
@@ -12402,16 +12402,16 @@
         <v>16</v>
       </c>
       <c r="F257" t="n">
-        <v>0.433</v>
+        <v>0.46</v>
       </c>
       <c r="G257" t="n">
         <v>0.393</v>
       </c>
       <c r="H257" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.293</v>
       </c>
       <c r="I257" t="n">
-        <v>1</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="258">
@@ -12587,13 +12587,13 @@
         <v>5</v>
       </c>
       <c r="F262" t="n">
-        <v>0.949</v>
+        <v>0.962</v>
       </c>
       <c r="G262" t="n">
         <v>0.93</v>
       </c>
       <c r="H262" t="n">
-        <v>0.749</v>
+        <v>0.5</v>
       </c>
       <c r="I262" t="n">
         <v>1</v>
@@ -12738,10 +12738,10 @@
         <v>0.964</v>
       </c>
       <c r="G266" t="n">
-        <v>0.92</v>
+        <v>0.919</v>
       </c>
       <c r="H266" t="n">
-        <v>0.24</v>
+        <v>0.239</v>
       </c>
       <c r="I266" t="n">
         <v>1</v>
@@ -12772,10 +12772,10 @@
         <v>10</v>
       </c>
       <c r="F267" t="n">
-        <v>0.98</v>
+        <v>0.982</v>
       </c>
       <c r="G267" t="n">
-        <v>0.984</v>
+        <v>0.985</v>
       </c>
       <c r="H267" t="n">
         <v>1</v>
@@ -12812,7 +12812,7 @@
         <v>0.864</v>
       </c>
       <c r="G268" t="n">
-        <v>0.875</v>
+        <v>0.877</v>
       </c>
       <c r="H268" t="n">
         <v>1</v>
@@ -12994,13 +12994,13 @@
         <v>16</v>
       </c>
       <c r="F273" t="n">
-        <v>0.364</v>
+        <v>0.38</v>
       </c>
       <c r="G273" t="n">
         <v>0.339</v>
       </c>
       <c r="H273" t="n">
-        <v>0.779</v>
+        <v>0.575</v>
       </c>
       <c r="I273" t="n">
         <v>1</v>
@@ -13330,13 +13330,13 @@
         <v>0.643</v>
       </c>
       <c r="G282" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H282" t="n">
-        <v>0.00273</v>
+        <v>0.00453</v>
       </c>
       <c r="I282" t="n">
-        <v>0.0436</v>
+        <v>0.07240000000000001</v>
       </c>
     </row>
     <row r="283">
@@ -13364,13 +13364,13 @@
         <v>10</v>
       </c>
       <c r="F283" t="n">
-        <v>0.6</v>
+        <v>0.675</v>
       </c>
       <c r="G283" t="n">
-        <v>0.75</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H283" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0694</v>
       </c>
       <c r="I283" t="n">
         <v>0.455</v>
@@ -13404,7 +13404,7 @@
         <v>0.769</v>
       </c>
       <c r="G284" t="n">
-        <v>0.769</v>
+        <v>0.78</v>
       </c>
       <c r="H284" t="n">
         <v>1</v>
@@ -13586,13 +13586,13 @@
         <v>16</v>
       </c>
       <c r="F289" t="n">
-        <v>0.727</v>
+        <v>0.745</v>
       </c>
       <c r="G289" t="n">
         <v>0.6909999999999999</v>
       </c>
       <c r="H289" t="n">
-        <v>0.834</v>
+        <v>0.672</v>
       </c>
       <c r="I289" t="n">
         <v>1</v>
@@ -13632,7 +13632,7 @@
         <v>0.188</v>
       </c>
       <c r="I290" t="n">
-        <v>0.93</v>
+        <v>0.838</v>
       </c>
     </row>
     <row r="291">
@@ -13771,16 +13771,16 @@
         <v>5</v>
       </c>
       <c r="F294" t="n">
-        <v>0.8</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G294" t="n">
         <v>0.787</v>
       </c>
       <c r="H294" t="n">
-        <v>0.887</v>
+        <v>0.774</v>
       </c>
       <c r="I294" t="n">
-        <v>0.946</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="295">
@@ -13817,7 +13817,7 @@
         <v>0.232</v>
       </c>
       <c r="I295" t="n">
-        <v>0.93</v>
+        <v>0.838</v>
       </c>
     </row>
     <row r="296">
@@ -13956,16 +13956,16 @@
         <v>10</v>
       </c>
       <c r="F299" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="G299" t="n">
-        <v>0.853</v>
+        <v>0.873</v>
       </c>
       <c r="H299" t="n">
-        <v>0.135</v>
+        <v>0.262</v>
       </c>
       <c r="I299" t="n">
-        <v>0.93</v>
+        <v>0.838</v>
       </c>
     </row>
     <row r="300">
@@ -13996,13 +13996,13 @@
         <v>0.787</v>
       </c>
       <c r="G300" t="n">
-        <v>0.767</v>
+        <v>0.773</v>
       </c>
       <c r="H300" t="n">
-        <v>0.782</v>
+        <v>0.889</v>
       </c>
       <c r="I300" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.949</v>
       </c>
     </row>
     <row r="301">
@@ -14178,16 +14178,16 @@
         <v>16</v>
       </c>
       <c r="F305" t="n">
-        <v>0.433</v>
+        <v>0.46</v>
       </c>
       <c r="G305" t="n">
         <v>0.38</v>
       </c>
       <c r="H305" t="n">
-        <v>0.411</v>
+        <v>0.198</v>
       </c>
       <c r="I305" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.838</v>
       </c>
     </row>
     <row r="306">
@@ -14363,13 +14363,13 @@
         <v>5</v>
       </c>
       <c r="F310" t="n">
-        <v>0.949</v>
+        <v>0.962</v>
       </c>
       <c r="G310" t="n">
         <v>0.897</v>
       </c>
       <c r="H310" t="n">
-        <v>0.255</v>
+        <v>0.138</v>
       </c>
       <c r="I310" t="n">
         <v>1</v>
@@ -14548,13 +14548,13 @@
         <v>10</v>
       </c>
       <c r="F315" t="n">
-        <v>0.98</v>
+        <v>0.982</v>
       </c>
       <c r="G315" t="n">
-        <v>0.953</v>
+        <v>0.955</v>
       </c>
       <c r="H315" t="n">
-        <v>0.632</v>
+        <v>0.626</v>
       </c>
       <c r="I315" t="n">
         <v>1</v>
@@ -14588,10 +14588,10 @@
         <v>0.864</v>
       </c>
       <c r="G316" t="n">
-        <v>0.85</v>
+        <v>0.852</v>
       </c>
       <c r="H316" t="n">
-        <v>0.825</v>
+        <v>1</v>
       </c>
       <c r="I316" t="n">
         <v>1</v>
@@ -14770,13 +14770,13 @@
         <v>16</v>
       </c>
       <c r="F321" t="n">
-        <v>0.364</v>
+        <v>0.38</v>
       </c>
       <c r="G321" t="n">
         <v>0.347</v>
       </c>
       <c r="H321" t="n">
-        <v>0.891</v>
+        <v>0.681</v>
       </c>
       <c r="I321" t="n">
         <v>1</v>
@@ -14816,7 +14816,7 @@
         <v>0.0853</v>
       </c>
       <c r="I322" t="n">
-        <v>0.341</v>
+        <v>0.421</v>
       </c>
     </row>
     <row r="323">
@@ -15001,7 +15001,7 @@
         <v>0.0313</v>
       </c>
       <c r="I327" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="328">
@@ -15140,16 +15140,16 @@
         <v>10</v>
       </c>
       <c r="F331" t="n">
-        <v>0.6</v>
+        <v>0.675</v>
       </c>
       <c r="G331" t="n">
-        <v>0.762</v>
+        <v>0.8</v>
       </c>
       <c r="H331" t="n">
-        <v>0.0412</v>
+        <v>0.105</v>
       </c>
       <c r="I331" t="n">
-        <v>0.22</v>
+        <v>0.421</v>
       </c>
     </row>
     <row r="332">
@@ -15180,10 +15180,10 @@
         <v>0.769</v>
       </c>
       <c r="G332" t="n">
-        <v>0.747</v>
+        <v>0.758</v>
       </c>
       <c r="H332" t="n">
-        <v>0.863</v>
+        <v>1</v>
       </c>
       <c r="I332" t="n">
         <v>1</v>
@@ -15362,13 +15362,13 @@
         <v>16</v>
       </c>
       <c r="F337" t="n">
-        <v>0.727</v>
+        <v>0.745</v>
       </c>
       <c r="G337" t="n">
         <v>0.782</v>
       </c>
       <c r="H337" t="n">
-        <v>0.658</v>
+        <v>0.823</v>
       </c>
       <c r="I337" t="n">
         <v>1</v>
@@ -15408,7 +15408,7 @@
         <v>0.188</v>
       </c>
       <c r="I338" t="n">
-        <v>0.78</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="339">
@@ -15547,13 +15547,13 @@
         <v>5</v>
       </c>
       <c r="F342" t="n">
-        <v>0.8</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G342" t="n">
         <v>0.753</v>
       </c>
       <c r="H342" t="n">
-        <v>0.406</v>
+        <v>0.329</v>
       </c>
       <c r="I342" t="n">
         <v>0.78</v>
@@ -15593,7 +15593,7 @@
         <v>0.13</v>
       </c>
       <c r="I343" t="n">
-        <v>0.78</v>
+        <v>0.6909999999999999</v>
       </c>
     </row>
     <row r="344">
@@ -15732,13 +15732,13 @@
         <v>10</v>
       </c>
       <c r="F347" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="G347" t="n">
-        <v>0.84</v>
+        <v>0.873</v>
       </c>
       <c r="H347" t="n">
-        <v>0.239</v>
+        <v>0.262</v>
       </c>
       <c r="I347" t="n">
         <v>0.78</v>
@@ -15772,10 +15772,10 @@
         <v>0.787</v>
       </c>
       <c r="G348" t="n">
-        <v>0.773</v>
+        <v>0.78</v>
       </c>
       <c r="H348" t="n">
-        <v>0.889</v>
+        <v>1</v>
       </c>
       <c r="I348" t="n">
         <v>1</v>
@@ -15954,16 +15954,16 @@
         <v>16</v>
       </c>
       <c r="F353" t="n">
-        <v>0.433</v>
+        <v>0.46</v>
       </c>
       <c r="G353" t="n">
         <v>0.367</v>
       </c>
       <c r="H353" t="n">
-        <v>0.289</v>
+        <v>0.127</v>
       </c>
       <c r="I353" t="n">
-        <v>0.78</v>
+        <v>0.6909999999999999</v>
       </c>
     </row>
     <row r="354">
@@ -16139,13 +16139,13 @@
         <v>5</v>
       </c>
       <c r="F358" t="n">
-        <v>0.949</v>
+        <v>0.962</v>
       </c>
       <c r="G358" t="n">
         <v>0.881</v>
       </c>
       <c r="H358" t="n">
-        <v>0.163</v>
+        <v>0.0822</v>
       </c>
       <c r="I358" t="n">
         <v>1</v>
@@ -16324,13 +16324,13 @@
         <v>10</v>
       </c>
       <c r="F363" t="n">
-        <v>0.98</v>
+        <v>0.982</v>
       </c>
       <c r="G363" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="H363" t="n">
-        <v>0.386</v>
+        <v>0.381</v>
       </c>
       <c r="I363" t="n">
         <v>1</v>
@@ -16364,7 +16364,7 @@
         <v>0.864</v>
       </c>
       <c r="G364" t="n">
-        <v>0.87</v>
+        <v>0.872</v>
       </c>
       <c r="H364" t="n">
         <v>1</v>
@@ -16546,13 +16546,13 @@
         <v>16</v>
       </c>
       <c r="F369" t="n">
-        <v>0.364</v>
+        <v>0.38</v>
       </c>
       <c r="G369" t="n">
         <v>0.333</v>
       </c>
       <c r="H369" t="n">
-        <v>0.678</v>
+        <v>0.491</v>
       </c>
       <c r="I369" t="n">
         <v>1</v>
@@ -16916,13 +16916,13 @@
         <v>10</v>
       </c>
       <c r="F379" t="n">
-        <v>0.6</v>
+        <v>0.675</v>
       </c>
       <c r="G379" t="n">
-        <v>0.75</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H379" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0694</v>
       </c>
       <c r="I379" t="n">
         <v>0.461</v>
@@ -16956,10 +16956,10 @@
         <v>0.769</v>
       </c>
       <c r="G380" t="n">
-        <v>0.736</v>
+        <v>0.747</v>
       </c>
       <c r="H380" t="n">
-        <v>0.731</v>
+        <v>0.863</v>
       </c>
       <c r="I380" t="n">
         <v>1</v>
@@ -17138,7 +17138,7 @@
         <v>16</v>
       </c>
       <c r="F385" t="n">
-        <v>0.727</v>
+        <v>0.745</v>
       </c>
       <c r="G385" t="n">
         <v>0.727</v>
@@ -17323,16 +17323,16 @@
         <v>5</v>
       </c>
       <c r="F390" t="n">
-        <v>0.8</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G390" t="n">
         <v>0.773</v>
       </c>
       <c r="H390" t="n">
-        <v>0.673</v>
+        <v>0.571</v>
       </c>
       <c r="I390" t="n">
-        <v>0.978</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="391">
@@ -17406,7 +17406,7 @@
         <v>0.539</v>
       </c>
       <c r="I392" t="n">
-        <v>0.862</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="393">
@@ -17508,16 +17508,16 @@
         <v>10</v>
       </c>
       <c r="F395" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="G395" t="n">
-        <v>0.867</v>
+        <v>0.893</v>
       </c>
       <c r="H395" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="I395" t="n">
-        <v>0.274</v>
+        <v>0.394</v>
       </c>
     </row>
     <row r="396">
@@ -17548,13 +17548,13 @@
         <v>0.787</v>
       </c>
       <c r="G396" t="n">
-        <v>0.74</v>
+        <v>0.747</v>
       </c>
       <c r="H396" t="n">
-        <v>0.415</v>
+        <v>0.495</v>
       </c>
       <c r="I396" t="n">
-        <v>0.738</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="397">
@@ -17591,7 +17591,7 @@
         <v>0.415</v>
       </c>
       <c r="I397" t="n">
-        <v>0.738</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="398">
@@ -17665,7 +17665,7 @@
         <v>0.0307</v>
       </c>
       <c r="I399" t="n">
-        <v>0.246</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="400">
@@ -17730,16 +17730,16 @@
         <v>16</v>
       </c>
       <c r="F401" t="n">
-        <v>0.433</v>
+        <v>0.46</v>
       </c>
       <c r="G401" t="n">
         <v>0.32</v>
       </c>
       <c r="H401" t="n">
-        <v>0.0564</v>
+        <v>0.0177</v>
       </c>
       <c r="I401" t="n">
-        <v>0.274</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="402">
@@ -17915,16 +17915,16 @@
         <v>5</v>
       </c>
       <c r="F406" t="n">
-        <v>0.949</v>
+        <v>0.962</v>
       </c>
       <c r="G406" t="n">
         <v>0.885</v>
       </c>
       <c r="H406" t="n">
-        <v>0.168</v>
+        <v>0.0858</v>
       </c>
       <c r="I406" t="n">
-        <v>1</v>
+        <v>0.6860000000000001</v>
       </c>
     </row>
     <row r="407">
@@ -18100,10 +18100,10 @@
         <v>10</v>
       </c>
       <c r="F411" t="n">
-        <v>0.98</v>
+        <v>0.982</v>
       </c>
       <c r="G411" t="n">
-        <v>0.969</v>
+        <v>0.971</v>
       </c>
       <c r="H411" t="n">
         <v>1</v>
@@ -18140,10 +18140,10 @@
         <v>0.864</v>
       </c>
       <c r="G412" t="n">
-        <v>0.833</v>
+        <v>0.835</v>
       </c>
       <c r="H412" t="n">
-        <v>0.661</v>
+        <v>0.662</v>
       </c>
       <c r="I412" t="n">
         <v>1</v>
@@ -18322,13 +18322,13 @@
         <v>16</v>
       </c>
       <c r="F417" t="n">
-        <v>0.364</v>
+        <v>0.38</v>
       </c>
       <c r="G417" t="n">
         <v>0.315</v>
       </c>
       <c r="H417" t="n">
-        <v>0.491</v>
+        <v>0.336</v>
       </c>
       <c r="I417" t="n">
         <v>1</v>
@@ -18405,7 +18405,7 @@
         <v>0.491</v>
       </c>
       <c r="I419" t="n">
-        <v>0.883</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="420">
@@ -18479,7 +18479,7 @@
         <v>0.607</v>
       </c>
       <c r="I421" t="n">
-        <v>0.883</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="422">
@@ -18590,7 +18590,7 @@
         <v>0.5659999999999999</v>
       </c>
       <c r="I424" t="n">
-        <v>0.883</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="425">
@@ -18692,16 +18692,16 @@
         <v>10</v>
       </c>
       <c r="F427" t="n">
-        <v>0.6</v>
+        <v>0.675</v>
       </c>
       <c r="G427" t="n">
-        <v>0.775</v>
+        <v>0.825</v>
       </c>
       <c r="H427" t="n">
-        <v>0.0261</v>
+        <v>0.0438</v>
       </c>
       <c r="I427" t="n">
-        <v>0.209</v>
+        <v>0.351</v>
       </c>
     </row>
     <row r="428">
@@ -18732,13 +18732,13 @@
         <v>0.769</v>
       </c>
       <c r="G428" t="n">
-        <v>0.714</v>
+        <v>0.725</v>
       </c>
       <c r="H428" t="n">
-        <v>0.498</v>
+        <v>0.609</v>
       </c>
       <c r="I428" t="n">
-        <v>0.883</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="429">
@@ -18775,7 +18775,7 @@
         <v>0.415</v>
       </c>
       <c r="I429" t="n">
-        <v>0.883</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="430">
@@ -18849,7 +18849,7 @@
         <v>0.529</v>
       </c>
       <c r="I431" t="n">
-        <v>0.883</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="432">
@@ -18886,7 +18886,7 @@
         <v>0.398</v>
       </c>
       <c r="I432" t="n">
-        <v>0.883</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="433">
@@ -18914,7 +18914,7 @@
         <v>16</v>
       </c>
       <c r="F433" t="n">
-        <v>0.727</v>
+        <v>0.745</v>
       </c>
       <c r="G433" t="n">
         <v>0.727</v>
@@ -18960,7 +18960,7 @@
         <v>0.312</v>
       </c>
       <c r="I434" t="n">
-        <v>0.833</v>
+        <v>0.908</v>
       </c>
     </row>
     <row r="435">
@@ -19099,13 +19099,13 @@
         <v>5</v>
       </c>
       <c r="F438" t="n">
-        <v>0.8</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G438" t="n">
         <v>0.787</v>
       </c>
       <c r="H438" t="n">
-        <v>0.887</v>
+        <v>0.774</v>
       </c>
       <c r="I438" t="n">
         <v>1</v>
@@ -19284,16 +19284,16 @@
         <v>10</v>
       </c>
       <c r="F443" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="G443" t="n">
-        <v>0.833</v>
+        <v>0.867</v>
       </c>
       <c r="H443" t="n">
-        <v>0.306</v>
+        <v>0.341</v>
       </c>
       <c r="I443" t="n">
-        <v>0.833</v>
+        <v>0.908</v>
       </c>
     </row>
     <row r="444">
@@ -19506,16 +19506,16 @@
         <v>16</v>
       </c>
       <c r="F449" t="n">
-        <v>0.433</v>
+        <v>0.46</v>
       </c>
       <c r="G449" t="n">
         <v>0.7</v>
       </c>
       <c r="H449" t="n">
-        <v>4.85e-06</v>
+        <v>3.88e-05</v>
       </c>
       <c r="I449" t="n">
-        <v>7.76e-05</v>
+        <v>0.000621</v>
       </c>
     </row>
     <row r="450">
@@ -19691,16 +19691,16 @@
         <v>5</v>
       </c>
       <c r="F454" t="n">
-        <v>0.949</v>
+        <v>0.962</v>
       </c>
       <c r="G454" t="n">
         <v>1</v>
       </c>
       <c r="H454" t="n">
-        <v>0.123</v>
+        <v>0.248</v>
       </c>
       <c r="I454" t="n">
-        <v>0.248</v>
+        <v>0.444</v>
       </c>
     </row>
     <row r="455">
@@ -19876,10 +19876,10 @@
         <v>10</v>
       </c>
       <c r="F459" t="n">
-        <v>0.98</v>
+        <v>0.982</v>
       </c>
       <c r="G459" t="n">
-        <v>0.966</v>
+        <v>0.969</v>
       </c>
       <c r="H459" t="n">
         <v>1</v>
@@ -19959,7 +19959,7 @@
         <v>0.124</v>
       </c>
       <c r="I461" t="n">
-        <v>0.248</v>
+        <v>0.283</v>
       </c>
     </row>
     <row r="462">
@@ -20098,16 +20098,16 @@
         <v>16</v>
       </c>
       <c r="F465" t="n">
-        <v>0.364</v>
+        <v>0.38</v>
       </c>
       <c r="G465" t="n">
         <v>0.647</v>
       </c>
       <c r="H465" t="n">
-        <v>0.00519</v>
+        <v>0.00953</v>
       </c>
       <c r="I465" t="n">
-        <v>0.0277</v>
+        <v>0.0508</v>
       </c>
     </row>
     <row r="466">
@@ -20468,13 +20468,13 @@
         <v>10</v>
       </c>
       <c r="F475" t="n">
-        <v>0.6</v>
+        <v>0.675</v>
       </c>
       <c r="G475" t="n">
-        <v>0.713</v>
+        <v>0.775</v>
       </c>
       <c r="H475" t="n">
-        <v>0.183</v>
+        <v>0.215</v>
       </c>
       <c r="I475" t="n">
         <v>0.642</v>
@@ -20690,16 +20690,16 @@
         <v>16</v>
       </c>
       <c r="F481" t="n">
-        <v>0.727</v>
+        <v>0.745</v>
       </c>
       <c r="G481" t="n">
         <v>0.4</v>
       </c>
       <c r="H481" t="n">
-        <v>0.000985</v>
+        <v>0.000461</v>
       </c>
       <c r="I481" t="n">
-        <v>0.00788</v>
+        <v>0.00369</v>
       </c>
     </row>
   </sheetData>

--- a/eval/learning-curve/results/statistical_tests_full150.xlsx
+++ b/eval/learning-curve/results/statistical_tests_full150.xlsx
@@ -503,22 +503,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0552</v>
+        <v>0.0629</v>
       </c>
       <c r="F2" t="n">
-        <v>0.831</v>
+        <v>0.844</v>
       </c>
       <c r="G2" t="n">
-        <v>0.862</v>
+        <v>0.875</v>
       </c>
       <c r="H2" t="n">
         <v>0.109</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0881</v>
+        <v>0.0842</v>
       </c>
       <c r="J2" t="n">
-        <v>0.11</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="3">
@@ -543,22 +543,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.0701</v>
+        <v>0.0785</v>
       </c>
       <c r="F3" t="n">
-        <v>0.831</v>
+        <v>0.844</v>
       </c>
       <c r="G3" t="n">
-        <v>0.862</v>
+        <v>0.875</v>
       </c>
       <c r="H3" t="n">
         <v>0.109</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0881</v>
+        <v>0.0842</v>
       </c>
       <c r="J3" t="n">
-        <v>0.14</v>
+        <v>0.196</v>
       </c>
     </row>
     <row r="4">
@@ -583,22 +583,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.162</v>
+        <v>0.276</v>
       </c>
       <c r="F4" t="n">
-        <v>0.831</v>
+        <v>0.844</v>
       </c>
       <c r="G4" t="n">
-        <v>0.855</v>
+        <v>0.862</v>
       </c>
       <c r="H4" t="n">
         <v>0.109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.27</v>
+        <v>0.345</v>
       </c>
     </row>
     <row r="5">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.201</v>
+        <v>0.28</v>
       </c>
       <c r="F5" t="n">
-        <v>0.831</v>
+        <v>0.844</v>
       </c>
       <c r="G5" t="n">
-        <v>0.855</v>
+        <v>0.862</v>
       </c>
       <c r="H5" t="n">
         <v>0.109</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.304</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="6">
@@ -663,22 +663,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.26</v>
+        <v>0.41</v>
       </c>
       <c r="F6" t="n">
-        <v>0.831</v>
+        <v>0.844</v>
       </c>
       <c r="G6" t="n">
-        <v>0.848</v>
+        <v>0.857</v>
       </c>
       <c r="H6" t="n">
         <v>0.109</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.325</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="7">
@@ -703,22 +703,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.334</v>
+        <v>0.495</v>
       </c>
       <c r="F7" t="n">
-        <v>0.831</v>
+        <v>0.844</v>
       </c>
       <c r="G7" t="n">
-        <v>0.848</v>
+        <v>0.857</v>
       </c>
       <c r="H7" t="n">
         <v>0.109</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.334</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="8">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.0281</v>
+        <v>0.0955</v>
       </c>
       <c r="F8" t="n">
-        <v>0.831</v>
+        <v>0.844</v>
       </c>
       <c r="G8" t="n">
-        <v>0.869</v>
+        <v>0.873</v>
       </c>
       <c r="H8" t="n">
         <v>0.109</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0709</v>
+        <v>0.0698</v>
       </c>
       <c r="J8" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="9">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.0689</v>
+        <v>0.139</v>
       </c>
       <c r="F9" t="n">
-        <v>0.831</v>
+        <v>0.844</v>
       </c>
       <c r="G9" t="n">
-        <v>0.869</v>
+        <v>0.873</v>
       </c>
       <c r="H9" t="n">
         <v>0.109</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0709</v>
+        <v>0.0698</v>
       </c>
       <c r="J9" t="n">
-        <v>0.14</v>
+        <v>0.233</v>
       </c>
     </row>
     <row r="10">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.000781</v>
+        <v>0.00116</v>
       </c>
       <c r="F10" t="n">
-        <v>0.831</v>
+        <v>0.844</v>
       </c>
       <c r="G10" t="n">
-        <v>0.898</v>
+        <v>0.91</v>
       </c>
       <c r="H10" t="n">
         <v>0.109</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0654</v>
+        <v>0.0633</v>
       </c>
       <c r="J10" t="n">
-        <v>0.00781</v>
+        <v>0.0116</v>
       </c>
     </row>
     <row r="11">
@@ -863,22 +863,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0009790000000000001</v>
+        <v>0.0015</v>
       </c>
       <c r="F11" t="n">
-        <v>0.831</v>
+        <v>0.844</v>
       </c>
       <c r="G11" t="n">
-        <v>0.898</v>
+        <v>0.91</v>
       </c>
       <c r="H11" t="n">
         <v>0.109</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0654</v>
+        <v>0.0633</v>
       </c>
       <c r="J11" t="n">
-        <v>0.00979</v>
+        <v>0.0094</v>
       </c>
     </row>
     <row r="12">
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.0493</v>
+        <v>0.0303</v>
       </c>
       <c r="F12" t="n">
-        <v>0.801</v>
+        <v>0.803</v>
       </c>
       <c r="G12" t="n">
-        <v>0.823</v>
+        <v>0.826</v>
       </c>
       <c r="H12" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="I12" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="J12" t="n">
-        <v>0.11</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="13">
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.0495</v>
+        <v>0.0353</v>
       </c>
       <c r="F13" t="n">
-        <v>0.801</v>
+        <v>0.803</v>
       </c>
       <c r="G13" t="n">
-        <v>0.823</v>
+        <v>0.826</v>
       </c>
       <c r="H13" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="I13" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="J13" t="n">
-        <v>0.14</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="14">
@@ -983,22 +983,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.218</v>
+        <v>0.149</v>
       </c>
       <c r="F14" t="n">
-        <v>0.801</v>
+        <v>0.803</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.821</v>
       </c>
       <c r="H14" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="I14" t="n">
-        <v>0.168</v>
+        <v>0.167</v>
       </c>
       <c r="J14" t="n">
-        <v>0.311</v>
+        <v>0.248</v>
       </c>
     </row>
     <row r="15">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.213</v>
+        <v>0.14</v>
       </c>
       <c r="F15" t="n">
-        <v>0.801</v>
+        <v>0.803</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.821</v>
       </c>
       <c r="H15" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="I15" t="n">
-        <v>0.168</v>
+        <v>0.167</v>
       </c>
       <c r="J15" t="n">
-        <v>0.304</v>
+        <v>0.233</v>
       </c>
     </row>
     <row r="16">
@@ -1063,22 +1063,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.302</v>
+        <v>0.239</v>
       </c>
       <c r="F16" t="n">
-        <v>0.801</v>
+        <v>0.803</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.819</v>
       </c>
       <c r="H16" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="I16" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="J16" t="n">
-        <v>0.336</v>
+        <v>0.341</v>
       </c>
     </row>
     <row r="17">
@@ -1103,22 +1103,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.3</v>
+        <v>0.272</v>
       </c>
       <c r="F17" t="n">
-        <v>0.801</v>
+        <v>0.803</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.819</v>
       </c>
       <c r="H17" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="I17" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="J17" t="n">
-        <v>0.334</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="18">
@@ -1143,22 +1143,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.418</v>
+        <v>0.358</v>
       </c>
       <c r="F18" t="n">
-        <v>0.801</v>
+        <v>0.803</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.819</v>
       </c>
       <c r="H18" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="I18" t="n">
-        <v>0.184</v>
+        <v>0.182</v>
       </c>
       <c r="J18" t="n">
-        <v>0.418</v>
+        <v>0.398</v>
       </c>
     </row>
     <row r="19">
@@ -1183,22 +1183,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.325</v>
+        <v>0.326</v>
       </c>
       <c r="F19" t="n">
-        <v>0.801</v>
+        <v>0.803</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.819</v>
       </c>
       <c r="H19" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="I19" t="n">
-        <v>0.184</v>
+        <v>0.182</v>
       </c>
       <c r="J19" t="n">
-        <v>0.334</v>
+        <v>0.362</v>
       </c>
     </row>
     <row r="20">
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0137</v>
+        <v>0.0144</v>
       </c>
       <c r="F20" t="n">
-        <v>0.801</v>
+        <v>0.803</v>
       </c>
       <c r="G20" t="n">
-        <v>0.851</v>
+        <v>0.854</v>
       </c>
       <c r="H20" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0917</v>
+        <v>0.0912</v>
       </c>
       <c r="J20" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1263,22 +1263,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.0023</v>
+        <v>0.00188</v>
       </c>
       <c r="F21" t="n">
-        <v>0.801</v>
+        <v>0.803</v>
       </c>
       <c r="G21" t="n">
-        <v>0.851</v>
+        <v>0.854</v>
       </c>
       <c r="H21" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0917</v>
+        <v>0.0912</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0115</v>
+        <v>0.0094</v>
       </c>
     </row>
     <row r="22">
@@ -1303,22 +1303,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.852</v>
+        <v>0.842</v>
       </c>
       <c r="F22" t="n">
-        <v>0.843</v>
+        <v>0.868</v>
       </c>
       <c r="G22" t="n">
-        <v>0.836</v>
+        <v>0.861</v>
       </c>
       <c r="H22" t="n">
-        <v>0.16</v>
+        <v>0.156</v>
       </c>
       <c r="I22" t="n">
-        <v>0.134</v>
+        <v>0.117</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="23">
@@ -1343,22 +1343,22 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.597</v>
+        <v>0.495</v>
       </c>
       <c r="F23" t="n">
-        <v>0.843</v>
+        <v>0.868</v>
       </c>
       <c r="G23" t="n">
-        <v>0.836</v>
+        <v>0.861</v>
       </c>
       <c r="H23" t="n">
-        <v>0.16</v>
+        <v>0.156</v>
       </c>
       <c r="I23" t="n">
-        <v>0.134</v>
+        <v>0.117</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="24">
@@ -1383,22 +1383,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.629</v>
       </c>
       <c r="F24" t="n">
-        <v>0.843</v>
+        <v>0.868</v>
       </c>
       <c r="G24" t="n">
-        <v>0.84</v>
+        <v>0.848</v>
       </c>
       <c r="H24" t="n">
-        <v>0.16</v>
+        <v>0.156</v>
       </c>
       <c r="I24" t="n">
-        <v>0.137</v>
+        <v>0.132</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="25">
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.632</v>
+        <v>0.348</v>
       </c>
       <c r="F25" t="n">
-        <v>0.843</v>
+        <v>0.868</v>
       </c>
       <c r="G25" t="n">
-        <v>0.84</v>
+        <v>0.848</v>
       </c>
       <c r="H25" t="n">
-        <v>0.16</v>
+        <v>0.156</v>
       </c>
       <c r="I25" t="n">
-        <v>0.137</v>
+        <v>0.132</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="26">
@@ -1463,22 +1463,22 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.38</v>
+        <v>0.799</v>
       </c>
       <c r="F26" t="n">
-        <v>0.843</v>
+        <v>0.868</v>
       </c>
       <c r="G26" t="n">
-        <v>0.867</v>
+        <v>0.876</v>
       </c>
       <c r="H26" t="n">
-        <v>0.16</v>
+        <v>0.156</v>
       </c>
       <c r="I26" t="n">
-        <v>0.116</v>
+        <v>0.104</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="27">
@@ -1503,22 +1503,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.632</v>
+        <v>0.609</v>
       </c>
       <c r="F27" t="n">
-        <v>0.843</v>
+        <v>0.868</v>
       </c>
       <c r="G27" t="n">
-        <v>0.867</v>
+        <v>0.876</v>
       </c>
       <c r="H27" t="n">
-        <v>0.16</v>
+        <v>0.156</v>
       </c>
       <c r="I27" t="n">
-        <v>0.116</v>
+        <v>0.104</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="28">
@@ -1543,22 +1543,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.711</v>
+        <v>0.74</v>
       </c>
       <c r="F28" t="n">
-        <v>0.843</v>
+        <v>0.868</v>
       </c>
       <c r="G28" t="n">
-        <v>0.854</v>
+        <v>0.857</v>
       </c>
       <c r="H28" t="n">
-        <v>0.16</v>
+        <v>0.156</v>
       </c>
       <c r="I28" t="n">
-        <v>0.104</v>
+        <v>0.1</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="29">
@@ -1583,22 +1583,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.91</v>
+        <v>0.427</v>
       </c>
       <c r="F29" t="n">
-        <v>0.843</v>
+        <v>0.868</v>
       </c>
       <c r="G29" t="n">
-        <v>0.854</v>
+        <v>0.857</v>
       </c>
       <c r="H29" t="n">
-        <v>0.16</v>
+        <v>0.156</v>
       </c>
       <c r="I29" t="n">
-        <v>0.104</v>
+        <v>0.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.91</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="30">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.0588</v>
+        <v>0.093</v>
       </c>
       <c r="F30" t="n">
-        <v>0.843</v>
+        <v>0.868</v>
       </c>
       <c r="G30" t="n">
-        <v>0.907</v>
+        <v>0.926</v>
       </c>
       <c r="H30" t="n">
-        <v>0.16</v>
+        <v>0.156</v>
       </c>
       <c r="I30" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.054</v>
       </c>
       <c r="J30" t="n">
-        <v>0.294</v>
+        <v>0.465</v>
       </c>
     </row>
     <row r="31">
@@ -1663,22 +1663,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.112</v>
+        <v>0.221</v>
       </c>
       <c r="F31" t="n">
-        <v>0.843</v>
+        <v>0.868</v>
       </c>
       <c r="G31" t="n">
-        <v>0.907</v>
+        <v>0.926</v>
       </c>
       <c r="H31" t="n">
-        <v>0.16</v>
+        <v>0.156</v>
       </c>
       <c r="I31" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.054</v>
       </c>
       <c r="J31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="32">
@@ -1703,22 +1703,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.471</v>
+        <v>0.431</v>
       </c>
       <c r="F32" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="G32" t="n">
-        <v>0.801</v>
+        <v>0.802</v>
       </c>
       <c r="H32" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="I32" t="n">
-        <v>0.194</v>
+        <v>0.192</v>
       </c>
       <c r="J32" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="33">
@@ -1743,22 +1743,22 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.46</v>
+        <v>0.427</v>
       </c>
       <c r="F33" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="G33" t="n">
-        <v>0.801</v>
+        <v>0.802</v>
       </c>
       <c r="H33" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="I33" t="n">
-        <v>0.194</v>
+        <v>0.192</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="34">
@@ -1783,22 +1783,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.892</v>
+        <v>0.855</v>
       </c>
       <c r="F34" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="G34" t="n">
-        <v>0.796</v>
+        <v>0.798</v>
       </c>
       <c r="H34" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="I34" t="n">
-        <v>0.179</v>
+        <v>0.177</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="35">
@@ -1823,22 +1823,22 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.744</v>
+        <v>0.782</v>
       </c>
       <c r="F35" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="G35" t="n">
-        <v>0.796</v>
+        <v>0.798</v>
       </c>
       <c r="H35" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="I35" t="n">
-        <v>0.179</v>
+        <v>0.177</v>
       </c>
       <c r="J35" t="n">
-        <v>0.827</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="36">
@@ -1863,22 +1863,22 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.758</v>
+        <v>0.731</v>
       </c>
       <c r="F36" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="G36" t="n">
-        <v>0.799</v>
+        <v>0.8</v>
       </c>
       <c r="H36" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="I36" t="n">
-        <v>0.187</v>
+        <v>0.185</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="37">
@@ -1906,19 +1906,19 @@
         <v>0.65</v>
       </c>
       <c r="F37" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="G37" t="n">
-        <v>0.799</v>
+        <v>0.8</v>
       </c>
       <c r="H37" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="I37" t="n">
-        <v>0.187</v>
+        <v>0.185</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="38">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.738</v>
+        <v>0.709</v>
       </c>
       <c r="F38" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8</v>
+        <v>0.801</v>
       </c>
       <c r="H38" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="I38" t="n">
-        <v>0.192</v>
+        <v>0.189</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="39">
@@ -1986,19 +1986,19 @@
         <v>0.597</v>
       </c>
       <c r="F39" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8</v>
+        <v>0.801</v>
       </c>
       <c r="H39" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="I39" t="n">
-        <v>0.192</v>
+        <v>0.189</v>
       </c>
       <c r="J39" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="40">
@@ -2023,22 +2023,22 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.00072</v>
+        <v>0.000852</v>
       </c>
       <c r="F40" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="G40" t="n">
-        <v>0.912</v>
+        <v>0.916</v>
       </c>
       <c r="H40" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="I40" t="n">
-        <v>0.103</v>
+        <v>0.0941</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0072</v>
+        <v>0.00852</v>
       </c>
     </row>
     <row r="41">
@@ -2066,16 +2066,16 @@
         <v>0.000987</v>
       </c>
       <c r="F41" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="G41" t="n">
-        <v>0.912</v>
+        <v>0.916</v>
       </c>
       <c r="H41" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="I41" t="n">
-        <v>0.103</v>
+        <v>0.0941</v>
       </c>
       <c r="J41" t="n">
         <v>0.00987</v>
@@ -2103,22 +2103,22 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.18</v>
+        <v>0.215</v>
       </c>
       <c r="F42" t="n">
-        <v>0.77</v>
+        <v>0.783</v>
       </c>
       <c r="G42" t="n">
-        <v>0.805</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>0.149</v>
+        <v>0.157</v>
       </c>
       <c r="I42" t="n">
-        <v>0.169</v>
+        <v>0.171</v>
       </c>
       <c r="J42" t="n">
-        <v>0.225</v>
+        <v>0.269</v>
       </c>
     </row>
     <row r="43">
@@ -2146,19 +2146,19 @@
         <v>0.133</v>
       </c>
       <c r="F43" t="n">
-        <v>0.77</v>
+        <v>0.783</v>
       </c>
       <c r="G43" t="n">
-        <v>0.805</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>0.149</v>
+        <v>0.157</v>
       </c>
       <c r="I43" t="n">
-        <v>0.169</v>
+        <v>0.171</v>
       </c>
       <c r="J43" t="n">
-        <v>0.175</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="44">
@@ -2183,22 +2183,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.728</v>
+        <v>0.661</v>
       </c>
       <c r="F44" t="n">
-        <v>0.77</v>
+        <v>0.783</v>
       </c>
       <c r="G44" t="n">
-        <v>0.779</v>
+        <v>0.795</v>
       </c>
       <c r="H44" t="n">
-        <v>0.149</v>
+        <v>0.157</v>
       </c>
       <c r="I44" t="n">
-        <v>0.131</v>
+        <v>0.137</v>
       </c>
       <c r="J44" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.734</v>
       </c>
     </row>
     <row r="45">
@@ -2223,22 +2223,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.91</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>0.77</v>
+        <v>0.783</v>
       </c>
       <c r="G45" t="n">
-        <v>0.779</v>
+        <v>0.795</v>
       </c>
       <c r="H45" t="n">
-        <v>0.149</v>
+        <v>0.157</v>
       </c>
       <c r="I45" t="n">
-        <v>0.131</v>
+        <v>0.137</v>
       </c>
       <c r="J45" t="n">
-        <v>0.91</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="46">
@@ -2263,22 +2263,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.882</v>
+        <v>0.845</v>
       </c>
       <c r="F46" t="n">
-        <v>0.77</v>
+        <v>0.783</v>
       </c>
       <c r="G46" t="n">
-        <v>0.774</v>
+        <v>0.789</v>
       </c>
       <c r="H46" t="n">
-        <v>0.149</v>
+        <v>0.157</v>
       </c>
       <c r="I46" t="n">
-        <v>0.124</v>
+        <v>0.135</v>
       </c>
       <c r="J46" t="n">
-        <v>0.882</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="47">
@@ -2303,22 +2303,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.897</v>
+        <v>0.754</v>
       </c>
       <c r="F47" t="n">
-        <v>0.77</v>
+        <v>0.783</v>
       </c>
       <c r="G47" t="n">
-        <v>0.774</v>
+        <v>0.789</v>
       </c>
       <c r="H47" t="n">
-        <v>0.149</v>
+        <v>0.157</v>
       </c>
       <c r="I47" t="n">
-        <v>0.124</v>
+        <v>0.135</v>
       </c>
       <c r="J47" t="n">
-        <v>0.91</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="48">
@@ -2343,22 +2343,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.123</v>
+        <v>0.189</v>
       </c>
       <c r="F48" t="n">
-        <v>0.77</v>
+        <v>0.783</v>
       </c>
       <c r="G48" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="H48" t="n">
-        <v>0.149</v>
+        <v>0.157</v>
       </c>
       <c r="I48" t="n">
-        <v>0.127</v>
+        <v>0.132</v>
       </c>
       <c r="J48" t="n">
-        <v>0.176</v>
+        <v>0.269</v>
       </c>
     </row>
     <row r="49">
@@ -2383,22 +2383,22 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.116</v>
+        <v>0.158</v>
       </c>
       <c r="F49" t="n">
-        <v>0.77</v>
+        <v>0.783</v>
       </c>
       <c r="G49" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="H49" t="n">
-        <v>0.149</v>
+        <v>0.157</v>
       </c>
       <c r="I49" t="n">
-        <v>0.127</v>
+        <v>0.132</v>
       </c>
       <c r="J49" t="n">
-        <v>0.175</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="50">
@@ -2423,22 +2423,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.0138</v>
+        <v>0.0155</v>
       </c>
       <c r="F50" t="n">
-        <v>0.77</v>
+        <v>0.783</v>
       </c>
       <c r="G50" t="n">
-        <v>0.848</v>
+        <v>0.861</v>
       </c>
       <c r="H50" t="n">
-        <v>0.149</v>
+        <v>0.157</v>
       </c>
       <c r="I50" t="n">
-        <v>0.127</v>
+        <v>0.13</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0407</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="51">
@@ -2463,22 +2463,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.0186</v>
+        <v>0.0199</v>
       </c>
       <c r="F51" t="n">
-        <v>0.77</v>
+        <v>0.783</v>
       </c>
       <c r="G51" t="n">
-        <v>0.848</v>
+        <v>0.861</v>
       </c>
       <c r="H51" t="n">
-        <v>0.149</v>
+        <v>0.157</v>
       </c>
       <c r="I51" t="n">
-        <v>0.127</v>
+        <v>0.13</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0465</v>
+        <v>0.0498</v>
       </c>
     </row>
     <row r="52">
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.0253</v>
+        <v>0.017</v>
       </c>
       <c r="F52" t="n">
-        <v>0.762</v>
+        <v>0.767</v>
       </c>
       <c r="G52" t="n">
-        <v>0.804</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="I52" t="n">
-        <v>0.173</v>
+        <v>0.176</v>
       </c>
       <c r="J52" t="n">
-        <v>0.0506</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="53">
@@ -2543,22 +2543,22 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.0356</v>
+        <v>0.0309</v>
       </c>
       <c r="F53" t="n">
-        <v>0.762</v>
+        <v>0.767</v>
       </c>
       <c r="G53" t="n">
-        <v>0.804</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="I53" t="n">
-        <v>0.173</v>
+        <v>0.176</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0712</v>
+        <v>0.0618</v>
       </c>
     </row>
     <row r="54">
@@ -2583,22 +2583,22 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.00231</v>
+        <v>0.00143</v>
       </c>
       <c r="F54" t="n">
-        <v>0.762</v>
+        <v>0.767</v>
       </c>
       <c r="G54" t="n">
-        <v>0.82</v>
+        <v>0.829</v>
       </c>
       <c r="H54" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="I54" t="n">
-        <v>0.152</v>
+        <v>0.156</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0231</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="55">
@@ -2623,22 +2623,22 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.00521</v>
+        <v>0.00351</v>
       </c>
       <c r="F55" t="n">
-        <v>0.762</v>
+        <v>0.767</v>
       </c>
       <c r="G55" t="n">
-        <v>0.82</v>
+        <v>0.829</v>
       </c>
       <c r="H55" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="I55" t="n">
-        <v>0.152</v>
+        <v>0.156</v>
       </c>
       <c r="J55" t="n">
-        <v>0.0314</v>
+        <v>0.0321</v>
       </c>
     </row>
     <row r="56">
@@ -2663,22 +2663,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.0163</v>
+        <v>0.0115</v>
       </c>
       <c r="F56" t="n">
-        <v>0.762</v>
+        <v>0.767</v>
       </c>
       <c r="G56" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="I56" t="n">
-        <v>0.149</v>
+        <v>0.152</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0407</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="57">
@@ -2703,22 +2703,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.0182</v>
+        <v>0.0146</v>
       </c>
       <c r="F57" t="n">
-        <v>0.762</v>
+        <v>0.767</v>
       </c>
       <c r="G57" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="I57" t="n">
-        <v>0.149</v>
+        <v>0.152</v>
       </c>
       <c r="J57" t="n">
-        <v>0.0465</v>
+        <v>0.0487</v>
       </c>
     </row>
     <row r="58">
@@ -2743,22 +2743,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.00933</v>
+        <v>0.00593</v>
       </c>
       <c r="F58" t="n">
-        <v>0.762</v>
+        <v>0.767</v>
       </c>
       <c r="G58" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.826</v>
       </c>
       <c r="H58" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="I58" t="n">
-        <v>0.152</v>
+        <v>0.156</v>
       </c>
       <c r="J58" t="n">
-        <v>0.0407</v>
+        <v>0.0297</v>
       </c>
     </row>
     <row r="59">
@@ -2783,22 +2783,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.00629</v>
+        <v>0.00641</v>
       </c>
       <c r="F59" t="n">
-        <v>0.762</v>
+        <v>0.767</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.826</v>
       </c>
       <c r="H59" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="I59" t="n">
-        <v>0.152</v>
+        <v>0.156</v>
       </c>
       <c r="J59" t="n">
-        <v>0.0314</v>
+        <v>0.0321</v>
       </c>
     </row>
     <row r="60">
@@ -2823,22 +2823,22 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.0853</v>
+        <v>0.0833</v>
       </c>
       <c r="F60" t="n">
-        <v>0.762</v>
+        <v>0.767</v>
       </c>
       <c r="G60" t="n">
-        <v>0.701</v>
+        <v>0.709</v>
       </c>
       <c r="H60" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="I60" t="n">
-        <v>0.159</v>
+        <v>0.162</v>
       </c>
       <c r="J60" t="n">
-        <v>0.142</v>
+        <v>0.139</v>
       </c>
     </row>
     <row r="61">
@@ -2866,19 +2866,19 @@
         <v>0.14</v>
       </c>
       <c r="F61" t="n">
-        <v>0.762</v>
+        <v>0.767</v>
       </c>
       <c r="G61" t="n">
-        <v>0.701</v>
+        <v>0.709</v>
       </c>
       <c r="H61" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="I61" t="n">
-        <v>0.159</v>
+        <v>0.162</v>
       </c>
       <c r="J61" t="n">
-        <v>0.175</v>
+        <v>0.198</v>
       </c>
     </row>
   </sheetData>
@@ -2976,7 +2976,7 @@
         <v>0.149</v>
       </c>
       <c r="I2" t="n">
-        <v>0.478</v>
+        <v>0.342</v>
       </c>
     </row>
     <row r="3">
@@ -3041,16 +3041,16 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0.973</v>
+        <v>0.98</v>
       </c>
       <c r="G4" t="n">
         <v>0.927</v>
       </c>
       <c r="H4" t="n">
-        <v>0.109</v>
+        <v>0.0517</v>
       </c>
       <c r="I4" t="n">
-        <v>0.437</v>
+        <v>0.276</v>
       </c>
     </row>
     <row r="5">
@@ -3078,16 +3078,16 @@
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>0.947</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.927</v>
+        <v>0.987</v>
       </c>
       <c r="H5" t="n">
-        <v>0.637</v>
+        <v>0.498</v>
       </c>
       <c r="I5" t="n">
-        <v>0.783</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="6">
@@ -3115,16 +3115,16 @@
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G6" t="n">
-        <v>0.88</v>
+        <v>0.873</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0825</v>
+        <v>0.262</v>
       </c>
       <c r="I6" t="n">
-        <v>0.437</v>
+        <v>0.466</v>
       </c>
     </row>
     <row r="7">
@@ -3152,16 +3152,16 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.887</v>
+        <v>0.893</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0398</v>
+        <v>0.0364</v>
       </c>
       <c r="I7" t="n">
-        <v>0.319</v>
+        <v>0.276</v>
       </c>
     </row>
     <row r="8">
@@ -3189,16 +3189,16 @@
         <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>0.847</v>
+        <v>0.86</v>
       </c>
       <c r="G8" t="n">
-        <v>0.887</v>
+        <v>0.92</v>
       </c>
       <c r="H8" t="n">
-        <v>0.396</v>
+        <v>0.139</v>
       </c>
       <c r="I8" t="n">
-        <v>0.634</v>
+        <v>0.342</v>
       </c>
     </row>
     <row r="9">
@@ -3235,7 +3235,7 @@
         <v>0.572</v>
       </c>
       <c r="I9" t="n">
-        <v>0.783</v>
+        <v>0.761</v>
       </c>
     </row>
     <row r="10">
@@ -3266,13 +3266,13 @@
         <v>0.6870000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.707</v>
+        <v>0.713</v>
       </c>
       <c r="H10" t="n">
-        <v>0.802</v>
+        <v>0.706</v>
       </c>
       <c r="I10" t="n">
-        <v>0.855</v>
+        <v>0.771</v>
       </c>
     </row>
     <row r="11">
@@ -3300,16 +3300,16 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>0.847</v>
+        <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.793</v>
+        <v>0.833</v>
       </c>
       <c r="H11" t="n">
-        <v>0.293</v>
+        <v>0.126</v>
       </c>
       <c r="I11" t="n">
-        <v>0.521</v>
+        <v>0.342</v>
       </c>
     </row>
     <row r="12">
@@ -3337,16 +3337,16 @@
         <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>0.707</v>
+        <v>0.713</v>
       </c>
       <c r="G12" t="n">
         <v>0.78</v>
       </c>
       <c r="H12" t="n">
-        <v>0.186</v>
+        <v>0.232</v>
       </c>
       <c r="I12" t="n">
-        <v>0.496</v>
+        <v>0.464</v>
       </c>
     </row>
     <row r="13">
@@ -3420,7 +3420,7 @@
         <v>0.723</v>
       </c>
       <c r="I14" t="n">
-        <v>0.826</v>
+        <v>0.771</v>
       </c>
     </row>
     <row r="15">
@@ -3457,7 +3457,7 @@
         <v>0.618</v>
       </c>
       <c r="I15" t="n">
-        <v>0.783</v>
+        <v>0.761</v>
       </c>
     </row>
     <row r="16">
@@ -3485,16 +3485,16 @@
         <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>0.68</v>
+        <v>0.707</v>
       </c>
       <c r="G16" t="n">
-        <v>0.747</v>
+        <v>0.767</v>
       </c>
       <c r="H16" t="n">
-        <v>0.25</v>
+        <v>0.294</v>
       </c>
       <c r="I16" t="n">
-        <v>0.501</v>
+        <v>0.471</v>
       </c>
     </row>
     <row r="17">
@@ -3522,16 +3522,16 @@
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="G17" t="n">
-        <v>0.713</v>
+        <v>0.76</v>
       </c>
       <c r="H17" t="n">
-        <v>0.217</v>
+        <v>0.0745</v>
       </c>
       <c r="I17" t="n">
-        <v>0.496</v>
+        <v>0.298</v>
       </c>
     </row>
     <row r="18">
@@ -3568,7 +3568,7 @@
         <v>0.213</v>
       </c>
       <c r="I18" t="n">
-        <v>0.681</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="19">
@@ -3633,16 +3633,16 @@
         <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>0.929</v>
+        <v>0.931</v>
       </c>
       <c r="G20" t="n">
         <v>0.718</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0574</v>
+        <v>0.0323</v>
       </c>
       <c r="I20" t="n">
-        <v>0.341</v>
+        <v>0.258</v>
       </c>
     </row>
     <row r="21">
@@ -3670,16 +3670,16 @@
         <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.677</v>
+        <v>0.917</v>
       </c>
       <c r="H21" t="n">
-        <v>0.578</v>
+        <v>0.49</v>
       </c>
       <c r="I21" t="n">
-        <v>0.711</v>
+        <v>0.793</v>
       </c>
     </row>
     <row r="22">
@@ -3707,16 +3707,16 @@
         <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.963</v>
       </c>
       <c r="G22" t="n">
         <v>0.988</v>
       </c>
       <c r="H22" t="n">
-        <v>0.111</v>
+        <v>0.358</v>
       </c>
       <c r="I22" t="n">
-        <v>0.443</v>
+        <v>0.717</v>
       </c>
     </row>
     <row r="23">
@@ -3744,16 +3744,16 @@
         <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="G23" t="n">
-        <v>0.931</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>0.467</v>
+        <v>0.699</v>
       </c>
       <c r="I23" t="n">
-        <v>0.711</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="24">
@@ -3781,16 +3781,16 @@
         <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.957</v>
       </c>
       <c r="G24" t="n">
-        <v>0.915</v>
+        <v>0.929</v>
       </c>
       <c r="H24" t="n">
-        <v>0.548</v>
+        <v>0.514</v>
       </c>
       <c r="I24" t="n">
-        <v>0.711</v>
+        <v>0.793</v>
       </c>
     </row>
     <row r="25">
@@ -3827,7 +3827,7 @@
         <v>0.545</v>
       </c>
       <c r="I25" t="n">
-        <v>0.711</v>
+        <v>0.793</v>
       </c>
     </row>
     <row r="26">
@@ -3892,16 +3892,16 @@
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>0.913</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>0.902</v>
+        <v>0.912</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0.756</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="28">
@@ -3929,16 +3929,16 @@
         <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>0.873</v>
+        <v>0.889</v>
       </c>
       <c r="G28" t="n">
-        <v>0.914</v>
+        <v>0.915</v>
       </c>
       <c r="H28" t="n">
-        <v>0.574</v>
+        <v>0.771</v>
       </c>
       <c r="I28" t="n">
-        <v>0.711</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="29">
@@ -3975,7 +3975,7 @@
         <v>0.285</v>
       </c>
       <c r="I29" t="n">
-        <v>0.698</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="30">
@@ -4012,7 +4012,7 @@
         <v>0.704</v>
       </c>
       <c r="I30" t="n">
-        <v>0.805</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="31">
@@ -4077,16 +4077,16 @@
         <v>15</v>
       </c>
       <c r="F32" t="n">
-        <v>0.617</v>
+        <v>0.649</v>
       </c>
       <c r="G32" t="n">
-        <v>0.704</v>
+        <v>0.735</v>
       </c>
       <c r="H32" t="n">
-        <v>0.305</v>
+        <v>0.286</v>
       </c>
       <c r="I32" t="n">
-        <v>0.698</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="33">
@@ -4114,16 +4114,16 @@
         <v>16</v>
       </c>
       <c r="F33" t="n">
-        <v>0.509</v>
+        <v>0.556</v>
       </c>
       <c r="G33" t="n">
-        <v>0.594</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>0.366</v>
+        <v>0.176</v>
       </c>
       <c r="I33" t="n">
-        <v>0.711</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="34">
@@ -4160,7 +4160,7 @@
         <v>0.515</v>
       </c>
       <c r="I34" t="n">
-        <v>0.863</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="35">
@@ -4225,16 +4225,16 @@
         <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>0.929</v>
+        <v>0.964</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0.491</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0.863</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -4262,10 +4262,10 @@
         <v>4</v>
       </c>
       <c r="F37" t="n">
-        <v>0.955</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.955</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
@@ -4299,16 +4299,16 @@
         <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>0.752</v>
+        <v>0.762</v>
       </c>
       <c r="G38" t="n">
-        <v>0.832</v>
+        <v>0.822</v>
       </c>
       <c r="H38" t="n">
-        <v>0.225</v>
+        <v>0.386</v>
       </c>
       <c r="I38" t="n">
-        <v>0.599</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="39">
@@ -4336,16 +4336,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="G39" t="n">
         <v>0.88</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00212</v>
+        <v>0.00354</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0339</v>
+        <v>0.0566</v>
       </c>
     </row>
     <row r="40">
@@ -4373,16 +4373,16 @@
         <v>7</v>
       </c>
       <c r="F40" t="n">
-        <v>0.776</v>
+        <v>0.788</v>
       </c>
       <c r="G40" t="n">
-        <v>0.882</v>
+        <v>0.929</v>
       </c>
       <c r="H40" t="n">
-        <v>0.102</v>
+        <v>0.0141</v>
       </c>
       <c r="I40" t="n">
-        <v>0.599</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="41">
@@ -4419,7 +4419,7 @@
         <v>0.637</v>
       </c>
       <c r="I41" t="n">
-        <v>0.923</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="42">
@@ -4450,13 +4450,13 @@
         <v>0.635</v>
       </c>
       <c r="G42" t="n">
-        <v>0.667</v>
+        <v>0.675</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.596</v>
       </c>
       <c r="I42" t="n">
-        <v>0.923</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="43">
@@ -4484,16 +4484,16 @@
         <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>0.787</v>
+        <v>0.877</v>
       </c>
       <c r="G43" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.765</v>
       </c>
       <c r="H43" t="n">
-        <v>0.208</v>
+        <v>0.1</v>
       </c>
       <c r="I43" t="n">
-        <v>0.599</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="44">
@@ -4521,16 +4521,16 @@
         <v>11</v>
       </c>
       <c r="F44" t="n">
-        <v>0.604</v>
+        <v>0.609</v>
       </c>
       <c r="G44" t="n">
-        <v>0.703</v>
+        <v>0.707</v>
       </c>
       <c r="H44" t="n">
-        <v>0.212</v>
+        <v>0.214</v>
       </c>
       <c r="I44" t="n">
-        <v>0.599</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -4567,7 +4567,7 @@
         <v>0.383</v>
       </c>
       <c r="I45" t="n">
-        <v>0.863</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="46">
@@ -4641,7 +4641,7 @@
         <v>0.539</v>
       </c>
       <c r="I47" t="n">
-        <v>0.863</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="48">
@@ -4706,16 +4706,16 @@
         <v>16</v>
       </c>
       <c r="F49" t="n">
-        <v>0.527</v>
+        <v>0.526</v>
       </c>
       <c r="G49" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>0.118</v>
+        <v>0.125</v>
       </c>
       <c r="I49" t="n">
-        <v>0.599</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50">
@@ -4752,7 +4752,7 @@
         <v>0.532</v>
       </c>
       <c r="I50" t="n">
-        <v>0.763</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="51">
@@ -4817,16 +4817,16 @@
         <v>3</v>
       </c>
       <c r="F52" t="n">
-        <v>0.973</v>
+        <v>0.98</v>
       </c>
       <c r="G52" t="n">
         <v>0.9</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0157</v>
+        <v>0.00592</v>
       </c>
       <c r="I52" t="n">
-        <v>0.125</v>
+        <v>0.0474</v>
       </c>
     </row>
     <row r="53">
@@ -4854,16 +4854,16 @@
         <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>0.947</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.967</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0.0604</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0.242</v>
       </c>
     </row>
     <row r="54">
@@ -4891,16 +4891,16 @@
         <v>5</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G54" t="n">
         <v>0.84</v>
       </c>
       <c r="H54" t="n">
-        <v>0.453</v>
+        <v>0.759</v>
       </c>
       <c r="I54" t="n">
-        <v>0.724</v>
+        <v>0.867</v>
       </c>
     </row>
     <row r="55">
@@ -4928,16 +4928,16 @@
         <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="G55" t="n">
         <v>0.887</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0398</v>
+        <v>0.0558</v>
       </c>
       <c r="I55" t="n">
-        <v>0.212</v>
+        <v>0.242</v>
       </c>
     </row>
     <row r="56">
@@ -4965,16 +4965,16 @@
         <v>7</v>
       </c>
       <c r="F56" t="n">
-        <v>0.847</v>
+        <v>0.86</v>
       </c>
       <c r="G56" t="n">
-        <v>0.86</v>
+        <v>0.887</v>
       </c>
       <c r="H56" t="n">
-        <v>0.871</v>
+        <v>0.603</v>
       </c>
       <c r="I56" t="n">
-        <v>0.995</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="57">
@@ -5011,7 +5011,7 @@
         <v>0.572</v>
       </c>
       <c r="I57" t="n">
-        <v>0.763</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="58">
@@ -5048,7 +5048,7 @@
         <v>0.197</v>
       </c>
       <c r="I58" t="n">
-        <v>0.45</v>
+        <v>0.393</v>
       </c>
     </row>
     <row r="59">
@@ -5076,16 +5076,16 @@
         <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>0.847</v>
+        <v>0.9</v>
       </c>
       <c r="G59" t="n">
-        <v>0.78</v>
+        <v>0.833</v>
       </c>
       <c r="H59" t="n">
-        <v>0.182</v>
+        <v>0.126</v>
       </c>
       <c r="I59" t="n">
-        <v>0.45</v>
+        <v>0.335</v>
       </c>
     </row>
     <row r="60">
@@ -5113,16 +5113,16 @@
         <v>11</v>
       </c>
       <c r="F60" t="n">
-        <v>0.707</v>
+        <v>0.713</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0592</v>
+        <v>0.106</v>
       </c>
       <c r="I60" t="n">
-        <v>0.237</v>
+        <v>0.335</v>
       </c>
     </row>
     <row r="61">
@@ -5233,7 +5233,7 @@
         <v>0.865</v>
       </c>
       <c r="I63" t="n">
-        <v>0.995</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="64">
@@ -5261,16 +5261,16 @@
         <v>15</v>
       </c>
       <c r="F64" t="n">
-        <v>0.68</v>
+        <v>0.707</v>
       </c>
       <c r="G64" t="n">
         <v>0.747</v>
       </c>
       <c r="H64" t="n">
-        <v>0.25</v>
+        <v>0.517</v>
       </c>
       <c r="I64" t="n">
-        <v>0.501</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="65">
@@ -5298,16 +5298,16 @@
         <v>16</v>
       </c>
       <c r="F65" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="G65" t="n">
-        <v>0.727</v>
+        <v>0.74</v>
       </c>
       <c r="H65" t="n">
-        <v>0.136</v>
+        <v>0.166</v>
       </c>
       <c r="I65" t="n">
-        <v>0.436</v>
+        <v>0.379</v>
       </c>
     </row>
     <row r="66">
@@ -5409,16 +5409,16 @@
         <v>3</v>
       </c>
       <c r="F68" t="n">
-        <v>0.929</v>
+        <v>0.931</v>
       </c>
       <c r="G68" t="n">
         <v>0.676</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0163</v>
+        <v>0.0151</v>
       </c>
       <c r="I68" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0804</v>
       </c>
     </row>
     <row r="69">
@@ -5446,16 +5446,16 @@
         <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0.741</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>0.0561</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="70">
@@ -5483,16 +5483,16 @@
         <v>5</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.963</v>
       </c>
       <c r="G70" t="n">
         <v>0.975</v>
       </c>
       <c r="H70" t="n">
-        <v>0.443</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>0.708</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="71">
@@ -5520,16 +5520,16 @@
         <v>6</v>
       </c>
       <c r="F71" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="G71" t="n">
         <v>0.921</v>
       </c>
       <c r="H71" t="n">
-        <v>0.304</v>
+        <v>0.303</v>
       </c>
       <c r="I71" t="n">
-        <v>0.706</v>
+        <v>0.643</v>
       </c>
     </row>
     <row r="72">
@@ -5557,16 +5557,16 @@
         <v>7</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.957</v>
       </c>
       <c r="G72" t="n">
-        <v>0.9</v>
+        <v>0.905</v>
       </c>
       <c r="H72" t="n">
-        <v>0.381</v>
+        <v>0.347</v>
       </c>
       <c r="I72" t="n">
-        <v>0.708</v>
+        <v>0.643</v>
       </c>
     </row>
     <row r="73">
@@ -5603,7 +5603,7 @@
         <v>0.5590000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.746</v>
       </c>
     </row>
     <row r="74">
@@ -5668,16 +5668,16 @@
         <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>0.913</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="G75" t="n">
-        <v>0.885</v>
+        <v>0.9</v>
       </c>
       <c r="H75" t="n">
-        <v>0.771</v>
+        <v>0.552</v>
       </c>
       <c r="I75" t="n">
-        <v>0.915</v>
+        <v>0.746</v>
       </c>
     </row>
     <row r="76">
@@ -5705,16 +5705,16 @@
         <v>11</v>
       </c>
       <c r="F76" t="n">
-        <v>0.873</v>
+        <v>0.889</v>
       </c>
       <c r="G76" t="n">
         <v>0.887</v>
       </c>
       <c r="H76" t="n">
-        <v>0.801</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>0.915</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -5751,7 +5751,7 @@
         <v>0.679</v>
       </c>
       <c r="I77" t="n">
-        <v>0.906</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="78">
@@ -5788,7 +5788,7 @@
         <v>0.309</v>
       </c>
       <c r="I78" t="n">
-        <v>0.706</v>
+        <v>0.643</v>
       </c>
     </row>
     <row r="79">
@@ -5825,7 +5825,7 @@
         <v>0.441</v>
       </c>
       <c r="I79" t="n">
-        <v>0.708</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="80">
@@ -5853,16 +5853,16 @@
         <v>15</v>
       </c>
       <c r="F80" t="n">
-        <v>0.617</v>
+        <v>0.649</v>
       </c>
       <c r="G80" t="n">
         <v>0.73</v>
       </c>
       <c r="H80" t="n">
-        <v>0.212</v>
+        <v>0.362</v>
       </c>
       <c r="I80" t="n">
-        <v>0.706</v>
+        <v>0.643</v>
       </c>
     </row>
     <row r="81">
@@ -5890,16 +5890,16 @@
         <v>16</v>
       </c>
       <c r="F81" t="n">
-        <v>0.509</v>
+        <v>0.556</v>
       </c>
       <c r="G81" t="n">
-        <v>0.621</v>
+        <v>0.655</v>
       </c>
       <c r="H81" t="n">
-        <v>0.262</v>
+        <v>0.335</v>
       </c>
       <c r="I81" t="n">
-        <v>0.706</v>
+        <v>0.643</v>
       </c>
     </row>
     <row r="82">
@@ -5973,7 +5973,7 @@
         <v>0.236</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.472</v>
       </c>
     </row>
     <row r="84">
@@ -6001,16 +6001,16 @@
         <v>3</v>
       </c>
       <c r="F84" t="n">
-        <v>0.929</v>
+        <v>0.964</v>
       </c>
       <c r="G84" t="n">
         <v>0.893</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>0.611</v>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>0.978</v>
       </c>
     </row>
     <row r="85">
@@ -6038,10 +6038,10 @@
         <v>4</v>
       </c>
       <c r="F85" t="n">
-        <v>0.955</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>0.909</v>
+        <v>1</v>
       </c>
       <c r="H85" t="n">
         <v>1</v>
@@ -6075,13 +6075,13 @@
         <v>5</v>
       </c>
       <c r="F86" t="n">
-        <v>0.752</v>
+        <v>0.762</v>
       </c>
       <c r="G86" t="n">
         <v>0.782</v>
       </c>
       <c r="H86" t="n">
-        <v>0.739</v>
+        <v>0.867</v>
       </c>
       <c r="I86" t="n">
         <v>1</v>
@@ -6112,16 +6112,16 @@
         <v>6</v>
       </c>
       <c r="F87" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="G87" t="n">
         <v>0.891</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0009940000000000001</v>
+        <v>0.00171</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0159</v>
+        <v>0.0274</v>
       </c>
     </row>
     <row r="88">
@@ -6149,16 +6149,16 @@
         <v>7</v>
       </c>
       <c r="F88" t="n">
-        <v>0.776</v>
+        <v>0.788</v>
       </c>
       <c r="G88" t="n">
-        <v>0.847</v>
+        <v>0.894</v>
       </c>
       <c r="H88" t="n">
-        <v>0.327</v>
+        <v>0.0919</v>
       </c>
       <c r="I88" t="n">
-        <v>0.653</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="89">
@@ -6232,7 +6232,7 @@
         <v>0.136</v>
       </c>
       <c r="I90" t="n">
-        <v>0.49</v>
+        <v>0.386</v>
       </c>
     </row>
     <row r="91">
@@ -6260,16 +6260,16 @@
         <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>0.787</v>
+        <v>0.877</v>
       </c>
       <c r="G91" t="n">
-        <v>0.675</v>
+        <v>0.778</v>
       </c>
       <c r="H91" t="n">
-        <v>0.153</v>
+        <v>0.145</v>
       </c>
       <c r="I91" t="n">
-        <v>0.49</v>
+        <v>0.386</v>
       </c>
     </row>
     <row r="92">
@@ -6297,16 +6297,16 @@
         <v>11</v>
       </c>
       <c r="F92" t="n">
-        <v>0.604</v>
+        <v>0.609</v>
       </c>
       <c r="G92" t="n">
-        <v>0.78</v>
+        <v>0.772</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0156</v>
+        <v>0.0252</v>
       </c>
       <c r="I92" t="n">
-        <v>0.125</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="93">
@@ -6454,7 +6454,7 @@
         <v>0.5659999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>0.978</v>
       </c>
     </row>
     <row r="97">
@@ -6482,16 +6482,16 @@
         <v>16</v>
       </c>
       <c r="F97" t="n">
-        <v>0.527</v>
+        <v>0.526</v>
       </c>
       <c r="G97" t="n">
-        <v>0.655</v>
+        <v>0.667</v>
       </c>
       <c r="H97" t="n">
-        <v>0.244</v>
+        <v>0.181</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.414</v>
       </c>
     </row>
     <row r="98">
@@ -6593,16 +6593,16 @@
         <v>3</v>
       </c>
       <c r="F100" t="n">
-        <v>0.973</v>
+        <v>0.98</v>
       </c>
       <c r="G100" t="n">
         <v>0.967</v>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>0.723</v>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="101">
@@ -6630,16 +6630,16 @@
         <v>4</v>
       </c>
       <c r="F101" t="n">
-        <v>0.947</v>
+        <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0.953</v>
+        <v>0.973</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>0.122</v>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="102">
@@ -6667,13 +6667,13 @@
         <v>5</v>
       </c>
       <c r="F102" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G102" t="n">
         <v>0.82</v>
       </c>
       <c r="H102" t="n">
-        <v>0.769</v>
+        <v>1</v>
       </c>
       <c r="I102" t="n">
         <v>1</v>
@@ -6704,16 +6704,16 @@
         <v>6</v>
       </c>
       <c r="F103" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="G103" t="n">
         <v>0.84</v>
       </c>
       <c r="H103" t="n">
-        <v>0.371</v>
+        <v>0.453</v>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>0.888</v>
       </c>
     </row>
     <row r="104">
@@ -6741,16 +6741,16 @@
         <v>7</v>
       </c>
       <c r="F104" t="n">
-        <v>0.847</v>
+        <v>0.86</v>
       </c>
       <c r="G104" t="n">
-        <v>0.82</v>
+        <v>0.873</v>
       </c>
       <c r="H104" t="n">
-        <v>0.642</v>
+        <v>0.865</v>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>0.989</v>
       </c>
     </row>
     <row r="105">
@@ -6824,7 +6824,7 @@
         <v>0.154</v>
       </c>
       <c r="I106" t="n">
-        <v>0.616</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="107">
@@ -6852,16 +6852,16 @@
         <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>0.847</v>
+        <v>0.9</v>
       </c>
       <c r="G107" t="n">
-        <v>0.847</v>
+        <v>0.867</v>
       </c>
       <c r="H107" t="n">
-        <v>1</v>
+        <v>0.472</v>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>0.888</v>
       </c>
     </row>
     <row r="108">
@@ -6889,13 +6889,13 @@
         <v>11</v>
       </c>
       <c r="F108" t="n">
-        <v>0.707</v>
+        <v>0.713</v>
       </c>
       <c r="G108" t="n">
-        <v>0.793</v>
+        <v>0.787</v>
       </c>
       <c r="H108" t="n">
-        <v>0.109</v>
+        <v>0.182</v>
       </c>
       <c r="I108" t="n">
         <v>0.583</v>
@@ -6935,7 +6935,7 @@
         <v>0.611</v>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>0.888</v>
       </c>
     </row>
     <row r="110">
@@ -6972,7 +6972,7 @@
         <v>0.723</v>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="111">
@@ -7009,7 +7009,7 @@
         <v>0.51</v>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>0.888</v>
       </c>
     </row>
     <row r="112">
@@ -7037,16 +7037,16 @@
         <v>15</v>
       </c>
       <c r="F112" t="n">
-        <v>0.68</v>
+        <v>0.707</v>
       </c>
       <c r="G112" t="n">
-        <v>0.727</v>
+        <v>0.74</v>
       </c>
       <c r="H112" t="n">
-        <v>0.448</v>
+        <v>0.606</v>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>0.888</v>
       </c>
     </row>
     <row r="113">
@@ -7074,16 +7074,16 @@
         <v>16</v>
       </c>
       <c r="F113" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="G113" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I113" t="n">
         <v>0.6929999999999999</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="I113" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -7185,7 +7185,7 @@
         <v>3</v>
       </c>
       <c r="F116" t="n">
-        <v>0.929</v>
+        <v>0.931</v>
       </c>
       <c r="G116" t="n">
         <v>0.926</v>
@@ -7222,16 +7222,16 @@
         <v>4</v>
       </c>
       <c r="F117" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>0.8</v>
+        <v>0.846</v>
       </c>
       <c r="H117" t="n">
-        <v>0.75</v>
+        <v>0.114</v>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>0.458</v>
       </c>
     </row>
     <row r="118">
@@ -7259,13 +7259,13 @@
         <v>5</v>
       </c>
       <c r="F118" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.963</v>
       </c>
       <c r="G118" t="n">
         <v>0.963</v>
       </c>
       <c r="H118" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="I118" t="n">
         <v>1</v>
@@ -7296,13 +7296,13 @@
         <v>6</v>
       </c>
       <c r="F119" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="G119" t="n">
         <v>0.886</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0723</v>
+        <v>0.0709</v>
       </c>
       <c r="I119" t="n">
         <v>0.442</v>
@@ -7333,16 +7333,16 @@
         <v>7</v>
       </c>
       <c r="F120" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.957</v>
       </c>
       <c r="G120" t="n">
-        <v>0.863</v>
+        <v>0.884</v>
       </c>
       <c r="H120" t="n">
-        <v>0.171</v>
+        <v>0.145</v>
       </c>
       <c r="I120" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.465</v>
       </c>
     </row>
     <row r="121">
@@ -7444,13 +7444,13 @@
         <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>0.913</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="G123" t="n">
-        <v>0.952</v>
+        <v>0.955</v>
       </c>
       <c r="H123" t="n">
-        <v>0.497</v>
+        <v>0.723</v>
       </c>
       <c r="I123" t="n">
         <v>1</v>
@@ -7481,13 +7481,13 @@
         <v>11</v>
       </c>
       <c r="F124" t="n">
-        <v>0.873</v>
+        <v>0.889</v>
       </c>
       <c r="G124" t="n">
         <v>0.895</v>
       </c>
       <c r="H124" t="n">
-        <v>0.792</v>
+        <v>1</v>
       </c>
       <c r="I124" t="n">
         <v>1</v>
@@ -7601,7 +7601,7 @@
         <v>0.273</v>
       </c>
       <c r="I127" t="n">
-        <v>0.875</v>
+        <v>0.729</v>
       </c>
     </row>
     <row r="128">
@@ -7629,13 +7629,13 @@
         <v>15</v>
       </c>
       <c r="F128" t="n">
-        <v>0.617</v>
+        <v>0.649</v>
       </c>
       <c r="G128" t="n">
-        <v>0.659</v>
+        <v>0.675</v>
       </c>
       <c r="H128" t="n">
-        <v>0.627</v>
+        <v>0.739</v>
       </c>
       <c r="I128" t="n">
         <v>1</v>
@@ -7666,13 +7666,13 @@
         <v>16</v>
       </c>
       <c r="F129" t="n">
-        <v>0.509</v>
+        <v>0.556</v>
       </c>
       <c r="G129" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.614</v>
       </c>
       <c r="H129" t="n">
-        <v>0.594</v>
+        <v>0.582</v>
       </c>
       <c r="I129" t="n">
         <v>1</v>
@@ -7777,16 +7777,16 @@
         <v>3</v>
       </c>
       <c r="F132" t="n">
-        <v>0.929</v>
+        <v>0.964</v>
       </c>
       <c r="G132" t="n">
         <v>0.893</v>
       </c>
       <c r="H132" t="n">
-        <v>1</v>
+        <v>0.611</v>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>0.978</v>
       </c>
     </row>
     <row r="133">
@@ -7814,10 +7814,10 @@
         <v>4</v>
       </c>
       <c r="F133" t="n">
-        <v>0.955</v>
+        <v>1</v>
       </c>
       <c r="G133" t="n">
-        <v>0.909</v>
+        <v>1</v>
       </c>
       <c r="H133" t="n">
         <v>1</v>
@@ -7851,7 +7851,7 @@
         <v>5</v>
       </c>
       <c r="F134" t="n">
-        <v>0.752</v>
+        <v>0.762</v>
       </c>
       <c r="G134" t="n">
         <v>0.762</v>
@@ -7888,16 +7888,16 @@
         <v>6</v>
       </c>
       <c r="F135" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="G135" t="n">
         <v>0.848</v>
       </c>
       <c r="H135" t="n">
-        <v>0.0141</v>
+        <v>0.0217</v>
       </c>
       <c r="I135" t="n">
-        <v>0.113</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="136">
@@ -7925,16 +7925,16 @@
         <v>7</v>
       </c>
       <c r="F136" t="n">
-        <v>0.776</v>
+        <v>0.788</v>
       </c>
       <c r="G136" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.894</v>
       </c>
       <c r="H136" t="n">
-        <v>0.705</v>
+        <v>0.0919</v>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>0.294</v>
       </c>
     </row>
     <row r="137">
@@ -8008,7 +8008,7 @@
         <v>0.136</v>
       </c>
       <c r="I138" t="n">
-        <v>0.436</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="139">
@@ -8036,16 +8036,16 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>0.787</v>
+        <v>0.877</v>
       </c>
       <c r="G139" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="H139" t="n">
-        <v>0.708</v>
+        <v>0.205</v>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="140">
@@ -8073,16 +8073,16 @@
         <v>11</v>
       </c>
       <c r="F140" t="n">
-        <v>0.604</v>
+        <v>0.609</v>
       </c>
       <c r="G140" t="n">
-        <v>0.747</v>
+        <v>0.739</v>
       </c>
       <c r="H140" t="n">
-        <v>0.0569</v>
+        <v>0.0832</v>
       </c>
       <c r="I140" t="n">
-        <v>0.228</v>
+        <v>0.294</v>
       </c>
     </row>
     <row r="141">
@@ -8156,7 +8156,7 @@
         <v>0.488</v>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="143">
@@ -8230,7 +8230,7 @@
         <v>0.535</v>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="145">
@@ -8258,16 +8258,16 @@
         <v>16</v>
       </c>
       <c r="F145" t="n">
-        <v>0.527</v>
+        <v>0.526</v>
       </c>
       <c r="G145" t="n">
-        <v>0.727</v>
+        <v>0.754</v>
       </c>
       <c r="H145" t="n">
-        <v>0.048</v>
+        <v>0.0187</v>
       </c>
       <c r="I145" t="n">
-        <v>0.228</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="146">
@@ -8369,16 +8369,16 @@
         <v>3</v>
       </c>
       <c r="F148" t="n">
-        <v>0.973</v>
+        <v>0.98</v>
       </c>
       <c r="G148" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="H148" t="n">
-        <v>0.169</v>
+        <v>0.0853</v>
       </c>
       <c r="I148" t="n">
-        <v>0.387</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="149">
@@ -8406,16 +8406,16 @@
         <v>4</v>
       </c>
       <c r="F149" t="n">
-        <v>0.947</v>
+        <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>0.953</v>
+        <v>0.96</v>
       </c>
       <c r="H149" t="n">
-        <v>1</v>
+        <v>0.0297</v>
       </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="150">
@@ -8443,16 +8443,16 @@
         <v>5</v>
       </c>
       <c r="F150" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G150" t="n">
         <v>0.827</v>
       </c>
       <c r="H150" t="n">
-        <v>0.657</v>
+        <v>1</v>
       </c>
       <c r="I150" t="n">
-        <v>0.992</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -8480,16 +8480,16 @@
         <v>6</v>
       </c>
       <c r="F151" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="G151" t="n">
         <v>0.887</v>
       </c>
       <c r="H151" t="n">
-        <v>0.0398</v>
+        <v>0.0558</v>
       </c>
       <c r="I151" t="n">
-        <v>0.153</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="152">
@@ -8517,16 +8517,16 @@
         <v>7</v>
       </c>
       <c r="F152" t="n">
-        <v>0.847</v>
+        <v>0.86</v>
       </c>
       <c r="G152" t="n">
-        <v>0.88</v>
+        <v>0.913</v>
       </c>
       <c r="H152" t="n">
-        <v>0.502</v>
+        <v>0.202</v>
       </c>
       <c r="I152" t="n">
-        <v>0.892</v>
+        <v>0.359</v>
       </c>
     </row>
     <row r="153">
@@ -8594,13 +8594,13 @@
         <v>0.6870000000000001</v>
       </c>
       <c r="G154" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="H154" t="n">
-        <v>0.0479</v>
+        <v>0.0341</v>
       </c>
       <c r="I154" t="n">
-        <v>0.153</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="155">
@@ -8628,16 +8628,16 @@
         <v>10</v>
       </c>
       <c r="F155" t="n">
-        <v>0.847</v>
+        <v>0.9</v>
       </c>
       <c r="G155" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="H155" t="n">
-        <v>0.364</v>
+        <v>0.0663</v>
       </c>
       <c r="I155" t="n">
-        <v>0.728</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="156">
@@ -8665,16 +8665,16 @@
         <v>11</v>
       </c>
       <c r="F156" t="n">
-        <v>0.707</v>
+        <v>0.713</v>
       </c>
       <c r="G156" t="n">
-        <v>0.787</v>
+        <v>0.78</v>
       </c>
       <c r="H156" t="n">
-        <v>0.144</v>
+        <v>0.232</v>
       </c>
       <c r="I156" t="n">
-        <v>0.384</v>
+        <v>0.371</v>
       </c>
     </row>
     <row r="157">
@@ -8813,16 +8813,16 @@
         <v>15</v>
       </c>
       <c r="F160" t="n">
-        <v>0.68</v>
+        <v>0.707</v>
       </c>
       <c r="G160" t="n">
         <v>0.8</v>
       </c>
       <c r="H160" t="n">
-        <v>0.0249</v>
+        <v>0.0813</v>
       </c>
       <c r="I160" t="n">
-        <v>0.153</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="161">
@@ -8850,16 +8850,16 @@
         <v>16</v>
       </c>
       <c r="F161" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="G161" t="n">
-        <v>0.76</v>
+        <v>0.773</v>
       </c>
       <c r="H161" t="n">
-        <v>0.0319</v>
+        <v>0.04</v>
       </c>
       <c r="I161" t="n">
-        <v>0.153</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="162">
@@ -8896,7 +8896,7 @@
         <v>0.0381</v>
       </c>
       <c r="I162" t="n">
-        <v>0.305</v>
+        <v>0.203</v>
       </c>
     </row>
     <row r="163">
@@ -8961,16 +8961,16 @@
         <v>3</v>
       </c>
       <c r="F164" t="n">
-        <v>0.929</v>
+        <v>0.931</v>
       </c>
       <c r="G164" t="n">
         <v>0.8</v>
       </c>
       <c r="H164" t="n">
-        <v>0.256</v>
+        <v>0.254</v>
       </c>
       <c r="I164" t="n">
-        <v>0.511</v>
+        <v>0.508</v>
       </c>
     </row>
     <row r="165">
@@ -8998,16 +8998,16 @@
         <v>4</v>
       </c>
       <c r="F165" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>0.778</v>
+        <v>0.786</v>
       </c>
       <c r="H165" t="n">
-        <v>1</v>
+        <v>0.0284</v>
       </c>
       <c r="I165" t="n">
-        <v>1</v>
+        <v>0.203</v>
       </c>
     </row>
     <row r="166">
@@ -9035,16 +9035,16 @@
         <v>5</v>
       </c>
       <c r="F166" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.963</v>
       </c>
       <c r="G166" t="n">
         <v>0.987</v>
       </c>
       <c r="H166" t="n">
-        <v>0.211</v>
+        <v>0.62</v>
       </c>
       <c r="I166" t="n">
-        <v>0.481</v>
+        <v>0.902</v>
       </c>
     </row>
     <row r="167">
@@ -9072,7 +9072,7 @@
         <v>6</v>
       </c>
       <c r="F167" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="G167" t="n">
         <v>0.931</v>
@@ -9081,7 +9081,7 @@
         <v>0.467</v>
       </c>
       <c r="I167" t="n">
-        <v>0.831</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="168">
@@ -9109,16 +9109,16 @@
         <v>7</v>
       </c>
       <c r="F168" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.957</v>
       </c>
       <c r="G168" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="H168" t="n">
-        <v>1</v>
+        <v>0.726</v>
       </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>0.968</v>
       </c>
     </row>
     <row r="169">
@@ -9220,16 +9220,16 @@
         <v>10</v>
       </c>
       <c r="F171" t="n">
-        <v>0.913</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="G171" t="n">
-        <v>0.879</v>
+        <v>0.886</v>
       </c>
       <c r="H171" t="n">
-        <v>0.58</v>
+        <v>0.388</v>
       </c>
       <c r="I171" t="n">
-        <v>0.929</v>
+        <v>0.6889999999999999</v>
       </c>
     </row>
     <row r="172">
@@ -9257,7 +9257,7 @@
         <v>11</v>
       </c>
       <c r="F172" t="n">
-        <v>0.873</v>
+        <v>0.889</v>
       </c>
       <c r="G172" t="n">
         <v>0.883</v>
@@ -9377,7 +9377,7 @@
         <v>0.0648</v>
       </c>
       <c r="I175" t="n">
-        <v>0.345</v>
+        <v>0.259</v>
       </c>
     </row>
     <row r="176">
@@ -9405,16 +9405,16 @@
         <v>15</v>
       </c>
       <c r="F176" t="n">
-        <v>0.617</v>
+        <v>0.649</v>
       </c>
       <c r="G176" t="n">
         <v>0.747</v>
       </c>
       <c r="H176" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.219</v>
       </c>
       <c r="I176" t="n">
-        <v>0.348</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="177">
@@ -9442,16 +9442,16 @@
         <v>16</v>
       </c>
       <c r="F177" t="n">
-        <v>0.509</v>
+        <v>0.556</v>
       </c>
       <c r="G177" t="n">
-        <v>0.651</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H177" t="n">
-        <v>0.139</v>
+        <v>0.183</v>
       </c>
       <c r="I177" t="n">
-        <v>0.372</v>
+        <v>0.488</v>
       </c>
     </row>
     <row r="178">
@@ -9488,7 +9488,7 @@
         <v>0.447</v>
       </c>
       <c r="I178" t="n">
-        <v>0.863</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="179">
@@ -9553,16 +9553,16 @@
         <v>3</v>
       </c>
       <c r="F180" t="n">
-        <v>0.929</v>
+        <v>0.964</v>
       </c>
       <c r="G180" t="n">
         <v>0.857</v>
       </c>
       <c r="H180" t="n">
-        <v>0.669</v>
+        <v>0.352</v>
       </c>
       <c r="I180" t="n">
-        <v>0.974</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="181">
@@ -9590,10 +9590,10 @@
         <v>4</v>
       </c>
       <c r="F181" t="n">
-        <v>0.955</v>
+        <v>1</v>
       </c>
       <c r="G181" t="n">
-        <v>0.955</v>
+        <v>1</v>
       </c>
       <c r="H181" t="n">
         <v>1</v>
@@ -9627,7 +9627,7 @@
         <v>5</v>
       </c>
       <c r="F182" t="n">
-        <v>0.752</v>
+        <v>0.762</v>
       </c>
       <c r="G182" t="n">
         <v>0.752</v>
@@ -9664,16 +9664,16 @@
         <v>6</v>
       </c>
       <c r="F183" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="G183" t="n">
         <v>0.88</v>
       </c>
       <c r="H183" t="n">
-        <v>0.00212</v>
+        <v>0.00354</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0339</v>
+        <v>0.0566</v>
       </c>
     </row>
     <row r="184">
@@ -9701,16 +9701,16 @@
         <v>7</v>
       </c>
       <c r="F184" t="n">
-        <v>0.776</v>
+        <v>0.788</v>
       </c>
       <c r="G184" t="n">
-        <v>0.847</v>
+        <v>0.906</v>
       </c>
       <c r="H184" t="n">
-        <v>0.327</v>
+        <v>0.0536</v>
       </c>
       <c r="I184" t="n">
-        <v>0.863</v>
+        <v>0.214</v>
       </c>
     </row>
     <row r="185">
@@ -9778,13 +9778,13 @@
         <v>0.635</v>
       </c>
       <c r="G186" t="n">
-        <v>0.77</v>
+        <v>0.778</v>
       </c>
       <c r="H186" t="n">
-        <v>0.0271</v>
+        <v>0.0184</v>
       </c>
       <c r="I186" t="n">
-        <v>0.153</v>
+        <v>0.09950000000000001</v>
       </c>
     </row>
     <row r="187">
@@ -9812,16 +9812,16 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>0.787</v>
+        <v>0.877</v>
       </c>
       <c r="G187" t="n">
-        <v>0.725</v>
+        <v>0.765</v>
       </c>
       <c r="H187" t="n">
-        <v>0.462</v>
+        <v>0.1</v>
       </c>
       <c r="I187" t="n">
-        <v>0.863</v>
+        <v>0.267</v>
       </c>
     </row>
     <row r="188">
@@ -9849,16 +9849,16 @@
         <v>11</v>
       </c>
       <c r="F188" t="n">
-        <v>0.604</v>
+        <v>0.609</v>
       </c>
       <c r="G188" t="n">
-        <v>0.747</v>
+        <v>0.739</v>
       </c>
       <c r="H188" t="n">
-        <v>0.0569</v>
+        <v>0.0832</v>
       </c>
       <c r="I188" t="n">
-        <v>0.228</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="189">
@@ -9895,7 +9895,7 @@
         <v>0.519</v>
       </c>
       <c r="I189" t="n">
-        <v>0.863</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="190">
@@ -9969,7 +9969,7 @@
         <v>0.539</v>
       </c>
       <c r="I191" t="n">
-        <v>0.863</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="192">
@@ -10006,7 +10006,7 @@
         <v>0.288</v>
       </c>
       <c r="I192" t="n">
-        <v>0.863</v>
+        <v>0.658</v>
       </c>
     </row>
     <row r="193">
@@ -10034,16 +10034,16 @@
         <v>16</v>
       </c>
       <c r="F193" t="n">
-        <v>0.527</v>
+        <v>0.526</v>
       </c>
       <c r="G193" t="n">
-        <v>0.745</v>
+        <v>0.754</v>
       </c>
       <c r="H193" t="n">
-        <v>0.0286</v>
+        <v>0.0187</v>
       </c>
       <c r="I193" t="n">
-        <v>0.153</v>
+        <v>0.09950000000000001</v>
       </c>
     </row>
     <row r="194">
@@ -10080,7 +10080,7 @@
         <v>0.1</v>
       </c>
       <c r="I194" t="n">
-        <v>0.267</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="195">
@@ -10117,7 +10117,7 @@
         <v>8.69e-05</v>
       </c>
       <c r="I195" t="n">
-        <v>0.00139</v>
+        <v>0.00114</v>
       </c>
     </row>
     <row r="196">
@@ -10145,16 +10145,16 @@
         <v>3</v>
       </c>
       <c r="F196" t="n">
-        <v>0.973</v>
+        <v>0.98</v>
       </c>
       <c r="G196" t="n">
         <v>0.987</v>
       </c>
       <c r="H196" t="n">
-        <v>0.6840000000000001</v>
+        <v>1</v>
       </c>
       <c r="I196" t="n">
-        <v>0.898</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -10182,16 +10182,16 @@
         <v>4</v>
       </c>
       <c r="F197" t="n">
-        <v>0.947</v>
+        <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0.96</v>
+        <v>0.993</v>
       </c>
       <c r="H197" t="n">
-        <v>0.785</v>
+        <v>1</v>
       </c>
       <c r="I197" t="n">
-        <v>0.898</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -10219,16 +10219,16 @@
         <v>5</v>
       </c>
       <c r="F198" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G198" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="H198" t="n">
-        <v>0.769</v>
+        <v>1</v>
       </c>
       <c r="I198" t="n">
-        <v>0.898</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -10256,16 +10256,16 @@
         <v>6</v>
       </c>
       <c r="F199" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="G199" t="n">
         <v>0.907</v>
       </c>
       <c r="H199" t="n">
-        <v>0.00911</v>
+        <v>0.0137</v>
       </c>
       <c r="I199" t="n">
-        <v>0.0292</v>
+        <v>0.0438</v>
       </c>
     </row>
     <row r="200">
@@ -10293,16 +10293,16 @@
         <v>7</v>
       </c>
       <c r="F200" t="n">
-        <v>0.847</v>
+        <v>0.86</v>
       </c>
       <c r="G200" t="n">
-        <v>0.893</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H200" t="n">
-        <v>0.303</v>
+        <v>0.0564</v>
       </c>
       <c r="I200" t="n">
-        <v>0.606</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="201">
@@ -10370,13 +10370,13 @@
         <v>0.6870000000000001</v>
       </c>
       <c r="G202" t="n">
-        <v>0.76</v>
+        <v>0.767</v>
       </c>
       <c r="H202" t="n">
-        <v>0.197</v>
+        <v>0.154</v>
       </c>
       <c r="I202" t="n">
-        <v>0.45</v>
+        <v>0.308</v>
       </c>
     </row>
     <row r="203">
@@ -10404,16 +10404,16 @@
         <v>10</v>
       </c>
       <c r="F203" t="n">
-        <v>0.847</v>
+        <v>0.9</v>
       </c>
       <c r="G203" t="n">
-        <v>0.867</v>
+        <v>0.92</v>
       </c>
       <c r="H203" t="n">
-        <v>0.742</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="I203" t="n">
-        <v>0.898</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204">
@@ -10441,16 +10441,16 @@
         <v>11</v>
       </c>
       <c r="F204" t="n">
-        <v>0.707</v>
+        <v>0.713</v>
       </c>
       <c r="G204" t="n">
-        <v>0.86</v>
+        <v>0.853</v>
       </c>
       <c r="H204" t="n">
-        <v>0.0019</v>
+        <v>0.00482</v>
       </c>
       <c r="I204" t="n">
-        <v>0.00761</v>
+        <v>0.0193</v>
       </c>
     </row>
     <row r="205">
@@ -10487,7 +10487,7 @@
         <v>0.575</v>
       </c>
       <c r="I205" t="n">
-        <v>0.898</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="206">
@@ -10589,16 +10589,16 @@
         <v>15</v>
       </c>
       <c r="F208" t="n">
-        <v>0.68</v>
+        <v>0.707</v>
       </c>
       <c r="G208" t="n">
-        <v>0.853</v>
+        <v>0.873</v>
       </c>
       <c r="H208" t="n">
-        <v>0.0005820000000000001</v>
+        <v>0.000595</v>
       </c>
       <c r="I208" t="n">
-        <v>0.00356</v>
+        <v>0.00317</v>
       </c>
     </row>
     <row r="209">
@@ -10626,16 +10626,16 @@
         <v>16</v>
       </c>
       <c r="F209" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="G209" t="n">
-        <v>0.82</v>
+        <v>0.853</v>
       </c>
       <c r="H209" t="n">
-        <v>0.000668</v>
+        <v>0.000143</v>
       </c>
       <c r="I209" t="n">
-        <v>0.00356</v>
+        <v>0.00114</v>
       </c>
     </row>
     <row r="210">
@@ -10672,7 +10672,7 @@
         <v>0.585</v>
       </c>
       <c r="I210" t="n">
-        <v>0.926</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -10737,16 +10737,16 @@
         <v>3</v>
       </c>
       <c r="F212" t="n">
-        <v>0.929</v>
+        <v>0.931</v>
       </c>
       <c r="G212" t="n">
         <v>1</v>
       </c>
       <c r="H212" t="n">
-        <v>0.491</v>
+        <v>0.492</v>
       </c>
       <c r="I212" t="n">
-        <v>0.917</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
@@ -10774,16 +10774,16 @@
         <v>4</v>
       </c>
       <c r="F213" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G213" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="H213" t="n">
-        <v>0.516</v>
+        <v>1</v>
       </c>
       <c r="I213" t="n">
-        <v>0.917</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214">
@@ -10811,16 +10811,16 @@
         <v>5</v>
       </c>
       <c r="F214" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.963</v>
       </c>
       <c r="G214" t="n">
         <v>0.963</v>
       </c>
       <c r="H214" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="I214" t="n">
-        <v>0.926</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
@@ -10848,7 +10848,7 @@
         <v>6</v>
       </c>
       <c r="F215" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="G215" t="n">
         <v>0.9429999999999999</v>
@@ -10857,7 +10857,7 @@
         <v>0.699</v>
       </c>
       <c r="I215" t="n">
-        <v>0.926</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
@@ -10885,16 +10885,16 @@
         <v>7</v>
       </c>
       <c r="F216" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.957</v>
       </c>
       <c r="G216" t="n">
-        <v>0.926</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="H216" t="n">
-        <v>0.752</v>
+        <v>0.73</v>
       </c>
       <c r="I216" t="n">
-        <v>0.926</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -10965,10 +10965,10 @@
         <v>0.95</v>
       </c>
       <c r="H218" t="n">
-        <v>0.227</v>
+        <v>0.228</v>
       </c>
       <c r="I218" t="n">
-        <v>0.725</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="219">
@@ -10996,10 +10996,10 @@
         <v>10</v>
       </c>
       <c r="F219" t="n">
-        <v>0.913</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="G219" t="n">
-        <v>0.917</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="H219" t="n">
         <v>1</v>
@@ -11033,16 +11033,16 @@
         <v>11</v>
       </c>
       <c r="F220" t="n">
-        <v>0.873</v>
+        <v>0.889</v>
       </c>
       <c r="G220" t="n">
         <v>0.927</v>
       </c>
       <c r="H220" t="n">
-        <v>0.396</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>0.905</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -11153,7 +11153,7 @@
         <v>0.185</v>
       </c>
       <c r="I223" t="n">
-        <v>0.725</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="224">
@@ -11181,16 +11181,16 @@
         <v>15</v>
       </c>
       <c r="F224" t="n">
-        <v>0.617</v>
+        <v>0.649</v>
       </c>
       <c r="G224" t="n">
-        <v>0.826</v>
+        <v>0.864</v>
       </c>
       <c r="H224" t="n">
-        <v>0.00635</v>
+        <v>0.0037</v>
       </c>
       <c r="I224" t="n">
-        <v>0.0508</v>
+        <v>0.0296</v>
       </c>
     </row>
     <row r="225">
@@ -11218,16 +11218,16 @@
         <v>16</v>
       </c>
       <c r="F225" t="n">
-        <v>0.509</v>
+        <v>0.556</v>
       </c>
       <c r="G225" t="n">
-        <v>0.733</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H225" t="n">
-        <v>0.0139</v>
+        <v>0.00743</v>
       </c>
       <c r="I225" t="n">
-        <v>0.0743</v>
+        <v>0.0396</v>
       </c>
     </row>
     <row r="226">
@@ -11264,7 +11264,7 @@
         <v>0.0974</v>
       </c>
       <c r="I226" t="n">
-        <v>0.203</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="227">
@@ -11329,7 +11329,7 @@
         <v>3</v>
       </c>
       <c r="F228" t="n">
-        <v>0.929</v>
+        <v>0.964</v>
       </c>
       <c r="G228" t="n">
         <v>0.929</v>
@@ -11366,10 +11366,10 @@
         <v>4</v>
       </c>
       <c r="F229" t="n">
+        <v>1</v>
+      </c>
+      <c r="G229" t="n">
         <v>0.955</v>
-      </c>
-      <c r="G229" t="n">
-        <v>0.909</v>
       </c>
       <c r="H229" t="n">
         <v>1</v>
@@ -11403,10 +11403,10 @@
         <v>5</v>
       </c>
       <c r="F230" t="n">
-        <v>0.752</v>
+        <v>0.762</v>
       </c>
       <c r="G230" t="n">
-        <v>0.762</v>
+        <v>0.772</v>
       </c>
       <c r="H230" t="n">
         <v>1</v>
@@ -11440,16 +11440,16 @@
         <v>6</v>
       </c>
       <c r="F231" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="G231" t="n">
         <v>0.902</v>
       </c>
       <c r="H231" t="n">
-        <v>0.000433</v>
+        <v>0.00077</v>
       </c>
       <c r="I231" t="n">
-        <v>0.0069</v>
+        <v>0.0123</v>
       </c>
     </row>
     <row r="232">
@@ -11477,16 +11477,16 @@
         <v>7</v>
       </c>
       <c r="F232" t="n">
-        <v>0.776</v>
+        <v>0.788</v>
       </c>
       <c r="G232" t="n">
-        <v>0.882</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="H232" t="n">
-        <v>0.102</v>
+        <v>0.00612</v>
       </c>
       <c r="I232" t="n">
-        <v>0.203</v>
+        <v>0.0245</v>
       </c>
     </row>
     <row r="233">
@@ -11554,13 +11554,13 @@
         <v>0.635</v>
       </c>
       <c r="G234" t="n">
-        <v>0.754</v>
+        <v>0.762</v>
       </c>
       <c r="H234" t="n">
-        <v>0.0552</v>
+        <v>0.0391</v>
       </c>
       <c r="I234" t="n">
-        <v>0.167</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="235">
@@ -11588,16 +11588,16 @@
         <v>10</v>
       </c>
       <c r="F235" t="n">
-        <v>0.787</v>
+        <v>0.877</v>
       </c>
       <c r="G235" t="n">
-        <v>0.825</v>
+        <v>0.914</v>
       </c>
       <c r="H235" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.609</v>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="236">
@@ -11625,16 +11625,16 @@
         <v>11</v>
       </c>
       <c r="F236" t="n">
-        <v>0.604</v>
+        <v>0.609</v>
       </c>
       <c r="G236" t="n">
-        <v>0.835</v>
+        <v>0.826</v>
       </c>
       <c r="H236" t="n">
-        <v>0.0008630000000000001</v>
+        <v>0.00172</v>
       </c>
       <c r="I236" t="n">
-        <v>0.0069</v>
+        <v>0.0137</v>
       </c>
     </row>
     <row r="237">
@@ -11671,7 +11671,7 @@
         <v>0.0625</v>
       </c>
       <c r="I237" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="238">
@@ -11745,7 +11745,7 @@
         <v>0.0216</v>
       </c>
       <c r="I239" t="n">
-        <v>0.0863</v>
+        <v>0.06909999999999999</v>
       </c>
     </row>
     <row r="240">
@@ -11810,16 +11810,16 @@
         <v>16</v>
       </c>
       <c r="F241" t="n">
-        <v>0.527</v>
+        <v>0.526</v>
       </c>
       <c r="G241" t="n">
-        <v>0.8</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H241" t="n">
-        <v>0.00439</v>
+        <v>0.00264</v>
       </c>
       <c r="I241" t="n">
-        <v>0.0234</v>
+        <v>0.0141</v>
       </c>
     </row>
     <row r="242">
@@ -11856,7 +11856,7 @@
         <v>0.141</v>
       </c>
       <c r="I242" t="n">
-        <v>0.703</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="243">
@@ -11958,13 +11958,13 @@
         <v>4</v>
       </c>
       <c r="F245" t="n">
-        <v>0.98</v>
+        <v>0.987</v>
       </c>
       <c r="G245" t="n">
-        <v>0.993</v>
+        <v>1</v>
       </c>
       <c r="H245" t="n">
-        <v>0.622</v>
+        <v>0.498</v>
       </c>
       <c r="I245" t="n">
         <v>1</v>
@@ -11998,10 +11998,10 @@
         <v>0.8070000000000001</v>
       </c>
       <c r="G246" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="H246" t="n">
-        <v>0.882</v>
+        <v>0.766</v>
       </c>
       <c r="I246" t="n">
         <v>1</v>
@@ -12032,16 +12032,16 @@
         <v>6</v>
       </c>
       <c r="F247" t="n">
-        <v>0.787</v>
+        <v>0.793</v>
       </c>
       <c r="G247" t="n">
         <v>0.853</v>
       </c>
       <c r="H247" t="n">
-        <v>0.176</v>
+        <v>0.226</v>
       </c>
       <c r="I247" t="n">
-        <v>0.703</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="248">
@@ -12069,13 +12069,13 @@
         <v>7</v>
       </c>
       <c r="F248" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="G248" t="n">
-        <v>0.827</v>
+        <v>0.86</v>
       </c>
       <c r="H248" t="n">
-        <v>0.881</v>
+        <v>0.747</v>
       </c>
       <c r="I248" t="n">
         <v>1</v>
@@ -12152,7 +12152,7 @@
         <v>0.0683</v>
       </c>
       <c r="I250" t="n">
-        <v>0.703</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="251">
@@ -12180,16 +12180,16 @@
         <v>10</v>
       </c>
       <c r="F251" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="G251" t="n">
         <v>0.893</v>
       </c>
       <c r="H251" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.134</v>
       </c>
       <c r="I251" t="n">
-        <v>0.703</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="252">
@@ -12217,13 +12217,13 @@
         <v>11</v>
       </c>
       <c r="F252" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="G252" t="n">
         <v>0.787</v>
       </c>
-      <c r="G252" t="n">
-        <v>0.8</v>
-      </c>
       <c r="H252" t="n">
-        <v>0.887</v>
+        <v>0.889</v>
       </c>
       <c r="I252" t="n">
         <v>1</v>
@@ -12405,13 +12405,13 @@
         <v>0.46</v>
       </c>
       <c r="G257" t="n">
-        <v>0.393</v>
+        <v>0.407</v>
       </c>
       <c r="H257" t="n">
-        <v>0.293</v>
+        <v>0.415</v>
       </c>
       <c r="I257" t="n">
-        <v>0.9389999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258">
@@ -12590,10 +12590,10 @@
         <v>0.962</v>
       </c>
       <c r="G262" t="n">
-        <v>0.93</v>
+        <v>0.931</v>
       </c>
       <c r="H262" t="n">
-        <v>0.5</v>
+        <v>0.502</v>
       </c>
       <c r="I262" t="n">
         <v>1</v>
@@ -12624,7 +12624,7 @@
         <v>6</v>
       </c>
       <c r="F263" t="n">
-        <v>0.875</v>
+        <v>0.877</v>
       </c>
       <c r="G263" t="n">
         <v>0.898</v>
@@ -12661,13 +12661,13 @@
         <v>7</v>
       </c>
       <c r="F264" t="n">
-        <v>0.88</v>
+        <v>0.886</v>
       </c>
       <c r="G264" t="n">
-        <v>0.893</v>
+        <v>0.9</v>
       </c>
       <c r="H264" t="n">
-        <v>1</v>
+        <v>0.803</v>
       </c>
       <c r="I264" t="n">
         <v>1</v>
@@ -12809,10 +12809,10 @@
         <v>11</v>
       </c>
       <c r="F268" t="n">
-        <v>0.864</v>
+        <v>0.863</v>
       </c>
       <c r="G268" t="n">
-        <v>0.877</v>
+        <v>0.875</v>
       </c>
       <c r="H268" t="n">
         <v>1</v>
@@ -12994,13 +12994,13 @@
         <v>16</v>
       </c>
       <c r="F273" t="n">
-        <v>0.38</v>
+        <v>0.389</v>
       </c>
       <c r="G273" t="n">
-        <v>0.339</v>
+        <v>0.357</v>
       </c>
       <c r="H273" t="n">
-        <v>0.575</v>
+        <v>0.677</v>
       </c>
       <c r="I273" t="n">
         <v>1</v>
@@ -13040,7 +13040,7 @@
         <v>0.0853</v>
       </c>
       <c r="I274" t="n">
-        <v>0.455</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="275">
@@ -13142,16 +13142,16 @@
         <v>4</v>
       </c>
       <c r="F277" t="n">
-        <v>0.864</v>
+        <v>0.909</v>
       </c>
       <c r="G277" t="n">
-        <v>0.955</v>
+        <v>1</v>
       </c>
       <c r="H277" t="n">
-        <v>0.607</v>
+        <v>0.488</v>
       </c>
       <c r="I277" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="278">
@@ -13182,13 +13182,13 @@
         <v>0.743</v>
       </c>
       <c r="G278" t="n">
-        <v>0.792</v>
+        <v>0.802</v>
       </c>
       <c r="H278" t="n">
-        <v>0.506</v>
+        <v>0.402</v>
       </c>
       <c r="I278" t="n">
-        <v>1</v>
+        <v>0.949</v>
       </c>
     </row>
     <row r="279">
@@ -13216,16 +13216,16 @@
         <v>6</v>
       </c>
       <c r="F279" t="n">
-        <v>0.761</v>
+        <v>0.772</v>
       </c>
       <c r="G279" t="n">
         <v>0.859</v>
       </c>
       <c r="H279" t="n">
-        <v>0.132</v>
+        <v>0.183</v>
       </c>
       <c r="I279" t="n">
-        <v>0.529</v>
+        <v>0.733</v>
       </c>
     </row>
     <row r="280">
@@ -13253,13 +13253,13 @@
         <v>7</v>
       </c>
       <c r="F280" t="n">
-        <v>0.776</v>
+        <v>0.824</v>
       </c>
       <c r="G280" t="n">
-        <v>0.788</v>
+        <v>0.847</v>
       </c>
       <c r="H280" t="n">
-        <v>1</v>
+        <v>0.837</v>
       </c>
       <c r="I280" t="n">
         <v>1</v>
@@ -13364,16 +13364,16 @@
         <v>10</v>
       </c>
       <c r="F283" t="n">
-        <v>0.675</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G283" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H283" t="n">
-        <v>0.0694</v>
+        <v>0.1</v>
       </c>
       <c r="I283" t="n">
-        <v>0.455</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="284">
@@ -13401,10 +13401,10 @@
         <v>11</v>
       </c>
       <c r="F284" t="n">
-        <v>0.769</v>
+        <v>0.75</v>
       </c>
       <c r="G284" t="n">
-        <v>0.78</v>
+        <v>0.761</v>
       </c>
       <c r="H284" t="n">
         <v>1</v>
@@ -13447,7 +13447,7 @@
         <v>0.415</v>
       </c>
       <c r="I285" t="n">
-        <v>1</v>
+        <v>0.949</v>
       </c>
     </row>
     <row r="286">
@@ -13586,13 +13586,13 @@
         <v>16</v>
       </c>
       <c r="F289" t="n">
-        <v>0.745</v>
+        <v>0.737</v>
       </c>
       <c r="G289" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.702</v>
       </c>
       <c r="H289" t="n">
-        <v>0.672</v>
+        <v>0.835</v>
       </c>
       <c r="I289" t="n">
         <v>1</v>
@@ -13632,7 +13632,7 @@
         <v>0.188</v>
       </c>
       <c r="I290" t="n">
-        <v>0.838</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="291">
@@ -13669,7 +13669,7 @@
         <v>0.785</v>
       </c>
       <c r="I291" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
@@ -13706,7 +13706,7 @@
         <v>0.825</v>
       </c>
       <c r="I292" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293">
@@ -13734,10 +13734,10 @@
         <v>4</v>
       </c>
       <c r="F293" t="n">
-        <v>0.98</v>
+        <v>0.987</v>
       </c>
       <c r="G293" t="n">
-        <v>0.987</v>
+        <v>0.993</v>
       </c>
       <c r="H293" t="n">
         <v>1</v>
@@ -13774,13 +13774,13 @@
         <v>0.8070000000000001</v>
       </c>
       <c r="G294" t="n">
-        <v>0.787</v>
+        <v>0.8</v>
       </c>
       <c r="H294" t="n">
-        <v>0.774</v>
+        <v>1</v>
       </c>
       <c r="I294" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
@@ -13808,16 +13808,16 @@
         <v>6</v>
       </c>
       <c r="F295" t="n">
-        <v>0.787</v>
+        <v>0.793</v>
       </c>
       <c r="G295" t="n">
-        <v>0.847</v>
+        <v>0.853</v>
       </c>
       <c r="H295" t="n">
-        <v>0.232</v>
+        <v>0.226</v>
       </c>
       <c r="I295" t="n">
-        <v>0.838</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="296">
@@ -13845,16 +13845,16 @@
         <v>7</v>
       </c>
       <c r="F296" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="G296" t="n">
-        <v>0.833</v>
+        <v>0.867</v>
       </c>
       <c r="H296" t="n">
-        <v>0.762</v>
+        <v>0.625</v>
       </c>
       <c r="I296" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297">
@@ -13891,7 +13891,7 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="I297" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298">
@@ -13956,16 +13956,16 @@
         <v>10</v>
       </c>
       <c r="F299" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="G299" t="n">
-        <v>0.873</v>
+        <v>0.88</v>
       </c>
       <c r="H299" t="n">
-        <v>0.262</v>
+        <v>0.253</v>
       </c>
       <c r="I299" t="n">
-        <v>0.838</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="300">
@@ -13993,16 +13993,16 @@
         <v>11</v>
       </c>
       <c r="F300" t="n">
-        <v>0.787</v>
+        <v>0.773</v>
       </c>
       <c r="G300" t="n">
-        <v>0.773</v>
+        <v>0.76</v>
       </c>
       <c r="H300" t="n">
-        <v>0.889</v>
+        <v>0.892</v>
       </c>
       <c r="I300" t="n">
-        <v>0.949</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301">
@@ -14039,7 +14039,7 @@
         <v>0.518</v>
       </c>
       <c r="I301" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302">
@@ -14076,7 +14076,7 @@
         <v>0.541</v>
       </c>
       <c r="I302" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303">
@@ -14113,7 +14113,7 @@
         <v>0.5659999999999999</v>
       </c>
       <c r="I303" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304">
@@ -14150,7 +14150,7 @@
         <v>0.419</v>
       </c>
       <c r="I304" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305">
@@ -14181,13 +14181,13 @@
         <v>0.46</v>
       </c>
       <c r="G305" t="n">
-        <v>0.38</v>
+        <v>0.393</v>
       </c>
       <c r="H305" t="n">
-        <v>0.198</v>
+        <v>0.293</v>
       </c>
       <c r="I305" t="n">
-        <v>0.838</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="306">
@@ -14329,7 +14329,7 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>0.955</v>
+        <v>0.957</v>
       </c>
       <c r="H309" t="n">
         <v>1</v>
@@ -14366,10 +14366,10 @@
         <v>0.962</v>
       </c>
       <c r="G310" t="n">
-        <v>0.897</v>
+        <v>0.899</v>
       </c>
       <c r="H310" t="n">
-        <v>0.138</v>
+        <v>0.142</v>
       </c>
       <c r="I310" t="n">
         <v>1</v>
@@ -14400,10 +14400,10 @@
         <v>6</v>
       </c>
       <c r="F311" t="n">
-        <v>0.875</v>
+        <v>0.877</v>
       </c>
       <c r="G311" t="n">
-        <v>0.863</v>
+        <v>0.865</v>
       </c>
       <c r="H311" t="n">
         <v>1</v>
@@ -14437,10 +14437,10 @@
         <v>7</v>
       </c>
       <c r="F312" t="n">
-        <v>0.88</v>
+        <v>0.886</v>
       </c>
       <c r="G312" t="n">
-        <v>0.875</v>
+        <v>0.882</v>
       </c>
       <c r="H312" t="n">
         <v>1</v>
@@ -14551,7 +14551,7 @@
         <v>0.982</v>
       </c>
       <c r="G315" t="n">
-        <v>0.955</v>
+        <v>0.957</v>
       </c>
       <c r="H315" t="n">
         <v>0.626</v>
@@ -14585,10 +14585,10 @@
         <v>11</v>
       </c>
       <c r="F316" t="n">
-        <v>0.864</v>
+        <v>0.863</v>
       </c>
       <c r="G316" t="n">
-        <v>0.852</v>
+        <v>0.85</v>
       </c>
       <c r="H316" t="n">
         <v>1</v>
@@ -14770,13 +14770,13 @@
         <v>16</v>
       </c>
       <c r="F321" t="n">
-        <v>0.38</v>
+        <v>0.389</v>
       </c>
       <c r="G321" t="n">
-        <v>0.347</v>
+        <v>0.363</v>
       </c>
       <c r="H321" t="n">
-        <v>0.681</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="I321" t="n">
         <v>1</v>
@@ -14816,7 +14816,7 @@
         <v>0.0853</v>
       </c>
       <c r="I322" t="n">
-        <v>0.421</v>
+        <v>0.401</v>
       </c>
     </row>
     <row r="323">
@@ -14918,16 +14918,16 @@
         <v>4</v>
       </c>
       <c r="F325" t="n">
-        <v>0.864</v>
+        <v>0.909</v>
       </c>
       <c r="G325" t="n">
-        <v>0.955</v>
+        <v>1</v>
       </c>
       <c r="H325" t="n">
-        <v>0.607</v>
+        <v>0.488</v>
       </c>
       <c r="I325" t="n">
-        <v>1</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="326">
@@ -14958,13 +14958,13 @@
         <v>0.743</v>
       </c>
       <c r="G326" t="n">
-        <v>0.772</v>
+        <v>0.792</v>
       </c>
       <c r="H326" t="n">
-        <v>0.743</v>
+        <v>0.506</v>
       </c>
       <c r="I326" t="n">
-        <v>1</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="327">
@@ -14992,16 +14992,16 @@
         <v>6</v>
       </c>
       <c r="F327" t="n">
-        <v>0.761</v>
+        <v>0.772</v>
       </c>
       <c r="G327" t="n">
-        <v>0.891</v>
+        <v>0.902</v>
       </c>
       <c r="H327" t="n">
-        <v>0.0313</v>
+        <v>0.0269</v>
       </c>
       <c r="I327" t="n">
-        <v>0.25</v>
+        <v>0.216</v>
       </c>
     </row>
     <row r="328">
@@ -15029,16 +15029,16 @@
         <v>7</v>
       </c>
       <c r="F328" t="n">
-        <v>0.776</v>
+        <v>0.824</v>
       </c>
       <c r="G328" t="n">
-        <v>0.824</v>
+        <v>0.882</v>
       </c>
       <c r="H328" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.387</v>
       </c>
       <c r="I328" t="n">
-        <v>1</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="329">
@@ -15140,16 +15140,16 @@
         <v>10</v>
       </c>
       <c r="F331" t="n">
-        <v>0.675</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G331" t="n">
-        <v>0.8</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H331" t="n">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="I331" t="n">
-        <v>0.421</v>
+        <v>0.401</v>
       </c>
     </row>
     <row r="332">
@@ -15177,10 +15177,10 @@
         <v>11</v>
       </c>
       <c r="F332" t="n">
-        <v>0.769</v>
+        <v>0.75</v>
       </c>
       <c r="G332" t="n">
-        <v>0.758</v>
+        <v>0.739</v>
       </c>
       <c r="H332" t="n">
         <v>1</v>
@@ -15223,7 +15223,7 @@
         <v>0.545</v>
       </c>
       <c r="I333" t="n">
-        <v>1</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="334">
@@ -15334,7 +15334,7 @@
         <v>0.398</v>
       </c>
       <c r="I336" t="n">
-        <v>1</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="337">
@@ -15362,13 +15362,13 @@
         <v>16</v>
       </c>
       <c r="F337" t="n">
-        <v>0.745</v>
+        <v>0.737</v>
       </c>
       <c r="G337" t="n">
-        <v>0.782</v>
+        <v>0.789</v>
       </c>
       <c r="H337" t="n">
-        <v>0.823</v>
+        <v>0.66</v>
       </c>
       <c r="I337" t="n">
         <v>1</v>
@@ -15408,7 +15408,7 @@
         <v>0.188</v>
       </c>
       <c r="I338" t="n">
-        <v>0.752</v>
+        <v>0.792</v>
       </c>
     </row>
     <row r="339">
@@ -15510,10 +15510,10 @@
         <v>4</v>
       </c>
       <c r="F341" t="n">
-        <v>0.98</v>
+        <v>0.987</v>
       </c>
       <c r="G341" t="n">
-        <v>0.987</v>
+        <v>0.993</v>
       </c>
       <c r="H341" t="n">
         <v>1</v>
@@ -15550,13 +15550,13 @@
         <v>0.8070000000000001</v>
       </c>
       <c r="G342" t="n">
-        <v>0.753</v>
+        <v>0.767</v>
       </c>
       <c r="H342" t="n">
-        <v>0.329</v>
+        <v>0.481</v>
       </c>
       <c r="I342" t="n">
-        <v>0.78</v>
+        <v>0.907</v>
       </c>
     </row>
     <row r="343">
@@ -15584,16 +15584,16 @@
         <v>6</v>
       </c>
       <c r="F343" t="n">
-        <v>0.787</v>
+        <v>0.793</v>
       </c>
       <c r="G343" t="n">
-        <v>0.86</v>
+        <v>0.867</v>
       </c>
       <c r="H343" t="n">
-        <v>0.13</v>
+        <v>0.124</v>
       </c>
       <c r="I343" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.792</v>
       </c>
     </row>
     <row r="344">
@@ -15621,16 +15621,16 @@
         <v>7</v>
       </c>
       <c r="F344" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="G344" t="n">
-        <v>0.853</v>
+        <v>0.873</v>
       </c>
       <c r="H344" t="n">
-        <v>0.439</v>
+        <v>0.51</v>
       </c>
       <c r="I344" t="n">
-        <v>0.78</v>
+        <v>0.907</v>
       </c>
     </row>
     <row r="345">
@@ -15732,16 +15732,16 @@
         <v>10</v>
       </c>
       <c r="F347" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="G347" t="n">
-        <v>0.873</v>
+        <v>0.88</v>
       </c>
       <c r="H347" t="n">
-        <v>0.262</v>
+        <v>0.253</v>
       </c>
       <c r="I347" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="348">
@@ -15769,10 +15769,10 @@
         <v>11</v>
       </c>
       <c r="F348" t="n">
-        <v>0.787</v>
+        <v>0.773</v>
       </c>
       <c r="G348" t="n">
-        <v>0.78</v>
+        <v>0.767</v>
       </c>
       <c r="H348" t="n">
         <v>1</v>
@@ -15889,7 +15889,7 @@
         <v>0.384</v>
       </c>
       <c r="I351" t="n">
-        <v>0.78</v>
+        <v>0.907</v>
       </c>
     </row>
     <row r="352">
@@ -15926,7 +15926,7 @@
         <v>0.419</v>
       </c>
       <c r="I352" t="n">
-        <v>0.78</v>
+        <v>0.907</v>
       </c>
     </row>
     <row r="353">
@@ -15957,13 +15957,13 @@
         <v>0.46</v>
       </c>
       <c r="G353" t="n">
-        <v>0.367</v>
+        <v>0.38</v>
       </c>
       <c r="H353" t="n">
-        <v>0.127</v>
+        <v>0.198</v>
       </c>
       <c r="I353" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.792</v>
       </c>
     </row>
     <row r="354">
@@ -16142,10 +16142,10 @@
         <v>0.962</v>
       </c>
       <c r="G358" t="n">
-        <v>0.881</v>
+        <v>0.884</v>
       </c>
       <c r="H358" t="n">
-        <v>0.0822</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="I358" t="n">
         <v>1</v>
@@ -16176,10 +16176,10 @@
         <v>6</v>
       </c>
       <c r="F359" t="n">
-        <v>0.875</v>
+        <v>0.877</v>
       </c>
       <c r="G359" t="n">
-        <v>0.899</v>
+        <v>0.9</v>
       </c>
       <c r="H359" t="n">
         <v>0.636</v>
@@ -16213,13 +16213,13 @@
         <v>7</v>
       </c>
       <c r="F360" t="n">
-        <v>0.88</v>
+        <v>0.886</v>
       </c>
       <c r="G360" t="n">
-        <v>0.899</v>
+        <v>0.902</v>
       </c>
       <c r="H360" t="n">
-        <v>0.8</v>
+        <v>0.801</v>
       </c>
       <c r="I360" t="n">
         <v>1</v>
@@ -16327,10 +16327,10 @@
         <v>0.982</v>
       </c>
       <c r="G363" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.944</v>
       </c>
       <c r="H363" t="n">
-        <v>0.381</v>
+        <v>0.38</v>
       </c>
       <c r="I363" t="n">
         <v>1</v>
@@ -16361,10 +16361,10 @@
         <v>11</v>
       </c>
       <c r="F364" t="n">
-        <v>0.864</v>
+        <v>0.863</v>
       </c>
       <c r="G364" t="n">
-        <v>0.872</v>
+        <v>0.87</v>
       </c>
       <c r="H364" t="n">
         <v>1</v>
@@ -16546,13 +16546,13 @@
         <v>16</v>
       </c>
       <c r="F369" t="n">
-        <v>0.38</v>
+        <v>0.389</v>
       </c>
       <c r="G369" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="H369" t="n">
-        <v>0.491</v>
+        <v>0.584</v>
       </c>
       <c r="I369" t="n">
         <v>1</v>
@@ -16694,10 +16694,10 @@
         <v>4</v>
       </c>
       <c r="F373" t="n">
-        <v>0.864</v>
+        <v>0.909</v>
       </c>
       <c r="G373" t="n">
-        <v>0.909</v>
+        <v>0.955</v>
       </c>
       <c r="H373" t="n">
         <v>1</v>
@@ -16734,7 +16734,7 @@
         <v>0.743</v>
       </c>
       <c r="G374" t="n">
-        <v>0.733</v>
+        <v>0.752</v>
       </c>
       <c r="H374" t="n">
         <v>1</v>
@@ -16768,16 +16768,16 @@
         <v>6</v>
       </c>
       <c r="F375" t="n">
-        <v>0.761</v>
+        <v>0.772</v>
       </c>
       <c r="G375" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="H375" t="n">
-        <v>0.0864</v>
+        <v>0.0789</v>
       </c>
       <c r="I375" t="n">
-        <v>0.461</v>
+        <v>0.421</v>
       </c>
     </row>
     <row r="376">
@@ -16805,13 +16805,13 @@
         <v>7</v>
       </c>
       <c r="F376" t="n">
-        <v>0.776</v>
+        <v>0.824</v>
       </c>
       <c r="G376" t="n">
-        <v>0.835</v>
+        <v>0.871</v>
       </c>
       <c r="H376" t="n">
-        <v>0.438</v>
+        <v>0.523</v>
       </c>
       <c r="I376" t="n">
         <v>1</v>
@@ -16916,16 +16916,16 @@
         <v>10</v>
       </c>
       <c r="F379" t="n">
-        <v>0.675</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G379" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.827</v>
       </c>
       <c r="H379" t="n">
-        <v>0.0694</v>
+        <v>0.0653</v>
       </c>
       <c r="I379" t="n">
-        <v>0.461</v>
+        <v>0.421</v>
       </c>
     </row>
     <row r="380">
@@ -16953,13 +16953,13 @@
         <v>11</v>
       </c>
       <c r="F380" t="n">
-        <v>0.769</v>
+        <v>0.75</v>
       </c>
       <c r="G380" t="n">
-        <v>0.747</v>
+        <v>0.728</v>
       </c>
       <c r="H380" t="n">
-        <v>0.863</v>
+        <v>0.867</v>
       </c>
       <c r="I380" t="n">
         <v>1</v>
@@ -17138,10 +17138,10 @@
         <v>16</v>
       </c>
       <c r="F385" t="n">
-        <v>0.745</v>
+        <v>0.737</v>
       </c>
       <c r="G385" t="n">
-        <v>0.727</v>
+        <v>0.737</v>
       </c>
       <c r="H385" t="n">
         <v>1</v>
@@ -17286,10 +17286,10 @@
         <v>4</v>
       </c>
       <c r="F389" t="n">
-        <v>0.98</v>
+        <v>0.987</v>
       </c>
       <c r="G389" t="n">
-        <v>0.987</v>
+        <v>0.993</v>
       </c>
       <c r="H389" t="n">
         <v>1</v>
@@ -17326,13 +17326,13 @@
         <v>0.8070000000000001</v>
       </c>
       <c r="G390" t="n">
-        <v>0.773</v>
+        <v>0.787</v>
       </c>
       <c r="H390" t="n">
-        <v>0.571</v>
+        <v>0.774</v>
       </c>
       <c r="I390" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
     </row>
     <row r="391">
@@ -17360,16 +17360,16 @@
         <v>6</v>
       </c>
       <c r="F391" t="n">
-        <v>0.787</v>
+        <v>0.793</v>
       </c>
       <c r="G391" t="n">
-        <v>0.84</v>
+        <v>0.847</v>
       </c>
       <c r="H391" t="n">
-        <v>0.3</v>
+        <v>0.293</v>
       </c>
       <c r="I391" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.669</v>
       </c>
     </row>
     <row r="392">
@@ -17397,16 +17397,16 @@
         <v>7</v>
       </c>
       <c r="F392" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="G392" t="n">
-        <v>0.847</v>
+        <v>0.867</v>
       </c>
       <c r="H392" t="n">
-        <v>0.539</v>
+        <v>0.625</v>
       </c>
       <c r="I392" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
     </row>
     <row r="393">
@@ -17508,16 +17508,16 @@
         <v>10</v>
       </c>
       <c r="F395" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="G395" t="n">
         <v>0.893</v>
       </c>
       <c r="H395" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.134</v>
       </c>
       <c r="I395" t="n">
-        <v>0.394</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="396">
@@ -17545,16 +17545,16 @@
         <v>11</v>
       </c>
       <c r="F396" t="n">
-        <v>0.787</v>
+        <v>0.773</v>
       </c>
       <c r="G396" t="n">
-        <v>0.747</v>
+        <v>0.74</v>
       </c>
       <c r="H396" t="n">
-        <v>0.495</v>
+        <v>0.591</v>
       </c>
       <c r="I396" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
     </row>
     <row r="397">
@@ -17665,7 +17665,7 @@
         <v>0.0307</v>
       </c>
       <c r="I399" t="n">
-        <v>0.164</v>
+        <v>0.178</v>
       </c>
     </row>
     <row r="400">
@@ -17733,13 +17733,13 @@
         <v>0.46</v>
       </c>
       <c r="G401" t="n">
-        <v>0.32</v>
+        <v>0.333</v>
       </c>
       <c r="H401" t="n">
-        <v>0.0177</v>
+        <v>0.0334</v>
       </c>
       <c r="I401" t="n">
-        <v>0.142</v>
+        <v>0.178</v>
       </c>
     </row>
     <row r="402">
@@ -17881,7 +17881,7 @@
         <v>1</v>
       </c>
       <c r="G405" t="n">
-        <v>0.955</v>
+        <v>0.957</v>
       </c>
       <c r="H405" t="n">
         <v>1</v>
@@ -17918,13 +17918,13 @@
         <v>0.962</v>
       </c>
       <c r="G406" t="n">
-        <v>0.885</v>
+        <v>0.888</v>
       </c>
       <c r="H406" t="n">
-        <v>0.0858</v>
+        <v>0.0888</v>
       </c>
       <c r="I406" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="407">
@@ -17952,10 +17952,10 @@
         <v>6</v>
       </c>
       <c r="F407" t="n">
-        <v>0.875</v>
+        <v>0.877</v>
       </c>
       <c r="G407" t="n">
-        <v>0.878</v>
+        <v>0.879</v>
       </c>
       <c r="H407" t="n">
         <v>1</v>
@@ -17989,13 +17989,13 @@
         <v>7</v>
       </c>
       <c r="F408" t="n">
-        <v>0.88</v>
+        <v>0.886</v>
       </c>
       <c r="G408" t="n">
-        <v>0.897</v>
+        <v>0.901</v>
       </c>
       <c r="H408" t="n">
-        <v>0.8</v>
+        <v>0.802</v>
       </c>
       <c r="I408" t="n">
         <v>1</v>
@@ -18137,13 +18137,13 @@
         <v>11</v>
       </c>
       <c r="F412" t="n">
-        <v>0.864</v>
+        <v>0.863</v>
       </c>
       <c r="G412" t="n">
         <v>0.835</v>
       </c>
       <c r="H412" t="n">
-        <v>0.662</v>
+        <v>0.664</v>
       </c>
       <c r="I412" t="n">
         <v>1</v>
@@ -18322,13 +18322,13 @@
         <v>16</v>
       </c>
       <c r="F417" t="n">
-        <v>0.38</v>
+        <v>0.389</v>
       </c>
       <c r="G417" t="n">
-        <v>0.315</v>
+        <v>0.331</v>
       </c>
       <c r="H417" t="n">
-        <v>0.336</v>
+        <v>0.413</v>
       </c>
       <c r="I417" t="n">
         <v>1</v>
@@ -18368,7 +18368,7 @@
         <v>0.125</v>
       </c>
       <c r="I418" t="n">
-        <v>0.529</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="419">
@@ -18405,7 +18405,7 @@
         <v>0.491</v>
       </c>
       <c r="I419" t="n">
-        <v>0.886</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="420">
@@ -18470,16 +18470,16 @@
         <v>4</v>
       </c>
       <c r="F421" t="n">
-        <v>0.864</v>
+        <v>0.909</v>
       </c>
       <c r="G421" t="n">
-        <v>0.955</v>
+        <v>1</v>
       </c>
       <c r="H421" t="n">
-        <v>0.607</v>
+        <v>0.488</v>
       </c>
       <c r="I421" t="n">
-        <v>0.886</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="422">
@@ -18510,13 +18510,13 @@
         <v>0.743</v>
       </c>
       <c r="G422" t="n">
-        <v>0.762</v>
+        <v>0.782</v>
       </c>
       <c r="H422" t="n">
-        <v>0.871</v>
+        <v>0.62</v>
       </c>
       <c r="I422" t="n">
-        <v>1</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="423">
@@ -18544,16 +18544,16 @@
         <v>6</v>
       </c>
       <c r="F423" t="n">
-        <v>0.761</v>
+        <v>0.772</v>
       </c>
       <c r="G423" t="n">
-        <v>0.859</v>
+        <v>0.87</v>
       </c>
       <c r="H423" t="n">
-        <v>0.132</v>
+        <v>0.123</v>
       </c>
       <c r="I423" t="n">
-        <v>0.529</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="424">
@@ -18581,16 +18581,16 @@
         <v>7</v>
       </c>
       <c r="F424" t="n">
-        <v>0.776</v>
+        <v>0.824</v>
       </c>
       <c r="G424" t="n">
-        <v>0.824</v>
+        <v>0.859</v>
       </c>
       <c r="H424" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.675</v>
       </c>
       <c r="I424" t="n">
-        <v>0.886</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="425">
@@ -18692,16 +18692,16 @@
         <v>10</v>
       </c>
       <c r="F427" t="n">
-        <v>0.675</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G427" t="n">
-        <v>0.825</v>
+        <v>0.827</v>
       </c>
       <c r="H427" t="n">
-        <v>0.0438</v>
+        <v>0.0653</v>
       </c>
       <c r="I427" t="n">
-        <v>0.351</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="428">
@@ -18729,16 +18729,16 @@
         <v>11</v>
       </c>
       <c r="F428" t="n">
-        <v>0.769</v>
+        <v>0.75</v>
       </c>
       <c r="G428" t="n">
-        <v>0.725</v>
+        <v>0.717</v>
       </c>
       <c r="H428" t="n">
-        <v>0.609</v>
+        <v>0.739</v>
       </c>
       <c r="I428" t="n">
-        <v>0.886</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="429">
@@ -18775,7 +18775,7 @@
         <v>0.415</v>
       </c>
       <c r="I429" t="n">
-        <v>0.886</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="430">
@@ -18849,7 +18849,7 @@
         <v>0.529</v>
       </c>
       <c r="I431" t="n">
-        <v>0.886</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="432">
@@ -18886,7 +18886,7 @@
         <v>0.398</v>
       </c>
       <c r="I432" t="n">
-        <v>0.886</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="433">
@@ -18914,10 +18914,10 @@
         <v>16</v>
       </c>
       <c r="F433" t="n">
-        <v>0.745</v>
+        <v>0.737</v>
       </c>
       <c r="G433" t="n">
-        <v>0.727</v>
+        <v>0.737</v>
       </c>
       <c r="H433" t="n">
         <v>1</v>
@@ -18960,7 +18960,7 @@
         <v>0.312</v>
       </c>
       <c r="I434" t="n">
-        <v>0.908</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="435">
@@ -19062,10 +19062,10 @@
         <v>4</v>
       </c>
       <c r="F437" t="n">
-        <v>0.98</v>
+        <v>0.987</v>
       </c>
       <c r="G437" t="n">
-        <v>0.98</v>
+        <v>0.987</v>
       </c>
       <c r="H437" t="n">
         <v>1</v>
@@ -19102,10 +19102,10 @@
         <v>0.8070000000000001</v>
       </c>
       <c r="G438" t="n">
-        <v>0.787</v>
+        <v>0.793</v>
       </c>
       <c r="H438" t="n">
-        <v>0.774</v>
+        <v>0.885</v>
       </c>
       <c r="I438" t="n">
         <v>1</v>
@@ -19136,16 +19136,16 @@
         <v>6</v>
       </c>
       <c r="F439" t="n">
-        <v>0.787</v>
+        <v>0.793</v>
       </c>
       <c r="G439" t="n">
         <v>0.853</v>
       </c>
       <c r="H439" t="n">
-        <v>0.176</v>
+        <v>0.226</v>
       </c>
       <c r="I439" t="n">
-        <v>0.703</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="440">
@@ -19173,13 +19173,13 @@
         <v>7</v>
       </c>
       <c r="F440" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="G440" t="n">
-        <v>0.84</v>
+        <v>0.867</v>
       </c>
       <c r="H440" t="n">
-        <v>0.648</v>
+        <v>0.625</v>
       </c>
       <c r="I440" t="n">
         <v>1</v>
@@ -19284,16 +19284,16 @@
         <v>10</v>
       </c>
       <c r="F443" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="G443" t="n">
-        <v>0.867</v>
+        <v>0.873</v>
       </c>
       <c r="H443" t="n">
-        <v>0.341</v>
+        <v>0.332</v>
       </c>
       <c r="I443" t="n">
-        <v>0.908</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="444">
@@ -19321,13 +19321,13 @@
         <v>11</v>
       </c>
       <c r="F444" t="n">
-        <v>0.787</v>
+        <v>0.773</v>
       </c>
       <c r="G444" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.793</v>
       </c>
       <c r="H444" t="n">
-        <v>0.774</v>
+        <v>0.779</v>
       </c>
       <c r="I444" t="n">
         <v>1</v>
@@ -19441,7 +19441,7 @@
         <v>0.135</v>
       </c>
       <c r="I447" t="n">
-        <v>0.703</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="448">
@@ -19509,13 +19509,13 @@
         <v>0.46</v>
       </c>
       <c r="G449" t="n">
-        <v>0.7</v>
+        <v>0.713</v>
       </c>
       <c r="H449" t="n">
-        <v>3.88e-05</v>
+        <v>1.28e-05</v>
       </c>
       <c r="I449" t="n">
-        <v>0.000621</v>
+        <v>0.000205</v>
       </c>
     </row>
     <row r="450">
@@ -19697,10 +19697,10 @@
         <v>1</v>
       </c>
       <c r="H454" t="n">
-        <v>0.248</v>
+        <v>0.247</v>
       </c>
       <c r="I454" t="n">
-        <v>0.444</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="455">
@@ -19728,16 +19728,16 @@
         <v>6</v>
       </c>
       <c r="F455" t="n">
-        <v>0.875</v>
+        <v>0.877</v>
       </c>
       <c r="G455" t="n">
         <v>0.961</v>
       </c>
       <c r="H455" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="I455" t="n">
-        <v>0.214</v>
+        <v>0.216</v>
       </c>
     </row>
     <row r="456">
@@ -19765,16 +19765,16 @@
         <v>7</v>
       </c>
       <c r="F456" t="n">
-        <v>0.88</v>
+        <v>0.886</v>
       </c>
       <c r="G456" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.945</v>
       </c>
       <c r="H456" t="n">
-        <v>0.25</v>
+        <v>0.251</v>
       </c>
       <c r="I456" t="n">
-        <v>0.444</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="457">
@@ -19879,7 +19879,7 @@
         <v>0.982</v>
       </c>
       <c r="G459" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="H459" t="n">
         <v>1</v>
@@ -19913,10 +19913,10 @@
         <v>11</v>
       </c>
       <c r="F460" t="n">
-        <v>0.864</v>
+        <v>0.863</v>
       </c>
       <c r="G460" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
       <c r="H460" t="n">
         <v>0.038</v>
@@ -20098,16 +20098,16 @@
         <v>16</v>
       </c>
       <c r="F465" t="n">
-        <v>0.38</v>
+        <v>0.389</v>
       </c>
       <c r="G465" t="n">
-        <v>0.647</v>
+        <v>0.706</v>
       </c>
       <c r="H465" t="n">
-        <v>0.00953</v>
+        <v>0.00154</v>
       </c>
       <c r="I465" t="n">
-        <v>0.0508</v>
+        <v>0.008189999999999999</v>
       </c>
     </row>
     <row r="466">
@@ -20246,10 +20246,10 @@
         <v>4</v>
       </c>
       <c r="F469" t="n">
-        <v>0.864</v>
+        <v>0.909</v>
       </c>
       <c r="G469" t="n">
-        <v>0.864</v>
+        <v>0.909</v>
       </c>
       <c r="H469" t="n">
         <v>1</v>
@@ -20286,13 +20286,13 @@
         <v>0.743</v>
       </c>
       <c r="G470" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H470" t="n">
-        <v>0.437</v>
+        <v>0.532</v>
       </c>
       <c r="I470" t="n">
-        <v>0.794</v>
+        <v>0.881</v>
       </c>
     </row>
     <row r="471">
@@ -20320,16 +20320,16 @@
         <v>6</v>
       </c>
       <c r="F471" t="n">
-        <v>0.761</v>
+        <v>0.772</v>
       </c>
       <c r="G471" t="n">
         <v>0.793</v>
       </c>
       <c r="H471" t="n">
-        <v>0.723</v>
+        <v>0.858</v>
       </c>
       <c r="I471" t="n">
-        <v>0.965</v>
+        <v>1</v>
       </c>
     </row>
     <row r="472">
@@ -20357,10 +20357,10 @@
         <v>7</v>
       </c>
       <c r="F472" t="n">
-        <v>0.776</v>
+        <v>0.824</v>
       </c>
       <c r="G472" t="n">
-        <v>0.765</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H472" t="n">
         <v>1</v>
@@ -20440,7 +20440,7 @@
         <v>0.791</v>
       </c>
       <c r="I474" t="n">
-        <v>0.974</v>
+        <v>1</v>
       </c>
     </row>
     <row r="475">
@@ -20468,13 +20468,13 @@
         <v>10</v>
       </c>
       <c r="F475" t="n">
-        <v>0.675</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G475" t="n">
-        <v>0.775</v>
+        <v>0.79</v>
       </c>
       <c r="H475" t="n">
-        <v>0.215</v>
+        <v>0.209</v>
       </c>
       <c r="I475" t="n">
         <v>0.642</v>
@@ -20505,16 +20505,16 @@
         <v>11</v>
       </c>
       <c r="F476" t="n">
-        <v>0.769</v>
+        <v>0.75</v>
       </c>
       <c r="G476" t="n">
-        <v>0.703</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="H476" t="n">
-        <v>0.4</v>
+        <v>0.413</v>
       </c>
       <c r="I476" t="n">
-        <v>0.794</v>
+        <v>0.881</v>
       </c>
     </row>
     <row r="477">
@@ -20625,7 +20625,7 @@
         <v>0.447</v>
       </c>
       <c r="I479" t="n">
-        <v>0.794</v>
+        <v>0.881</v>
       </c>
     </row>
     <row r="480">
@@ -20690,16 +20690,16 @@
         <v>16</v>
       </c>
       <c r="F481" t="n">
-        <v>0.745</v>
+        <v>0.737</v>
       </c>
       <c r="G481" t="n">
-        <v>0.4</v>
+        <v>0.421</v>
       </c>
       <c r="H481" t="n">
-        <v>0.000461</v>
+        <v>0.00115</v>
       </c>
       <c r="I481" t="n">
-        <v>0.00369</v>
+        <v>0.00923</v>
       </c>
     </row>
   </sheetData>

--- a/eval/learning-curve/results/statistical_tests_full150.xlsx
+++ b/eval/learning-curve/results/statistical_tests_full150.xlsx
@@ -506,16 +506,16 @@
         <v>0.0629</v>
       </c>
       <c r="F2" t="n">
-        <v>0.844</v>
+        <v>0.845</v>
       </c>
       <c r="G2" t="n">
         <v>0.875</v>
       </c>
       <c r="H2" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0842</v>
+        <v>0.0838</v>
       </c>
       <c r="J2" t="n">
         <v>0.157</v>
@@ -546,16 +546,16 @@
         <v>0.0785</v>
       </c>
       <c r="F3" t="n">
-        <v>0.844</v>
+        <v>0.845</v>
       </c>
       <c r="G3" t="n">
         <v>0.875</v>
       </c>
       <c r="H3" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0842</v>
+        <v>0.0838</v>
       </c>
       <c r="J3" t="n">
         <v>0.196</v>
@@ -586,16 +586,16 @@
         <v>0.276</v>
       </c>
       <c r="F4" t="n">
-        <v>0.844</v>
+        <v>0.845</v>
       </c>
       <c r="G4" t="n">
-        <v>0.862</v>
+        <v>0.863</v>
       </c>
       <c r="H4" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="J4" t="n">
         <v>0.345</v>
@@ -626,16 +626,16 @@
         <v>0.28</v>
       </c>
       <c r="F5" t="n">
-        <v>0.844</v>
+        <v>0.845</v>
       </c>
       <c r="G5" t="n">
-        <v>0.862</v>
+        <v>0.863</v>
       </c>
       <c r="H5" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="J5" t="n">
         <v>0.35</v>
@@ -663,22 +663,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.41</v>
+        <v>0.392</v>
       </c>
       <c r="F6" t="n">
-        <v>0.844</v>
+        <v>0.845</v>
       </c>
       <c r="G6" t="n">
-        <v>0.857</v>
+        <v>0.858</v>
       </c>
       <c r="H6" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0892</v>
       </c>
       <c r="J6" t="n">
-        <v>0.41</v>
+        <v>0.392</v>
       </c>
     </row>
     <row r="7">
@@ -703,22 +703,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.495</v>
+        <v>0.477</v>
       </c>
       <c r="F7" t="n">
-        <v>0.844</v>
+        <v>0.845</v>
       </c>
       <c r="G7" t="n">
-        <v>0.857</v>
+        <v>0.858</v>
       </c>
       <c r="H7" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0892</v>
       </c>
       <c r="J7" t="n">
-        <v>0.495</v>
+        <v>0.477</v>
       </c>
     </row>
     <row r="8">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.0955</v>
+        <v>0.0881</v>
       </c>
       <c r="F8" t="n">
-        <v>0.844</v>
+        <v>0.845</v>
       </c>
       <c r="G8" t="n">
-        <v>0.873</v>
+        <v>0.875</v>
       </c>
       <c r="H8" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0698</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.191</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="9">
@@ -786,19 +786,19 @@
         <v>0.139</v>
       </c>
       <c r="F9" t="n">
-        <v>0.844</v>
+        <v>0.845</v>
       </c>
       <c r="G9" t="n">
-        <v>0.873</v>
+        <v>0.875</v>
       </c>
       <c r="H9" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0698</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.233</v>
+        <v>0.232</v>
       </c>
     </row>
     <row r="10">
@@ -826,16 +826,16 @@
         <v>0.00116</v>
       </c>
       <c r="F10" t="n">
-        <v>0.844</v>
+        <v>0.845</v>
       </c>
       <c r="G10" t="n">
-        <v>0.91</v>
+        <v>0.911</v>
       </c>
       <c r="H10" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0633</v>
+        <v>0.0636</v>
       </c>
       <c r="J10" t="n">
         <v>0.0116</v>
@@ -866,16 +866,16 @@
         <v>0.0015</v>
       </c>
       <c r="F11" t="n">
-        <v>0.844</v>
+        <v>0.845</v>
       </c>
       <c r="G11" t="n">
-        <v>0.91</v>
+        <v>0.911</v>
       </c>
       <c r="H11" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0633</v>
+        <v>0.0636</v>
       </c>
       <c r="J11" t="n">
         <v>0.0094</v>
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.0303</v>
+        <v>0.0294</v>
       </c>
       <c r="F12" t="n">
         <v>0.803</v>
       </c>
       <c r="G12" t="n">
-        <v>0.826</v>
+        <v>0.828</v>
       </c>
       <c r="H12" t="n">
         <v>0.149</v>
       </c>
       <c r="I12" t="n">
-        <v>0.16</v>
+        <v>0.161</v>
       </c>
       <c r="J12" t="n">
-        <v>0.101</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="13">
@@ -949,13 +949,13 @@
         <v>0.803</v>
       </c>
       <c r="G13" t="n">
-        <v>0.826</v>
+        <v>0.828</v>
       </c>
       <c r="H13" t="n">
         <v>0.149</v>
       </c>
       <c r="I13" t="n">
-        <v>0.16</v>
+        <v>0.161</v>
       </c>
       <c r="J13" t="n">
         <v>0.118</v>
@@ -983,13 +983,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.149</v>
+        <v>0.133</v>
       </c>
       <c r="F14" t="n">
         <v>0.803</v>
       </c>
       <c r="G14" t="n">
-        <v>0.821</v>
+        <v>0.823</v>
       </c>
       <c r="H14" t="n">
         <v>0.149</v>
@@ -998,7 +998,7 @@
         <v>0.167</v>
       </c>
       <c r="J14" t="n">
-        <v>0.248</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="15">
@@ -1023,13 +1023,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F15" t="n">
         <v>0.803</v>
       </c>
       <c r="G15" t="n">
-        <v>0.821</v>
+        <v>0.823</v>
       </c>
       <c r="H15" t="n">
         <v>0.149</v>
@@ -1038,7 +1038,7 @@
         <v>0.167</v>
       </c>
       <c r="J15" t="n">
-        <v>0.233</v>
+        <v>0.232</v>
       </c>
     </row>
     <row r="16">
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.239</v>
+        <v>0.23</v>
       </c>
       <c r="F16" t="n">
         <v>0.803</v>
       </c>
       <c r="G16" t="n">
-        <v>0.819</v>
+        <v>0.82</v>
       </c>
       <c r="H16" t="n">
         <v>0.149</v>
@@ -1078,7 +1078,7 @@
         <v>0.169</v>
       </c>
       <c r="J16" t="n">
-        <v>0.341</v>
+        <v>0.329</v>
       </c>
     </row>
     <row r="17">
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.272</v>
+        <v>0.258</v>
       </c>
       <c r="F17" t="n">
         <v>0.803</v>
       </c>
       <c r="G17" t="n">
-        <v>0.819</v>
+        <v>0.82</v>
       </c>
       <c r="H17" t="n">
         <v>0.149</v>
@@ -1143,22 +1143,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.358</v>
+        <v>0.349</v>
       </c>
       <c r="F18" t="n">
         <v>0.803</v>
       </c>
       <c r="G18" t="n">
-        <v>0.819</v>
+        <v>0.82</v>
       </c>
       <c r="H18" t="n">
         <v>0.149</v>
       </c>
       <c r="I18" t="n">
-        <v>0.182</v>
+        <v>0.183</v>
       </c>
       <c r="J18" t="n">
-        <v>0.398</v>
+        <v>0.388</v>
       </c>
     </row>
     <row r="19">
@@ -1189,13 +1189,13 @@
         <v>0.803</v>
       </c>
       <c r="G19" t="n">
-        <v>0.819</v>
+        <v>0.82</v>
       </c>
       <c r="H19" t="n">
         <v>0.149</v>
       </c>
       <c r="I19" t="n">
-        <v>0.182</v>
+        <v>0.183</v>
       </c>
       <c r="J19" t="n">
         <v>0.362</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0144</v>
+        <v>0.0152</v>
       </c>
       <c r="F20" t="n">
         <v>0.803</v>
@@ -1238,7 +1238,7 @@
         <v>0.0912</v>
       </c>
       <c r="J20" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="21">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.842</v>
+        <v>0.843</v>
       </c>
       <c r="F22" t="n">
         <v>0.868</v>
@@ -1318,7 +1318,7 @@
         <v>0.117</v>
       </c>
       <c r="J22" t="n">
-        <v>0.855</v>
+        <v>0.849</v>
       </c>
     </row>
     <row r="23">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.629</v>
+        <v>0.63</v>
       </c>
       <c r="F24" t="n">
         <v>0.868</v>
@@ -1398,7 +1398,7 @@
         <v>0.132</v>
       </c>
       <c r="J24" t="n">
-        <v>0.855</v>
+        <v>0.849</v>
       </c>
     </row>
     <row r="25">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="F26" t="n">
         <v>0.868</v>
@@ -1478,7 +1478,7 @@
         <v>0.104</v>
       </c>
       <c r="J26" t="n">
-        <v>0.855</v>
+        <v>0.849</v>
       </c>
     </row>
     <row r="27">
@@ -1543,13 +1543,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.74</v>
+        <v>0.745</v>
       </c>
       <c r="F28" t="n">
         <v>0.868</v>
       </c>
       <c r="G28" t="n">
-        <v>0.857</v>
+        <v>0.858</v>
       </c>
       <c r="H28" t="n">
         <v>0.156</v>
@@ -1558,7 +1558,7 @@
         <v>0.1</v>
       </c>
       <c r="J28" t="n">
-        <v>0.855</v>
+        <v>0.849</v>
       </c>
     </row>
     <row r="29">
@@ -1589,7 +1589,7 @@
         <v>0.868</v>
       </c>
       <c r="G29" t="n">
-        <v>0.857</v>
+        <v>0.858</v>
       </c>
       <c r="H29" t="n">
         <v>0.156</v>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.431</v>
+        <v>0.428</v>
       </c>
       <c r="F32" t="n">
         <v>0.795</v>
@@ -1718,7 +1718,7 @@
         <v>0.192</v>
       </c>
       <c r="J32" t="n">
-        <v>0.855</v>
+        <v>0.849</v>
       </c>
     </row>
     <row r="33">
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.855</v>
+        <v>0.849</v>
       </c>
       <c r="F34" t="n">
         <v>0.795</v>
@@ -1798,7 +1798,7 @@
         <v>0.177</v>
       </c>
       <c r="J34" t="n">
-        <v>0.855</v>
+        <v>0.849</v>
       </c>
     </row>
     <row r="35">
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.731</v>
+        <v>0.727</v>
       </c>
       <c r="F36" t="n">
         <v>0.795</v>
@@ -1878,7 +1878,7 @@
         <v>0.185</v>
       </c>
       <c r="J36" t="n">
-        <v>0.855</v>
+        <v>0.849</v>
       </c>
     </row>
     <row r="37">
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.709</v>
+        <v>0.708</v>
       </c>
       <c r="F38" t="n">
         <v>0.795</v>
@@ -1958,7 +1958,7 @@
         <v>0.189</v>
       </c>
       <c r="J38" t="n">
-        <v>0.855</v>
+        <v>0.849</v>
       </c>
     </row>
     <row r="39">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.000852</v>
+        <v>0.000855</v>
       </c>
       <c r="F40" t="n">
         <v>0.795</v>
@@ -2038,7 +2038,7 @@
         <v>0.0941</v>
       </c>
       <c r="J40" t="n">
-        <v>0.00852</v>
+        <v>0.00855</v>
       </c>
     </row>
     <row r="41">
@@ -2106,16 +2106,16 @@
         <v>0.215</v>
       </c>
       <c r="F42" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="G42" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="I42" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="J42" t="n">
         <v>0.269</v>
@@ -2146,19 +2146,19 @@
         <v>0.133</v>
       </c>
       <c r="F43" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="I43" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="J43" t="n">
-        <v>0.198</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="44">
@@ -2186,13 +2186,13 @@
         <v>0.661</v>
       </c>
       <c r="F44" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="G44" t="n">
-        <v>0.795</v>
+        <v>0.796</v>
       </c>
       <c r="H44" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="I44" t="n">
         <v>0.137</v>
@@ -2226,13 +2226,13 @@
         <v>0.6830000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="G45" t="n">
-        <v>0.795</v>
+        <v>0.796</v>
       </c>
       <c r="H45" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="I45" t="n">
         <v>0.137</v>
@@ -2263,22 +2263,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.845</v>
+        <v>0.824</v>
       </c>
       <c r="F46" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="G46" t="n">
-        <v>0.789</v>
+        <v>0.791</v>
       </c>
       <c r="H46" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="I46" t="n">
         <v>0.135</v>
       </c>
       <c r="J46" t="n">
-        <v>0.845</v>
+        <v>0.824</v>
       </c>
     </row>
     <row r="47">
@@ -2306,13 +2306,13 @@
         <v>0.754</v>
       </c>
       <c r="F47" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="G47" t="n">
-        <v>0.789</v>
+        <v>0.791</v>
       </c>
       <c r="H47" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="I47" t="n">
         <v>0.135</v>
@@ -2343,22 +2343,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.189</v>
+        <v>0.176</v>
       </c>
       <c r="F48" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="G48" t="n">
-        <v>0.82</v>
+        <v>0.822</v>
       </c>
       <c r="H48" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="I48" t="n">
-        <v>0.132</v>
+        <v>0.131</v>
       </c>
       <c r="J48" t="n">
-        <v>0.269</v>
+        <v>0.251</v>
       </c>
     </row>
     <row r="49">
@@ -2386,16 +2386,16 @@
         <v>0.158</v>
       </c>
       <c r="F49" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="G49" t="n">
-        <v>0.82</v>
+        <v>0.822</v>
       </c>
       <c r="H49" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="I49" t="n">
-        <v>0.132</v>
+        <v>0.131</v>
       </c>
       <c r="J49" t="n">
         <v>0.198</v>
@@ -2426,19 +2426,19 @@
         <v>0.0155</v>
       </c>
       <c r="F50" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="G50" t="n">
-        <v>0.861</v>
+        <v>0.862</v>
       </c>
       <c r="H50" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="I50" t="n">
-        <v>0.13</v>
+        <v>0.131</v>
       </c>
       <c r="J50" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="51">
@@ -2466,16 +2466,16 @@
         <v>0.0199</v>
       </c>
       <c r="F51" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="G51" t="n">
-        <v>0.861</v>
+        <v>0.862</v>
       </c>
       <c r="H51" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="I51" t="n">
-        <v>0.13</v>
+        <v>0.131</v>
       </c>
       <c r="J51" t="n">
         <v>0.0498</v>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.017</v>
+        <v>0.0175</v>
       </c>
       <c r="F52" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="G52" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H52" t="n">
         <v>0.18</v>
       </c>
       <c r="I52" t="n">
-        <v>0.176</v>
+        <v>0.177</v>
       </c>
       <c r="J52" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="53">
@@ -2546,16 +2546,16 @@
         <v>0.0309</v>
       </c>
       <c r="F53" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H53" t="n">
         <v>0.18</v>
       </c>
       <c r="I53" t="n">
-        <v>0.176</v>
+        <v>0.177</v>
       </c>
       <c r="J53" t="n">
         <v>0.0618</v>
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.00143</v>
+        <v>0.00155</v>
       </c>
       <c r="F54" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="G54" t="n">
-        <v>0.829</v>
+        <v>0.832</v>
       </c>
       <c r="H54" t="n">
         <v>0.18</v>
@@ -2598,7 +2598,7 @@
         <v>0.156</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0143</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="55">
@@ -2626,10 +2626,10 @@
         <v>0.00351</v>
       </c>
       <c r="F55" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="G55" t="n">
-        <v>0.829</v>
+        <v>0.832</v>
       </c>
       <c r="H55" t="n">
         <v>0.18</v>
@@ -2666,10 +2666,10 @@
         <v>0.0115</v>
       </c>
       <c r="F56" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="G56" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H56" t="n">
         <v>0.18</v>
@@ -2678,7 +2678,7 @@
         <v>0.152</v>
       </c>
       <c r="J56" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="57">
@@ -2706,10 +2706,10 @@
         <v>0.0146</v>
       </c>
       <c r="F57" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="G57" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H57" t="n">
         <v>0.18</v>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.00593</v>
+        <v>0.00591</v>
       </c>
       <c r="F58" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="G58" t="n">
-        <v>0.826</v>
+        <v>0.827</v>
       </c>
       <c r="H58" t="n">
         <v>0.18</v>
@@ -2758,7 +2758,7 @@
         <v>0.156</v>
       </c>
       <c r="J58" t="n">
-        <v>0.0297</v>
+        <v>0.0295</v>
       </c>
     </row>
     <row r="59">
@@ -2786,10 +2786,10 @@
         <v>0.00641</v>
       </c>
       <c r="F59" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="G59" t="n">
-        <v>0.826</v>
+        <v>0.827</v>
       </c>
       <c r="H59" t="n">
         <v>0.18</v>
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.0833</v>
+        <v>0.0776</v>
       </c>
       <c r="F60" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="G60" t="n">
         <v>0.709</v>
@@ -2838,7 +2838,7 @@
         <v>0.162</v>
       </c>
       <c r="J60" t="n">
-        <v>0.139</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="61">
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.14</v>
+        <v>0.125</v>
       </c>
       <c r="F61" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="G61" t="n">
         <v>0.709</v>
@@ -2878,7 +2878,7 @@
         <v>0.162</v>
       </c>
       <c r="J61" t="n">
-        <v>0.198</v>
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -3300,13 +3300,13 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9</v>
+        <v>0.913</v>
       </c>
       <c r="G11" t="n">
-        <v>0.833</v>
+        <v>0.847</v>
       </c>
       <c r="H11" t="n">
-        <v>0.126</v>
+        <v>0.109</v>
       </c>
       <c r="I11" t="n">
         <v>0.342</v>
@@ -3892,13 +3892,13 @@
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>0.912</v>
+        <v>0.914</v>
       </c>
       <c r="H27" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="I27" t="n">
         <v>0.823</v>
@@ -4484,16 +4484,16 @@
         <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>0.877</v>
+        <v>0.901</v>
       </c>
       <c r="G43" t="n">
-        <v>0.765</v>
+        <v>0.79</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1</v>
+        <v>0.0804</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
     </row>
     <row r="44">
@@ -5076,16 +5076,16 @@
         <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9</v>
+        <v>0.913</v>
       </c>
       <c r="G59" t="n">
-        <v>0.833</v>
+        <v>0.847</v>
       </c>
       <c r="H59" t="n">
-        <v>0.126</v>
+        <v>0.109</v>
       </c>
       <c r="I59" t="n">
-        <v>0.335</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="60">
@@ -5122,7 +5122,7 @@
         <v>0.106</v>
       </c>
       <c r="I60" t="n">
-        <v>0.335</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="61">
@@ -5668,13 +5668,13 @@
         <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="G75" t="n">
-        <v>0.9</v>
+        <v>0.903</v>
       </c>
       <c r="H75" t="n">
-        <v>0.552</v>
+        <v>0.553</v>
       </c>
       <c r="I75" t="n">
         <v>0.746</v>
@@ -6158,7 +6158,7 @@
         <v>0.0919</v>
       </c>
       <c r="I88" t="n">
-        <v>0.368</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="89">
@@ -6232,7 +6232,7 @@
         <v>0.136</v>
       </c>
       <c r="I90" t="n">
-        <v>0.386</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="91">
@@ -6260,16 +6260,16 @@
         <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>0.877</v>
+        <v>0.901</v>
       </c>
       <c r="G91" t="n">
-        <v>0.778</v>
+        <v>0.802</v>
       </c>
       <c r="H91" t="n">
-        <v>0.145</v>
+        <v>0.12</v>
       </c>
       <c r="I91" t="n">
-        <v>0.386</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="92">
@@ -6852,13 +6852,13 @@
         <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>0.9</v>
+        <v>0.913</v>
       </c>
       <c r="G107" t="n">
-        <v>0.867</v>
+        <v>0.887</v>
       </c>
       <c r="H107" t="n">
-        <v>0.472</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="I107" t="n">
         <v>0.888</v>
@@ -7444,13 +7444,13 @@
         <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="G123" t="n">
-        <v>0.955</v>
+        <v>0.957</v>
       </c>
       <c r="H123" t="n">
-        <v>0.723</v>
+        <v>0.722</v>
       </c>
       <c r="I123" t="n">
         <v>1</v>
@@ -8036,16 +8036,16 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>0.877</v>
+        <v>0.901</v>
       </c>
       <c r="G139" t="n">
-        <v>0.79</v>
+        <v>0.827</v>
       </c>
       <c r="H139" t="n">
-        <v>0.205</v>
+        <v>0.251</v>
       </c>
       <c r="I139" t="n">
-        <v>0.469</v>
+        <v>0.574</v>
       </c>
     </row>
     <row r="140">
@@ -8628,13 +8628,13 @@
         <v>10</v>
       </c>
       <c r="F155" t="n">
-        <v>0.9</v>
+        <v>0.913</v>
       </c>
       <c r="G155" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="H155" t="n">
-        <v>0.0663</v>
+        <v>0.078</v>
       </c>
       <c r="I155" t="n">
         <v>0.171</v>
@@ -9220,16 +9220,16 @@
         <v>10</v>
       </c>
       <c r="F171" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="G171" t="n">
-        <v>0.886</v>
+        <v>0.89</v>
       </c>
       <c r="H171" t="n">
-        <v>0.388</v>
+        <v>0.391</v>
       </c>
       <c r="I171" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.694</v>
       </c>
     </row>
     <row r="172">
@@ -9812,16 +9812,16 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>0.877</v>
+        <v>0.901</v>
       </c>
       <c r="G187" t="n">
-        <v>0.765</v>
+        <v>0.802</v>
       </c>
       <c r="H187" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="I187" t="n">
-        <v>0.267</v>
+        <v>0.321</v>
       </c>
     </row>
     <row r="188">
@@ -10404,16 +10404,16 @@
         <v>10</v>
       </c>
       <c r="F203" t="n">
-        <v>0.9</v>
+        <v>0.913</v>
       </c>
       <c r="G203" t="n">
-        <v>0.92</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H203" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.665</v>
       </c>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>0.967</v>
       </c>
     </row>
     <row r="204">
@@ -10996,10 +10996,10 @@
         <v>10</v>
       </c>
       <c r="F219" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="G219" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="H219" t="n">
         <v>1</v>
@@ -11588,16 +11588,16 @@
         <v>10</v>
       </c>
       <c r="F235" t="n">
-        <v>0.877</v>
+        <v>0.901</v>
       </c>
       <c r="G235" t="n">
-        <v>0.914</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="H235" t="n">
-        <v>0.609</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="I235" t="n">
-        <v>0.886</v>
+        <v>0.821</v>
       </c>
     </row>
     <row r="236">
@@ -12152,7 +12152,7 @@
         <v>0.0683</v>
       </c>
       <c r="I250" t="n">
-        <v>0.75</v>
+        <v>0.546</v>
       </c>
     </row>
     <row r="251">
@@ -12180,16 +12180,16 @@
         <v>10</v>
       </c>
       <c r="F251" t="n">
-        <v>0.827</v>
+        <v>0.833</v>
       </c>
       <c r="G251" t="n">
-        <v>0.893</v>
+        <v>0.927</v>
       </c>
       <c r="H251" t="n">
-        <v>0.134</v>
+        <v>0.0199</v>
       </c>
       <c r="I251" t="n">
-        <v>0.75</v>
+        <v>0.318</v>
       </c>
     </row>
     <row r="252">
@@ -12772,10 +12772,10 @@
         <v>10</v>
       </c>
       <c r="F267" t="n">
-        <v>0.982</v>
+        <v>0.983</v>
       </c>
       <c r="G267" t="n">
-        <v>0.985</v>
+        <v>0.986</v>
       </c>
       <c r="H267" t="n">
         <v>1</v>
@@ -13040,7 +13040,7 @@
         <v>0.0853</v>
       </c>
       <c r="I274" t="n">
-        <v>0.535</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="275">
@@ -13364,16 +13364,16 @@
         <v>10</v>
       </c>
       <c r="F283" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="G283" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.877</v>
       </c>
       <c r="H283" t="n">
-        <v>0.1</v>
+        <v>0.0114</v>
       </c>
       <c r="I283" t="n">
-        <v>0.535</v>
+        <v>0.09130000000000001</v>
       </c>
     </row>
     <row r="284">
@@ -13632,7 +13632,7 @@
         <v>0.188</v>
       </c>
       <c r="I290" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="291">
@@ -13817,7 +13817,7 @@
         <v>0.226</v>
       </c>
       <c r="I295" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="296">
@@ -13956,16 +13956,16 @@
         <v>10</v>
       </c>
       <c r="F299" t="n">
-        <v>0.827</v>
+        <v>0.833</v>
       </c>
       <c r="G299" t="n">
-        <v>0.88</v>
+        <v>0.907</v>
       </c>
       <c r="H299" t="n">
-        <v>0.253</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="I299" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="300">
@@ -14548,13 +14548,13 @@
         <v>10</v>
       </c>
       <c r="F315" t="n">
-        <v>0.982</v>
+        <v>0.983</v>
       </c>
       <c r="G315" t="n">
-        <v>0.957</v>
+        <v>0.959</v>
       </c>
       <c r="H315" t="n">
-        <v>0.626</v>
+        <v>0.629</v>
       </c>
       <c r="I315" t="n">
         <v>1</v>
@@ -14816,7 +14816,7 @@
         <v>0.0853</v>
       </c>
       <c r="I322" t="n">
-        <v>0.401</v>
+        <v>0.341</v>
       </c>
     </row>
     <row r="323">
@@ -15001,7 +15001,7 @@
         <v>0.0269</v>
       </c>
       <c r="I327" t="n">
-        <v>0.216</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="328">
@@ -15140,16 +15140,16 @@
         <v>10</v>
       </c>
       <c r="F331" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="G331" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.864</v>
       </c>
       <c r="H331" t="n">
-        <v>0.1</v>
+        <v>0.0211</v>
       </c>
       <c r="I331" t="n">
-        <v>0.401</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="332">
@@ -15408,7 +15408,7 @@
         <v>0.188</v>
       </c>
       <c r="I338" t="n">
-        <v>0.792</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="339">
@@ -15593,7 +15593,7 @@
         <v>0.124</v>
       </c>
       <c r="I343" t="n">
-        <v>0.792</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="344">
@@ -15732,16 +15732,16 @@
         <v>10</v>
       </c>
       <c r="F347" t="n">
-        <v>0.827</v>
+        <v>0.833</v>
       </c>
       <c r="G347" t="n">
-        <v>0.88</v>
+        <v>0.893</v>
       </c>
       <c r="H347" t="n">
-        <v>0.253</v>
+        <v>0.178</v>
       </c>
       <c r="I347" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="348">
@@ -15963,7 +15963,7 @@
         <v>0.198</v>
       </c>
       <c r="I353" t="n">
-        <v>0.792</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="354">
@@ -16324,13 +16324,13 @@
         <v>10</v>
       </c>
       <c r="F363" t="n">
-        <v>0.982</v>
+        <v>0.983</v>
       </c>
       <c r="G363" t="n">
-        <v>0.944</v>
+        <v>0.945</v>
       </c>
       <c r="H363" t="n">
-        <v>0.38</v>
+        <v>0.382</v>
       </c>
       <c r="I363" t="n">
         <v>1</v>
@@ -16916,16 +16916,16 @@
         <v>10</v>
       </c>
       <c r="F379" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="G379" t="n">
-        <v>0.827</v>
+        <v>0.852</v>
       </c>
       <c r="H379" t="n">
-        <v>0.0653</v>
+        <v>0.0367</v>
       </c>
       <c r="I379" t="n">
-        <v>0.421</v>
+        <v>0.294</v>
       </c>
     </row>
     <row r="380">
@@ -17508,16 +17508,16 @@
         <v>10</v>
       </c>
       <c r="F395" t="n">
-        <v>0.827</v>
+        <v>0.833</v>
       </c>
       <c r="G395" t="n">
-        <v>0.893</v>
+        <v>0.907</v>
       </c>
       <c r="H395" t="n">
-        <v>0.134</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="I395" t="n">
-        <v>0.534</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="396">
@@ -18100,10 +18100,10 @@
         <v>10</v>
       </c>
       <c r="F411" t="n">
-        <v>0.982</v>
+        <v>0.983</v>
       </c>
       <c r="G411" t="n">
-        <v>0.971</v>
+        <v>0.972</v>
       </c>
       <c r="H411" t="n">
         <v>1</v>
@@ -18692,16 +18692,16 @@
         <v>10</v>
       </c>
       <c r="F427" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="G427" t="n">
-        <v>0.827</v>
+        <v>0.852</v>
       </c>
       <c r="H427" t="n">
-        <v>0.0653</v>
+        <v>0.0367</v>
       </c>
       <c r="I427" t="n">
-        <v>0.5</v>
+        <v>0.294</v>
       </c>
     </row>
     <row r="428">
@@ -18960,7 +18960,7 @@
         <v>0.312</v>
       </c>
       <c r="I434" t="n">
-        <v>0.885</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="435">
@@ -19145,7 +19145,7 @@
         <v>0.226</v>
       </c>
       <c r="I439" t="n">
-        <v>0.885</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="440">
@@ -19284,16 +19284,16 @@
         <v>10</v>
       </c>
       <c r="F443" t="n">
-        <v>0.827</v>
+        <v>0.833</v>
       </c>
       <c r="G443" t="n">
         <v>0.873</v>
       </c>
       <c r="H443" t="n">
-        <v>0.332</v>
+        <v>0.415</v>
       </c>
       <c r="I443" t="n">
-        <v>0.885</v>
+        <v>1</v>
       </c>
     </row>
     <row r="444">
@@ -19876,7 +19876,7 @@
         <v>10</v>
       </c>
       <c r="F459" t="n">
-        <v>0.982</v>
+        <v>0.983</v>
       </c>
       <c r="G459" t="n">
         <v>0.97</v>
@@ -20144,7 +20144,7 @@
         <v>0.241</v>
       </c>
       <c r="I466" t="n">
-        <v>0.642</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="467">
@@ -20181,7 +20181,7 @@
         <v>0.236</v>
       </c>
       <c r="I467" t="n">
-        <v>0.642</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="468">
@@ -20468,16 +20468,16 @@
         <v>10</v>
       </c>
       <c r="F475" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="G475" t="n">
         <v>0.79</v>
       </c>
       <c r="H475" t="n">
-        <v>0.209</v>
+        <v>0.278</v>
       </c>
       <c r="I475" t="n">
-        <v>0.642</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="476">

--- a/eval/learning-curve/results/statistical_tests_full150.xlsx
+++ b/eval/learning-curve/results/statistical_tests_full150.xlsx
@@ -503,22 +503,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0629</v>
+        <v>0.111</v>
       </c>
       <c r="F2" t="n">
-        <v>0.845</v>
+        <v>0.832</v>
       </c>
       <c r="G2" t="n">
-        <v>0.875</v>
+        <v>0.86</v>
       </c>
       <c r="H2" t="n">
-        <v>0.11</v>
+        <v>0.123</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0838</v>
+        <v>0.103</v>
       </c>
       <c r="J2" t="n">
-        <v>0.157</v>
+        <v>0.185</v>
       </c>
     </row>
     <row r="3">
@@ -543,22 +543,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.0785</v>
+        <v>0.161</v>
       </c>
       <c r="F3" t="n">
-        <v>0.845</v>
+        <v>0.832</v>
       </c>
       <c r="G3" t="n">
-        <v>0.875</v>
+        <v>0.86</v>
       </c>
       <c r="H3" t="n">
-        <v>0.11</v>
+        <v>0.123</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0838</v>
+        <v>0.103</v>
       </c>
       <c r="J3" t="n">
-        <v>0.196</v>
+        <v>0.268</v>
       </c>
     </row>
     <row r="4">
@@ -583,22 +583,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.276</v>
+        <v>0.271</v>
       </c>
       <c r="F4" t="n">
-        <v>0.845</v>
+        <v>0.832</v>
       </c>
       <c r="G4" t="n">
-        <v>0.863</v>
+        <v>0.851</v>
       </c>
       <c r="H4" t="n">
-        <v>0.11</v>
+        <v>0.123</v>
       </c>
       <c r="I4" t="n">
-        <v>0.076</v>
+        <v>0.0907</v>
       </c>
       <c r="J4" t="n">
-        <v>0.345</v>
+        <v>0.329</v>
       </c>
     </row>
     <row r="5">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.28</v>
+        <v>0.268</v>
       </c>
       <c r="F5" t="n">
-        <v>0.845</v>
+        <v>0.832</v>
       </c>
       <c r="G5" t="n">
-        <v>0.863</v>
+        <v>0.851</v>
       </c>
       <c r="H5" t="n">
-        <v>0.11</v>
+        <v>0.123</v>
       </c>
       <c r="I5" t="n">
-        <v>0.076</v>
+        <v>0.0907</v>
       </c>
       <c r="J5" t="n">
-        <v>0.35</v>
+        <v>0.335</v>
       </c>
     </row>
     <row r="6">
@@ -663,22 +663,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.392</v>
+        <v>0.456</v>
       </c>
       <c r="F6" t="n">
-        <v>0.845</v>
+        <v>0.832</v>
       </c>
       <c r="G6" t="n">
-        <v>0.858</v>
+        <v>0.842</v>
       </c>
       <c r="H6" t="n">
-        <v>0.11</v>
+        <v>0.123</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0892</v>
+        <v>0.108</v>
       </c>
       <c r="J6" t="n">
-        <v>0.392</v>
+        <v>0.456</v>
       </c>
     </row>
     <row r="7">
@@ -703,22 +703,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.477</v>
+        <v>0.569</v>
       </c>
       <c r="F7" t="n">
-        <v>0.845</v>
+        <v>0.832</v>
       </c>
       <c r="G7" t="n">
-        <v>0.858</v>
+        <v>0.842</v>
       </c>
       <c r="H7" t="n">
-        <v>0.11</v>
+        <v>0.123</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0892</v>
+        <v>0.108</v>
       </c>
       <c r="J7" t="n">
-        <v>0.477</v>
+        <v>0.569</v>
       </c>
     </row>
     <row r="8">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.0881</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.845</v>
+        <v>0.832</v>
       </c>
       <c r="G8" t="n">
-        <v>0.875</v>
+        <v>0.861</v>
       </c>
       <c r="H8" t="n">
-        <v>0.11</v>
+        <v>0.123</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0873</v>
       </c>
       <c r="J8" t="n">
-        <v>0.176</v>
+        <v>0.185</v>
       </c>
     </row>
     <row r="9">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.139</v>
+        <v>0.125</v>
       </c>
       <c r="F9" t="n">
-        <v>0.845</v>
+        <v>0.832</v>
       </c>
       <c r="G9" t="n">
-        <v>0.875</v>
+        <v>0.861</v>
       </c>
       <c r="H9" t="n">
-        <v>0.11</v>
+        <v>0.123</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0873</v>
       </c>
       <c r="J9" t="n">
-        <v>0.232</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="10">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.00116</v>
+        <v>0.00173</v>
       </c>
       <c r="F10" t="n">
-        <v>0.845</v>
+        <v>0.832</v>
       </c>
       <c r="G10" t="n">
-        <v>0.911</v>
+        <v>0.9</v>
       </c>
       <c r="H10" t="n">
-        <v>0.11</v>
+        <v>0.123</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0636</v>
+        <v>0.0725</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0116</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="11">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0015</v>
+        <v>0.00144</v>
       </c>
       <c r="F11" t="n">
-        <v>0.845</v>
+        <v>0.832</v>
       </c>
       <c r="G11" t="n">
-        <v>0.911</v>
+        <v>0.9</v>
       </c>
       <c r="H11" t="n">
-        <v>0.11</v>
+        <v>0.123</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0636</v>
+        <v>0.0725</v>
       </c>
       <c r="J11" t="n">
         <v>0.0094</v>
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.0294</v>
+        <v>0.0239</v>
       </c>
       <c r="F12" t="n">
-        <v>0.803</v>
+        <v>0.793</v>
       </c>
       <c r="G12" t="n">
-        <v>0.828</v>
+        <v>0.82</v>
       </c>
       <c r="H12" t="n">
-        <v>0.149</v>
+        <v>0.162</v>
       </c>
       <c r="I12" t="n">
-        <v>0.161</v>
+        <v>0.173</v>
       </c>
       <c r="J12" t="n">
-        <v>0.098</v>
+        <v>0.07969999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.0353</v>
+        <v>0.0197</v>
       </c>
       <c r="F13" t="n">
-        <v>0.803</v>
+        <v>0.793</v>
       </c>
       <c r="G13" t="n">
-        <v>0.828</v>
+        <v>0.82</v>
       </c>
       <c r="H13" t="n">
-        <v>0.149</v>
+        <v>0.162</v>
       </c>
       <c r="I13" t="n">
-        <v>0.161</v>
+        <v>0.173</v>
       </c>
       <c r="J13" t="n">
-        <v>0.118</v>
+        <v>0.06569999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -983,22 +983,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.133</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.803</v>
+        <v>0.793</v>
       </c>
       <c r="G14" t="n">
-        <v>0.823</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>0.149</v>
+        <v>0.162</v>
       </c>
       <c r="I14" t="n">
-        <v>0.167</v>
+        <v>0.177</v>
       </c>
       <c r="J14" t="n">
-        <v>0.222</v>
+        <v>0.185</v>
       </c>
     </row>
     <row r="15">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.12</v>
+        <v>0.114</v>
       </c>
       <c r="F15" t="n">
-        <v>0.803</v>
+        <v>0.793</v>
       </c>
       <c r="G15" t="n">
-        <v>0.823</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>0.149</v>
+        <v>0.162</v>
       </c>
       <c r="I15" t="n">
-        <v>0.167</v>
+        <v>0.177</v>
       </c>
       <c r="J15" t="n">
-        <v>0.232</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="16">
@@ -1063,22 +1063,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.23</v>
+        <v>0.157</v>
       </c>
       <c r="F16" t="n">
-        <v>0.803</v>
+        <v>0.793</v>
       </c>
       <c r="G16" t="n">
-        <v>0.82</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.149</v>
+        <v>0.162</v>
       </c>
       <c r="I16" t="n">
-        <v>0.169</v>
+        <v>0.178</v>
       </c>
       <c r="J16" t="n">
-        <v>0.329</v>
+        <v>0.224</v>
       </c>
     </row>
     <row r="17">
@@ -1103,22 +1103,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.258</v>
+        <v>0.221</v>
       </c>
       <c r="F17" t="n">
-        <v>0.803</v>
+        <v>0.793</v>
       </c>
       <c r="G17" t="n">
-        <v>0.82</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.149</v>
+        <v>0.162</v>
       </c>
       <c r="I17" t="n">
-        <v>0.169</v>
+        <v>0.178</v>
       </c>
       <c r="J17" t="n">
-        <v>0.35</v>
+        <v>0.316</v>
       </c>
     </row>
     <row r="18">
@@ -1143,22 +1143,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.349</v>
+        <v>0.296</v>
       </c>
       <c r="F18" t="n">
-        <v>0.803</v>
+        <v>0.793</v>
       </c>
       <c r="G18" t="n">
-        <v>0.82</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>0.149</v>
+        <v>0.162</v>
       </c>
       <c r="I18" t="n">
-        <v>0.183</v>
+        <v>0.195</v>
       </c>
       <c r="J18" t="n">
-        <v>0.388</v>
+        <v>0.329</v>
       </c>
     </row>
     <row r="19">
@@ -1186,16 +1186,16 @@
         <v>0.326</v>
       </c>
       <c r="F19" t="n">
-        <v>0.803</v>
+        <v>0.793</v>
       </c>
       <c r="G19" t="n">
-        <v>0.82</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.149</v>
+        <v>0.162</v>
       </c>
       <c r="I19" t="n">
-        <v>0.183</v>
+        <v>0.195</v>
       </c>
       <c r="J19" t="n">
         <v>0.362</v>
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0152</v>
+        <v>0.0181</v>
       </c>
       <c r="F20" t="n">
-        <v>0.803</v>
+        <v>0.793</v>
       </c>
       <c r="G20" t="n">
-        <v>0.854</v>
+        <v>0.85</v>
       </c>
       <c r="H20" t="n">
-        <v>0.149</v>
+        <v>0.162</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0912</v>
+        <v>0.0941</v>
       </c>
       <c r="J20" t="n">
-        <v>0.076</v>
+        <v>0.07969999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1266,16 +1266,16 @@
         <v>0.00188</v>
       </c>
       <c r="F21" t="n">
-        <v>0.803</v>
+        <v>0.793</v>
       </c>
       <c r="G21" t="n">
-        <v>0.854</v>
+        <v>0.85</v>
       </c>
       <c r="H21" t="n">
-        <v>0.149</v>
+        <v>0.162</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0912</v>
+        <v>0.0941</v>
       </c>
       <c r="J21" t="n">
         <v>0.0094</v>
@@ -1303,22 +1303,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.843</v>
+        <v>0.963</v>
       </c>
       <c r="F22" t="n">
-        <v>0.868</v>
+        <v>0.857</v>
       </c>
       <c r="G22" t="n">
-        <v>0.861</v>
+        <v>0.856</v>
       </c>
       <c r="H22" t="n">
-        <v>0.156</v>
+        <v>0.179</v>
       </c>
       <c r="I22" t="n">
-        <v>0.117</v>
+        <v>0.122</v>
       </c>
       <c r="J22" t="n">
-        <v>0.849</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="23">
@@ -1343,22 +1343,22 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.495</v>
+        <v>0.464</v>
       </c>
       <c r="F23" t="n">
-        <v>0.868</v>
+        <v>0.857</v>
       </c>
       <c r="G23" t="n">
-        <v>0.861</v>
+        <v>0.856</v>
       </c>
       <c r="H23" t="n">
-        <v>0.156</v>
+        <v>0.179</v>
       </c>
       <c r="I23" t="n">
-        <v>0.117</v>
+        <v>0.122</v>
       </c>
       <c r="J23" t="n">
-        <v>0.722</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="24">
@@ -1383,22 +1383,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.63</v>
+        <v>0.736</v>
       </c>
       <c r="F24" t="n">
-        <v>0.868</v>
+        <v>0.857</v>
       </c>
       <c r="G24" t="n">
-        <v>0.848</v>
+        <v>0.843</v>
       </c>
       <c r="H24" t="n">
-        <v>0.156</v>
+        <v>0.179</v>
       </c>
       <c r="I24" t="n">
-        <v>0.132</v>
+        <v>0.137</v>
       </c>
       <c r="J24" t="n">
-        <v>0.849</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.348</v>
+        <v>0.404</v>
       </c>
       <c r="F25" t="n">
-        <v>0.868</v>
+        <v>0.857</v>
       </c>
       <c r="G25" t="n">
-        <v>0.848</v>
+        <v>0.843</v>
       </c>
       <c r="H25" t="n">
-        <v>0.156</v>
+        <v>0.179</v>
       </c>
       <c r="I25" t="n">
-        <v>0.132</v>
+        <v>0.137</v>
       </c>
       <c r="J25" t="n">
-        <v>0.722</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="26">
@@ -1463,22 +1463,22 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.798</v>
+        <v>0.75</v>
       </c>
       <c r="F26" t="n">
-        <v>0.868</v>
+        <v>0.857</v>
       </c>
       <c r="G26" t="n">
-        <v>0.876</v>
+        <v>0.867</v>
       </c>
       <c r="H26" t="n">
-        <v>0.156</v>
+        <v>0.179</v>
       </c>
       <c r="I26" t="n">
-        <v>0.104</v>
+        <v>0.125</v>
       </c>
       <c r="J26" t="n">
-        <v>0.849</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1503,22 +1503,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.609</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.868</v>
+        <v>0.857</v>
       </c>
       <c r="G27" t="n">
-        <v>0.876</v>
+        <v>0.867</v>
       </c>
       <c r="H27" t="n">
-        <v>0.156</v>
+        <v>0.179</v>
       </c>
       <c r="I27" t="n">
-        <v>0.104</v>
+        <v>0.125</v>
       </c>
       <c r="J27" t="n">
-        <v>0.722</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="28">
@@ -1543,22 +1543,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.745</v>
+        <v>0.846</v>
       </c>
       <c r="F28" t="n">
-        <v>0.868</v>
+        <v>0.857</v>
       </c>
       <c r="G28" t="n">
-        <v>0.858</v>
+        <v>0.851</v>
       </c>
       <c r="H28" t="n">
-        <v>0.156</v>
+        <v>0.179</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1</v>
+        <v>0.112</v>
       </c>
       <c r="J28" t="n">
-        <v>0.849</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1583,22 +1583,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.427</v>
+        <v>0.532</v>
       </c>
       <c r="F29" t="n">
-        <v>0.868</v>
+        <v>0.857</v>
       </c>
       <c r="G29" t="n">
-        <v>0.858</v>
+        <v>0.851</v>
       </c>
       <c r="H29" t="n">
-        <v>0.156</v>
+        <v>0.179</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1</v>
+        <v>0.112</v>
       </c>
       <c r="J29" t="n">
-        <v>0.722</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="30">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.093</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>0.868</v>
+        <v>0.857</v>
       </c>
       <c r="G30" t="n">
-        <v>0.926</v>
+        <v>0.923</v>
       </c>
       <c r="H30" t="n">
-        <v>0.156</v>
+        <v>0.179</v>
       </c>
       <c r="I30" t="n">
-        <v>0.054</v>
+        <v>0.0587</v>
       </c>
       <c r="J30" t="n">
-        <v>0.465</v>
+        <v>0.435</v>
       </c>
     </row>
     <row r="31">
@@ -1663,22 +1663,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.221</v>
+        <v>0.245</v>
       </c>
       <c r="F31" t="n">
-        <v>0.868</v>
+        <v>0.857</v>
       </c>
       <c r="G31" t="n">
-        <v>0.926</v>
+        <v>0.923</v>
       </c>
       <c r="H31" t="n">
-        <v>0.156</v>
+        <v>0.179</v>
       </c>
       <c r="I31" t="n">
-        <v>0.054</v>
+        <v>0.0587</v>
       </c>
       <c r="J31" t="n">
-        <v>0.722</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="32">
@@ -1703,22 +1703,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.428</v>
+        <v>0.393</v>
       </c>
       <c r="F32" t="n">
-        <v>0.795</v>
+        <v>0.79</v>
       </c>
       <c r="G32" t="n">
-        <v>0.802</v>
+        <v>0.798</v>
       </c>
       <c r="H32" t="n">
-        <v>0.201</v>
+        <v>0.211</v>
       </c>
       <c r="I32" t="n">
-        <v>0.192</v>
+        <v>0.202</v>
       </c>
       <c r="J32" t="n">
-        <v>0.849</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1743,22 +1743,22 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.427</v>
+        <v>0.394</v>
       </c>
       <c r="F33" t="n">
-        <v>0.795</v>
+        <v>0.79</v>
       </c>
       <c r="G33" t="n">
-        <v>0.802</v>
+        <v>0.798</v>
       </c>
       <c r="H33" t="n">
-        <v>0.201</v>
+        <v>0.211</v>
       </c>
       <c r="I33" t="n">
-        <v>0.192</v>
+        <v>0.202</v>
       </c>
       <c r="J33" t="n">
-        <v>0.722</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="34">
@@ -1783,22 +1783,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.849</v>
+        <v>0.786</v>
       </c>
       <c r="F34" t="n">
-        <v>0.795</v>
+        <v>0.79</v>
       </c>
       <c r="G34" t="n">
-        <v>0.798</v>
+        <v>0.794</v>
       </c>
       <c r="H34" t="n">
-        <v>0.201</v>
+        <v>0.211</v>
       </c>
       <c r="I34" t="n">
-        <v>0.177</v>
+        <v>0.184</v>
       </c>
       <c r="J34" t="n">
-        <v>0.849</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1826,16 +1826,16 @@
         <v>0.782</v>
       </c>
       <c r="F35" t="n">
-        <v>0.795</v>
+        <v>0.79</v>
       </c>
       <c r="G35" t="n">
-        <v>0.798</v>
+        <v>0.794</v>
       </c>
       <c r="H35" t="n">
-        <v>0.201</v>
+        <v>0.211</v>
       </c>
       <c r="I35" t="n">
-        <v>0.177</v>
+        <v>0.184</v>
       </c>
       <c r="J35" t="n">
         <v>0.782</v>
@@ -1863,22 +1863,22 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.727</v>
+        <v>0.652</v>
       </c>
       <c r="F36" t="n">
-        <v>0.795</v>
+        <v>0.79</v>
       </c>
       <c r="G36" t="n">
-        <v>0.8</v>
+        <v>0.797</v>
       </c>
       <c r="H36" t="n">
-        <v>0.201</v>
+        <v>0.211</v>
       </c>
       <c r="I36" t="n">
-        <v>0.185</v>
+        <v>0.192</v>
       </c>
       <c r="J36" t="n">
-        <v>0.849</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1903,22 +1903,22 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.65</v>
+        <v>0.776</v>
       </c>
       <c r="F37" t="n">
-        <v>0.795</v>
+        <v>0.79</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8</v>
+        <v>0.797</v>
       </c>
       <c r="H37" t="n">
-        <v>0.201</v>
+        <v>0.211</v>
       </c>
       <c r="I37" t="n">
-        <v>0.185</v>
+        <v>0.192</v>
       </c>
       <c r="J37" t="n">
-        <v>0.722</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="38">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.708</v>
+        <v>0.675</v>
       </c>
       <c r="F38" t="n">
-        <v>0.795</v>
+        <v>0.79</v>
       </c>
       <c r="G38" t="n">
-        <v>0.801</v>
+        <v>0.797</v>
       </c>
       <c r="H38" t="n">
-        <v>0.201</v>
+        <v>0.211</v>
       </c>
       <c r="I38" t="n">
-        <v>0.189</v>
+        <v>0.199</v>
       </c>
       <c r="J38" t="n">
-        <v>0.849</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -1986,19 +1986,19 @@
         <v>0.597</v>
       </c>
       <c r="F39" t="n">
-        <v>0.795</v>
+        <v>0.79</v>
       </c>
       <c r="G39" t="n">
-        <v>0.801</v>
+        <v>0.797</v>
       </c>
       <c r="H39" t="n">
-        <v>0.201</v>
+        <v>0.211</v>
       </c>
       <c r="I39" t="n">
-        <v>0.189</v>
+        <v>0.199</v>
       </c>
       <c r="J39" t="n">
-        <v>0.722</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="40">
@@ -2023,22 +2023,22 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.000855</v>
+        <v>0.00102</v>
       </c>
       <c r="F40" t="n">
-        <v>0.795</v>
+        <v>0.79</v>
       </c>
       <c r="G40" t="n">
-        <v>0.916</v>
+        <v>0.915</v>
       </c>
       <c r="H40" t="n">
-        <v>0.201</v>
+        <v>0.211</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0941</v>
+        <v>0.0968</v>
       </c>
       <c r="J40" t="n">
-        <v>0.00855</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="41">
@@ -2066,16 +2066,16 @@
         <v>0.000987</v>
       </c>
       <c r="F41" t="n">
-        <v>0.795</v>
+        <v>0.79</v>
       </c>
       <c r="G41" t="n">
-        <v>0.916</v>
+        <v>0.915</v>
       </c>
       <c r="H41" t="n">
-        <v>0.201</v>
+        <v>0.211</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0941</v>
+        <v>0.0968</v>
       </c>
       <c r="J41" t="n">
         <v>0.00987</v>
@@ -2103,22 +2103,22 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.215</v>
+        <v>0.245</v>
       </c>
       <c r="F42" t="n">
-        <v>0.784</v>
+        <v>0.753</v>
       </c>
       <c r="G42" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.788</v>
       </c>
       <c r="H42" t="n">
-        <v>0.158</v>
+        <v>0.186</v>
       </c>
       <c r="I42" t="n">
-        <v>0.17</v>
+        <v>0.189</v>
       </c>
       <c r="J42" t="n">
-        <v>0.269</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="43">
@@ -2143,22 +2143,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.133</v>
+        <v>0.112</v>
       </c>
       <c r="F43" t="n">
-        <v>0.784</v>
+        <v>0.753</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.788</v>
       </c>
       <c r="H43" t="n">
-        <v>0.158</v>
+        <v>0.186</v>
       </c>
       <c r="I43" t="n">
-        <v>0.17</v>
+        <v>0.189</v>
       </c>
       <c r="J43" t="n">
-        <v>0.19</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="44">
@@ -2183,22 +2183,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.661</v>
+        <v>0.522</v>
       </c>
       <c r="F44" t="n">
-        <v>0.784</v>
+        <v>0.753</v>
       </c>
       <c r="G44" t="n">
-        <v>0.796</v>
+        <v>0.773</v>
       </c>
       <c r="H44" t="n">
-        <v>0.158</v>
+        <v>0.186</v>
       </c>
       <c r="I44" t="n">
-        <v>0.137</v>
+        <v>0.155</v>
       </c>
       <c r="J44" t="n">
-        <v>0.734</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="45">
@@ -2223,22 +2223,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>0.784</v>
+        <v>0.753</v>
       </c>
       <c r="G45" t="n">
-        <v>0.796</v>
+        <v>0.773</v>
       </c>
       <c r="H45" t="n">
-        <v>0.158</v>
+        <v>0.186</v>
       </c>
       <c r="I45" t="n">
-        <v>0.137</v>
+        <v>0.155</v>
       </c>
       <c r="J45" t="n">
-        <v>0.754</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="46">
@@ -2263,22 +2263,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.824</v>
+        <v>0.877</v>
       </c>
       <c r="F46" t="n">
-        <v>0.784</v>
+        <v>0.753</v>
       </c>
       <c r="G46" t="n">
-        <v>0.791</v>
+        <v>0.758</v>
       </c>
       <c r="H46" t="n">
-        <v>0.158</v>
+        <v>0.186</v>
       </c>
       <c r="I46" t="n">
-        <v>0.135</v>
+        <v>0.154</v>
       </c>
       <c r="J46" t="n">
-        <v>0.824</v>
+        <v>0.877</v>
       </c>
     </row>
     <row r="47">
@@ -2303,22 +2303,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.754</v>
+        <v>0.887</v>
       </c>
       <c r="F47" t="n">
-        <v>0.784</v>
+        <v>0.753</v>
       </c>
       <c r="G47" t="n">
-        <v>0.791</v>
+        <v>0.758</v>
       </c>
       <c r="H47" t="n">
-        <v>0.158</v>
+        <v>0.186</v>
       </c>
       <c r="I47" t="n">
-        <v>0.135</v>
+        <v>0.154</v>
       </c>
       <c r="J47" t="n">
-        <v>0.754</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="48">
@@ -2343,22 +2343,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.176</v>
+        <v>0.142</v>
       </c>
       <c r="F48" t="n">
-        <v>0.784</v>
+        <v>0.753</v>
       </c>
       <c r="G48" t="n">
-        <v>0.822</v>
+        <v>0.794</v>
       </c>
       <c r="H48" t="n">
-        <v>0.158</v>
+        <v>0.186</v>
       </c>
       <c r="I48" t="n">
-        <v>0.131</v>
+        <v>0.151</v>
       </c>
       <c r="J48" t="n">
-        <v>0.251</v>
+        <v>0.203</v>
       </c>
     </row>
     <row r="49">
@@ -2383,22 +2383,22 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.158</v>
+        <v>0.156</v>
       </c>
       <c r="F49" t="n">
-        <v>0.784</v>
+        <v>0.753</v>
       </c>
       <c r="G49" t="n">
-        <v>0.822</v>
+        <v>0.794</v>
       </c>
       <c r="H49" t="n">
-        <v>0.158</v>
+        <v>0.186</v>
       </c>
       <c r="I49" t="n">
-        <v>0.131</v>
+        <v>0.151</v>
       </c>
       <c r="J49" t="n">
-        <v>0.198</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="50">
@@ -2423,22 +2423,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.0155</v>
+        <v>0.0146</v>
       </c>
       <c r="F50" t="n">
-        <v>0.784</v>
+        <v>0.753</v>
       </c>
       <c r="G50" t="n">
-        <v>0.862</v>
+        <v>0.841</v>
       </c>
       <c r="H50" t="n">
-        <v>0.158</v>
+        <v>0.186</v>
       </c>
       <c r="I50" t="n">
-        <v>0.131</v>
+        <v>0.138</v>
       </c>
       <c r="J50" t="n">
-        <v>0.035</v>
+        <v>0.0342</v>
       </c>
     </row>
     <row r="51">
@@ -2463,22 +2463,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.0199</v>
+        <v>0.0131</v>
       </c>
       <c r="F51" t="n">
-        <v>0.784</v>
+        <v>0.753</v>
       </c>
       <c r="G51" t="n">
-        <v>0.862</v>
+        <v>0.841</v>
       </c>
       <c r="H51" t="n">
-        <v>0.158</v>
+        <v>0.186</v>
       </c>
       <c r="I51" t="n">
-        <v>0.131</v>
+        <v>0.138</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0498</v>
+        <v>0.0328</v>
       </c>
     </row>
     <row r="52">
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.0175</v>
+        <v>0.0171</v>
       </c>
       <c r="F52" t="n">
-        <v>0.768</v>
+        <v>0.747</v>
       </c>
       <c r="G52" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.799</v>
       </c>
       <c r="H52" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="I52" t="n">
-        <v>0.177</v>
+        <v>0.189</v>
       </c>
       <c r="J52" t="n">
-        <v>0.035</v>
+        <v>0.0342</v>
       </c>
     </row>
     <row r="53">
@@ -2546,16 +2546,16 @@
         <v>0.0309</v>
       </c>
       <c r="F53" t="n">
-        <v>0.768</v>
+        <v>0.747</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.799</v>
       </c>
       <c r="H53" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="I53" t="n">
-        <v>0.177</v>
+        <v>0.189</v>
       </c>
       <c r="J53" t="n">
         <v>0.0618</v>
@@ -2583,22 +2583,22 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.00155</v>
+        <v>0.00171</v>
       </c>
       <c r="F54" t="n">
-        <v>0.768</v>
+        <v>0.747</v>
       </c>
       <c r="G54" t="n">
-        <v>0.832</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="I54" t="n">
-        <v>0.156</v>
+        <v>0.16</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0155</v>
+        <v>0.0171</v>
       </c>
     </row>
     <row r="55">
@@ -2626,19 +2626,19 @@
         <v>0.00351</v>
       </c>
       <c r="F55" t="n">
-        <v>0.768</v>
+        <v>0.747</v>
       </c>
       <c r="G55" t="n">
-        <v>0.832</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="I55" t="n">
-        <v>0.156</v>
+        <v>0.16</v>
       </c>
       <c r="J55" t="n">
-        <v>0.0321</v>
+        <v>0.0254</v>
       </c>
     </row>
     <row r="56">
@@ -2663,22 +2663,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.0115</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>0.768</v>
+        <v>0.747</v>
       </c>
       <c r="G56" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.803</v>
       </c>
       <c r="H56" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="I56" t="n">
-        <v>0.152</v>
+        <v>0.159</v>
       </c>
       <c r="J56" t="n">
-        <v>0.035</v>
+        <v>0.0263</v>
       </c>
     </row>
     <row r="57">
@@ -2703,22 +2703,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.0146</v>
+        <v>0.00763</v>
       </c>
       <c r="F57" t="n">
-        <v>0.768</v>
+        <v>0.747</v>
       </c>
       <c r="G57" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.803</v>
       </c>
       <c r="H57" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="I57" t="n">
-        <v>0.152</v>
+        <v>0.159</v>
       </c>
       <c r="J57" t="n">
-        <v>0.0487</v>
+        <v>0.0254</v>
       </c>
     </row>
     <row r="58">
@@ -2743,22 +2743,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.00591</v>
+        <v>0.00645</v>
       </c>
       <c r="F58" t="n">
-        <v>0.768</v>
+        <v>0.747</v>
       </c>
       <c r="G58" t="n">
-        <v>0.827</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="I58" t="n">
-        <v>0.156</v>
+        <v>0.168</v>
       </c>
       <c r="J58" t="n">
-        <v>0.0295</v>
+        <v>0.0263</v>
       </c>
     </row>
     <row r="59">
@@ -2783,22 +2783,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.00641</v>
+        <v>0.0076</v>
       </c>
       <c r="F59" t="n">
-        <v>0.768</v>
+        <v>0.747</v>
       </c>
       <c r="G59" t="n">
-        <v>0.827</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="I59" t="n">
-        <v>0.156</v>
+        <v>0.168</v>
       </c>
       <c r="J59" t="n">
-        <v>0.0321</v>
+        <v>0.0254</v>
       </c>
     </row>
     <row r="60">
@@ -2823,22 +2823,22 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.0776</v>
+        <v>0.124</v>
       </c>
       <c r="F60" t="n">
-        <v>0.768</v>
+        <v>0.747</v>
       </c>
       <c r="G60" t="n">
-        <v>0.709</v>
+        <v>0.702</v>
       </c>
       <c r="H60" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="I60" t="n">
-        <v>0.162</v>
+        <v>0.165</v>
       </c>
       <c r="J60" t="n">
-        <v>0.129</v>
+        <v>0.203</v>
       </c>
     </row>
     <row r="61">
@@ -2863,22 +2863,22 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.125</v>
+        <v>0.156</v>
       </c>
       <c r="F61" t="n">
-        <v>0.768</v>
+        <v>0.747</v>
       </c>
       <c r="G61" t="n">
-        <v>0.709</v>
+        <v>0.702</v>
       </c>
       <c r="H61" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="I61" t="n">
-        <v>0.162</v>
+        <v>0.165</v>
       </c>
       <c r="J61" t="n">
-        <v>0.19</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="62">
@@ -2903,22 +2903,22 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.492</v>
+        <v>0.482</v>
       </c>
       <c r="F62" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="G62" t="n">
         <v>0.8110000000000001</v>
       </c>
-      <c r="G62" t="n">
-        <v>0.831</v>
-      </c>
       <c r="H62" t="n">
-        <v>0.124</v>
+        <v>0.155</v>
       </c>
       <c r="I62" t="n">
-        <v>0.131</v>
+        <v>0.142</v>
       </c>
       <c r="J62" t="n">
-        <v>0.615</v>
+        <v>0.603</v>
       </c>
     </row>
     <row r="63">
@@ -2943,22 +2943,22 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.323</v>
+        <v>0.404</v>
       </c>
       <c r="F63" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="G63" t="n">
         <v>0.8110000000000001</v>
       </c>
-      <c r="G63" t="n">
-        <v>0.831</v>
-      </c>
       <c r="H63" t="n">
-        <v>0.124</v>
+        <v>0.155</v>
       </c>
       <c r="I63" t="n">
-        <v>0.131</v>
+        <v>0.142</v>
       </c>
       <c r="J63" t="n">
-        <v>0.461</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="64">
@@ -2983,22 +2983,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.896</v>
+        <v>0.747</v>
       </c>
       <c r="F64" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.789</v>
       </c>
       <c r="G64" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.798</v>
       </c>
       <c r="H64" t="n">
-        <v>0.124</v>
+        <v>0.155</v>
       </c>
       <c r="I64" t="n">
-        <v>0.109</v>
+        <v>0.121</v>
       </c>
       <c r="J64" t="n">
-        <v>0.896</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="65">
@@ -3023,22 +3023,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.9</v>
+        <v>0.782</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.789</v>
       </c>
       <c r="G65" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.798</v>
       </c>
       <c r="H65" t="n">
-        <v>0.124</v>
+        <v>0.155</v>
       </c>
       <c r="I65" t="n">
-        <v>0.109</v>
+        <v>0.121</v>
       </c>
       <c r="J65" t="n">
-        <v>0.9</v>
+        <v>0.869</v>
       </c>
     </row>
     <row r="66">
@@ -3063,22 +3063,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.63</v>
+        <v>0.608</v>
       </c>
       <c r="F66" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.789</v>
       </c>
       <c r="G66" t="n">
-        <v>0.822</v>
+        <v>0.801</v>
       </c>
       <c r="H66" t="n">
-        <v>0.124</v>
+        <v>0.155</v>
       </c>
       <c r="I66" t="n">
-        <v>0.0958</v>
+        <v>0.121</v>
       </c>
       <c r="J66" t="n">
-        <v>0.7</v>
+        <v>0.676</v>
       </c>
     </row>
     <row r="67">
@@ -3103,22 +3103,22 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.865</v>
+        <v>0.91</v>
       </c>
       <c r="F67" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.789</v>
       </c>
       <c r="G67" t="n">
-        <v>0.822</v>
+        <v>0.801</v>
       </c>
       <c r="H67" t="n">
-        <v>0.124</v>
+        <v>0.155</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0958</v>
+        <v>0.121</v>
       </c>
       <c r="J67" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="68">
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.388</v>
+        <v>0.326</v>
       </c>
       <c r="F68" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.789</v>
       </c>
       <c r="G68" t="n">
-        <v>0.834</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H68" t="n">
-        <v>0.124</v>
+        <v>0.155</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0969</v>
+        <v>0.115</v>
       </c>
       <c r="J68" t="n">
-        <v>0.554</v>
+        <v>0.466</v>
       </c>
     </row>
     <row r="69">
@@ -3183,22 +3183,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.46</v>
+        <v>0.427</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.789</v>
       </c>
       <c r="G69" t="n">
-        <v>0.834</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>0.124</v>
+        <v>0.155</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0969</v>
+        <v>0.115</v>
       </c>
       <c r="J69" t="n">
-        <v>0.575</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="70">
@@ -3223,22 +3223,22 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.00452</v>
+        <v>0.00727</v>
       </c>
       <c r="F70" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.789</v>
       </c>
       <c r="G70" t="n">
-        <v>0.886</v>
+        <v>0.873</v>
       </c>
       <c r="H70" t="n">
-        <v>0.124</v>
+        <v>0.155</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0858</v>
+        <v>0.0925</v>
       </c>
       <c r="J70" t="n">
-        <v>0.0452</v>
+        <v>0.0282</v>
       </c>
     </row>
     <row r="71">
@@ -3263,22 +3263,22 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.00451</v>
+        <v>0.00286</v>
       </c>
       <c r="F71" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.789</v>
       </c>
       <c r="G71" t="n">
-        <v>0.886</v>
+        <v>0.873</v>
       </c>
       <c r="H71" t="n">
-        <v>0.124</v>
+        <v>0.155</v>
       </c>
       <c r="I71" t="n">
-        <v>0.0858</v>
+        <v>0.0925</v>
       </c>
       <c r="J71" t="n">
-        <v>0.0275</v>
+        <v>0.0258</v>
       </c>
     </row>
     <row r="72">
@@ -3303,22 +3303,22 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.0104</v>
+        <v>0.0113</v>
       </c>
       <c r="F72" t="n">
-        <v>0.764</v>
+        <v>0.752</v>
       </c>
       <c r="G72" t="n">
-        <v>0.794</v>
+        <v>0.785</v>
       </c>
       <c r="H72" t="n">
-        <v>0.165</v>
+        <v>0.176</v>
       </c>
       <c r="I72" t="n">
-        <v>0.177</v>
+        <v>0.189</v>
       </c>
       <c r="J72" t="n">
-        <v>0.0473</v>
+        <v>0.0282</v>
       </c>
     </row>
     <row r="73">
@@ -3346,16 +3346,16 @@
         <v>0.011</v>
       </c>
       <c r="F73" t="n">
-        <v>0.764</v>
+        <v>0.752</v>
       </c>
       <c r="G73" t="n">
-        <v>0.794</v>
+        <v>0.785</v>
       </c>
       <c r="H73" t="n">
-        <v>0.165</v>
+        <v>0.176</v>
       </c>
       <c r="I73" t="n">
-        <v>0.177</v>
+        <v>0.189</v>
       </c>
       <c r="J73" t="n">
         <v>0.0275</v>
@@ -3383,22 +3383,22 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.0142</v>
+        <v>0.009679999999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>0.764</v>
+        <v>0.752</v>
       </c>
       <c r="G74" t="n">
-        <v>0.799</v>
+        <v>0.791</v>
       </c>
       <c r="H74" t="n">
-        <v>0.165</v>
+        <v>0.176</v>
       </c>
       <c r="I74" t="n">
-        <v>0.153</v>
+        <v>0.161</v>
       </c>
       <c r="J74" t="n">
-        <v>0.0473</v>
+        <v>0.0282</v>
       </c>
     </row>
     <row r="75">
@@ -3423,22 +3423,22 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.011</v>
+        <v>0.00516</v>
       </c>
       <c r="F75" t="n">
-        <v>0.764</v>
+        <v>0.752</v>
       </c>
       <c r="G75" t="n">
-        <v>0.799</v>
+        <v>0.791</v>
       </c>
       <c r="H75" t="n">
-        <v>0.165</v>
+        <v>0.176</v>
       </c>
       <c r="I75" t="n">
-        <v>0.153</v>
+        <v>0.161</v>
       </c>
       <c r="J75" t="n">
-        <v>0.0275</v>
+        <v>0.0258</v>
       </c>
     </row>
     <row r="76">
@@ -3463,22 +3463,22 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.0358</v>
+        <v>0.0198</v>
       </c>
       <c r="F76" t="n">
-        <v>0.764</v>
+        <v>0.752</v>
       </c>
       <c r="G76" t="n">
-        <v>0.794</v>
+        <v>0.786</v>
       </c>
       <c r="H76" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="I76" t="n">
         <v>0.165</v>
       </c>
-      <c r="I76" t="n">
-        <v>0.157</v>
-      </c>
       <c r="J76" t="n">
-        <v>0.0597</v>
+        <v>0.0396</v>
       </c>
     </row>
     <row r="77">
@@ -3503,22 +3503,22 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.0577</v>
+        <v>0.0386</v>
       </c>
       <c r="F77" t="n">
-        <v>0.764</v>
+        <v>0.752</v>
       </c>
       <c r="G77" t="n">
-        <v>0.794</v>
+        <v>0.786</v>
       </c>
       <c r="H77" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="I77" t="n">
         <v>0.165</v>
       </c>
-      <c r="I77" t="n">
-        <v>0.157</v>
-      </c>
       <c r="J77" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.0643</v>
       </c>
     </row>
     <row r="78">
@@ -3543,22 +3543,22 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.0334</v>
+        <v>0.0256</v>
       </c>
       <c r="F78" t="n">
-        <v>0.764</v>
+        <v>0.752</v>
       </c>
       <c r="G78" t="n">
-        <v>0.799</v>
+        <v>0.79</v>
       </c>
       <c r="H78" t="n">
-        <v>0.165</v>
+        <v>0.176</v>
       </c>
       <c r="I78" t="n">
-        <v>0.162</v>
+        <v>0.175</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0597</v>
+        <v>0.0427</v>
       </c>
     </row>
     <row r="79">
@@ -3586,19 +3586,19 @@
         <v>0.0335</v>
       </c>
       <c r="F79" t="n">
-        <v>0.764</v>
+        <v>0.752</v>
       </c>
       <c r="G79" t="n">
-        <v>0.799</v>
+        <v>0.79</v>
       </c>
       <c r="H79" t="n">
-        <v>0.165</v>
+        <v>0.176</v>
       </c>
       <c r="I79" t="n">
-        <v>0.162</v>
+        <v>0.175</v>
       </c>
       <c r="J79" t="n">
-        <v>0.067</v>
+        <v>0.0643</v>
       </c>
     </row>
     <row r="80">
@@ -3623,22 +3623,22 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.025</v>
+        <v>0.0109</v>
       </c>
       <c r="F80" t="n">
-        <v>0.764</v>
+        <v>0.752</v>
       </c>
       <c r="G80" t="n">
-        <v>0.793</v>
+        <v>0.788</v>
       </c>
       <c r="H80" t="n">
-        <v>0.165</v>
+        <v>0.176</v>
       </c>
       <c r="I80" t="n">
-        <v>0.135</v>
+        <v>0.139</v>
       </c>
       <c r="J80" t="n">
-        <v>0.0597</v>
+        <v>0.0282</v>
       </c>
     </row>
     <row r="81">
@@ -3663,19 +3663,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.0076</v>
+        <v>0.00898</v>
       </c>
       <c r="F81" t="n">
-        <v>0.764</v>
+        <v>0.752</v>
       </c>
       <c r="G81" t="n">
-        <v>0.793</v>
+        <v>0.788</v>
       </c>
       <c r="H81" t="n">
-        <v>0.165</v>
+        <v>0.176</v>
       </c>
       <c r="I81" t="n">
-        <v>0.135</v>
+        <v>0.139</v>
       </c>
       <c r="J81" t="n">
         <v>0.0275</v>
@@ -3776,7 +3776,7 @@
         <v>0.149</v>
       </c>
       <c r="I2" t="n">
-        <v>0.342</v>
+        <v>0.398</v>
       </c>
     </row>
     <row r="3">
@@ -3850,7 +3850,7 @@
         <v>0.0517</v>
       </c>
       <c r="I4" t="n">
-        <v>0.276</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="5">
@@ -3878,16 +3878,16 @@
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.993</v>
       </c>
       <c r="G5" t="n">
         <v>0.987</v>
       </c>
       <c r="H5" t="n">
-        <v>0.498</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.725</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3924,7 +3924,7 @@
         <v>0.262</v>
       </c>
       <c r="I6" t="n">
-        <v>0.466</v>
+        <v>0.524</v>
       </c>
     </row>
     <row r="7">
@@ -3952,16 +3952,16 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8</v>
+        <v>0.793</v>
       </c>
       <c r="G7" t="n">
-        <v>0.893</v>
+        <v>0.88</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0364</v>
+        <v>0.0601</v>
       </c>
       <c r="I7" t="n">
-        <v>0.276</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="8">
@@ -3992,13 +3992,13 @@
         <v>0.86</v>
       </c>
       <c r="G8" t="n">
-        <v>0.92</v>
+        <v>0.913</v>
       </c>
       <c r="H8" t="n">
-        <v>0.139</v>
+        <v>0.202</v>
       </c>
       <c r="I8" t="n">
-        <v>0.342</v>
+        <v>0.461</v>
       </c>
     </row>
     <row r="9">
@@ -4035,7 +4035,7 @@
         <v>0.572</v>
       </c>
       <c r="I9" t="n">
-        <v>0.761</v>
+        <v>0.824</v>
       </c>
     </row>
     <row r="10">
@@ -4063,16 +4063,16 @@
         <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.673</v>
       </c>
       <c r="G10" t="n">
-        <v>0.713</v>
+        <v>0.647</v>
       </c>
       <c r="H10" t="n">
-        <v>0.706</v>
+        <v>0.715</v>
       </c>
       <c r="I10" t="n">
-        <v>0.771</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="11">
@@ -4100,16 +4100,16 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>0.913</v>
+        <v>0.853</v>
       </c>
       <c r="G11" t="n">
-        <v>0.847</v>
+        <v>0.78</v>
       </c>
       <c r="H11" t="n">
-        <v>0.109</v>
+        <v>0.135</v>
       </c>
       <c r="I11" t="n">
-        <v>0.342</v>
+        <v>0.398</v>
       </c>
     </row>
     <row r="12">
@@ -4137,16 +4137,16 @@
         <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>0.713</v>
+        <v>0.707</v>
       </c>
       <c r="G12" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="H12" t="n">
-        <v>0.232</v>
+        <v>0.361</v>
       </c>
       <c r="I12" t="n">
-        <v>0.464</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="13">
@@ -4220,7 +4220,7 @@
         <v>0.723</v>
       </c>
       <c r="I14" t="n">
-        <v>0.771</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="15">
@@ -4257,7 +4257,7 @@
         <v>0.618</v>
       </c>
       <c r="I15" t="n">
-        <v>0.761</v>
+        <v>0.824</v>
       </c>
     </row>
     <row r="16">
@@ -4285,16 +4285,16 @@
         <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>0.707</v>
+        <v>0.673</v>
       </c>
       <c r="G16" t="n">
-        <v>0.767</v>
+        <v>0.727</v>
       </c>
       <c r="H16" t="n">
-        <v>0.294</v>
+        <v>0.378</v>
       </c>
       <c r="I16" t="n">
-        <v>0.471</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="17">
@@ -4322,16 +4322,16 @@
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>0.66</v>
+        <v>0.573</v>
       </c>
       <c r="G17" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0745</v>
+        <v>0.011</v>
       </c>
       <c r="I17" t="n">
-        <v>0.298</v>
+        <v>0.0882</v>
       </c>
     </row>
     <row r="18">
@@ -4368,7 +4368,7 @@
         <v>0.213</v>
       </c>
       <c r="I18" t="n">
-        <v>0.653</v>
+        <v>0.681</v>
       </c>
     </row>
     <row r="19">
@@ -4442,7 +4442,7 @@
         <v>0.0323</v>
       </c>
       <c r="I20" t="n">
-        <v>0.258</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="21">
@@ -4476,10 +4476,10 @@
         <v>0.917</v>
       </c>
       <c r="H21" t="n">
-        <v>0.49</v>
+        <v>0.491</v>
       </c>
       <c r="I21" t="n">
-        <v>0.793</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="22">
@@ -4516,7 +4516,7 @@
         <v>0.358</v>
       </c>
       <c r="I22" t="n">
-        <v>0.717</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="23">
@@ -4544,16 +4544,16 @@
         <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>0.699</v>
+        <v>0.469</v>
       </c>
       <c r="I23" t="n">
-        <v>0.823</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="24">
@@ -4587,10 +4587,10 @@
         <v>0.929</v>
       </c>
       <c r="H24" t="n">
-        <v>0.514</v>
+        <v>0.512</v>
       </c>
       <c r="I24" t="n">
-        <v>0.793</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="25">
@@ -4627,7 +4627,7 @@
         <v>0.545</v>
       </c>
       <c r="I25" t="n">
-        <v>0.793</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="26">
@@ -4655,16 +4655,16 @@
         <v>9</v>
       </c>
       <c r="F26" t="n">
-        <v>0.988</v>
+        <v>0.987</v>
       </c>
       <c r="G26" t="n">
-        <v>0.977</v>
+        <v>0.974</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0.618</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="27">
@@ -4692,16 +4692,16 @@
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.928</v>
       </c>
       <c r="G27" t="n">
-        <v>0.914</v>
+        <v>0.9</v>
       </c>
       <c r="H27" t="n">
-        <v>0.757</v>
+        <v>0.754</v>
       </c>
       <c r="I27" t="n">
-        <v>0.823</v>
+        <v>0.772</v>
       </c>
     </row>
     <row r="28">
@@ -4729,16 +4729,16 @@
         <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>0.889</v>
+        <v>0.887</v>
       </c>
       <c r="G28" t="n">
-        <v>0.915</v>
+        <v>0.912</v>
       </c>
       <c r="H28" t="n">
-        <v>0.771</v>
+        <v>0.772</v>
       </c>
       <c r="I28" t="n">
-        <v>0.823</v>
+        <v>0.772</v>
       </c>
     </row>
     <row r="29">
@@ -4775,7 +4775,7 @@
         <v>0.285</v>
       </c>
       <c r="I29" t="n">
-        <v>0.653</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="30">
@@ -4812,7 +4812,7 @@
         <v>0.704</v>
       </c>
       <c r="I30" t="n">
-        <v>0.823</v>
+        <v>0.772</v>
       </c>
     </row>
     <row r="31">
@@ -4849,7 +4849,7 @@
         <v>0.064</v>
       </c>
       <c r="I31" t="n">
-        <v>0.341</v>
+        <v>0.256</v>
       </c>
     </row>
     <row r="32">
@@ -4877,16 +4877,16 @@
         <v>15</v>
       </c>
       <c r="F32" t="n">
-        <v>0.649</v>
+        <v>0.625</v>
       </c>
       <c r="G32" t="n">
-        <v>0.735</v>
+        <v>0.71</v>
       </c>
       <c r="H32" t="n">
-        <v>0.286</v>
+        <v>0.36</v>
       </c>
       <c r="I32" t="n">
-        <v>0.653</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="33">
@@ -4914,16 +4914,16 @@
         <v>16</v>
       </c>
       <c r="F33" t="n">
-        <v>0.556</v>
+        <v>0.415</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.647</v>
       </c>
       <c r="H33" t="n">
-        <v>0.176</v>
+        <v>0.0354</v>
       </c>
       <c r="I33" t="n">
-        <v>0.653</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="34">
@@ -4960,7 +4960,7 @@
         <v>0.515</v>
       </c>
       <c r="I34" t="n">
-        <v>0.927</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="35">
@@ -5062,7 +5062,7 @@
         <v>4</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0.955</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
@@ -5136,16 +5136,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.696</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>0.88</v>
+        <v>0.859</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00354</v>
+        <v>0.007939999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0566</v>
+        <v>0.0635</v>
       </c>
     </row>
     <row r="40">
@@ -5176,13 +5176,13 @@
         <v>0.788</v>
       </c>
       <c r="G40" t="n">
-        <v>0.929</v>
+        <v>0.918</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0141</v>
+        <v>0.0288</v>
       </c>
       <c r="I40" t="n">
-        <v>0.113</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="41">
@@ -5219,7 +5219,7 @@
         <v>0.637</v>
       </c>
       <c r="I41" t="n">
-        <v>0.927</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -5247,16 +5247,16 @@
         <v>9</v>
       </c>
       <c r="F42" t="n">
-        <v>0.635</v>
+        <v>0.619</v>
       </c>
       <c r="G42" t="n">
-        <v>0.675</v>
+        <v>0.595</v>
       </c>
       <c r="H42" t="n">
-        <v>0.596</v>
+        <v>0.797</v>
       </c>
       <c r="I42" t="n">
-        <v>0.927</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -5284,16 +5284,16 @@
         <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>0.901</v>
+        <v>0.79</v>
       </c>
       <c r="G43" t="n">
-        <v>0.79</v>
+        <v>0.667</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0804</v>
+        <v>0.111</v>
       </c>
       <c r="I43" t="n">
-        <v>0.429</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="44">
@@ -5321,16 +5321,16 @@
         <v>11</v>
       </c>
       <c r="F44" t="n">
-        <v>0.609</v>
+        <v>0.598</v>
       </c>
       <c r="G44" t="n">
-        <v>0.707</v>
+        <v>0.674</v>
       </c>
       <c r="H44" t="n">
-        <v>0.214</v>
+        <v>0.358</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="45">
@@ -5441,7 +5441,7 @@
         <v>0.539</v>
       </c>
       <c r="I47" t="n">
-        <v>0.927</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="48">
@@ -5469,10 +5469,10 @@
         <v>15</v>
       </c>
       <c r="F48" t="n">
-        <v>0.746</v>
+        <v>0.672</v>
       </c>
       <c r="G48" t="n">
-        <v>0.746</v>
+        <v>0.657</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
@@ -5506,16 +5506,16 @@
         <v>16</v>
       </c>
       <c r="F49" t="n">
-        <v>0.526</v>
+        <v>0.298</v>
       </c>
       <c r="G49" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.579</v>
       </c>
       <c r="H49" t="n">
-        <v>0.125</v>
+        <v>0.00441</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>0.0635</v>
       </c>
     </row>
     <row r="50">
@@ -5552,7 +5552,7 @@
         <v>0.156</v>
       </c>
       <c r="I50" t="n">
-        <v>0.312</v>
+        <v>0.356</v>
       </c>
     </row>
     <row r="51">
@@ -5589,7 +5589,7 @@
         <v>0.000103</v>
       </c>
       <c r="I51" t="n">
-        <v>0.00165</v>
+        <v>0.00134</v>
       </c>
     </row>
     <row r="52">
@@ -5626,7 +5626,7 @@
         <v>0.0849</v>
       </c>
       <c r="I52" t="n">
-        <v>0.226</v>
+        <v>0.272</v>
       </c>
     </row>
     <row r="53">
@@ -5654,16 +5654,16 @@
         <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
       <c r="G53" t="n">
         <v>0.957</v>
       </c>
       <c r="H53" t="n">
-        <v>0.495</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.66</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -5700,7 +5700,7 @@
         <v>0.208</v>
       </c>
       <c r="I54" t="n">
-        <v>0.37</v>
+        <v>0.416</v>
       </c>
     </row>
     <row r="55">
@@ -5728,16 +5728,16 @@
         <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.803</v>
       </c>
       <c r="G55" t="n">
-        <v>0.91</v>
+        <v>0.898</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0105</v>
+        <v>0.0195</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0837</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="56">
@@ -5768,13 +5768,13 @@
         <v>0.865</v>
       </c>
       <c r="G56" t="n">
-        <v>0.929</v>
+        <v>0.923</v>
       </c>
       <c r="H56" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="I56" t="n">
-        <v>0.226</v>
+        <v>0.274</v>
       </c>
     </row>
     <row r="57">
@@ -5839,16 +5839,16 @@
         <v>9</v>
       </c>
       <c r="F58" t="n">
-        <v>0.773</v>
+        <v>0.761</v>
       </c>
       <c r="G58" t="n">
-        <v>0.798</v>
+        <v>0.739</v>
       </c>
       <c r="H58" t="n">
-        <v>0.554</v>
+        <v>0.648</v>
       </c>
       <c r="I58" t="n">
-        <v>0.681</v>
+        <v>0.789</v>
       </c>
     </row>
     <row r="59">
@@ -5876,16 +5876,16 @@
         <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>0.918</v>
+        <v>0.853</v>
       </c>
       <c r="G59" t="n">
-        <v>0.848</v>
+        <v>0.766</v>
       </c>
       <c r="H59" t="n">
-        <v>0.075</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>0.226</v>
+        <v>0.272</v>
       </c>
     </row>
     <row r="60">
@@ -5913,16 +5913,16 @@
         <v>11</v>
       </c>
       <c r="F60" t="n">
-        <v>0.723</v>
+        <v>0.714</v>
       </c>
       <c r="G60" t="n">
-        <v>0.798</v>
+        <v>0.775</v>
       </c>
       <c r="H60" t="n">
-        <v>0.148</v>
+        <v>0.244</v>
       </c>
       <c r="I60" t="n">
-        <v>0.312</v>
+        <v>0.435</v>
       </c>
     </row>
     <row r="61">
@@ -5959,7 +5959,7 @@
         <v>0.715</v>
       </c>
       <c r="I61" t="n">
-        <v>0.74</v>
+        <v>0.789</v>
       </c>
     </row>
     <row r="62">
@@ -5996,7 +5996,7 @@
         <v>0.714</v>
       </c>
       <c r="I62" t="n">
-        <v>0.74</v>
+        <v>0.789</v>
       </c>
     </row>
     <row r="63">
@@ -6033,7 +6033,7 @@
         <v>0.74</v>
       </c>
       <c r="I63" t="n">
-        <v>0.74</v>
+        <v>0.789</v>
       </c>
     </row>
     <row r="64">
@@ -6061,16 +6061,16 @@
         <v>15</v>
       </c>
       <c r="F64" t="n">
-        <v>0.694</v>
+        <v>0.647</v>
       </c>
       <c r="G64" t="n">
-        <v>0.741</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H64" t="n">
-        <v>0.426</v>
+        <v>0.605</v>
       </c>
       <c r="I64" t="n">
-        <v>0.62</v>
+        <v>0.789</v>
       </c>
     </row>
     <row r="65">
@@ -6098,16 +6098,16 @@
         <v>16</v>
       </c>
       <c r="F65" t="n">
-        <v>0.541</v>
+        <v>0.347</v>
       </c>
       <c r="G65" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.611</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0293</v>
+        <v>0.000168</v>
       </c>
       <c r="I65" t="n">
-        <v>0.156</v>
+        <v>0.00134</v>
       </c>
     </row>
     <row r="66">
@@ -6246,16 +6246,16 @@
         <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0.993</v>
       </c>
       <c r="G69" t="n">
         <v>0.967</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0604</v>
+        <v>0.214</v>
       </c>
       <c r="I69" t="n">
-        <v>0.242</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="70">
@@ -6320,16 +6320,16 @@
         <v>6</v>
       </c>
       <c r="F71" t="n">
-        <v>0.8</v>
+        <v>0.793</v>
       </c>
       <c r="G71" t="n">
         <v>0.887</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0558</v>
+        <v>0.0398</v>
       </c>
       <c r="I71" t="n">
-        <v>0.242</v>
+        <v>0.166</v>
       </c>
     </row>
     <row r="72">
@@ -6431,16 +6431,16 @@
         <v>9</v>
       </c>
       <c r="F74" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.673</v>
       </c>
       <c r="G74" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="H74" t="n">
-        <v>0.197</v>
+        <v>0.451</v>
       </c>
       <c r="I74" t="n">
-        <v>0.393</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="75">
@@ -6468,16 +6468,16 @@
         <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>0.913</v>
+        <v>0.853</v>
       </c>
       <c r="G75" t="n">
-        <v>0.847</v>
+        <v>0.773</v>
       </c>
       <c r="H75" t="n">
-        <v>0.109</v>
+        <v>0.103</v>
       </c>
       <c r="I75" t="n">
-        <v>0.29</v>
+        <v>0.291</v>
       </c>
     </row>
     <row r="76">
@@ -6505,16 +6505,16 @@
         <v>11</v>
       </c>
       <c r="F76" t="n">
-        <v>0.713</v>
+        <v>0.707</v>
       </c>
       <c r="G76" t="n">
-        <v>0.8</v>
+        <v>0.793</v>
       </c>
       <c r="H76" t="n">
-        <v>0.106</v>
+        <v>0.109</v>
       </c>
       <c r="I76" t="n">
-        <v>0.29</v>
+        <v>0.291</v>
       </c>
     </row>
     <row r="77">
@@ -6588,7 +6588,7 @@
         <v>0.335</v>
       </c>
       <c r="I78" t="n">
-        <v>0.596</v>
+        <v>0.671</v>
       </c>
     </row>
     <row r="79">
@@ -6653,16 +6653,16 @@
         <v>15</v>
       </c>
       <c r="F80" t="n">
-        <v>0.707</v>
+        <v>0.673</v>
       </c>
       <c r="G80" t="n">
-        <v>0.747</v>
+        <v>0.72</v>
       </c>
       <c r="H80" t="n">
-        <v>0.517</v>
+        <v>0.451</v>
       </c>
       <c r="I80" t="n">
-        <v>0.742</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="81">
@@ -6690,16 +6690,16 @@
         <v>16</v>
       </c>
       <c r="F81" t="n">
-        <v>0.66</v>
+        <v>0.573</v>
       </c>
       <c r="G81" t="n">
-        <v>0.74</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H81" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="I81" t="n">
         <v>0.166</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0.379</v>
       </c>
     </row>
     <row r="82">
@@ -6844,10 +6844,10 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0561</v>
+        <v>0.059</v>
       </c>
       <c r="I85" t="n">
-        <v>0.225</v>
+        <v>0.236</v>
       </c>
     </row>
     <row r="86">
@@ -6912,16 +6912,16 @@
         <v>6</v>
       </c>
       <c r="F87" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
       <c r="G87" t="n">
         <v>0.921</v>
       </c>
       <c r="H87" t="n">
-        <v>0.303</v>
+        <v>0.304</v>
       </c>
       <c r="I87" t="n">
-        <v>0.643</v>
+        <v>0.629</v>
       </c>
     </row>
     <row r="88">
@@ -6958,7 +6958,7 @@
         <v>0.347</v>
       </c>
       <c r="I88" t="n">
-        <v>0.643</v>
+        <v>0.629</v>
       </c>
     </row>
     <row r="89">
@@ -7023,10 +7023,10 @@
         <v>9</v>
       </c>
       <c r="F90" t="n">
-        <v>0.988</v>
+        <v>0.987</v>
       </c>
       <c r="G90" t="n">
-        <v>0.979</v>
+        <v>0.977</v>
       </c>
       <c r="H90" t="n">
         <v>1</v>
@@ -7060,13 +7060,13 @@
         <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.928</v>
       </c>
       <c r="G91" t="n">
-        <v>0.903</v>
+        <v>0.885</v>
       </c>
       <c r="H91" t="n">
-        <v>0.553</v>
+        <v>0.546</v>
       </c>
       <c r="I91" t="n">
         <v>0.746</v>
@@ -7097,10 +7097,10 @@
         <v>11</v>
       </c>
       <c r="F92" t="n">
-        <v>0.889</v>
+        <v>0.887</v>
       </c>
       <c r="G92" t="n">
-        <v>0.887</v>
+        <v>0.886</v>
       </c>
       <c r="H92" t="n">
         <v>1</v>
@@ -7180,7 +7180,7 @@
         <v>0.309</v>
       </c>
       <c r="I94" t="n">
-        <v>0.643</v>
+        <v>0.629</v>
       </c>
     </row>
     <row r="95">
@@ -7245,16 +7245,16 @@
         <v>15</v>
       </c>
       <c r="F96" t="n">
-        <v>0.649</v>
+        <v>0.625</v>
       </c>
       <c r="G96" t="n">
-        <v>0.73</v>
+        <v>0.712</v>
       </c>
       <c r="H96" t="n">
-        <v>0.362</v>
+        <v>0.354</v>
       </c>
       <c r="I96" t="n">
-        <v>0.643</v>
+        <v>0.629</v>
       </c>
     </row>
     <row r="97">
@@ -7282,16 +7282,16 @@
         <v>16</v>
       </c>
       <c r="F97" t="n">
-        <v>0.556</v>
+        <v>0.415</v>
       </c>
       <c r="G97" t="n">
-        <v>0.655</v>
+        <v>0.608</v>
       </c>
       <c r="H97" t="n">
-        <v>0.335</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="I97" t="n">
-        <v>0.643</v>
+        <v>0.297</v>
       </c>
     </row>
     <row r="98">
@@ -7328,7 +7328,7 @@
         <v>0.0352</v>
       </c>
       <c r="I98" t="n">
-        <v>0.188</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="99">
@@ -7365,7 +7365,7 @@
         <v>0.236</v>
       </c>
       <c r="I99" t="n">
-        <v>0.472</v>
+        <v>0.539</v>
       </c>
     </row>
     <row r="100">
@@ -7402,7 +7402,7 @@
         <v>0.611</v>
       </c>
       <c r="I100" t="n">
-        <v>0.978</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -7430,7 +7430,7 @@
         <v>4</v>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>0.955</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
@@ -7504,16 +7504,16 @@
         <v>6</v>
       </c>
       <c r="F103" t="n">
-        <v>0.696</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G103" t="n">
         <v>0.891</v>
       </c>
       <c r="H103" t="n">
-        <v>0.00171</v>
+        <v>0.0009940000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0274</v>
+        <v>0.0159</v>
       </c>
     </row>
     <row r="104">
@@ -7550,7 +7550,7 @@
         <v>0.0919</v>
       </c>
       <c r="I104" t="n">
-        <v>0.364</v>
+        <v>0.294</v>
       </c>
     </row>
     <row r="105">
@@ -7615,16 +7615,16 @@
         <v>9</v>
       </c>
       <c r="F106" t="n">
-        <v>0.635</v>
+        <v>0.619</v>
       </c>
       <c r="G106" t="n">
-        <v>0.73</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H106" t="n">
-        <v>0.136</v>
+        <v>0.355</v>
       </c>
       <c r="I106" t="n">
-        <v>0.364</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="107">
@@ -7652,16 +7652,16 @@
         <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>0.901</v>
+        <v>0.79</v>
       </c>
       <c r="G107" t="n">
-        <v>0.802</v>
+        <v>0.667</v>
       </c>
       <c r="H107" t="n">
-        <v>0.12</v>
+        <v>0.111</v>
       </c>
       <c r="I107" t="n">
-        <v>0.364</v>
+        <v>0.297</v>
       </c>
     </row>
     <row r="108">
@@ -7689,16 +7689,16 @@
         <v>11</v>
       </c>
       <c r="F108" t="n">
-        <v>0.609</v>
+        <v>0.598</v>
       </c>
       <c r="G108" t="n">
-        <v>0.772</v>
+        <v>0.761</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0252</v>
+        <v>0.0266</v>
       </c>
       <c r="I108" t="n">
-        <v>0.188</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="109">
@@ -7837,16 +7837,16 @@
         <v>15</v>
       </c>
       <c r="F112" t="n">
-        <v>0.746</v>
+        <v>0.672</v>
       </c>
       <c r="G112" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="H112" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.718</v>
       </c>
       <c r="I112" t="n">
-        <v>0.978</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -7874,16 +7874,16 @@
         <v>16</v>
       </c>
       <c r="F113" t="n">
-        <v>0.526</v>
+        <v>0.298</v>
       </c>
       <c r="G113" t="n">
-        <v>0.667</v>
+        <v>0.544</v>
       </c>
       <c r="H113" t="n">
-        <v>0.181</v>
+        <v>0.0133</v>
       </c>
       <c r="I113" t="n">
-        <v>0.414</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="114">
@@ -7920,7 +7920,7 @@
         <v>0.283</v>
       </c>
       <c r="I114" t="n">
-        <v>0.503</v>
+        <v>0.549</v>
       </c>
     </row>
     <row r="115">
@@ -7957,7 +7957,7 @@
         <v>0.00116</v>
       </c>
       <c r="I115" t="n">
-        <v>0.0185</v>
+        <v>0.0104</v>
       </c>
     </row>
     <row r="116">
@@ -7994,7 +7994,7 @@
         <v>0.00903</v>
       </c>
       <c r="I116" t="n">
-        <v>0.0635</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="117">
@@ -8022,16 +8022,16 @@
         <v>4</v>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
       <c r="G117" t="n">
         <v>0.898</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0576</v>
+        <v>0.209</v>
       </c>
       <c r="I117" t="n">
-        <v>0.177</v>
+        <v>0.478</v>
       </c>
     </row>
     <row r="118">
@@ -8096,16 +8096,16 @@
         <v>6</v>
       </c>
       <c r="F119" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.803</v>
       </c>
       <c r="G119" t="n">
         <v>0.906</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0119</v>
+        <v>0.00775</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0635</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="120">
@@ -8207,16 +8207,16 @@
         <v>9</v>
       </c>
       <c r="F122" t="n">
-        <v>0.773</v>
+        <v>0.761</v>
       </c>
       <c r="G122" t="n">
-        <v>0.836</v>
+        <v>0.804</v>
       </c>
       <c r="H122" t="n">
-        <v>0.112</v>
+        <v>0.343</v>
       </c>
       <c r="I122" t="n">
-        <v>0.224</v>
+        <v>0.549</v>
       </c>
     </row>
     <row r="123">
@@ -8244,16 +8244,16 @@
         <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>0.918</v>
+        <v>0.853</v>
       </c>
       <c r="G123" t="n">
-        <v>0.85</v>
+        <v>0.761</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0756</v>
+        <v>0.0532</v>
       </c>
       <c r="I123" t="n">
-        <v>0.177</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="124">
@@ -8281,16 +8281,16 @@
         <v>11</v>
       </c>
       <c r="F124" t="n">
-        <v>0.723</v>
+        <v>0.714</v>
       </c>
       <c r="G124" t="n">
-        <v>0.826</v>
+        <v>0.819</v>
       </c>
       <c r="H124" t="n">
-        <v>0.033</v>
+        <v>0.0345</v>
       </c>
       <c r="I124" t="n">
-        <v>0.132</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="125">
@@ -8364,7 +8364,7 @@
         <v>0.321</v>
       </c>
       <c r="I126" t="n">
-        <v>0.514</v>
+        <v>0.549</v>
       </c>
     </row>
     <row r="127">
@@ -8401,7 +8401,7 @@
         <v>0.865</v>
       </c>
       <c r="I127" t="n">
-        <v>0.955</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="128">
@@ -8429,16 +8429,16 @@
         <v>15</v>
       </c>
       <c r="F128" t="n">
-        <v>0.694</v>
+        <v>0.647</v>
       </c>
       <c r="G128" t="n">
-        <v>0.708</v>
+        <v>0.667</v>
       </c>
       <c r="H128" t="n">
-        <v>0.895</v>
+        <v>0.796</v>
       </c>
       <c r="I128" t="n">
-        <v>0.955</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="129">
@@ -8466,16 +8466,16 @@
         <v>16</v>
       </c>
       <c r="F129" t="n">
-        <v>0.541</v>
+        <v>0.347</v>
       </c>
       <c r="G129" t="n">
-        <v>0.661</v>
+        <v>0.574</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0775</v>
+        <v>0.0013</v>
       </c>
       <c r="I129" t="n">
-        <v>0.177</v>
+        <v>0.0104</v>
       </c>
     </row>
     <row r="130">
@@ -8586,7 +8586,7 @@
         <v>0.723</v>
       </c>
       <c r="I132" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -8614,16 +8614,16 @@
         <v>4</v>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
+        <v>0.993</v>
       </c>
       <c r="G133" t="n">
         <v>0.973</v>
       </c>
       <c r="H133" t="n">
-        <v>0.122</v>
+        <v>0.371</v>
       </c>
       <c r="I133" t="n">
-        <v>0.583</v>
+        <v>0.989</v>
       </c>
     </row>
     <row r="134">
@@ -8688,16 +8688,16 @@
         <v>6</v>
       </c>
       <c r="F135" t="n">
-        <v>0.8</v>
+        <v>0.793</v>
       </c>
       <c r="G135" t="n">
-        <v>0.84</v>
+        <v>0.833</v>
       </c>
       <c r="H135" t="n">
-        <v>0.453</v>
+        <v>0.459</v>
       </c>
       <c r="I135" t="n">
-        <v>0.888</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -8734,7 +8734,7 @@
         <v>0.865</v>
       </c>
       <c r="I136" t="n">
-        <v>0.989</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -8799,16 +8799,16 @@
         <v>9</v>
       </c>
       <c r="F138" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.673</v>
       </c>
       <c r="G138" t="n">
-        <v>0.767</v>
+        <v>0.733</v>
       </c>
       <c r="H138" t="n">
-        <v>0.154</v>
+        <v>0.312</v>
       </c>
       <c r="I138" t="n">
-        <v>0.583</v>
+        <v>0.989</v>
       </c>
     </row>
     <row r="139">
@@ -8836,16 +8836,16 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>0.913</v>
+        <v>0.853</v>
       </c>
       <c r="G139" t="n">
-        <v>0.887</v>
+        <v>0.847</v>
       </c>
       <c r="H139" t="n">
-        <v>0.5639999999999999</v>
+        <v>1</v>
       </c>
       <c r="I139" t="n">
-        <v>0.888</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -8873,16 +8873,16 @@
         <v>11</v>
       </c>
       <c r="F140" t="n">
-        <v>0.713</v>
+        <v>0.707</v>
       </c>
       <c r="G140" t="n">
-        <v>0.787</v>
+        <v>0.76</v>
       </c>
       <c r="H140" t="n">
-        <v>0.182</v>
+        <v>0.361</v>
       </c>
       <c r="I140" t="n">
-        <v>0.583</v>
+        <v>0.989</v>
       </c>
     </row>
     <row r="141">
@@ -8919,7 +8919,7 @@
         <v>0.611</v>
       </c>
       <c r="I141" t="n">
-        <v>0.888</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -8956,7 +8956,7 @@
         <v>0.723</v>
       </c>
       <c r="I142" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -8993,7 +8993,7 @@
         <v>0.51</v>
       </c>
       <c r="I143" t="n">
-        <v>0.888</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -9021,16 +9021,16 @@
         <v>15</v>
       </c>
       <c r="F144" t="n">
-        <v>0.707</v>
+        <v>0.673</v>
       </c>
       <c r="G144" t="n">
-        <v>0.74</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="H144" t="n">
-        <v>0.606</v>
+        <v>0.902</v>
       </c>
       <c r="I144" t="n">
-        <v>0.888</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -9058,16 +9058,16 @@
         <v>16</v>
       </c>
       <c r="F145" t="n">
-        <v>0.66</v>
+        <v>0.573</v>
       </c>
       <c r="G145" t="n">
-        <v>0.727</v>
+        <v>0.633</v>
       </c>
       <c r="H145" t="n">
-        <v>0.26</v>
+        <v>0.345</v>
       </c>
       <c r="I145" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.989</v>
       </c>
     </row>
     <row r="146">
@@ -9212,10 +9212,10 @@
         <v>0.846</v>
       </c>
       <c r="H149" t="n">
-        <v>0.114</v>
+        <v>0.117</v>
       </c>
       <c r="I149" t="n">
-        <v>0.458</v>
+        <v>0.465</v>
       </c>
     </row>
     <row r="150">
@@ -9280,13 +9280,13 @@
         <v>6</v>
       </c>
       <c r="F151" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
       <c r="G151" t="n">
-        <v>0.886</v>
+        <v>0.885</v>
       </c>
       <c r="H151" t="n">
-        <v>0.0709</v>
+        <v>0.0711</v>
       </c>
       <c r="I151" t="n">
         <v>0.442</v>
@@ -9391,7 +9391,7 @@
         <v>9</v>
       </c>
       <c r="F154" t="n">
-        <v>0.988</v>
+        <v>0.987</v>
       </c>
       <c r="G154" t="n">
         <v>0.989</v>
@@ -9428,13 +9428,13 @@
         <v>10</v>
       </c>
       <c r="F155" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.928</v>
       </c>
       <c r="G155" t="n">
-        <v>0.957</v>
+        <v>0.953</v>
       </c>
       <c r="H155" t="n">
-        <v>0.722</v>
+        <v>0.72</v>
       </c>
       <c r="I155" t="n">
         <v>1</v>
@@ -9465,10 +9465,10 @@
         <v>11</v>
       </c>
       <c r="F156" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="G156" t="n">
         <v>0.889</v>
-      </c>
-      <c r="G156" t="n">
-        <v>0.895</v>
       </c>
       <c r="H156" t="n">
         <v>1</v>
@@ -9613,13 +9613,13 @@
         <v>15</v>
       </c>
       <c r="F160" t="n">
-        <v>0.649</v>
+        <v>0.625</v>
       </c>
       <c r="G160" t="n">
-        <v>0.675</v>
+        <v>0.639</v>
       </c>
       <c r="H160" t="n">
-        <v>0.739</v>
+        <v>1</v>
       </c>
       <c r="I160" t="n">
         <v>1</v>
@@ -9650,16 +9650,16 @@
         <v>16</v>
       </c>
       <c r="F161" t="n">
-        <v>0.556</v>
+        <v>0.415</v>
       </c>
       <c r="G161" t="n">
-        <v>0.614</v>
+        <v>0.518</v>
       </c>
       <c r="H161" t="n">
-        <v>0.582</v>
+        <v>0.411</v>
       </c>
       <c r="I161" t="n">
-        <v>1</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="162">
@@ -9770,7 +9770,7 @@
         <v>0.611</v>
       </c>
       <c r="I164" t="n">
-        <v>0.978</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -9798,7 +9798,7 @@
         <v>4</v>
       </c>
       <c r="F165" t="n">
-        <v>1</v>
+        <v>0.955</v>
       </c>
       <c r="G165" t="n">
         <v>1</v>
@@ -9872,16 +9872,16 @@
         <v>6</v>
       </c>
       <c r="F167" t="n">
-        <v>0.696</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G167" t="n">
-        <v>0.848</v>
+        <v>0.837</v>
       </c>
       <c r="H167" t="n">
-        <v>0.0217</v>
+        <v>0.024</v>
       </c>
       <c r="I167" t="n">
-        <v>0.116</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="168">
@@ -9918,7 +9918,7 @@
         <v>0.0919</v>
       </c>
       <c r="I168" t="n">
-        <v>0.294</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="169">
@@ -9983,16 +9983,16 @@
         <v>9</v>
       </c>
       <c r="F170" t="n">
-        <v>0.635</v>
+        <v>0.619</v>
       </c>
       <c r="G170" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H170" t="n">
-        <v>0.136</v>
+        <v>0.289</v>
       </c>
       <c r="I170" t="n">
-        <v>0.364</v>
+        <v>0.771</v>
       </c>
     </row>
     <row r="171">
@@ -10020,16 +10020,16 @@
         <v>10</v>
       </c>
       <c r="F171" t="n">
-        <v>0.901</v>
+        <v>0.79</v>
       </c>
       <c r="G171" t="n">
-        <v>0.827</v>
+        <v>0.753</v>
       </c>
       <c r="H171" t="n">
-        <v>0.251</v>
+        <v>0.709</v>
       </c>
       <c r="I171" t="n">
-        <v>0.574</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -10057,16 +10057,16 @@
         <v>11</v>
       </c>
       <c r="F172" t="n">
-        <v>0.609</v>
+        <v>0.598</v>
       </c>
       <c r="G172" t="n">
-        <v>0.739</v>
+        <v>0.696</v>
       </c>
       <c r="H172" t="n">
-        <v>0.0832</v>
+        <v>0.217</v>
       </c>
       <c r="I172" t="n">
-        <v>0.294</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="173">
@@ -10140,7 +10140,7 @@
         <v>0.488</v>
       </c>
       <c r="I174" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -10205,16 +10205,16 @@
         <v>15</v>
       </c>
       <c r="F176" t="n">
-        <v>0.746</v>
+        <v>0.672</v>
       </c>
       <c r="G176" t="n">
-        <v>0.806</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="H176" t="n">
-        <v>0.535</v>
+        <v>1</v>
       </c>
       <c r="I176" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -10242,16 +10242,16 @@
         <v>16</v>
       </c>
       <c r="F177" t="n">
-        <v>0.526</v>
+        <v>0.298</v>
       </c>
       <c r="G177" t="n">
-        <v>0.754</v>
+        <v>0.509</v>
       </c>
       <c r="H177" t="n">
-        <v>0.0187</v>
+        <v>0.0352</v>
       </c>
       <c r="I177" t="n">
-        <v>0.116</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="178">
@@ -10362,7 +10362,7 @@
         <v>0.486</v>
       </c>
       <c r="I180" t="n">
-        <v>0.636</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="181">
@@ -10390,16 +10390,16 @@
         <v>4</v>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
       <c r="G181" t="n">
         <v>0.917</v>
       </c>
       <c r="H181" t="n">
-        <v>0.118</v>
+        <v>0.365</v>
       </c>
       <c r="I181" t="n">
-        <v>0.315</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="182">
@@ -10464,16 +10464,16 @@
         <v>6</v>
       </c>
       <c r="F183" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.803</v>
       </c>
       <c r="G183" t="n">
-        <v>0.867</v>
+        <v>0.86</v>
       </c>
       <c r="H183" t="n">
-        <v>0.181</v>
+        <v>0.187</v>
       </c>
       <c r="I183" t="n">
-        <v>0.414</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="184">
@@ -10510,7 +10510,7 @@
         <v>0.613</v>
       </c>
       <c r="I184" t="n">
-        <v>0.7</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="185">
@@ -10547,7 +10547,7 @@
         <v>0.71</v>
       </c>
       <c r="I185" t="n">
-        <v>0.758</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="186">
@@ -10575,16 +10575,16 @@
         <v>9</v>
       </c>
       <c r="F186" t="n">
-        <v>0.773</v>
+        <v>0.761</v>
       </c>
       <c r="G186" t="n">
-        <v>0.84</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H186" t="n">
-        <v>0.0859</v>
+        <v>0.232</v>
       </c>
       <c r="I186" t="n">
-        <v>0.275</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="187">
@@ -10612,16 +10612,16 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>0.918</v>
+        <v>0.853</v>
       </c>
       <c r="G187" t="n">
-        <v>0.887</v>
+        <v>0.841</v>
       </c>
       <c r="H187" t="n">
-        <v>0.443</v>
+        <v>0.872</v>
       </c>
       <c r="I187" t="n">
-        <v>0.636</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="188">
@@ -10649,16 +10649,16 @@
         <v>11</v>
       </c>
       <c r="F188" t="n">
-        <v>0.723</v>
+        <v>0.714</v>
       </c>
       <c r="G188" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="H188" t="n">
-        <v>0.0667</v>
+        <v>0.197</v>
       </c>
       <c r="I188" t="n">
-        <v>0.267</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="189">
@@ -10695,7 +10695,7 @@
         <v>0.486</v>
       </c>
       <c r="I189" t="n">
-        <v>0.636</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="190">
@@ -10732,7 +10732,7 @@
         <v>0.479</v>
       </c>
       <c r="I190" t="n">
-        <v>0.636</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="191">
@@ -10769,7 +10769,7 @@
         <v>0.507</v>
       </c>
       <c r="I191" t="n">
-        <v>0.636</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="192">
@@ -10797,16 +10797,16 @@
         <v>15</v>
       </c>
       <c r="F192" t="n">
-        <v>0.694</v>
+        <v>0.647</v>
       </c>
       <c r="G192" t="n">
-        <v>0.735</v>
+        <v>0.662</v>
       </c>
       <c r="H192" t="n">
-        <v>0.516</v>
+        <v>0.9</v>
       </c>
       <c r="I192" t="n">
-        <v>0.636</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="193">
@@ -10834,16 +10834,16 @@
         <v>16</v>
       </c>
       <c r="F193" t="n">
-        <v>0.541</v>
+        <v>0.347</v>
       </c>
       <c r="G193" t="n">
-        <v>0.677</v>
+        <v>0.513</v>
       </c>
       <c r="H193" t="n">
-        <v>0.0336</v>
+        <v>0.0181</v>
       </c>
       <c r="I193" t="n">
-        <v>0.179</v>
+        <v>0.0964</v>
       </c>
     </row>
     <row r="194">
@@ -10954,7 +10954,7 @@
         <v>0.0853</v>
       </c>
       <c r="I196" t="n">
-        <v>0.171</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="197">
@@ -10982,16 +10982,16 @@
         <v>4</v>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>0.993</v>
       </c>
       <c r="G197" t="n">
         <v>0.96</v>
       </c>
       <c r="H197" t="n">
-        <v>0.0297</v>
+        <v>0.121</v>
       </c>
       <c r="I197" t="n">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="198">
@@ -11056,16 +11056,16 @@
         <v>6</v>
       </c>
       <c r="F199" t="n">
-        <v>0.8</v>
+        <v>0.793</v>
       </c>
       <c r="G199" t="n">
         <v>0.887</v>
       </c>
       <c r="H199" t="n">
-        <v>0.0558</v>
+        <v>0.0398</v>
       </c>
       <c r="I199" t="n">
-        <v>0.171</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="200">
@@ -11102,7 +11102,7 @@
         <v>0.202</v>
       </c>
       <c r="I200" t="n">
-        <v>0.359</v>
+        <v>0.378</v>
       </c>
     </row>
     <row r="201">
@@ -11167,16 +11167,16 @@
         <v>9</v>
       </c>
       <c r="F202" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.673</v>
       </c>
       <c r="G202" t="n">
-        <v>0.8</v>
+        <v>0.753</v>
       </c>
       <c r="H202" t="n">
-        <v>0.0341</v>
+        <v>0.16</v>
       </c>
       <c r="I202" t="n">
-        <v>0.16</v>
+        <v>0.366</v>
       </c>
     </row>
     <row r="203">
@@ -11204,16 +11204,16 @@
         <v>10</v>
       </c>
       <c r="F203" t="n">
-        <v>0.913</v>
+        <v>0.853</v>
       </c>
       <c r="G203" t="n">
-        <v>0.84</v>
+        <v>0.793</v>
       </c>
       <c r="H203" t="n">
-        <v>0.078</v>
+        <v>0.226</v>
       </c>
       <c r="I203" t="n">
-        <v>0.171</v>
+        <v>0.378</v>
       </c>
     </row>
     <row r="204">
@@ -11241,16 +11241,16 @@
         <v>11</v>
       </c>
       <c r="F204" t="n">
-        <v>0.713</v>
+        <v>0.707</v>
       </c>
       <c r="G204" t="n">
-        <v>0.78</v>
+        <v>0.773</v>
       </c>
       <c r="H204" t="n">
-        <v>0.232</v>
+        <v>0.236</v>
       </c>
       <c r="I204" t="n">
-        <v>0.371</v>
+        <v>0.378</v>
       </c>
     </row>
     <row r="205">
@@ -11389,16 +11389,16 @@
         <v>15</v>
       </c>
       <c r="F208" t="n">
-        <v>0.707</v>
+        <v>0.673</v>
       </c>
       <c r="G208" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="H208" t="n">
-        <v>0.0813</v>
+        <v>0.124</v>
       </c>
       <c r="I208" t="n">
-        <v>0.171</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="209">
@@ -11426,16 +11426,16 @@
         <v>16</v>
       </c>
       <c r="F209" t="n">
-        <v>0.66</v>
+        <v>0.573</v>
       </c>
       <c r="G209" t="n">
-        <v>0.773</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H209" t="n">
-        <v>0.04</v>
+        <v>0.0414</v>
       </c>
       <c r="I209" t="n">
-        <v>0.16</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="210">
@@ -11580,7 +11580,7 @@
         <v>0.786</v>
       </c>
       <c r="H213" t="n">
-        <v>0.0284</v>
+        <v>0.0308</v>
       </c>
       <c r="I213" t="n">
         <v>0.203</v>
@@ -11648,7 +11648,7 @@
         <v>6</v>
       </c>
       <c r="F215" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
       <c r="G215" t="n">
         <v>0.931</v>
@@ -11657,7 +11657,7 @@
         <v>0.467</v>
       </c>
       <c r="I215" t="n">
-        <v>0.747</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="216">
@@ -11759,10 +11759,10 @@
         <v>9</v>
       </c>
       <c r="F218" t="n">
-        <v>0.988</v>
+        <v>0.987</v>
       </c>
       <c r="G218" t="n">
-        <v>0.98</v>
+        <v>0.978</v>
       </c>
       <c r="H218" t="n">
         <v>1</v>
@@ -11796,16 +11796,16 @@
         <v>10</v>
       </c>
       <c r="F219" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.928</v>
       </c>
       <c r="G219" t="n">
-        <v>0.89</v>
+        <v>0.879</v>
       </c>
       <c r="H219" t="n">
-        <v>0.391</v>
+        <v>0.392</v>
       </c>
       <c r="I219" t="n">
-        <v>0.694</v>
+        <v>0.697</v>
       </c>
     </row>
     <row r="220">
@@ -11833,10 +11833,10 @@
         <v>11</v>
       </c>
       <c r="F220" t="n">
-        <v>0.889</v>
+        <v>0.887</v>
       </c>
       <c r="G220" t="n">
-        <v>0.883</v>
+        <v>0.882</v>
       </c>
       <c r="H220" t="n">
         <v>1</v>
@@ -11879,7 +11879,7 @@
         <v>0.109</v>
       </c>
       <c r="I221" t="n">
-        <v>0.348</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="222">
@@ -11981,16 +11981,16 @@
         <v>15</v>
       </c>
       <c r="F224" t="n">
-        <v>0.649</v>
+        <v>0.625</v>
       </c>
       <c r="G224" t="n">
-        <v>0.747</v>
+        <v>0.725</v>
       </c>
       <c r="H224" t="n">
-        <v>0.219</v>
+        <v>0.215</v>
       </c>
       <c r="I224" t="n">
-        <v>0.5</v>
+        <v>0.492</v>
       </c>
     </row>
     <row r="225">
@@ -12018,16 +12018,16 @@
         <v>16</v>
       </c>
       <c r="F225" t="n">
-        <v>0.556</v>
+        <v>0.415</v>
       </c>
       <c r="G225" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.608</v>
       </c>
       <c r="H225" t="n">
-        <v>0.183</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="I225" t="n">
-        <v>0.488</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="226">
@@ -12138,7 +12138,7 @@
         <v>0.352</v>
       </c>
       <c r="I228" t="n">
-        <v>0.703</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="229">
@@ -12166,7 +12166,7 @@
         <v>4</v>
       </c>
       <c r="F229" t="n">
-        <v>1</v>
+        <v>0.955</v>
       </c>
       <c r="G229" t="n">
         <v>1</v>
@@ -12240,16 +12240,16 @@
         <v>6</v>
       </c>
       <c r="F231" t="n">
-        <v>0.696</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G231" t="n">
         <v>0.88</v>
       </c>
       <c r="H231" t="n">
-        <v>0.00354</v>
+        <v>0.00212</v>
       </c>
       <c r="I231" t="n">
-        <v>0.0566</v>
+        <v>0.0339</v>
       </c>
     </row>
     <row r="232">
@@ -12286,7 +12286,7 @@
         <v>0.0536</v>
       </c>
       <c r="I232" t="n">
-        <v>0.214</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="233">
@@ -12351,16 +12351,16 @@
         <v>9</v>
       </c>
       <c r="F234" t="n">
-        <v>0.635</v>
+        <v>0.619</v>
       </c>
       <c r="G234" t="n">
-        <v>0.778</v>
+        <v>0.722</v>
       </c>
       <c r="H234" t="n">
-        <v>0.0184</v>
+        <v>0.107</v>
       </c>
       <c r="I234" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.344</v>
       </c>
     </row>
     <row r="235">
@@ -12388,16 +12388,16 @@
         <v>10</v>
       </c>
       <c r="F235" t="n">
-        <v>0.901</v>
+        <v>0.79</v>
       </c>
       <c r="G235" t="n">
-        <v>0.802</v>
+        <v>0.716</v>
       </c>
       <c r="H235" t="n">
-        <v>0.12</v>
+        <v>0.362</v>
       </c>
       <c r="I235" t="n">
-        <v>0.321</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="236">
@@ -12425,16 +12425,16 @@
         <v>11</v>
       </c>
       <c r="F236" t="n">
-        <v>0.609</v>
+        <v>0.598</v>
       </c>
       <c r="G236" t="n">
-        <v>0.739</v>
+        <v>0.728</v>
       </c>
       <c r="H236" t="n">
-        <v>0.0832</v>
+        <v>0.0858</v>
       </c>
       <c r="I236" t="n">
-        <v>0.266</v>
+        <v>0.343</v>
       </c>
     </row>
     <row r="237">
@@ -12573,16 +12573,16 @@
         <v>15</v>
       </c>
       <c r="F240" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="G240" t="n">
         <v>0.746</v>
       </c>
-      <c r="G240" t="n">
-        <v>0.836</v>
-      </c>
       <c r="H240" t="n">
-        <v>0.288</v>
+        <v>0.447</v>
       </c>
       <c r="I240" t="n">
-        <v>0.658</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="241">
@@ -12610,16 +12610,16 @@
         <v>16</v>
       </c>
       <c r="F241" t="n">
-        <v>0.526</v>
+        <v>0.298</v>
       </c>
       <c r="G241" t="n">
-        <v>0.754</v>
+        <v>0.544</v>
       </c>
       <c r="H241" t="n">
-        <v>0.0187</v>
+        <v>0.0133</v>
       </c>
       <c r="I241" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="242">
@@ -12693,7 +12693,7 @@
         <v>0.00224</v>
       </c>
       <c r="I243" t="n">
-        <v>0.0358</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="244">
@@ -12730,7 +12730,7 @@
         <v>0.0742</v>
       </c>
       <c r="I244" t="n">
-        <v>0.158</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="245">
@@ -12758,16 +12758,16 @@
         <v>4</v>
       </c>
       <c r="F245" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
       <c r="G245" t="n">
         <v>0.88</v>
       </c>
       <c r="H245" t="n">
-        <v>0.0282</v>
+        <v>0.118</v>
       </c>
       <c r="I245" t="n">
-        <v>0.0902</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="246">
@@ -12832,16 +12832,16 @@
         <v>6</v>
       </c>
       <c r="F247" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.803</v>
       </c>
       <c r="G247" t="n">
         <v>0.905</v>
       </c>
       <c r="H247" t="n">
-        <v>0.0174</v>
+        <v>0.008059999999999999</v>
       </c>
       <c r="I247" t="n">
-        <v>0.0697</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="248">
@@ -12878,7 +12878,7 @@
         <v>0.104</v>
       </c>
       <c r="I248" t="n">
-        <v>0.167</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="249">
@@ -12943,16 +12943,16 @@
         <v>9</v>
       </c>
       <c r="F250" t="n">
-        <v>0.773</v>
+        <v>0.761</v>
       </c>
       <c r="G250" t="n">
-        <v>0.867</v>
+        <v>0.831</v>
       </c>
       <c r="H250" t="n">
-        <v>0.0118</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="I250" t="n">
-        <v>0.063</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="251">
@@ -12980,16 +12980,16 @@
         <v>10</v>
       </c>
       <c r="F251" t="n">
-        <v>0.918</v>
+        <v>0.853</v>
       </c>
       <c r="G251" t="n">
-        <v>0.844</v>
+        <v>0.789</v>
       </c>
       <c r="H251" t="n">
-        <v>0.0536</v>
+        <v>0.173</v>
       </c>
       <c r="I251" t="n">
-        <v>0.143</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="252">
@@ -13017,16 +13017,16 @@
         <v>11</v>
       </c>
       <c r="F252" t="n">
-        <v>0.723</v>
+        <v>0.714</v>
       </c>
       <c r="G252" t="n">
-        <v>0.805</v>
+        <v>0.798</v>
       </c>
       <c r="H252" t="n">
-        <v>0.089</v>
+        <v>0.0912</v>
       </c>
       <c r="I252" t="n">
-        <v>0.158</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="253">
@@ -13165,16 +13165,16 @@
         <v>15</v>
       </c>
       <c r="F256" t="n">
-        <v>0.694</v>
+        <v>0.647</v>
       </c>
       <c r="G256" t="n">
-        <v>0.789</v>
+        <v>0.735</v>
       </c>
       <c r="H256" t="n">
-        <v>0.0795</v>
+        <v>0.12</v>
       </c>
       <c r="I256" t="n">
-        <v>0.158</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="257">
@@ -13202,16 +13202,16 @@
         <v>16</v>
       </c>
       <c r="F257" t="n">
-        <v>0.541</v>
+        <v>0.347</v>
       </c>
       <c r="G257" t="n">
-        <v>0.717</v>
+        <v>0.574</v>
       </c>
       <c r="H257" t="n">
-        <v>0.0064</v>
+        <v>0.0013</v>
       </c>
       <c r="I257" t="n">
-        <v>0.0512</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="258">
@@ -13285,7 +13285,7 @@
         <v>8.69e-05</v>
       </c>
       <c r="I259" t="n">
-        <v>0.00114</v>
+        <v>0.000695</v>
       </c>
     </row>
     <row r="260">
@@ -13350,7 +13350,7 @@
         <v>4</v>
       </c>
       <c r="F261" t="n">
-        <v>1</v>
+        <v>0.993</v>
       </c>
       <c r="G261" t="n">
         <v>0.993</v>
@@ -13424,16 +13424,16 @@
         <v>6</v>
       </c>
       <c r="F263" t="n">
-        <v>0.8</v>
+        <v>0.793</v>
       </c>
       <c r="G263" t="n">
         <v>0.907</v>
       </c>
       <c r="H263" t="n">
-        <v>0.0137</v>
+        <v>0.00911</v>
       </c>
       <c r="I263" t="n">
-        <v>0.0438</v>
+        <v>0.0292</v>
       </c>
     </row>
     <row r="264">
@@ -13464,13 +13464,13 @@
         <v>0.86</v>
       </c>
       <c r="G264" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.927</v>
       </c>
       <c r="H264" t="n">
-        <v>0.0564</v>
+        <v>0.0911</v>
       </c>
       <c r="I264" t="n">
-        <v>0.151</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="265">
@@ -13535,16 +13535,16 @@
         <v>9</v>
       </c>
       <c r="F266" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.673</v>
       </c>
       <c r="G266" t="n">
-        <v>0.767</v>
+        <v>0.74</v>
       </c>
       <c r="H266" t="n">
-        <v>0.154</v>
+        <v>0.254</v>
       </c>
       <c r="I266" t="n">
-        <v>0.308</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="267">
@@ -13572,16 +13572,16 @@
         <v>10</v>
       </c>
       <c r="F267" t="n">
-        <v>0.913</v>
+        <v>0.853</v>
       </c>
       <c r="G267" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.873</v>
       </c>
       <c r="H267" t="n">
-        <v>0.665</v>
+        <v>0.737</v>
       </c>
       <c r="I267" t="n">
-        <v>0.967</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
@@ -13609,16 +13609,16 @@
         <v>11</v>
       </c>
       <c r="F268" t="n">
-        <v>0.713</v>
+        <v>0.707</v>
       </c>
       <c r="G268" t="n">
-        <v>0.853</v>
+        <v>0.847</v>
       </c>
       <c r="H268" t="n">
-        <v>0.00482</v>
+        <v>0.00532</v>
       </c>
       <c r="I268" t="n">
-        <v>0.0193</v>
+        <v>0.0213</v>
       </c>
     </row>
     <row r="269">
@@ -13757,16 +13757,16 @@
         <v>15</v>
       </c>
       <c r="F272" t="n">
-        <v>0.707</v>
+        <v>0.673</v>
       </c>
       <c r="G272" t="n">
-        <v>0.873</v>
+        <v>0.847</v>
       </c>
       <c r="H272" t="n">
-        <v>0.000595</v>
+        <v>0.000662</v>
       </c>
       <c r="I272" t="n">
-        <v>0.00317</v>
+        <v>0.00353</v>
       </c>
     </row>
     <row r="273">
@@ -13794,16 +13794,16 @@
         <v>16</v>
       </c>
       <c r="F273" t="n">
-        <v>0.66</v>
+        <v>0.573</v>
       </c>
       <c r="G273" t="n">
-        <v>0.853</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H273" t="n">
-        <v>0.000143</v>
+        <v>1.87e-05</v>
       </c>
       <c r="I273" t="n">
-        <v>0.00114</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="274">
@@ -13877,7 +13877,7 @@
         <v>0.0005820000000000001</v>
       </c>
       <c r="I275" t="n">
-        <v>0.00932</v>
+        <v>0.00466</v>
       </c>
     </row>
     <row r="276">
@@ -14016,7 +14016,7 @@
         <v>6</v>
       </c>
       <c r="F279" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
       <c r="G279" t="n">
         <v>0.9429999999999999</v>
@@ -14056,10 +14056,10 @@
         <v>0.957</v>
       </c>
       <c r="G280" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H280" t="n">
-        <v>0.73</v>
+        <v>0.729</v>
       </c>
       <c r="I280" t="n">
         <v>1</v>
@@ -14127,16 +14127,16 @@
         <v>9</v>
       </c>
       <c r="F282" t="n">
-        <v>0.988</v>
+        <v>0.987</v>
       </c>
       <c r="G282" t="n">
-        <v>0.95</v>
+        <v>0.948</v>
       </c>
       <c r="H282" t="n">
-        <v>0.228</v>
+        <v>0.226</v>
       </c>
       <c r="I282" t="n">
-        <v>0.73</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="283">
@@ -14164,10 +14164,10 @@
         <v>10</v>
       </c>
       <c r="F283" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.928</v>
       </c>
       <c r="G283" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.931</v>
       </c>
       <c r="H283" t="n">
         <v>1</v>
@@ -14201,13 +14201,13 @@
         <v>11</v>
       </c>
       <c r="F284" t="n">
-        <v>0.889</v>
+        <v>0.887</v>
       </c>
       <c r="G284" t="n">
-        <v>0.927</v>
+        <v>0.926</v>
       </c>
       <c r="H284" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="I284" t="n">
         <v>1</v>
@@ -14321,7 +14321,7 @@
         <v>0.185</v>
       </c>
       <c r="I287" t="n">
-        <v>0.73</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="288">
@@ -14349,16 +14349,16 @@
         <v>15</v>
       </c>
       <c r="F288" t="n">
-        <v>0.649</v>
+        <v>0.625</v>
       </c>
       <c r="G288" t="n">
-        <v>0.864</v>
+        <v>0.855</v>
       </c>
       <c r="H288" t="n">
-        <v>0.0037</v>
+        <v>0.00328</v>
       </c>
       <c r="I288" t="n">
-        <v>0.0296</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="289">
@@ -14386,16 +14386,16 @@
         <v>16</v>
       </c>
       <c r="F289" t="n">
-        <v>0.556</v>
+        <v>0.415</v>
       </c>
       <c r="G289" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="H289" t="n">
-        <v>0.00743</v>
+        <v>0.000502</v>
       </c>
       <c r="I289" t="n">
-        <v>0.0396</v>
+        <v>0.00466</v>
       </c>
     </row>
     <row r="290">
@@ -14534,7 +14534,7 @@
         <v>4</v>
       </c>
       <c r="F293" t="n">
-        <v>1</v>
+        <v>0.955</v>
       </c>
       <c r="G293" t="n">
         <v>0.955</v>
@@ -14608,16 +14608,16 @@
         <v>6</v>
       </c>
       <c r="F295" t="n">
-        <v>0.696</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G295" t="n">
         <v>0.902</v>
       </c>
       <c r="H295" t="n">
-        <v>0.00077</v>
+        <v>0.000433</v>
       </c>
       <c r="I295" t="n">
-        <v>0.0123</v>
+        <v>0.00347</v>
       </c>
     </row>
     <row r="296">
@@ -14648,13 +14648,13 @@
         <v>0.788</v>
       </c>
       <c r="G296" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.929</v>
       </c>
       <c r="H296" t="n">
-        <v>0.00612</v>
+        <v>0.0141</v>
       </c>
       <c r="I296" t="n">
-        <v>0.0245</v>
+        <v>0.0563</v>
       </c>
     </row>
     <row r="297">
@@ -14719,16 +14719,16 @@
         <v>9</v>
       </c>
       <c r="F298" t="n">
-        <v>0.635</v>
+        <v>0.619</v>
       </c>
       <c r="G298" t="n">
-        <v>0.762</v>
+        <v>0.73</v>
       </c>
       <c r="H298" t="n">
-        <v>0.0391</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>0.104</v>
+        <v>0.183</v>
       </c>
     </row>
     <row r="299">
@@ -14756,16 +14756,16 @@
         <v>10</v>
       </c>
       <c r="F299" t="n">
-        <v>0.901</v>
+        <v>0.79</v>
       </c>
       <c r="G299" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.827</v>
       </c>
       <c r="H299" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I299" t="n">
-        <v>0.821</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300">
@@ -14793,16 +14793,16 @@
         <v>11</v>
       </c>
       <c r="F300" t="n">
-        <v>0.609</v>
+        <v>0.598</v>
       </c>
       <c r="G300" t="n">
-        <v>0.826</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H300" t="n">
-        <v>0.00172</v>
+        <v>0.00195</v>
       </c>
       <c r="I300" t="n">
-        <v>0.0137</v>
+        <v>0.0104</v>
       </c>
     </row>
     <row r="301">
@@ -14839,7 +14839,7 @@
         <v>0.0625</v>
       </c>
       <c r="I301" t="n">
-        <v>0.143</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="302">
@@ -14941,16 +14941,16 @@
         <v>15</v>
       </c>
       <c r="F304" t="n">
-        <v>0.746</v>
+        <v>0.672</v>
       </c>
       <c r="G304" t="n">
-        <v>0.851</v>
+        <v>0.791</v>
       </c>
       <c r="H304" t="n">
-        <v>0.196</v>
+        <v>0.172</v>
       </c>
       <c r="I304" t="n">
-        <v>0.348</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="305">
@@ -14978,16 +14978,16 @@
         <v>16</v>
       </c>
       <c r="F305" t="n">
-        <v>0.526</v>
+        <v>0.298</v>
       </c>
       <c r="G305" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H305" t="n">
-        <v>0.00264</v>
+        <v>6.95e-05</v>
       </c>
       <c r="I305" t="n">
-        <v>0.0141</v>
+        <v>0.00111</v>
       </c>
     </row>
     <row r="306">
@@ -15024,7 +15024,7 @@
         <v>0.0728</v>
       </c>
       <c r="I306" t="n">
-        <v>0.146</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="307">
@@ -15126,16 +15126,16 @@
         <v>4</v>
       </c>
       <c r="F309" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
       <c r="G309" t="n">
         <v>0.977</v>
       </c>
       <c r="H309" t="n">
-        <v>0.494</v>
+        <v>1</v>
       </c>
       <c r="I309" t="n">
-        <v>0.697</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
@@ -15200,16 +15200,16 @@
         <v>6</v>
       </c>
       <c r="F311" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.803</v>
       </c>
       <c r="G311" t="n">
         <v>0.922</v>
       </c>
       <c r="H311" t="n">
-        <v>0.00321</v>
+        <v>0.00202</v>
       </c>
       <c r="I311" t="n">
-        <v>0.0103</v>
+        <v>0.00645</v>
       </c>
     </row>
     <row r="312">
@@ -15240,13 +15240,13 @@
         <v>0.865</v>
       </c>
       <c r="G312" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="H312" t="n">
-        <v>0.0229</v>
+        <v>0.0404</v>
       </c>
       <c r="I312" t="n">
-        <v>0.0611</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="313">
@@ -15311,16 +15311,16 @@
         <v>9</v>
       </c>
       <c r="F314" t="n">
-        <v>0.773</v>
+        <v>0.761</v>
       </c>
       <c r="G314" t="n">
-        <v>0.846</v>
+        <v>0.825</v>
       </c>
       <c r="H314" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="I314" t="n">
-        <v>0.146</v>
+        <v>0.239</v>
       </c>
     </row>
     <row r="315">
@@ -15348,16 +15348,16 @@
         <v>10</v>
       </c>
       <c r="F315" t="n">
-        <v>0.918</v>
+        <v>0.853</v>
       </c>
       <c r="G315" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.876</v>
       </c>
       <c r="H315" t="n">
-        <v>0.523</v>
+        <v>0.616</v>
       </c>
       <c r="I315" t="n">
-        <v>0.697</v>
+        <v>0.897</v>
       </c>
     </row>
     <row r="316">
@@ -15385,13 +15385,13 @@
         <v>11</v>
       </c>
       <c r="F316" t="n">
-        <v>0.723</v>
+        <v>0.714</v>
       </c>
       <c r="G316" t="n">
-        <v>0.874</v>
+        <v>0.867</v>
       </c>
       <c r="H316" t="n">
-        <v>0.000795</v>
+        <v>0.000901</v>
       </c>
       <c r="I316" t="n">
         <v>0.00634</v>
@@ -15533,13 +15533,13 @@
         <v>15</v>
       </c>
       <c r="F320" t="n">
-        <v>0.694</v>
+        <v>0.647</v>
       </c>
       <c r="G320" t="n">
-        <v>0.857</v>
+        <v>0.822</v>
       </c>
       <c r="H320" t="n">
-        <v>0.00151</v>
+        <v>0.00148</v>
       </c>
       <c r="I320" t="n">
         <v>0.00634</v>
@@ -15570,16 +15570,16 @@
         <v>16</v>
       </c>
       <c r="F321" t="n">
-        <v>0.541</v>
+        <v>0.347</v>
       </c>
       <c r="G321" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.729</v>
       </c>
       <c r="H321" t="n">
-        <v>3.04e-05</v>
+        <v>3.83e-08</v>
       </c>
       <c r="I321" t="n">
-        <v>0.000486</v>
+        <v>6.13e-07</v>
       </c>
     </row>
     <row r="322">
@@ -15616,7 +15616,7 @@
         <v>0.141</v>
       </c>
       <c r="I322" t="n">
-        <v>0.75</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="323">
@@ -15792,16 +15792,16 @@
         <v>6</v>
       </c>
       <c r="F327" t="n">
-        <v>0.793</v>
+        <v>0.787</v>
       </c>
       <c r="G327" t="n">
         <v>0.853</v>
       </c>
       <c r="H327" t="n">
-        <v>0.226</v>
+        <v>0.176</v>
       </c>
       <c r="I327" t="n">
-        <v>0.903</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="328">
@@ -15903,16 +15903,16 @@
         <v>9</v>
       </c>
       <c r="F330" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="G330" t="n">
-        <v>0.78</v>
+        <v>0.753</v>
       </c>
       <c r="H330" t="n">
-        <v>0.0683</v>
+        <v>0.099</v>
       </c>
       <c r="I330" t="n">
-        <v>0.546</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="331">
@@ -15940,16 +15940,16 @@
         <v>10</v>
       </c>
       <c r="F331" t="n">
-        <v>0.833</v>
+        <v>0.787</v>
       </c>
       <c r="G331" t="n">
-        <v>0.927</v>
+        <v>0.907</v>
       </c>
       <c r="H331" t="n">
-        <v>0.0199</v>
+        <v>0.006</v>
       </c>
       <c r="I331" t="n">
-        <v>0.318</v>
+        <v>0.0959</v>
       </c>
     </row>
     <row r="332">
@@ -15977,13 +15977,13 @@
         <v>11</v>
       </c>
       <c r="F332" t="n">
-        <v>0.773</v>
+        <v>0.767</v>
       </c>
       <c r="G332" t="n">
-        <v>0.787</v>
+        <v>0.78</v>
       </c>
       <c r="H332" t="n">
-        <v>0.889</v>
+        <v>0.89</v>
       </c>
       <c r="I332" t="n">
         <v>1</v>
@@ -16125,13 +16125,13 @@
         <v>15</v>
       </c>
       <c r="F336" t="n">
-        <v>0.52</v>
+        <v>0.507</v>
       </c>
       <c r="G336" t="n">
         <v>0.5</v>
       </c>
       <c r="H336" t="n">
-        <v>0.8169999999999999</v>
+        <v>1</v>
       </c>
       <c r="I336" t="n">
         <v>1</v>
@@ -16162,13 +16162,13 @@
         <v>16</v>
       </c>
       <c r="F337" t="n">
-        <v>0.46</v>
+        <v>0.393</v>
       </c>
       <c r="G337" t="n">
-        <v>0.407</v>
+        <v>0.34</v>
       </c>
       <c r="H337" t="n">
-        <v>0.415</v>
+        <v>0.402</v>
       </c>
       <c r="I337" t="n">
         <v>1</v>
@@ -16384,7 +16384,7 @@
         <v>6</v>
       </c>
       <c r="F343" t="n">
-        <v>0.877</v>
+        <v>0.875</v>
       </c>
       <c r="G343" t="n">
         <v>0.898</v>
@@ -16495,13 +16495,13 @@
         <v>9</v>
       </c>
       <c r="F346" t="n">
-        <v>0.964</v>
+        <v>0.963</v>
       </c>
       <c r="G346" t="n">
-        <v>0.919</v>
+        <v>0.916</v>
       </c>
       <c r="H346" t="n">
-        <v>0.239</v>
+        <v>0.238</v>
       </c>
       <c r="I346" t="n">
         <v>1</v>
@@ -16532,7 +16532,7 @@
         <v>10</v>
       </c>
       <c r="F347" t="n">
-        <v>0.983</v>
+        <v>0.98</v>
       </c>
       <c r="G347" t="n">
         <v>0.986</v>
@@ -16569,10 +16569,10 @@
         <v>11</v>
       </c>
       <c r="F348" t="n">
-        <v>0.863</v>
+        <v>0.861</v>
       </c>
       <c r="G348" t="n">
-        <v>0.875</v>
+        <v>0.873</v>
       </c>
       <c r="H348" t="n">
         <v>1</v>
@@ -16717,13 +16717,13 @@
         <v>15</v>
       </c>
       <c r="F352" t="n">
-        <v>0.479</v>
+        <v>0.471</v>
       </c>
       <c r="G352" t="n">
         <v>0.47</v>
       </c>
       <c r="H352" t="n">
-        <v>0.901</v>
+        <v>1</v>
       </c>
       <c r="I352" t="n">
         <v>1</v>
@@ -16754,13 +16754,13 @@
         <v>16</v>
       </c>
       <c r="F353" t="n">
-        <v>0.389</v>
+        <v>0.327</v>
       </c>
       <c r="G353" t="n">
-        <v>0.357</v>
+        <v>0.294</v>
       </c>
       <c r="H353" t="n">
-        <v>0.677</v>
+        <v>0.649</v>
       </c>
       <c r="I353" t="n">
         <v>1</v>
@@ -16800,7 +16800,7 @@
         <v>0.0853</v>
       </c>
       <c r="I354" t="n">
-        <v>0.455</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="355">
@@ -16976,16 +16976,16 @@
         <v>6</v>
       </c>
       <c r="F359" t="n">
-        <v>0.772</v>
+        <v>0.761</v>
       </c>
       <c r="G359" t="n">
         <v>0.859</v>
       </c>
       <c r="H359" t="n">
-        <v>0.183</v>
+        <v>0.132</v>
       </c>
       <c r="I359" t="n">
-        <v>0.733</v>
+        <v>0.423</v>
       </c>
     </row>
     <row r="360">
@@ -17087,16 +17087,16 @@
         <v>9</v>
       </c>
       <c r="F362" t="n">
-        <v>0.643</v>
+        <v>0.619</v>
       </c>
       <c r="G362" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.778</v>
       </c>
       <c r="H362" t="n">
-        <v>0.00453</v>
+        <v>0.008880000000000001</v>
       </c>
       <c r="I362" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="363">
@@ -17124,16 +17124,16 @@
         <v>10</v>
       </c>
       <c r="F363" t="n">
-        <v>0.704</v>
+        <v>0.617</v>
       </c>
       <c r="G363" t="n">
-        <v>0.877</v>
+        <v>0.84</v>
       </c>
       <c r="H363" t="n">
-        <v>0.0114</v>
+        <v>0.00245</v>
       </c>
       <c r="I363" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.0392</v>
       </c>
     </row>
     <row r="364">
@@ -17161,10 +17161,10 @@
         <v>11</v>
       </c>
       <c r="F364" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="G364" t="n">
         <v>0.75</v>
-      </c>
-      <c r="G364" t="n">
-        <v>0.761</v>
       </c>
       <c r="H364" t="n">
         <v>1</v>
@@ -17309,16 +17309,16 @@
         <v>15</v>
       </c>
       <c r="F368" t="n">
-        <v>0.866</v>
+        <v>0.836</v>
       </c>
       <c r="G368" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="H368" t="n">
-        <v>0.242</v>
+        <v>0.0977</v>
       </c>
       <c r="I368" t="n">
-        <v>0.776</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="369">
@@ -17346,13 +17346,13 @@
         <v>16</v>
       </c>
       <c r="F369" t="n">
-        <v>0.737</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="G369" t="n">
-        <v>0.702</v>
+        <v>0.526</v>
       </c>
       <c r="H369" t="n">
-        <v>0.835</v>
+        <v>0.851</v>
       </c>
       <c r="I369" t="n">
         <v>1</v>
@@ -17392,7 +17392,7 @@
         <v>0.0842</v>
       </c>
       <c r="I370" t="n">
-        <v>0.449</v>
+        <v>0.421</v>
       </c>
     </row>
     <row r="371">
@@ -17540,7 +17540,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I374" t="n">
-        <v>1</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="375">
@@ -17568,16 +17568,16 @@
         <v>6</v>
       </c>
       <c r="F375" t="n">
-        <v>0.821</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G375" t="n">
         <v>0.878</v>
       </c>
       <c r="H375" t="n">
-        <v>0.14</v>
+        <v>0.105</v>
       </c>
       <c r="I375" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.421</v>
       </c>
     </row>
     <row r="376">
@@ -17614,7 +17614,7 @@
         <v>0.634</v>
       </c>
       <c r="I376" t="n">
-        <v>1</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="377">
@@ -17679,16 +17679,16 @@
         <v>9</v>
       </c>
       <c r="F378" t="n">
-        <v>0.771</v>
+        <v>0.754</v>
       </c>
       <c r="G378" t="n">
-        <v>0.861</v>
+        <v>0.841</v>
       </c>
       <c r="H378" t="n">
-        <v>0.0191</v>
+        <v>0.0236</v>
       </c>
       <c r="I378" t="n">
-        <v>0.152</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="379">
@@ -17716,16 +17716,16 @@
         <v>10</v>
       </c>
       <c r="F379" t="n">
-        <v>0.82</v>
+        <v>0.758</v>
       </c>
       <c r="G379" t="n">
-        <v>0.928</v>
+        <v>0.907</v>
       </c>
       <c r="H379" t="n">
-        <v>0.00694</v>
+        <v>0.00107</v>
       </c>
       <c r="I379" t="n">
-        <v>0.111</v>
+        <v>0.0172</v>
       </c>
     </row>
     <row r="380">
@@ -17753,13 +17753,13 @@
         <v>11</v>
       </c>
       <c r="F380" t="n">
-        <v>0.802</v>
+        <v>0.795</v>
       </c>
       <c r="G380" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H380" t="n">
-        <v>0.891</v>
+        <v>0.892</v>
       </c>
       <c r="I380" t="n">
         <v>1</v>
@@ -17836,7 +17836,7 @@
         <v>0.739</v>
       </c>
       <c r="I382" t="n">
-        <v>1</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="383">
@@ -17873,7 +17873,7 @@
         <v>0.5649999999999999</v>
       </c>
       <c r="I383" t="n">
-        <v>1</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="384">
@@ -17901,16 +17901,16 @@
         <v>15</v>
       </c>
       <c r="F384" t="n">
-        <v>0.617</v>
+        <v>0.602</v>
       </c>
       <c r="G384" t="n">
         <v>0.627</v>
       </c>
       <c r="H384" t="n">
-        <v>0.917</v>
+        <v>0.676</v>
       </c>
       <c r="I384" t="n">
-        <v>1</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="385">
@@ -17938,16 +17938,16 @@
         <v>16</v>
       </c>
       <c r="F385" t="n">
-        <v>0.509</v>
+        <v>0.413</v>
       </c>
       <c r="G385" t="n">
-        <v>0.473</v>
+        <v>0.377</v>
       </c>
       <c r="H385" t="n">
-        <v>0.584</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="I385" t="n">
-        <v>1</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="386">
@@ -17984,7 +17984,7 @@
         <v>0.188</v>
       </c>
       <c r="I386" t="n">
-        <v>0.903</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="387">
@@ -18021,7 +18021,7 @@
         <v>0.785</v>
       </c>
       <c r="I387" t="n">
-        <v>1</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="388">
@@ -18058,7 +18058,7 @@
         <v>0.825</v>
       </c>
       <c r="I388" t="n">
-        <v>1</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="389">
@@ -18160,16 +18160,16 @@
         <v>6</v>
       </c>
       <c r="F391" t="n">
-        <v>0.793</v>
+        <v>0.787</v>
       </c>
       <c r="G391" t="n">
-        <v>0.853</v>
+        <v>0.847</v>
       </c>
       <c r="H391" t="n">
-        <v>0.226</v>
+        <v>0.232</v>
       </c>
       <c r="I391" t="n">
-        <v>0.903</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="392">
@@ -18206,7 +18206,7 @@
         <v>0.625</v>
       </c>
       <c r="I392" t="n">
-        <v>1</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="393">
@@ -18243,7 +18243,7 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="I393" t="n">
-        <v>1</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="394">
@@ -18271,16 +18271,16 @@
         <v>9</v>
       </c>
       <c r="F394" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="G394" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="H394" t="n">
-        <v>0.017</v>
+        <v>0.0285</v>
       </c>
       <c r="I394" t="n">
-        <v>0.272</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="395">
@@ -18308,16 +18308,16 @@
         <v>10</v>
       </c>
       <c r="F395" t="n">
-        <v>0.833</v>
+        <v>0.787</v>
       </c>
       <c r="G395" t="n">
-        <v>0.907</v>
+        <v>0.887</v>
       </c>
       <c r="H395" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.028</v>
       </c>
       <c r="I395" t="n">
-        <v>0.68</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="396">
@@ -18345,16 +18345,16 @@
         <v>11</v>
       </c>
       <c r="F396" t="n">
-        <v>0.773</v>
+        <v>0.767</v>
       </c>
       <c r="G396" t="n">
-        <v>0.76</v>
+        <v>0.747</v>
       </c>
       <c r="H396" t="n">
-        <v>0.892</v>
+        <v>0.788</v>
       </c>
       <c r="I396" t="n">
-        <v>1</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="397">
@@ -18391,7 +18391,7 @@
         <v>0.518</v>
       </c>
       <c r="I397" t="n">
-        <v>1</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="398">
@@ -18428,7 +18428,7 @@
         <v>0.541</v>
       </c>
       <c r="I398" t="n">
-        <v>1</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="399">
@@ -18465,7 +18465,7 @@
         <v>0.5659999999999999</v>
       </c>
       <c r="I399" t="n">
-        <v>1</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="400">
@@ -18493,16 +18493,16 @@
         <v>15</v>
       </c>
       <c r="F400" t="n">
-        <v>0.52</v>
+        <v>0.507</v>
       </c>
       <c r="G400" t="n">
-        <v>0.467</v>
+        <v>0.453</v>
       </c>
       <c r="H400" t="n">
         <v>0.419</v>
       </c>
       <c r="I400" t="n">
-        <v>1</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="401">
@@ -18530,16 +18530,16 @@
         <v>16</v>
       </c>
       <c r="F401" t="n">
-        <v>0.46</v>
+        <v>0.393</v>
       </c>
       <c r="G401" t="n">
-        <v>0.393</v>
+        <v>0.347</v>
       </c>
       <c r="H401" t="n">
-        <v>0.293</v>
+        <v>0.473</v>
       </c>
       <c r="I401" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="402">
@@ -18752,10 +18752,10 @@
         <v>6</v>
       </c>
       <c r="F407" t="n">
-        <v>0.877</v>
+        <v>0.875</v>
       </c>
       <c r="G407" t="n">
-        <v>0.865</v>
+        <v>0.863</v>
       </c>
       <c r="H407" t="n">
         <v>1</v>
@@ -18863,10 +18863,10 @@
         <v>9</v>
       </c>
       <c r="F410" t="n">
-        <v>0.964</v>
+        <v>0.963</v>
       </c>
       <c r="G410" t="n">
-        <v>0.929</v>
+        <v>0.927</v>
       </c>
       <c r="H410" t="n">
         <v>0.359</v>
@@ -18900,13 +18900,13 @@
         <v>10</v>
       </c>
       <c r="F411" t="n">
-        <v>0.983</v>
+        <v>0.98</v>
       </c>
       <c r="G411" t="n">
-        <v>0.959</v>
+        <v>0.957</v>
       </c>
       <c r="H411" t="n">
-        <v>0.629</v>
+        <v>0.638</v>
       </c>
       <c r="I411" t="n">
         <v>1</v>
@@ -18937,13 +18937,13 @@
         <v>11</v>
       </c>
       <c r="F412" t="n">
-        <v>0.863</v>
+        <v>0.861</v>
       </c>
       <c r="G412" t="n">
-        <v>0.85</v>
+        <v>0.846</v>
       </c>
       <c r="H412" t="n">
-        <v>1</v>
+        <v>0.825</v>
       </c>
       <c r="I412" t="n">
         <v>1</v>
@@ -19085,13 +19085,13 @@
         <v>15</v>
       </c>
       <c r="F416" t="n">
-        <v>0.479</v>
+        <v>0.471</v>
       </c>
       <c r="G416" t="n">
-        <v>0.453</v>
+        <v>0.444</v>
       </c>
       <c r="H416" t="n">
-        <v>0.708</v>
+        <v>0.706</v>
       </c>
       <c r="I416" t="n">
         <v>1</v>
@@ -19122,13 +19122,13 @@
         <v>16</v>
       </c>
       <c r="F417" t="n">
-        <v>0.389</v>
+        <v>0.327</v>
       </c>
       <c r="G417" t="n">
-        <v>0.363</v>
+        <v>0.325</v>
       </c>
       <c r="H417" t="n">
-        <v>0.6860000000000001</v>
+        <v>1</v>
       </c>
       <c r="I417" t="n">
         <v>1</v>
@@ -19279,7 +19279,7 @@
         <v>0.488</v>
       </c>
       <c r="I421" t="n">
-        <v>0.969</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="422">
@@ -19316,7 +19316,7 @@
         <v>0.506</v>
       </c>
       <c r="I422" t="n">
-        <v>0.969</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="423">
@@ -19344,16 +19344,16 @@
         <v>6</v>
       </c>
       <c r="F423" t="n">
-        <v>0.772</v>
+        <v>0.761</v>
       </c>
       <c r="G423" t="n">
-        <v>0.902</v>
+        <v>0.891</v>
       </c>
       <c r="H423" t="n">
-        <v>0.0269</v>
+        <v>0.0313</v>
       </c>
       <c r="I423" t="n">
-        <v>0.144</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="424">
@@ -19390,7 +19390,7 @@
         <v>0.387</v>
       </c>
       <c r="I424" t="n">
-        <v>0.969</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="425">
@@ -19455,16 +19455,16 @@
         <v>9</v>
       </c>
       <c r="F426" t="n">
-        <v>0.643</v>
+        <v>0.619</v>
       </c>
       <c r="G426" t="n">
-        <v>0.833</v>
+        <v>0.802</v>
       </c>
       <c r="H426" t="n">
-        <v>0.000901</v>
+        <v>0.00213</v>
       </c>
       <c r="I426" t="n">
-        <v>0.0144</v>
+        <v>0.0341</v>
       </c>
     </row>
     <row r="427">
@@ -19492,16 +19492,16 @@
         <v>10</v>
       </c>
       <c r="F427" t="n">
-        <v>0.704</v>
+        <v>0.617</v>
       </c>
       <c r="G427" t="n">
-        <v>0.864</v>
+        <v>0.827</v>
       </c>
       <c r="H427" t="n">
-        <v>0.0211</v>
+        <v>0.0047</v>
       </c>
       <c r="I427" t="n">
-        <v>0.144</v>
+        <v>0.0376</v>
       </c>
     </row>
     <row r="428">
@@ -19529,13 +19529,13 @@
         <v>11</v>
       </c>
       <c r="F428" t="n">
-        <v>0.75</v>
+        <v>0.739</v>
       </c>
       <c r="G428" t="n">
-        <v>0.739</v>
+        <v>0.717</v>
       </c>
       <c r="H428" t="n">
-        <v>1</v>
+        <v>0.869</v>
       </c>
       <c r="I428" t="n">
         <v>1</v>
@@ -19575,7 +19575,7 @@
         <v>0.545</v>
       </c>
       <c r="I429" t="n">
-        <v>0.969</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="430">
@@ -19677,16 +19677,16 @@
         <v>15</v>
       </c>
       <c r="F432" t="n">
-        <v>0.866</v>
+        <v>0.836</v>
       </c>
       <c r="G432" t="n">
-        <v>0.925</v>
+        <v>0.896</v>
       </c>
       <c r="H432" t="n">
-        <v>0.398</v>
+        <v>0.448</v>
       </c>
       <c r="I432" t="n">
-        <v>0.969</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="433">
@@ -19714,16 +19714,16 @@
         <v>16</v>
       </c>
       <c r="F433" t="n">
-        <v>0.737</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="G433" t="n">
-        <v>0.789</v>
+        <v>0.667</v>
       </c>
       <c r="H433" t="n">
-        <v>0.66</v>
+        <v>0.336</v>
       </c>
       <c r="I433" t="n">
-        <v>1</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="434">
@@ -19797,7 +19797,7 @@
         <v>0.779</v>
       </c>
       <c r="I435" t="n">
-        <v>0.979</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="436">
@@ -19834,7 +19834,7 @@
         <v>0.8159999999999999</v>
       </c>
       <c r="I436" t="n">
-        <v>0.979</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="437">
@@ -19871,7 +19871,7 @@
         <v>0.608</v>
       </c>
       <c r="I437" t="n">
-        <v>0.979</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="438">
@@ -19936,13 +19936,13 @@
         <v>6</v>
       </c>
       <c r="F439" t="n">
-        <v>0.821</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G439" t="n">
-        <v>0.883</v>
+        <v>0.877</v>
       </c>
       <c r="H439" t="n">
-        <v>0.103</v>
+        <v>0.108</v>
       </c>
       <c r="I439" t="n">
         <v>0.464</v>
@@ -19982,7 +19982,7 @@
         <v>0.518</v>
       </c>
       <c r="I440" t="n">
-        <v>0.979</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="441">
@@ -20019,7 +20019,7 @@
         <v>0.695</v>
       </c>
       <c r="I441" t="n">
-        <v>0.979</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="442">
@@ -20047,16 +20047,16 @@
         <v>9</v>
       </c>
       <c r="F442" t="n">
-        <v>0.771</v>
+        <v>0.754</v>
       </c>
       <c r="G442" t="n">
-        <v>0.879</v>
+        <v>0.86</v>
       </c>
       <c r="H442" t="n">
-        <v>0.00371</v>
+        <v>0.00518</v>
       </c>
       <c r="I442" t="n">
-        <v>0.0594</v>
+        <v>0.0415</v>
       </c>
     </row>
     <row r="443">
@@ -20084,16 +20084,16 @@
         <v>10</v>
       </c>
       <c r="F443" t="n">
-        <v>0.82</v>
+        <v>0.758</v>
       </c>
       <c r="G443" t="n">
-        <v>0.909</v>
+        <v>0.887</v>
       </c>
       <c r="H443" t="n">
-        <v>0.0377</v>
+        <v>0.00456</v>
       </c>
       <c r="I443" t="n">
-        <v>0.302</v>
+        <v>0.0415</v>
       </c>
     </row>
     <row r="444">
@@ -20121,16 +20121,16 @@
         <v>11</v>
       </c>
       <c r="F444" t="n">
-        <v>0.802</v>
+        <v>0.795</v>
       </c>
       <c r="G444" t="n">
-        <v>0.791</v>
+        <v>0.776</v>
       </c>
       <c r="H444" t="n">
-        <v>0.894</v>
+        <v>0.694</v>
       </c>
       <c r="I444" t="n">
-        <v>0.979</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="445">
@@ -20167,7 +20167,7 @@
         <v>0.405</v>
       </c>
       <c r="I445" t="n">
-        <v>0.979</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="446">
@@ -20204,7 +20204,7 @@
         <v>0.525</v>
       </c>
       <c r="I446" t="n">
-        <v>0.979</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="447">
@@ -20241,7 +20241,7 @@
         <v>0.666</v>
       </c>
       <c r="I447" t="n">
-        <v>0.979</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="448">
@@ -20269,13 +20269,13 @@
         <v>15</v>
       </c>
       <c r="F448" t="n">
-        <v>0.617</v>
+        <v>0.602</v>
       </c>
       <c r="G448" t="n">
-        <v>0.608</v>
+        <v>0.594</v>
       </c>
       <c r="H448" t="n">
-        <v>0.917</v>
+        <v>0.918</v>
       </c>
       <c r="I448" t="n">
         <v>0.979</v>
@@ -20306,16 +20306,16 @@
         <v>16</v>
       </c>
       <c r="F449" t="n">
-        <v>0.509</v>
+        <v>0.413</v>
       </c>
       <c r="G449" t="n">
-        <v>0.497</v>
+        <v>0.437</v>
       </c>
       <c r="H449" t="n">
-        <v>0.83</v>
+        <v>0.738</v>
       </c>
       <c r="I449" t="n">
-        <v>0.979</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="450">
@@ -20352,7 +20352,7 @@
         <v>0.188</v>
       </c>
       <c r="I450" t="n">
-        <v>0.634</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="451">
@@ -20528,16 +20528,16 @@
         <v>6</v>
       </c>
       <c r="F455" t="n">
-        <v>0.793</v>
+        <v>0.787</v>
       </c>
       <c r="G455" t="n">
-        <v>0.867</v>
+        <v>0.86</v>
       </c>
       <c r="H455" t="n">
-        <v>0.124</v>
+        <v>0.13</v>
       </c>
       <c r="I455" t="n">
-        <v>0.634</v>
+        <v>0.6909999999999999</v>
       </c>
     </row>
     <row r="456">
@@ -20639,16 +20639,16 @@
         <v>9</v>
       </c>
       <c r="F458" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="G458" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="H458" t="n">
-        <v>0.017</v>
+        <v>0.0285</v>
       </c>
       <c r="I458" t="n">
-        <v>0.272</v>
+        <v>0.456</v>
       </c>
     </row>
     <row r="459">
@@ -20676,16 +20676,16 @@
         <v>10</v>
       </c>
       <c r="F459" t="n">
-        <v>0.833</v>
+        <v>0.787</v>
       </c>
       <c r="G459" t="n">
-        <v>0.893</v>
+        <v>0.873</v>
       </c>
       <c r="H459" t="n">
-        <v>0.178</v>
+        <v>0.0644</v>
       </c>
       <c r="I459" t="n">
-        <v>0.634</v>
+        <v>0.515</v>
       </c>
     </row>
     <row r="460">
@@ -20713,13 +20713,13 @@
         <v>11</v>
       </c>
       <c r="F460" t="n">
-        <v>0.773</v>
+        <v>0.767</v>
       </c>
       <c r="G460" t="n">
-        <v>0.767</v>
+        <v>0.753</v>
       </c>
       <c r="H460" t="n">
-        <v>1</v>
+        <v>0.893</v>
       </c>
       <c r="I460" t="n">
         <v>1</v>
@@ -20861,13 +20861,13 @@
         <v>15</v>
       </c>
       <c r="F464" t="n">
-        <v>0.52</v>
+        <v>0.507</v>
       </c>
       <c r="G464" t="n">
-        <v>0.467</v>
+        <v>0.46</v>
       </c>
       <c r="H464" t="n">
-        <v>0.419</v>
+        <v>0.488</v>
       </c>
       <c r="I464" t="n">
         <v>0.907</v>
@@ -20898,16 +20898,16 @@
         <v>16</v>
       </c>
       <c r="F465" t="n">
-        <v>0.46</v>
+        <v>0.393</v>
       </c>
       <c r="G465" t="n">
-        <v>0.38</v>
+        <v>0.333</v>
       </c>
       <c r="H465" t="n">
-        <v>0.198</v>
+        <v>0.337</v>
       </c>
       <c r="I465" t="n">
-        <v>0.634</v>
+        <v>0.907</v>
       </c>
     </row>
     <row r="466">
@@ -21120,10 +21120,10 @@
         <v>6</v>
       </c>
       <c r="F471" t="n">
-        <v>0.877</v>
+        <v>0.875</v>
       </c>
       <c r="G471" t="n">
-        <v>0.9</v>
+        <v>0.899</v>
       </c>
       <c r="H471" t="n">
         <v>0.636</v>
@@ -21231,10 +21231,10 @@
         <v>9</v>
       </c>
       <c r="F474" t="n">
-        <v>0.964</v>
+        <v>0.963</v>
       </c>
       <c r="G474" t="n">
-        <v>0.929</v>
+        <v>0.927</v>
       </c>
       <c r="H474" t="n">
         <v>0.359</v>
@@ -21268,13 +21268,13 @@
         <v>10</v>
       </c>
       <c r="F475" t="n">
-        <v>0.983</v>
+        <v>0.98</v>
       </c>
       <c r="G475" t="n">
-        <v>0.945</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="H475" t="n">
-        <v>0.382</v>
+        <v>0.396</v>
       </c>
       <c r="I475" t="n">
         <v>1</v>
@@ -21305,10 +21305,10 @@
         <v>11</v>
       </c>
       <c r="F476" t="n">
-        <v>0.863</v>
+        <v>0.861</v>
       </c>
       <c r="G476" t="n">
-        <v>0.87</v>
+        <v>0.867</v>
       </c>
       <c r="H476" t="n">
         <v>1</v>
@@ -21453,13 +21453,13 @@
         <v>15</v>
       </c>
       <c r="F480" t="n">
-        <v>0.479</v>
+        <v>0.471</v>
       </c>
       <c r="G480" t="n">
-        <v>0.451</v>
+        <v>0.447</v>
       </c>
       <c r="H480" t="n">
-        <v>0.706</v>
+        <v>0.8</v>
       </c>
       <c r="I480" t="n">
         <v>1</v>
@@ -21490,13 +21490,13 @@
         <v>16</v>
       </c>
       <c r="F481" t="n">
-        <v>0.389</v>
+        <v>0.327</v>
       </c>
       <c r="G481" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="H481" t="n">
-        <v>0.584</v>
+        <v>0.882</v>
       </c>
       <c r="I481" t="n">
         <v>1</v>
@@ -21712,16 +21712,16 @@
         <v>6</v>
       </c>
       <c r="F487" t="n">
-        <v>0.772</v>
+        <v>0.761</v>
       </c>
       <c r="G487" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="H487" t="n">
-        <v>0.0789</v>
+        <v>0.0864</v>
       </c>
       <c r="I487" t="n">
-        <v>0.421</v>
+        <v>0.461</v>
       </c>
     </row>
     <row r="488">
@@ -21823,16 +21823,16 @@
         <v>9</v>
       </c>
       <c r="F490" t="n">
-        <v>0.643</v>
+        <v>0.619</v>
       </c>
       <c r="G490" t="n">
-        <v>0.833</v>
+        <v>0.802</v>
       </c>
       <c r="H490" t="n">
-        <v>0.000901</v>
+        <v>0.00213</v>
       </c>
       <c r="I490" t="n">
-        <v>0.0144</v>
+        <v>0.0341</v>
       </c>
     </row>
     <row r="491">
@@ -21860,16 +21860,16 @@
         <v>10</v>
       </c>
       <c r="F491" t="n">
-        <v>0.704</v>
+        <v>0.617</v>
       </c>
       <c r="G491" t="n">
-        <v>0.852</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H491" t="n">
-        <v>0.0367</v>
+        <v>0.00856</v>
       </c>
       <c r="I491" t="n">
-        <v>0.294</v>
+        <v>0.06850000000000001</v>
       </c>
     </row>
     <row r="492">
@@ -21897,13 +21897,13 @@
         <v>11</v>
       </c>
       <c r="F492" t="n">
-        <v>0.75</v>
+        <v>0.739</v>
       </c>
       <c r="G492" t="n">
-        <v>0.728</v>
+        <v>0.707</v>
       </c>
       <c r="H492" t="n">
-        <v>0.867</v>
+        <v>0.742</v>
       </c>
       <c r="I492" t="n">
         <v>1</v>
@@ -22045,13 +22045,13 @@
         <v>15</v>
       </c>
       <c r="F496" t="n">
-        <v>0.866</v>
+        <v>0.836</v>
       </c>
       <c r="G496" t="n">
-        <v>0.896</v>
+        <v>0.881</v>
       </c>
       <c r="H496" t="n">
-        <v>0.791</v>
+        <v>0.621</v>
       </c>
       <c r="I496" t="n">
         <v>1</v>
@@ -22082,13 +22082,13 @@
         <v>16</v>
       </c>
       <c r="F497" t="n">
-        <v>0.737</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="G497" t="n">
-        <v>0.737</v>
+        <v>0.614</v>
       </c>
       <c r="H497" t="n">
-        <v>1</v>
+        <v>0.704</v>
       </c>
       <c r="I497" t="n">
         <v>1</v>
@@ -22239,7 +22239,7 @@
         <v>0.616</v>
       </c>
       <c r="I501" t="n">
-        <v>0.986</v>
+        <v>1</v>
       </c>
     </row>
     <row r="502">
@@ -22276,7 +22276,7 @@
         <v>0.583</v>
       </c>
       <c r="I502" t="n">
-        <v>0.986</v>
+        <v>1</v>
       </c>
     </row>
     <row r="503">
@@ -22304,16 +22304,16 @@
         <v>6</v>
       </c>
       <c r="F503" t="n">
-        <v>0.821</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G503" t="n">
-        <v>0.89</v>
+        <v>0.884</v>
       </c>
       <c r="H503" t="n">
-        <v>0.0701</v>
+        <v>0.0743</v>
       </c>
       <c r="I503" t="n">
-        <v>0.374</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="504">
@@ -22350,7 +22350,7 @@
         <v>0.416</v>
       </c>
       <c r="I504" t="n">
-        <v>0.986</v>
+        <v>1</v>
       </c>
     </row>
     <row r="505">
@@ -22415,16 +22415,16 @@
         <v>9</v>
       </c>
       <c r="F506" t="n">
-        <v>0.771</v>
+        <v>0.754</v>
       </c>
       <c r="G506" t="n">
-        <v>0.879</v>
+        <v>0.86</v>
       </c>
       <c r="H506" t="n">
-        <v>0.00371</v>
+        <v>0.00518</v>
       </c>
       <c r="I506" t="n">
-        <v>0.0594</v>
+        <v>0.0829</v>
       </c>
     </row>
     <row r="507">
@@ -22452,16 +22452,16 @@
         <v>10</v>
       </c>
       <c r="F507" t="n">
-        <v>0.82</v>
+        <v>0.758</v>
       </c>
       <c r="G507" t="n">
-        <v>0.896</v>
+        <v>0.874</v>
       </c>
       <c r="H507" t="n">
-        <v>0.0658</v>
+        <v>0.013</v>
       </c>
       <c r="I507" t="n">
-        <v>0.374</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="508">
@@ -22489,13 +22489,13 @@
         <v>11</v>
       </c>
       <c r="F508" t="n">
-        <v>0.802</v>
+        <v>0.795</v>
       </c>
       <c r="G508" t="n">
-        <v>0.793</v>
+        <v>0.778</v>
       </c>
       <c r="H508" t="n">
-        <v>0.893</v>
+        <v>0.791</v>
       </c>
       <c r="I508" t="n">
         <v>1</v>
@@ -22535,7 +22535,7 @@
         <v>0.508</v>
       </c>
       <c r="I509" t="n">
-        <v>0.986</v>
+        <v>1</v>
       </c>
     </row>
     <row r="510">
@@ -22609,7 +22609,7 @@
         <v>0.384</v>
       </c>
       <c r="I511" t="n">
-        <v>0.986</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512">
@@ -22637,13 +22637,13 @@
         <v>15</v>
       </c>
       <c r="F512" t="n">
-        <v>0.617</v>
+        <v>0.602</v>
       </c>
       <c r="G512" t="n">
-        <v>0.6</v>
+        <v>0.593</v>
       </c>
       <c r="H512" t="n">
-        <v>0.756</v>
+        <v>0.917</v>
       </c>
       <c r="I512" t="n">
         <v>1</v>
@@ -22674,16 +22674,16 @@
         <v>16</v>
       </c>
       <c r="F513" t="n">
-        <v>0.509</v>
+        <v>0.413</v>
       </c>
       <c r="G513" t="n">
-        <v>0.475</v>
+        <v>0.412</v>
       </c>
       <c r="H513" t="n">
-        <v>0.588</v>
+        <v>1</v>
       </c>
       <c r="I513" t="n">
-        <v>0.986</v>
+        <v>1</v>
       </c>
     </row>
     <row r="514">
@@ -22720,7 +22720,7 @@
         <v>0.245</v>
       </c>
       <c r="I514" t="n">
-        <v>0.654</v>
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="515">
@@ -22896,16 +22896,16 @@
         <v>6</v>
       </c>
       <c r="F519" t="n">
-        <v>0.793</v>
+        <v>0.787</v>
       </c>
       <c r="G519" t="n">
-        <v>0.847</v>
+        <v>0.84</v>
       </c>
       <c r="H519" t="n">
-        <v>0.293</v>
+        <v>0.3</v>
       </c>
       <c r="I519" t="n">
-        <v>0.669</v>
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="520">
@@ -23007,16 +23007,16 @@
         <v>9</v>
       </c>
       <c r="F522" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="G522" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="H522" t="n">
-        <v>0.00292</v>
+        <v>0.00906</v>
       </c>
       <c r="I522" t="n">
-        <v>0.0467</v>
+        <v>0.0838</v>
       </c>
     </row>
     <row r="523">
@@ -23044,16 +23044,16 @@
         <v>10</v>
       </c>
       <c r="F523" t="n">
-        <v>0.833</v>
+        <v>0.787</v>
       </c>
       <c r="G523" t="n">
-        <v>0.907</v>
+        <v>0.9</v>
       </c>
       <c r="H523" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0105</v>
       </c>
       <c r="I523" t="n">
-        <v>0.34</v>
+        <v>0.0838</v>
       </c>
     </row>
     <row r="524">
@@ -23081,16 +23081,16 @@
         <v>11</v>
       </c>
       <c r="F524" t="n">
-        <v>0.773</v>
+        <v>0.767</v>
       </c>
       <c r="G524" t="n">
-        <v>0.74</v>
+        <v>0.727</v>
       </c>
       <c r="H524" t="n">
-        <v>0.591</v>
+        <v>0.507</v>
       </c>
       <c r="I524" t="n">
-        <v>1</v>
+        <v>0.901</v>
       </c>
     </row>
     <row r="525">
@@ -23201,7 +23201,7 @@
         <v>0.0307</v>
       </c>
       <c r="I527" t="n">
-        <v>0.178</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="528">
@@ -23229,16 +23229,16 @@
         <v>15</v>
       </c>
       <c r="F528" t="n">
-        <v>0.52</v>
+        <v>0.507</v>
       </c>
       <c r="G528" t="n">
         <v>0.44</v>
       </c>
       <c r="H528" t="n">
-        <v>0.204</v>
+        <v>0.298</v>
       </c>
       <c r="I528" t="n">
-        <v>0.651</v>
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="529">
@@ -23266,16 +23266,16 @@
         <v>16</v>
       </c>
       <c r="F529" t="n">
-        <v>0.46</v>
+        <v>0.393</v>
       </c>
       <c r="G529" t="n">
-        <v>0.333</v>
+        <v>0.267</v>
       </c>
       <c r="H529" t="n">
-        <v>0.0334</v>
+        <v>0.0268</v>
       </c>
       <c r="I529" t="n">
-        <v>0.178</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="530">
@@ -23488,10 +23488,10 @@
         <v>6</v>
       </c>
       <c r="F535" t="n">
-        <v>0.877</v>
+        <v>0.875</v>
       </c>
       <c r="G535" t="n">
-        <v>0.879</v>
+        <v>0.878</v>
       </c>
       <c r="H535" t="n">
         <v>1</v>
@@ -23599,13 +23599,13 @@
         <v>9</v>
       </c>
       <c r="F538" t="n">
-        <v>0.964</v>
+        <v>0.963</v>
       </c>
       <c r="G538" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.929</v>
       </c>
       <c r="H538" t="n">
-        <v>0.365</v>
+        <v>0.363</v>
       </c>
       <c r="I538" t="n">
         <v>1</v>
@@ -23636,10 +23636,10 @@
         <v>10</v>
       </c>
       <c r="F539" t="n">
-        <v>0.983</v>
+        <v>0.98</v>
       </c>
       <c r="G539" t="n">
-        <v>0.972</v>
+        <v>0.971</v>
       </c>
       <c r="H539" t="n">
         <v>1</v>
@@ -23673,13 +23673,13 @@
         <v>11</v>
       </c>
       <c r="F540" t="n">
-        <v>0.863</v>
+        <v>0.861</v>
       </c>
       <c r="G540" t="n">
-        <v>0.835</v>
+        <v>0.831</v>
       </c>
       <c r="H540" t="n">
-        <v>0.664</v>
+        <v>0.661</v>
       </c>
       <c r="I540" t="n">
         <v>1</v>
@@ -23821,13 +23821,13 @@
         <v>15</v>
       </c>
       <c r="F544" t="n">
-        <v>0.479</v>
+        <v>0.471</v>
       </c>
       <c r="G544" t="n">
         <v>0.44</v>
       </c>
       <c r="H544" t="n">
-        <v>0.536</v>
+        <v>0.708</v>
       </c>
       <c r="I544" t="n">
         <v>1</v>
@@ -23858,13 +23858,13 @@
         <v>16</v>
       </c>
       <c r="F545" t="n">
-        <v>0.389</v>
+        <v>0.327</v>
       </c>
       <c r="G545" t="n">
-        <v>0.331</v>
+        <v>0.274</v>
       </c>
       <c r="H545" t="n">
-        <v>0.413</v>
+        <v>0.455</v>
       </c>
       <c r="I545" t="n">
         <v>1</v>
@@ -23904,7 +23904,7 @@
         <v>0.125</v>
       </c>
       <c r="I546" t="n">
-        <v>0.5</v>
+        <v>0.529</v>
       </c>
     </row>
     <row r="547">
@@ -23941,7 +23941,7 @@
         <v>0.491</v>
       </c>
       <c r="I547" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="548">
@@ -24015,7 +24015,7 @@
         <v>0.488</v>
       </c>
       <c r="I549" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="550">
@@ -24052,7 +24052,7 @@
         <v>0.62</v>
       </c>
       <c r="I550" t="n">
-        <v>0.982</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="551">
@@ -24080,16 +24080,16 @@
         <v>6</v>
       </c>
       <c r="F551" t="n">
-        <v>0.772</v>
+        <v>0.761</v>
       </c>
       <c r="G551" t="n">
-        <v>0.87</v>
+        <v>0.859</v>
       </c>
       <c r="H551" t="n">
-        <v>0.123</v>
+        <v>0.132</v>
       </c>
       <c r="I551" t="n">
-        <v>0.5</v>
+        <v>0.529</v>
       </c>
     </row>
     <row r="552">
@@ -24126,7 +24126,7 @@
         <v>0.675</v>
       </c>
       <c r="I552" t="n">
-        <v>0.982</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="553">
@@ -24191,16 +24191,16 @@
         <v>9</v>
       </c>
       <c r="F554" t="n">
-        <v>0.643</v>
+        <v>0.619</v>
       </c>
       <c r="G554" t="n">
-        <v>0.865</v>
+        <v>0.825</v>
       </c>
       <c r="H554" t="n">
-        <v>6.389999999999999e-05</v>
+        <v>0.000395</v>
       </c>
       <c r="I554" t="n">
-        <v>0.00102</v>
+        <v>0.00632</v>
       </c>
     </row>
     <row r="555">
@@ -24228,16 +24228,16 @@
         <v>10</v>
       </c>
       <c r="F555" t="n">
-        <v>0.704</v>
+        <v>0.617</v>
       </c>
       <c r="G555" t="n">
-        <v>0.852</v>
+        <v>0.84</v>
       </c>
       <c r="H555" t="n">
-        <v>0.0367</v>
+        <v>0.00245</v>
       </c>
       <c r="I555" t="n">
-        <v>0.294</v>
+        <v>0.0196</v>
       </c>
     </row>
     <row r="556">
@@ -24265,16 +24265,16 @@
         <v>11</v>
       </c>
       <c r="F556" t="n">
-        <v>0.75</v>
+        <v>0.739</v>
       </c>
       <c r="G556" t="n">
-        <v>0.717</v>
+        <v>0.696</v>
       </c>
       <c r="H556" t="n">
-        <v>0.739</v>
+        <v>0.624</v>
       </c>
       <c r="I556" t="n">
-        <v>0.985</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="557">
@@ -24311,7 +24311,7 @@
         <v>0.415</v>
       </c>
       <c r="I557" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="558">
@@ -24385,7 +24385,7 @@
         <v>0.529</v>
       </c>
       <c r="I559" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="560">
@@ -24413,16 +24413,16 @@
         <v>15</v>
       </c>
       <c r="F560" t="n">
-        <v>0.866</v>
+        <v>0.836</v>
       </c>
       <c r="G560" t="n">
         <v>0.925</v>
       </c>
       <c r="H560" t="n">
-        <v>0.398</v>
+        <v>0.182</v>
       </c>
       <c r="I560" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.581</v>
       </c>
     </row>
     <row r="561">
@@ -24450,10 +24450,10 @@
         <v>16</v>
       </c>
       <c r="F561" t="n">
-        <v>0.737</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="G561" t="n">
-        <v>0.737</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H561" t="n">
         <v>1</v>
@@ -24496,7 +24496,7 @@
         <v>0.156</v>
       </c>
       <c r="I562" t="n">
-        <v>0.589</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="563">
@@ -24533,7 +24533,7 @@
         <v>0.796</v>
       </c>
       <c r="I563" t="n">
-        <v>0.882</v>
+        <v>0.918</v>
       </c>
     </row>
     <row r="564">
@@ -24570,7 +24570,7 @@
         <v>0.827</v>
       </c>
       <c r="I564" t="n">
-        <v>0.882</v>
+        <v>0.918</v>
       </c>
     </row>
     <row r="565">
@@ -24607,7 +24607,7 @@
         <v>0.608</v>
       </c>
       <c r="I565" t="n">
-        <v>0.878</v>
+        <v>0.918</v>
       </c>
     </row>
     <row r="566">
@@ -24644,7 +24644,7 @@
         <v>0.889</v>
       </c>
       <c r="I566" t="n">
-        <v>0.889</v>
+        <v>0.918</v>
       </c>
     </row>
     <row r="567">
@@ -24672,16 +24672,16 @@
         <v>6</v>
       </c>
       <c r="F567" t="n">
-        <v>0.821</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G567" t="n">
-        <v>0.874</v>
+        <v>0.868</v>
       </c>
       <c r="H567" t="n">
-        <v>0.184</v>
+        <v>0.19</v>
       </c>
       <c r="I567" t="n">
-        <v>0.589</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="568">
@@ -24718,7 +24718,7 @@
         <v>0.52</v>
       </c>
       <c r="I568" t="n">
-        <v>0.878</v>
+        <v>0.918</v>
       </c>
     </row>
     <row r="569">
@@ -24755,7 +24755,7 @@
         <v>0.695</v>
       </c>
       <c r="I569" t="n">
-        <v>0.878</v>
+        <v>0.918</v>
       </c>
     </row>
     <row r="570">
@@ -24783,16 +24783,16 @@
         <v>9</v>
       </c>
       <c r="F570" t="n">
-        <v>0.771</v>
+        <v>0.754</v>
       </c>
       <c r="G570" t="n">
-        <v>0.897</v>
+        <v>0.874</v>
       </c>
       <c r="H570" t="n">
-        <v>0.000316</v>
+        <v>0.00129</v>
       </c>
       <c r="I570" t="n">
-        <v>0.00505</v>
+        <v>0.0109</v>
       </c>
     </row>
     <row r="571">
@@ -24820,16 +24820,16 @@
         <v>10</v>
       </c>
       <c r="F571" t="n">
-        <v>0.82</v>
+        <v>0.758</v>
       </c>
       <c r="G571" t="n">
-        <v>0.908</v>
+        <v>0.901</v>
       </c>
       <c r="H571" t="n">
-        <v>0.0379</v>
+        <v>0.00136</v>
       </c>
       <c r="I571" t="n">
-        <v>0.235</v>
+        <v>0.0109</v>
       </c>
     </row>
     <row r="572">
@@ -24857,16 +24857,16 @@
         <v>11</v>
       </c>
       <c r="F572" t="n">
-        <v>0.802</v>
+        <v>0.795</v>
       </c>
       <c r="G572" t="n">
-        <v>0.772</v>
+        <v>0.757</v>
       </c>
       <c r="H572" t="n">
-        <v>0.512</v>
+        <v>0.436</v>
       </c>
       <c r="I572" t="n">
-        <v>0.878</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="573">
@@ -24903,7 +24903,7 @@
         <v>0.313</v>
       </c>
       <c r="I573" t="n">
-        <v>0.769</v>
+        <v>0.834</v>
       </c>
     </row>
     <row r="574">
@@ -24940,7 +24940,7 @@
         <v>0.714</v>
       </c>
       <c r="I574" t="n">
-        <v>0.878</v>
+        <v>0.918</v>
       </c>
     </row>
     <row r="575">
@@ -25005,16 +25005,16 @@
         <v>15</v>
       </c>
       <c r="F576" t="n">
-        <v>0.617</v>
+        <v>0.602</v>
       </c>
       <c r="G576" t="n">
         <v>0.596</v>
       </c>
       <c r="H576" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.918</v>
       </c>
       <c r="I576" t="n">
-        <v>0.878</v>
+        <v>0.918</v>
       </c>
     </row>
     <row r="577">
@@ -25042,16 +25042,16 @@
         <v>16</v>
       </c>
       <c r="F577" t="n">
-        <v>0.509</v>
+        <v>0.413</v>
       </c>
       <c r="G577" t="n">
-        <v>0.457</v>
+        <v>0.368</v>
       </c>
       <c r="H577" t="n">
-        <v>0.336</v>
+        <v>0.429</v>
       </c>
       <c r="I577" t="n">
-        <v>0.769</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="578">
@@ -25088,7 +25088,7 @@
         <v>0.312</v>
       </c>
       <c r="I578" t="n">
-        <v>0.999</v>
+        <v>0.833</v>
       </c>
     </row>
     <row r="579">
@@ -25264,16 +25264,16 @@
         <v>6</v>
       </c>
       <c r="F583" t="n">
-        <v>0.793</v>
+        <v>0.787</v>
       </c>
       <c r="G583" t="n">
         <v>0.853</v>
       </c>
       <c r="H583" t="n">
-        <v>0.226</v>
+        <v>0.176</v>
       </c>
       <c r="I583" t="n">
-        <v>0.903</v>
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="584">
@@ -25304,10 +25304,10 @@
         <v>0.84</v>
       </c>
       <c r="G584" t="n">
-        <v>0.867</v>
+        <v>0.86</v>
       </c>
       <c r="H584" t="n">
-        <v>0.625</v>
+        <v>0.747</v>
       </c>
       <c r="I584" t="n">
         <v>1</v>
@@ -25375,13 +25375,13 @@
         <v>9</v>
       </c>
       <c r="F586" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="G586" t="n">
-        <v>0.713</v>
+        <v>0.7</v>
       </c>
       <c r="H586" t="n">
-        <v>0.616</v>
+        <v>0.536</v>
       </c>
       <c r="I586" t="n">
         <v>1</v>
@@ -25412,16 +25412,16 @@
         <v>10</v>
       </c>
       <c r="F587" t="n">
-        <v>0.833</v>
+        <v>0.787</v>
       </c>
       <c r="G587" t="n">
-        <v>0.873</v>
+        <v>0.853</v>
       </c>
       <c r="H587" t="n">
-        <v>0.415</v>
+        <v>0.176</v>
       </c>
       <c r="I587" t="n">
-        <v>1</v>
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="588">
@@ -25449,13 +25449,13 @@
         <v>11</v>
       </c>
       <c r="F588" t="n">
-        <v>0.773</v>
+        <v>0.767</v>
       </c>
       <c r="G588" t="n">
-        <v>0.793</v>
+        <v>0.787</v>
       </c>
       <c r="H588" t="n">
-        <v>0.779</v>
+        <v>0.782</v>
       </c>
       <c r="I588" t="n">
         <v>1</v>
@@ -25569,7 +25569,7 @@
         <v>0.135</v>
       </c>
       <c r="I591" t="n">
-        <v>0.721</v>
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="592">
@@ -25597,16 +25597,16 @@
         <v>15</v>
       </c>
       <c r="F592" t="n">
-        <v>0.52</v>
+        <v>0.507</v>
       </c>
       <c r="G592" t="n">
         <v>0.727</v>
       </c>
       <c r="H592" t="n">
-        <v>0.000331</v>
+        <v>0.000135</v>
       </c>
       <c r="I592" t="n">
-        <v>0.00265</v>
+        <v>0.00108</v>
       </c>
     </row>
     <row r="593">
@@ -25634,16 +25634,16 @@
         <v>16</v>
       </c>
       <c r="F593" t="n">
-        <v>0.46</v>
+        <v>0.393</v>
       </c>
       <c r="G593" t="n">
-        <v>0.713</v>
+        <v>0.7</v>
       </c>
       <c r="H593" t="n">
-        <v>1.28e-05</v>
+        <v>1.44e-07</v>
       </c>
       <c r="I593" t="n">
-        <v>0.000205</v>
+        <v>2.31e-06</v>
       </c>
     </row>
     <row r="594">
@@ -25828,7 +25828,7 @@
         <v>0.247</v>
       </c>
       <c r="I598" t="n">
-        <v>0.446</v>
+        <v>0.449</v>
       </c>
     </row>
     <row r="599">
@@ -25856,16 +25856,16 @@
         <v>6</v>
       </c>
       <c r="F599" t="n">
-        <v>0.877</v>
+        <v>0.875</v>
       </c>
       <c r="G599" t="n">
         <v>0.961</v>
       </c>
       <c r="H599" t="n">
-        <v>0.081</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="I599" t="n">
-        <v>0.216</v>
+        <v>0.214</v>
       </c>
     </row>
     <row r="600">
@@ -25896,13 +25896,13 @@
         <v>0.886</v>
       </c>
       <c r="G600" t="n">
-        <v>0.945</v>
+        <v>0.944</v>
       </c>
       <c r="H600" t="n">
-        <v>0.251</v>
+        <v>0.252</v>
       </c>
       <c r="I600" t="n">
-        <v>0.446</v>
+        <v>0.449</v>
       </c>
     </row>
     <row r="601">
@@ -25967,16 +25967,16 @@
         <v>9</v>
       </c>
       <c r="F602" t="n">
-        <v>0.964</v>
+        <v>0.963</v>
       </c>
       <c r="G602" t="n">
         <v>0.988</v>
       </c>
       <c r="H602" t="n">
-        <v>0.368</v>
+        <v>0.364</v>
       </c>
       <c r="I602" t="n">
-        <v>0.588</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="603">
@@ -26004,10 +26004,10 @@
         <v>10</v>
       </c>
       <c r="F603" t="n">
-        <v>0.983</v>
+        <v>0.98</v>
       </c>
       <c r="G603" t="n">
-        <v>0.97</v>
+        <v>0.968</v>
       </c>
       <c r="H603" t="n">
         <v>1</v>
@@ -26041,13 +26041,13 @@
         <v>11</v>
       </c>
       <c r="F604" t="n">
-        <v>0.863</v>
+        <v>0.861</v>
       </c>
       <c r="G604" t="n">
         <v>0.969</v>
       </c>
       <c r="H604" t="n">
-        <v>0.038</v>
+        <v>0.0379</v>
       </c>
       <c r="I604" t="n">
         <v>0.152</v>
@@ -26161,7 +26161,7 @@
         <v>0.0005330000000000001</v>
       </c>
       <c r="I607" t="n">
-        <v>0.00459</v>
+        <v>0.00284</v>
       </c>
     </row>
     <row r="608">
@@ -26189,16 +26189,16 @@
         <v>15</v>
       </c>
       <c r="F608" t="n">
-        <v>0.479</v>
+        <v>0.471</v>
       </c>
       <c r="G608" t="n">
         <v>0.771</v>
       </c>
       <c r="H608" t="n">
-        <v>0.0005730000000000001</v>
+        <v>0.00051</v>
       </c>
       <c r="I608" t="n">
-        <v>0.00459</v>
+        <v>0.00284</v>
       </c>
     </row>
     <row r="609">
@@ -26226,16 +26226,16 @@
         <v>16</v>
       </c>
       <c r="F609" t="n">
-        <v>0.389</v>
+        <v>0.327</v>
       </c>
       <c r="G609" t="n">
-        <v>0.706</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H609" t="n">
-        <v>0.00154</v>
+        <v>0.000426</v>
       </c>
       <c r="I609" t="n">
-        <v>0.008189999999999999</v>
+        <v>0.00284</v>
       </c>
     </row>
     <row r="610">
@@ -26272,7 +26272,7 @@
         <v>0.241</v>
       </c>
       <c r="I610" t="n">
-        <v>0.742</v>
+        <v>0.642</v>
       </c>
     </row>
     <row r="611">
@@ -26309,7 +26309,7 @@
         <v>0.236</v>
       </c>
       <c r="I611" t="n">
-        <v>0.742</v>
+        <v>0.642</v>
       </c>
     </row>
     <row r="612">
@@ -26346,7 +26346,7 @@
         <v>0.101</v>
       </c>
       <c r="I612" t="n">
-        <v>0.54</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="613">
@@ -26448,16 +26448,16 @@
         <v>6</v>
       </c>
       <c r="F615" t="n">
-        <v>0.772</v>
+        <v>0.761</v>
       </c>
       <c r="G615" t="n">
         <v>0.793</v>
       </c>
       <c r="H615" t="n">
-        <v>0.858</v>
+        <v>0.723</v>
       </c>
       <c r="I615" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="616">
@@ -26488,13 +26488,13 @@
         <v>0.824</v>
       </c>
       <c r="G616" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H616" t="n">
-        <v>1</v>
+        <v>0.845</v>
       </c>
       <c r="I616" t="n">
-        <v>1</v>
+        <v>0.965</v>
       </c>
     </row>
     <row r="617">
@@ -26559,16 +26559,16 @@
         <v>9</v>
       </c>
       <c r="F618" t="n">
-        <v>0.643</v>
+        <v>0.619</v>
       </c>
       <c r="G618" t="n">
-        <v>0.667</v>
+        <v>0.651</v>
       </c>
       <c r="H618" t="n">
-        <v>0.791</v>
+        <v>0.695</v>
       </c>
       <c r="I618" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="619">
@@ -26596,16 +26596,16 @@
         <v>10</v>
       </c>
       <c r="F619" t="n">
-        <v>0.704</v>
+        <v>0.617</v>
       </c>
       <c r="G619" t="n">
-        <v>0.79</v>
+        <v>0.753</v>
       </c>
       <c r="H619" t="n">
-        <v>0.278</v>
+        <v>0.0902</v>
       </c>
       <c r="I619" t="n">
-        <v>0.742</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="620">
@@ -26633,13 +26633,13 @@
         <v>11</v>
       </c>
       <c r="F620" t="n">
-        <v>0.75</v>
+        <v>0.739</v>
       </c>
       <c r="G620" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="H620" t="n">
-        <v>0.413</v>
+        <v>0.418</v>
       </c>
       <c r="I620" t="n">
         <v>0.881</v>
@@ -26781,16 +26781,16 @@
         <v>15</v>
       </c>
       <c r="F624" t="n">
-        <v>0.866</v>
+        <v>0.836</v>
       </c>
       <c r="G624" t="n">
         <v>0.552</v>
       </c>
       <c r="H624" t="n">
-        <v>0.00011</v>
+        <v>0.0006400000000000001</v>
       </c>
       <c r="I624" t="n">
-        <v>0.00175</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="625">
@@ -26818,16 +26818,16 @@
         <v>16</v>
       </c>
       <c r="F625" t="n">
-        <v>0.737</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="G625" t="n">
-        <v>0.421</v>
+        <v>0.386</v>
       </c>
       <c r="H625" t="n">
-        <v>0.00115</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="I625" t="n">
-        <v>0.00923</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="626">
@@ -26864,7 +26864,7 @@
         <v>0.207</v>
       </c>
       <c r="I626" t="n">
-        <v>1</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="627">
@@ -27040,16 +27040,16 @@
         <v>6</v>
       </c>
       <c r="F631" t="n">
-        <v>0.821</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G631" t="n">
         <v>0.869</v>
       </c>
       <c r="H631" t="n">
-        <v>0.235</v>
+        <v>0.183</v>
       </c>
       <c r="I631" t="n">
-        <v>1</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="632">
@@ -27080,10 +27080,10 @@
         <v>0.854</v>
       </c>
       <c r="G632" t="n">
-        <v>0.873</v>
+        <v>0.866</v>
       </c>
       <c r="H632" t="n">
-        <v>0.63</v>
+        <v>0.751</v>
       </c>
       <c r="I632" t="n">
         <v>1</v>
@@ -27151,13 +27151,13 @@
         <v>9</v>
       </c>
       <c r="F634" t="n">
-        <v>0.771</v>
+        <v>0.754</v>
       </c>
       <c r="G634" t="n">
-        <v>0.796</v>
+        <v>0.785</v>
       </c>
       <c r="H634" t="n">
-        <v>0.556</v>
+        <v>0.486</v>
       </c>
       <c r="I634" t="n">
         <v>1</v>
@@ -27188,16 +27188,16 @@
         <v>10</v>
       </c>
       <c r="F635" t="n">
-        <v>0.82</v>
+        <v>0.758</v>
       </c>
       <c r="G635" t="n">
-        <v>0.871</v>
+        <v>0.847</v>
       </c>
       <c r="H635" t="n">
-        <v>0.255</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="I635" t="n">
-        <v>1</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="636">
@@ -27225,10 +27225,10 @@
         <v>11</v>
       </c>
       <c r="F636" t="n">
-        <v>0.802</v>
+        <v>0.795</v>
       </c>
       <c r="G636" t="n">
-        <v>0.803</v>
+        <v>0.795</v>
       </c>
       <c r="H636" t="n">
         <v>1</v>
@@ -27373,13 +27373,13 @@
         <v>15</v>
       </c>
       <c r="F640" t="n">
-        <v>0.617</v>
+        <v>0.602</v>
       </c>
       <c r="G640" t="n">
         <v>0.643</v>
       </c>
       <c r="H640" t="n">
-        <v>0.714</v>
+        <v>0.542</v>
       </c>
       <c r="I640" t="n">
         <v>1</v>
@@ -27410,16 +27410,16 @@
         <v>16</v>
       </c>
       <c r="F641" t="n">
-        <v>0.509</v>
+        <v>0.413</v>
       </c>
       <c r="G641" t="n">
-        <v>0.527</v>
+        <v>0.494</v>
       </c>
       <c r="H641" t="n">
-        <v>0.795</v>
+        <v>0.231</v>
       </c>
       <c r="I641" t="n">
-        <v>1</v>
+        <v>0.922</v>
       </c>
     </row>
   </sheetData>

--- a/eval/learning-curve/results/statistical_tests_full150.xlsx
+++ b/eval/learning-curve/results/statistical_tests_full150.xlsx
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.126</v>
+        <v>0.117</v>
       </c>
       <c r="F2" t="n">
         <v>0.835</v>
@@ -518,7 +518,7 @@
         <v>0.102</v>
       </c>
       <c r="J2" t="n">
-        <v>0.189</v>
+        <v>0.293</v>
       </c>
     </row>
     <row r="3">
@@ -558,7 +558,7 @@
         <v>0.102</v>
       </c>
       <c r="J3" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="4">
@@ -583,22 +583,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.014</v>
+        <v>0.475</v>
       </c>
       <c r="F4" t="n">
         <v>0.835</v>
       </c>
       <c r="G4" t="n">
-        <v>0.734</v>
+        <v>0.8</v>
       </c>
       <c r="H4" t="n">
         <v>0.117</v>
       </c>
       <c r="I4" t="n">
-        <v>0.147</v>
+        <v>0.169</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0468</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="5">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.00445</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0.835</v>
       </c>
       <c r="G5" t="n">
-        <v>0.734</v>
+        <v>0.8</v>
       </c>
       <c r="H5" t="n">
         <v>0.117</v>
       </c>
       <c r="I5" t="n">
-        <v>0.147</v>
+        <v>0.169</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0167</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.303</v>
+        <v>0.288</v>
       </c>
       <c r="F6" t="n">
         <v>0.835</v>
@@ -678,7 +678,7 @@
         <v>0.0877</v>
       </c>
       <c r="J6" t="n">
-        <v>0.35</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="7">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.28</v>
+        <v>0.268</v>
       </c>
       <c r="F7" t="n">
         <v>0.835</v>
@@ -718,7 +718,7 @@
         <v>0.0877</v>
       </c>
       <c r="J7" t="n">
-        <v>0.323</v>
+        <v>0.453</v>
       </c>
     </row>
     <row r="8">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.0303</v>
+        <v>0.604</v>
       </c>
       <c r="F8" t="n">
         <v>0.835</v>
       </c>
       <c r="G8" t="n">
-        <v>0.75</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H8" t="n">
         <v>0.117</v>
       </c>
       <c r="I8" t="n">
-        <v>0.136</v>
+        <v>0.156</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0649</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="9">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.0124</v>
+        <v>0.629</v>
       </c>
       <c r="F9" t="n">
         <v>0.835</v>
       </c>
       <c r="G9" t="n">
-        <v>0.75</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H9" t="n">
         <v>0.117</v>
       </c>
       <c r="I9" t="n">
-        <v>0.136</v>
+        <v>0.156</v>
       </c>
       <c r="J9" t="n">
-        <v>0.031</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="10">
@@ -838,7 +838,7 @@
         <v>0.167</v>
       </c>
       <c r="J10" t="n">
-        <v>0.407</v>
+        <v>0.555</v>
       </c>
     </row>
     <row r="11">
@@ -878,7 +878,7 @@
         <v>0.167</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="12">
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.0156</v>
+        <v>0.544</v>
       </c>
       <c r="F12" t="n">
         <v>0.835</v>
       </c>
       <c r="G12" t="n">
-        <v>0.744</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>0.117</v>
       </c>
       <c r="I12" t="n">
-        <v>0.136</v>
+        <v>0.152</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0468</v>
+        <v>0.628</v>
       </c>
     </row>
     <row r="13">
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.00318</v>
+        <v>0.51</v>
       </c>
       <c r="F13" t="n">
         <v>0.835</v>
       </c>
       <c r="G13" t="n">
-        <v>0.744</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H13" t="n">
         <v>0.117</v>
       </c>
       <c r="I13" t="n">
-        <v>0.136</v>
+        <v>0.152</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0159</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="14">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0712</v>
       </c>
       <c r="F14" t="n">
         <v>0.835</v>
@@ -998,7 +998,7 @@
         <v>0.0829</v>
       </c>
       <c r="J14" t="n">
-        <v>0.13</v>
+        <v>0.214</v>
       </c>
     </row>
     <row r="15">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.125</v>
+        <v>0.118</v>
       </c>
       <c r="F15" t="n">
         <v>0.835</v>
@@ -1038,7 +1038,7 @@
         <v>0.0829</v>
       </c>
       <c r="J15" t="n">
-        <v>0.208</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="16">
@@ -1063,22 +1063,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.0373</v>
+        <v>0.653</v>
       </c>
       <c r="F16" t="n">
         <v>0.835</v>
       </c>
       <c r="G16" t="n">
-        <v>0.748</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H16" t="n">
         <v>0.117</v>
       </c>
       <c r="I16" t="n">
-        <v>0.145</v>
+        <v>0.174</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0699</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="17">
@@ -1103,22 +1103,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.00834</v>
+        <v>0.641</v>
       </c>
       <c r="F17" t="n">
         <v>0.835</v>
       </c>
       <c r="G17" t="n">
-        <v>0.748</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H17" t="n">
         <v>0.117</v>
       </c>
       <c r="I17" t="n">
-        <v>0.145</v>
+        <v>0.174</v>
       </c>
       <c r="J17" t="n">
-        <v>0.025</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="18">
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.0011</v>
+        <v>0.001</v>
       </c>
       <c r="F18" t="n">
         <v>0.835</v>
@@ -1158,7 +1158,7 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0165</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="19">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0107</v>
+        <v>0.01</v>
       </c>
       <c r="F20" t="n">
         <v>0.835</v>
@@ -1238,7 +1238,7 @@
         <v>0.0842</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0468</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.0259</v>
+        <v>0.0243</v>
       </c>
       <c r="F21" t="n">
         <v>0.835</v>
@@ -1278,7 +1278,7 @@
         <v>0.0842</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0499</v>
+        <v>0.0997</v>
       </c>
     </row>
     <row r="22">
@@ -1315,10 +1315,10 @@
         <v>0.155</v>
       </c>
       <c r="I22" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0649</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="23">
@@ -1355,10 +1355,10 @@
         <v>0.155</v>
       </c>
       <c r="I23" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0499</v>
+        <v>0.0997</v>
       </c>
     </row>
     <row r="24">
@@ -1389,7 +1389,7 @@
         <v>0.797</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H24" t="n">
         <v>0.155</v>
@@ -1398,7 +1398,7 @@
         <v>0.175</v>
       </c>
       <c r="J24" t="n">
-        <v>0.233</v>
+        <v>0.366</v>
       </c>
     </row>
     <row r="25">
@@ -1429,7 +1429,7 @@
         <v>0.797</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H25" t="n">
         <v>0.155</v>
@@ -1438,7 +1438,7 @@
         <v>0.175</v>
       </c>
       <c r="J25" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="26">
@@ -1469,7 +1469,7 @@
         <v>0.797</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H26" t="n">
         <v>0.155</v>
@@ -1478,7 +1478,7 @@
         <v>0.175</v>
       </c>
       <c r="J26" t="n">
-        <v>0.29</v>
+        <v>0.435</v>
       </c>
     </row>
     <row r="27">
@@ -1509,7 +1509,7 @@
         <v>0.797</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H27" t="n">
         <v>0.155</v>
@@ -1518,7 +1518,7 @@
         <v>0.175</v>
       </c>
       <c r="J27" t="n">
-        <v>0.323</v>
+        <v>0.453</v>
       </c>
     </row>
     <row r="28">
@@ -1549,7 +1549,7 @@
         <v>0.797</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H28" t="n">
         <v>0.155</v>
@@ -1558,7 +1558,7 @@
         <v>0.19</v>
       </c>
       <c r="J28" t="n">
-        <v>0.386</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="29">
@@ -1589,7 +1589,7 @@
         <v>0.797</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H29" t="n">
         <v>0.155</v>
@@ -1598,7 +1598,7 @@
         <v>0.19</v>
       </c>
       <c r="J29" t="n">
-        <v>0.363</v>
+        <v>0.508</v>
       </c>
     </row>
     <row r="30">
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.015</v>
+        <v>0.0144</v>
       </c>
       <c r="F30" t="n">
         <v>0.797</v>
@@ -1638,7 +1638,7 @@
         <v>0.0931</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0468</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.00187</v>
+        <v>0.00186</v>
       </c>
       <c r="F31" t="n">
         <v>0.797</v>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.857</v>
+        <v>0.858</v>
       </c>
       <c r="F32" t="n">
         <v>0.864</v>
@@ -1718,7 +1718,7 @@
         <v>0.12</v>
       </c>
       <c r="J32" t="n">
-        <v>0.885</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="33">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.408</v>
+        <v>0.433</v>
       </c>
       <c r="F33" t="n">
         <v>0.864</v>
@@ -1783,22 +1783,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.0501</v>
+        <v>0.0814</v>
       </c>
       <c r="F34" t="n">
         <v>0.864</v>
       </c>
       <c r="G34" t="n">
-        <v>0.707</v>
+        <v>0.729</v>
       </c>
       <c r="H34" t="n">
         <v>0.163</v>
       </c>
       <c r="I34" t="n">
-        <v>0.261</v>
+        <v>0.249</v>
       </c>
       <c r="J34" t="n">
-        <v>0.376</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="35">
@@ -1823,22 +1823,22 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.0076</v>
+        <v>0.00763</v>
       </c>
       <c r="F35" t="n">
         <v>0.864</v>
       </c>
       <c r="G35" t="n">
-        <v>0.707</v>
+        <v>0.729</v>
       </c>
       <c r="H35" t="n">
         <v>0.163</v>
       </c>
       <c r="I35" t="n">
-        <v>0.261</v>
+        <v>0.249</v>
       </c>
       <c r="J35" t="n">
-        <v>0.057</v>
+        <v>0.0572</v>
       </c>
     </row>
     <row r="36">
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.649</v>
+        <v>0.651</v>
       </c>
       <c r="F36" t="n">
         <v>0.864</v>
@@ -1878,7 +1878,7 @@
         <v>0.134</v>
       </c>
       <c r="J36" t="n">
-        <v>0.885</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="37">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.241</v>
+        <v>0.31</v>
       </c>
       <c r="F38" t="n">
         <v>0.864</v>
       </c>
       <c r="G38" t="n">
-        <v>0.779</v>
+        <v>0.793</v>
       </c>
       <c r="H38" t="n">
         <v>0.163</v>
       </c>
       <c r="I38" t="n">
-        <v>0.222</v>
+        <v>0.22</v>
       </c>
       <c r="J38" t="n">
-        <v>0.516</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="39">
@@ -1983,22 +1983,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.159</v>
+        <v>0.231</v>
       </c>
       <c r="F39" t="n">
         <v>0.864</v>
       </c>
       <c r="G39" t="n">
-        <v>0.779</v>
+        <v>0.793</v>
       </c>
       <c r="H39" t="n">
         <v>0.163</v>
       </c>
       <c r="I39" t="n">
-        <v>0.222</v>
+        <v>0.22</v>
       </c>
       <c r="J39" t="n">
-        <v>0.474</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="40">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.16</v>
+        <v>0.161</v>
       </c>
       <c r="F40" t="n">
         <v>0.864</v>
@@ -2038,7 +2038,7 @@
         <v>0.185</v>
       </c>
       <c r="J40" t="n">
-        <v>0.4</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="41">
@@ -2078,7 +2078,7 @@
         <v>0.185</v>
       </c>
       <c r="J41" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="42">
@@ -2103,22 +2103,22 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.138</v>
+        <v>0.165</v>
       </c>
       <c r="F42" t="n">
         <v>0.864</v>
       </c>
       <c r="G42" t="n">
-        <v>0.746</v>
+        <v>0.76</v>
       </c>
       <c r="H42" t="n">
         <v>0.163</v>
       </c>
       <c r="I42" t="n">
-        <v>0.277</v>
+        <v>0.255</v>
       </c>
       <c r="J42" t="n">
-        <v>0.4</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="43">
@@ -2143,22 +2143,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.193</v>
+        <v>0.175</v>
       </c>
       <c r="F43" t="n">
         <v>0.864</v>
       </c>
       <c r="G43" t="n">
-        <v>0.746</v>
+        <v>0.76</v>
       </c>
       <c r="H43" t="n">
         <v>0.163</v>
       </c>
       <c r="I43" t="n">
-        <v>0.277</v>
+        <v>0.255</v>
       </c>
       <c r="J43" t="n">
-        <v>0.474</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="44">
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.745</v>
+        <v>0.746</v>
       </c>
       <c r="F44" t="n">
         <v>0.864</v>
@@ -2198,7 +2198,7 @@
         <v>0.107</v>
       </c>
       <c r="J44" t="n">
-        <v>0.885</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="45">
@@ -2263,22 +2263,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.118</v>
+        <v>0.178</v>
       </c>
       <c r="F46" t="n">
         <v>0.864</v>
       </c>
       <c r="G46" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="H46" t="n">
         <v>0.163</v>
       </c>
       <c r="I46" t="n">
-        <v>0.24</v>
+        <v>0.224</v>
       </c>
       <c r="J46" t="n">
-        <v>0.4</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="47">
@@ -2303,22 +2303,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.0507</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="F47" t="n">
         <v>0.864</v>
       </c>
       <c r="G47" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="H47" t="n">
         <v>0.163</v>
       </c>
       <c r="I47" t="n">
-        <v>0.24</v>
+        <v>0.224</v>
       </c>
       <c r="J47" t="n">
-        <v>0.19</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="48">
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="F48" t="n">
         <v>0.864</v>
@@ -2358,7 +2358,7 @@
         <v>0.0584</v>
       </c>
       <c r="J48" t="n">
-        <v>0.4</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="49">
@@ -2398,7 +2398,7 @@
         <v>0.0584</v>
       </c>
       <c r="J49" t="n">
-        <v>0.474</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="50">
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="F50" t="n">
         <v>0.864</v>
@@ -2438,7 +2438,7 @@
         <v>0.11</v>
       </c>
       <c r="J50" t="n">
-        <v>0.885</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="51">
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.415</v>
+        <v>0.414</v>
       </c>
       <c r="F52" t="n">
         <v>0.793</v>
@@ -2518,7 +2518,7 @@
         <v>0.195</v>
       </c>
       <c r="J52" t="n">
-        <v>0.778</v>
+        <v>0.776</v>
       </c>
     </row>
     <row r="53">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.885</v>
+        <v>0.886</v>
       </c>
       <c r="F54" t="n">
         <v>0.793</v>
@@ -2598,7 +2598,7 @@
         <v>0.183</v>
       </c>
       <c r="J54" t="n">
-        <v>0.885</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="55">
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.734</v>
+        <v>0.736</v>
       </c>
       <c r="F56" t="n">
         <v>0.793</v>
@@ -2678,7 +2678,7 @@
         <v>0.189</v>
       </c>
       <c r="J56" t="n">
-        <v>0.885</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="57">
@@ -2758,7 +2758,7 @@
         <v>0.195</v>
       </c>
       <c r="J58" t="n">
-        <v>0.885</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="59">
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.000898</v>
+        <v>0.000894</v>
       </c>
       <c r="F60" t="n">
         <v>0.793</v>
@@ -2838,7 +2838,7 @@
         <v>0.0954</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0135</v>
+        <v>0.0134</v>
       </c>
     </row>
     <row r="61">
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.289</v>
+        <v>0.27</v>
       </c>
       <c r="F62" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G62" t="n">
         <v>0.792</v>
@@ -2918,7 +2918,7 @@
         <v>0.186</v>
       </c>
       <c r="J62" t="n">
-        <v>0.333</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="63">
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.14</v>
+        <v>0.124</v>
       </c>
       <c r="F63" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G63" t="n">
         <v>0.792</v>
@@ -2958,7 +2958,7 @@
         <v>0.186</v>
       </c>
       <c r="J63" t="n">
-        <v>0.175</v>
+        <v>0.232</v>
       </c>
     </row>
     <row r="64">
@@ -2983,22 +2983,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.00604</v>
+        <v>0.994</v>
       </c>
       <c r="F64" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="G64" t="n">
         <v>0.764</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0.582</v>
       </c>
       <c r="H64" t="n">
         <v>0.166</v>
       </c>
       <c r="I64" t="n">
-        <v>0.212</v>
+        <v>0.266</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0181</v>
+        <v>0.994</v>
       </c>
     </row>
     <row r="65">
@@ -3023,22 +3023,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.0008050000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="F65" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="G65" t="n">
         <v>0.764</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0.582</v>
       </c>
       <c r="H65" t="n">
         <v>0.166</v>
       </c>
       <c r="I65" t="n">
-        <v>0.212</v>
+        <v>0.266</v>
       </c>
       <c r="J65" t="n">
-        <v>0.00402</v>
+        <v>0.233</v>
       </c>
     </row>
     <row r="66">
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.615</v>
+        <v>0.592</v>
       </c>
       <c r="F66" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G66" t="n">
         <v>0.778</v>
@@ -3078,7 +3078,7 @@
         <v>0.149</v>
       </c>
       <c r="J66" t="n">
-        <v>0.615</v>
+        <v>0.6830000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -3106,7 +3106,7 @@
         <v>0.649</v>
       </c>
       <c r="F67" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G67" t="n">
         <v>0.778</v>
@@ -3118,7 +3118,7 @@
         <v>0.149</v>
       </c>
       <c r="J67" t="n">
-        <v>0.649</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="68">
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.000785</v>
+        <v>0.484</v>
       </c>
       <c r="F68" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G68" t="n">
-        <v>0.552</v>
+        <v>0.719</v>
       </c>
       <c r="H68" t="n">
         <v>0.166</v>
       </c>
       <c r="I68" t="n">
-        <v>0.185</v>
+        <v>0.239</v>
       </c>
       <c r="J68" t="n">
-        <v>0.00923</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="69">
@@ -3183,22 +3183,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.000803</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G69" t="n">
-        <v>0.552</v>
+        <v>0.719</v>
       </c>
       <c r="H69" t="n">
         <v>0.166</v>
       </c>
       <c r="I69" t="n">
-        <v>0.185</v>
+        <v>0.239</v>
       </c>
       <c r="J69" t="n">
-        <v>0.00402</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -3226,7 +3226,7 @@
         <v>0.446</v>
       </c>
       <c r="F70" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G70" t="n">
         <v>0.787</v>
@@ -3238,7 +3238,7 @@
         <v>0.148</v>
       </c>
       <c r="J70" t="n">
-        <v>0.478</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="71">
@@ -3266,7 +3266,7 @@
         <v>0.433</v>
       </c>
       <c r="F71" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G71" t="n">
         <v>0.787</v>
@@ -3278,7 +3278,7 @@
         <v>0.148</v>
       </c>
       <c r="J71" t="n">
-        <v>0.464</v>
+        <v>0.541</v>
       </c>
     </row>
     <row r="72">
@@ -3303,22 +3303,22 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.00123</v>
+        <v>0.488</v>
       </c>
       <c r="F72" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G72" t="n">
-        <v>0.539</v>
+        <v>0.714</v>
       </c>
       <c r="H72" t="n">
         <v>0.166</v>
       </c>
       <c r="I72" t="n">
-        <v>0.213</v>
+        <v>0.267</v>
       </c>
       <c r="J72" t="n">
-        <v>0.00923</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="73">
@@ -3343,22 +3343,22 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.000437</v>
+        <v>0.86</v>
       </c>
       <c r="F73" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G73" t="n">
-        <v>0.539</v>
+        <v>0.714</v>
       </c>
       <c r="H73" t="n">
         <v>0.166</v>
       </c>
       <c r="I73" t="n">
-        <v>0.213</v>
+        <v>0.267</v>
       </c>
       <c r="J73" t="n">
-        <v>0.00402</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="74">
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.144</v>
+        <v>0.133</v>
       </c>
       <c r="F74" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G74" t="n">
         <v>0.801</v>
@@ -3398,7 +3398,7 @@
         <v>0.144</v>
       </c>
       <c r="J74" t="n">
-        <v>0.18</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="75">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.132</v>
+        <v>0.118</v>
       </c>
       <c r="F75" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G75" t="n">
         <v>0.801</v>
@@ -3438,7 +3438,7 @@
         <v>0.144</v>
       </c>
       <c r="J75" t="n">
-        <v>0.175</v>
+        <v>0.232</v>
       </c>
     </row>
     <row r="76">
@@ -3463,22 +3463,22 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.0056</v>
+        <v>0.917</v>
       </c>
       <c r="F76" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G76" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.755</v>
       </c>
       <c r="H76" t="n">
         <v>0.166</v>
       </c>
       <c r="I76" t="n">
-        <v>0.222</v>
+        <v>0.264</v>
       </c>
       <c r="J76" t="n">
-        <v>0.0181</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="77">
@@ -3503,22 +3503,22 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.00112</v>
+        <v>0.363</v>
       </c>
       <c r="F77" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G77" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.755</v>
       </c>
       <c r="H77" t="n">
         <v>0.166</v>
       </c>
       <c r="I77" t="n">
-        <v>0.222</v>
+        <v>0.264</v>
       </c>
       <c r="J77" t="n">
-        <v>0.0042</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="78">
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.011</v>
+        <v>0.0102</v>
       </c>
       <c r="F78" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G78" t="n">
         <v>0.842</v>
@@ -3558,7 +3558,7 @@
         <v>0.137</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0251</v>
+        <v>0.0585</v>
       </c>
     </row>
     <row r="79">
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.0131</v>
+        <v>0.011</v>
       </c>
       <c r="F79" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G79" t="n">
         <v>0.842</v>
@@ -3598,7 +3598,7 @@
         <v>0.137</v>
       </c>
       <c r="J79" t="n">
-        <v>0.0281</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="80">
@@ -3623,10 +3623,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.115</v>
+        <v>0.11</v>
       </c>
       <c r="F80" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G80" t="n">
         <v>0.8159999999999999</v>
@@ -3638,7 +3638,7 @@
         <v>0.185</v>
       </c>
       <c r="J80" t="n">
-        <v>0.157</v>
+        <v>0.236</v>
       </c>
     </row>
     <row r="81">
@@ -3666,7 +3666,7 @@
         <v>0.112</v>
       </c>
       <c r="F81" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G81" t="n">
         <v>0.8159999999999999</v>
@@ -3678,7 +3678,7 @@
         <v>0.185</v>
       </c>
       <c r="J81" t="n">
-        <v>0.168</v>
+        <v>0.232</v>
       </c>
     </row>
     <row r="82">
@@ -3706,19 +3706,19 @@
         <v>0.0199</v>
       </c>
       <c r="F82" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="G82" t="n">
-        <v>0.806</v>
+        <v>0.805</v>
       </c>
       <c r="H82" t="n">
         <v>0.185</v>
       </c>
       <c r="I82" t="n">
-        <v>0.181</v>
+        <v>0.18</v>
       </c>
       <c r="J82" t="n">
-        <v>0.0332</v>
+        <v>0.0597</v>
       </c>
     </row>
     <row r="83">
@@ -3746,19 +3746,19 @@
         <v>0.0303</v>
       </c>
       <c r="F83" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="G83" t="n">
-        <v>0.806</v>
+        <v>0.805</v>
       </c>
       <c r="H83" t="n">
         <v>0.185</v>
       </c>
       <c r="I83" t="n">
-        <v>0.181</v>
+        <v>0.18</v>
       </c>
       <c r="J83" t="n">
-        <v>0.0505</v>
+        <v>0.09089999999999999</v>
       </c>
     </row>
     <row r="84">
@@ -3786,10 +3786,10 @@
         <v>0.00389</v>
       </c>
       <c r="F84" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="G84" t="n">
-        <v>0.819</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H84" t="n">
         <v>0.185</v>
@@ -3798,7 +3798,7 @@
         <v>0.16</v>
       </c>
       <c r="J84" t="n">
-        <v>0.0181</v>
+        <v>0.0583</v>
       </c>
     </row>
     <row r="85">
@@ -3826,10 +3826,10 @@
         <v>0.00521</v>
       </c>
       <c r="F85" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="G85" t="n">
-        <v>0.819</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H85" t="n">
         <v>0.185</v>
@@ -3838,7 +3838,7 @@
         <v>0.16</v>
       </c>
       <c r="J85" t="n">
-        <v>0.0156</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="86">
@@ -3866,10 +3866,10 @@
         <v>0.0163</v>
       </c>
       <c r="F86" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="G86" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="H86" t="n">
         <v>0.185</v>
@@ -3878,7 +3878,7 @@
         <v>0.155</v>
       </c>
       <c r="J86" t="n">
-        <v>0.0306</v>
+        <v>0.0597</v>
       </c>
     </row>
     <row r="87">
@@ -3906,10 +3906,10 @@
         <v>0.0199</v>
       </c>
       <c r="F87" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="G87" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="H87" t="n">
         <v>0.185</v>
@@ -3918,7 +3918,7 @@
         <v>0.155</v>
       </c>
       <c r="J87" t="n">
-        <v>0.0373</v>
+        <v>0.0746</v>
       </c>
     </row>
     <row r="88">
@@ -3946,10 +3946,10 @@
         <v>0.0117</v>
       </c>
       <c r="F88" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="G88" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H88" t="n">
         <v>0.185</v>
@@ -3958,7 +3958,7 @@
         <v>0.162</v>
       </c>
       <c r="J88" t="n">
-        <v>0.0251</v>
+        <v>0.0585</v>
       </c>
     </row>
     <row r="89">
@@ -3986,10 +3986,10 @@
         <v>0.00763</v>
       </c>
       <c r="F89" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="G89" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H89" t="n">
         <v>0.185</v>
@@ -3998,7 +3998,7 @@
         <v>0.162</v>
       </c>
       <c r="J89" t="n">
-        <v>0.0191</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="90">
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.102</v>
+        <v>0.11</v>
       </c>
       <c r="F90" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="G90" t="n">
         <v>0.703</v>
@@ -4038,7 +4038,7 @@
         <v>0.163</v>
       </c>
       <c r="J90" t="n">
-        <v>0.153</v>
+        <v>0.236</v>
       </c>
     </row>
     <row r="91">
@@ -4066,7 +4066,7 @@
         <v>0.156</v>
       </c>
       <c r="F91" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="G91" t="n">
         <v>0.703</v>
@@ -4078,7 +4078,7 @@
         <v>0.163</v>
       </c>
       <c r="J91" t="n">
-        <v>0.18</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="92">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.574</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="F92" t="n">
         <v>0.797</v>
@@ -4118,7 +4118,7 @@
         <v>0.139</v>
       </c>
       <c r="J92" t="n">
-        <v>0.662</v>
+        <v>0.648</v>
       </c>
     </row>
     <row r="93">
@@ -4158,7 +4158,7 @@
         <v>0.139</v>
       </c>
       <c r="J93" t="n">
-        <v>0.493</v>
+        <v>0.673</v>
       </c>
     </row>
     <row r="94">
@@ -4183,22 +4183,22 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.0191</v>
+        <v>0.423</v>
       </c>
       <c r="F94" t="n">
         <v>0.797</v>
       </c>
       <c r="G94" t="n">
-        <v>0.635</v>
+        <v>0.741</v>
       </c>
       <c r="H94" t="n">
         <v>0.132</v>
       </c>
       <c r="I94" t="n">
-        <v>0.226</v>
+        <v>0.247</v>
       </c>
       <c r="J94" t="n">
-        <v>0.0426</v>
+        <v>0.577</v>
       </c>
     </row>
     <row r="95">
@@ -4223,22 +4223,22 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.00168</v>
+        <v>0.865</v>
       </c>
       <c r="F95" t="n">
         <v>0.797</v>
       </c>
       <c r="G95" t="n">
-        <v>0.635</v>
+        <v>0.741</v>
       </c>
       <c r="H95" t="n">
         <v>0.132</v>
       </c>
       <c r="I95" t="n">
-        <v>0.226</v>
+        <v>0.247</v>
       </c>
       <c r="J95" t="n">
-        <v>0.008019999999999999</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="96">
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.862</v>
+        <v>0.848</v>
       </c>
       <c r="F96" t="n">
         <v>0.797</v>
@@ -4278,7 +4278,7 @@
         <v>0.116</v>
       </c>
       <c r="J96" t="n">
-        <v>0.862</v>
+        <v>0.848</v>
       </c>
     </row>
     <row r="97">
@@ -4318,7 +4318,7 @@
         <v>0.116</v>
       </c>
       <c r="J97" t="n">
-        <v>0.86</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="98">
@@ -4343,22 +4343,22 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.0155</v>
+        <v>0.409</v>
       </c>
       <c r="F98" t="n">
         <v>0.797</v>
       </c>
       <c r="G98" t="n">
-        <v>0.637</v>
+        <v>0.743</v>
       </c>
       <c r="H98" t="n">
         <v>0.132</v>
       </c>
       <c r="I98" t="n">
-        <v>0.199</v>
+        <v>0.224</v>
       </c>
       <c r="J98" t="n">
-        <v>0.0426</v>
+        <v>0.577</v>
       </c>
     </row>
     <row r="99">
@@ -4383,22 +4383,22 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.00214</v>
+        <v>0.86</v>
       </c>
       <c r="F99" t="n">
         <v>0.797</v>
       </c>
       <c r="G99" t="n">
-        <v>0.637</v>
+        <v>0.743</v>
       </c>
       <c r="H99" t="n">
         <v>0.132</v>
       </c>
       <c r="I99" t="n">
-        <v>0.199</v>
+        <v>0.224</v>
       </c>
       <c r="J99" t="n">
-        <v>0.008019999999999999</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="100">
@@ -4478,7 +4478,7 @@
         <v>0.152</v>
       </c>
       <c r="J101" t="n">
-        <v>0.696</v>
+        <v>0.836</v>
       </c>
     </row>
     <row r="102">
@@ -4503,22 +4503,22 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.0123</v>
+        <v>0.346</v>
       </c>
       <c r="F102" t="n">
         <v>0.797</v>
       </c>
       <c r="G102" t="n">
-        <v>0.622</v>
+        <v>0.732</v>
       </c>
       <c r="H102" t="n">
         <v>0.132</v>
       </c>
       <c r="I102" t="n">
-        <v>0.236</v>
+        <v>0.256</v>
       </c>
       <c r="J102" t="n">
-        <v>0.0426</v>
+        <v>0.577</v>
       </c>
     </row>
     <row r="103">
@@ -4543,22 +4543,22 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.000305</v>
+        <v>0.632</v>
       </c>
       <c r="F103" t="n">
         <v>0.797</v>
       </c>
       <c r="G103" t="n">
-        <v>0.622</v>
+        <v>0.732</v>
       </c>
       <c r="H103" t="n">
         <v>0.132</v>
       </c>
       <c r="I103" t="n">
-        <v>0.236</v>
+        <v>0.256</v>
       </c>
       <c r="J103" t="n">
-        <v>0.00458</v>
+        <v>0.836</v>
       </c>
     </row>
     <row r="104">
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.36</v>
+        <v>0.349</v>
       </c>
       <c r="F104" t="n">
         <v>0.797</v>
@@ -4598,7 +4598,7 @@
         <v>0.107</v>
       </c>
       <c r="J104" t="n">
-        <v>0.45</v>
+        <v>0.577</v>
       </c>
     </row>
     <row r="105">
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.427</v>
+        <v>0.394</v>
       </c>
       <c r="F105" t="n">
         <v>0.797</v>
@@ -4638,7 +4638,7 @@
         <v>0.107</v>
       </c>
       <c r="J105" t="n">
-        <v>0.493</v>
+        <v>0.673</v>
       </c>
     </row>
     <row r="106">
@@ -4663,22 +4663,22 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.0227</v>
+        <v>0.534</v>
       </c>
       <c r="F106" t="n">
         <v>0.797</v>
       </c>
       <c r="G106" t="n">
-        <v>0.637</v>
+        <v>0.755</v>
       </c>
       <c r="H106" t="n">
         <v>0.132</v>
       </c>
       <c r="I106" t="n">
-        <v>0.232</v>
+        <v>0.238</v>
       </c>
       <c r="J106" t="n">
-        <v>0.0426</v>
+        <v>0.648</v>
       </c>
     </row>
     <row r="107">
@@ -4703,22 +4703,22 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.00131</v>
+        <v>0.669</v>
       </c>
       <c r="F107" t="n">
         <v>0.797</v>
       </c>
       <c r="G107" t="n">
-        <v>0.637</v>
+        <v>0.755</v>
       </c>
       <c r="H107" t="n">
         <v>0.132</v>
       </c>
       <c r="I107" t="n">
-        <v>0.232</v>
+        <v>0.238</v>
       </c>
       <c r="J107" t="n">
-        <v>0.008019999999999999</v>
+        <v>0.836</v>
       </c>
     </row>
     <row r="108">
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.00346</v>
+        <v>0.00322</v>
       </c>
       <c r="F108" t="n">
         <v>0.797</v>
@@ -4758,7 +4758,7 @@
         <v>0.0919</v>
       </c>
       <c r="J108" t="n">
-        <v>0.0426</v>
+        <v>0.0483</v>
       </c>
     </row>
     <row r="109">
@@ -4798,7 +4798,7 @@
         <v>0.0919</v>
       </c>
       <c r="J109" t="n">
-        <v>0.008580000000000001</v>
+        <v>0.0429</v>
       </c>
     </row>
     <row r="110">
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.199</v>
+        <v>0.193</v>
       </c>
       <c r="F110" t="n">
         <v>0.797</v>
@@ -4838,7 +4838,7 @@
         <v>0.149</v>
       </c>
       <c r="J110" t="n">
-        <v>0.271</v>
+        <v>0.414</v>
       </c>
     </row>
     <row r="111">
@@ -4878,7 +4878,7 @@
         <v>0.149</v>
       </c>
       <c r="J111" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="112">
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.0136</v>
+        <v>0.0138</v>
       </c>
       <c r="F112" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="G112" t="n">
         <v>0.789</v>
@@ -4915,10 +4915,10 @@
         <v>0.169</v>
       </c>
       <c r="I112" t="n">
-        <v>0.181</v>
+        <v>0.18</v>
       </c>
       <c r="J112" t="n">
-        <v>0.0426</v>
+        <v>0.0755</v>
       </c>
     </row>
     <row r="113">
@@ -4946,7 +4946,7 @@
         <v>0.011</v>
       </c>
       <c r="F113" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="G113" t="n">
         <v>0.789</v>
@@ -4955,10 +4955,10 @@
         <v>0.169</v>
       </c>
       <c r="I113" t="n">
-        <v>0.181</v>
+        <v>0.18</v>
       </c>
       <c r="J113" t="n">
-        <v>0.0236</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="114">
@@ -4986,7 +4986,7 @@
         <v>0.0222</v>
       </c>
       <c r="F114" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="G114" t="n">
         <v>0.792</v>
@@ -4998,7 +4998,7 @@
         <v>0.159</v>
       </c>
       <c r="J114" t="n">
-        <v>0.0426</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="115">
@@ -5026,7 +5026,7 @@
         <v>0.0386</v>
       </c>
       <c r="F115" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="G115" t="n">
         <v>0.792</v>
@@ -5038,7 +5038,7 @@
         <v>0.159</v>
       </c>
       <c r="J115" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="116">
@@ -5063,10 +5063,10 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.0385</v>
+        <v>0.0384</v>
       </c>
       <c r="F116" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="G116" t="n">
         <v>0.788</v>
@@ -5078,7 +5078,7 @@
         <v>0.161</v>
       </c>
       <c r="J116" t="n">
-        <v>0.0641</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="117">
@@ -5106,7 +5106,7 @@
         <v>0.0577</v>
       </c>
       <c r="F117" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="G117" t="n">
         <v>0.788</v>
@@ -5118,7 +5118,7 @@
         <v>0.161</v>
       </c>
       <c r="J117" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="118">
@@ -5146,10 +5146,10 @@
         <v>0.0427</v>
       </c>
       <c r="F118" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="G118" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="H118" t="n">
         <v>0.169</v>
@@ -5158,7 +5158,7 @@
         <v>0.169</v>
       </c>
       <c r="J118" t="n">
-        <v>0.0641</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="119">
@@ -5186,10 +5186,10 @@
         <v>0.0507</v>
       </c>
       <c r="F119" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="G119" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="H119" t="n">
         <v>0.169</v>
@@ -5198,7 +5198,7 @@
         <v>0.169</v>
       </c>
       <c r="J119" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="120">
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.0154</v>
+        <v>0.0151</v>
       </c>
       <c r="F120" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="G120" t="n">
         <v>0.789</v>
@@ -5238,7 +5238,7 @@
         <v>0.137</v>
       </c>
       <c r="J120" t="n">
-        <v>0.0426</v>
+        <v>0.0755</v>
       </c>
     </row>
     <row r="121">
@@ -5266,7 +5266,7 @@
         <v>0.0076</v>
       </c>
       <c r="F121" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="G121" t="n">
         <v>0.789</v>
@@ -5278,7 +5278,7 @@
         <v>0.137</v>
       </c>
       <c r="J121" t="n">
-        <v>0.019</v>
+        <v>0.055</v>
       </c>
     </row>
   </sheetData>
@@ -5700,16 +5700,16 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>0.86</v>
+        <v>0.853</v>
       </c>
       <c r="G11" t="n">
         <v>0.78</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0977</v>
+        <v>0.135</v>
       </c>
       <c r="I11" t="n">
-        <v>0.313</v>
+        <v>0.398</v>
       </c>
     </row>
     <row r="12">
@@ -6292,7 +6292,7 @@
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>0.929</v>
+        <v>0.928</v>
       </c>
       <c r="G27" t="n">
         <v>0.9</v>
@@ -6884,16 +6884,16 @@
         <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>0.802</v>
+        <v>0.79</v>
       </c>
       <c r="G43" t="n">
         <v>0.667</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0745</v>
+        <v>0.111</v>
       </c>
       <c r="I43" t="n">
-        <v>0.364</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="44">
@@ -7115,7 +7115,7 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>0.364</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="50">
@@ -7476,16 +7476,16 @@
         <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>0.861</v>
+        <v>0.853</v>
       </c>
       <c r="G59" t="n">
         <v>0.766</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0493</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>0.197</v>
+        <v>0.272</v>
       </c>
     </row>
     <row r="60">
@@ -7738,13 +7738,13 @@
         <v>0.853</v>
       </c>
       <c r="G66" t="n">
-        <v>0.74</v>
+        <v>0.867</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0212</v>
+        <v>0.868</v>
       </c>
       <c r="I66" t="n">
-        <v>0.0566</v>
+        <v>0.929</v>
       </c>
     </row>
     <row r="67">
@@ -7775,13 +7775,13 @@
         <v>0.827</v>
       </c>
       <c r="G67" t="n">
-        <v>0.947</v>
+        <v>0.967</v>
       </c>
       <c r="H67" t="n">
-        <v>0.00162</v>
+        <v>8.69e-05</v>
       </c>
       <c r="I67" t="n">
-        <v>0.008630000000000001</v>
+        <v>0.000695</v>
       </c>
     </row>
     <row r="68">
@@ -7812,13 +7812,13 @@
         <v>0.98</v>
       </c>
       <c r="G68" t="n">
-        <v>0.9</v>
+        <v>0.947</v>
       </c>
       <c r="H68" t="n">
-        <v>0.00592</v>
+        <v>0.218</v>
       </c>
       <c r="I68" t="n">
-        <v>0.019</v>
+        <v>0.451</v>
       </c>
     </row>
     <row r="69">
@@ -7849,13 +7849,13 @@
         <v>0.993</v>
       </c>
       <c r="G69" t="n">
-        <v>0.4</v>
+        <v>0.273</v>
       </c>
       <c r="H69" t="n">
-        <v>3.1e-34</v>
+        <v>1.79e-45</v>
       </c>
       <c r="I69" t="n">
-        <v>4.96e-33</v>
+        <v>2.86e-44</v>
       </c>
     </row>
     <row r="70">
@@ -7886,13 +7886,13 @@
         <v>0.82</v>
       </c>
       <c r="G70" t="n">
-        <v>0.707</v>
+        <v>0.8</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0293</v>
+        <v>0.769</v>
       </c>
       <c r="I70" t="n">
-        <v>0.067</v>
+        <v>0.929</v>
       </c>
     </row>
     <row r="71">
@@ -7923,13 +7923,13 @@
         <v>0.793</v>
       </c>
       <c r="G71" t="n">
-        <v>0.733</v>
+        <v>0.853</v>
       </c>
       <c r="H71" t="n">
-        <v>0.277</v>
+        <v>0.226</v>
       </c>
       <c r="I71" t="n">
-        <v>0.341</v>
+        <v>0.451</v>
       </c>
     </row>
     <row r="72">
@@ -7960,13 +7960,13 @@
         <v>0.86</v>
       </c>
       <c r="G72" t="n">
-        <v>0.767</v>
+        <v>0.847</v>
       </c>
       <c r="H72" t="n">
-        <v>0.0534</v>
+        <v>0.871</v>
       </c>
       <c r="I72" t="n">
-        <v>0.107</v>
+        <v>0.929</v>
       </c>
     </row>
     <row r="73">
@@ -7997,13 +7997,13 @@
         <v>0.967</v>
       </c>
       <c r="G73" t="n">
-        <v>0.92</v>
+        <v>0.927</v>
       </c>
       <c r="H73" t="n">
-        <v>0.132</v>
+        <v>0.198</v>
       </c>
       <c r="I73" t="n">
-        <v>0.197</v>
+        <v>0.451</v>
       </c>
     </row>
     <row r="74">
@@ -8034,13 +8034,13 @@
         <v>0.66</v>
       </c>
       <c r="G74" t="n">
-        <v>0.613</v>
+        <v>0.753</v>
       </c>
       <c r="H74" t="n">
-        <v>0.471</v>
+        <v>0.099</v>
       </c>
       <c r="I74" t="n">
-        <v>0.503</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="75">
@@ -8068,16 +8068,16 @@
         <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>0.86</v>
+        <v>0.853</v>
       </c>
       <c r="G75" t="n">
-        <v>0.78</v>
+        <v>0.893</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0977</v>
+        <v>0.386</v>
       </c>
       <c r="I75" t="n">
-        <v>0.174</v>
+        <v>0.617</v>
       </c>
     </row>
     <row r="76">
@@ -8108,13 +8108,13 @@
         <v>0.707</v>
       </c>
       <c r="G76" t="n">
-        <v>0.653</v>
+        <v>0.76</v>
       </c>
       <c r="H76" t="n">
-        <v>0.386</v>
+        <v>0.361</v>
       </c>
       <c r="I76" t="n">
-        <v>0.442</v>
+        <v>0.617</v>
       </c>
     </row>
     <row r="77">
@@ -8145,13 +8145,13 @@
         <v>0.88</v>
       </c>
       <c r="G77" t="n">
-        <v>0.747</v>
+        <v>0.847</v>
       </c>
       <c r="H77" t="n">
-        <v>0.00458</v>
+        <v>0.502</v>
       </c>
       <c r="I77" t="n">
-        <v>0.0183</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="78">
@@ -8182,13 +8182,13 @@
         <v>0.98</v>
       </c>
       <c r="G78" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.947</v>
       </c>
       <c r="H78" t="n">
-        <v>0.138</v>
+        <v>0.218</v>
       </c>
       <c r="I78" t="n">
-        <v>0.197</v>
+        <v>0.451</v>
       </c>
     </row>
     <row r="79">
@@ -8219,13 +8219,13 @@
         <v>0.873</v>
       </c>
       <c r="G79" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.793</v>
       </c>
       <c r="H79" t="n">
-        <v>0.000142</v>
+        <v>0.0877</v>
       </c>
       <c r="I79" t="n">
-        <v>0.00114</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="80">
@@ -8256,13 +8256,13 @@
         <v>0.6870000000000001</v>
       </c>
       <c r="G80" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="H80" t="n">
-        <v>0.148</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>0.197</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -8293,13 +8293,13 @@
         <v>0.627</v>
       </c>
       <c r="G81" t="n">
-        <v>0.607</v>
+        <v>0.647</v>
       </c>
       <c r="H81" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.929</v>
       </c>
     </row>
     <row r="82">
@@ -8330,13 +8330,13 @@
         <v>0.917</v>
       </c>
       <c r="G82" t="n">
-        <v>0.889</v>
+        <v>0.887</v>
       </c>
       <c r="H82" t="n">
-        <v>0.613</v>
+        <v>0.638</v>
       </c>
       <c r="I82" t="n">
-        <v>0.754</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="83">
@@ -8367,13 +8367,13 @@
         <v>0.509</v>
       </c>
       <c r="G83" t="n">
-        <v>0.913</v>
+        <v>0.923</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0006890000000000001</v>
+        <v>0.000325</v>
       </c>
       <c r="I83" t="n">
-        <v>0.00368</v>
+        <v>0.00173</v>
       </c>
     </row>
     <row r="84">
@@ -8404,13 +8404,13 @@
         <v>0.931</v>
       </c>
       <c r="G84" t="n">
-        <v>0.724</v>
+        <v>0.778</v>
       </c>
       <c r="H84" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.165</v>
       </c>
       <c r="I84" t="n">
-        <v>0.18</v>
+        <v>0.293</v>
       </c>
     </row>
     <row r="85">
@@ -8444,10 +8444,10 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>7.68e-21</v>
+        <v>8.13e-23</v>
       </c>
       <c r="I85" t="n">
-        <v>1.23e-19</v>
+        <v>1.3e-21</v>
       </c>
     </row>
     <row r="86">
@@ -8478,13 +8478,13 @@
         <v>0.963</v>
       </c>
       <c r="G86" t="n">
-        <v>0.901</v>
+        <v>0.899</v>
       </c>
       <c r="H86" t="n">
-        <v>0.191</v>
+        <v>0.138</v>
       </c>
       <c r="I86" t="n">
-        <v>0.335</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="87">
@@ -8515,13 +8515,13 @@
         <v>0.969</v>
       </c>
       <c r="G87" t="n">
-        <v>0.842</v>
+        <v>0.857</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0209</v>
+        <v>0.0286</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0557</v>
+        <v>0.0764</v>
       </c>
     </row>
     <row r="88">
@@ -8552,13 +8552,13 @@
         <v>0.957</v>
       </c>
       <c r="G88" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0101</v>
+        <v>0.00489</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0324</v>
+        <v>0.0195</v>
       </c>
     </row>
     <row r="89">
@@ -8589,13 +8589,13 @@
         <v>0.833</v>
       </c>
       <c r="G89" t="n">
-        <v>0.286</v>
+        <v>0.375</v>
       </c>
       <c r="H89" t="n">
-        <v>0.103</v>
+        <v>0.138</v>
       </c>
       <c r="I89" t="n">
-        <v>0.205</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="90">
@@ -8626,13 +8626,13 @@
         <v>0.987</v>
       </c>
       <c r="G90" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.949</v>
       </c>
       <c r="H90" t="n">
-        <v>0.21</v>
+        <v>0.233</v>
       </c>
       <c r="I90" t="n">
-        <v>0.335</v>
+        <v>0.373</v>
       </c>
     </row>
     <row r="91">
@@ -8660,10 +8660,10 @@
         <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>0.929</v>
+        <v>0.928</v>
       </c>
       <c r="G91" t="n">
-        <v>0.929</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H91" t="n">
         <v>1</v>
@@ -8700,13 +8700,13 @@
         <v>0.887</v>
       </c>
       <c r="G92" t="n">
-        <v>0.833</v>
+        <v>0.85</v>
       </c>
       <c r="H92" t="n">
-        <v>0.441</v>
+        <v>0.623</v>
       </c>
       <c r="I92" t="n">
-        <v>0.589</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="93">
@@ -8737,13 +8737,13 @@
         <v>0.957</v>
       </c>
       <c r="G93" t="n">
-        <v>0.735</v>
+        <v>0.788</v>
       </c>
       <c r="H93" t="n">
-        <v>0.00382</v>
+        <v>0.0128</v>
       </c>
       <c r="I93" t="n">
-        <v>0.0153</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="94">
@@ -8774,13 +8774,13 @@
         <v>0.875</v>
       </c>
       <c r="G94" t="n">
-        <v>0.8</v>
+        <v>0.724</v>
       </c>
       <c r="H94" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.308</v>
       </c>
       <c r="I94" t="n">
-        <v>0.782</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="95">
@@ -8811,13 +8811,13 @@
         <v>0.966</v>
       </c>
       <c r="G95" t="n">
-        <v>0.676</v>
+        <v>0.728</v>
       </c>
       <c r="H95" t="n">
-        <v>1.58e-05</v>
+        <v>0.000136</v>
       </c>
       <c r="I95" t="n">
-        <v>0.000126</v>
+        <v>0.00109</v>
       </c>
     </row>
     <row r="96">
@@ -8848,13 +8848,13 @@
         <v>0.635</v>
       </c>
       <c r="G96" t="n">
-        <v>0.556</v>
+        <v>0.623</v>
       </c>
       <c r="H96" t="n">
-        <v>0.384</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>0.5590000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -8885,13 +8885,13 @@
         <v>0.51</v>
       </c>
       <c r="G97" t="n">
-        <v>0.481</v>
+        <v>0.532</v>
       </c>
       <c r="H97" t="n">
-        <v>0.843</v>
+        <v>0.85</v>
       </c>
       <c r="I97" t="n">
-        <v>0.899</v>
+        <v>0.971</v>
       </c>
     </row>
     <row r="98">
@@ -8922,13 +8922,13 @@
         <v>0.863</v>
       </c>
       <c r="G98" t="n">
-        <v>0.706</v>
+        <v>0.922</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0101</v>
+        <v>0.259</v>
       </c>
       <c r="I98" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.414</v>
       </c>
     </row>
     <row r="99">
@@ -8959,13 +8959,13 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0.778</v>
+        <v>0.889</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0229</v>
+        <v>0.236</v>
       </c>
       <c r="I99" t="n">
-        <v>0.117</v>
+        <v>0.414</v>
       </c>
     </row>
     <row r="100">
@@ -8996,13 +8996,13 @@
         <v>0.964</v>
       </c>
       <c r="G100" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0511</v>
+        <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>0.117</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -9070,13 +9070,13 @@
         <v>0.762</v>
       </c>
       <c r="G102" t="n">
-        <v>0.634</v>
+        <v>0.792</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0655</v>
+        <v>0.735</v>
       </c>
       <c r="I102" t="n">
-        <v>0.131</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="103">
@@ -9107,13 +9107,13 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="G103" t="n">
-        <v>0.696</v>
+        <v>0.913</v>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>0.000174</v>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>0.00139</v>
       </c>
     </row>
     <row r="104">
@@ -9144,13 +9144,13 @@
         <v>0.788</v>
       </c>
       <c r="G104" t="n">
-        <v>0.765</v>
+        <v>0.953</v>
       </c>
       <c r="H104" t="n">
-        <v>0.854</v>
+        <v>0.00231</v>
       </c>
       <c r="I104" t="n">
-        <v>0.976</v>
+        <v>0.0123</v>
       </c>
     </row>
     <row r="105">
@@ -9181,13 +9181,13 @@
         <v>0.556</v>
       </c>
       <c r="G105" t="n">
-        <v>0.222</v>
+        <v>0.333</v>
       </c>
       <c r="H105" t="n">
-        <v>0.335</v>
+        <v>0.637</v>
       </c>
       <c r="I105" t="n">
-        <v>0.514</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="106">
@@ -9218,13 +9218,13 @@
         <v>0.603</v>
       </c>
       <c r="G106" t="n">
-        <v>0.579</v>
+        <v>0.746</v>
       </c>
       <c r="H106" t="n">
-        <v>0.798</v>
+        <v>0.022</v>
       </c>
       <c r="I106" t="n">
-        <v>0.976</v>
+        <v>0.0703</v>
       </c>
     </row>
     <row r="107">
@@ -9252,16 +9252,16 @@
         <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>0.802</v>
+        <v>0.79</v>
       </c>
       <c r="G107" t="n">
-        <v>0.642</v>
+        <v>0.864</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0347</v>
+        <v>0.299</v>
       </c>
       <c r="I107" t="n">
-        <v>0.117</v>
+        <v>0.435</v>
       </c>
     </row>
     <row r="108">
@@ -9292,13 +9292,13 @@
         <v>0.598</v>
       </c>
       <c r="G108" t="n">
-        <v>0.543</v>
+        <v>0.739</v>
       </c>
       <c r="H108" t="n">
-        <v>0.551</v>
+        <v>0.0598</v>
       </c>
       <c r="I108" t="n">
-        <v>0.735</v>
+        <v>0.159</v>
       </c>
     </row>
     <row r="109">
@@ -9329,13 +9329,13 @@
         <v>0.738</v>
       </c>
       <c r="G109" t="n">
-        <v>0.59</v>
+        <v>0.852</v>
       </c>
       <c r="H109" t="n">
-        <v>0.125</v>
+        <v>0.178</v>
       </c>
       <c r="I109" t="n">
-        <v>0.222</v>
+        <v>0.379</v>
       </c>
     </row>
     <row r="110">
@@ -9366,13 +9366,13 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0.762</v>
+        <v>1</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0478</v>
+        <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>0.117</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -9403,13 +9403,13 @@
         <v>0.767</v>
       </c>
       <c r="G111" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.918</v>
       </c>
       <c r="H111" t="n">
-        <v>0.354</v>
+        <v>0.0216</v>
       </c>
       <c r="I111" t="n">
-        <v>0.514</v>
+        <v>0.0703</v>
       </c>
     </row>
     <row r="112">
@@ -9440,13 +9440,13 @@
         <v>0.701</v>
       </c>
       <c r="G112" t="n">
-        <v>0.522</v>
+        <v>0.716</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0507</v>
+        <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>0.117</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -9477,13 +9477,13 @@
         <v>0.439</v>
       </c>
       <c r="G113" t="n">
-        <v>0.439</v>
+        <v>0.579</v>
       </c>
       <c r="H113" t="n">
-        <v>1</v>
+        <v>0.19</v>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>0.379</v>
       </c>
     </row>
     <row r="114">
@@ -9514,13 +9514,13 @@
         <v>0.889</v>
       </c>
       <c r="G114" t="n">
-        <v>0.787</v>
+        <v>0.904</v>
       </c>
       <c r="H114" t="n">
-        <v>0.00777</v>
+        <v>0.629</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0249</v>
+        <v>0.839</v>
       </c>
     </row>
     <row r="115">
@@ -9551,13 +9551,13 @@
         <v>0.675</v>
       </c>
       <c r="G115" t="n">
-        <v>0.84</v>
+        <v>0.906</v>
       </c>
       <c r="H115" t="n">
-        <v>0.042</v>
+        <v>0.00293</v>
       </c>
       <c r="I115" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0234</v>
       </c>
     </row>
     <row r="116">
@@ -9588,13 +9588,13 @@
         <v>0.947</v>
       </c>
       <c r="G116" t="n">
-        <v>0.737</v>
+        <v>0.875</v>
       </c>
       <c r="H116" t="n">
-        <v>0.00372</v>
+        <v>0.214</v>
       </c>
       <c r="I116" t="n">
-        <v>0.0149</v>
+        <v>0.411</v>
       </c>
     </row>
     <row r="117">
@@ -9628,10 +9628,10 @@
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>5.49e-34</v>
+        <v>7.32e-37</v>
       </c>
       <c r="I117" t="n">
-        <v>8.79e-33</v>
+        <v>1.17e-35</v>
       </c>
     </row>
     <row r="118">
@@ -9662,13 +9662,13 @@
         <v>0.851</v>
       </c>
       <c r="G118" t="n">
-        <v>0.744</v>
+        <v>0.842</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0165</v>
+        <v>0.886</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0439</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="119">
@@ -9699,13 +9699,13 @@
         <v>0.803</v>
       </c>
       <c r="G119" t="n">
-        <v>0.762</v>
+        <v>0.884</v>
       </c>
       <c r="H119" t="n">
-        <v>0.421</v>
+        <v>0.0372</v>
       </c>
       <c r="I119" t="n">
-        <v>0.481</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="120">
@@ -9736,13 +9736,13 @@
         <v>0.865</v>
       </c>
       <c r="G120" t="n">
-        <v>0.788</v>
+        <v>0.876</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0785</v>
+        <v>0.871</v>
       </c>
       <c r="I120" t="n">
-        <v>0.105</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="121">
@@ -9773,13 +9773,13 @@
         <v>0.667</v>
       </c>
       <c r="G121" t="n">
-        <v>0.25</v>
+        <v>0.353</v>
       </c>
       <c r="H121" t="n">
-        <v>0.032</v>
+        <v>0.156</v>
       </c>
       <c r="I121" t="n">
-        <v>0.062</v>
+        <v>0.411</v>
       </c>
     </row>
     <row r="122">
@@ -9810,13 +9810,13 @@
         <v>0.749</v>
       </c>
       <c r="G122" t="n">
-        <v>0.716</v>
+        <v>0.836</v>
       </c>
       <c r="H122" t="n">
-        <v>0.502</v>
+        <v>0.031</v>
       </c>
       <c r="I122" t="n">
-        <v>0.536</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="123">
@@ -9844,16 +9844,16 @@
         <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>0.861</v>
+        <v>0.853</v>
       </c>
       <c r="G123" t="n">
-        <v>0.759</v>
+        <v>0.897</v>
       </c>
       <c r="H123" t="n">
-        <v>0.034</v>
+        <v>0.299</v>
       </c>
       <c r="I123" t="n">
-        <v>0.062</v>
+        <v>0.478</v>
       </c>
     </row>
     <row r="124">
@@ -9884,13 +9884,13 @@
         <v>0.714</v>
       </c>
       <c r="G124" t="n">
-        <v>0.658</v>
+        <v>0.791</v>
       </c>
       <c r="H124" t="n">
-        <v>0.325</v>
+        <v>0.123</v>
       </c>
       <c r="I124" t="n">
-        <v>0.4</v>
+        <v>0.392</v>
       </c>
     </row>
     <row r="125">
@@ -9921,13 +9921,13 @@
         <v>0.833</v>
       </c>
       <c r="G125" t="n">
-        <v>0.655</v>
+        <v>0.819</v>
       </c>
       <c r="H125" t="n">
-        <v>0.00311</v>
+        <v>0.864</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0149</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="126">
@@ -9958,13 +9958,13 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G126" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0608</v>
+        <v>0.206</v>
       </c>
       <c r="I126" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.411</v>
       </c>
     </row>
     <row r="127">
@@ -9995,13 +9995,13 @@
         <v>0.855</v>
       </c>
       <c r="G127" t="n">
-        <v>0.68</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H127" t="n">
-        <v>0.000675</v>
+        <v>0.353</v>
       </c>
       <c r="I127" t="n">
-        <v>0.0054</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="128">
@@ -10032,13 +10032,13 @@
         <v>0.667</v>
       </c>
       <c r="G128" t="n">
-        <v>0.538</v>
+        <v>0.667</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0349</v>
+        <v>1</v>
       </c>
       <c r="I128" t="n">
-        <v>0.062</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -10069,13 +10069,13 @@
         <v>0.472</v>
       </c>
       <c r="G129" t="n">
-        <v>0.459</v>
+        <v>0.555</v>
       </c>
       <c r="H129" t="n">
-        <v>0.892</v>
+        <v>0.231</v>
       </c>
       <c r="I129" t="n">
-        <v>0.892</v>
+        <v>0.411</v>
       </c>
     </row>
     <row r="130">
@@ -10436,16 +10436,16 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>0.86</v>
+        <v>0.853</v>
       </c>
       <c r="G139" t="n">
         <v>0.773</v>
       </c>
       <c r="H139" t="n">
-        <v>0.0727</v>
+        <v>0.103</v>
       </c>
       <c r="I139" t="n">
-        <v>0.26</v>
+        <v>0.328</v>
       </c>
     </row>
     <row r="140">
@@ -10482,7 +10482,7 @@
         <v>0.0813</v>
       </c>
       <c r="I140" t="n">
-        <v>0.26</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="141">
@@ -11028,7 +11028,7 @@
         <v>10</v>
       </c>
       <c r="F155" t="n">
-        <v>0.929</v>
+        <v>0.928</v>
       </c>
       <c r="G155" t="n">
         <v>0.885</v>
@@ -11518,7 +11518,7 @@
         <v>0.0919</v>
       </c>
       <c r="I168" t="n">
-        <v>0.294</v>
+        <v>0.356</v>
       </c>
     </row>
     <row r="169">
@@ -11620,16 +11620,16 @@
         <v>10</v>
       </c>
       <c r="F171" t="n">
-        <v>0.802</v>
+        <v>0.79</v>
       </c>
       <c r="G171" t="n">
         <v>0.667</v>
       </c>
       <c r="H171" t="n">
-        <v>0.0745</v>
+        <v>0.111</v>
       </c>
       <c r="I171" t="n">
-        <v>0.294</v>
+        <v>0.356</v>
       </c>
     </row>
     <row r="172">
@@ -12212,16 +12212,16 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>0.861</v>
+        <v>0.853</v>
       </c>
       <c r="G187" t="n">
         <v>0.761</v>
       </c>
       <c r="H187" t="n">
-        <v>0.0357</v>
+        <v>0.0532</v>
       </c>
       <c r="I187" t="n">
-        <v>0.111</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="188">
@@ -12443,7 +12443,7 @@
         <v>0.0416</v>
       </c>
       <c r="I193" t="n">
-        <v>0.111</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="194">
@@ -12474,13 +12474,13 @@
         <v>0.853</v>
       </c>
       <c r="G194" t="n">
-        <v>0.753</v>
+        <v>0.867</v>
       </c>
       <c r="H194" t="n">
-        <v>0.0414</v>
+        <v>0.868</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0828</v>
+        <v>0.992</v>
       </c>
     </row>
     <row r="195">
@@ -12517,7 +12517,7 @@
         <v>0.0035</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0187</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="196">
@@ -12548,13 +12548,13 @@
         <v>0.98</v>
       </c>
       <c r="G196" t="n">
-        <v>0.913</v>
+        <v>0.96</v>
       </c>
       <c r="H196" t="n">
-        <v>0.018</v>
+        <v>0.501</v>
       </c>
       <c r="I196" t="n">
-        <v>0.0481</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="197">
@@ -12585,13 +12585,13 @@
         <v>0.993</v>
       </c>
       <c r="G197" t="n">
-        <v>0.447</v>
+        <v>0.313</v>
       </c>
       <c r="H197" t="n">
-        <v>1.3e-30</v>
+        <v>1.15e-41</v>
       </c>
       <c r="I197" t="n">
-        <v>2.08e-29</v>
+        <v>1.84e-40</v>
       </c>
     </row>
     <row r="198">
@@ -12622,13 +12622,13 @@
         <v>0.82</v>
       </c>
       <c r="G198" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="H198" t="n">
-        <v>0.0543</v>
+        <v>1</v>
       </c>
       <c r="I198" t="n">
-        <v>0.094</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -12659,13 +12659,13 @@
         <v>0.793</v>
       </c>
       <c r="G199" t="n">
-        <v>0.753</v>
+        <v>0.873</v>
       </c>
       <c r="H199" t="n">
-        <v>0.491</v>
+        <v>0.0877</v>
       </c>
       <c r="I199" t="n">
-        <v>0.604</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="200">
@@ -12696,13 +12696,13 @@
         <v>0.86</v>
       </c>
       <c r="G200" t="n">
-        <v>0.773</v>
+        <v>0.867</v>
       </c>
       <c r="H200" t="n">
-        <v>0.0727</v>
+        <v>1</v>
       </c>
       <c r="I200" t="n">
-        <v>0.106</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -12733,13 +12733,13 @@
         <v>0.967</v>
       </c>
       <c r="G201" t="n">
-        <v>0.947</v>
+        <v>0.953</v>
       </c>
       <c r="H201" t="n">
-        <v>0.572</v>
+        <v>0.77</v>
       </c>
       <c r="I201" t="n">
-        <v>0.654</v>
+        <v>0.992</v>
       </c>
     </row>
     <row r="202">
@@ -12770,13 +12770,13 @@
         <v>0.66</v>
       </c>
       <c r="G202" t="n">
-        <v>0.547</v>
+        <v>0.68</v>
       </c>
       <c r="H202" t="n">
-        <v>0.0588</v>
+        <v>0.806</v>
       </c>
       <c r="I202" t="n">
-        <v>0.094</v>
+        <v>0.992</v>
       </c>
     </row>
     <row r="203">
@@ -12804,16 +12804,16 @@
         <v>10</v>
       </c>
       <c r="F203" t="n">
-        <v>0.86</v>
+        <v>0.853</v>
       </c>
       <c r="G203" t="n">
-        <v>0.733</v>
+        <v>0.833</v>
       </c>
       <c r="H203" t="n">
-        <v>0.00945</v>
+        <v>0.751</v>
       </c>
       <c r="I203" t="n">
-        <v>0.0325</v>
+        <v>0.992</v>
       </c>
     </row>
     <row r="204">
@@ -12844,13 +12844,13 @@
         <v>0.707</v>
       </c>
       <c r="G204" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.793</v>
       </c>
       <c r="H204" t="n">
-        <v>0.802</v>
+        <v>0.109</v>
       </c>
       <c r="I204" t="n">
-        <v>0.855</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="205">
@@ -12881,13 +12881,13 @@
         <v>0.88</v>
       </c>
       <c r="G205" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="H205" t="n">
-        <v>0.0102</v>
+        <v>0.406</v>
       </c>
       <c r="I205" t="n">
-        <v>0.0325</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="206">
@@ -12918,13 +12918,13 @@
         <v>0.98</v>
       </c>
       <c r="G206" t="n">
-        <v>0.92</v>
+        <v>0.947</v>
       </c>
       <c r="H206" t="n">
-        <v>0.0308</v>
+        <v>0.218</v>
       </c>
       <c r="I206" t="n">
-        <v>0.0704</v>
+        <v>0.581</v>
       </c>
     </row>
     <row r="207">
@@ -12955,13 +12955,13 @@
         <v>0.873</v>
       </c>
       <c r="G207" t="n">
-        <v>0.707</v>
+        <v>0.82</v>
       </c>
       <c r="H207" t="n">
-        <v>0.000595</v>
+        <v>0.262</v>
       </c>
       <c r="I207" t="n">
-        <v>0.00476</v>
+        <v>0.599</v>
       </c>
     </row>
     <row r="208">
@@ -12992,13 +12992,13 @@
         <v>0.6870000000000001</v>
       </c>
       <c r="G208" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.747</v>
       </c>
       <c r="H208" t="n">
-        <v>1</v>
+        <v>0.305</v>
       </c>
       <c r="I208" t="n">
-        <v>1</v>
+        <v>0.611</v>
       </c>
     </row>
     <row r="209">
@@ -13029,13 +13029,13 @@
         <v>0.627</v>
       </c>
       <c r="G209" t="n">
-        <v>0.707</v>
+        <v>0.72</v>
       </c>
       <c r="H209" t="n">
-        <v>0.178</v>
+        <v>0.109</v>
       </c>
       <c r="I209" t="n">
-        <v>0.237</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="210">
@@ -13066,13 +13066,13 @@
         <v>0.917</v>
       </c>
       <c r="G210" t="n">
-        <v>0.922</v>
+        <v>0.894</v>
       </c>
       <c r="H210" t="n">
-        <v>1</v>
+        <v>0.636</v>
       </c>
       <c r="I210" t="n">
-        <v>1</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="211">
@@ -13103,13 +13103,13 @@
         <v>0.509</v>
       </c>
       <c r="G211" t="n">
-        <v>0.875</v>
+        <v>0.821</v>
       </c>
       <c r="H211" t="n">
-        <v>0.00226</v>
+        <v>0.00792</v>
       </c>
       <c r="I211" t="n">
-        <v>0.012</v>
+        <v>0.0423</v>
       </c>
     </row>
     <row r="212">
@@ -13140,13 +13140,13 @@
         <v>0.931</v>
       </c>
       <c r="G212" t="n">
-        <v>0.826</v>
+        <v>0.867</v>
       </c>
       <c r="H212" t="n">
-        <v>0.387</v>
+        <v>0.671</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="213">
@@ -13177,13 +13177,13 @@
         <v>1</v>
       </c>
       <c r="G213" t="n">
-        <v>0.0308</v>
+        <v>0.0235</v>
       </c>
       <c r="H213" t="n">
-        <v>4.4e-18</v>
+        <v>3.18e-20</v>
       </c>
       <c r="I213" t="n">
-        <v>7.04e-17</v>
+        <v>5.08e-19</v>
       </c>
     </row>
     <row r="214">
@@ -13217,10 +13217,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="H214" t="n">
-        <v>0.702</v>
+        <v>0.72</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="215">
@@ -13251,13 +13251,13 @@
         <v>0.969</v>
       </c>
       <c r="G215" t="n">
-        <v>0.867</v>
+        <v>0.876</v>
       </c>
       <c r="H215" t="n">
-        <v>0.0362</v>
+        <v>0.0469</v>
       </c>
       <c r="I215" t="n">
-        <v>0.116</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="216">
@@ -13288,13 +13288,13 @@
         <v>0.957</v>
       </c>
       <c r="G216" t="n">
-        <v>0.881</v>
+        <v>0.874</v>
       </c>
       <c r="H216" t="n">
-        <v>0.123</v>
+        <v>0.0915</v>
       </c>
       <c r="I216" t="n">
-        <v>0.328</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="217">
@@ -13325,7 +13325,7 @@
         <v>0.833</v>
       </c>
       <c r="G217" t="n">
-        <v>0.667</v>
+        <v>0.75</v>
       </c>
       <c r="H217" t="n">
         <v>1</v>
@@ -13362,13 +13362,13 @@
         <v>0.987</v>
       </c>
       <c r="G218" t="n">
-        <v>0.953</v>
+        <v>0.964</v>
       </c>
       <c r="H218" t="n">
-        <v>0.329</v>
+        <v>0.622</v>
       </c>
       <c r="I218" t="n">
-        <v>0.527</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="219">
@@ -13396,10 +13396,10 @@
         <v>10</v>
       </c>
       <c r="F219" t="n">
-        <v>0.929</v>
+        <v>0.928</v>
       </c>
       <c r="G219" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="H219" t="n">
         <v>1</v>
@@ -13436,13 +13436,13 @@
         <v>0.887</v>
       </c>
       <c r="G220" t="n">
-        <v>0.909</v>
+        <v>0.907</v>
       </c>
       <c r="H220" t="n">
-        <v>0.767</v>
+        <v>0.781</v>
       </c>
       <c r="I220" t="n">
-        <v>0.945</v>
+        <v>0.892</v>
       </c>
     </row>
     <row r="221">
@@ -13473,13 +13473,13 @@
         <v>0.957</v>
       </c>
       <c r="G221" t="n">
-        <v>0.791</v>
+        <v>0.825</v>
       </c>
       <c r="H221" t="n">
-        <v>0.0227</v>
+        <v>0.0609</v>
       </c>
       <c r="I221" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="222">
@@ -13510,13 +13510,13 @@
         <v>0.875</v>
       </c>
       <c r="G222" t="n">
-        <v>0.714</v>
+        <v>0.741</v>
       </c>
       <c r="H222" t="n">
-        <v>0.267</v>
+        <v>0.3</v>
       </c>
       <c r="I222" t="n">
-        <v>0.527</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="223">
@@ -13547,13 +13547,13 @@
         <v>0.966</v>
       </c>
       <c r="G223" t="n">
-        <v>0.746</v>
+        <v>0.803</v>
       </c>
       <c r="H223" t="n">
-        <v>0.00107</v>
+        <v>0.00724</v>
       </c>
       <c r="I223" t="n">
-        <v>0.00859</v>
+        <v>0.0423</v>
       </c>
     </row>
     <row r="224">
@@ -13584,13 +13584,13 @@
         <v>0.635</v>
       </c>
       <c r="G224" t="n">
-        <v>0.738</v>
+        <v>0.784</v>
       </c>
       <c r="H224" t="n">
-        <v>0.306</v>
+        <v>0.0798</v>
       </c>
       <c r="I224" t="n">
-        <v>0.527</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="225">
@@ -13621,13 +13621,13 @@
         <v>0.51</v>
       </c>
       <c r="G225" t="n">
-        <v>0.676</v>
+        <v>0.674</v>
       </c>
       <c r="H225" t="n">
-        <v>0.185</v>
+        <v>0.139</v>
       </c>
       <c r="I225" t="n">
-        <v>0.423</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="226">
@@ -13658,13 +13658,13 @@
         <v>0.863</v>
       </c>
       <c r="G226" t="n">
-        <v>0.696</v>
+        <v>0.912</v>
       </c>
       <c r="H226" t="n">
-        <v>0.00649</v>
+        <v>0.376</v>
       </c>
       <c r="I226" t="n">
-        <v>0.0333</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="227">
@@ -13695,13 +13695,13 @@
         <v>1</v>
       </c>
       <c r="G227" t="n">
-        <v>0.778</v>
+        <v>0.852</v>
       </c>
       <c r="H227" t="n">
-        <v>0.0229</v>
+        <v>0.111</v>
       </c>
       <c r="I227" t="n">
-        <v>0.0524</v>
+        <v>0.355</v>
       </c>
     </row>
     <row r="228">
@@ -13732,13 +13732,13 @@
         <v>0.964</v>
       </c>
       <c r="G228" t="n">
-        <v>0.679</v>
+        <v>0.929</v>
       </c>
       <c r="H228" t="n">
-        <v>0.0116</v>
+        <v>1</v>
       </c>
       <c r="I228" t="n">
-        <v>0.0371</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -13806,13 +13806,13 @@
         <v>0.762</v>
       </c>
       <c r="G230" t="n">
-        <v>0.624</v>
+        <v>0.782</v>
       </c>
       <c r="H230" t="n">
-        <v>0.0469</v>
+        <v>0.867</v>
       </c>
       <c r="I230" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="231">
@@ -13843,13 +13843,13 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="G231" t="n">
-        <v>0.707</v>
+        <v>0.924</v>
       </c>
       <c r="H231" t="n">
-        <v>0.873</v>
+        <v>6.35e-05</v>
       </c>
       <c r="I231" t="n">
-        <v>0.931</v>
+        <v>0.000508</v>
       </c>
     </row>
     <row r="232">
@@ -13880,13 +13880,13 @@
         <v>0.788</v>
       </c>
       <c r="G232" t="n">
-        <v>0.694</v>
+        <v>0.894</v>
       </c>
       <c r="H232" t="n">
-        <v>0.22</v>
+        <v>0.0919</v>
       </c>
       <c r="I232" t="n">
-        <v>0.293</v>
+        <v>0.355</v>
       </c>
     </row>
     <row r="233">
@@ -13917,13 +13917,13 @@
         <v>0.556</v>
       </c>
       <c r="G233" t="n">
-        <v>0.222</v>
+        <v>0.333</v>
       </c>
       <c r="H233" t="n">
-        <v>0.335</v>
+        <v>0.637</v>
       </c>
       <c r="I233" t="n">
-        <v>0.412</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="234">
@@ -13954,13 +13954,13 @@
         <v>0.603</v>
       </c>
       <c r="G234" t="n">
-        <v>0.484</v>
+        <v>0.643</v>
       </c>
       <c r="H234" t="n">
-        <v>0.0764</v>
+        <v>0.603</v>
       </c>
       <c r="I234" t="n">
-        <v>0.111</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="235">
@@ -13988,16 +13988,16 @@
         <v>10</v>
       </c>
       <c r="F235" t="n">
-        <v>0.802</v>
+        <v>0.79</v>
       </c>
       <c r="G235" t="n">
-        <v>0.543</v>
+        <v>0.741</v>
       </c>
       <c r="H235" t="n">
-        <v>0.000731</v>
+        <v>0.578</v>
       </c>
       <c r="I235" t="n">
-        <v>0.00585</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="236">
@@ -14028,13 +14028,13 @@
         <v>0.598</v>
       </c>
       <c r="G236" t="n">
-        <v>0.543</v>
+        <v>0.739</v>
       </c>
       <c r="H236" t="n">
-        <v>0.551</v>
+        <v>0.0598</v>
       </c>
       <c r="I236" t="n">
-        <v>0.63</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="237">
@@ -14065,13 +14065,13 @@
         <v>0.738</v>
       </c>
       <c r="G237" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="H237" t="n">
-        <v>0.0575</v>
+        <v>0.834</v>
       </c>
       <c r="I237" t="n">
-        <v>0.092</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="238">
@@ -14102,13 +14102,13 @@
         <v>1</v>
       </c>
       <c r="G238" t="n">
-        <v>0.714</v>
+        <v>0.952</v>
       </c>
       <c r="H238" t="n">
-        <v>0.0207</v>
+        <v>1</v>
       </c>
       <c r="I238" t="n">
-        <v>0.0524</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239">
@@ -14139,13 +14139,13 @@
         <v>0.767</v>
       </c>
       <c r="G239" t="n">
-        <v>0.603</v>
+        <v>0.836</v>
       </c>
       <c r="H239" t="n">
-        <v>0.0494</v>
+        <v>0.407</v>
       </c>
       <c r="I239" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="240">
@@ -14176,13 +14176,13 @@
         <v>0.701</v>
       </c>
       <c r="G240" t="n">
-        <v>0.463</v>
+        <v>0.597</v>
       </c>
       <c r="H240" t="n">
-        <v>0.00834</v>
+        <v>0.277</v>
       </c>
       <c r="I240" t="n">
-        <v>0.0333</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="241">
@@ -14213,13 +14213,13 @@
         <v>0.439</v>
       </c>
       <c r="G241" t="n">
-        <v>0.439</v>
+        <v>0.509</v>
       </c>
       <c r="H241" t="n">
-        <v>1</v>
+        <v>0.574</v>
       </c>
       <c r="I241" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="242">
@@ -14250,13 +14250,13 @@
         <v>0.889</v>
       </c>
       <c r="G242" t="n">
-        <v>0.793</v>
+        <v>0.903</v>
       </c>
       <c r="H242" t="n">
-        <v>0.0153</v>
+        <v>0.745</v>
       </c>
       <c r="I242" t="n">
-        <v>0.035</v>
+        <v>0.851</v>
       </c>
     </row>
     <row r="243">
@@ -14287,13 +14287,13 @@
         <v>0.675</v>
       </c>
       <c r="G243" t="n">
-        <v>0.824</v>
+        <v>0.836</v>
       </c>
       <c r="H243" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0456</v>
       </c>
       <c r="I243" t="n">
-        <v>0.103</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="244">
@@ -14324,13 +14324,13 @@
         <v>0.947</v>
       </c>
       <c r="G244" t="n">
-        <v>0.745</v>
+        <v>0.897</v>
       </c>
       <c r="H244" t="n">
-        <v>0.00534</v>
+        <v>0.49</v>
       </c>
       <c r="I244" t="n">
-        <v>0.0171</v>
+        <v>0.794</v>
       </c>
     </row>
     <row r="245">
@@ -14361,13 +14361,13 @@
         <v>0.977</v>
       </c>
       <c r="G245" t="n">
-        <v>0.046</v>
+        <v>0.0374</v>
       </c>
       <c r="H245" t="n">
-        <v>2.7e-28</v>
+        <v>2.2e-31</v>
       </c>
       <c r="I245" t="n">
-        <v>4.32e-27</v>
+        <v>3.52e-30</v>
       </c>
     </row>
     <row r="246">
@@ -14398,13 +14398,13 @@
         <v>0.851</v>
       </c>
       <c r="G246" t="n">
-        <v>0.75</v>
+        <v>0.854</v>
       </c>
       <c r="H246" t="n">
-        <v>0.022</v>
+        <v>1</v>
       </c>
       <c r="I246" t="n">
-        <v>0.044</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
@@ -14435,13 +14435,13 @@
         <v>0.803</v>
       </c>
       <c r="G247" t="n">
-        <v>0.778</v>
+        <v>0.899</v>
       </c>
       <c r="H247" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.0136</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="248">
@@ -14472,13 +14472,13 @@
         <v>0.865</v>
       </c>
       <c r="G248" t="n">
-        <v>0.776</v>
+        <v>0.884</v>
       </c>
       <c r="H248" t="n">
-        <v>0.0529</v>
+        <v>0.62</v>
       </c>
       <c r="I248" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.794</v>
       </c>
     </row>
     <row r="249">
@@ -14509,13 +14509,13 @@
         <v>0.667</v>
       </c>
       <c r="G249" t="n">
-        <v>0.333</v>
+        <v>0.462</v>
       </c>
       <c r="H249" t="n">
-        <v>0.128</v>
+        <v>0.445</v>
       </c>
       <c r="I249" t="n">
-        <v>0.158</v>
+        <v>0.794</v>
       </c>
     </row>
     <row r="250">
@@ -14546,13 +14546,13 @@
         <v>0.749</v>
       </c>
       <c r="G250" t="n">
-        <v>0.642</v>
+        <v>0.771</v>
       </c>
       <c r="H250" t="n">
-        <v>0.0278</v>
+        <v>0.645</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0494</v>
+        <v>0.794</v>
       </c>
     </row>
     <row r="251">
@@ -14580,16 +14580,16 @@
         <v>10</v>
       </c>
       <c r="F251" t="n">
-        <v>0.861</v>
+        <v>0.853</v>
       </c>
       <c r="G251" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.828</v>
       </c>
       <c r="H251" t="n">
-        <v>0.000742</v>
+        <v>0.634</v>
       </c>
       <c r="I251" t="n">
-        <v>0.00396</v>
+        <v>0.794</v>
       </c>
     </row>
     <row r="252">
@@ -14620,13 +14620,13 @@
         <v>0.714</v>
       </c>
       <c r="G252" t="n">
-        <v>0.68</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H252" t="n">
-        <v>0.533</v>
+        <v>0.0358</v>
       </c>
       <c r="I252" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="253">
@@ -14657,13 +14657,13 @@
         <v>0.833</v>
       </c>
       <c r="G253" t="n">
-        <v>0.654</v>
+        <v>0.797</v>
       </c>
       <c r="H253" t="n">
-        <v>0.00428</v>
+        <v>0.499</v>
       </c>
       <c r="I253" t="n">
-        <v>0.0171</v>
+        <v>0.794</v>
       </c>
     </row>
     <row r="254">
@@ -14694,13 +14694,13 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G254" t="n">
-        <v>0.714</v>
+        <v>0.833</v>
       </c>
       <c r="H254" t="n">
-        <v>0.009679999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="I254" t="n">
-        <v>0.0258</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="255">
@@ -14731,13 +14731,13 @@
         <v>0.855</v>
       </c>
       <c r="G255" t="n">
-        <v>0.667</v>
+        <v>0.819</v>
       </c>
       <c r="H255" t="n">
-        <v>0.00047</v>
+        <v>0.425</v>
       </c>
       <c r="I255" t="n">
-        <v>0.00376</v>
+        <v>0.794</v>
       </c>
     </row>
     <row r="256">
@@ -14768,13 +14768,13 @@
         <v>0.667</v>
       </c>
       <c r="G256" t="n">
-        <v>0.569</v>
+        <v>0.678</v>
       </c>
       <c r="H256" t="n">
-        <v>0.117</v>
+        <v>0.895</v>
       </c>
       <c r="I256" t="n">
-        <v>0.156</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="257">
@@ -14805,13 +14805,13 @@
         <v>0.472</v>
       </c>
       <c r="G257" t="n">
-        <v>0.532</v>
+        <v>0.58</v>
       </c>
       <c r="H257" t="n">
-        <v>0.479</v>
+        <v>0.127</v>
       </c>
       <c r="I257" t="n">
-        <v>0.547</v>
+        <v>0.407</v>
       </c>
     </row>
     <row r="258">
@@ -15172,13 +15172,13 @@
         <v>10</v>
       </c>
       <c r="F267" t="n">
-        <v>0.86</v>
+        <v>0.853</v>
       </c>
       <c r="G267" t="n">
-        <v>0.88</v>
+        <v>0.873</v>
       </c>
       <c r="H267" t="n">
-        <v>0.732</v>
+        <v>0.737</v>
       </c>
       <c r="I267" t="n">
         <v>1</v>
@@ -15764,13 +15764,13 @@
         <v>10</v>
       </c>
       <c r="F283" t="n">
-        <v>0.929</v>
+        <v>0.928</v>
       </c>
       <c r="G283" t="n">
         <v>0.97</v>
       </c>
       <c r="H283" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="I283" t="n">
         <v>0.642</v>
@@ -16356,10 +16356,10 @@
         <v>10</v>
       </c>
       <c r="F299" t="n">
-        <v>0.802</v>
+        <v>0.79</v>
       </c>
       <c r="G299" t="n">
-        <v>0.802</v>
+        <v>0.79</v>
       </c>
       <c r="H299" t="n">
         <v>1</v>
@@ -16948,13 +16948,13 @@
         <v>10</v>
       </c>
       <c r="F315" t="n">
-        <v>0.861</v>
+        <v>0.853</v>
       </c>
       <c r="G315" t="n">
-        <v>0.878</v>
+        <v>0.871</v>
       </c>
       <c r="H315" t="n">
-        <v>0.732</v>
+        <v>0.738</v>
       </c>
       <c r="I315" t="n">
         <v>0.987</v>
@@ -17210,13 +17210,13 @@
         <v>0.853</v>
       </c>
       <c r="G322" t="n">
-        <v>0.74</v>
+        <v>0.873</v>
       </c>
       <c r="H322" t="n">
-        <v>0.0212</v>
+        <v>0.737</v>
       </c>
       <c r="I322" t="n">
-        <v>0.0849</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="323">
@@ -17247,13 +17247,13 @@
         <v>0.827</v>
       </c>
       <c r="G323" t="n">
-        <v>0.913</v>
+        <v>0.927</v>
       </c>
       <c r="H323" t="n">
-        <v>0.0383</v>
+        <v>0.0131</v>
       </c>
       <c r="I323" t="n">
-        <v>0.0917</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="324">
@@ -17284,13 +17284,13 @@
         <v>0.98</v>
       </c>
       <c r="G324" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="H324" t="n">
-        <v>0.0853</v>
+        <v>1</v>
       </c>
       <c r="I324" t="n">
-        <v>0.171</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">
@@ -17321,13 +17321,13 @@
         <v>0.993</v>
       </c>
       <c r="G325" t="n">
-        <v>0.453</v>
+        <v>0.347</v>
       </c>
       <c r="H325" t="n">
-        <v>4.1e-30</v>
+        <v>1.09e-38</v>
       </c>
       <c r="I325" t="n">
-        <v>6.560000000000001e-29</v>
+        <v>1.75e-37</v>
       </c>
     </row>
     <row r="326">
@@ -17358,13 +17358,13 @@
         <v>0.82</v>
       </c>
       <c r="G326" t="n">
-        <v>0.713</v>
+        <v>0.827</v>
       </c>
       <c r="H326" t="n">
-        <v>0.0401</v>
+        <v>1</v>
       </c>
       <c r="I326" t="n">
-        <v>0.0917</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
@@ -17395,13 +17395,13 @@
         <v>0.793</v>
       </c>
       <c r="G327" t="n">
-        <v>0.747</v>
+        <v>0.86</v>
       </c>
       <c r="H327" t="n">
-        <v>0.411</v>
+        <v>0.169</v>
       </c>
       <c r="I327" t="n">
-        <v>0.505</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="328">
@@ -17432,13 +17432,13 @@
         <v>0.86</v>
       </c>
       <c r="G328" t="n">
-        <v>0.78</v>
+        <v>0.86</v>
       </c>
       <c r="H328" t="n">
-        <v>0.0977</v>
+        <v>1</v>
       </c>
       <c r="I328" t="n">
-        <v>0.174</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -17469,13 +17469,13 @@
         <v>0.967</v>
       </c>
       <c r="G329" t="n">
-        <v>0.927</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H329" t="n">
-        <v>0.198</v>
+        <v>0.289</v>
       </c>
       <c r="I329" t="n">
-        <v>0.316</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="330">
@@ -17506,13 +17506,13 @@
         <v>0.66</v>
       </c>
       <c r="G330" t="n">
-        <v>0.587</v>
+        <v>0.72</v>
       </c>
       <c r="H330" t="n">
-        <v>0.233</v>
+        <v>0.318</v>
       </c>
       <c r="I330" t="n">
-        <v>0.339</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="331">
@@ -17540,16 +17540,16 @@
         <v>10</v>
       </c>
       <c r="F331" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="G331" t="n">
         <v>0.86</v>
       </c>
-      <c r="G331" t="n">
-        <v>0.753</v>
-      </c>
       <c r="H331" t="n">
-        <v>0.0277</v>
+        <v>1</v>
       </c>
       <c r="I331" t="n">
-        <v>0.0888</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -17580,13 +17580,13 @@
         <v>0.707</v>
       </c>
       <c r="G332" t="n">
-        <v>0.66</v>
+        <v>0.767</v>
       </c>
       <c r="H332" t="n">
-        <v>0.457</v>
+        <v>0.294</v>
       </c>
       <c r="I332" t="n">
-        <v>0.522</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="333">
@@ -17617,13 +17617,13 @@
         <v>0.88</v>
       </c>
       <c r="G333" t="n">
-        <v>0.713</v>
+        <v>0.793</v>
       </c>
       <c r="H333" t="n">
-        <v>0.000506</v>
+        <v>0.0601</v>
       </c>
       <c r="I333" t="n">
-        <v>0.00405</v>
+        <v>0.321</v>
       </c>
     </row>
     <row r="334">
@@ -17654,13 +17654,13 @@
         <v>0.98</v>
       </c>
       <c r="G334" t="n">
-        <v>0.953</v>
+        <v>0.967</v>
       </c>
       <c r="H334" t="n">
-        <v>0.335</v>
+        <v>0.723</v>
       </c>
       <c r="I334" t="n">
-        <v>0.447</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="335">
@@ -17691,13 +17691,13 @@
         <v>0.873</v>
       </c>
       <c r="G335" t="n">
-        <v>0.727</v>
+        <v>0.827</v>
       </c>
       <c r="H335" t="n">
-        <v>0.00225</v>
+        <v>0.332</v>
       </c>
       <c r="I335" t="n">
-        <v>0.012</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="336">
@@ -17728,13 +17728,13 @@
         <v>0.6870000000000001</v>
       </c>
       <c r="G336" t="n">
-        <v>0.66</v>
+        <v>0.727</v>
       </c>
       <c r="H336" t="n">
-        <v>0.712</v>
+        <v>0.526</v>
       </c>
       <c r="I336" t="n">
-        <v>0.759</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="337">
@@ -17765,13 +17765,13 @@
         <v>0.627</v>
       </c>
       <c r="G337" t="n">
-        <v>0.64</v>
+        <v>0.667</v>
       </c>
       <c r="H337" t="n">
-        <v>0.905</v>
+        <v>0.546</v>
       </c>
       <c r="I337" t="n">
-        <v>0.905</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="338">
@@ -17802,13 +17802,13 @@
         <v>0.917</v>
       </c>
       <c r="G338" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="H338" t="n">
-        <v>0.779</v>
+        <v>0.782</v>
       </c>
       <c r="I338" t="n">
-        <v>0.906</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="339">
@@ -17839,13 +17839,13 @@
         <v>0.509</v>
       </c>
       <c r="G339" t="n">
-        <v>0.792</v>
+        <v>0.786</v>
       </c>
       <c r="H339" t="n">
-        <v>0.0245</v>
+        <v>0.0181</v>
       </c>
       <c r="I339" t="n">
-        <v>0.0982</v>
+        <v>0.0725</v>
       </c>
     </row>
     <row r="340">
@@ -17876,7 +17876,7 @@
         <v>0.931</v>
       </c>
       <c r="G340" t="n">
-        <v>0.95</v>
+        <v>0.963</v>
       </c>
       <c r="H340" t="n">
         <v>1</v>
@@ -17916,10 +17916,10 @@
         <v>0</v>
       </c>
       <c r="H341" t="n">
-        <v>7.33e-20</v>
+        <v>9.999999999999999e-22</v>
       </c>
       <c r="I341" t="n">
-        <v>1.17e-18</v>
+        <v>1.6e-20</v>
       </c>
     </row>
     <row r="342">
@@ -17950,13 +17950,13 @@
         <v>0.963</v>
       </c>
       <c r="G342" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="H342" t="n">
-        <v>0.701</v>
+        <v>0.721</v>
       </c>
       <c r="I342" t="n">
-        <v>0.906</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="343">
@@ -17987,13 +17987,13 @@
         <v>0.969</v>
       </c>
       <c r="G343" t="n">
-        <v>0.886</v>
+        <v>0.89</v>
       </c>
       <c r="H343" t="n">
-        <v>0.0987</v>
+        <v>0.0764</v>
       </c>
       <c r="I343" t="n">
-        <v>0.316</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="344">
@@ -18024,13 +18024,13 @@
         <v>0.957</v>
       </c>
       <c r="G344" t="n">
-        <v>0.882</v>
+        <v>0.864</v>
       </c>
       <c r="H344" t="n">
-        <v>0.126</v>
+        <v>0.0572</v>
       </c>
       <c r="I344" t="n">
-        <v>0.335</v>
+        <v>0.183</v>
       </c>
     </row>
     <row r="345">
@@ -18061,13 +18061,13 @@
         <v>0.833</v>
       </c>
       <c r="G345" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="H345" t="n">
-        <v>0.19</v>
+        <v>0.242</v>
       </c>
       <c r="I345" t="n">
-        <v>0.435</v>
+        <v>0.554</v>
       </c>
     </row>
     <row r="346">
@@ -18098,13 +18098,13 @@
         <v>0.987</v>
       </c>
       <c r="G346" t="n">
-        <v>0.957</v>
+        <v>0.967</v>
       </c>
       <c r="H346" t="n">
-        <v>0.347</v>
+        <v>0.625</v>
       </c>
       <c r="I346" t="n">
-        <v>0.695</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="347">
@@ -18132,16 +18132,16 @@
         <v>10</v>
       </c>
       <c r="F347" t="n">
-        <v>0.929</v>
+        <v>0.928</v>
       </c>
       <c r="G347" t="n">
-        <v>0.978</v>
+        <v>0.955</v>
       </c>
       <c r="H347" t="n">
-        <v>0.4</v>
+        <v>0.719</v>
       </c>
       <c r="I347" t="n">
-        <v>0.711</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="348">
@@ -18172,13 +18172,13 @@
         <v>0.887</v>
       </c>
       <c r="G348" t="n">
-        <v>0.825</v>
+        <v>0.852</v>
       </c>
       <c r="H348" t="n">
-        <v>0.446</v>
+        <v>0.624</v>
       </c>
       <c r="I348" t="n">
-        <v>0.713</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="349">
@@ -18209,13 +18209,13 @@
         <v>0.957</v>
       </c>
       <c r="G349" t="n">
-        <v>0.673</v>
+        <v>0.721</v>
       </c>
       <c r="H349" t="n">
-        <v>0.000277</v>
+        <v>0.00111</v>
       </c>
       <c r="I349" t="n">
-        <v>0.00214</v>
+        <v>0.00592</v>
       </c>
     </row>
     <row r="350">
@@ -18246,13 +18246,13 @@
         <v>0.875</v>
       </c>
       <c r="G350" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.833</v>
       </c>
       <c r="H350" t="n">
-        <v>0.638</v>
+        <v>1</v>
       </c>
       <c r="I350" t="n">
-        <v>0.906</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351">
@@ -18283,13 +18283,13 @@
         <v>0.966</v>
       </c>
       <c r="G351" t="n">
-        <v>0.735</v>
+        <v>0.77</v>
       </c>
       <c r="H351" t="n">
-        <v>0.000401</v>
+        <v>0.000887</v>
       </c>
       <c r="I351" t="n">
-        <v>0.00214</v>
+        <v>0.00592</v>
       </c>
     </row>
     <row r="352">
@@ -18320,13 +18320,13 @@
         <v>0.635</v>
       </c>
       <c r="G352" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="H352" t="n">
-        <v>0.849</v>
+        <v>0.368</v>
       </c>
       <c r="I352" t="n">
-        <v>0.906</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="353">
@@ -18357,13 +18357,13 @@
         <v>0.51</v>
       </c>
       <c r="G353" t="n">
-        <v>0.541</v>
+        <v>0.574</v>
       </c>
       <c r="H353" t="n">
-        <v>0.83</v>
+        <v>0.546</v>
       </c>
       <c r="I353" t="n">
-        <v>0.906</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="354">
@@ -18394,13 +18394,13 @@
         <v>0.863</v>
       </c>
       <c r="G354" t="n">
-        <v>0.667</v>
+        <v>0.873</v>
       </c>
       <c r="H354" t="n">
-        <v>0.00154</v>
+        <v>1</v>
       </c>
       <c r="I354" t="n">
-        <v>0.00822</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -18431,13 +18431,13 @@
         <v>1</v>
       </c>
       <c r="G355" t="n">
-        <v>0.704</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H355" t="n">
-        <v>0.00427</v>
+        <v>0.0511</v>
       </c>
       <c r="I355" t="n">
-        <v>0.0171</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="356">
@@ -18468,13 +18468,13 @@
         <v>0.964</v>
       </c>
       <c r="G356" t="n">
-        <v>0.679</v>
+        <v>0.929</v>
       </c>
       <c r="H356" t="n">
-        <v>0.0116</v>
+        <v>1</v>
       </c>
       <c r="I356" t="n">
-        <v>0.0371</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
@@ -18542,13 +18542,13 @@
         <v>0.762</v>
       </c>
       <c r="G358" t="n">
-        <v>0.614</v>
+        <v>0.792</v>
       </c>
       <c r="H358" t="n">
-        <v>0.0331</v>
+        <v>0.735</v>
       </c>
       <c r="I358" t="n">
-        <v>0.06610000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="359">
@@ -18579,13 +18579,13 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="G359" t="n">
-        <v>0.674</v>
+        <v>0.88</v>
       </c>
       <c r="H359" t="n">
-        <v>1</v>
+        <v>0.00212</v>
       </c>
       <c r="I359" t="n">
-        <v>1</v>
+        <v>0.0169</v>
       </c>
     </row>
     <row r="360">
@@ -18616,13 +18616,13 @@
         <v>0.788</v>
       </c>
       <c r="G360" t="n">
-        <v>0.706</v>
+        <v>0.894</v>
       </c>
       <c r="H360" t="n">
-        <v>0.29</v>
+        <v>0.0919</v>
       </c>
       <c r="I360" t="n">
-        <v>0.412</v>
+        <v>0.245</v>
       </c>
     </row>
     <row r="361">
@@ -18653,13 +18653,13 @@
         <v>0.556</v>
       </c>
       <c r="G361" t="n">
-        <v>0.111</v>
+        <v>0.222</v>
       </c>
       <c r="H361" t="n">
-        <v>0.131</v>
+        <v>0.335</v>
       </c>
       <c r="I361" t="n">
-        <v>0.21</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="362">
@@ -18690,13 +18690,13 @@
         <v>0.603</v>
       </c>
       <c r="G362" t="n">
-        <v>0.532</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H362" t="n">
-        <v>0.309</v>
+        <v>0.187</v>
       </c>
       <c r="I362" t="n">
-        <v>0.412</v>
+        <v>0.428</v>
       </c>
     </row>
     <row r="363">
@@ -18724,16 +18724,16 @@
         <v>10</v>
       </c>
       <c r="F363" t="n">
-        <v>0.802</v>
+        <v>0.79</v>
       </c>
       <c r="G363" t="n">
-        <v>0.556</v>
+        <v>0.778</v>
       </c>
       <c r="H363" t="n">
-        <v>0.00127</v>
+        <v>1</v>
       </c>
       <c r="I363" t="n">
-        <v>0.00822</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
@@ -18764,13 +18764,13 @@
         <v>0.598</v>
       </c>
       <c r="G364" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="H364" t="n">
-        <v>0.765</v>
+        <v>0.0405</v>
       </c>
       <c r="I364" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="365">
@@ -18801,13 +18801,13 @@
         <v>0.738</v>
       </c>
       <c r="G365" t="n">
-        <v>0.574</v>
+        <v>0.803</v>
       </c>
       <c r="H365" t="n">
-        <v>0.0858</v>
+        <v>0.519</v>
       </c>
       <c r="I365" t="n">
-        <v>0.152</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="366">
@@ -18838,13 +18838,13 @@
         <v>1</v>
       </c>
       <c r="G366" t="n">
-        <v>0.714</v>
+        <v>0.952</v>
       </c>
       <c r="H366" t="n">
-        <v>0.0207</v>
+        <v>1</v>
       </c>
       <c r="I366" t="n">
-        <v>0.0495</v>
+        <v>1</v>
       </c>
     </row>
     <row r="367">
@@ -18875,13 +18875,13 @@
         <v>0.767</v>
       </c>
       <c r="G367" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.918</v>
       </c>
       <c r="H367" t="n">
-        <v>0.354</v>
+        <v>0.0216</v>
       </c>
       <c r="I367" t="n">
-        <v>0.435</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="368">
@@ -18912,13 +18912,13 @@
         <v>0.701</v>
       </c>
       <c r="G368" t="n">
-        <v>0.493</v>
+        <v>0.657</v>
       </c>
       <c r="H368" t="n">
-        <v>0.0216</v>
+        <v>0.712</v>
       </c>
       <c r="I368" t="n">
-        <v>0.0495</v>
+        <v>1</v>
       </c>
     </row>
     <row r="369">
@@ -18949,13 +18949,13 @@
         <v>0.439</v>
       </c>
       <c r="G369" t="n">
-        <v>0.351</v>
+        <v>0.474</v>
       </c>
       <c r="H369" t="n">
-        <v>0.444</v>
+        <v>0.851</v>
       </c>
       <c r="I369" t="n">
-        <v>0.507</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370">
@@ -18986,13 +18986,13 @@
         <v>0.889</v>
       </c>
       <c r="G370" t="n">
-        <v>0.777</v>
+        <v>0.904</v>
       </c>
       <c r="H370" t="n">
-        <v>0.00477</v>
+        <v>0.742</v>
       </c>
       <c r="I370" t="n">
-        <v>0.0166</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="371">
@@ -19023,13 +19023,13 @@
         <v>0.675</v>
       </c>
       <c r="G371" t="n">
-        <v>0.745</v>
+        <v>0.8</v>
       </c>
       <c r="H371" t="n">
-        <v>0.438</v>
+        <v>0.121</v>
       </c>
       <c r="I371" t="n">
-        <v>0.526</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="372">
@@ -19060,13 +19060,13 @@
         <v>0.947</v>
       </c>
       <c r="G372" t="n">
-        <v>0.792</v>
+        <v>0.945</v>
       </c>
       <c r="H372" t="n">
-        <v>0.0192</v>
+        <v>1</v>
       </c>
       <c r="I372" t="n">
-        <v>0.0384</v>
+        <v>1</v>
       </c>
     </row>
     <row r="373">
@@ -19100,10 +19100,10 @@
         <v>0</v>
       </c>
       <c r="H373" t="n">
-        <v>1.27e-32</v>
+        <v>2.97e-35</v>
       </c>
       <c r="I373" t="n">
-        <v>2.03e-31</v>
+        <v>4.75e-34</v>
       </c>
     </row>
     <row r="374">
@@ -19134,13 +19134,13 @@
         <v>0.851</v>
       </c>
       <c r="G374" t="n">
-        <v>0.743</v>
+        <v>0.86</v>
       </c>
       <c r="H374" t="n">
-        <v>0.0156</v>
+        <v>0.882</v>
       </c>
       <c r="I374" t="n">
-        <v>0.0357</v>
+        <v>1</v>
       </c>
     </row>
     <row r="375">
@@ -19171,13 +19171,13 @@
         <v>0.803</v>
       </c>
       <c r="G375" t="n">
-        <v>0.765</v>
+        <v>0.885</v>
       </c>
       <c r="H375" t="n">
-        <v>0.497</v>
+        <v>0.0487</v>
       </c>
       <c r="I375" t="n">
-        <v>0.53</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="376">
@@ -19208,13 +19208,13 @@
         <v>0.865</v>
       </c>
       <c r="G376" t="n">
-        <v>0.784</v>
+        <v>0.879</v>
       </c>
       <c r="H376" t="n">
-        <v>0.0728</v>
+        <v>0.742</v>
       </c>
       <c r="I376" t="n">
-        <v>0.129</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="377">
@@ -19245,13 +19245,13 @@
         <v>0.667</v>
       </c>
       <c r="G377" t="n">
-        <v>0.154</v>
+        <v>0.286</v>
       </c>
       <c r="H377" t="n">
-        <v>0.00932</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="I377" t="n">
-        <v>0.0249</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="378">
@@ -19282,13 +19282,13 @@
         <v>0.749</v>
       </c>
       <c r="G378" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="H378" t="n">
-        <v>0.182</v>
+        <v>0.196</v>
       </c>
       <c r="I378" t="n">
-        <v>0.243</v>
+        <v>0.453</v>
       </c>
     </row>
     <row r="379">
@@ -19316,16 +19316,16 @@
         <v>10</v>
       </c>
       <c r="F379" t="n">
-        <v>0.861</v>
+        <v>0.853</v>
       </c>
       <c r="G379" t="n">
-        <v>0.709</v>
+        <v>0.857</v>
       </c>
       <c r="H379" t="n">
-        <v>0.00283</v>
+        <v>1</v>
       </c>
       <c r="I379" t="n">
-        <v>0.0151</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -19356,13 +19356,13 @@
         <v>0.714</v>
       </c>
       <c r="G380" t="n">
-        <v>0.671</v>
+        <v>0.798</v>
       </c>
       <c r="H380" t="n">
-        <v>0.46</v>
+        <v>0.0926</v>
       </c>
       <c r="I380" t="n">
-        <v>0.526</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="381">
@@ -19393,13 +19393,13 @@
         <v>0.833</v>
       </c>
       <c r="G381" t="n">
-        <v>0.619</v>
+        <v>0.76</v>
       </c>
       <c r="H381" t="n">
-        <v>0.000488</v>
+        <v>0.198</v>
       </c>
       <c r="I381" t="n">
-        <v>0.00391</v>
+        <v>0.453</v>
       </c>
     </row>
     <row r="382">
@@ -19430,13 +19430,13 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G382" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.889</v>
       </c>
       <c r="H382" t="n">
-        <v>0.173</v>
+        <v>0.714</v>
       </c>
       <c r="I382" t="n">
-        <v>0.243</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="383">
@@ -19467,13 +19467,13 @@
         <v>0.855</v>
       </c>
       <c r="G383" t="n">
-        <v>0.709</v>
+        <v>0.838</v>
       </c>
       <c r="H383" t="n">
-        <v>0.00517</v>
+        <v>0.746</v>
       </c>
       <c r="I383" t="n">
-        <v>0.0166</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="384">
@@ -19504,13 +19504,13 @@
         <v>0.667</v>
       </c>
       <c r="G384" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H384" t="n">
-        <v>0.0959</v>
+        <v>0.796</v>
       </c>
       <c r="I384" t="n">
-        <v>0.153</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="385">
@@ -19541,13 +19541,13 @@
         <v>0.472</v>
       </c>
       <c r="G385" t="n">
-        <v>0.426</v>
+        <v>0.519</v>
       </c>
       <c r="H385" t="n">
-        <v>0.57</v>
+        <v>0.581</v>
       </c>
       <c r="I385" t="n">
-        <v>0.57</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="386">
@@ -19806,7 +19806,7 @@
         <v>0.202</v>
       </c>
       <c r="I392" t="n">
-        <v>0.378</v>
+        <v>0.404</v>
       </c>
     </row>
     <row r="393">
@@ -19908,16 +19908,16 @@
         <v>10</v>
       </c>
       <c r="F395" t="n">
-        <v>0.86</v>
+        <v>0.853</v>
       </c>
       <c r="G395" t="n">
         <v>0.8</v>
       </c>
       <c r="H395" t="n">
-        <v>0.219</v>
+        <v>0.286</v>
       </c>
       <c r="I395" t="n">
-        <v>0.378</v>
+        <v>0.457</v>
       </c>
     </row>
     <row r="396">
@@ -19954,7 +19954,7 @@
         <v>0.236</v>
       </c>
       <c r="I396" t="n">
-        <v>0.378</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="397">
@@ -20500,16 +20500,16 @@
         <v>10</v>
       </c>
       <c r="F411" t="n">
-        <v>0.929</v>
+        <v>0.928</v>
       </c>
       <c r="G411" t="n">
         <v>0.881</v>
       </c>
       <c r="H411" t="n">
-        <v>0.392</v>
+        <v>0.395</v>
       </c>
       <c r="I411" t="n">
-        <v>0.697</v>
+        <v>0.702</v>
       </c>
     </row>
     <row r="412">
@@ -20842,7 +20842,7 @@
         <v>0.352</v>
       </c>
       <c r="I420" t="n">
-        <v>0.708</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="421">
@@ -21092,16 +21092,16 @@
         <v>10</v>
       </c>
       <c r="F427" t="n">
-        <v>0.802</v>
+        <v>0.79</v>
       </c>
       <c r="G427" t="n">
         <v>0.728</v>
       </c>
       <c r="H427" t="n">
-        <v>0.354</v>
+        <v>0.463</v>
       </c>
       <c r="I427" t="n">
-        <v>0.708</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="428">
@@ -21286,7 +21286,7 @@
         <v>0.321</v>
       </c>
       <c r="I432" t="n">
-        <v>0.708</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="433">
@@ -21684,16 +21684,16 @@
         <v>10</v>
       </c>
       <c r="F443" t="n">
-        <v>0.861</v>
+        <v>0.853</v>
       </c>
       <c r="G443" t="n">
         <v>0.797</v>
       </c>
       <c r="H443" t="n">
-        <v>0.167</v>
+        <v>0.224</v>
       </c>
       <c r="I443" t="n">
-        <v>0.267</v>
+        <v>0.359</v>
       </c>
     </row>
     <row r="444">
@@ -21946,13 +21946,13 @@
         <v>0.853</v>
       </c>
       <c r="G450" t="n">
-        <v>0.747</v>
+        <v>0.86</v>
       </c>
       <c r="H450" t="n">
-        <v>0.0298</v>
+        <v>1</v>
       </c>
       <c r="I450" t="n">
-        <v>0.0682</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451">
@@ -21983,13 +21983,13 @@
         <v>0.827</v>
       </c>
       <c r="G451" t="n">
-        <v>0.92</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H451" t="n">
-        <v>0.023</v>
+        <v>0.00702</v>
       </c>
       <c r="I451" t="n">
-        <v>0.0629</v>
+        <v>0.0561</v>
       </c>
     </row>
     <row r="452">
@@ -22020,13 +22020,13 @@
         <v>0.98</v>
       </c>
       <c r="G452" t="n">
-        <v>0.913</v>
+        <v>0.96</v>
       </c>
       <c r="H452" t="n">
-        <v>0.018</v>
+        <v>0.501</v>
       </c>
       <c r="I452" t="n">
-        <v>0.0629</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453">
@@ -22057,13 +22057,13 @@
         <v>0.993</v>
       </c>
       <c r="G453" t="n">
-        <v>0.38</v>
+        <v>0.233</v>
       </c>
       <c r="H453" t="n">
-        <v>7.3e-36</v>
+        <v>1.4e-49</v>
       </c>
       <c r="I453" t="n">
-        <v>1.17e-34</v>
+        <v>2.25e-48</v>
       </c>
     </row>
     <row r="454">
@@ -22094,13 +22094,13 @@
         <v>0.82</v>
       </c>
       <c r="G454" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H454" t="n">
-        <v>0.0106</v>
+        <v>0.769</v>
       </c>
       <c r="I454" t="n">
-        <v>0.0568</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -22131,13 +22131,13 @@
         <v>0.793</v>
       </c>
       <c r="G455" t="n">
-        <v>0.753</v>
+        <v>0.867</v>
       </c>
       <c r="H455" t="n">
-        <v>0.491</v>
+        <v>0.124</v>
       </c>
       <c r="I455" t="n">
-        <v>0.523</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="456">
@@ -22168,13 +22168,13 @@
         <v>0.86</v>
       </c>
       <c r="G456" t="n">
-        <v>0.767</v>
+        <v>0.873</v>
       </c>
       <c r="H456" t="n">
-        <v>0.0534</v>
+        <v>0.865</v>
       </c>
       <c r="I456" t="n">
-        <v>0.095</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457">
@@ -22205,13 +22205,13 @@
         <v>0.967</v>
       </c>
       <c r="G457" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.953</v>
       </c>
       <c r="H457" t="n">
-        <v>0.413</v>
+        <v>0.77</v>
       </c>
       <c r="I457" t="n">
-        <v>0.508</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458">
@@ -22242,13 +22242,13 @@
         <v>0.66</v>
       </c>
       <c r="G458" t="n">
-        <v>0.607</v>
+        <v>0.767</v>
       </c>
       <c r="H458" t="n">
-        <v>0.402</v>
+        <v>0.0551</v>
       </c>
       <c r="I458" t="n">
-        <v>0.508</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="459">
@@ -22276,16 +22276,16 @@
         <v>10</v>
       </c>
       <c r="F459" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="G459" t="n">
         <v>0.86</v>
       </c>
-      <c r="G459" t="n">
-        <v>0.767</v>
-      </c>
       <c r="H459" t="n">
-        <v>0.0534</v>
+        <v>1</v>
       </c>
       <c r="I459" t="n">
-        <v>0.095</v>
+        <v>1</v>
       </c>
     </row>
     <row r="460">
@@ -22316,13 +22316,13 @@
         <v>0.707</v>
       </c>
       <c r="G460" t="n">
-        <v>0.713</v>
+        <v>0.827</v>
       </c>
       <c r="H460" t="n">
-        <v>1</v>
+        <v>0.0199</v>
       </c>
       <c r="I460" t="n">
-        <v>1</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="461">
@@ -22353,13 +22353,13 @@
         <v>0.88</v>
       </c>
       <c r="G461" t="n">
-        <v>0.753</v>
+        <v>0.84</v>
       </c>
       <c r="H461" t="n">
-        <v>0.00686</v>
+        <v>0.406</v>
       </c>
       <c r="I461" t="n">
-        <v>0.0549</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="462">
@@ -22390,13 +22390,13 @@
         <v>0.98</v>
       </c>
       <c r="G462" t="n">
-        <v>0.947</v>
+        <v>0.967</v>
       </c>
       <c r="H462" t="n">
-        <v>0.218</v>
+        <v>0.723</v>
       </c>
       <c r="I462" t="n">
-        <v>0.349</v>
+        <v>1</v>
       </c>
     </row>
     <row r="463">
@@ -22427,13 +22427,13 @@
         <v>0.873</v>
       </c>
       <c r="G463" t="n">
-        <v>0.767</v>
+        <v>0.847</v>
       </c>
       <c r="H463" t="n">
-        <v>0.0236</v>
+        <v>0.618</v>
       </c>
       <c r="I463" t="n">
-        <v>0.0629</v>
+        <v>1</v>
       </c>
     </row>
     <row r="464">
@@ -22464,13 +22464,13 @@
         <v>0.6870000000000001</v>
       </c>
       <c r="G464" t="n">
-        <v>0.633</v>
+        <v>0.7</v>
       </c>
       <c r="H464" t="n">
-        <v>0.394</v>
+        <v>0.9</v>
       </c>
       <c r="I464" t="n">
-        <v>0.508</v>
+        <v>1</v>
       </c>
     </row>
     <row r="465">
@@ -22501,13 +22501,13 @@
         <v>0.627</v>
       </c>
       <c r="G465" t="n">
-        <v>0.673</v>
+        <v>0.7</v>
       </c>
       <c r="H465" t="n">
-        <v>0.468</v>
+        <v>0.222</v>
       </c>
       <c r="I465" t="n">
-        <v>0.523</v>
+        <v>0.591</v>
       </c>
     </row>
     <row r="466">
@@ -22538,13 +22538,13 @@
         <v>0.917</v>
       </c>
       <c r="G466" t="n">
-        <v>0.881</v>
+        <v>0.858</v>
       </c>
       <c r="H466" t="n">
-        <v>0.464</v>
+        <v>0.201</v>
       </c>
       <c r="I466" t="n">
-        <v>0.662</v>
+        <v>0.459</v>
       </c>
     </row>
     <row r="467">
@@ -22575,13 +22575,13 @@
         <v>0.509</v>
       </c>
       <c r="G467" t="n">
-        <v>0.778</v>
+        <v>0.774</v>
       </c>
       <c r="H467" t="n">
-        <v>0.0294</v>
+        <v>0.021</v>
       </c>
       <c r="I467" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0766</v>
       </c>
     </row>
     <row r="468">
@@ -22612,13 +22612,13 @@
         <v>0.931</v>
       </c>
       <c r="G468" t="n">
-        <v>0.8</v>
+        <v>0.844</v>
       </c>
       <c r="H468" t="n">
-        <v>0.229</v>
+        <v>0.429</v>
       </c>
       <c r="I468" t="n">
-        <v>0.459</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="469">
@@ -22652,10 +22652,10 @@
         <v>0</v>
       </c>
       <c r="H469" t="n">
-        <v>3.49e-21</v>
+        <v>2.32e-23</v>
       </c>
       <c r="I469" t="n">
-        <v>5.59e-20</v>
+        <v>3.72e-22</v>
       </c>
     </row>
     <row r="470">
@@ -22686,13 +22686,13 @@
         <v>0.963</v>
       </c>
       <c r="G470" t="n">
-        <v>0.909</v>
+        <v>0.918</v>
       </c>
       <c r="H470" t="n">
-        <v>0.3</v>
+        <v>0.331</v>
       </c>
       <c r="I470" t="n">
-        <v>0.533</v>
+        <v>0.529</v>
       </c>
     </row>
     <row r="471">
@@ -22723,13 +22723,13 @@
         <v>0.969</v>
       </c>
       <c r="G471" t="n">
-        <v>0.867</v>
+        <v>0.875</v>
       </c>
       <c r="H471" t="n">
-        <v>0.0362</v>
+        <v>0.0462</v>
       </c>
       <c r="I471" t="n">
-        <v>0.0965</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="472">
@@ -22760,13 +22760,13 @@
         <v>0.957</v>
       </c>
       <c r="G472" t="n">
-        <v>0.821</v>
+        <v>0.837</v>
       </c>
       <c r="H472" t="n">
-        <v>0.01</v>
+        <v>0.0239</v>
       </c>
       <c r="I472" t="n">
-        <v>0.04</v>
+        <v>0.0766</v>
       </c>
     </row>
     <row r="473">
@@ -22797,13 +22797,13 @@
         <v>0.833</v>
       </c>
       <c r="G473" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="H473" t="n">
-        <v>0.464</v>
+        <v>1</v>
       </c>
       <c r="I473" t="n">
-        <v>0.662</v>
+        <v>1</v>
       </c>
     </row>
     <row r="474">
@@ -22834,13 +22834,13 @@
         <v>0.987</v>
       </c>
       <c r="G474" t="n">
-        <v>0.924</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="H474" t="n">
-        <v>0.117</v>
+        <v>0.241</v>
       </c>
       <c r="I474" t="n">
-        <v>0.267</v>
+        <v>0.483</v>
       </c>
     </row>
     <row r="475">
@@ -22868,16 +22868,16 @@
         <v>10</v>
       </c>
       <c r="F475" t="n">
-        <v>0.929</v>
+        <v>0.928</v>
       </c>
       <c r="G475" t="n">
-        <v>0.911</v>
+        <v>0.905</v>
       </c>
       <c r="H475" t="n">
-        <v>0.75</v>
+        <v>0.766</v>
       </c>
       <c r="I475" t="n">
-        <v>0.857</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="476">
@@ -22908,7 +22908,7 @@
         <v>0.887</v>
       </c>
       <c r="G476" t="n">
-        <v>0.877</v>
+        <v>0.875</v>
       </c>
       <c r="H476" t="n">
         <v>1</v>
@@ -22945,13 +22945,13 @@
         <v>0.957</v>
       </c>
       <c r="G477" t="n">
-        <v>0.714</v>
+        <v>0.747</v>
       </c>
       <c r="H477" t="n">
-        <v>0.00133</v>
+        <v>0.00259</v>
       </c>
       <c r="I477" t="n">
-        <v>0.0107</v>
+        <v>0.0207</v>
       </c>
     </row>
     <row r="478">
@@ -22982,13 +22982,13 @@
         <v>0.875</v>
       </c>
       <c r="G478" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H478" t="n">
-        <v>0.538</v>
+        <v>1</v>
       </c>
       <c r="I478" t="n">
-        <v>0.662</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479">
@@ -23019,13 +23019,13 @@
         <v>0.966</v>
       </c>
       <c r="G479" t="n">
-        <v>0.797</v>
+        <v>0.805</v>
       </c>
       <c r="H479" t="n">
-        <v>0.00515</v>
+        <v>0.00468</v>
       </c>
       <c r="I479" t="n">
-        <v>0.0275</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="480">
@@ -23056,13 +23056,13 @@
         <v>0.635</v>
       </c>
       <c r="G480" t="n">
-        <v>0.62</v>
+        <v>0.672</v>
       </c>
       <c r="H480" t="n">
-        <v>1</v>
+        <v>0.721</v>
       </c>
       <c r="I480" t="n">
-        <v>1</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="481">
@@ -23093,13 +23093,13 @@
         <v>0.51</v>
       </c>
       <c r="G481" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H481" t="n">
-        <v>0.521</v>
+        <v>0.314</v>
       </c>
       <c r="I481" t="n">
-        <v>0.662</v>
+        <v>0.529</v>
       </c>
     </row>
     <row r="482">
@@ -23130,13 +23130,13 @@
         <v>0.863</v>
       </c>
       <c r="G482" t="n">
-        <v>0.725</v>
+        <v>0.951</v>
       </c>
       <c r="H482" t="n">
-        <v>0.0236</v>
+        <v>0.0515</v>
       </c>
       <c r="I482" t="n">
-        <v>0.0496</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="483">
@@ -23167,13 +23167,13 @@
         <v>1</v>
       </c>
       <c r="G483" t="n">
-        <v>0.778</v>
+        <v>0.889</v>
       </c>
       <c r="H483" t="n">
-        <v>0.0229</v>
+        <v>0.236</v>
       </c>
       <c r="I483" t="n">
-        <v>0.0496</v>
+        <v>0.377</v>
       </c>
     </row>
     <row r="484">
@@ -23204,13 +23204,13 @@
         <v>0.964</v>
       </c>
       <c r="G484" t="n">
-        <v>0.714</v>
+        <v>0.964</v>
       </c>
       <c r="H484" t="n">
-        <v>0.0248</v>
+        <v>1</v>
       </c>
       <c r="I484" t="n">
-        <v>0.0496</v>
+        <v>1</v>
       </c>
     </row>
     <row r="485">
@@ -23278,13 +23278,13 @@
         <v>0.762</v>
       </c>
       <c r="G486" t="n">
-        <v>0.594</v>
+        <v>0.772</v>
       </c>
       <c r="H486" t="n">
-        <v>0.0156</v>
+        <v>1</v>
       </c>
       <c r="I486" t="n">
-        <v>0.0496</v>
+        <v>1</v>
       </c>
     </row>
     <row r="487">
@@ -23315,13 +23315,13 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="G487" t="n">
-        <v>0.707</v>
+        <v>0.913</v>
       </c>
       <c r="H487" t="n">
-        <v>0.873</v>
+        <v>0.000174</v>
       </c>
       <c r="I487" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.00139</v>
       </c>
     </row>
     <row r="488">
@@ -23352,13 +23352,13 @@
         <v>0.788</v>
       </c>
       <c r="G488" t="n">
-        <v>0.753</v>
+        <v>0.965</v>
       </c>
       <c r="H488" t="n">
-        <v>0.716</v>
+        <v>0.000727</v>
       </c>
       <c r="I488" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.00291</v>
       </c>
     </row>
     <row r="489">
@@ -23389,13 +23389,13 @@
         <v>0.556</v>
       </c>
       <c r="G489" t="n">
-        <v>0.111</v>
+        <v>0.333</v>
       </c>
       <c r="H489" t="n">
-        <v>0.131</v>
+        <v>0.637</v>
       </c>
       <c r="I489" t="n">
-        <v>0.233</v>
+        <v>0.784</v>
       </c>
     </row>
     <row r="490">
@@ -23426,13 +23426,13 @@
         <v>0.603</v>
       </c>
       <c r="G490" t="n">
-        <v>0.579</v>
+        <v>0.77</v>
       </c>
       <c r="H490" t="n">
-        <v>0.798</v>
+        <v>0.00642</v>
       </c>
       <c r="I490" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.0206</v>
       </c>
     </row>
     <row r="491">
@@ -23460,16 +23460,16 @@
         <v>10</v>
       </c>
       <c r="F491" t="n">
-        <v>0.802</v>
+        <v>0.79</v>
       </c>
       <c r="G491" t="n">
-        <v>0.63</v>
+        <v>0.827</v>
       </c>
       <c r="H491" t="n">
-        <v>0.0229</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I491" t="n">
-        <v>0.0496</v>
+        <v>0.789</v>
       </c>
     </row>
     <row r="492">
@@ -23500,13 +23500,13 @@
         <v>0.598</v>
       </c>
       <c r="G492" t="n">
-        <v>0.62</v>
+        <v>0.837</v>
       </c>
       <c r="H492" t="n">
-        <v>0.88</v>
+        <v>0.000515</v>
       </c>
       <c r="I492" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.00275</v>
       </c>
     </row>
     <row r="493">
@@ -23537,13 +23537,13 @@
         <v>0.738</v>
       </c>
       <c r="G493" t="n">
-        <v>0.656</v>
+        <v>0.918</v>
       </c>
       <c r="H493" t="n">
-        <v>0.431</v>
+        <v>0.015</v>
       </c>
       <c r="I493" t="n">
-        <v>0.661</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="494">
@@ -23574,13 +23574,13 @@
         <v>1</v>
       </c>
       <c r="G494" t="n">
-        <v>0.619</v>
+        <v>0.857</v>
       </c>
       <c r="H494" t="n">
-        <v>0.00345</v>
+        <v>0.232</v>
       </c>
       <c r="I494" t="n">
-        <v>0.0276</v>
+        <v>0.377</v>
       </c>
     </row>
     <row r="495">
@@ -23611,13 +23611,13 @@
         <v>0.767</v>
       </c>
       <c r="G495" t="n">
-        <v>0.699</v>
+        <v>0.904</v>
       </c>
       <c r="H495" t="n">
-        <v>0.455</v>
+        <v>0.0429</v>
       </c>
       <c r="I495" t="n">
-        <v>0.661</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="496">
@@ -23648,13 +23648,13 @@
         <v>0.701</v>
       </c>
       <c r="G496" t="n">
-        <v>0.463</v>
+        <v>0.642</v>
       </c>
       <c r="H496" t="n">
-        <v>0.00834</v>
+        <v>0.581</v>
       </c>
       <c r="I496" t="n">
-        <v>0.0445</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="497">
@@ -23685,13 +23685,13 @@
         <v>0.439</v>
       </c>
       <c r="G497" t="n">
-        <v>0.421</v>
+        <v>0.544</v>
       </c>
       <c r="H497" t="n">
-        <v>1</v>
+        <v>0.349</v>
       </c>
       <c r="I497" t="n">
-        <v>1</v>
+        <v>0.508</v>
       </c>
     </row>
     <row r="498">
@@ -23722,13 +23722,13 @@
         <v>0.889</v>
       </c>
       <c r="G498" t="n">
-        <v>0.796</v>
+        <v>0.902</v>
       </c>
       <c r="H498" t="n">
-        <v>0.0163</v>
+        <v>0.748</v>
       </c>
       <c r="I498" t="n">
-        <v>0.0445</v>
+        <v>0.958</v>
       </c>
     </row>
     <row r="499">
@@ -23759,13 +23759,13 @@
         <v>0.675</v>
       </c>
       <c r="G499" t="n">
-        <v>0.778</v>
+        <v>0.828</v>
       </c>
       <c r="H499" t="n">
-        <v>0.242</v>
+        <v>0.0509</v>
       </c>
       <c r="I499" t="n">
-        <v>0.323</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="500">
@@ -23796,13 +23796,13 @@
         <v>0.947</v>
       </c>
       <c r="G500" t="n">
-        <v>0.755</v>
+        <v>0.9</v>
       </c>
       <c r="H500" t="n">
-        <v>0.00582</v>
+        <v>0.492</v>
       </c>
       <c r="I500" t="n">
-        <v>0.0311</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="501">
@@ -23836,10 +23836,10 @@
         <v>0</v>
       </c>
       <c r="H501" t="n">
-        <v>1.8e-34</v>
+        <v>1.11e-37</v>
       </c>
       <c r="I501" t="n">
-        <v>2.87e-33</v>
+        <v>1.77e-36</v>
       </c>
     </row>
     <row r="502">
@@ -23870,13 +23870,13 @@
         <v>0.851</v>
       </c>
       <c r="G502" t="n">
-        <v>0.719</v>
+        <v>0.839</v>
       </c>
       <c r="H502" t="n">
-        <v>0.00373</v>
+        <v>0.775</v>
       </c>
       <c r="I502" t="n">
-        <v>0.0299</v>
+        <v>0.958</v>
       </c>
     </row>
     <row r="503">
@@ -23907,13 +23907,13 @@
         <v>0.803</v>
       </c>
       <c r="G503" t="n">
-        <v>0.778</v>
+        <v>0.894</v>
       </c>
       <c r="H503" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.022</v>
       </c>
       <c r="I503" t="n">
-        <v>0.78</v>
+        <v>0.08790000000000001</v>
       </c>
     </row>
     <row r="504">
@@ -23944,13 +23944,13 @@
         <v>0.865</v>
       </c>
       <c r="G504" t="n">
-        <v>0.785</v>
+        <v>0.896</v>
       </c>
       <c r="H504" t="n">
-        <v>0.0771</v>
+        <v>0.401</v>
       </c>
       <c r="I504" t="n">
-        <v>0.112</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="505">
@@ -23981,13 +23981,13 @@
         <v>0.667</v>
       </c>
       <c r="G505" t="n">
-        <v>0.182</v>
+        <v>0.462</v>
       </c>
       <c r="H505" t="n">
-        <v>0.0214</v>
+        <v>0.445</v>
       </c>
       <c r="I505" t="n">
-        <v>0.049</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="506">
@@ -24018,13 +24018,13 @@
         <v>0.749</v>
       </c>
       <c r="G506" t="n">
-        <v>0.712</v>
+        <v>0.847</v>
       </c>
       <c r="H506" t="n">
-        <v>0.436</v>
+        <v>0.0114</v>
       </c>
       <c r="I506" t="n">
-        <v>0.536</v>
+        <v>0.0609</v>
       </c>
     </row>
     <row r="507">
@@ -24052,16 +24052,16 @@
         <v>10</v>
       </c>
       <c r="F507" t="n">
-        <v>0.861</v>
+        <v>0.853</v>
       </c>
       <c r="G507" t="n">
-        <v>0.745</v>
+        <v>0.865</v>
       </c>
       <c r="H507" t="n">
-        <v>0.0167</v>
+        <v>0.87</v>
       </c>
       <c r="I507" t="n">
-        <v>0.0445</v>
+        <v>0.958</v>
       </c>
     </row>
     <row r="508">
@@ -24092,13 +24092,13 @@
         <v>0.714</v>
       </c>
       <c r="G508" t="n">
-        <v>0.726</v>
+        <v>0.856</v>
       </c>
       <c r="H508" t="n">
-        <v>0.9</v>
+        <v>0.00187</v>
       </c>
       <c r="I508" t="n">
-        <v>0.9</v>
+        <v>0.0149</v>
       </c>
     </row>
     <row r="509">
@@ -24129,13 +24129,13 @@
         <v>0.833</v>
       </c>
       <c r="G509" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.824</v>
       </c>
       <c r="H509" t="n">
-        <v>0.0126</v>
+        <v>0.866</v>
       </c>
       <c r="I509" t="n">
-        <v>0.0445</v>
+        <v>0.958</v>
       </c>
     </row>
     <row r="510">
@@ -24166,13 +24166,13 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G510" t="n">
-        <v>0.765</v>
+        <v>0.878</v>
       </c>
       <c r="H510" t="n">
-        <v>0.0481</v>
+        <v>0.47</v>
       </c>
       <c r="I510" t="n">
-        <v>0.0769</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="511">
@@ -24203,13 +24203,13 @@
         <v>0.855</v>
       </c>
       <c r="G511" t="n">
-        <v>0.745</v>
+        <v>0.852</v>
       </c>
       <c r="H511" t="n">
-        <v>0.0324</v>
+        <v>1</v>
       </c>
       <c r="I511" t="n">
-        <v>0.0576</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512">
@@ -24240,13 +24240,13 @@
         <v>0.667</v>
       </c>
       <c r="G512" t="n">
-        <v>0.53</v>
+        <v>0.656</v>
       </c>
       <c r="H512" t="n">
-        <v>0.0298</v>
+        <v>0.898</v>
       </c>
       <c r="I512" t="n">
-        <v>0.0576</v>
+        <v>0.958</v>
       </c>
     </row>
     <row r="513">
@@ -24277,13 +24277,13 @@
         <v>0.472</v>
       </c>
       <c r="G513" t="n">
-        <v>0.495</v>
+        <v>0.579</v>
       </c>
       <c r="H513" t="n">
-        <v>0.78</v>
+        <v>0.132</v>
       </c>
       <c r="I513" t="n">
-        <v>0.832</v>
+        <v>0.352</v>
       </c>
     </row>
     <row r="514">
@@ -24644,13 +24644,13 @@
         <v>10</v>
       </c>
       <c r="F523" t="n">
-        <v>0.86</v>
+        <v>0.853</v>
       </c>
       <c r="G523" t="n">
         <v>0.873</v>
       </c>
       <c r="H523" t="n">
-        <v>0.865</v>
+        <v>0.737</v>
       </c>
       <c r="I523" t="n">
         <v>1</v>
@@ -25236,7 +25236,7 @@
         <v>10</v>
       </c>
       <c r="F539" t="n">
-        <v>0.929</v>
+        <v>0.928</v>
       </c>
       <c r="G539" t="n">
         <v>0.931</v>
@@ -25828,13 +25828,13 @@
         <v>10</v>
       </c>
       <c r="F555" t="n">
-        <v>0.802</v>
+        <v>0.79</v>
       </c>
       <c r="G555" t="n">
         <v>0.827</v>
       </c>
       <c r="H555" t="n">
-        <v>0.84</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I555" t="n">
         <v>1</v>
@@ -26420,16 +26420,16 @@
         <v>10</v>
       </c>
       <c r="F571" t="n">
-        <v>0.861</v>
+        <v>0.853</v>
       </c>
       <c r="G571" t="n">
         <v>0.876</v>
       </c>
       <c r="H571" t="n">
-        <v>0.737</v>
+        <v>0.616</v>
       </c>
       <c r="I571" t="n">
-        <v>1</v>
+        <v>0.897</v>
       </c>
     </row>
     <row r="572">
@@ -27012,16 +27012,16 @@
         <v>10</v>
       </c>
       <c r="F587" t="n">
-        <v>0.86</v>
+        <v>0.853</v>
       </c>
       <c r="G587" t="n">
         <v>0.893</v>
       </c>
       <c r="H587" t="n">
-        <v>0.483</v>
+        <v>0.386</v>
       </c>
       <c r="I587" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.771</v>
       </c>
     </row>
     <row r="588">
@@ -27604,7 +27604,7 @@
         <v>10</v>
       </c>
       <c r="F603" t="n">
-        <v>0.929</v>
+        <v>0.928</v>
       </c>
       <c r="G603" t="n">
         <v>0.9330000000000001</v>
@@ -27909,7 +27909,7 @@
         <v>0.236</v>
       </c>
       <c r="I611" t="n">
-        <v>0.538</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="612">
@@ -28196,16 +28196,16 @@
         <v>10</v>
       </c>
       <c r="F619" t="n">
-        <v>0.802</v>
+        <v>0.79</v>
       </c>
       <c r="G619" t="n">
         <v>0.864</v>
       </c>
       <c r="H619" t="n">
-        <v>0.399</v>
+        <v>0.299</v>
       </c>
       <c r="I619" t="n">
-        <v>0.71</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="620">
@@ -28279,7 +28279,7 @@
         <v>0.269</v>
       </c>
       <c r="I621" t="n">
-        <v>0.538</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="622">
@@ -28686,7 +28686,7 @@
         <v>0.294</v>
       </c>
       <c r="I632" t="n">
-        <v>0.658</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="633">
@@ -28723,7 +28723,7 @@
         <v>0.272</v>
       </c>
       <c r="I633" t="n">
-        <v>0.658</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="634">
@@ -28788,16 +28788,16 @@
         <v>10</v>
       </c>
       <c r="F635" t="n">
-        <v>0.861</v>
+        <v>0.853</v>
       </c>
       <c r="G635" t="n">
         <v>0.897</v>
       </c>
       <c r="H635" t="n">
-        <v>0.382</v>
+        <v>0.299</v>
       </c>
       <c r="I635" t="n">
-        <v>0.679</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="636">
@@ -29019,7 +29019,7 @@
         <v>0.329</v>
       </c>
       <c r="I641" t="n">
-        <v>0.658</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="642">
@@ -29380,16 +29380,16 @@
         <v>10</v>
       </c>
       <c r="F651" t="n">
-        <v>0.793</v>
+        <v>0.787</v>
       </c>
       <c r="G651" t="n">
-        <v>0.913</v>
+        <v>0.907</v>
       </c>
       <c r="H651" t="n">
-        <v>0.00509</v>
+        <v>0.006</v>
       </c>
       <c r="I651" t="n">
-        <v>0.0814</v>
+        <v>0.0959</v>
       </c>
     </row>
     <row r="652">
@@ -29972,7 +29972,7 @@
         <v>10</v>
       </c>
       <c r="F667" t="n">
-        <v>0.981</v>
+        <v>0.98</v>
       </c>
       <c r="G667" t="n">
         <v>0.986</v>
@@ -30564,16 +30564,16 @@
         <v>10</v>
       </c>
       <c r="F683" t="n">
-        <v>0.63</v>
+        <v>0.617</v>
       </c>
       <c r="G683" t="n">
-        <v>0.852</v>
+        <v>0.84</v>
       </c>
       <c r="H683" t="n">
-        <v>0.00208</v>
+        <v>0.00245</v>
       </c>
       <c r="I683" t="n">
-        <v>0.0333</v>
+        <v>0.0392</v>
       </c>
     </row>
     <row r="684">
@@ -31156,16 +31156,16 @@
         <v>10</v>
       </c>
       <c r="F699" t="n">
-        <v>0.767</v>
+        <v>0.758</v>
       </c>
       <c r="G699" t="n">
-        <v>0.914</v>
+        <v>0.907</v>
       </c>
       <c r="H699" t="n">
-        <v>0.0008720000000000001</v>
+        <v>0.00107</v>
       </c>
       <c r="I699" t="n">
-        <v>0.014</v>
+        <v>0.0172</v>
       </c>
     </row>
     <row r="700">
@@ -31748,13 +31748,13 @@
         <v>10</v>
       </c>
       <c r="F715" t="n">
-        <v>0.793</v>
+        <v>0.787</v>
       </c>
       <c r="G715" t="n">
-        <v>0.893</v>
+        <v>0.887</v>
       </c>
       <c r="H715" t="n">
-        <v>0.0254</v>
+        <v>0.028</v>
       </c>
       <c r="I715" t="n">
         <v>0.228</v>
@@ -32340,13 +32340,13 @@
         <v>10</v>
       </c>
       <c r="F731" t="n">
-        <v>0.981</v>
+        <v>0.98</v>
       </c>
       <c r="G731" t="n">
-        <v>0.958</v>
+        <v>0.957</v>
       </c>
       <c r="H731" t="n">
-        <v>0.637</v>
+        <v>0.638</v>
       </c>
       <c r="I731" t="n">
         <v>1</v>
@@ -32904,7 +32904,7 @@
         <v>0.00213</v>
       </c>
       <c r="I746" t="n">
-        <v>0.0328</v>
+        <v>0.0341</v>
       </c>
     </row>
     <row r="747">
@@ -32932,16 +32932,16 @@
         <v>10</v>
       </c>
       <c r="F747" t="n">
-        <v>0.63</v>
+        <v>0.617</v>
       </c>
       <c r="G747" t="n">
-        <v>0.84</v>
+        <v>0.827</v>
       </c>
       <c r="H747" t="n">
-        <v>0.0041</v>
+        <v>0.0047</v>
       </c>
       <c r="I747" t="n">
-        <v>0.0328</v>
+        <v>0.0376</v>
       </c>
     </row>
     <row r="748">
@@ -33524,13 +33524,13 @@
         <v>10</v>
       </c>
       <c r="F763" t="n">
-        <v>0.767</v>
+        <v>0.758</v>
       </c>
       <c r="G763" t="n">
-        <v>0.895</v>
+        <v>0.887</v>
       </c>
       <c r="H763" t="n">
-        <v>0.00406</v>
+        <v>0.00456</v>
       </c>
       <c r="I763" t="n">
         <v>0.0415</v>
@@ -34116,16 +34116,16 @@
         <v>10</v>
       </c>
       <c r="F779" t="n">
-        <v>0.793</v>
+        <v>0.787</v>
       </c>
       <c r="G779" t="n">
-        <v>0.88</v>
+        <v>0.873</v>
       </c>
       <c r="H779" t="n">
-        <v>0.0601</v>
+        <v>0.0644</v>
       </c>
       <c r="I779" t="n">
-        <v>0.481</v>
+        <v>0.515</v>
       </c>
     </row>
     <row r="780">
@@ -34708,13 +34708,13 @@
         <v>10</v>
       </c>
       <c r="F795" t="n">
-        <v>0.981</v>
+        <v>0.98</v>
       </c>
       <c r="G795" t="n">
-        <v>0.944</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="H795" t="n">
-        <v>0.395</v>
+        <v>0.396</v>
       </c>
       <c r="I795" t="n">
         <v>1</v>
@@ -35300,16 +35300,16 @@
         <v>10</v>
       </c>
       <c r="F811" t="n">
-        <v>0.63</v>
+        <v>0.617</v>
       </c>
       <c r="G811" t="n">
-        <v>0.827</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H811" t="n">
-        <v>0.00765</v>
+        <v>0.00856</v>
       </c>
       <c r="I811" t="n">
-        <v>0.0612</v>
+        <v>0.06850000000000001</v>
       </c>
     </row>
     <row r="812">
@@ -35892,16 +35892,16 @@
         <v>10</v>
       </c>
       <c r="F827" t="n">
-        <v>0.767</v>
+        <v>0.758</v>
       </c>
       <c r="G827" t="n">
-        <v>0.882</v>
+        <v>0.874</v>
       </c>
       <c r="H827" t="n">
-        <v>0.0119</v>
+        <v>0.013</v>
       </c>
       <c r="I827" t="n">
-        <v>0.0954</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="828">
@@ -36456,7 +36456,7 @@
         <v>0.00906</v>
       </c>
       <c r="I842" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0838</v>
       </c>
     </row>
     <row r="843">
@@ -36484,16 +36484,16 @@
         <v>10</v>
       </c>
       <c r="F843" t="n">
-        <v>0.793</v>
+        <v>0.787</v>
       </c>
       <c r="G843" t="n">
-        <v>0.907</v>
+        <v>0.9</v>
       </c>
       <c r="H843" t="n">
-        <v>0.00911</v>
+        <v>0.0105</v>
       </c>
       <c r="I843" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0838</v>
       </c>
     </row>
     <row r="844">
@@ -37076,10 +37076,10 @@
         <v>10</v>
       </c>
       <c r="F859" t="n">
-        <v>0.981</v>
+        <v>0.98</v>
       </c>
       <c r="G859" t="n">
-        <v>0.972</v>
+        <v>0.971</v>
       </c>
       <c r="H859" t="n">
         <v>1</v>
@@ -37668,16 +37668,16 @@
         <v>10</v>
       </c>
       <c r="F875" t="n">
-        <v>0.63</v>
+        <v>0.617</v>
       </c>
       <c r="G875" t="n">
-        <v>0.852</v>
+        <v>0.84</v>
       </c>
       <c r="H875" t="n">
-        <v>0.00208</v>
+        <v>0.00245</v>
       </c>
       <c r="I875" t="n">
-        <v>0.0167</v>
+        <v>0.0196</v>
       </c>
     </row>
     <row r="876">
@@ -38232,7 +38232,7 @@
         <v>0.00129</v>
       </c>
       <c r="I890" t="n">
-        <v>0.014</v>
+        <v>0.0109</v>
       </c>
     </row>
     <row r="891">
@@ -38260,16 +38260,16 @@
         <v>10</v>
       </c>
       <c r="F891" t="n">
-        <v>0.767</v>
+        <v>0.758</v>
       </c>
       <c r="G891" t="n">
-        <v>0.908</v>
+        <v>0.901</v>
       </c>
       <c r="H891" t="n">
-        <v>0.00174</v>
+        <v>0.00136</v>
       </c>
       <c r="I891" t="n">
-        <v>0.014</v>
+        <v>0.0109</v>
       </c>
     </row>
     <row r="892">
@@ -38713,7 +38713,7 @@
         <v>0.176</v>
       </c>
       <c r="I903" t="n">
-        <v>0.703</v>
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="904">
@@ -38852,16 +38852,16 @@
         <v>10</v>
       </c>
       <c r="F907" t="n">
-        <v>0.793</v>
+        <v>0.787</v>
       </c>
       <c r="G907" t="n">
         <v>0.853</v>
       </c>
       <c r="H907" t="n">
-        <v>0.226</v>
+        <v>0.176</v>
       </c>
       <c r="I907" t="n">
-        <v>0.722</v>
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="908">
@@ -39009,7 +39009,7 @@
         <v>0.135</v>
       </c>
       <c r="I911" t="n">
-        <v>0.703</v>
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="912">
@@ -39444,7 +39444,7 @@
         <v>10</v>
       </c>
       <c r="F923" t="n">
-        <v>0.981</v>
+        <v>0.98</v>
       </c>
       <c r="G923" t="n">
         <v>0.968</v>
@@ -39786,7 +39786,7 @@
         <v>0.101</v>
       </c>
       <c r="I932" t="n">
-        <v>0.502</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="933">
@@ -40036,16 +40036,16 @@
         <v>10</v>
       </c>
       <c r="F939" t="n">
-        <v>0.63</v>
+        <v>0.617</v>
       </c>
       <c r="G939" t="n">
         <v>0.753</v>
       </c>
       <c r="H939" t="n">
-        <v>0.125</v>
+        <v>0.0902</v>
       </c>
       <c r="I939" t="n">
-        <v>0.502</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="940">
@@ -40628,13 +40628,13 @@
         <v>10</v>
       </c>
       <c r="F955" t="n">
-        <v>0.767</v>
+        <v>0.758</v>
       </c>
       <c r="G955" t="n">
         <v>0.847</v>
       </c>
       <c r="H955" t="n">
-        <v>0.0951</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="I955" t="n">
         <v>1</v>

--- a/eval/learning-curve/results/statistical_tests_full150.xlsx
+++ b/eval/learning-curve/results/statistical_tests_full150.xlsx
@@ -518,7 +518,7 @@
         <v>0.102</v>
       </c>
       <c r="J2" t="n">
-        <v>0.293</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="3">
@@ -558,7 +558,7 @@
         <v>0.102</v>
       </c>
       <c r="J3" t="n">
-        <v>0.33</v>
+        <v>0.334</v>
       </c>
     </row>
     <row r="4">
@@ -598,7 +598,7 @@
         <v>0.169</v>
       </c>
       <c r="J4" t="n">
-        <v>0.594</v>
+        <v>0.681</v>
       </c>
     </row>
     <row r="5">
@@ -678,7 +678,7 @@
         <v>0.0877</v>
       </c>
       <c r="J6" t="n">
-        <v>0.48</v>
+        <v>0.5570000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -718,7 +718,7 @@
         <v>0.0877</v>
       </c>
       <c r="J7" t="n">
-        <v>0.453</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="8">
@@ -758,7 +758,7 @@
         <v>0.156</v>
       </c>
       <c r="J8" t="n">
-        <v>0.647</v>
+        <v>0.755</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.156</v>
       </c>
       <c r="J9" t="n">
-        <v>0.732</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="10">
@@ -838,7 +838,7 @@
         <v>0.167</v>
       </c>
       <c r="J10" t="n">
-        <v>0.555</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="11">
@@ -878,7 +878,7 @@
         <v>0.167</v>
       </c>
       <c r="J11" t="n">
-        <v>0.732</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="12">
@@ -918,7 +918,7 @@
         <v>0.152</v>
       </c>
       <c r="J12" t="n">
-        <v>0.628</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="13">
@@ -998,7 +998,7 @@
         <v>0.0829</v>
       </c>
       <c r="J14" t="n">
-        <v>0.214</v>
+        <v>0.251</v>
       </c>
     </row>
     <row r="15">
@@ -1038,7 +1038,7 @@
         <v>0.0829</v>
       </c>
       <c r="J15" t="n">
-        <v>0.33</v>
+        <v>0.308</v>
       </c>
     </row>
     <row r="16">
@@ -1078,7 +1078,7 @@
         <v>0.174</v>
       </c>
       <c r="J16" t="n">
-        <v>0.653</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="17">
@@ -1118,7 +1118,7 @@
         <v>0.174</v>
       </c>
       <c r="J17" t="n">
-        <v>0.732</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="18">
@@ -1158,7 +1158,7 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.015</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="19">
@@ -1198,7 +1198,7 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.014</v>
+        <v>0.0372</v>
       </c>
     </row>
     <row r="20">
@@ -1238,7 +1238,7 @@
         <v>0.0842</v>
       </c>
       <c r="J20" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.08890000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1278,7 +1278,7 @@
         <v>0.0842</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0997</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="22">
@@ -1318,7 +1318,7 @@
         <v>0.165</v>
       </c>
       <c r="J22" t="n">
-        <v>0.111</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="23">
@@ -1358,7 +1358,7 @@
         <v>0.165</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0997</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="24">
@@ -1398,7 +1398,7 @@
         <v>0.175</v>
       </c>
       <c r="J24" t="n">
-        <v>0.366</v>
+        <v>0.395</v>
       </c>
     </row>
     <row r="25">
@@ -1438,7 +1438,7 @@
         <v>0.175</v>
       </c>
       <c r="J25" t="n">
-        <v>0.33</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="26">
@@ -1478,7 +1478,7 @@
         <v>0.175</v>
       </c>
       <c r="J26" t="n">
-        <v>0.435</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="27">
@@ -1518,7 +1518,7 @@
         <v>0.175</v>
       </c>
       <c r="J27" t="n">
-        <v>0.453</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="28">
@@ -1558,7 +1558,7 @@
         <v>0.19</v>
       </c>
       <c r="J28" t="n">
-        <v>0.54</v>
+        <v>0.617</v>
       </c>
     </row>
     <row r="29">
@@ -1598,7 +1598,7 @@
         <v>0.19</v>
       </c>
       <c r="J29" t="n">
-        <v>0.508</v>
+        <v>0.598</v>
       </c>
     </row>
     <row r="30">
@@ -1638,7 +1638,7 @@
         <v>0.0931</v>
       </c>
       <c r="J30" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.08890000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1678,7 +1678,7 @@
         <v>0.0931</v>
       </c>
       <c r="J31" t="n">
-        <v>0.014</v>
+        <v>0.0372</v>
       </c>
     </row>
     <row r="32">
@@ -1718,7 +1718,7 @@
         <v>0.12</v>
       </c>
       <c r="J32" t="n">
-        <v>0.886</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="33">
@@ -1758,7 +1758,7 @@
         <v>0.12</v>
       </c>
       <c r="J33" t="n">
-        <v>0.575</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="34">
@@ -1798,7 +1798,7 @@
         <v>0.249</v>
       </c>
       <c r="J34" t="n">
-        <v>0.445</v>
+        <v>0.271</v>
       </c>
     </row>
     <row r="35">
@@ -1878,7 +1878,7 @@
         <v>0.134</v>
       </c>
       <c r="J36" t="n">
-        <v>0.886</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="37">
@@ -1918,7 +1918,7 @@
         <v>0.134</v>
       </c>
       <c r="J37" t="n">
-        <v>0.575</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="38">
@@ -1958,7 +1958,7 @@
         <v>0.22</v>
       </c>
       <c r="J38" t="n">
-        <v>0.664</v>
+        <v>0.581</v>
       </c>
     </row>
     <row r="39">
@@ -1998,7 +1998,7 @@
         <v>0.22</v>
       </c>
       <c r="J39" t="n">
-        <v>0.495</v>
+        <v>0.447</v>
       </c>
     </row>
     <row r="40">
@@ -2038,7 +2038,7 @@
         <v>0.185</v>
       </c>
       <c r="J40" t="n">
-        <v>0.445</v>
+        <v>0.395</v>
       </c>
     </row>
     <row r="41">
@@ -2078,7 +2078,7 @@
         <v>0.185</v>
       </c>
       <c r="J41" t="n">
-        <v>0.24</v>
+        <v>0.179</v>
       </c>
     </row>
     <row r="42">
@@ -2118,7 +2118,7 @@
         <v>0.255</v>
       </c>
       <c r="J42" t="n">
-        <v>0.445</v>
+        <v>0.395</v>
       </c>
     </row>
     <row r="43">
@@ -2158,7 +2158,7 @@
         <v>0.255</v>
       </c>
       <c r="J43" t="n">
-        <v>0.495</v>
+        <v>0.362</v>
       </c>
     </row>
     <row r="44">
@@ -2198,7 +2198,7 @@
         <v>0.107</v>
       </c>
       <c r="J44" t="n">
-        <v>0.886</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="45">
@@ -2238,7 +2238,7 @@
         <v>0.107</v>
       </c>
       <c r="J45" t="n">
-        <v>0.575</v>
+        <v>0.642</v>
       </c>
     </row>
     <row r="46">
@@ -2278,7 +2278,7 @@
         <v>0.224</v>
       </c>
       <c r="J46" t="n">
-        <v>0.445</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="47">
@@ -2318,7 +2318,7 @@
         <v>0.224</v>
       </c>
       <c r="J47" t="n">
-        <v>0.277</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="48">
@@ -2358,7 +2358,7 @@
         <v>0.0584</v>
       </c>
       <c r="J48" t="n">
-        <v>0.445</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="49">
@@ -2398,7 +2398,7 @@
         <v>0.0584</v>
       </c>
       <c r="J49" t="n">
-        <v>0.495</v>
+        <v>0.442</v>
       </c>
     </row>
     <row r="50">
@@ -2438,7 +2438,7 @@
         <v>0.11</v>
       </c>
       <c r="J50" t="n">
-        <v>0.886</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="51">
@@ -2478,7 +2478,7 @@
         <v>0.11</v>
       </c>
       <c r="J51" t="n">
-        <v>0.575</v>
+        <v>0.642</v>
       </c>
     </row>
     <row r="52">
@@ -2518,7 +2518,7 @@
         <v>0.195</v>
       </c>
       <c r="J52" t="n">
-        <v>0.776</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="53">
@@ -2558,7 +2558,7 @@
         <v>0.195</v>
       </c>
       <c r="J53" t="n">
-        <v>0.575</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="54">
@@ -2598,7 +2598,7 @@
         <v>0.183</v>
       </c>
       <c r="J54" t="n">
-        <v>0.886</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="55">
@@ -2638,7 +2638,7 @@
         <v>0.183</v>
       </c>
       <c r="J55" t="n">
-        <v>0.744</v>
+        <v>0.827</v>
       </c>
     </row>
     <row r="56">
@@ -2678,7 +2678,7 @@
         <v>0.189</v>
       </c>
       <c r="J56" t="n">
-        <v>0.886</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="57">
@@ -2718,7 +2718,7 @@
         <v>0.189</v>
       </c>
       <c r="J57" t="n">
-        <v>0.696</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="58">
@@ -2758,7 +2758,7 @@
         <v>0.195</v>
       </c>
       <c r="J58" t="n">
-        <v>0.886</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="59">
@@ -2798,7 +2798,7 @@
         <v>0.195</v>
       </c>
       <c r="J59" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="60">
@@ -2838,7 +2838,7 @@
         <v>0.0954</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0134</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="61">
@@ -2878,7 +2878,7 @@
         <v>0.0954</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0148</v>
+        <v>0.0372</v>
       </c>
     </row>
     <row r="62">
@@ -2918,7 +2918,7 @@
         <v>0.186</v>
       </c>
       <c r="J62" t="n">
-        <v>0.45</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="63">
@@ -2958,7 +2958,7 @@
         <v>0.186</v>
       </c>
       <c r="J63" t="n">
-        <v>0.232</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="64">
@@ -3038,7 +3038,7 @@
         <v>0.266</v>
       </c>
       <c r="J65" t="n">
-        <v>0.233</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="66">
@@ -3078,7 +3078,7 @@
         <v>0.149</v>
       </c>
       <c r="J66" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.755</v>
       </c>
     </row>
     <row r="67">
@@ -3118,7 +3118,7 @@
         <v>0.149</v>
       </c>
       <c r="J67" t="n">
-        <v>0.749</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="68">
@@ -3158,7 +3158,7 @@
         <v>0.239</v>
       </c>
       <c r="J68" t="n">
-        <v>0.61</v>
+        <v>0.681</v>
       </c>
     </row>
     <row r="69">
@@ -3238,7 +3238,7 @@
         <v>0.148</v>
       </c>
       <c r="J70" t="n">
-        <v>0.61</v>
+        <v>0.669</v>
       </c>
     </row>
     <row r="71">
@@ -3278,7 +3278,7 @@
         <v>0.148</v>
       </c>
       <c r="J71" t="n">
-        <v>0.541</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="72">
@@ -3318,7 +3318,7 @@
         <v>0.267</v>
       </c>
       <c r="J72" t="n">
-        <v>0.61</v>
+        <v>0.681</v>
       </c>
     </row>
     <row r="73">
@@ -3358,7 +3358,7 @@
         <v>0.267</v>
       </c>
       <c r="J73" t="n">
-        <v>0.921</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="74">
@@ -3398,7 +3398,7 @@
         <v>0.144</v>
       </c>
       <c r="J74" t="n">
-        <v>0.249</v>
+        <v>0.347</v>
       </c>
     </row>
     <row r="75">
@@ -3438,7 +3438,7 @@
         <v>0.144</v>
       </c>
       <c r="J75" t="n">
-        <v>0.232</v>
+        <v>0.308</v>
       </c>
     </row>
     <row r="76">
@@ -3478,7 +3478,7 @@
         <v>0.264</v>
       </c>
       <c r="J76" t="n">
-        <v>0.983</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3518,7 +3518,7 @@
         <v>0.264</v>
       </c>
       <c r="J77" t="n">
-        <v>0.495</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="78">
@@ -3558,7 +3558,7 @@
         <v>0.137</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0585</v>
+        <v>0.08890000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3598,7 +3598,7 @@
         <v>0.137</v>
       </c>
       <c r="J79" t="n">
-        <v>0.055</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="80">
@@ -3638,7 +3638,7 @@
         <v>0.185</v>
       </c>
       <c r="J80" t="n">
-        <v>0.236</v>
+        <v>0.314</v>
       </c>
     </row>
     <row r="81">
@@ -3678,7 +3678,7 @@
         <v>0.185</v>
       </c>
       <c r="J81" t="n">
-        <v>0.232</v>
+        <v>0.308</v>
       </c>
     </row>
     <row r="82">
@@ -3718,7 +3718,7 @@
         <v>0.18</v>
       </c>
       <c r="J82" t="n">
-        <v>0.0597</v>
+        <v>0.09950000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3758,7 +3758,7 @@
         <v>0.18</v>
       </c>
       <c r="J83" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="84">
@@ -3838,7 +3838,7 @@
         <v>0.16</v>
       </c>
       <c r="J85" t="n">
-        <v>0.055</v>
+        <v>0.0572</v>
       </c>
     </row>
     <row r="86">
@@ -3878,7 +3878,7 @@
         <v>0.155</v>
       </c>
       <c r="J86" t="n">
-        <v>0.0597</v>
+        <v>0.08890000000000001</v>
       </c>
     </row>
     <row r="87">
@@ -3918,7 +3918,7 @@
         <v>0.155</v>
       </c>
       <c r="J87" t="n">
-        <v>0.0746</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="88">
@@ -3958,7 +3958,7 @@
         <v>0.162</v>
       </c>
       <c r="J88" t="n">
-        <v>0.0585</v>
+        <v>0.08890000000000001</v>
       </c>
     </row>
     <row r="89">
@@ -3998,7 +3998,7 @@
         <v>0.162</v>
       </c>
       <c r="J89" t="n">
-        <v>0.055</v>
+        <v>0.0572</v>
       </c>
     </row>
     <row r="90">
@@ -4038,7 +4038,7 @@
         <v>0.163</v>
       </c>
       <c r="J90" t="n">
-        <v>0.236</v>
+        <v>0.314</v>
       </c>
     </row>
     <row r="91">
@@ -4078,7 +4078,7 @@
         <v>0.163</v>
       </c>
       <c r="J91" t="n">
-        <v>0.234</v>
+        <v>0.334</v>
       </c>
     </row>
     <row r="92">
@@ -4118,7 +4118,7 @@
         <v>0.139</v>
       </c>
       <c r="J92" t="n">
-        <v>0.648</v>
+        <v>0.733</v>
       </c>
     </row>
     <row r="93">
@@ -4158,7 +4158,7 @@
         <v>0.139</v>
       </c>
       <c r="J93" t="n">
-        <v>0.673</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="94">
@@ -4198,7 +4198,7 @@
         <v>0.247</v>
       </c>
       <c r="J94" t="n">
-        <v>0.577</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="95">
@@ -4238,7 +4238,7 @@
         <v>0.247</v>
       </c>
       <c r="J95" t="n">
-        <v>0.865</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="96">
@@ -4278,7 +4278,7 @@
         <v>0.116</v>
       </c>
       <c r="J96" t="n">
-        <v>0.848</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="97">
@@ -4318,7 +4318,7 @@
         <v>0.116</v>
       </c>
       <c r="J97" t="n">
-        <v>0.865</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="98">
@@ -4358,7 +4358,7 @@
         <v>0.224</v>
       </c>
       <c r="J98" t="n">
-        <v>0.577</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="99">
@@ -4398,7 +4398,7 @@
         <v>0.224</v>
       </c>
       <c r="J99" t="n">
-        <v>0.865</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="100">
@@ -4438,7 +4438,7 @@
         <v>0.152</v>
       </c>
       <c r="J100" t="n">
-        <v>0.694</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="101">
@@ -4478,7 +4478,7 @@
         <v>0.152</v>
       </c>
       <c r="J101" t="n">
-        <v>0.836</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="102">
@@ -4518,7 +4518,7 @@
         <v>0.256</v>
       </c>
       <c r="J102" t="n">
-        <v>0.577</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="103">
@@ -4558,7 +4558,7 @@
         <v>0.256</v>
       </c>
       <c r="J103" t="n">
-        <v>0.836</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="104">
@@ -4598,7 +4598,7 @@
         <v>0.107</v>
       </c>
       <c r="J104" t="n">
-        <v>0.577</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="105">
@@ -4638,7 +4638,7 @@
         <v>0.107</v>
       </c>
       <c r="J105" t="n">
-        <v>0.673</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="106">
@@ -4678,7 +4678,7 @@
         <v>0.238</v>
       </c>
       <c r="J106" t="n">
-        <v>0.648</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="107">
@@ -4718,7 +4718,7 @@
         <v>0.238</v>
       </c>
       <c r="J107" t="n">
-        <v>0.836</v>
+        <v>0.772</v>
       </c>
     </row>
     <row r="108">
@@ -4758,7 +4758,7 @@
         <v>0.0919</v>
       </c>
       <c r="J108" t="n">
-        <v>0.0483</v>
+        <v>0.0583</v>
       </c>
     </row>
     <row r="109">
@@ -4878,7 +4878,7 @@
         <v>0.149</v>
       </c>
       <c r="J111" t="n">
-        <v>0.124</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="112">
@@ -4918,7 +4918,7 @@
         <v>0.18</v>
       </c>
       <c r="J112" t="n">
-        <v>0.0755</v>
+        <v>0.08890000000000001</v>
       </c>
     </row>
     <row r="113">
@@ -4958,7 +4958,7 @@
         <v>0.18</v>
       </c>
       <c r="J113" t="n">
-        <v>0.055</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="114">
@@ -4998,7 +4998,7 @@
         <v>0.159</v>
       </c>
       <c r="J114" t="n">
-        <v>0.0833</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="115">
@@ -5038,7 +5038,7 @@
         <v>0.159</v>
       </c>
       <c r="J115" t="n">
-        <v>0.124</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="116">
@@ -5078,7 +5078,7 @@
         <v>0.161</v>
       </c>
       <c r="J116" t="n">
-        <v>0.107</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="117">
@@ -5118,7 +5118,7 @@
         <v>0.161</v>
       </c>
       <c r="J117" t="n">
-        <v>0.124</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="118">
@@ -5158,7 +5158,7 @@
         <v>0.169</v>
       </c>
       <c r="J118" t="n">
-        <v>0.107</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="119">
@@ -5198,7 +5198,7 @@
         <v>0.169</v>
       </c>
       <c r="J119" t="n">
-        <v>0.124</v>
+        <v>0.179</v>
       </c>
     </row>
     <row r="120">
@@ -5238,7 +5238,7 @@
         <v>0.137</v>
       </c>
       <c r="J120" t="n">
-        <v>0.0755</v>
+        <v>0.08890000000000001</v>
       </c>
     </row>
     <row r="121">
@@ -5278,7 +5278,7 @@
         <v>0.137</v>
       </c>
       <c r="J121" t="n">
-        <v>0.055</v>
+        <v>0.0572</v>
       </c>
     </row>
   </sheetData>

--- a/eval/learning-curve/results/statistical_tests_full150.xlsx
+++ b/eval/learning-curve/results/statistical_tests_full150.xlsx
@@ -5376,7 +5376,7 @@
         <v>0.149</v>
       </c>
       <c r="I2" t="n">
-        <v>0.398</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="3">
@@ -5413,7 +5413,7 @@
         <v>5.94e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>9.509999999999999e-05</v>
+        <v>8.91e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5450,7 +5450,7 @@
         <v>0.0517</v>
       </c>
       <c r="I4" t="n">
-        <v>0.252</v>
+        <v>0.259</v>
       </c>
     </row>
     <row r="5">
@@ -5524,7 +5524,7 @@
         <v>0.262</v>
       </c>
       <c r="I6" t="n">
-        <v>0.524</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -5561,7 +5561,7 @@
         <v>0.0601</v>
       </c>
       <c r="I7" t="n">
-        <v>0.252</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="8">
@@ -5598,7 +5598,7 @@
         <v>0.202</v>
       </c>
       <c r="I8" t="n">
-        <v>0.461</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -5635,7 +5635,7 @@
         <v>0.572</v>
       </c>
       <c r="I9" t="n">
-        <v>0.824</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -5672,7 +5672,7 @@
         <v>0.717</v>
       </c>
       <c r="I10" t="n">
-        <v>0.826</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="11">
@@ -5709,7 +5709,7 @@
         <v>0.135</v>
       </c>
       <c r="I11" t="n">
-        <v>0.398</v>
+        <v>0.338</v>
       </c>
     </row>
     <row r="12">
@@ -5746,7 +5746,7 @@
         <v>0.361</v>
       </c>
       <c r="I12" t="n">
-        <v>0.577</v>
+        <v>0.602</v>
       </c>
     </row>
     <row r="13">
@@ -5820,7 +5820,7 @@
         <v>0.723</v>
       </c>
       <c r="I14" t="n">
-        <v>0.826</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -5857,7 +5857,7 @@
         <v>0.618</v>
       </c>
       <c r="I15" t="n">
-        <v>0.824</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="16">
@@ -5894,7 +5894,7 @@
         <v>0.305</v>
       </c>
       <c r="I16" t="n">
-        <v>0.543</v>
+        <v>0.572</v>
       </c>
     </row>
     <row r="17">
@@ -5931,7 +5931,7 @@
         <v>0.0631</v>
       </c>
       <c r="I17" t="n">
-        <v>0.252</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="18">
@@ -5968,7 +5968,7 @@
         <v>0.213</v>
       </c>
       <c r="I18" t="n">
-        <v>0.652</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="19">
@@ -6005,7 +6005,7 @@
         <v>0.000154</v>
       </c>
       <c r="I19" t="n">
-        <v>0.00247</v>
+        <v>0.00115</v>
       </c>
     </row>
     <row r="20">
@@ -6042,7 +6042,7 @@
         <v>0.0323</v>
       </c>
       <c r="I20" t="n">
-        <v>0.258</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="21">
@@ -6079,7 +6079,7 @@
         <v>0.491</v>
       </c>
       <c r="I21" t="n">
-        <v>0.727</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -6116,7 +6116,7 @@
         <v>0.358</v>
       </c>
       <c r="I22" t="n">
-        <v>0.717</v>
+        <v>0.671</v>
       </c>
     </row>
     <row r="23">
@@ -6153,7 +6153,7 @@
         <v>0.469</v>
       </c>
       <c r="I23" t="n">
-        <v>0.727</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="24">
@@ -6190,7 +6190,7 @@
         <v>0.512</v>
       </c>
       <c r="I24" t="n">
-        <v>0.727</v>
+        <v>0.853</v>
       </c>
     </row>
     <row r="25">
@@ -6227,7 +6227,7 @@
         <v>0.545</v>
       </c>
       <c r="I25" t="n">
-        <v>0.727</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -6264,7 +6264,7 @@
         <v>0.618</v>
       </c>
       <c r="I26" t="n">
-        <v>0.76</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="27">
@@ -6301,7 +6301,7 @@
         <v>0.754</v>
       </c>
       <c r="I27" t="n">
-        <v>0.772</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -6338,7 +6338,7 @@
         <v>0.772</v>
       </c>
       <c r="I28" t="n">
-        <v>0.772</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -6375,7 +6375,7 @@
         <v>0.285</v>
       </c>
       <c r="I29" t="n">
-        <v>0.652</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="30">
@@ -6412,7 +6412,7 @@
         <v>0.704</v>
       </c>
       <c r="I30" t="n">
-        <v>0.772</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -6449,7 +6449,7 @@
         <v>0.064</v>
       </c>
       <c r="I31" t="n">
-        <v>0.341</v>
+        <v>0.09719999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -6486,7 +6486,7 @@
         <v>0.282</v>
       </c>
       <c r="I32" t="n">
-        <v>0.652</v>
+        <v>0.604</v>
       </c>
     </row>
     <row r="33">
@@ -6523,7 +6523,7 @@
         <v>0.159</v>
       </c>
       <c r="I33" t="n">
-        <v>0.638</v>
+        <v>0.477</v>
       </c>
     </row>
     <row r="34">
@@ -6560,7 +6560,7 @@
         <v>0.515</v>
       </c>
       <c r="I34" t="n">
-        <v>0.959</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="35">
@@ -6708,7 +6708,7 @@
         <v>0.386</v>
       </c>
       <c r="I38" t="n">
-        <v>0.883</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -6745,7 +6745,7 @@
         <v>0.007939999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>0.127</v>
+        <v>0.0132</v>
       </c>
     </row>
     <row r="40">
@@ -6782,7 +6782,7 @@
         <v>0.0288</v>
       </c>
       <c r="I40" t="n">
-        <v>0.231</v>
+        <v>0.0864</v>
       </c>
     </row>
     <row r="41">
@@ -6856,7 +6856,7 @@
         <v>0.798</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0.798</v>
       </c>
     </row>
     <row r="43">
@@ -6893,7 +6893,7 @@
         <v>0.111</v>
       </c>
       <c r="I43" t="n">
-        <v>0.445</v>
+        <v>0.238</v>
       </c>
     </row>
     <row r="44">
@@ -6930,7 +6930,7 @@
         <v>0.358</v>
       </c>
       <c r="I44" t="n">
-        <v>0.883</v>
+        <v>0.537</v>
       </c>
     </row>
     <row r="45">
@@ -6967,7 +6967,7 @@
         <v>0.383</v>
       </c>
       <c r="I45" t="n">
-        <v>0.883</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="46">
@@ -7041,7 +7041,7 @@
         <v>0.539</v>
       </c>
       <c r="I47" t="n">
-        <v>0.959</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -7115,7 +7115,7 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>0.445</v>
+        <v>0.273</v>
       </c>
     </row>
     <row r="50">
@@ -7152,7 +7152,7 @@
         <v>0.156</v>
       </c>
       <c r="I50" t="n">
-        <v>0.356</v>
+        <v>0.334</v>
       </c>
     </row>
     <row r="51">
@@ -7189,7 +7189,7 @@
         <v>0.000103</v>
       </c>
       <c r="I51" t="n">
-        <v>0.00165</v>
+        <v>0.00154</v>
       </c>
     </row>
     <row r="52">
@@ -7226,7 +7226,7 @@
         <v>0.0849</v>
       </c>
       <c r="I52" t="n">
-        <v>0.272</v>
+        <v>0.318</v>
       </c>
     </row>
     <row r="53">
@@ -7300,7 +7300,7 @@
         <v>0.208</v>
       </c>
       <c r="I54" t="n">
-        <v>0.416</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -7337,7 +7337,7 @@
         <v>0.0195</v>
       </c>
       <c r="I55" t="n">
-        <v>0.105</v>
+        <v>0.0482</v>
       </c>
     </row>
     <row r="56">
@@ -7374,7 +7374,7 @@
         <v>0.103</v>
       </c>
       <c r="I56" t="n">
-        <v>0.274</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="57">
@@ -7411,7 +7411,7 @@
         <v>0.272</v>
       </c>
       <c r="I57" t="n">
-        <v>0.436</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="58">
@@ -7448,7 +7448,7 @@
         <v>0.652</v>
       </c>
       <c r="I58" t="n">
-        <v>0.789</v>
+        <v>0.652</v>
       </c>
     </row>
     <row r="59">
@@ -7485,7 +7485,7 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>0.272</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="60">
@@ -7522,7 +7522,7 @@
         <v>0.244</v>
       </c>
       <c r="I60" t="n">
-        <v>0.435</v>
+        <v>0.407</v>
       </c>
     </row>
     <row r="61">
@@ -7559,7 +7559,7 @@
         <v>0.715</v>
       </c>
       <c r="I61" t="n">
-        <v>0.789</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -7596,7 +7596,7 @@
         <v>0.714</v>
       </c>
       <c r="I62" t="n">
-        <v>0.789</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -7633,7 +7633,7 @@
         <v>0.74</v>
       </c>
       <c r="I63" t="n">
-        <v>0.789</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="64">
@@ -7670,7 +7670,7 @@
         <v>0.435</v>
       </c>
       <c r="I64" t="n">
-        <v>0.633</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="65">
@@ -7707,7 +7707,7 @@
         <v>0.0197</v>
       </c>
       <c r="I65" t="n">
-        <v>0.105</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="66">
@@ -7744,7 +7744,7 @@
         <v>0.868</v>
       </c>
       <c r="I66" t="n">
-        <v>0.929</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -7781,7 +7781,7 @@
         <v>8.69e-05</v>
       </c>
       <c r="I67" t="n">
-        <v>0.000695</v>
+        <v>0.000326</v>
       </c>
     </row>
     <row r="68">
@@ -7818,7 +7818,7 @@
         <v>0.218</v>
       </c>
       <c r="I68" t="n">
-        <v>0.451</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="69">
@@ -7855,7 +7855,7 @@
         <v>1.79e-45</v>
       </c>
       <c r="I69" t="n">
-        <v>2.86e-44</v>
+        <v>1.34e-44</v>
       </c>
     </row>
     <row r="70">
@@ -7892,7 +7892,7 @@
         <v>0.769</v>
       </c>
       <c r="I70" t="n">
-        <v>0.929</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -7929,7 +7929,7 @@
         <v>0.226</v>
       </c>
       <c r="I71" t="n">
-        <v>0.451</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="72">
@@ -7966,7 +7966,7 @@
         <v>0.871</v>
       </c>
       <c r="I72" t="n">
-        <v>0.929</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -8003,7 +8003,7 @@
         <v>0.198</v>
       </c>
       <c r="I73" t="n">
-        <v>0.451</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="74">
@@ -8040,7 +8040,7 @@
         <v>0.099</v>
       </c>
       <c r="I74" t="n">
-        <v>0.396</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="75">
@@ -8077,7 +8077,7 @@
         <v>0.386</v>
       </c>
       <c r="I75" t="n">
-        <v>0.617</v>
+        <v>0.579</v>
       </c>
     </row>
     <row r="76">
@@ -8114,7 +8114,7 @@
         <v>0.361</v>
       </c>
       <c r="I76" t="n">
-        <v>0.617</v>
+        <v>0.602</v>
       </c>
     </row>
     <row r="77">
@@ -8151,7 +8151,7 @@
         <v>0.502</v>
       </c>
       <c r="I77" t="n">
-        <v>0.73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -8188,7 +8188,7 @@
         <v>0.218</v>
       </c>
       <c r="I78" t="n">
-        <v>0.451</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -8225,7 +8225,7 @@
         <v>0.0877</v>
       </c>
       <c r="I79" t="n">
-        <v>0.396</v>
+        <v>0.658</v>
       </c>
     </row>
     <row r="80">
@@ -8299,7 +8299,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>0.929</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -8336,7 +8336,7 @@
         <v>0.638</v>
       </c>
       <c r="I82" t="n">
-        <v>0.785</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -8373,7 +8373,7 @@
         <v>0.000325</v>
       </c>
       <c r="I83" t="n">
-        <v>0.00173</v>
+        <v>0.00162</v>
       </c>
     </row>
     <row r="84">
@@ -8410,7 +8410,7 @@
         <v>0.165</v>
       </c>
       <c r="I84" t="n">
-        <v>0.293</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="85">
@@ -8447,7 +8447,7 @@
         <v>8.13e-23</v>
       </c>
       <c r="I85" t="n">
-        <v>1.3e-21</v>
+        <v>6.1e-22</v>
       </c>
     </row>
     <row r="86">
@@ -8484,7 +8484,7 @@
         <v>0.138</v>
       </c>
       <c r="I86" t="n">
-        <v>0.277</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="87">
@@ -8521,7 +8521,7 @@
         <v>0.0286</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0764</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="88">
@@ -8558,7 +8558,7 @@
         <v>0.00489</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0195</v>
+        <v>0.0733</v>
       </c>
     </row>
     <row r="89">
@@ -8595,7 +8595,7 @@
         <v>0.138</v>
       </c>
       <c r="I89" t="n">
-        <v>0.277</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -8632,7 +8632,7 @@
         <v>0.233</v>
       </c>
       <c r="I90" t="n">
-        <v>0.373</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="91">
@@ -8706,7 +8706,7 @@
         <v>0.623</v>
       </c>
       <c r="I92" t="n">
-        <v>0.785</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -8743,7 +8743,7 @@
         <v>0.0128</v>
       </c>
       <c r="I93" t="n">
-        <v>0.041</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="94">
@@ -8780,7 +8780,7 @@
         <v>0.308</v>
       </c>
       <c r="I94" t="n">
-        <v>0.448</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -8817,7 +8817,7 @@
         <v>0.000136</v>
       </c>
       <c r="I95" t="n">
-        <v>0.00109</v>
+        <v>0.00204</v>
       </c>
     </row>
     <row r="96">
@@ -8891,7 +8891,7 @@
         <v>0.85</v>
       </c>
       <c r="I97" t="n">
-        <v>0.971</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="98">
@@ -8928,7 +8928,7 @@
         <v>0.259</v>
       </c>
       <c r="I98" t="n">
-        <v>0.414</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="99">
@@ -8965,7 +8965,7 @@
         <v>0.236</v>
       </c>
       <c r="I99" t="n">
-        <v>0.414</v>
+        <v>0.443</v>
       </c>
     </row>
     <row r="100">
@@ -9039,7 +9039,7 @@
         <v>2.19e-11</v>
       </c>
       <c r="I101" t="n">
-        <v>3.5e-10</v>
+        <v>1.09e-10</v>
       </c>
     </row>
     <row r="102">
@@ -9076,7 +9076,7 @@
         <v>0.735</v>
       </c>
       <c r="I102" t="n">
-        <v>0.905</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -9113,7 +9113,7 @@
         <v>0.000174</v>
       </c>
       <c r="I103" t="n">
-        <v>0.00139</v>
+        <v>0.00087</v>
       </c>
     </row>
     <row r="104">
@@ -9150,7 +9150,7 @@
         <v>0.00231</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0123</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="105">
@@ -9187,7 +9187,7 @@
         <v>0.637</v>
       </c>
       <c r="I105" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -9224,7 +9224,7 @@
         <v>0.022</v>
       </c>
       <c r="I106" t="n">
-        <v>0.0703</v>
+        <v>0.0412</v>
       </c>
     </row>
     <row r="107">
@@ -9261,7 +9261,7 @@
         <v>0.299</v>
       </c>
       <c r="I107" t="n">
-        <v>0.435</v>
+        <v>0.498</v>
       </c>
     </row>
     <row r="108">
@@ -9298,7 +9298,7 @@
         <v>0.0598</v>
       </c>
       <c r="I108" t="n">
-        <v>0.159</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="109">
@@ -9335,7 +9335,7 @@
         <v>0.178</v>
       </c>
       <c r="I109" t="n">
-        <v>0.379</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="110">
@@ -9409,7 +9409,7 @@
         <v>0.0216</v>
       </c>
       <c r="I111" t="n">
-        <v>0.0703</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="112">
@@ -9483,7 +9483,7 @@
         <v>0.19</v>
       </c>
       <c r="I113" t="n">
-        <v>0.379</v>
+        <v>0.407</v>
       </c>
     </row>
     <row r="114">
@@ -9520,7 +9520,7 @@
         <v>0.629</v>
       </c>
       <c r="I114" t="n">
-        <v>0.839</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="115">
@@ -9557,7 +9557,7 @@
         <v>0.00293</v>
       </c>
       <c r="I115" t="n">
-        <v>0.0234</v>
+        <v>0.008789999999999999</v>
       </c>
     </row>
     <row r="116">
@@ -9594,7 +9594,7 @@
         <v>0.214</v>
       </c>
       <c r="I116" t="n">
-        <v>0.411</v>
+        <v>0.642</v>
       </c>
     </row>
     <row r="117">
@@ -9631,7 +9631,7 @@
         <v>7.32e-37</v>
       </c>
       <c r="I117" t="n">
-        <v>1.17e-35</v>
+        <v>5.49e-36</v>
       </c>
     </row>
     <row r="118">
@@ -9668,7 +9668,7 @@
         <v>0.886</v>
       </c>
       <c r="I118" t="n">
-        <v>0.945</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -9705,7 +9705,7 @@
         <v>0.0372</v>
       </c>
       <c r="I119" t="n">
-        <v>0.149</v>
+        <v>0.0697</v>
       </c>
     </row>
     <row r="120">
@@ -9742,7 +9742,7 @@
         <v>0.871</v>
       </c>
       <c r="I120" t="n">
-        <v>0.945</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="121">
@@ -9779,7 +9779,7 @@
         <v>0.156</v>
       </c>
       <c r="I121" t="n">
-        <v>0.411</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="122">
@@ -9816,7 +9816,7 @@
         <v>0.031</v>
       </c>
       <c r="I122" t="n">
-        <v>0.149</v>
+        <v>0.0598</v>
       </c>
     </row>
     <row r="123">
@@ -9853,7 +9853,7 @@
         <v>0.299</v>
       </c>
       <c r="I123" t="n">
-        <v>0.478</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="124">
@@ -9890,7 +9890,7 @@
         <v>0.123</v>
       </c>
       <c r="I124" t="n">
-        <v>0.392</v>
+        <v>0.231</v>
       </c>
     </row>
     <row r="125">
@@ -9927,7 +9927,7 @@
         <v>0.864</v>
       </c>
       <c r="I125" t="n">
-        <v>0.945</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -9964,7 +9964,7 @@
         <v>0.206</v>
       </c>
       <c r="I126" t="n">
-        <v>0.411</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -10001,7 +10001,7 @@
         <v>0.353</v>
       </c>
       <c r="I127" t="n">
-        <v>0.513</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="128">
@@ -10075,7 +10075,7 @@
         <v>0.231</v>
       </c>
       <c r="I129" t="n">
-        <v>0.411</v>
+        <v>0.433</v>
       </c>
     </row>
     <row r="130">
@@ -10112,7 +10112,7 @@
         <v>0.532</v>
       </c>
       <c r="I130" t="n">
-        <v>0.742</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="131">
@@ -10149,7 +10149,7 @@
         <v>2.5e-05</v>
       </c>
       <c r="I131" t="n">
-        <v>0.0004</v>
+        <v>0.000188</v>
       </c>
     </row>
     <row r="132">
@@ -10186,7 +10186,7 @@
         <v>0.00592</v>
       </c>
       <c r="I132" t="n">
-        <v>0.0474</v>
+        <v>0.0444</v>
       </c>
     </row>
     <row r="133">
@@ -10223,7 +10223,7 @@
         <v>0.214</v>
       </c>
       <c r="I133" t="n">
-        <v>0.489</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="134">
@@ -10260,7 +10260,7 @@
         <v>0.759</v>
       </c>
       <c r="I134" t="n">
-        <v>0.867</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -10297,7 +10297,7 @@
         <v>0.0398</v>
       </c>
       <c r="I135" t="n">
-        <v>0.212</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="136">
@@ -10334,7 +10334,7 @@
         <v>0.603</v>
       </c>
       <c r="I136" t="n">
-        <v>0.742</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -10371,7 +10371,7 @@
         <v>0.572</v>
       </c>
       <c r="I137" t="n">
-        <v>0.742</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="138">
@@ -10408,7 +10408,7 @@
         <v>0.384</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="139">
@@ -10445,7 +10445,7 @@
         <v>0.103</v>
       </c>
       <c r="I139" t="n">
-        <v>0.328</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="140">
@@ -10482,7 +10482,7 @@
         <v>0.0813</v>
       </c>
       <c r="I140" t="n">
-        <v>0.325</v>
+        <v>0.305</v>
       </c>
     </row>
     <row r="141">
@@ -10556,7 +10556,7 @@
         <v>0.335</v>
       </c>
       <c r="I142" t="n">
-        <v>0.671</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -10593,7 +10593,7 @@
         <v>0.865</v>
       </c>
       <c r="I143" t="n">
-        <v>0.923</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="144">
@@ -10630,7 +10630,7 @@
         <v>0.445</v>
       </c>
       <c r="I144" t="n">
-        <v>0.713</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="145">
@@ -10667,7 +10667,7 @@
         <v>0.14</v>
       </c>
       <c r="I145" t="n">
-        <v>0.375</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="146">
@@ -10704,7 +10704,7 @@
         <v>0.009730000000000001</v>
       </c>
       <c r="I146" t="n">
-        <v>0.0779</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="147">
@@ -10741,7 +10741,7 @@
         <v>7.26e-05</v>
       </c>
       <c r="I147" t="n">
-        <v>0.00116</v>
+        <v>0.00109</v>
       </c>
     </row>
     <row r="148">
@@ -10778,7 +10778,7 @@
         <v>0.0151</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0804</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="149">
@@ -10815,7 +10815,7 @@
         <v>0.059</v>
       </c>
       <c r="I149" t="n">
-        <v>0.236</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="150">
@@ -10852,7 +10852,7 @@
         <v>0.6820000000000001</v>
       </c>
       <c r="I150" t="n">
-        <v>0.779</v>
+        <v>0.772</v>
       </c>
     </row>
     <row r="151">
@@ -10889,7 +10889,7 @@
         <v>0.304</v>
       </c>
       <c r="I151" t="n">
-        <v>0.635</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="152">
@@ -10926,7 +10926,7 @@
         <v>0.347</v>
       </c>
       <c r="I152" t="n">
-        <v>0.635</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="153">
@@ -10963,7 +10963,7 @@
         <v>0.5590000000000001</v>
       </c>
       <c r="I153" t="n">
-        <v>0.746</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -11037,7 +11037,7 @@
         <v>0.546</v>
       </c>
       <c r="I155" t="n">
-        <v>0.746</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -11111,7 +11111,7 @@
         <v>0.679</v>
       </c>
       <c r="I157" t="n">
-        <v>0.779</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="158">
@@ -11148,7 +11148,7 @@
         <v>0.309</v>
       </c>
       <c r="I158" t="n">
-        <v>0.635</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -11185,7 +11185,7 @@
         <v>0.441</v>
       </c>
       <c r="I159" t="n">
-        <v>0.705</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="160">
@@ -11222,7 +11222,7 @@
         <v>0.357</v>
       </c>
       <c r="I160" t="n">
-        <v>0.635</v>
+        <v>0.613</v>
       </c>
     </row>
     <row r="161">
@@ -11259,7 +11259,7 @@
         <v>0.238</v>
       </c>
       <c r="I161" t="n">
-        <v>0.635</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="162">
@@ -11296,7 +11296,7 @@
         <v>0.0352</v>
       </c>
       <c r="I162" t="n">
-        <v>0.188</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="163">
@@ -11333,7 +11333,7 @@
         <v>0.236</v>
       </c>
       <c r="I163" t="n">
-        <v>0.539</v>
+        <v>0.443</v>
       </c>
     </row>
     <row r="164">
@@ -11481,7 +11481,7 @@
         <v>0.0009940000000000001</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0159</v>
+        <v>0.00249</v>
       </c>
     </row>
     <row r="168">
@@ -11518,7 +11518,7 @@
         <v>0.0919</v>
       </c>
       <c r="I168" t="n">
-        <v>0.356</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="169">
@@ -11592,7 +11592,7 @@
         <v>0.294</v>
       </c>
       <c r="I170" t="n">
-        <v>0.588</v>
+        <v>0.367</v>
       </c>
     </row>
     <row r="171">
@@ -11629,7 +11629,7 @@
         <v>0.111</v>
       </c>
       <c r="I171" t="n">
-        <v>0.356</v>
+        <v>0.238</v>
       </c>
     </row>
     <row r="172">
@@ -11666,7 +11666,7 @@
         <v>0.0169</v>
       </c>
       <c r="I172" t="n">
-        <v>0.135</v>
+        <v>0.0634</v>
       </c>
     </row>
     <row r="173">
@@ -11703,7 +11703,7 @@
         <v>0.834</v>
       </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="174">
@@ -11814,7 +11814,7 @@
         <v>0.712</v>
       </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="177">
@@ -11851,7 +11851,7 @@
         <v>0.133</v>
       </c>
       <c r="I177" t="n">
-        <v>0.356</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="178">
@@ -11888,7 +11888,7 @@
         <v>0.283</v>
       </c>
       <c r="I178" t="n">
-        <v>0.503</v>
+        <v>0.472</v>
       </c>
     </row>
     <row r="179">
@@ -11925,7 +11925,7 @@
         <v>0.00116</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0185</v>
+        <v>0.007900000000000001</v>
       </c>
     </row>
     <row r="180">
@@ -11962,7 +11962,7 @@
         <v>0.00903</v>
       </c>
       <c r="I180" t="n">
-        <v>0.0481</v>
+        <v>0.0677</v>
       </c>
     </row>
     <row r="181">
@@ -11999,7 +11999,7 @@
         <v>0.209</v>
       </c>
       <c r="I181" t="n">
-        <v>0.478</v>
+        <v>0.506</v>
       </c>
     </row>
     <row r="182">
@@ -12036,7 +12036,7 @@
         <v>0.653</v>
       </c>
       <c r="I182" t="n">
-        <v>0.804</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -12073,7 +12073,7 @@
         <v>0.00775</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0481</v>
+        <v>0.0403</v>
       </c>
     </row>
     <row r="184">
@@ -12110,7 +12110,7 @@
         <v>0.389</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="185">
@@ -12147,7 +12147,7 @@
         <v>0.473</v>
       </c>
       <c r="I185" t="n">
-        <v>0.63</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="186">
@@ -12184,7 +12184,7 @@
         <v>0.243</v>
       </c>
       <c r="I186" t="n">
-        <v>0.485</v>
+        <v>0.304</v>
       </c>
     </row>
     <row r="187">
@@ -12221,7 +12221,7 @@
         <v>0.0532</v>
       </c>
       <c r="I187" t="n">
-        <v>0.142</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="188">
@@ -12258,7 +12258,7 @@
         <v>0.0176</v>
       </c>
       <c r="I188" t="n">
-        <v>0.0706</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="189">
@@ -12332,7 +12332,7 @@
         <v>0.321</v>
       </c>
       <c r="I190" t="n">
-        <v>0.514</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -12369,7 +12369,7 @@
         <v>0.865</v>
       </c>
       <c r="I191" t="n">
-        <v>0.922</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="192">
@@ -12406,7 +12406,7 @@
         <v>0.794</v>
       </c>
       <c r="I192" t="n">
-        <v>0.908</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="193">
@@ -12443,7 +12443,7 @@
         <v>0.0416</v>
       </c>
       <c r="I193" t="n">
-        <v>0.133</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="194">
@@ -12480,7 +12480,7 @@
         <v>0.868</v>
       </c>
       <c r="I194" t="n">
-        <v>0.992</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
@@ -12517,7 +12517,7 @@
         <v>0.0035</v>
       </c>
       <c r="I195" t="n">
-        <v>0.028</v>
+        <v>0.00656</v>
       </c>
     </row>
     <row r="196">
@@ -12554,7 +12554,7 @@
         <v>0.501</v>
       </c>
       <c r="I196" t="n">
-        <v>0.802</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="197">
@@ -12591,7 +12591,7 @@
         <v>1.15e-41</v>
       </c>
       <c r="I197" t="n">
-        <v>1.84e-40</v>
+        <v>5.75e-41</v>
       </c>
     </row>
     <row r="198">
@@ -12665,7 +12665,7 @@
         <v>0.0877</v>
       </c>
       <c r="I199" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="200">
@@ -12739,7 +12739,7 @@
         <v>0.77</v>
       </c>
       <c r="I201" t="n">
-        <v>0.992</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="202">
@@ -12776,7 +12776,7 @@
         <v>0.806</v>
       </c>
       <c r="I202" t="n">
-        <v>0.992</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="203">
@@ -12813,7 +12813,7 @@
         <v>0.751</v>
       </c>
       <c r="I203" t="n">
-        <v>0.992</v>
+        <v>0.867</v>
       </c>
     </row>
     <row r="204">
@@ -12850,7 +12850,7 @@
         <v>0.109</v>
       </c>
       <c r="I204" t="n">
-        <v>0.35</v>
+        <v>0.327</v>
       </c>
     </row>
     <row r="205">
@@ -12887,7 +12887,7 @@
         <v>0.406</v>
       </c>
       <c r="I205" t="n">
-        <v>0.721</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
@@ -12924,7 +12924,7 @@
         <v>0.218</v>
       </c>
       <c r="I206" t="n">
-        <v>0.581</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
@@ -12961,7 +12961,7 @@
         <v>0.262</v>
       </c>
       <c r="I207" t="n">
-        <v>0.599</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="208">
@@ -12998,7 +12998,7 @@
         <v>0.305</v>
       </c>
       <c r="I208" t="n">
-        <v>0.611</v>
+        <v>0.572</v>
       </c>
     </row>
     <row r="209">
@@ -13035,7 +13035,7 @@
         <v>0.109</v>
       </c>
       <c r="I209" t="n">
-        <v>0.35</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="210">
@@ -13072,7 +13072,7 @@
         <v>0.636</v>
       </c>
       <c r="I210" t="n">
-        <v>0.887</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -13109,7 +13109,7 @@
         <v>0.00792</v>
       </c>
       <c r="I211" t="n">
-        <v>0.0423</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="212">
@@ -13146,7 +13146,7 @@
         <v>0.671</v>
       </c>
       <c r="I212" t="n">
-        <v>0.887</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="213">
@@ -13183,7 +13183,7 @@
         <v>3.18e-20</v>
       </c>
       <c r="I213" t="n">
-        <v>5.08e-19</v>
+        <v>1.19e-19</v>
       </c>
     </row>
     <row r="214">
@@ -13220,7 +13220,7 @@
         <v>0.72</v>
       </c>
       <c r="I214" t="n">
-        <v>0.887</v>
+        <v>0.772</v>
       </c>
     </row>
     <row r="215">
@@ -13257,7 +13257,7 @@
         <v>0.0469</v>
       </c>
       <c r="I215" t="n">
-        <v>0.187</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="216">
@@ -13294,7 +13294,7 @@
         <v>0.0915</v>
       </c>
       <c r="I216" t="n">
-        <v>0.209</v>
+        <v>0.343</v>
       </c>
     </row>
     <row r="217">
@@ -13368,7 +13368,7 @@
         <v>0.622</v>
       </c>
       <c r="I218" t="n">
-        <v>0.887</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="219">
@@ -13442,7 +13442,7 @@
         <v>0.781</v>
       </c>
       <c r="I220" t="n">
-        <v>0.892</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -13479,7 +13479,7 @@
         <v>0.0609</v>
       </c>
       <c r="I221" t="n">
-        <v>0.195</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="222">
@@ -13516,7 +13516,7 @@
         <v>0.3</v>
       </c>
       <c r="I222" t="n">
-        <v>0.534</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -13553,7 +13553,7 @@
         <v>0.00724</v>
       </c>
       <c r="I223" t="n">
-        <v>0.0423</v>
+        <v>0.0181</v>
       </c>
     </row>
     <row r="224">
@@ -13590,7 +13590,7 @@
         <v>0.0798</v>
       </c>
       <c r="I224" t="n">
-        <v>0.209</v>
+        <v>0.299</v>
       </c>
     </row>
     <row r="225">
@@ -13627,7 +13627,7 @@
         <v>0.139</v>
       </c>
       <c r="I225" t="n">
-        <v>0.278</v>
+        <v>0.477</v>
       </c>
     </row>
     <row r="226">
@@ -13664,7 +13664,7 @@
         <v>0.376</v>
       </c>
       <c r="I226" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="227">
@@ -13701,7 +13701,7 @@
         <v>0.111</v>
       </c>
       <c r="I227" t="n">
-        <v>0.355</v>
+        <v>0.443</v>
       </c>
     </row>
     <row r="228">
@@ -13775,7 +13775,7 @@
         <v>5.07e-09</v>
       </c>
       <c r="I229" t="n">
-        <v>8.12e-08</v>
+        <v>1.9e-08</v>
       </c>
     </row>
     <row r="230">
@@ -13812,7 +13812,7 @@
         <v>0.867</v>
       </c>
       <c r="I230" t="n">
-        <v>0.991</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -13849,7 +13849,7 @@
         <v>6.35e-05</v>
       </c>
       <c r="I231" t="n">
-        <v>0.000508</v>
+        <v>0.00087</v>
       </c>
     </row>
     <row r="232">
@@ -13886,7 +13886,7 @@
         <v>0.0919</v>
       </c>
       <c r="I232" t="n">
-        <v>0.355</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="233">
@@ -13923,7 +13923,7 @@
         <v>0.637</v>
       </c>
       <c r="I233" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
@@ -13960,7 +13960,7 @@
         <v>0.603</v>
       </c>
       <c r="I234" t="n">
-        <v>0.85</v>
+        <v>0.696</v>
       </c>
     </row>
     <row r="235">
@@ -13997,7 +13997,7 @@
         <v>0.578</v>
       </c>
       <c r="I235" t="n">
-        <v>0.85</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="236">
@@ -14034,7 +14034,7 @@
         <v>0.0598</v>
       </c>
       <c r="I236" t="n">
-        <v>0.319</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="237">
@@ -14071,7 +14071,7 @@
         <v>0.834</v>
       </c>
       <c r="I237" t="n">
-        <v>0.991</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="238">
@@ -14145,7 +14145,7 @@
         <v>0.407</v>
       </c>
       <c r="I239" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="240">
@@ -14182,7 +14182,7 @@
         <v>0.277</v>
       </c>
       <c r="I240" t="n">
-        <v>0.74</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="241">
@@ -14219,7 +14219,7 @@
         <v>0.574</v>
       </c>
       <c r="I241" t="n">
-        <v>0.85</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="242">
@@ -14256,7 +14256,7 @@
         <v>0.745</v>
       </c>
       <c r="I242" t="n">
-        <v>0.851</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="243">
@@ -14293,7 +14293,7 @@
         <v>0.0456</v>
       </c>
       <c r="I243" t="n">
-        <v>0.182</v>
+        <v>0.0848</v>
       </c>
     </row>
     <row r="244">
@@ -14330,7 +14330,7 @@
         <v>0.49</v>
       </c>
       <c r="I244" t="n">
-        <v>0.794</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="245">
@@ -14367,7 +14367,7 @@
         <v>2.2e-31</v>
       </c>
       <c r="I245" t="n">
-        <v>3.52e-30</v>
+        <v>8.250000000000001e-31</v>
       </c>
     </row>
     <row r="246">
@@ -14441,7 +14441,7 @@
         <v>0.0136</v>
       </c>
       <c r="I247" t="n">
-        <v>0.109</v>
+        <v>0.0482</v>
       </c>
     </row>
     <row r="248">
@@ -14478,7 +14478,7 @@
         <v>0.62</v>
       </c>
       <c r="I248" t="n">
-        <v>0.794</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="249">
@@ -14515,7 +14515,7 @@
         <v>0.445</v>
       </c>
       <c r="I249" t="n">
-        <v>0.794</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="250">
@@ -14552,7 +14552,7 @@
         <v>0.645</v>
       </c>
       <c r="I250" t="n">
-        <v>0.794</v>
+        <v>0.652</v>
       </c>
     </row>
     <row r="251">
@@ -14589,7 +14589,7 @@
         <v>0.634</v>
       </c>
       <c r="I251" t="n">
-        <v>0.794</v>
+        <v>0.792</v>
       </c>
     </row>
     <row r="252">
@@ -14626,7 +14626,7 @@
         <v>0.0358</v>
       </c>
       <c r="I252" t="n">
-        <v>0.182</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="253">
@@ -14663,7 +14663,7 @@
         <v>0.499</v>
       </c>
       <c r="I253" t="n">
-        <v>0.794</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
@@ -14700,7 +14700,7 @@
         <v>0.2</v>
       </c>
       <c r="I254" t="n">
-        <v>0.535</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -14737,7 +14737,7 @@
         <v>0.425</v>
       </c>
       <c r="I255" t="n">
-        <v>0.794</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="256">
@@ -14774,7 +14774,7 @@
         <v>0.895</v>
       </c>
       <c r="I256" t="n">
-        <v>0.954</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="257">
@@ -14811,7 +14811,7 @@
         <v>0.127</v>
       </c>
       <c r="I257" t="n">
-        <v>0.407</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="258">
@@ -14885,7 +14885,7 @@
         <v>0.0035</v>
       </c>
       <c r="I259" t="n">
-        <v>0.014</v>
+        <v>0.00656</v>
       </c>
     </row>
     <row r="260">
@@ -14922,7 +14922,7 @@
         <v>0.00333</v>
       </c>
       <c r="I260" t="n">
-        <v>0.014</v>
+        <v>0.0444</v>
       </c>
     </row>
     <row r="261">
@@ -14996,7 +14996,7 @@
         <v>0.318</v>
       </c>
       <c r="I262" t="n">
-        <v>0.727</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
@@ -15033,7 +15033,7 @@
         <v>0.226</v>
       </c>
       <c r="I263" t="n">
-        <v>0.602</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="264">
@@ -15107,7 +15107,7 @@
         <v>0.77</v>
       </c>
       <c r="I265" t="n">
-        <v>1</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="266">
@@ -15144,7 +15144,7 @@
         <v>0.129</v>
       </c>
       <c r="I266" t="n">
-        <v>0.413</v>
+        <v>0.215</v>
       </c>
     </row>
     <row r="267">
@@ -15181,7 +15181,7 @@
         <v>0.737</v>
       </c>
       <c r="I267" t="n">
-        <v>1</v>
+        <v>0.867</v>
       </c>
     </row>
     <row r="268">
@@ -15218,7 +15218,7 @@
         <v>0.517</v>
       </c>
       <c r="I268" t="n">
-        <v>0.92</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="269">
@@ -15329,7 +15329,7 @@
         <v>0.51</v>
       </c>
       <c r="I271" t="n">
-        <v>0.92</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="272">
@@ -15366,7 +15366,7 @@
         <v>0.000646</v>
       </c>
       <c r="I272" t="n">
-        <v>0.00517</v>
+        <v>0.00323</v>
       </c>
     </row>
     <row r="273">
@@ -15403,7 +15403,7 @@
         <v>2.96e-05</v>
       </c>
       <c r="I273" t="n">
-        <v>0.000474</v>
+        <v>0.000222</v>
       </c>
     </row>
     <row r="274">
@@ -15440,7 +15440,7 @@
         <v>0.377</v>
       </c>
       <c r="I274" t="n">
-        <v>0.604</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
@@ -15477,7 +15477,7 @@
         <v>0.0104</v>
       </c>
       <c r="I275" t="n">
-        <v>0.104</v>
+        <v>0.0195</v>
       </c>
     </row>
     <row r="276">
@@ -15514,7 +15514,7 @@
         <v>0.0141</v>
       </c>
       <c r="I276" t="n">
-        <v>0.104</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="277">
@@ -15588,7 +15588,7 @@
         <v>0.211</v>
       </c>
       <c r="I278" t="n">
-        <v>0.421</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="279">
@@ -15625,7 +15625,7 @@
         <v>0.189</v>
       </c>
       <c r="I279" t="n">
-        <v>0.421</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="280">
@@ -15662,7 +15662,7 @@
         <v>0.336</v>
       </c>
       <c r="I280" t="n">
-        <v>0.598</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="281">
@@ -15736,7 +15736,7 @@
         <v>0.0805</v>
       </c>
       <c r="I282" t="n">
-        <v>0.215</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="283">
@@ -15773,7 +15773,7 @@
         <v>0.441</v>
       </c>
       <c r="I283" t="n">
-        <v>0.642</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284">
@@ -15847,7 +15847,7 @@
         <v>0.678</v>
       </c>
       <c r="I285" t="n">
-        <v>0.905</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="286">
@@ -15921,7 +15921,7 @@
         <v>0.0639</v>
       </c>
       <c r="I287" t="n">
-        <v>0.204</v>
+        <v>0.09719999999999999</v>
       </c>
     </row>
     <row r="288">
@@ -15958,7 +15958,7 @@
         <v>0.0196</v>
       </c>
       <c r="I288" t="n">
-        <v>0.104</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="289">
@@ -15995,7 +15995,7 @@
         <v>0.0534</v>
       </c>
       <c r="I289" t="n">
-        <v>0.204</v>
+        <v>0.267</v>
       </c>
     </row>
     <row r="290">
@@ -16032,7 +16032,7 @@
         <v>0.5639999999999999</v>
       </c>
       <c r="I290" t="n">
-        <v>0.995</v>
+        <v>0.604</v>
       </c>
     </row>
     <row r="291">
@@ -16069,7 +16069,7 @@
         <v>0.236</v>
       </c>
       <c r="I291" t="n">
-        <v>0.752</v>
+        <v>0.443</v>
       </c>
     </row>
     <row r="292">
@@ -16106,7 +16106,7 @@
         <v>0.352</v>
       </c>
       <c r="I292" t="n">
-        <v>0.804</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293">
@@ -16180,7 +16180,7 @@
         <v>0.746</v>
       </c>
       <c r="I294" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
@@ -16217,7 +16217,7 @@
         <v>0.0141</v>
       </c>
       <c r="I295" t="n">
-        <v>0.0934</v>
+        <v>0.0211</v>
       </c>
     </row>
     <row r="296">
@@ -16254,7 +16254,7 @@
         <v>0.427</v>
       </c>
       <c r="I296" t="n">
-        <v>0.855</v>
+        <v>0.582</v>
       </c>
     </row>
     <row r="297">
@@ -16291,7 +16291,7 @@
         <v>0.637</v>
       </c>
       <c r="I297" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298">
@@ -16328,7 +16328,7 @@
         <v>0.00991</v>
       </c>
       <c r="I298" t="n">
-        <v>0.0934</v>
+        <v>0.0212</v>
       </c>
     </row>
     <row r="299">
@@ -16402,7 +16402,7 @@
         <v>0.282</v>
       </c>
       <c r="I300" t="n">
-        <v>0.752</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="301">
@@ -16513,7 +16513,7 @@
         <v>0.6860000000000001</v>
       </c>
       <c r="I303" t="n">
-        <v>0.995</v>
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="304">
@@ -16550,7 +16550,7 @@
         <v>0.0184</v>
       </c>
       <c r="I304" t="n">
-        <v>0.0934</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="305">
@@ -16587,7 +16587,7 @@
         <v>0.0234</v>
       </c>
       <c r="I305" t="n">
-        <v>0.0934</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="306">
@@ -16661,7 +16661,7 @@
         <v>0.0301</v>
       </c>
       <c r="I307" t="n">
-        <v>0.17</v>
+        <v>0.0645</v>
       </c>
     </row>
     <row r="308">
@@ -16698,7 +16698,7 @@
         <v>0.00483</v>
       </c>
       <c r="I308" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0677</v>
       </c>
     </row>
     <row r="309">
@@ -16735,7 +16735,7 @@
         <v>0.616</v>
       </c>
       <c r="I309" t="n">
-        <v>0.987</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="310">
@@ -16772,7 +16772,7 @@
         <v>0.33</v>
       </c>
       <c r="I310" t="n">
-        <v>0.753</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -16809,7 +16809,7 @@
         <v>0.0726</v>
       </c>
       <c r="I311" t="n">
-        <v>0.29</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="312">
@@ -16846,7 +16846,7 @@
         <v>0.741</v>
       </c>
       <c r="I312" t="n">
-        <v>0.987</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="313">
@@ -16883,7 +16883,7 @@
         <v>0.445</v>
       </c>
       <c r="I313" t="n">
-        <v>0.891</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="314">
@@ -16920,7 +16920,7 @@
         <v>0.0319</v>
       </c>
       <c r="I314" t="n">
-        <v>0.17</v>
+        <v>0.0598</v>
       </c>
     </row>
     <row r="315">
@@ -16957,7 +16957,7 @@
         <v>0.738</v>
       </c>
       <c r="I315" t="n">
-        <v>0.987</v>
+        <v>0.852</v>
       </c>
     </row>
     <row r="316">
@@ -16994,7 +16994,7 @@
         <v>0.306</v>
       </c>
       <c r="I316" t="n">
-        <v>0.753</v>
+        <v>0.459</v>
       </c>
     </row>
     <row r="317">
@@ -17105,7 +17105,7 @@
         <v>0.621</v>
       </c>
       <c r="I319" t="n">
-        <v>0.987</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="320">
@@ -17142,7 +17142,7 @@
         <v>0.255</v>
       </c>
       <c r="I320" t="n">
-        <v>0.753</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="321">
@@ -17179,7 +17179,7 @@
         <v>0.804</v>
       </c>
       <c r="I321" t="n">
-        <v>0.989</v>
+        <v>0.804</v>
       </c>
     </row>
     <row r="322">
@@ -17216,7 +17216,7 @@
         <v>0.737</v>
       </c>
       <c r="I322" t="n">
-        <v>0.983</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323">
@@ -17253,7 +17253,7 @@
         <v>0.0131</v>
       </c>
       <c r="I323" t="n">
-        <v>0.105</v>
+        <v>0.0197</v>
       </c>
     </row>
     <row r="324">
@@ -17327,7 +17327,7 @@
         <v>1.09e-38</v>
       </c>
       <c r="I325" t="n">
-        <v>1.75e-37</v>
+        <v>4.09e-38</v>
       </c>
     </row>
     <row r="326">
@@ -17401,7 +17401,7 @@
         <v>0.169</v>
       </c>
       <c r="I327" t="n">
-        <v>0.664</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="328">
@@ -17475,7 +17475,7 @@
         <v>0.289</v>
       </c>
       <c r="I329" t="n">
-        <v>0.664</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="330">
@@ -17512,7 +17512,7 @@
         <v>0.318</v>
       </c>
       <c r="I330" t="n">
-        <v>0.664</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="331">
@@ -17586,7 +17586,7 @@
         <v>0.294</v>
       </c>
       <c r="I332" t="n">
-        <v>0.664</v>
+        <v>0.602</v>
       </c>
     </row>
     <row r="333">
@@ -17623,7 +17623,7 @@
         <v>0.0601</v>
       </c>
       <c r="I333" t="n">
-        <v>0.321</v>
+        <v>0.901</v>
       </c>
     </row>
     <row r="334">
@@ -17660,7 +17660,7 @@
         <v>0.723</v>
       </c>
       <c r="I334" t="n">
-        <v>0.983</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -17697,7 +17697,7 @@
         <v>0.332</v>
       </c>
       <c r="I335" t="n">
-        <v>0.664</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="336">
@@ -17734,7 +17734,7 @@
         <v>0.526</v>
       </c>
       <c r="I336" t="n">
-        <v>0.874</v>
+        <v>0.658</v>
       </c>
     </row>
     <row r="337">
@@ -17771,7 +17771,7 @@
         <v>0.546</v>
       </c>
       <c r="I337" t="n">
-        <v>0.874</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="338">
@@ -17808,7 +17808,7 @@
         <v>0.782</v>
       </c>
       <c r="I338" t="n">
-        <v>0.894</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339">
@@ -17845,7 +17845,7 @@
         <v>0.0181</v>
       </c>
       <c r="I339" t="n">
-        <v>0.0725</v>
+        <v>0.0302</v>
       </c>
     </row>
     <row r="340">
@@ -17919,7 +17919,7 @@
         <v>9.999999999999999e-22</v>
       </c>
       <c r="I341" t="n">
-        <v>1.6e-20</v>
+        <v>5e-21</v>
       </c>
     </row>
     <row r="342">
@@ -17956,7 +17956,7 @@
         <v>0.721</v>
       </c>
       <c r="I342" t="n">
-        <v>0.887</v>
+        <v>0.772</v>
       </c>
     </row>
     <row r="343">
@@ -17993,7 +17993,7 @@
         <v>0.0764</v>
       </c>
       <c r="I343" t="n">
-        <v>0.204</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="344">
@@ -18030,7 +18030,7 @@
         <v>0.0572</v>
       </c>
       <c r="I344" t="n">
-        <v>0.183</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="345">
@@ -18067,7 +18067,7 @@
         <v>0.242</v>
       </c>
       <c r="I345" t="n">
-        <v>0.554</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346">
@@ -18104,7 +18104,7 @@
         <v>0.625</v>
       </c>
       <c r="I346" t="n">
-        <v>0.887</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="347">
@@ -18141,7 +18141,7 @@
         <v>0.719</v>
       </c>
       <c r="I347" t="n">
-        <v>0.887</v>
+        <v>1</v>
       </c>
     </row>
     <row r="348">
@@ -18178,7 +18178,7 @@
         <v>0.624</v>
       </c>
       <c r="I348" t="n">
-        <v>0.887</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349">
@@ -18215,7 +18215,7 @@
         <v>0.00111</v>
       </c>
       <c r="I349" t="n">
-        <v>0.00592</v>
+        <v>0.0167</v>
       </c>
     </row>
     <row r="350">
@@ -18289,7 +18289,7 @@
         <v>0.000887</v>
       </c>
       <c r="I351" t="n">
-        <v>0.00592</v>
+        <v>0.00443</v>
       </c>
     </row>
     <row r="352">
@@ -18326,7 +18326,7 @@
         <v>0.368</v>
       </c>
       <c r="I352" t="n">
-        <v>0.737</v>
+        <v>0.613</v>
       </c>
     </row>
     <row r="353">
@@ -18363,7 +18363,7 @@
         <v>0.546</v>
       </c>
       <c r="I353" t="n">
-        <v>0.887</v>
+        <v>0.716</v>
       </c>
     </row>
     <row r="354">
@@ -18437,7 +18437,7 @@
         <v>0.0511</v>
       </c>
       <c r="I355" t="n">
-        <v>0.163</v>
+        <v>0.443</v>
       </c>
     </row>
     <row r="356">
@@ -18511,7 +18511,7 @@
         <v>2.19e-11</v>
       </c>
       <c r="I357" t="n">
-        <v>3.5e-10</v>
+        <v>1.09e-10</v>
       </c>
     </row>
     <row r="358">
@@ -18585,7 +18585,7 @@
         <v>0.00212</v>
       </c>
       <c r="I359" t="n">
-        <v>0.0169</v>
+        <v>0.00398</v>
       </c>
     </row>
     <row r="360">
@@ -18622,7 +18622,7 @@
         <v>0.0919</v>
       </c>
       <c r="I360" t="n">
-        <v>0.245</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="361">
@@ -18659,7 +18659,7 @@
         <v>0.335</v>
       </c>
       <c r="I361" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362">
@@ -18696,7 +18696,7 @@
         <v>0.187</v>
       </c>
       <c r="I362" t="n">
-        <v>0.428</v>
+        <v>0.255</v>
       </c>
     </row>
     <row r="363">
@@ -18770,7 +18770,7 @@
         <v>0.0405</v>
       </c>
       <c r="I364" t="n">
-        <v>0.162</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="365">
@@ -18807,7 +18807,7 @@
         <v>0.519</v>
       </c>
       <c r="I365" t="n">
-        <v>0.922</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="366">
@@ -18881,7 +18881,7 @@
         <v>0.0216</v>
       </c>
       <c r="I367" t="n">
-        <v>0.115</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="368">
@@ -18918,7 +18918,7 @@
         <v>0.712</v>
       </c>
       <c r="I368" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="369">
@@ -18955,7 +18955,7 @@
         <v>0.851</v>
       </c>
       <c r="I369" t="n">
-        <v>1</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="370">
@@ -18992,7 +18992,7 @@
         <v>0.742</v>
       </c>
       <c r="I370" t="n">
-        <v>0.98</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="371">
@@ -19029,7 +19029,7 @@
         <v>0.121</v>
       </c>
       <c r="I371" t="n">
-        <v>0.387</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="372">
@@ -19103,7 +19103,7 @@
         <v>2.97e-35</v>
       </c>
       <c r="I373" t="n">
-        <v>4.75e-34</v>
+        <v>1.49e-34</v>
       </c>
     </row>
     <row r="374">
@@ -19177,7 +19177,7 @@
         <v>0.0487</v>
       </c>
       <c r="I375" t="n">
-        <v>0.35</v>
+        <v>0.08119999999999999</v>
       </c>
     </row>
     <row r="376">
@@ -19214,7 +19214,7 @@
         <v>0.742</v>
       </c>
       <c r="I376" t="n">
-        <v>0.98</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="377">
@@ -19251,7 +19251,7 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I377" t="n">
-        <v>0.35</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="378">
@@ -19288,7 +19288,7 @@
         <v>0.196</v>
       </c>
       <c r="I378" t="n">
-        <v>0.453</v>
+        <v>0.267</v>
       </c>
     </row>
     <row r="379">
@@ -19362,7 +19362,7 @@
         <v>0.0926</v>
       </c>
       <c r="I380" t="n">
-        <v>0.37</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="381">
@@ -19399,7 +19399,7 @@
         <v>0.198</v>
       </c>
       <c r="I381" t="n">
-        <v>0.453</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382">
@@ -19436,7 +19436,7 @@
         <v>0.714</v>
       </c>
       <c r="I382" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383">
@@ -19473,7 +19473,7 @@
         <v>0.746</v>
       </c>
       <c r="I383" t="n">
-        <v>0.98</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="384">
@@ -19510,7 +19510,7 @@
         <v>0.796</v>
       </c>
       <c r="I384" t="n">
-        <v>0.98</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="385">
@@ -19547,7 +19547,7 @@
         <v>0.581</v>
       </c>
       <c r="I385" t="n">
-        <v>0.98</v>
+        <v>0.6909999999999999</v>
       </c>
     </row>
     <row r="386">
@@ -19584,7 +19584,7 @@
         <v>0.868</v>
       </c>
       <c r="I386" t="n">
-        <v>0.992</v>
+        <v>1</v>
       </c>
     </row>
     <row r="387">
@@ -19621,7 +19621,7 @@
         <v>0.000259</v>
       </c>
       <c r="I387" t="n">
-        <v>0.00415</v>
+        <v>0.000777</v>
       </c>
     </row>
     <row r="388">
@@ -19658,7 +19658,7 @@
         <v>0.0853</v>
       </c>
       <c r="I388" t="n">
-        <v>0.295</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="389">
@@ -19695,7 +19695,7 @@
         <v>0.121</v>
       </c>
       <c r="I389" t="n">
-        <v>0.295</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="390">
@@ -19769,7 +19769,7 @@
         <v>0.0398</v>
       </c>
       <c r="I391" t="n">
-        <v>0.295</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="392">
@@ -19806,7 +19806,7 @@
         <v>0.202</v>
       </c>
       <c r="I392" t="n">
-        <v>0.404</v>
+        <v>1</v>
       </c>
     </row>
     <row r="393">
@@ -19843,7 +19843,7 @@
         <v>0.77</v>
       </c>
       <c r="I393" t="n">
-        <v>0.992</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="394">
@@ -19880,7 +19880,7 @@
         <v>0.129</v>
       </c>
       <c r="I394" t="n">
-        <v>0.295</v>
+        <v>0.215</v>
       </c>
     </row>
     <row r="395">
@@ -19917,7 +19917,7 @@
         <v>0.286</v>
       </c>
       <c r="I395" t="n">
-        <v>0.457</v>
+        <v>0.536</v>
       </c>
     </row>
     <row r="396">
@@ -19954,7 +19954,7 @@
         <v>0.236</v>
       </c>
       <c r="I396" t="n">
-        <v>0.42</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="397">
@@ -19991,7 +19991,7 @@
         <v>0.862</v>
       </c>
       <c r="I397" t="n">
-        <v>0.992</v>
+        <v>1</v>
       </c>
     </row>
     <row r="398">
@@ -20065,7 +20065,7 @@
         <v>0.737</v>
       </c>
       <c r="I399" t="n">
-        <v>0.992</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="400">
@@ -20102,7 +20102,7 @@
         <v>0.0893</v>
       </c>
       <c r="I400" t="n">
-        <v>0.295</v>
+        <v>0.335</v>
       </c>
     </row>
     <row r="401">
@@ -20139,7 +20139,7 @@
         <v>0.109</v>
       </c>
       <c r="I401" t="n">
-        <v>0.295</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="402">
@@ -20176,7 +20176,7 @@
         <v>0.0381</v>
       </c>
       <c r="I402" t="n">
-        <v>0.203</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="403">
@@ -20213,7 +20213,7 @@
         <v>0.0026</v>
       </c>
       <c r="I403" t="n">
-        <v>0.0417</v>
+        <v>0.0078</v>
       </c>
     </row>
     <row r="404">
@@ -20250,7 +20250,7 @@
         <v>0.254</v>
       </c>
       <c r="I404" t="n">
-        <v>0.508</v>
+        <v>0.635</v>
       </c>
     </row>
     <row r="405">
@@ -20287,7 +20287,7 @@
         <v>0.0308</v>
       </c>
       <c r="I405" t="n">
-        <v>0.203</v>
+        <v>0.0924</v>
       </c>
     </row>
     <row r="406">
@@ -20324,7 +20324,7 @@
         <v>0.62</v>
       </c>
       <c r="I406" t="n">
-        <v>0.902</v>
+        <v>0.772</v>
       </c>
     </row>
     <row r="407">
@@ -20361,7 +20361,7 @@
         <v>0.467</v>
       </c>
       <c r="I407" t="n">
-        <v>0.748</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="408">
@@ -20398,7 +20398,7 @@
         <v>0.726</v>
       </c>
       <c r="I408" t="n">
-        <v>0.968</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="409">
@@ -20509,7 +20509,7 @@
         <v>0.395</v>
       </c>
       <c r="I411" t="n">
-        <v>0.702</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
@@ -20583,7 +20583,7 @@
         <v>0.109</v>
       </c>
       <c r="I413" t="n">
-        <v>0.348</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="414">
@@ -20657,7 +20657,7 @@
         <v>0.0648</v>
       </c>
       <c r="I415" t="n">
-        <v>0.259</v>
+        <v>0.09719999999999999</v>
       </c>
     </row>
     <row r="416">
@@ -20694,7 +20694,7 @@
         <v>0.215</v>
       </c>
       <c r="I416" t="n">
-        <v>0.508</v>
+        <v>0.537</v>
       </c>
     </row>
     <row r="417">
@@ -20731,7 +20731,7 @@
         <v>0.235</v>
       </c>
       <c r="I417" t="n">
-        <v>0.508</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="418">
@@ -20768,7 +20768,7 @@
         <v>0.447</v>
       </c>
       <c r="I418" t="n">
-        <v>0.785</v>
+        <v>0.5590000000000001</v>
       </c>
     </row>
     <row r="419">
@@ -20842,7 +20842,7 @@
         <v>0.352</v>
       </c>
       <c r="I420" t="n">
-        <v>0.785</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421">
@@ -20953,7 +20953,7 @@
         <v>0.00212</v>
       </c>
       <c r="I423" t="n">
-        <v>0.0339</v>
+        <v>0.00398</v>
       </c>
     </row>
     <row r="424">
@@ -20990,7 +20990,7 @@
         <v>0.0536</v>
       </c>
       <c r="I424" t="n">
-        <v>0.291</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="425">
@@ -21064,7 +21064,7 @@
         <v>0.0838</v>
       </c>
       <c r="I426" t="n">
-        <v>0.291</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="427">
@@ -21101,7 +21101,7 @@
         <v>0.463</v>
       </c>
       <c r="I427" t="n">
-        <v>0.785</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="428">
@@ -21138,7 +21138,7 @@
         <v>0.0858</v>
       </c>
       <c r="I428" t="n">
-        <v>0.291</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="429">
@@ -21175,7 +21175,7 @@
         <v>0.519</v>
       </c>
       <c r="I429" t="n">
-        <v>0.785</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="430">
@@ -21249,7 +21249,7 @@
         <v>0.539</v>
       </c>
       <c r="I431" t="n">
-        <v>0.785</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="432">
@@ -21286,7 +21286,7 @@
         <v>0.321</v>
       </c>
       <c r="I432" t="n">
-        <v>0.785</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="433">
@@ -21323,7 +21323,7 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I433" t="n">
-        <v>0.291</v>
+        <v>0.273</v>
       </c>
     </row>
     <row r="434">
@@ -21397,7 +21397,7 @@
         <v>0.00224</v>
       </c>
       <c r="I435" t="n">
-        <v>0.0358</v>
+        <v>0.008399999999999999</v>
       </c>
     </row>
     <row r="436">
@@ -21434,7 +21434,7 @@
         <v>0.0742</v>
       </c>
       <c r="I436" t="n">
-        <v>0.208</v>
+        <v>0.318</v>
       </c>
     </row>
     <row r="437">
@@ -21471,7 +21471,7 @@
         <v>0.118</v>
       </c>
       <c r="I437" t="n">
-        <v>0.21</v>
+        <v>0.354</v>
       </c>
     </row>
     <row r="438">
@@ -21545,7 +21545,7 @@
         <v>0.008059999999999999</v>
       </c>
       <c r="I439" t="n">
-        <v>0.0645</v>
+        <v>0.0403</v>
       </c>
     </row>
     <row r="440">
@@ -21582,7 +21582,7 @@
         <v>0.104</v>
       </c>
       <c r="I440" t="n">
-        <v>0.209</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="441">
@@ -21619,7 +21619,7 @@
         <v>0.71</v>
       </c>
       <c r="I441" t="n">
-        <v>1</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="442">
@@ -21656,7 +21656,7 @@
         <v>0.0568</v>
       </c>
       <c r="I442" t="n">
-        <v>0.208</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="443">
@@ -21693,7 +21693,7 @@
         <v>0.224</v>
       </c>
       <c r="I443" t="n">
-        <v>0.359</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="444">
@@ -21730,7 +21730,7 @@
         <v>0.0912</v>
       </c>
       <c r="I444" t="n">
-        <v>0.208</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="445">
@@ -21841,7 +21841,7 @@
         <v>0.866</v>
       </c>
       <c r="I447" t="n">
-        <v>1</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="448">
@@ -21878,7 +21878,7 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I448" t="n">
-        <v>0.208</v>
+        <v>0.645</v>
       </c>
     </row>
     <row r="449">
@@ -21915,7 +21915,7 @@
         <v>0.0292</v>
       </c>
       <c r="I449" t="n">
-        <v>0.156</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="450">
@@ -21989,7 +21989,7 @@
         <v>0.00702</v>
       </c>
       <c r="I451" t="n">
-        <v>0.0561</v>
+        <v>0.0117</v>
       </c>
     </row>
     <row r="452">
@@ -22026,7 +22026,7 @@
         <v>0.501</v>
       </c>
       <c r="I452" t="n">
-        <v>1</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="453">
@@ -22063,7 +22063,7 @@
         <v>1.4e-49</v>
       </c>
       <c r="I453" t="n">
-        <v>2.25e-48</v>
+        <v>2.1e-48</v>
       </c>
     </row>
     <row r="454">
@@ -22137,7 +22137,7 @@
         <v>0.124</v>
       </c>
       <c r="I455" t="n">
-        <v>0.396</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="456">
@@ -22211,7 +22211,7 @@
         <v>0.77</v>
       </c>
       <c r="I457" t="n">
-        <v>1</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="458">
@@ -22248,7 +22248,7 @@
         <v>0.0551</v>
       </c>
       <c r="I458" t="n">
-        <v>0.221</v>
+        <v>0.165</v>
       </c>
     </row>
     <row r="459">
@@ -22322,7 +22322,7 @@
         <v>0.0199</v>
       </c>
       <c r="I460" t="n">
-        <v>0.106</v>
+        <v>0.09950000000000001</v>
       </c>
     </row>
     <row r="461">
@@ -22359,7 +22359,7 @@
         <v>0.406</v>
       </c>
       <c r="I461" t="n">
-        <v>0.927</v>
+        <v>1</v>
       </c>
     </row>
     <row r="462">
@@ -22433,7 +22433,7 @@
         <v>0.618</v>
       </c>
       <c r="I463" t="n">
-        <v>1</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="464">
@@ -22470,7 +22470,7 @@
         <v>0.9</v>
       </c>
       <c r="I464" t="n">
-        <v>1</v>
+        <v>0.973</v>
       </c>
     </row>
     <row r="465">
@@ -22507,7 +22507,7 @@
         <v>0.222</v>
       </c>
       <c r="I465" t="n">
-        <v>0.591</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="466">
@@ -22544,7 +22544,7 @@
         <v>0.201</v>
       </c>
       <c r="I466" t="n">
-        <v>0.459</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="467">
@@ -22581,7 +22581,7 @@
         <v>0.021</v>
       </c>
       <c r="I467" t="n">
-        <v>0.0766</v>
+        <v>0.0315</v>
       </c>
     </row>
     <row r="468">
@@ -22618,7 +22618,7 @@
         <v>0.429</v>
       </c>
       <c r="I468" t="n">
-        <v>0.624</v>
+        <v>0.919</v>
       </c>
     </row>
     <row r="469">
@@ -22655,7 +22655,7 @@
         <v>2.32e-23</v>
       </c>
       <c r="I469" t="n">
-        <v>3.72e-22</v>
+        <v>3.48e-22</v>
       </c>
     </row>
     <row r="470">
@@ -22692,7 +22692,7 @@
         <v>0.331</v>
       </c>
       <c r="I470" t="n">
-        <v>0.529</v>
+        <v>0.671</v>
       </c>
     </row>
     <row r="471">
@@ -22729,7 +22729,7 @@
         <v>0.0462</v>
       </c>
       <c r="I471" t="n">
-        <v>0.123</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="472">
@@ -22766,7 +22766,7 @@
         <v>0.0239</v>
       </c>
       <c r="I472" t="n">
-        <v>0.0766</v>
+        <v>0.179</v>
       </c>
     </row>
     <row r="473">
@@ -22840,7 +22840,7 @@
         <v>0.241</v>
       </c>
       <c r="I474" t="n">
-        <v>0.483</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="475">
@@ -22877,7 +22877,7 @@
         <v>0.766</v>
       </c>
       <c r="I475" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="476">
@@ -22951,7 +22951,7 @@
         <v>0.00259</v>
       </c>
       <c r="I477" t="n">
-        <v>0.0207</v>
+        <v>0.0194</v>
       </c>
     </row>
     <row r="478">
@@ -23025,7 +23025,7 @@
         <v>0.00468</v>
       </c>
       <c r="I479" t="n">
-        <v>0.025</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="480">
@@ -23062,7 +23062,7 @@
         <v>0.721</v>
       </c>
       <c r="I480" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.832</v>
       </c>
     </row>
     <row r="481">
@@ -23099,7 +23099,7 @@
         <v>0.314</v>
       </c>
       <c r="I481" t="n">
-        <v>0.529</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="482">
@@ -23136,7 +23136,7 @@
         <v>0.0515</v>
       </c>
       <c r="I482" t="n">
-        <v>0.103</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="483">
@@ -23173,7 +23173,7 @@
         <v>0.236</v>
       </c>
       <c r="I483" t="n">
-        <v>0.377</v>
+        <v>0.443</v>
       </c>
     </row>
     <row r="484">
@@ -23247,7 +23247,7 @@
         <v>2.19e-11</v>
       </c>
       <c r="I485" t="n">
-        <v>3.5e-10</v>
+        <v>1.09e-10</v>
       </c>
     </row>
     <row r="486">
@@ -23321,7 +23321,7 @@
         <v>0.000174</v>
       </c>
       <c r="I487" t="n">
-        <v>0.00139</v>
+        <v>0.00087</v>
       </c>
     </row>
     <row r="488">
@@ -23358,7 +23358,7 @@
         <v>0.000727</v>
       </c>
       <c r="I488" t="n">
-        <v>0.00291</v>
+        <v>0.0109</v>
       </c>
     </row>
     <row r="489">
@@ -23395,7 +23395,7 @@
         <v>0.637</v>
       </c>
       <c r="I489" t="n">
-        <v>0.784</v>
+        <v>1</v>
       </c>
     </row>
     <row r="490">
@@ -23432,7 +23432,7 @@
         <v>0.00642</v>
       </c>
       <c r="I490" t="n">
-        <v>0.0206</v>
+        <v>0.0212</v>
       </c>
     </row>
     <row r="491">
@@ -23469,7 +23469,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I491" t="n">
-        <v>0.789</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="492">
@@ -23506,7 +23506,7 @@
         <v>0.000515</v>
       </c>
       <c r="I492" t="n">
-        <v>0.00275</v>
+        <v>0.00386</v>
       </c>
     </row>
     <row r="493">
@@ -23543,7 +23543,7 @@
         <v>0.015</v>
       </c>
       <c r="I493" t="n">
-        <v>0.04</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="494">
@@ -23580,7 +23580,7 @@
         <v>0.232</v>
       </c>
       <c r="I494" t="n">
-        <v>0.377</v>
+        <v>1</v>
       </c>
     </row>
     <row r="495">
@@ -23617,7 +23617,7 @@
         <v>0.0429</v>
       </c>
       <c r="I495" t="n">
-        <v>0.098</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="496">
@@ -23654,7 +23654,7 @@
         <v>0.581</v>
       </c>
       <c r="I496" t="n">
-        <v>0.775</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="497">
@@ -23691,7 +23691,7 @@
         <v>0.349</v>
       </c>
       <c r="I497" t="n">
-        <v>0.508</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="498">
@@ -23728,7 +23728,7 @@
         <v>0.748</v>
       </c>
       <c r="I498" t="n">
-        <v>0.958</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="499">
@@ -23765,7 +23765,7 @@
         <v>0.0509</v>
       </c>
       <c r="I499" t="n">
-        <v>0.163</v>
+        <v>0.0848</v>
       </c>
     </row>
     <row r="500">
@@ -23802,7 +23802,7 @@
         <v>0.492</v>
       </c>
       <c r="I500" t="n">
-        <v>0.787</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="501">
@@ -23839,7 +23839,7 @@
         <v>1.11e-37</v>
       </c>
       <c r="I501" t="n">
-        <v>1.77e-36</v>
+        <v>1.66e-36</v>
       </c>
     </row>
     <row r="502">
@@ -23876,7 +23876,7 @@
         <v>0.775</v>
       </c>
       <c r="I502" t="n">
-        <v>0.958</v>
+        <v>1</v>
       </c>
     </row>
     <row r="503">
@@ -23913,7 +23913,7 @@
         <v>0.022</v>
       </c>
       <c r="I503" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.0482</v>
       </c>
     </row>
     <row r="504">
@@ -23950,7 +23950,7 @@
         <v>0.401</v>
       </c>
       <c r="I504" t="n">
-        <v>0.787</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="505">
@@ -23987,7 +23987,7 @@
         <v>0.445</v>
       </c>
       <c r="I505" t="n">
-        <v>0.787</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="506">
@@ -24024,7 +24024,7 @@
         <v>0.0114</v>
       </c>
       <c r="I506" t="n">
-        <v>0.0609</v>
+        <v>0.0342</v>
       </c>
     </row>
     <row r="507">
@@ -24061,7 +24061,7 @@
         <v>0.87</v>
       </c>
       <c r="I507" t="n">
-        <v>0.958</v>
+        <v>0.9320000000000001</v>
       </c>
     </row>
     <row r="508">
@@ -24098,7 +24098,7 @@
         <v>0.00187</v>
       </c>
       <c r="I508" t="n">
-        <v>0.0149</v>
+        <v>0.009350000000000001</v>
       </c>
     </row>
     <row r="509">
@@ -24135,7 +24135,7 @@
         <v>0.866</v>
       </c>
       <c r="I509" t="n">
-        <v>0.958</v>
+        <v>1</v>
       </c>
     </row>
     <row r="510">
@@ -24172,7 +24172,7 @@
         <v>0.47</v>
       </c>
       <c r="I510" t="n">
-        <v>0.787</v>
+        <v>1</v>
       </c>
     </row>
     <row r="511">
@@ -24246,7 +24246,7 @@
         <v>0.898</v>
       </c>
       <c r="I512" t="n">
-        <v>0.958</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="513">
@@ -24283,7 +24283,7 @@
         <v>0.132</v>
       </c>
       <c r="I513" t="n">
-        <v>0.352</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="514">
@@ -24320,7 +24320,7 @@
         <v>0.1</v>
       </c>
       <c r="I514" t="n">
-        <v>0.229</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="515">
@@ -24357,7 +24357,7 @@
         <v>8.69e-05</v>
       </c>
       <c r="I515" t="n">
-        <v>0.00139</v>
+        <v>0.000326</v>
       </c>
     </row>
     <row r="516">
@@ -24505,7 +24505,7 @@
         <v>0.00911</v>
       </c>
       <c r="I519" t="n">
-        <v>0.0292</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="520">
@@ -24542,7 +24542,7 @@
         <v>0.0911</v>
       </c>
       <c r="I520" t="n">
-        <v>0.229</v>
+        <v>1</v>
       </c>
     </row>
     <row r="521">
@@ -24616,7 +24616,7 @@
         <v>0.166</v>
       </c>
       <c r="I522" t="n">
-        <v>0.331</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="523">
@@ -24653,7 +24653,7 @@
         <v>0.737</v>
       </c>
       <c r="I523" t="n">
-        <v>1</v>
+        <v>0.867</v>
       </c>
     </row>
     <row r="524">
@@ -24690,7 +24690,7 @@
         <v>0.00532</v>
       </c>
       <c r="I524" t="n">
-        <v>0.0213</v>
+        <v>0.0399</v>
       </c>
     </row>
     <row r="525">
@@ -24727,7 +24727,7 @@
         <v>0.575</v>
       </c>
       <c r="I525" t="n">
-        <v>0.921</v>
+        <v>1</v>
       </c>
     </row>
     <row r="526">
@@ -24801,7 +24801,7 @@
         <v>0.461</v>
       </c>
       <c r="I527" t="n">
-        <v>0.819</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="528">
@@ -24838,7 +24838,7 @@
         <v>0.000507</v>
       </c>
       <c r="I528" t="n">
-        <v>0.00406</v>
+        <v>0.00323</v>
       </c>
     </row>
     <row r="529">
@@ -24875,7 +24875,7 @@
         <v>0.000809</v>
       </c>
       <c r="I529" t="n">
-        <v>0.00431</v>
+        <v>0.00404</v>
       </c>
     </row>
     <row r="530">
@@ -24949,7 +24949,7 @@
         <v>0.0005820000000000001</v>
       </c>
       <c r="I531" t="n">
-        <v>0.00932</v>
+        <v>0.00218</v>
       </c>
     </row>
     <row r="532">
@@ -24986,7 +24986,7 @@
         <v>0.492</v>
       </c>
       <c r="I532" t="n">
-        <v>1</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="533">
@@ -25097,7 +25097,7 @@
         <v>0.699</v>
       </c>
       <c r="I535" t="n">
-        <v>1</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="536">
@@ -25134,7 +25134,7 @@
         <v>0.729</v>
       </c>
       <c r="I536" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="537">
@@ -25208,7 +25208,7 @@
         <v>0.229</v>
       </c>
       <c r="I538" t="n">
-        <v>0.734</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="539">
@@ -25319,7 +25319,7 @@
         <v>0.294</v>
       </c>
       <c r="I541" t="n">
-        <v>0.784</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="542">
@@ -25393,7 +25393,7 @@
         <v>0.185</v>
       </c>
       <c r="I543" t="n">
-        <v>0.734</v>
+        <v>0.252</v>
       </c>
     </row>
     <row r="544">
@@ -25430,7 +25430,7 @@
         <v>0.00339</v>
       </c>
       <c r="I544" t="n">
-        <v>0.0272</v>
+        <v>0.0254</v>
       </c>
     </row>
     <row r="545">
@@ -25467,7 +25467,7 @@
         <v>0.00637</v>
       </c>
       <c r="I545" t="n">
-        <v>0.034</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="546">
@@ -25504,7 +25504,7 @@
         <v>0.0974</v>
       </c>
       <c r="I546" t="n">
-        <v>0.195</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="547">
@@ -25541,7 +25541,7 @@
         <v>0.491</v>
       </c>
       <c r="I547" t="n">
-        <v>0.785</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="548">
@@ -25689,7 +25689,7 @@
         <v>0.000433</v>
       </c>
       <c r="I551" t="n">
-        <v>0.00694</v>
+        <v>0.0013</v>
       </c>
     </row>
     <row r="552">
@@ -25726,7 +25726,7 @@
         <v>0.0141</v>
       </c>
       <c r="I552" t="n">
-        <v>0.0563</v>
+        <v>0.07049999999999999</v>
       </c>
     </row>
     <row r="553">
@@ -25800,7 +25800,7 @@
         <v>0.0447</v>
       </c>
       <c r="I554" t="n">
-        <v>0.119</v>
+        <v>0.0745</v>
       </c>
     </row>
     <row r="555">
@@ -25837,7 +25837,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I555" t="n">
-        <v>1</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="556">
@@ -25874,7 +25874,7 @@
         <v>0.00195</v>
       </c>
       <c r="I556" t="n">
-        <v>0.0156</v>
+        <v>0.00975</v>
       </c>
     </row>
     <row r="557">
@@ -25911,7 +25911,7 @@
         <v>0.0625</v>
       </c>
       <c r="I557" t="n">
-        <v>0.143</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="558">
@@ -25985,7 +25985,7 @@
         <v>0.0216</v>
       </c>
       <c r="I559" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="560">
@@ -26022,7 +26022,7 @@
         <v>0.155</v>
       </c>
       <c r="I560" t="n">
-        <v>0.276</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="561">
@@ -26059,7 +26059,7 @@
         <v>0.0138</v>
       </c>
       <c r="I561" t="n">
-        <v>0.0563</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="562">
@@ -26096,7 +26096,7 @@
         <v>0.0728</v>
       </c>
       <c r="I562" t="n">
-        <v>0.146</v>
+        <v>0.334</v>
       </c>
     </row>
     <row r="563">
@@ -26133,7 +26133,7 @@
         <v>0.00158</v>
       </c>
       <c r="I563" t="n">
-        <v>0.00634</v>
+        <v>0.007900000000000001</v>
       </c>
     </row>
     <row r="564">
@@ -26281,7 +26281,7 @@
         <v>0.00202</v>
       </c>
       <c r="I567" t="n">
-        <v>0.00645</v>
+        <v>0.0303</v>
       </c>
     </row>
     <row r="568">
@@ -26318,7 +26318,7 @@
         <v>0.0404</v>
       </c>
       <c r="I568" t="n">
-        <v>0.108</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="569">
@@ -26392,7 +26392,7 @@
         <v>0.058</v>
       </c>
       <c r="I570" t="n">
-        <v>0.133</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="571">
@@ -26429,7 +26429,7 @@
         <v>0.616</v>
       </c>
       <c r="I571" t="n">
-        <v>0.897</v>
+        <v>0.792</v>
       </c>
     </row>
     <row r="572">
@@ -26466,7 +26466,7 @@
         <v>0.000901</v>
       </c>
       <c r="I572" t="n">
-        <v>0.00634</v>
+        <v>0.00676</v>
       </c>
     </row>
     <row r="573">
@@ -26503,7 +26503,7 @@
         <v>0.34</v>
       </c>
       <c r="I573" t="n">
-        <v>0.544</v>
+        <v>1</v>
       </c>
     </row>
     <row r="574">
@@ -26577,7 +26577,7 @@
         <v>0.2</v>
       </c>
       <c r="I575" t="n">
-        <v>0.356</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="576">
@@ -26614,7 +26614,7 @@
         <v>0.0012</v>
       </c>
       <c r="I576" t="n">
-        <v>0.00634</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="577">
@@ -26651,7 +26651,7 @@
         <v>0.000152</v>
       </c>
       <c r="I577" t="n">
-        <v>0.00243</v>
+        <v>0.00228</v>
       </c>
     </row>
     <row r="578">
@@ -26688,7 +26688,7 @@
         <v>0.06370000000000001</v>
       </c>
       <c r="I578" t="n">
-        <v>0.255</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="579">
@@ -26725,7 +26725,7 @@
         <v>0.000683</v>
       </c>
       <c r="I579" t="n">
-        <v>0.00546</v>
+        <v>0.00171</v>
       </c>
     </row>
     <row r="580">
@@ -26762,7 +26762,7 @@
         <v>0.723</v>
       </c>
       <c r="I580" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
     </row>
     <row r="581">
@@ -26873,7 +26873,7 @@
         <v>0.124</v>
       </c>
       <c r="I583" t="n">
-        <v>0.396</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="584">
@@ -26910,7 +26910,7 @@
         <v>0.483</v>
       </c>
       <c r="I584" t="n">
-        <v>0.8159999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="585">
@@ -26947,7 +26947,7 @@
         <v>0.572</v>
       </c>
       <c r="I585" t="n">
-        <v>0.833</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="586">
@@ -26984,7 +26984,7 @@
         <v>0.04</v>
       </c>
       <c r="I586" t="n">
-        <v>0.213</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="587">
@@ -27021,7 +27021,7 @@
         <v>0.386</v>
       </c>
       <c r="I587" t="n">
-        <v>0.771</v>
+        <v>0.579</v>
       </c>
     </row>
     <row r="588">
@@ -27058,7 +27058,7 @@
         <v>0.000595</v>
       </c>
       <c r="I588" t="n">
-        <v>0.00546</v>
+        <v>0.00893</v>
       </c>
     </row>
     <row r="589">
@@ -27132,7 +27132,7 @@
         <v>0.723</v>
       </c>
       <c r="I590" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
     </row>
     <row r="591">
@@ -27169,7 +27169,7 @@
         <v>0.51</v>
       </c>
       <c r="I591" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="592">
@@ -27206,7 +27206,7 @@
         <v>0.247</v>
       </c>
       <c r="I592" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.572</v>
       </c>
     </row>
     <row r="593">
@@ -27243,7 +27243,7 @@
         <v>0.222</v>
       </c>
       <c r="I593" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="594">
@@ -27280,7 +27280,7 @@
         <v>0.584</v>
       </c>
       <c r="I594" t="n">
-        <v>0.849</v>
+        <v>1</v>
       </c>
     </row>
     <row r="595">
@@ -27317,7 +27317,7 @@
         <v>0.00324</v>
       </c>
       <c r="I595" t="n">
-        <v>0.0375</v>
+        <v>0.0081</v>
       </c>
     </row>
     <row r="596">
@@ -27354,7 +27354,7 @@
         <v>0.672</v>
       </c>
       <c r="I596" t="n">
-        <v>0.887</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="597">
@@ -27428,7 +27428,7 @@
         <v>0.721</v>
       </c>
       <c r="I598" t="n">
-        <v>0.887</v>
+        <v>0.772</v>
       </c>
     </row>
     <row r="599">
@@ -27465,7 +27465,7 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I599" t="n">
-        <v>0.402</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="600">
@@ -27502,7 +27502,7 @@
         <v>0.228</v>
       </c>
       <c r="I600" t="n">
-        <v>0.609</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="601">
@@ -27539,7 +27539,7 @@
         <v>0.545</v>
       </c>
       <c r="I601" t="n">
-        <v>0.849</v>
+        <v>1</v>
       </c>
     </row>
     <row r="602">
@@ -27576,7 +27576,7 @@
         <v>0.389</v>
       </c>
       <c r="I602" t="n">
-        <v>0.778</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="603">
@@ -27650,7 +27650,7 @@
         <v>0.574</v>
       </c>
       <c r="I604" t="n">
-        <v>0.849</v>
+        <v>1</v>
       </c>
     </row>
     <row r="605">
@@ -27687,7 +27687,7 @@
         <v>0.108</v>
       </c>
       <c r="I605" t="n">
-        <v>0.404</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="606">
@@ -27761,7 +27761,7 @@
         <v>0.00468</v>
       </c>
       <c r="I607" t="n">
-        <v>0.0375</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="608">
@@ -27798,7 +27798,7 @@
         <v>0.126</v>
       </c>
       <c r="I608" t="n">
-        <v>0.404</v>
+        <v>0.378</v>
       </c>
     </row>
     <row r="609">
@@ -27835,7 +27835,7 @@
         <v>0.288</v>
       </c>
       <c r="I609" t="n">
-        <v>0.658</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="610">
@@ -27872,7 +27872,7 @@
         <v>0.0515</v>
       </c>
       <c r="I610" t="n">
-        <v>0.137</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="611">
@@ -27909,7 +27909,7 @@
         <v>0.236</v>
       </c>
       <c r="I611" t="n">
-        <v>0.531</v>
+        <v>0.443</v>
       </c>
     </row>
     <row r="612">
@@ -28020,7 +28020,7 @@
         <v>0.735</v>
       </c>
       <c r="I614" t="n">
-        <v>0.981</v>
+        <v>1</v>
       </c>
     </row>
     <row r="615">
@@ -28057,7 +28057,7 @@
         <v>0.000433</v>
       </c>
       <c r="I615" t="n">
-        <v>0.00347</v>
+        <v>0.0013</v>
       </c>
     </row>
     <row r="616">
@@ -28094,7 +28094,7 @@
         <v>0.0288</v>
       </c>
       <c r="I616" t="n">
-        <v>0.115</v>
+        <v>0.0864</v>
       </c>
     </row>
     <row r="617">
@@ -28131,7 +28131,7 @@
         <v>0.637</v>
       </c>
       <c r="I617" t="n">
-        <v>0.927</v>
+        <v>1</v>
       </c>
     </row>
     <row r="618">
@@ -28168,7 +28168,7 @@
         <v>0.00991</v>
       </c>
       <c r="I618" t="n">
-        <v>0.0528</v>
+        <v>0.0212</v>
       </c>
     </row>
     <row r="619">
@@ -28205,7 +28205,7 @@
         <v>0.299</v>
       </c>
       <c r="I619" t="n">
-        <v>0.531</v>
+        <v>0.498</v>
       </c>
     </row>
     <row r="620">
@@ -28242,7 +28242,7 @@
         <v>4.79e-05</v>
       </c>
       <c r="I620" t="n">
-        <v>0.000766</v>
+        <v>0.000718</v>
       </c>
     </row>
     <row r="621">
@@ -28279,7 +28279,7 @@
         <v>0.269</v>
       </c>
       <c r="I621" t="n">
-        <v>0.531</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="622">
@@ -28353,7 +28353,7 @@
         <v>0.0429</v>
       </c>
       <c r="I623" t="n">
-        <v>0.137</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="624">
@@ -28390,7 +28390,7 @@
         <v>0.581</v>
       </c>
       <c r="I624" t="n">
-        <v>0.927</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="625">
@@ -28427,7 +28427,7 @@
         <v>0.851</v>
       </c>
       <c r="I625" t="n">
-        <v>1</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="626">
@@ -28464,7 +28464,7 @@
         <v>0.0449</v>
       </c>
       <c r="I626" t="n">
-        <v>0.144</v>
+        <v>0.334</v>
       </c>
     </row>
     <row r="627">
@@ -28501,7 +28501,7 @@
         <v>0.008710000000000001</v>
       </c>
       <c r="I627" t="n">
-        <v>0.0571</v>
+        <v>0.0218</v>
       </c>
     </row>
     <row r="628">
@@ -28538,7 +28538,7 @@
         <v>0.717</v>
       </c>
       <c r="I628" t="n">
-        <v>0.882</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="629">
@@ -28575,7 +28575,7 @@
         <v>0.494</v>
       </c>
       <c r="I629" t="n">
-        <v>0.791</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="630">
@@ -28612,7 +28612,7 @@
         <v>0.882</v>
       </c>
       <c r="I630" t="n">
-        <v>0.882</v>
+        <v>1</v>
       </c>
     </row>
     <row r="631">
@@ -28649,7 +28649,7 @@
         <v>0.0225</v>
       </c>
       <c r="I631" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.0482</v>
       </c>
     </row>
     <row r="632">
@@ -28686,7 +28686,7 @@
         <v>0.294</v>
       </c>
       <c r="I632" t="n">
-        <v>0.585</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="633">
@@ -28723,7 +28723,7 @@
         <v>0.272</v>
       </c>
       <c r="I633" t="n">
-        <v>0.585</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="634">
@@ -28760,7 +28760,7 @@
         <v>0.0107</v>
       </c>
       <c r="I634" t="n">
-        <v>0.0571</v>
+        <v>0.0342</v>
       </c>
     </row>
     <row r="635">
@@ -28797,7 +28797,7 @@
         <v>0.299</v>
       </c>
       <c r="I635" t="n">
-        <v>0.585</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="636">
@@ -28834,7 +28834,7 @@
         <v>3.8e-05</v>
       </c>
       <c r="I636" t="n">
-        <v>0.000608</v>
+        <v>0.00057</v>
       </c>
     </row>
     <row r="637">
@@ -28871,7 +28871,7 @@
         <v>0.859</v>
       </c>
       <c r="I637" t="n">
-        <v>0.882</v>
+        <v>1</v>
       </c>
     </row>
     <row r="638">
@@ -28908,7 +28908,7 @@
         <v>0.714</v>
       </c>
       <c r="I638" t="n">
-        <v>0.882</v>
+        <v>1</v>
       </c>
     </row>
     <row r="639">
@@ -28945,7 +28945,7 @@
         <v>0.869</v>
       </c>
       <c r="I639" t="n">
-        <v>0.882</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="640">
@@ -28982,7 +28982,7 @@
         <v>0.598</v>
       </c>
       <c r="I640" t="n">
-        <v>0.87</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="641">
@@ -29019,7 +29019,7 @@
         <v>0.329</v>
       </c>
       <c r="I641" t="n">
-        <v>0.585</v>
+        <v>0.548</v>
       </c>
     </row>
     <row r="642">
@@ -29056,7 +29056,7 @@
         <v>0.141</v>
       </c>
       <c r="I642" t="n">
-        <v>0.703</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="643">
@@ -29241,7 +29241,7 @@
         <v>0.176</v>
       </c>
       <c r="I647" t="n">
-        <v>0.703</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="648">
@@ -29352,7 +29352,7 @@
         <v>0.099</v>
       </c>
       <c r="I650" t="n">
-        <v>0.703</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="651">
@@ -29389,7 +29389,7 @@
         <v>0.006</v>
       </c>
       <c r="I651" t="n">
-        <v>0.0959</v>
+        <v>0.0788</v>
       </c>
     </row>
     <row r="652">
@@ -29537,7 +29537,7 @@
         <v>0.5659999999999999</v>
       </c>
       <c r="I655" t="n">
-        <v>1</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="656">
@@ -29574,7 +29574,7 @@
         <v>0.908</v>
       </c>
       <c r="I656" t="n">
-        <v>1</v>
+        <v>0.973</v>
       </c>
     </row>
     <row r="657">
@@ -29611,7 +29611,7 @@
         <v>0.411</v>
       </c>
       <c r="I657" t="n">
-        <v>1</v>
+        <v>0.474</v>
       </c>
     </row>
     <row r="658">
@@ -29722,7 +29722,7 @@
         <v>0.789</v>
       </c>
       <c r="I660" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="661">
@@ -29796,7 +29796,7 @@
         <v>0.502</v>
       </c>
       <c r="I662" t="n">
-        <v>1</v>
+        <v>0.772</v>
       </c>
     </row>
     <row r="663">
@@ -29833,7 +29833,7 @@
         <v>0.8080000000000001</v>
       </c>
       <c r="I663" t="n">
-        <v>1</v>
+        <v>0.9320000000000001</v>
       </c>
     </row>
     <row r="664">
@@ -29870,7 +29870,7 @@
         <v>0.803</v>
       </c>
       <c r="I664" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="665">
@@ -29944,7 +29944,7 @@
         <v>0.238</v>
       </c>
       <c r="I666" t="n">
-        <v>1</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="667">
@@ -30129,7 +30129,7 @@
         <v>0.6870000000000001</v>
       </c>
       <c r="I671" t="n">
-        <v>1</v>
+        <v>0.6870000000000001</v>
       </c>
     </row>
     <row r="672">
@@ -30203,7 +30203,7 @@
         <v>0.667</v>
       </c>
       <c r="I673" t="n">
-        <v>1</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="674">
@@ -30240,7 +30240,7 @@
         <v>0.0853</v>
       </c>
       <c r="I674" t="n">
-        <v>0.455</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="675">
@@ -30351,7 +30351,7 @@
         <v>0.488</v>
       </c>
       <c r="I677" t="n">
-        <v>0.977</v>
+        <v>1</v>
       </c>
     </row>
     <row r="678">
@@ -30388,7 +30388,7 @@
         <v>0.402</v>
       </c>
       <c r="I678" t="n">
-        <v>0.949</v>
+        <v>1</v>
       </c>
     </row>
     <row r="679">
@@ -30425,7 +30425,7 @@
         <v>0.132</v>
       </c>
       <c r="I679" t="n">
-        <v>0.499</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="680">
@@ -30462,7 +30462,7 @@
         <v>0.837</v>
       </c>
       <c r="I680" t="n">
-        <v>1</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="681">
@@ -30536,7 +30536,7 @@
         <v>0.008880000000000001</v>
       </c>
       <c r="I682" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0212</v>
       </c>
     </row>
     <row r="683">
@@ -30573,7 +30573,7 @@
         <v>0.00245</v>
       </c>
       <c r="I683" t="n">
-        <v>0.0392</v>
+        <v>0.0184</v>
       </c>
     </row>
     <row r="684">
@@ -30647,7 +30647,7 @@
         <v>0.415</v>
       </c>
       <c r="I685" t="n">
-        <v>0.949</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="686">
@@ -30721,7 +30721,7 @@
         <v>0.838</v>
       </c>
       <c r="I687" t="n">
-        <v>1</v>
+        <v>0.967</v>
       </c>
     </row>
     <row r="688">
@@ -30758,7 +30758,7 @@
         <v>0.156</v>
       </c>
       <c r="I688" t="n">
-        <v>0.499</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="689">
@@ -30795,7 +30795,7 @@
         <v>0.845</v>
       </c>
       <c r="I689" t="n">
-        <v>1</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="690">
@@ -30832,7 +30832,7 @@
         <v>0.0842</v>
       </c>
       <c r="I690" t="n">
-        <v>0.421</v>
+        <v>0.334</v>
       </c>
     </row>
     <row r="691">
@@ -30906,7 +30906,7 @@
         <v>0.8179999999999999</v>
       </c>
       <c r="I692" t="n">
-        <v>1</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="693">
@@ -30943,7 +30943,7 @@
         <v>0.236</v>
       </c>
       <c r="I693" t="n">
-        <v>0.754</v>
+        <v>0.506</v>
       </c>
     </row>
     <row r="694">
@@ -31017,7 +31017,7 @@
         <v>0.105</v>
       </c>
       <c r="I695" t="n">
-        <v>0.421</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="696">
@@ -31054,7 +31054,7 @@
         <v>0.634</v>
       </c>
       <c r="I696" t="n">
-        <v>1</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="697">
@@ -31128,7 +31128,7 @@
         <v>0.0236</v>
       </c>
       <c r="I698" t="n">
-        <v>0.189</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="699">
@@ -31165,7 +31165,7 @@
         <v>0.00107</v>
       </c>
       <c r="I699" t="n">
-        <v>0.0172</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="700">
@@ -31239,7 +31239,7 @@
         <v>0.323</v>
       </c>
       <c r="I701" t="n">
-        <v>0.862</v>
+        <v>1</v>
       </c>
     </row>
     <row r="702">
@@ -31313,7 +31313,7 @@
         <v>0.5649999999999999</v>
       </c>
       <c r="I703" t="n">
-        <v>1</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="704">
@@ -31350,7 +31350,7 @@
         <v>0.754</v>
       </c>
       <c r="I704" t="n">
-        <v>1</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="705">
@@ -31387,7 +31387,7 @@
         <v>0.578</v>
       </c>
       <c r="I705" t="n">
-        <v>1</v>
+        <v>0.6909999999999999</v>
       </c>
     </row>
     <row r="706">
@@ -31424,7 +31424,7 @@
         <v>0.188</v>
       </c>
       <c r="I706" t="n">
-        <v>0.744</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="707">
@@ -31461,7 +31461,7 @@
         <v>0.785</v>
       </c>
       <c r="I707" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="708">
@@ -31498,7 +31498,7 @@
         <v>0.825</v>
       </c>
       <c r="I708" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="709">
@@ -31609,7 +31609,7 @@
         <v>0.232</v>
       </c>
       <c r="I711" t="n">
-        <v>0.744</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="712">
@@ -31646,7 +31646,7 @@
         <v>0.625</v>
       </c>
       <c r="I712" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="713">
@@ -31683,7 +31683,7 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="I713" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="714">
@@ -31720,7 +31720,7 @@
         <v>0.0285</v>
       </c>
       <c r="I714" t="n">
-        <v>0.228</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="715">
@@ -31757,7 +31757,7 @@
         <v>0.028</v>
       </c>
       <c r="I715" t="n">
-        <v>0.228</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="716">
@@ -31794,7 +31794,7 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="I716" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="717">
@@ -31831,7 +31831,7 @@
         <v>0.518</v>
       </c>
       <c r="I717" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="718">
@@ -31868,7 +31868,7 @@
         <v>0.541</v>
       </c>
       <c r="I718" t="n">
-        <v>0.9429999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="719">
@@ -31905,7 +31905,7 @@
         <v>0.5659999999999999</v>
       </c>
       <c r="I719" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="720">
@@ -31942,7 +31942,7 @@
         <v>0.419</v>
       </c>
       <c r="I720" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="721">
@@ -31979,7 +31979,7 @@
         <v>0.193</v>
       </c>
       <c r="I721" t="n">
-        <v>0.744</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="722">
@@ -32053,7 +32053,7 @@
         <v>0.549</v>
       </c>
       <c r="I723" t="n">
-        <v>1</v>
+        <v>0.6860000000000001</v>
       </c>
     </row>
     <row r="724">
@@ -32090,7 +32090,7 @@
         <v>0.796</v>
       </c>
       <c r="I724" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="725">
@@ -32164,7 +32164,7 @@
         <v>0.142</v>
       </c>
       <c r="I726" t="n">
-        <v>1</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="727">
@@ -32312,7 +32312,7 @@
         <v>0.359</v>
       </c>
       <c r="I730" t="n">
-        <v>1</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="731">
@@ -32423,7 +32423,7 @@
         <v>0.755</v>
       </c>
       <c r="I733" t="n">
-        <v>1</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="734">
@@ -32497,7 +32497,7 @@
         <v>0.4</v>
       </c>
       <c r="I735" t="n">
-        <v>1</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="736">
@@ -32534,7 +32534,7 @@
         <v>0.707</v>
       </c>
       <c r="I736" t="n">
-        <v>1</v>
+        <v>0.832</v>
       </c>
     </row>
     <row r="737">
@@ -32571,7 +32571,7 @@
         <v>0.672</v>
       </c>
       <c r="I737" t="n">
-        <v>1</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="738">
@@ -32608,7 +32608,7 @@
         <v>0.0853</v>
       </c>
       <c r="I738" t="n">
-        <v>0.341</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="739">
@@ -32719,7 +32719,7 @@
         <v>0.488</v>
       </c>
       <c r="I741" t="n">
-        <v>0.969</v>
+        <v>1</v>
       </c>
     </row>
     <row r="742">
@@ -32756,7 +32756,7 @@
         <v>0.506</v>
       </c>
       <c r="I742" t="n">
-        <v>0.969</v>
+        <v>1</v>
       </c>
     </row>
     <row r="743">
@@ -32793,7 +32793,7 @@
         <v>0.0313</v>
       </c>
       <c r="I743" t="n">
-        <v>0.167</v>
+        <v>0.0427</v>
       </c>
     </row>
     <row r="744">
@@ -32830,7 +32830,7 @@
         <v>0.387</v>
       </c>
       <c r="I744" t="n">
-        <v>0.969</v>
+        <v>0.581</v>
       </c>
     </row>
     <row r="745">
@@ -32904,7 +32904,7 @@
         <v>0.00213</v>
       </c>
       <c r="I746" t="n">
-        <v>0.0341</v>
+        <v>0.0106</v>
       </c>
     </row>
     <row r="747">
@@ -32941,7 +32941,7 @@
         <v>0.0047</v>
       </c>
       <c r="I747" t="n">
-        <v>0.0376</v>
+        <v>0.0235</v>
       </c>
     </row>
     <row r="748">
@@ -32978,7 +32978,7 @@
         <v>0.739</v>
       </c>
       <c r="I748" t="n">
-        <v>1</v>
+        <v>0.792</v>
       </c>
     </row>
     <row r="749">
@@ -33015,7 +33015,7 @@
         <v>0.545</v>
       </c>
       <c r="I749" t="n">
-        <v>0.969</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="750">
@@ -33126,7 +33126,7 @@
         <v>0.425</v>
       </c>
       <c r="I752" t="n">
-        <v>0.969</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="753">
@@ -33200,7 +33200,7 @@
         <v>0.116</v>
       </c>
       <c r="I754" t="n">
-        <v>0.464</v>
+        <v>0.334</v>
       </c>
     </row>
     <row r="755">
@@ -33237,7 +33237,7 @@
         <v>0.779</v>
       </c>
       <c r="I755" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="756">
@@ -33274,7 +33274,7 @@
         <v>0.8159999999999999</v>
       </c>
       <c r="I756" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="757">
@@ -33311,7 +33311,7 @@
         <v>0.608</v>
       </c>
       <c r="I757" t="n">
-        <v>0.926</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="758">
@@ -33385,7 +33385,7 @@
         <v>0.108</v>
       </c>
       <c r="I759" t="n">
-        <v>0.464</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="760">
@@ -33422,7 +33422,7 @@
         <v>0.518</v>
       </c>
       <c r="I760" t="n">
-        <v>0.926</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="761">
@@ -33459,7 +33459,7 @@
         <v>0.695</v>
       </c>
       <c r="I761" t="n">
-        <v>0.926</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="762">
@@ -33496,7 +33496,7 @@
         <v>0.00518</v>
       </c>
       <c r="I762" t="n">
-        <v>0.0415</v>
+        <v>0.0259</v>
       </c>
     </row>
     <row r="763">
@@ -33533,7 +33533,7 @@
         <v>0.00456</v>
       </c>
       <c r="I763" t="n">
-        <v>0.0415</v>
+        <v>0.0228</v>
       </c>
     </row>
     <row r="764">
@@ -33570,7 +33570,7 @@
         <v>0.597</v>
       </c>
       <c r="I764" t="n">
-        <v>0.926</v>
+        <v>0.6889999999999999</v>
       </c>
     </row>
     <row r="765">
@@ -33607,7 +33607,7 @@
         <v>0.405</v>
       </c>
       <c r="I765" t="n">
-        <v>0.926</v>
+        <v>1</v>
       </c>
     </row>
     <row r="766">
@@ -33644,7 +33644,7 @@
         <v>0.525</v>
       </c>
       <c r="I766" t="n">
-        <v>0.926</v>
+        <v>1</v>
       </c>
     </row>
     <row r="767">
@@ -33681,7 +33681,7 @@
         <v>0.666</v>
       </c>
       <c r="I767" t="n">
-        <v>0.926</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="768">
@@ -33718,7 +33718,7 @@
         <v>0.917</v>
       </c>
       <c r="I768" t="n">
-        <v>0.979</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="769">
@@ -33755,7 +33755,7 @@
         <v>0.662</v>
       </c>
       <c r="I769" t="n">
-        <v>0.926</v>
+        <v>0.709</v>
       </c>
     </row>
     <row r="770">
@@ -33792,7 +33792,7 @@
         <v>0.188</v>
       </c>
       <c r="I770" t="n">
-        <v>0.619</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="771">
@@ -33940,7 +33940,7 @@
         <v>0.481</v>
       </c>
       <c r="I774" t="n">
-        <v>0.907</v>
+        <v>1</v>
       </c>
     </row>
     <row r="775">
@@ -33977,7 +33977,7 @@
         <v>0.13</v>
       </c>
       <c r="I775" t="n">
-        <v>0.619</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="776">
@@ -34014,7 +34014,7 @@
         <v>0.51</v>
       </c>
       <c r="I776" t="n">
-        <v>0.907</v>
+        <v>1</v>
       </c>
     </row>
     <row r="777">
@@ -34051,7 +34051,7 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="I777" t="n">
-        <v>1</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="778">
@@ -34088,7 +34088,7 @@
         <v>0.0285</v>
       </c>
       <c r="I778" t="n">
-        <v>0.456</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="779">
@@ -34125,7 +34125,7 @@
         <v>0.0644</v>
       </c>
       <c r="I779" t="n">
-        <v>0.515</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="780">
@@ -34162,7 +34162,7 @@
         <v>0.786</v>
       </c>
       <c r="I780" t="n">
-        <v>1</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="781">
@@ -34273,7 +34273,7 @@
         <v>0.384</v>
       </c>
       <c r="I783" t="n">
-        <v>0.907</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="784">
@@ -34310,7 +34310,7 @@
         <v>0.419</v>
       </c>
       <c r="I784" t="n">
-        <v>0.907</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="785">
@@ -34347,7 +34347,7 @@
         <v>0.193</v>
       </c>
       <c r="I785" t="n">
-        <v>0.619</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="786">
@@ -34421,7 +34421,7 @@
         <v>0.772</v>
       </c>
       <c r="I787" t="n">
-        <v>1</v>
+        <v>0.891</v>
       </c>
     </row>
     <row r="788">
@@ -34532,7 +34532,7 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I790" t="n">
-        <v>1</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="791">
@@ -34569,7 +34569,7 @@
         <v>0.636</v>
       </c>
       <c r="I791" t="n">
-        <v>1</v>
+        <v>0.867</v>
       </c>
     </row>
     <row r="792">
@@ -34606,7 +34606,7 @@
         <v>0.801</v>
       </c>
       <c r="I792" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="793">
@@ -34680,7 +34680,7 @@
         <v>0.359</v>
       </c>
       <c r="I794" t="n">
-        <v>1</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="795">
@@ -34865,7 +34865,7 @@
         <v>0.41</v>
       </c>
       <c r="I799" t="n">
-        <v>1</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="800">
@@ -34902,7 +34902,7 @@
         <v>0.705</v>
       </c>
       <c r="I800" t="n">
-        <v>1</v>
+        <v>0.832</v>
       </c>
     </row>
     <row r="801">
@@ -34939,7 +34939,7 @@
         <v>0.573</v>
       </c>
       <c r="I801" t="n">
-        <v>1</v>
+        <v>0.716</v>
       </c>
     </row>
     <row r="802">
@@ -34976,7 +34976,7 @@
         <v>0.125</v>
       </c>
       <c r="I802" t="n">
-        <v>0.5</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="803">
@@ -35013,7 +35013,7 @@
         <v>0.491</v>
       </c>
       <c r="I803" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="804">
@@ -35161,7 +35161,7 @@
         <v>0.0864</v>
       </c>
       <c r="I807" t="n">
-        <v>0.461</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="808">
@@ -35198,7 +35198,7 @@
         <v>0.523</v>
       </c>
       <c r="I808" t="n">
-        <v>1</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="809">
@@ -35272,7 +35272,7 @@
         <v>0.00213</v>
       </c>
       <c r="I810" t="n">
-        <v>0.0341</v>
+        <v>0.0106</v>
       </c>
     </row>
     <row r="811">
@@ -35309,7 +35309,7 @@
         <v>0.00856</v>
       </c>
       <c r="I811" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0321</v>
       </c>
     </row>
     <row r="812">
@@ -35346,7 +35346,7 @@
         <v>0.619</v>
       </c>
       <c r="I812" t="n">
-        <v>1</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="813">
@@ -35383,7 +35383,7 @@
         <v>0.545</v>
       </c>
       <c r="I813" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="814">
@@ -35457,7 +35457,7 @@
         <v>0.838</v>
       </c>
       <c r="I815" t="n">
-        <v>1</v>
+        <v>0.967</v>
       </c>
     </row>
     <row r="816">
@@ -35494,7 +35494,7 @@
         <v>0.801</v>
       </c>
       <c r="I816" t="n">
-        <v>1</v>
+        <v>0.924</v>
       </c>
     </row>
     <row r="817">
@@ -35568,7 +35568,7 @@
         <v>0.117</v>
       </c>
       <c r="I818" t="n">
-        <v>0.466</v>
+        <v>0.334</v>
       </c>
     </row>
     <row r="819">
@@ -35642,7 +35642,7 @@
         <v>0.827</v>
       </c>
       <c r="I820" t="n">
-        <v>0.945</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="821">
@@ -35679,7 +35679,7 @@
         <v>0.616</v>
       </c>
       <c r="I821" t="n">
-        <v>0.896</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="822">
@@ -35716,7 +35716,7 @@
         <v>0.583</v>
       </c>
       <c r="I822" t="n">
-        <v>0.896</v>
+        <v>1</v>
       </c>
     </row>
     <row r="823">
@@ -35753,7 +35753,7 @@
         <v>0.0743</v>
       </c>
       <c r="I823" t="n">
-        <v>0.396</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="824">
@@ -35790,7 +35790,7 @@
         <v>0.416</v>
       </c>
       <c r="I824" t="n">
-        <v>0.896</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="825">
@@ -35827,7 +35827,7 @@
         <v>0.695</v>
       </c>
       <c r="I825" t="n">
-        <v>0.926</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="826">
@@ -35864,7 +35864,7 @@
         <v>0.00518</v>
       </c>
       <c r="I826" t="n">
-        <v>0.0829</v>
+        <v>0.0259</v>
       </c>
     </row>
     <row r="827">
@@ -35901,7 +35901,7 @@
         <v>0.013</v>
       </c>
       <c r="I827" t="n">
-        <v>0.104</v>
+        <v>0.0487</v>
       </c>
     </row>
     <row r="828">
@@ -35938,7 +35938,7 @@
         <v>0.596</v>
       </c>
       <c r="I828" t="n">
-        <v>0.896</v>
+        <v>0.6889999999999999</v>
       </c>
     </row>
     <row r="829">
@@ -35975,7 +35975,7 @@
         <v>0.508</v>
       </c>
       <c r="I829" t="n">
-        <v>0.896</v>
+        <v>1</v>
       </c>
     </row>
     <row r="830">
@@ -36049,7 +36049,7 @@
         <v>0.384</v>
       </c>
       <c r="I831" t="n">
-        <v>0.896</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="832">
@@ -36086,7 +36086,7 @@
         <v>0.756</v>
       </c>
       <c r="I832" t="n">
-        <v>0.93</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="833">
@@ -36123,7 +36123,7 @@
         <v>0.583</v>
       </c>
       <c r="I833" t="n">
-        <v>0.896</v>
+        <v>0.6909999999999999</v>
       </c>
     </row>
     <row r="834">
@@ -36160,7 +36160,7 @@
         <v>0.245</v>
       </c>
       <c r="I834" t="n">
-        <v>0.66</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="835">
@@ -36345,7 +36345,7 @@
         <v>0.3</v>
       </c>
       <c r="I839" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="840">
@@ -36419,7 +36419,7 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="I841" t="n">
-        <v>1</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="842">
@@ -36456,7 +36456,7 @@
         <v>0.00906</v>
       </c>
       <c r="I842" t="n">
-        <v>0.0838</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="843">
@@ -36493,7 +36493,7 @@
         <v>0.0105</v>
       </c>
       <c r="I843" t="n">
-        <v>0.0838</v>
+        <v>0.0788</v>
       </c>
     </row>
     <row r="844">
@@ -36530,7 +36530,7 @@
         <v>0.424</v>
       </c>
       <c r="I844" t="n">
-        <v>0.753</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="845">
@@ -36567,7 +36567,7 @@
         <v>0.415</v>
       </c>
       <c r="I845" t="n">
-        <v>0.753</v>
+        <v>1</v>
       </c>
     </row>
     <row r="846">
@@ -36641,7 +36641,7 @@
         <v>0.0307</v>
       </c>
       <c r="I847" t="n">
-        <v>0.123</v>
+        <v>0.461</v>
       </c>
     </row>
     <row r="848">
@@ -36678,7 +36678,7 @@
         <v>0.248</v>
       </c>
       <c r="I848" t="n">
-        <v>0.66</v>
+        <v>0.572</v>
       </c>
     </row>
     <row r="849">
@@ -36715,7 +36715,7 @@
         <v>0.0162</v>
       </c>
       <c r="I849" t="n">
-        <v>0.0862</v>
+        <v>0.0607</v>
       </c>
     </row>
     <row r="850">
@@ -36900,7 +36900,7 @@
         <v>0.0888</v>
       </c>
       <c r="I854" t="n">
-        <v>0.71</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="855">
@@ -36974,7 +36974,7 @@
         <v>0.802</v>
       </c>
       <c r="I856" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="857">
@@ -37048,7 +37048,7 @@
         <v>0.363</v>
       </c>
       <c r="I858" t="n">
-        <v>1</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="859">
@@ -37159,7 +37159,7 @@
         <v>0.754</v>
       </c>
       <c r="I861" t="n">
-        <v>1</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="862">
@@ -37233,7 +37233,7 @@
         <v>0.0384</v>
       </c>
       <c r="I863" t="n">
-        <v>0.614</v>
+        <v>0.0823</v>
       </c>
     </row>
     <row r="864">
@@ -37270,7 +37270,7 @@
         <v>0.619</v>
       </c>
       <c r="I864" t="n">
-        <v>1</v>
+        <v>0.832</v>
       </c>
     </row>
     <row r="865">
@@ -37307,7 +37307,7 @@
         <v>0.32</v>
       </c>
       <c r="I865" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="866">
@@ -37344,7 +37344,7 @@
         <v>0.125</v>
       </c>
       <c r="I866" t="n">
-        <v>0.529</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="867">
@@ -37381,7 +37381,7 @@
         <v>0.491</v>
       </c>
       <c r="I867" t="n">
-        <v>0.846</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="868">
@@ -37455,7 +37455,7 @@
         <v>0.488</v>
       </c>
       <c r="I869" t="n">
-        <v>0.846</v>
+        <v>1</v>
       </c>
     </row>
     <row r="870">
@@ -37492,7 +37492,7 @@
         <v>0.62</v>
       </c>
       <c r="I870" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="871">
@@ -37529,7 +37529,7 @@
         <v>0.132</v>
       </c>
       <c r="I871" t="n">
-        <v>0.529</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="872">
@@ -37566,7 +37566,7 @@
         <v>0.675</v>
       </c>
       <c r="I872" t="n">
-        <v>0.9</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="873">
@@ -37640,7 +37640,7 @@
         <v>0.000395</v>
       </c>
       <c r="I874" t="n">
-        <v>0.00632</v>
+        <v>0.00592</v>
       </c>
     </row>
     <row r="875">
@@ -37677,7 +37677,7 @@
         <v>0.00245</v>
       </c>
       <c r="I875" t="n">
-        <v>0.0196</v>
+        <v>0.0184</v>
       </c>
     </row>
     <row r="876">
@@ -37714,7 +37714,7 @@
         <v>0.51</v>
       </c>
       <c r="I876" t="n">
-        <v>0.846</v>
+        <v>0.638</v>
       </c>
     </row>
     <row r="877">
@@ -37751,7 +37751,7 @@
         <v>0.415</v>
       </c>
       <c r="I877" t="n">
-        <v>0.846</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="878">
@@ -37825,7 +37825,7 @@
         <v>0.529</v>
       </c>
       <c r="I879" t="n">
-        <v>0.846</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="880">
@@ -37862,7 +37862,7 @@
         <v>0.273</v>
       </c>
       <c r="I880" t="n">
-        <v>0.846</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="881">
@@ -37899,7 +37899,7 @@
         <v>0.845</v>
       </c>
       <c r="I881" t="n">
-        <v>1</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="882">
@@ -37936,7 +37936,7 @@
         <v>0.156</v>
       </c>
       <c r="I882" t="n">
-        <v>0.609</v>
+        <v>0.334</v>
       </c>
     </row>
     <row r="883">
@@ -37973,7 +37973,7 @@
         <v>0.796</v>
       </c>
       <c r="I883" t="n">
-        <v>0.889</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="884">
@@ -38010,7 +38010,7 @@
         <v>0.827</v>
       </c>
       <c r="I884" t="n">
-        <v>0.889</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="885">
@@ -38047,7 +38047,7 @@
         <v>0.608</v>
       </c>
       <c r="I885" t="n">
-        <v>0.889</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="886">
@@ -38084,7 +38084,7 @@
         <v>0.889</v>
       </c>
       <c r="I886" t="n">
-        <v>0.889</v>
+        <v>1</v>
       </c>
     </row>
     <row r="887">
@@ -38121,7 +38121,7 @@
         <v>0.19</v>
       </c>
       <c r="I887" t="n">
-        <v>0.609</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="888">
@@ -38158,7 +38158,7 @@
         <v>0.52</v>
       </c>
       <c r="I888" t="n">
-        <v>0.889</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="889">
@@ -38195,7 +38195,7 @@
         <v>0.695</v>
       </c>
       <c r="I889" t="n">
-        <v>0.889</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="890">
@@ -38232,7 +38232,7 @@
         <v>0.00129</v>
       </c>
       <c r="I890" t="n">
-        <v>0.0109</v>
+        <v>0.0193</v>
       </c>
     </row>
     <row r="891">
@@ -38269,7 +38269,7 @@
         <v>0.00136</v>
       </c>
       <c r="I891" t="n">
-        <v>0.0109</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="892">
@@ -38306,7 +38306,7 @@
         <v>0.361</v>
       </c>
       <c r="I892" t="n">
-        <v>0.721</v>
+        <v>0.492</v>
       </c>
     </row>
     <row r="893">
@@ -38343,7 +38343,7 @@
         <v>0.313</v>
       </c>
       <c r="I893" t="n">
-        <v>0.715</v>
+        <v>1</v>
       </c>
     </row>
     <row r="894">
@@ -38380,7 +38380,7 @@
         <v>0.714</v>
       </c>
       <c r="I894" t="n">
-        <v>0.889</v>
+        <v>1</v>
       </c>
     </row>
     <row r="895">
@@ -38417,7 +38417,7 @@
         <v>0.0441</v>
       </c>
       <c r="I895" t="n">
-        <v>0.235</v>
+        <v>0.661</v>
       </c>
     </row>
     <row r="896">
@@ -38454,7 +38454,7 @@
         <v>0.837</v>
       </c>
       <c r="I896" t="n">
-        <v>0.889</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="897">
@@ -38491,7 +38491,7 @@
         <v>0.229</v>
       </c>
       <c r="I897" t="n">
-        <v>0.61</v>
+        <v>0.433</v>
       </c>
     </row>
     <row r="898">
@@ -38528,7 +38528,7 @@
         <v>0.312</v>
       </c>
       <c r="I898" t="n">
-        <v>0.833</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="899">
@@ -38602,7 +38602,7 @@
         <v>0.488</v>
       </c>
       <c r="I900" t="n">
-        <v>1</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="901">
@@ -38713,7 +38713,7 @@
         <v>0.176</v>
       </c>
       <c r="I903" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="904">
@@ -38787,7 +38787,7 @@
         <v>0.619</v>
       </c>
       <c r="I905" t="n">
-        <v>1</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="906">
@@ -38824,7 +38824,7 @@
         <v>0.536</v>
       </c>
       <c r="I906" t="n">
-        <v>1</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="907">
@@ -38861,7 +38861,7 @@
         <v>0.176</v>
       </c>
       <c r="I907" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.377</v>
       </c>
     </row>
     <row r="908">
@@ -38898,7 +38898,7 @@
         <v>0.779</v>
       </c>
       <c r="I908" t="n">
-        <v>1</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="909">
@@ -39009,7 +39009,7 @@
         <v>0.135</v>
       </c>
       <c r="I911" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="912">
@@ -39046,7 +39046,7 @@
         <v>0.000212</v>
       </c>
       <c r="I912" t="n">
-        <v>0.0017</v>
+        <v>0.00318</v>
       </c>
     </row>
     <row r="913">
@@ -39083,7 +39083,7 @@
         <v>2.67e-06</v>
       </c>
       <c r="I913" t="n">
-        <v>4.27e-05</v>
+        <v>4e-05</v>
       </c>
     </row>
     <row r="914">
@@ -39157,7 +39157,7 @@
         <v>0.523</v>
       </c>
       <c r="I915" t="n">
-        <v>0.698</v>
+        <v>0.6860000000000001</v>
       </c>
     </row>
     <row r="916">
@@ -39194,7 +39194,7 @@
         <v>0.0623</v>
       </c>
       <c r="I916" t="n">
-        <v>0.199</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="917">
@@ -39268,7 +39268,7 @@
         <v>0.247</v>
       </c>
       <c r="I918" t="n">
-        <v>0.449</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="919">
@@ -39305,7 +39305,7 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I919" t="n">
-        <v>0.214</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="920">
@@ -39342,7 +39342,7 @@
         <v>0.252</v>
       </c>
       <c r="I920" t="n">
-        <v>0.449</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="921">
@@ -39379,7 +39379,7 @@
         <v>0.524</v>
       </c>
       <c r="I921" t="n">
-        <v>0.698</v>
+        <v>1</v>
       </c>
     </row>
     <row r="922">
@@ -39416,7 +39416,7 @@
         <v>0.364</v>
       </c>
       <c r="I922" t="n">
-        <v>0.583</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="923">
@@ -39490,7 +39490,7 @@
         <v>0.038</v>
       </c>
       <c r="I924" t="n">
-        <v>0.152</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="925">
@@ -39527,7 +39527,7 @@
         <v>0.124</v>
       </c>
       <c r="I925" t="n">
-        <v>0.283</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="926">
@@ -39564,7 +39564,7 @@
         <v>0.613</v>
       </c>
       <c r="I926" t="n">
-        <v>0.755</v>
+        <v>1</v>
       </c>
     </row>
     <row r="927">
@@ -39601,7 +39601,7 @@
         <v>0.0005330000000000001</v>
       </c>
       <c r="I927" t="n">
-        <v>0.00428</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="928">
@@ -39638,7 +39638,7 @@
         <v>0.000535</v>
       </c>
       <c r="I928" t="n">
-        <v>0.00428</v>
+        <v>0.008019999999999999</v>
       </c>
     </row>
     <row r="929">
@@ -39675,7 +39675,7 @@
         <v>0.00117</v>
       </c>
       <c r="I929" t="n">
-        <v>0.00623</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="930">
@@ -39712,7 +39712,7 @@
         <v>0.241</v>
       </c>
       <c r="I930" t="n">
-        <v>0.642</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="931">
@@ -39749,7 +39749,7 @@
         <v>0.236</v>
       </c>
       <c r="I931" t="n">
-        <v>0.642</v>
+        <v>0.443</v>
       </c>
     </row>
     <row r="932">
@@ -39786,7 +39786,7 @@
         <v>0.101</v>
       </c>
       <c r="I932" t="n">
-        <v>0.405</v>
+        <v>1</v>
       </c>
     </row>
     <row r="933">
@@ -39860,7 +39860,7 @@
         <v>0.532</v>
       </c>
       <c r="I934" t="n">
-        <v>0.881</v>
+        <v>1</v>
       </c>
     </row>
     <row r="935">
@@ -39897,7 +39897,7 @@
         <v>0.723</v>
       </c>
       <c r="I935" t="n">
-        <v>0.89</v>
+        <v>0.723</v>
       </c>
     </row>
     <row r="936">
@@ -39934,7 +39934,7 @@
         <v>0.845</v>
       </c>
       <c r="I936" t="n">
-        <v>0.965</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="937">
@@ -40008,7 +40008,7 @@
         <v>0.695</v>
       </c>
       <c r="I938" t="n">
-        <v>0.89</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="939">
@@ -40045,7 +40045,7 @@
         <v>0.0902</v>
       </c>
       <c r="I939" t="n">
-        <v>0.405</v>
+        <v>0.238</v>
       </c>
     </row>
     <row r="940">
@@ -40082,7 +40082,7 @@
         <v>0.413</v>
       </c>
       <c r="I940" t="n">
-        <v>0.881</v>
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="941">
@@ -40119,7 +40119,7 @@
         <v>0.5679999999999999</v>
       </c>
       <c r="I941" t="n">
-        <v>0.881</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="942">
@@ -40156,7 +40156,7 @@
         <v>0.606</v>
       </c>
       <c r="I942" t="n">
-        <v>0.881</v>
+        <v>1</v>
       </c>
     </row>
     <row r="943">
@@ -40193,7 +40193,7 @@
         <v>0.447</v>
       </c>
       <c r="I943" t="n">
-        <v>0.881</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="944">
@@ -40230,7 +40230,7 @@
         <v>0.000275</v>
       </c>
       <c r="I944" t="n">
-        <v>0.0044</v>
+        <v>0.00413</v>
       </c>
     </row>
     <row r="945">
@@ -40267,7 +40267,7 @@
         <v>0.00827</v>
       </c>
       <c r="I945" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="946">
@@ -40304,7 +40304,7 @@
         <v>0.207</v>
       </c>
       <c r="I946" t="n">
-        <v>1</v>
+        <v>0.388</v>
       </c>
     </row>
     <row r="947">
@@ -40378,7 +40378,7 @@
         <v>0.8070000000000001</v>
       </c>
       <c r="I948" t="n">
-        <v>1</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="949">
@@ -40489,7 +40489,7 @@
         <v>0.183</v>
       </c>
       <c r="I951" t="n">
-        <v>1</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="952">
@@ -40526,7 +40526,7 @@
         <v>0.751</v>
       </c>
       <c r="I952" t="n">
-        <v>1</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="953">
@@ -40563,7 +40563,7 @@
         <v>0.44</v>
       </c>
       <c r="I953" t="n">
-        <v>1</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="954">
@@ -40600,7 +40600,7 @@
         <v>0.486</v>
       </c>
       <c r="I954" t="n">
-        <v>1</v>
+        <v>0.5610000000000001</v>
       </c>
     </row>
     <row r="955">
@@ -40637,7 +40637,7 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I955" t="n">
-        <v>1</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="956">
@@ -40785,7 +40785,7 @@
         <v>0.364</v>
       </c>
       <c r="I959" t="n">
-        <v>1</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="960">
@@ -40822,7 +40822,7 @@
         <v>0.625</v>
       </c>
       <c r="I960" t="n">
-        <v>1</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="961">
@@ -40859,7 +40859,7 @@
         <v>0.599</v>
       </c>
       <c r="I961" t="n">
-        <v>1</v>
+        <v>0.6909999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/eval/learning-curve/results/statistical_tests_full150.xlsx
+++ b/eval/learning-curve/results/statistical_tests_full150.xlsx
@@ -518,7 +518,7 @@
         <v>0.102</v>
       </c>
       <c r="J2" t="n">
-        <v>0.319</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="3">
@@ -558,7 +558,7 @@
         <v>0.102</v>
       </c>
       <c r="J3" t="n">
-        <v>0.334</v>
+        <v>0.2566666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -598,7 +598,7 @@
         <v>0.169</v>
       </c>
       <c r="J4" t="n">
-        <v>0.681</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="5">
@@ -678,7 +678,7 @@
         <v>0.0877</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="7">
@@ -718,7 +718,7 @@
         <v>0.0877</v>
       </c>
       <c r="J7" t="n">
-        <v>0.495</v>
+        <v>0.335</v>
       </c>
     </row>
     <row r="8">
@@ -758,7 +758,7 @@
         <v>0.156</v>
       </c>
       <c r="J8" t="n">
-        <v>0.755</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.156</v>
       </c>
       <c r="J9" t="n">
-        <v>0.765</v>
+        <v>0.80125</v>
       </c>
     </row>
     <row r="10">
@@ -838,7 +838,7 @@
         <v>0.167</v>
       </c>
       <c r="J10" t="n">
-        <v>0.651</v>
+        <v>0.4069999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -878,7 +878,7 @@
         <v>0.167</v>
       </c>
       <c r="J11" t="n">
-        <v>0.773</v>
+        <v>0.6830000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -918,7 +918,7 @@
         <v>0.152</v>
       </c>
       <c r="J12" t="n">
-        <v>0.725</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="13">
@@ -958,7 +958,7 @@
         <v>0.152</v>
       </c>
       <c r="J13" t="n">
-        <v>0.695</v>
+        <v>0.80125</v>
       </c>
     </row>
     <row r="14">
@@ -998,7 +998,7 @@
         <v>0.0829</v>
       </c>
       <c r="J14" t="n">
-        <v>0.251</v>
+        <v>0.178</v>
       </c>
     </row>
     <row r="15">
@@ -1038,7 +1038,7 @@
         <v>0.0829</v>
       </c>
       <c r="J15" t="n">
-        <v>0.308</v>
+        <v>0.2566666666666667</v>
       </c>
     </row>
     <row r="16">
@@ -1078,7 +1078,7 @@
         <v>0.174</v>
       </c>
       <c r="J16" t="n">
-        <v>0.768</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="17">
@@ -1118,7 +1118,7 @@
         <v>0.174</v>
       </c>
       <c r="J17" t="n">
-        <v>0.765</v>
+        <v>0.80125</v>
       </c>
     </row>
     <row r="18">
@@ -1158,7 +1158,7 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="19">
@@ -1198,7 +1198,7 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0372</v>
+        <v>0.007299999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1238,7 +1238,7 @@
         <v>0.0842</v>
       </c>
       <c r="J20" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="21">
@@ -1278,7 +1278,7 @@
         <v>0.0842</v>
       </c>
       <c r="J21" t="n">
-        <v>0.121</v>
+        <v>0.1215</v>
       </c>
     </row>
     <row r="22">
@@ -1318,7 +1318,7 @@
         <v>0.165</v>
       </c>
       <c r="J22" t="n">
-        <v>0.126</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="23">
@@ -1358,7 +1358,7 @@
         <v>0.165</v>
       </c>
       <c r="J23" t="n">
-        <v>0.123</v>
+        <v>0.1064</v>
       </c>
     </row>
     <row r="24">
@@ -1398,7 +1398,7 @@
         <v>0.175</v>
       </c>
       <c r="J24" t="n">
-        <v>0.395</v>
+        <v>0.3093333333333333</v>
       </c>
     </row>
     <row r="25">
@@ -1438,7 +1438,7 @@
         <v>0.175</v>
       </c>
       <c r="J25" t="n">
-        <v>0.323</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="26">
@@ -1478,7 +1478,7 @@
         <v>0.175</v>
       </c>
       <c r="J26" t="n">
-        <v>0.48</v>
+        <v>0.3093333333333333</v>
       </c>
     </row>
     <row r="27">
@@ -1518,7 +1518,7 @@
         <v>0.175</v>
       </c>
       <c r="J27" t="n">
-        <v>0.495</v>
+        <v>0.339</v>
       </c>
     </row>
     <row r="28">
@@ -1558,7 +1558,7 @@
         <v>0.19</v>
       </c>
       <c r="J28" t="n">
-        <v>0.617</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="29">
@@ -1598,7 +1598,7 @@
         <v>0.19</v>
       </c>
       <c r="J29" t="n">
-        <v>0.598</v>
+        <v>0.339</v>
       </c>
     </row>
     <row r="30">
@@ -1638,7 +1638,7 @@
         <v>0.0931</v>
       </c>
       <c r="J30" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0144</v>
       </c>
     </row>
     <row r="31">
@@ -1678,7 +1678,7 @@
         <v>0.0931</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0372</v>
+        <v>0.00186</v>
       </c>
     </row>
     <row r="32">
@@ -1718,7 +1718,7 @@
         <v>0.12</v>
       </c>
       <c r="J32" t="n">
-        <v>0.903</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="33">
@@ -1758,7 +1758,7 @@
         <v>0.12</v>
       </c>
       <c r="J33" t="n">
-        <v>0.634</v>
+        <v>0.4600000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1798,7 +1798,7 @@
         <v>0.249</v>
       </c>
       <c r="J34" t="n">
-        <v>0.271</v>
+        <v>0.2966666666666666</v>
       </c>
     </row>
     <row r="35">
@@ -1838,7 +1838,7 @@
         <v>0.249</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0572</v>
+        <v>0.03815</v>
       </c>
     </row>
     <row r="36">
@@ -1878,7 +1878,7 @@
         <v>0.134</v>
       </c>
       <c r="J36" t="n">
-        <v>0.768</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="37">
@@ -1918,7 +1918,7 @@
         <v>0.134</v>
       </c>
       <c r="J37" t="n">
-        <v>0.622</v>
+        <v>0.4600000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1958,7 +1958,7 @@
         <v>0.22</v>
       </c>
       <c r="J38" t="n">
-        <v>0.581</v>
+        <v>0.3875</v>
       </c>
     </row>
     <row r="39">
@@ -1998,7 +1998,7 @@
         <v>0.22</v>
       </c>
       <c r="J39" t="n">
-        <v>0.447</v>
+        <v>0.28875</v>
       </c>
     </row>
     <row r="40">
@@ -2038,7 +2038,7 @@
         <v>0.185</v>
       </c>
       <c r="J40" t="n">
-        <v>0.395</v>
+        <v>0.4025</v>
       </c>
     </row>
     <row r="41">
@@ -2078,7 +2078,7 @@
         <v>0.185</v>
       </c>
       <c r="J41" t="n">
-        <v>0.179</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="42">
@@ -2118,7 +2118,7 @@
         <v>0.255</v>
       </c>
       <c r="J42" t="n">
-        <v>0.395</v>
+        <v>0.2966666666666666</v>
       </c>
     </row>
     <row r="43">
@@ -2158,7 +2158,7 @@
         <v>0.255</v>
       </c>
       <c r="J43" t="n">
-        <v>0.362</v>
+        <v>0.28875</v>
       </c>
     </row>
     <row r="44">
@@ -2198,7 +2198,7 @@
         <v>0.107</v>
       </c>
       <c r="J44" t="n">
-        <v>0.829</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="45">
@@ -2238,7 +2238,7 @@
         <v>0.107</v>
       </c>
       <c r="J45" t="n">
-        <v>0.642</v>
+        <v>0.4600000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -2278,7 +2278,7 @@
         <v>0.224</v>
       </c>
       <c r="J46" t="n">
-        <v>0.396</v>
+        <v>0.2966666666666666</v>
       </c>
     </row>
     <row r="47">
@@ -2318,7 +2318,7 @@
         <v>0.224</v>
       </c>
       <c r="J47" t="n">
-        <v>0.222</v>
+        <v>0.18475</v>
       </c>
     </row>
     <row r="48">
@@ -2358,7 +2358,7 @@
         <v>0.0584</v>
       </c>
       <c r="J48" t="n">
-        <v>0.285</v>
+        <v>0.4025</v>
       </c>
     </row>
     <row r="49">
@@ -2398,7 +2398,7 @@
         <v>0.0584</v>
       </c>
       <c r="J49" t="n">
-        <v>0.442</v>
+        <v>0.4600000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2438,7 +2438,7 @@
         <v>0.11</v>
       </c>
       <c r="J50" t="n">
-        <v>0.883</v>
+        <v>0.8089999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2478,7 +2478,7 @@
         <v>0.11</v>
       </c>
       <c r="J51" t="n">
-        <v>0.642</v>
+        <v>0.4600000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2518,7 +2518,7 @@
         <v>0.195</v>
       </c>
       <c r="J52" t="n">
-        <v>0.651</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="53">
@@ -2558,7 +2558,7 @@
         <v>0.195</v>
       </c>
       <c r="J53" t="n">
-        <v>0.622</v>
+        <v>0.744</v>
       </c>
     </row>
     <row r="54">
@@ -2598,7 +2598,7 @@
         <v>0.183</v>
       </c>
       <c r="J54" t="n">
-        <v>0.917</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="55">
@@ -2638,7 +2638,7 @@
         <v>0.183</v>
       </c>
       <c r="J55" t="n">
-        <v>0.827</v>
+        <v>0.744</v>
       </c>
     </row>
     <row r="56">
@@ -2678,7 +2678,7 @@
         <v>0.189</v>
       </c>
       <c r="J56" t="n">
-        <v>0.829</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="57">
@@ -2718,7 +2718,7 @@
         <v>0.189</v>
       </c>
       <c r="J57" t="n">
-        <v>0.765</v>
+        <v>0.744</v>
       </c>
     </row>
     <row r="58">
@@ -2758,7 +2758,7 @@
         <v>0.195</v>
       </c>
       <c r="J58" t="n">
-        <v>0.829</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="59">
@@ -2798,7 +2798,7 @@
         <v>0.195</v>
       </c>
       <c r="J59" t="n">
-        <v>0.765</v>
+        <v>0.744</v>
       </c>
     </row>
     <row r="60">
@@ -2838,7 +2838,7 @@
         <v>0.0954</v>
       </c>
       <c r="J60" t="n">
-        <v>0.03</v>
+        <v>0.000894</v>
       </c>
     </row>
     <row r="61">
@@ -2878,7 +2878,7 @@
         <v>0.0954</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0372</v>
+        <v>0.000987</v>
       </c>
     </row>
     <row r="62">
@@ -2918,7 +2918,7 @@
         <v>0.186</v>
       </c>
       <c r="J62" t="n">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="63">
@@ -2958,7 +2958,7 @@
         <v>0.186</v>
       </c>
       <c r="J63" t="n">
-        <v>0.31</v>
+        <v>0.2066666666666667</v>
       </c>
     </row>
     <row r="64">
@@ -3038,7 +3038,7 @@
         <v>0.266</v>
       </c>
       <c r="J65" t="n">
-        <v>0.323</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="66">
@@ -3078,7 +3078,7 @@
         <v>0.149</v>
       </c>
       <c r="J66" t="n">
-        <v>0.755</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="67">
@@ -3118,7 +3118,7 @@
         <v>0.149</v>
       </c>
       <c r="J67" t="n">
-        <v>0.765</v>
+        <v>0.649</v>
       </c>
     </row>
     <row r="68">
@@ -3158,7 +3158,7 @@
         <v>0.239</v>
       </c>
       <c r="J68" t="n">
-        <v>0.681</v>
+        <v>0.8133333333333334</v>
       </c>
     </row>
     <row r="69">
@@ -3238,7 +3238,7 @@
         <v>0.148</v>
       </c>
       <c r="J70" t="n">
-        <v>0.669</v>
+        <v>0.5575</v>
       </c>
     </row>
     <row r="71">
@@ -3278,7 +3278,7 @@
         <v>0.148</v>
       </c>
       <c r="J71" t="n">
-        <v>0.634</v>
+        <v>0.54125</v>
       </c>
     </row>
     <row r="72">
@@ -3318,7 +3318,7 @@
         <v>0.267</v>
       </c>
       <c r="J72" t="n">
-        <v>0.681</v>
+        <v>0.8133333333333334</v>
       </c>
     </row>
     <row r="73">
@@ -3358,7 +3358,7 @@
         <v>0.267</v>
       </c>
       <c r="J73" t="n">
-        <v>0.895</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -3398,7 +3398,7 @@
         <v>0.144</v>
       </c>
       <c r="J74" t="n">
-        <v>0.347</v>
+        <v>0.3325</v>
       </c>
     </row>
     <row r="75">
@@ -3438,7 +3438,7 @@
         <v>0.144</v>
       </c>
       <c r="J75" t="n">
-        <v>0.308</v>
+        <v>0.2066666666666667</v>
       </c>
     </row>
     <row r="76">
@@ -3478,7 +3478,7 @@
         <v>0.264</v>
       </c>
       <c r="J76" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.994</v>
       </c>
     </row>
     <row r="77">
@@ -3518,7 +3518,7 @@
         <v>0.264</v>
       </c>
       <c r="J77" t="n">
-        <v>0.622</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="78">
@@ -3558,7 +3558,7 @@
         <v>0.137</v>
       </c>
       <c r="J78" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="79">
@@ -3598,7 +3598,7 @@
         <v>0.137</v>
       </c>
       <c r="J79" t="n">
-        <v>0.066</v>
+        <v>0.05499999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3638,7 +3638,7 @@
         <v>0.185</v>
       </c>
       <c r="J80" t="n">
-        <v>0.314</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="81">
@@ -3678,7 +3678,7 @@
         <v>0.185</v>
       </c>
       <c r="J81" t="n">
-        <v>0.308</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="82">
@@ -3718,7 +3718,7 @@
         <v>0.18</v>
       </c>
       <c r="J82" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.0199</v>
       </c>
     </row>
     <row r="83">
@@ -3758,7 +3758,7 @@
         <v>0.18</v>
       </c>
       <c r="J83" t="n">
-        <v>0.13</v>
+        <v>0.0303</v>
       </c>
     </row>
     <row r="84">
@@ -3798,7 +3798,7 @@
         <v>0.16</v>
       </c>
       <c r="J84" t="n">
-        <v>0.0583</v>
+        <v>0.01556</v>
       </c>
     </row>
     <row r="85">
@@ -3838,7 +3838,7 @@
         <v>0.16</v>
       </c>
       <c r="J85" t="n">
-        <v>0.0572</v>
+        <v>0.01526</v>
       </c>
     </row>
     <row r="86">
@@ -3878,7 +3878,7 @@
         <v>0.155</v>
       </c>
       <c r="J86" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0199</v>
       </c>
     </row>
     <row r="87">
@@ -3918,7 +3918,7 @@
         <v>0.155</v>
       </c>
       <c r="J87" t="n">
-        <v>0.109</v>
+        <v>0.02653333333333334</v>
       </c>
     </row>
     <row r="88">
@@ -3958,7 +3958,7 @@
         <v>0.162</v>
       </c>
       <c r="J88" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0199</v>
       </c>
     </row>
     <row r="89">
@@ -3998,7 +3998,7 @@
         <v>0.162</v>
       </c>
       <c r="J89" t="n">
-        <v>0.0572</v>
+        <v>0.01526</v>
       </c>
     </row>
     <row r="90">
@@ -4038,7 +4038,7 @@
         <v>0.163</v>
       </c>
       <c r="J90" t="n">
-        <v>0.314</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="91">
@@ -4078,7 +4078,7 @@
         <v>0.163</v>
       </c>
       <c r="J91" t="n">
-        <v>0.334</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="92">
@@ -4118,7 +4118,7 @@
         <v>0.139</v>
       </c>
       <c r="J92" t="n">
-        <v>0.733</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="93">
@@ -4158,7 +4158,7 @@
         <v>0.139</v>
       </c>
       <c r="J93" t="n">
-        <v>0.622</v>
+        <v>0.6733333333333333</v>
       </c>
     </row>
     <row r="94">
@@ -4198,7 +4198,7 @@
         <v>0.247</v>
       </c>
       <c r="J94" t="n">
-        <v>0.651</v>
+        <v>0.5287499999999999</v>
       </c>
     </row>
     <row r="95">
@@ -4238,7 +4238,7 @@
         <v>0.247</v>
       </c>
       <c r="J95" t="n">
-        <v>0.895</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="96">
@@ -4278,7 +4278,7 @@
         <v>0.116</v>
       </c>
       <c r="J96" t="n">
-        <v>0.903</v>
+        <v>0.8480000000000001</v>
       </c>
     </row>
     <row r="97">
@@ -4318,7 +4318,7 @@
         <v>0.116</v>
       </c>
       <c r="J97" t="n">
-        <v>0.895</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="98">
@@ -4358,7 +4358,7 @@
         <v>0.224</v>
       </c>
       <c r="J98" t="n">
-        <v>0.651</v>
+        <v>0.5287499999999999</v>
       </c>
     </row>
     <row r="99">
@@ -4398,7 +4398,7 @@
         <v>0.224</v>
       </c>
       <c r="J99" t="n">
-        <v>0.895</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="100">
@@ -4438,7 +4438,7 @@
         <v>0.152</v>
       </c>
       <c r="J100" t="n">
-        <v>0.768</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -4478,7 +4478,7 @@
         <v>0.152</v>
       </c>
       <c r="J101" t="n">
-        <v>0.765</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="102">
@@ -4518,7 +4518,7 @@
         <v>0.256</v>
       </c>
       <c r="J102" t="n">
-        <v>0.616</v>
+        <v>0.5287499999999999</v>
       </c>
     </row>
     <row r="103">
@@ -4558,7 +4558,7 @@
         <v>0.256</v>
       </c>
       <c r="J103" t="n">
-        <v>0.765</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="104">
@@ -4598,7 +4598,7 @@
         <v>0.107</v>
       </c>
       <c r="J104" t="n">
-        <v>0.616</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="105">
@@ -4638,7 +4638,7 @@
         <v>0.107</v>
       </c>
       <c r="J105" t="n">
-        <v>0.622</v>
+        <v>0.6733333333333333</v>
       </c>
     </row>
     <row r="106">
@@ -4678,7 +4678,7 @@
         <v>0.238</v>
       </c>
       <c r="J106" t="n">
-        <v>0.725</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="107">
@@ -4718,7 +4718,7 @@
         <v>0.238</v>
       </c>
       <c r="J107" t="n">
-        <v>0.772</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="108">
@@ -4758,7 +4758,7 @@
         <v>0.0919</v>
       </c>
       <c r="J108" t="n">
-        <v>0.0583</v>
+        <v>0.0161</v>
       </c>
     </row>
     <row r="109">
@@ -4798,7 +4798,7 @@
         <v>0.0919</v>
       </c>
       <c r="J109" t="n">
-        <v>0.0429</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="110">
@@ -4838,7 +4838,7 @@
         <v>0.149</v>
       </c>
       <c r="J110" t="n">
-        <v>0.414</v>
+        <v>0.5287499999999999</v>
       </c>
     </row>
     <row r="111">
@@ -4878,7 +4878,7 @@
         <v>0.149</v>
       </c>
       <c r="J111" t="n">
-        <v>0.182</v>
+        <v>0.2885</v>
       </c>
     </row>
     <row r="112">
@@ -4918,7 +4918,7 @@
         <v>0.18</v>
       </c>
       <c r="J112" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0427</v>
       </c>
     </row>
     <row r="113">
@@ -4958,7 +4958,7 @@
         <v>0.18</v>
       </c>
       <c r="J113" t="n">
-        <v>0.066</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="114">
@@ -4998,7 +4998,7 @@
         <v>0.159</v>
       </c>
       <c r="J114" t="n">
-        <v>0.102</v>
+        <v>0.0427</v>
       </c>
     </row>
     <row r="115">
@@ -5038,7 +5038,7 @@
         <v>0.159</v>
       </c>
       <c r="J115" t="n">
-        <v>0.154</v>
+        <v>0.0577</v>
       </c>
     </row>
     <row r="116">
@@ -5078,7 +5078,7 @@
         <v>0.161</v>
       </c>
       <c r="J116" t="n">
-        <v>0.154</v>
+        <v>0.0427</v>
       </c>
     </row>
     <row r="117">
@@ -5118,7 +5118,7 @@
         <v>0.161</v>
       </c>
       <c r="J117" t="n">
-        <v>0.182</v>
+        <v>0.0577</v>
       </c>
     </row>
     <row r="118">
@@ -5158,7 +5158,7 @@
         <v>0.169</v>
       </c>
       <c r="J118" t="n">
-        <v>0.16</v>
+        <v>0.0427</v>
       </c>
     </row>
     <row r="119">
@@ -5198,7 +5198,7 @@
         <v>0.169</v>
       </c>
       <c r="J119" t="n">
-        <v>0.179</v>
+        <v>0.0577</v>
       </c>
     </row>
     <row r="120">
@@ -5238,7 +5238,7 @@
         <v>0.137</v>
       </c>
       <c r="J120" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0151</v>
       </c>
     </row>
     <row r="121">
@@ -5278,7 +5278,7 @@
         <v>0.137</v>
       </c>
       <c r="J121" t="n">
-        <v>0.0572</v>
+        <v>0.0076</v>
       </c>
     </row>
   </sheetData>

--- a/eval/learning-curve/results/statistical_tests_full150.xlsx
+++ b/eval/learning-curve/results/statistical_tests_full150.xlsx
@@ -503,22 +503,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.117</v>
+        <v>0.12</v>
       </c>
       <c r="F2" t="n">
-        <v>0.835</v>
+        <v>0.837</v>
       </c>
       <c r="G2" t="n">
-        <v>0.861</v>
+        <v>0.863</v>
       </c>
       <c r="H2" t="n">
-        <v>0.117</v>
+        <v>0.115</v>
       </c>
       <c r="I2" t="n">
         <v>0.102</v>
       </c>
       <c r="J2" t="n">
-        <v>0.195</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3">
@@ -546,13 +546,13 @@
         <v>0.154</v>
       </c>
       <c r="F3" t="n">
-        <v>0.835</v>
+        <v>0.837</v>
       </c>
       <c r="G3" t="n">
-        <v>0.861</v>
+        <v>0.863</v>
       </c>
       <c r="H3" t="n">
-        <v>0.117</v>
+        <v>0.115</v>
       </c>
       <c r="I3" t="n">
         <v>0.102</v>
@@ -583,22 +583,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.288</v>
+        <v>0.311</v>
       </c>
       <c r="F4" t="n">
-        <v>0.835</v>
+        <v>0.837</v>
       </c>
       <c r="G4" t="n">
-        <v>0.853</v>
+        <v>0.854</v>
       </c>
       <c r="H4" t="n">
-        <v>0.117</v>
+        <v>0.115</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0877</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.36</v>
+        <v>0.38875</v>
       </c>
     </row>
     <row r="5">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.268</v>
+        <v>0.32</v>
       </c>
       <c r="F5" t="n">
-        <v>0.835</v>
+        <v>0.837</v>
       </c>
       <c r="G5" t="n">
-        <v>0.853</v>
+        <v>0.854</v>
       </c>
       <c r="H5" t="n">
-        <v>0.117</v>
+        <v>0.115</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0877</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.335</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="6">
@@ -663,22 +663,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.407</v>
+        <v>0.397</v>
       </c>
       <c r="F6" t="n">
-        <v>0.835</v>
+        <v>0.837</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.117</v>
+        <v>0.115</v>
       </c>
       <c r="I6" t="n">
         <v>0.167</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4069999999999999</v>
+        <v>0.397</v>
       </c>
     </row>
     <row r="7">
@@ -703,22 +703,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="F7" t="n">
-        <v>0.835</v>
+        <v>0.837</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.117</v>
+        <v>0.115</v>
       </c>
       <c r="I7" t="n">
         <v>0.167</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="8">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.0712</v>
+        <v>0.0771</v>
       </c>
       <c r="F8" t="n">
-        <v>0.835</v>
+        <v>0.837</v>
       </c>
       <c r="G8" t="n">
-        <v>0.864</v>
+        <v>0.865</v>
       </c>
       <c r="H8" t="n">
-        <v>0.117</v>
+        <v>0.115</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0829</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.178</v>
+        <v>0.19275</v>
       </c>
     </row>
     <row r="9">
@@ -786,16 +786,16 @@
         <v>0.118</v>
       </c>
       <c r="F9" t="n">
-        <v>0.835</v>
+        <v>0.837</v>
       </c>
       <c r="G9" t="n">
-        <v>0.864</v>
+        <v>0.865</v>
       </c>
       <c r="H9" t="n">
-        <v>0.117</v>
+        <v>0.115</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0829</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="J9" t="n">
         <v>0.2566666666666667</v>
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.001</v>
+        <v>0.0009790000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.835</v>
+        <v>0.837</v>
       </c>
       <c r="G10" t="n">
-        <v>0.901</v>
+        <v>0.903</v>
       </c>
       <c r="H10" t="n">
-        <v>0.117</v>
+        <v>0.115</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0697</v>
       </c>
       <c r="J10" t="n">
-        <v>0.005</v>
+        <v>0.004895</v>
       </c>
     </row>
     <row r="11">
@@ -866,16 +866,16 @@
         <v>0.00146</v>
       </c>
       <c r="F11" t="n">
-        <v>0.835</v>
+        <v>0.837</v>
       </c>
       <c r="G11" t="n">
-        <v>0.901</v>
+        <v>0.903</v>
       </c>
       <c r="H11" t="n">
-        <v>0.117</v>
+        <v>0.115</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0697</v>
       </c>
       <c r="J11" t="n">
         <v>0.007299999999999999</v>
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.01</v>
+        <v>0.0104</v>
       </c>
       <c r="F12" t="n">
-        <v>0.835</v>
+        <v>0.837</v>
       </c>
       <c r="G12" t="n">
-        <v>0.878</v>
+        <v>0.88</v>
       </c>
       <c r="H12" t="n">
-        <v>0.117</v>
+        <v>0.115</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0842</v>
+        <v>0.0828</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01</v>
+        <v>0.0104</v>
       </c>
     </row>
     <row r="13">
@@ -946,16 +946,16 @@
         <v>0.0243</v>
       </c>
       <c r="F13" t="n">
-        <v>0.835</v>
+        <v>0.837</v>
       </c>
       <c r="G13" t="n">
-        <v>0.878</v>
+        <v>0.88</v>
       </c>
       <c r="H13" t="n">
-        <v>0.117</v>
+        <v>0.115</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0842</v>
+        <v>0.0828</v>
       </c>
       <c r="J13" t="n">
         <v>0.0243</v>
@@ -983,22 +983,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.0295</v>
+        <v>0.0334</v>
       </c>
       <c r="F14" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="G14" t="n">
-        <v>0.823</v>
+        <v>0.824</v>
       </c>
       <c r="H14" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="I14" t="n">
         <v>0.165</v>
       </c>
       <c r="J14" t="n">
-        <v>0.07375</v>
+        <v>0.08349999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.0266</v>
+        <v>0.0307</v>
       </c>
       <c r="F15" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="G15" t="n">
-        <v>0.823</v>
+        <v>0.824</v>
       </c>
       <c r="H15" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="I15" t="n">
         <v>0.165</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0665</v>
+        <v>0.07675</v>
       </c>
     </row>
     <row r="16">
@@ -1063,22 +1063,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.171</v>
+        <v>0.206</v>
       </c>
       <c r="F16" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="I16" t="n">
         <v>0.175</v>
       </c>
       <c r="J16" t="n">
-        <v>0.285</v>
+        <v>0.305</v>
       </c>
     </row>
     <row r="17">
@@ -1103,22 +1103,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.14</v>
+        <v>0.214</v>
       </c>
       <c r="F17" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="I17" t="n">
         <v>0.175</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2333333333333334</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="18">
@@ -1143,22 +1143,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.232</v>
+        <v>0.244</v>
       </c>
       <c r="F18" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="I18" t="n">
         <v>0.175</v>
       </c>
       <c r="J18" t="n">
-        <v>0.29</v>
+        <v>0.305</v>
       </c>
     </row>
     <row r="19">
@@ -1186,19 +1186,19 @@
         <v>0.272</v>
       </c>
       <c r="F19" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="I19" t="n">
         <v>0.175</v>
       </c>
       <c r="J19" t="n">
-        <v>0.339</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="20">
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.36</v>
+        <v>0.374</v>
       </c>
       <c r="F20" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="I20" t="n">
         <v>0.19</v>
       </c>
       <c r="J20" t="n">
-        <v>0.36</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="21">
@@ -1263,22 +1263,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.339</v>
+        <v>0.352</v>
       </c>
       <c r="F21" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="I21" t="n">
         <v>0.19</v>
       </c>
       <c r="J21" t="n">
-        <v>0.339</v>
+        <v>0.352</v>
       </c>
     </row>
     <row r="22">
@@ -1303,22 +1303,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.0144</v>
+        <v>0.0142</v>
       </c>
       <c r="F22" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="G22" t="n">
-        <v>0.851</v>
+        <v>0.853</v>
       </c>
       <c r="H22" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0931</v>
+        <v>0.0919</v>
       </c>
       <c r="J22" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07100000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1343,22 +1343,22 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.00186</v>
+        <v>0.00188</v>
       </c>
       <c r="F23" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="G23" t="n">
-        <v>0.851</v>
+        <v>0.853</v>
       </c>
       <c r="H23" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0931</v>
+        <v>0.0919</v>
       </c>
       <c r="J23" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.0094</v>
       </c>
     </row>
     <row r="24">
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.651</v>
+        <v>0.639</v>
       </c>
       <c r="F26" t="n">
         <v>0.864</v>
       </c>
       <c r="G26" t="n">
-        <v>0.845</v>
+        <v>0.844</v>
       </c>
       <c r="H26" t="n">
         <v>0.163</v>
@@ -1509,7 +1509,7 @@
         <v>0.864</v>
       </c>
       <c r="G27" t="n">
-        <v>0.845</v>
+        <v>0.844</v>
       </c>
       <c r="H27" t="n">
         <v>0.163</v>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.161</v>
+        <v>0.156</v>
       </c>
       <c r="F28" t="n">
         <v>0.864</v>
@@ -1558,7 +1558,7 @@
         <v>0.185</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4025</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="29">
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.746</v>
+        <v>0.73</v>
       </c>
       <c r="F30" t="n">
         <v>0.864</v>
@@ -1635,7 +1635,7 @@
         <v>0.163</v>
       </c>
       <c r="I30" t="n">
-        <v>0.107</v>
+        <v>0.106</v>
       </c>
       <c r="J30" t="n">
         <v>0.858</v>
@@ -1675,7 +1675,7 @@
         <v>0.163</v>
       </c>
       <c r="I31" t="n">
-        <v>0.107</v>
+        <v>0.106</v>
       </c>
       <c r="J31" t="n">
         <v>0.4600000000000001</v>
@@ -1718,7 +1718,7 @@
         <v>0.0584</v>
       </c>
       <c r="J32" t="n">
-        <v>0.4025</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="33">
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.414</v>
+        <v>0.461</v>
       </c>
       <c r="F36" t="n">
         <v>0.793</v>
@@ -1878,7 +1878,7 @@
         <v>0.195</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8859999999999999</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="37">
@@ -1918,7 +1918,7 @@
         <v>0.195</v>
       </c>
       <c r="J37" t="n">
-        <v>0.744</v>
+        <v>0.669</v>
       </c>
     </row>
     <row r="38">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.886</v>
+        <v>0.946</v>
       </c>
       <c r="F38" t="n">
         <v>0.793</v>
       </c>
       <c r="G38" t="n">
-        <v>0.795</v>
+        <v>0.794</v>
       </c>
       <c r="H38" t="n">
         <v>0.205</v>
       </c>
       <c r="I38" t="n">
-        <v>0.183</v>
+        <v>0.182</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8859999999999999</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="39">
@@ -1983,22 +1983,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.744</v>
+        <v>0.669</v>
       </c>
       <c r="F39" t="n">
         <v>0.793</v>
       </c>
       <c r="G39" t="n">
-        <v>0.795</v>
+        <v>0.794</v>
       </c>
       <c r="H39" t="n">
         <v>0.205</v>
       </c>
       <c r="I39" t="n">
-        <v>0.183</v>
+        <v>0.182</v>
       </c>
       <c r="J39" t="n">
-        <v>0.744</v>
+        <v>0.669</v>
       </c>
     </row>
     <row r="40">
@@ -2023,22 +2023,22 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.736</v>
+        <v>0.767</v>
       </c>
       <c r="F40" t="n">
         <v>0.793</v>
       </c>
       <c r="G40" t="n">
-        <v>0.798</v>
+        <v>0.797</v>
       </c>
       <c r="H40" t="n">
         <v>0.205</v>
       </c>
       <c r="I40" t="n">
-        <v>0.189</v>
+        <v>0.188</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8859999999999999</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="41">
@@ -2069,16 +2069,16 @@
         <v>0.793</v>
       </c>
       <c r="G41" t="n">
-        <v>0.798</v>
+        <v>0.797</v>
       </c>
       <c r="H41" t="n">
         <v>0.205</v>
       </c>
       <c r="I41" t="n">
-        <v>0.189</v>
+        <v>0.188</v>
       </c>
       <c r="J41" t="n">
-        <v>0.744</v>
+        <v>0.669</v>
       </c>
     </row>
     <row r="42">
@@ -2103,13 +2103,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.734</v>
+        <v>0.761</v>
       </c>
       <c r="F42" t="n">
         <v>0.793</v>
       </c>
       <c r="G42" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="H42" t="n">
         <v>0.205</v>
@@ -2118,7 +2118,7 @@
         <v>0.195</v>
       </c>
       <c r="J42" t="n">
-        <v>0.8859999999999999</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="43">
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.597</v>
+        <v>0.495</v>
       </c>
       <c r="F43" t="n">
         <v>0.793</v>
       </c>
       <c r="G43" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="H43" t="n">
         <v>0.205</v>
@@ -2158,7 +2158,7 @@
         <v>0.195</v>
       </c>
       <c r="J43" t="n">
-        <v>0.744</v>
+        <v>0.669</v>
       </c>
     </row>
     <row r="44">
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.000894</v>
+        <v>0.0009</v>
       </c>
       <c r="F44" t="n">
         <v>0.793</v>
@@ -2198,7 +2198,7 @@
         <v>0.0954</v>
       </c>
       <c r="J44" t="n">
-        <v>0.00447</v>
+        <v>0.0045</v>
       </c>
     </row>
     <row r="45">
@@ -2263,22 +2263,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.27</v>
+        <v>0.274</v>
       </c>
       <c r="F46" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="G46" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="H46" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I46" t="n">
         <v>0.186</v>
       </c>
       <c r="J46" t="n">
-        <v>0.45</v>
+        <v>0.4566666666666667</v>
       </c>
     </row>
     <row r="47">
@@ -2306,13 +2306,13 @@
         <v>0.124</v>
       </c>
       <c r="F47" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="G47" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="H47" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I47" t="n">
         <v>0.186</v>
@@ -2343,22 +2343,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.592</v>
+        <v>0.612</v>
       </c>
       <c r="F48" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="G48" t="n">
-        <v>0.778</v>
+        <v>0.779</v>
       </c>
       <c r="H48" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I48" t="n">
-        <v>0.149</v>
+        <v>0.15</v>
       </c>
       <c r="J48" t="n">
-        <v>0.592</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="49">
@@ -2386,16 +2386,16 @@
         <v>0.649</v>
       </c>
       <c r="F49" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="G49" t="n">
-        <v>0.778</v>
+        <v>0.779</v>
       </c>
       <c r="H49" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I49" t="n">
-        <v>0.149</v>
+        <v>0.15</v>
       </c>
       <c r="J49" t="n">
         <v>0.649</v>
@@ -2423,22 +2423,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="F50" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="G50" t="n">
-        <v>0.787</v>
+        <v>0.789</v>
       </c>
       <c r="H50" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I50" t="n">
         <v>0.148</v>
       </c>
       <c r="J50" t="n">
-        <v>0.5575</v>
+        <v>0.55625</v>
       </c>
     </row>
     <row r="51">
@@ -2466,13 +2466,13 @@
         <v>0.433</v>
       </c>
       <c r="F51" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="G51" t="n">
-        <v>0.787</v>
+        <v>0.789</v>
       </c>
       <c r="H51" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I51" t="n">
         <v>0.148</v>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.133</v>
+        <v>0.136</v>
       </c>
       <c r="F52" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="G52" t="n">
-        <v>0.801</v>
+        <v>0.802</v>
       </c>
       <c r="H52" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I52" t="n">
-        <v>0.144</v>
+        <v>0.143</v>
       </c>
       <c r="J52" t="n">
-        <v>0.3325</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="53">
@@ -2543,19 +2543,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.118</v>
+        <v>0.112</v>
       </c>
       <c r="F53" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="G53" t="n">
-        <v>0.801</v>
+        <v>0.802</v>
       </c>
       <c r="H53" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I53" t="n">
-        <v>0.144</v>
+        <v>0.143</v>
       </c>
       <c r="J53" t="n">
         <v>0.2066666666666667</v>
@@ -2583,22 +2583,22 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.0102</v>
+        <v>0.00993</v>
       </c>
       <c r="F54" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="G54" t="n">
-        <v>0.842</v>
+        <v>0.845</v>
       </c>
       <c r="H54" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I54" t="n">
         <v>0.137</v>
       </c>
       <c r="J54" t="n">
-        <v>0.051</v>
+        <v>0.04965</v>
       </c>
     </row>
     <row r="55">
@@ -2626,13 +2626,13 @@
         <v>0.011</v>
       </c>
       <c r="F55" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="G55" t="n">
-        <v>0.842</v>
+        <v>0.845</v>
       </c>
       <c r="H55" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I55" t="n">
         <v>0.137</v>
@@ -2663,22 +2663,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="F56" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="G56" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I56" t="n">
         <v>0.185</v>
       </c>
       <c r="J56" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="57">
@@ -2706,13 +2706,13 @@
         <v>0.112</v>
       </c>
       <c r="F57" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="G57" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I57" t="n">
         <v>0.185</v>
@@ -2743,22 +2743,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.0199</v>
+        <v>0.0216</v>
       </c>
       <c r="F58" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="G58" t="n">
-        <v>0.805</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H58" t="n">
         <v>0.185</v>
       </c>
       <c r="I58" t="n">
-        <v>0.18</v>
+        <v>0.181</v>
       </c>
       <c r="J58" t="n">
-        <v>0.024875</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="59">
@@ -2786,16 +2786,16 @@
         <v>0.0303</v>
       </c>
       <c r="F59" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="G59" t="n">
-        <v>0.805</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H59" t="n">
         <v>0.185</v>
       </c>
       <c r="I59" t="n">
-        <v>0.18</v>
+        <v>0.181</v>
       </c>
       <c r="J59" t="n">
         <v>0.037875</v>
@@ -2823,13 +2823,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.00389</v>
+        <v>0.00441</v>
       </c>
       <c r="F60" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="H60" t="n">
         <v>0.185</v>
@@ -2838,7 +2838,7 @@
         <v>0.16</v>
       </c>
       <c r="J60" t="n">
-        <v>0.01945</v>
+        <v>0.02205</v>
       </c>
     </row>
     <row r="61">
@@ -2866,10 +2866,10 @@
         <v>0.00521</v>
       </c>
       <c r="F61" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="G61" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="H61" t="n">
         <v>0.185</v>
@@ -2903,22 +2903,22 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.0163</v>
+        <v>0.017</v>
       </c>
       <c r="F62" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="G62" t="n">
-        <v>0.806</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="H62" t="n">
         <v>0.185</v>
       </c>
       <c r="I62" t="n">
-        <v>0.155</v>
+        <v>0.156</v>
       </c>
       <c r="J62" t="n">
-        <v>0.024875</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="63">
@@ -2946,16 +2946,16 @@
         <v>0.0199</v>
       </c>
       <c r="F63" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="G63" t="n">
-        <v>0.806</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="H63" t="n">
         <v>0.185</v>
       </c>
       <c r="I63" t="n">
-        <v>0.155</v>
+        <v>0.156</v>
       </c>
       <c r="J63" t="n">
         <v>0.03316666666666667</v>
@@ -2983,13 +2983,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.0117</v>
+        <v>0.0124</v>
       </c>
       <c r="F64" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="G64" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H64" t="n">
         <v>0.185</v>
@@ -2998,7 +2998,7 @@
         <v>0.162</v>
       </c>
       <c r="J64" t="n">
-        <v>0.024875</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="65">
@@ -3026,10 +3026,10 @@
         <v>0.00763</v>
       </c>
       <c r="F65" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="G65" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H65" t="n">
         <v>0.185</v>
@@ -3063,22 +3063,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="F66" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="G66" t="n">
-        <v>0.703</v>
+        <v>0.706</v>
       </c>
       <c r="H66" t="n">
         <v>0.185</v>
       </c>
       <c r="I66" t="n">
-        <v>0.163</v>
+        <v>0.164</v>
       </c>
       <c r="J66" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="67">
@@ -3103,22 +3103,22 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.156</v>
+        <v>0.14</v>
       </c>
       <c r="F67" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="G67" t="n">
-        <v>0.703</v>
+        <v>0.706</v>
       </c>
       <c r="H67" t="n">
         <v>0.185</v>
       </c>
       <c r="I67" t="n">
-        <v>0.163</v>
+        <v>0.164</v>
       </c>
       <c r="J67" t="n">
-        <v>0.156</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="68">
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.571</v>
       </c>
       <c r="F68" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="G68" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H68" t="n">
         <v>0.132</v>
@@ -3158,7 +3158,7 @@
         <v>0.139</v>
       </c>
       <c r="J68" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7887500000000001</v>
       </c>
     </row>
     <row r="69">
@@ -3186,10 +3186,10 @@
         <v>0.404</v>
       </c>
       <c r="F69" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="G69" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H69" t="n">
         <v>0.132</v>
@@ -3198,7 +3198,7 @@
         <v>0.139</v>
       </c>
       <c r="J69" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.7116666666666666</v>
       </c>
     </row>
     <row r="70">
@@ -3223,13 +3223,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.848</v>
+        <v>0.88</v>
       </c>
       <c r="F70" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="G70" t="n">
-        <v>0.802</v>
+        <v>0.803</v>
       </c>
       <c r="H70" t="n">
         <v>0.132</v>
@@ -3238,7 +3238,7 @@
         <v>0.116</v>
       </c>
       <c r="J70" t="n">
-        <v>0.8480000000000001</v>
+        <v>0.8800000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -3263,13 +3263,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="F71" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="G71" t="n">
-        <v>0.802</v>
+        <v>0.803</v>
       </c>
       <c r="H71" t="n">
         <v>0.132</v>
@@ -3278,7 +3278,7 @@
         <v>0.116</v>
       </c>
       <c r="J71" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="72">
@@ -3303,13 +3303,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.648</v>
+        <v>0.631</v>
       </c>
       <c r="F72" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="G72" t="n">
-        <v>0.786</v>
+        <v>0.787</v>
       </c>
       <c r="H72" t="n">
         <v>0.132</v>
@@ -3318,7 +3318,7 @@
         <v>0.152</v>
       </c>
       <c r="J72" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7887500000000001</v>
       </c>
     </row>
     <row r="73">
@@ -3343,13 +3343,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.65</v>
+        <v>0.609</v>
       </c>
       <c r="F73" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="G73" t="n">
-        <v>0.786</v>
+        <v>0.787</v>
       </c>
       <c r="H73" t="n">
         <v>0.132</v>
@@ -3358,7 +3358,7 @@
         <v>0.152</v>
       </c>
       <c r="J73" t="n">
-        <v>0.8125</v>
+        <v>0.76125</v>
       </c>
     </row>
     <row r="74">
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.349</v>
+        <v>0.368</v>
       </c>
       <c r="F74" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="G74" t="n">
         <v>0.821</v>
@@ -3398,7 +3398,7 @@
         <v>0.107</v>
       </c>
       <c r="J74" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7887500000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.394</v>
+        <v>0.427</v>
       </c>
       <c r="F75" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="G75" t="n">
         <v>0.821</v>
@@ -3438,7 +3438,7 @@
         <v>0.107</v>
       </c>
       <c r="J75" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.7116666666666666</v>
       </c>
     </row>
     <row r="76">
@@ -3463,22 +3463,22 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.00322</v>
+        <v>0.00321</v>
       </c>
       <c r="F76" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="G76" t="n">
-        <v>0.874</v>
+        <v>0.875</v>
       </c>
       <c r="H76" t="n">
         <v>0.132</v>
       </c>
       <c r="I76" t="n">
-        <v>0.0919</v>
+        <v>0.092</v>
       </c>
       <c r="J76" t="n">
-        <v>0.0161</v>
+        <v>0.01605</v>
       </c>
     </row>
     <row r="77">
@@ -3506,16 +3506,16 @@
         <v>0.00286</v>
       </c>
       <c r="F77" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="G77" t="n">
-        <v>0.874</v>
+        <v>0.875</v>
       </c>
       <c r="H77" t="n">
         <v>0.132</v>
       </c>
       <c r="I77" t="n">
-        <v>0.0919</v>
+        <v>0.092</v>
       </c>
       <c r="J77" t="n">
         <v>0.0143</v>
@@ -3543,22 +3543,22 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.193</v>
+        <v>0.195</v>
       </c>
       <c r="F78" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="G78" t="n">
-        <v>0.83</v>
+        <v>0.832</v>
       </c>
       <c r="H78" t="n">
         <v>0.132</v>
       </c>
       <c r="I78" t="n">
-        <v>0.149</v>
+        <v>0.15</v>
       </c>
       <c r="J78" t="n">
-        <v>0.193</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="79">
@@ -3586,16 +3586,16 @@
         <v>0.0577</v>
       </c>
       <c r="F79" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="G79" t="n">
-        <v>0.83</v>
+        <v>0.832</v>
       </c>
       <c r="H79" t="n">
         <v>0.132</v>
       </c>
       <c r="I79" t="n">
-        <v>0.149</v>
+        <v>0.15</v>
       </c>
       <c r="J79" t="n">
         <v>0.0577</v>
@@ -3623,22 +3623,22 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.0138</v>
+        <v>0.0157</v>
       </c>
       <c r="F80" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="G80" t="n">
         <v>0.789</v>
       </c>
       <c r="H80" t="n">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
       <c r="I80" t="n">
-        <v>0.18</v>
+        <v>0.181</v>
       </c>
       <c r="J80" t="n">
-        <v>0.037</v>
+        <v>0.03924999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -3666,16 +3666,16 @@
         <v>0.011</v>
       </c>
       <c r="F81" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="G81" t="n">
         <v>0.789</v>
       </c>
       <c r="H81" t="n">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
       <c r="I81" t="n">
-        <v>0.18</v>
+        <v>0.181</v>
       </c>
       <c r="J81" t="n">
         <v>0.0275</v>
@@ -3703,22 +3703,22 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.0222</v>
+        <v>0.0273</v>
       </c>
       <c r="F82" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="G82" t="n">
         <v>0.792</v>
       </c>
       <c r="H82" t="n">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
       <c r="I82" t="n">
-        <v>0.159</v>
+        <v>0.16</v>
       </c>
       <c r="J82" t="n">
-        <v>0.037</v>
+        <v>0.04550000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3743,19 +3743,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.0386</v>
+        <v>0.0507</v>
       </c>
       <c r="F83" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="G83" t="n">
         <v>0.792</v>
       </c>
       <c r="H83" t="n">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
       <c r="I83" t="n">
-        <v>0.159</v>
+        <v>0.16</v>
       </c>
       <c r="J83" t="n">
         <v>0.05769999999999999</v>
@@ -3783,22 +3783,22 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.0384</v>
+        <v>0.0409</v>
       </c>
       <c r="F84" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="G84" t="n">
-        <v>0.788</v>
+        <v>0.789</v>
       </c>
       <c r="H84" t="n">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
       <c r="I84" t="n">
         <v>0.161</v>
       </c>
       <c r="J84" t="n">
-        <v>0.0427</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="85">
@@ -3826,13 +3826,13 @@
         <v>0.0577</v>
       </c>
       <c r="F85" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="G85" t="n">
-        <v>0.788</v>
+        <v>0.789</v>
       </c>
       <c r="H85" t="n">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
       <c r="I85" t="n">
         <v>0.161</v>
@@ -3863,22 +3863,22 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.0427</v>
+        <v>0.0458</v>
       </c>
       <c r="F86" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="G86" t="n">
-        <v>0.792</v>
+        <v>0.793</v>
       </c>
       <c r="H86" t="n">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
       <c r="I86" t="n">
         <v>0.169</v>
       </c>
       <c r="J86" t="n">
-        <v>0.0427</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="87">
@@ -3903,16 +3903,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.0507</v>
+        <v>0.0577</v>
       </c>
       <c r="F87" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="G87" t="n">
-        <v>0.792</v>
+        <v>0.793</v>
       </c>
       <c r="H87" t="n">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
       <c r="I87" t="n">
         <v>0.169</v>
@@ -3943,22 +3943,22 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.0151</v>
+        <v>0.0141</v>
       </c>
       <c r="F88" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="G88" t="n">
-        <v>0.789</v>
+        <v>0.791</v>
       </c>
       <c r="H88" t="n">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
       <c r="I88" t="n">
         <v>0.137</v>
       </c>
       <c r="J88" t="n">
-        <v>0.037</v>
+        <v>0.03924999999999999</v>
       </c>
     </row>
     <row r="89">
@@ -3986,13 +3986,13 @@
         <v>0.0076</v>
       </c>
       <c r="F89" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="G89" t="n">
-        <v>0.789</v>
+        <v>0.791</v>
       </c>
       <c r="H89" t="n">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
       <c r="I89" t="n">
         <v>0.137</v>
@@ -4235,13 +4235,13 @@
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="G6" t="n">
-        <v>0.873</v>
+        <v>0.88</v>
       </c>
       <c r="H6" t="n">
-        <v>0.262</v>
+        <v>0.253</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -4272,16 +4272,16 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.793</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.88</v>
+        <v>0.893</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0601</v>
+        <v>0.0717</v>
       </c>
       <c r="I7" t="n">
-        <v>0.165</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="8">
@@ -4383,16 +4383,16 @@
         <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>0.66</v>
+        <v>0.667</v>
       </c>
       <c r="G10" t="n">
-        <v>0.633</v>
+        <v>0.64</v>
       </c>
       <c r="H10" t="n">
-        <v>0.717</v>
+        <v>0.716</v>
       </c>
       <c r="I10" t="n">
-        <v>0.717</v>
+        <v>0.716</v>
       </c>
     </row>
     <row r="11">
@@ -4864,16 +4864,16 @@
         <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="G23" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>0.469</v>
+        <v>0.466</v>
       </c>
       <c r="I23" t="n">
-        <v>0.86</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="24">
@@ -5419,13 +5419,13 @@
         <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G38" t="n">
-        <v>0.822</v>
+        <v>0.83</v>
       </c>
       <c r="H38" t="n">
-        <v>0.386</v>
+        <v>0.377</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
@@ -5456,16 +5456,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="G39" t="n">
-        <v>0.859</v>
+        <v>0.878</v>
       </c>
       <c r="H39" t="n">
-        <v>0.007939999999999999</v>
+        <v>0.0092</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0175</v>
+        <v>0.0202</v>
       </c>
     </row>
     <row r="40">
@@ -5567,16 +5567,16 @@
         <v>9</v>
       </c>
       <c r="F42" t="n">
-        <v>0.603</v>
+        <v>0.608</v>
       </c>
       <c r="G42" t="n">
-        <v>0.579</v>
+        <v>0.584</v>
       </c>
       <c r="H42" t="n">
-        <v>0.798</v>
+        <v>0.797</v>
       </c>
       <c r="I42" t="n">
-        <v>0.798</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="43">
@@ -5650,7 +5650,7 @@
         <v>0.358</v>
       </c>
       <c r="I44" t="n">
-        <v>0.649</v>
+        <v>0.656</v>
       </c>
     </row>
     <row r="45">
@@ -6011,16 +6011,16 @@
         <v>5</v>
       </c>
       <c r="F54" t="n">
-        <v>0.851</v>
+        <v>0.856</v>
       </c>
       <c r="G54" t="n">
-        <v>0.897</v>
+        <v>0.902</v>
       </c>
       <c r="H54" t="n">
-        <v>0.208</v>
+        <v>0.199</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="55">
@@ -6048,16 +6048,16 @@
         <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>0.803</v>
+        <v>0.821</v>
       </c>
       <c r="G55" t="n">
-        <v>0.898</v>
+        <v>0.908</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0195</v>
+        <v>0.0231</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0495</v>
+        <v>0.0834</v>
       </c>
     </row>
     <row r="56">
@@ -6159,16 +6159,16 @@
         <v>9</v>
       </c>
       <c r="F58" t="n">
-        <v>0.749</v>
+        <v>0.752</v>
       </c>
       <c r="G58" t="n">
-        <v>0.726</v>
+        <v>0.73</v>
       </c>
       <c r="H58" t="n">
-        <v>0.652</v>
+        <v>0.649</v>
       </c>
       <c r="I58" t="n">
-        <v>0.652</v>
+        <v>0.649</v>
       </c>
     </row>
     <row r="59">
@@ -6603,13 +6603,13 @@
         <v>5</v>
       </c>
       <c r="F70" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="G70" t="n">
-        <v>0.84</v>
+        <v>0.847</v>
       </c>
       <c r="H70" t="n">
-        <v>0.759</v>
+        <v>0.755</v>
       </c>
       <c r="I70" t="n">
         <v>1</v>
@@ -6640,16 +6640,16 @@
         <v>6</v>
       </c>
       <c r="F71" t="n">
-        <v>0.793</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G71" t="n">
         <v>0.887</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0398</v>
+        <v>0.105</v>
       </c>
       <c r="I71" t="n">
-        <v>0.146</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="72">
@@ -6751,16 +6751,16 @@
         <v>9</v>
       </c>
       <c r="F74" t="n">
-        <v>0.66</v>
+        <v>0.667</v>
       </c>
       <c r="G74" t="n">
-        <v>0.713</v>
+        <v>0.72</v>
       </c>
       <c r="H74" t="n">
-        <v>0.384</v>
+        <v>0.381</v>
       </c>
       <c r="I74" t="n">
-        <v>0.469</v>
+        <v>0.466</v>
       </c>
     </row>
     <row r="75">
@@ -7232,16 +7232,16 @@
         <v>6</v>
       </c>
       <c r="F87" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="G87" t="n">
-        <v>0.921</v>
+        <v>0.91</v>
       </c>
       <c r="H87" t="n">
-        <v>0.304</v>
+        <v>0.191</v>
       </c>
       <c r="I87" t="n">
-        <v>0.836</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="88">
@@ -7787,13 +7787,13 @@
         <v>5</v>
       </c>
       <c r="F102" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G102" t="n">
-        <v>0.782</v>
+        <v>0.79</v>
       </c>
       <c r="H102" t="n">
-        <v>0.867</v>
+        <v>0.865</v>
       </c>
       <c r="I102" t="n">
         <v>1</v>
@@ -7824,16 +7824,16 @@
         <v>6</v>
       </c>
       <c r="F103" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="G103" t="n">
-        <v>0.891</v>
+        <v>0.9</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0009940000000000001</v>
+        <v>0.00225</v>
       </c>
       <c r="I103" t="n">
-        <v>0.00364</v>
+        <v>0.00825</v>
       </c>
     </row>
     <row r="104">
@@ -7935,16 +7935,16 @@
         <v>9</v>
       </c>
       <c r="F106" t="n">
-        <v>0.603</v>
+        <v>0.608</v>
       </c>
       <c r="G106" t="n">
-        <v>0.675</v>
+        <v>0.68</v>
       </c>
       <c r="H106" t="n">
-        <v>0.294</v>
+        <v>0.291</v>
       </c>
       <c r="I106" t="n">
-        <v>0.359</v>
+        <v>0.356</v>
       </c>
     </row>
     <row r="107">
@@ -8379,16 +8379,16 @@
         <v>5</v>
       </c>
       <c r="F118" t="n">
-        <v>0.851</v>
+        <v>0.856</v>
       </c>
       <c r="G118" t="n">
-        <v>0.868</v>
+        <v>0.873</v>
       </c>
       <c r="H118" t="n">
-        <v>0.653</v>
+        <v>0.648</v>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="119">
@@ -8416,16 +8416,16 @@
         <v>6</v>
       </c>
       <c r="F119" t="n">
-        <v>0.803</v>
+        <v>0.821</v>
       </c>
       <c r="G119" t="n">
-        <v>0.906</v>
+        <v>0.905</v>
       </c>
       <c r="H119" t="n">
-        <v>0.00775</v>
+        <v>0.0254</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0296</v>
+        <v>0.0834</v>
       </c>
     </row>
     <row r="120">
@@ -8527,16 +8527,16 @@
         <v>9</v>
       </c>
       <c r="F122" t="n">
-        <v>0.749</v>
+        <v>0.752</v>
       </c>
       <c r="G122" t="n">
-        <v>0.798</v>
+        <v>0.802</v>
       </c>
       <c r="H122" t="n">
-        <v>0.243</v>
+        <v>0.239</v>
       </c>
       <c r="I122" t="n">
-        <v>0.297</v>
+        <v>0.292</v>
       </c>
     </row>
     <row r="123">
@@ -8971,13 +8971,13 @@
         <v>5</v>
       </c>
       <c r="F134" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="G134" t="n">
-        <v>0.767</v>
+        <v>0.773</v>
       </c>
       <c r="H134" t="n">
-        <v>0.318</v>
+        <v>0.312</v>
       </c>
       <c r="I134" t="n">
         <v>1</v>
@@ -9008,16 +9008,16 @@
         <v>6</v>
       </c>
       <c r="F135" t="n">
-        <v>0.793</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G135" t="n">
-        <v>0.853</v>
+        <v>0.86</v>
       </c>
       <c r="H135" t="n">
-        <v>0.226</v>
+        <v>0.349</v>
       </c>
       <c r="I135" t="n">
-        <v>0.255</v>
+        <v>0.393</v>
       </c>
     </row>
     <row r="136">
@@ -9119,16 +9119,16 @@
         <v>9</v>
       </c>
       <c r="F138" t="n">
-        <v>0.66</v>
+        <v>0.667</v>
       </c>
       <c r="G138" t="n">
-        <v>0.747</v>
+        <v>0.76</v>
       </c>
       <c r="H138" t="n">
-        <v>0.129</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="I138" t="n">
-        <v>0.203</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="139">
@@ -9600,16 +9600,16 @@
         <v>6</v>
       </c>
       <c r="F151" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="G151" t="n">
-        <v>0.907</v>
+        <v>0.897</v>
       </c>
       <c r="H151" t="n">
-        <v>0.189</v>
+        <v>0.116</v>
       </c>
       <c r="I151" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.425</v>
       </c>
     </row>
     <row r="152">
@@ -9714,13 +9714,13 @@
         <v>0.987</v>
       </c>
       <c r="G154" t="n">
-        <v>0.923</v>
+        <v>0.924</v>
       </c>
       <c r="H154" t="n">
-        <v>0.0805</v>
+        <v>0.0809</v>
       </c>
       <c r="I154" t="n">
-        <v>0.535</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="155">
@@ -10155,13 +10155,13 @@
         <v>5</v>
       </c>
       <c r="F166" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G166" t="n">
-        <v>0.733</v>
+        <v>0.74</v>
       </c>
       <c r="H166" t="n">
-        <v>0.746</v>
+        <v>0.743</v>
       </c>
       <c r="I166" t="n">
         <v>1</v>
@@ -10192,16 +10192,16 @@
         <v>6</v>
       </c>
       <c r="F167" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="G167" t="n">
-        <v>0.848</v>
+        <v>0.867</v>
       </c>
       <c r="H167" t="n">
-        <v>0.0141</v>
+        <v>0.0168</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0258</v>
+        <v>0.0308</v>
       </c>
     </row>
     <row r="168">
@@ -10303,16 +10303,16 @@
         <v>9</v>
       </c>
       <c r="F170" t="n">
-        <v>0.603</v>
+        <v>0.608</v>
       </c>
       <c r="G170" t="n">
-        <v>0.762</v>
+        <v>0.776</v>
       </c>
       <c r="H170" t="n">
-        <v>0.00991</v>
+        <v>0.00596</v>
       </c>
       <c r="I170" t="n">
-        <v>0.0182</v>
+        <v>0.0131</v>
       </c>
     </row>
     <row r="171">
@@ -10747,16 +10747,16 @@
         <v>5</v>
       </c>
       <c r="F182" t="n">
-        <v>0.851</v>
+        <v>0.856</v>
       </c>
       <c r="G182" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H182" t="n">
-        <v>0.33</v>
+        <v>0.323</v>
       </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="183">
@@ -10784,16 +10784,16 @@
         <v>6</v>
       </c>
       <c r="F183" t="n">
-        <v>0.803</v>
+        <v>0.821</v>
       </c>
       <c r="G183" t="n">
-        <v>0.876</v>
+        <v>0.881</v>
       </c>
       <c r="H183" t="n">
-        <v>0.0726</v>
+        <v>0.124</v>
       </c>
       <c r="I183" t="n">
-        <v>0.117</v>
+        <v>0.196</v>
       </c>
     </row>
     <row r="184">
@@ -10895,16 +10895,16 @@
         <v>9</v>
       </c>
       <c r="F186" t="n">
-        <v>0.749</v>
+        <v>0.752</v>
       </c>
       <c r="G186" t="n">
-        <v>0.835</v>
+        <v>0.843</v>
       </c>
       <c r="H186" t="n">
-        <v>0.0319</v>
+        <v>0.0216</v>
       </c>
       <c r="I186" t="n">
-        <v>0.0585</v>
+        <v>0.0413</v>
       </c>
     </row>
     <row r="187">
@@ -11339,10 +11339,10 @@
         <v>5</v>
       </c>
       <c r="F198" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="G198" t="n">
-        <v>0.827</v>
+        <v>0.833</v>
       </c>
       <c r="H198" t="n">
         <v>1</v>
@@ -11376,16 +11376,16 @@
         <v>6</v>
       </c>
       <c r="F199" t="n">
-        <v>0.793</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G199" t="n">
         <v>0.887</v>
       </c>
       <c r="H199" t="n">
-        <v>0.0398</v>
+        <v>0.105</v>
       </c>
       <c r="I199" t="n">
-        <v>0.146</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="200">
@@ -11487,16 +11487,16 @@
         <v>9</v>
       </c>
       <c r="F202" t="n">
-        <v>0.66</v>
+        <v>0.667</v>
       </c>
       <c r="G202" t="n">
-        <v>0.747</v>
+        <v>0.753</v>
       </c>
       <c r="H202" t="n">
-        <v>0.129</v>
+        <v>0.127</v>
       </c>
       <c r="I202" t="n">
-        <v>0.203</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="203">
@@ -11968,16 +11968,16 @@
         <v>6</v>
       </c>
       <c r="F215" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="G215" t="n">
-        <v>0.931</v>
+        <v>0.92</v>
       </c>
       <c r="H215" t="n">
-        <v>0.467</v>
+        <v>0.301</v>
       </c>
       <c r="I215" t="n">
-        <v>0.86</v>
+        <v>0.662</v>
       </c>
     </row>
     <row r="216">
@@ -12523,10 +12523,10 @@
         <v>5</v>
       </c>
       <c r="F230" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G230" t="n">
-        <v>0.752</v>
+        <v>0.76</v>
       </c>
       <c r="H230" t="n">
         <v>1</v>
@@ -12560,16 +12560,16 @@
         <v>6</v>
       </c>
       <c r="F231" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="G231" t="n">
-        <v>0.88</v>
+        <v>0.889</v>
       </c>
       <c r="H231" t="n">
-        <v>0.00212</v>
+        <v>0.00472</v>
       </c>
       <c r="I231" t="n">
-        <v>0.00583</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="232">
@@ -12671,16 +12671,16 @@
         <v>9</v>
       </c>
       <c r="F234" t="n">
-        <v>0.603</v>
+        <v>0.608</v>
       </c>
       <c r="G234" t="n">
-        <v>0.714</v>
+        <v>0.72</v>
       </c>
       <c r="H234" t="n">
-        <v>0.0838</v>
+        <v>0.0814</v>
       </c>
       <c r="I234" t="n">
-        <v>0.115</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="235">
@@ -13115,10 +13115,10 @@
         <v>5</v>
       </c>
       <c r="F246" t="n">
-        <v>0.851</v>
+        <v>0.856</v>
       </c>
       <c r="G246" t="n">
-        <v>0.854</v>
+        <v>0.859</v>
       </c>
       <c r="H246" t="n">
         <v>1</v>
@@ -13152,16 +13152,16 @@
         <v>6</v>
       </c>
       <c r="F247" t="n">
-        <v>0.803</v>
+        <v>0.821</v>
       </c>
       <c r="G247" t="n">
-        <v>0.905</v>
+        <v>0.904</v>
       </c>
       <c r="H247" t="n">
-        <v>0.008059999999999999</v>
+        <v>0.036</v>
       </c>
       <c r="I247" t="n">
-        <v>0.0296</v>
+        <v>0.0834</v>
       </c>
     </row>
     <row r="248">
@@ -13263,16 +13263,16 @@
         <v>9</v>
       </c>
       <c r="F250" t="n">
-        <v>0.749</v>
+        <v>0.752</v>
       </c>
       <c r="G250" t="n">
-        <v>0.826</v>
+        <v>0.829</v>
       </c>
       <c r="H250" t="n">
-        <v>0.0568</v>
+        <v>0.0548</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0798</v>
+        <v>0.07539999999999999</v>
       </c>
     </row>
     <row r="251">
@@ -13707,10 +13707,10 @@
         <v>5</v>
       </c>
       <c r="F262" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="G262" t="n">
-        <v>0.827</v>
+        <v>0.833</v>
       </c>
       <c r="H262" t="n">
         <v>1</v>
@@ -13744,16 +13744,16 @@
         <v>6</v>
       </c>
       <c r="F263" t="n">
-        <v>0.793</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G263" t="n">
-        <v>0.907</v>
+        <v>0.92</v>
       </c>
       <c r="H263" t="n">
-        <v>0.00911</v>
+        <v>0.0102</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="264">
@@ -13855,16 +13855,16 @@
         <v>9</v>
       </c>
       <c r="F266" t="n">
-        <v>0.66</v>
+        <v>0.667</v>
       </c>
       <c r="G266" t="n">
-        <v>0.74</v>
+        <v>0.753</v>
       </c>
       <c r="H266" t="n">
-        <v>0.166</v>
+        <v>0.127</v>
       </c>
       <c r="I266" t="n">
-        <v>0.228</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="267">
@@ -14336,7 +14336,7 @@
         <v>6</v>
       </c>
       <c r="F279" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="G279" t="n">
         <v>0.9429999999999999</v>
@@ -14345,7 +14345,7 @@
         <v>0.699</v>
       </c>
       <c r="I279" t="n">
-        <v>0.961</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280">
@@ -14450,13 +14450,13 @@
         <v>0.987</v>
       </c>
       <c r="G282" t="n">
-        <v>0.948</v>
+        <v>0.949</v>
       </c>
       <c r="H282" t="n">
-        <v>0.229</v>
+        <v>0.231</v>
       </c>
       <c r="I282" t="n">
-        <v>0.535</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="283">
@@ -14891,10 +14891,10 @@
         <v>5</v>
       </c>
       <c r="F294" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G294" t="n">
-        <v>0.772</v>
+        <v>0.78</v>
       </c>
       <c r="H294" t="n">
         <v>1</v>
@@ -14928,16 +14928,16 @@
         <v>6</v>
       </c>
       <c r="F295" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="G295" t="n">
-        <v>0.902</v>
+        <v>0.922</v>
       </c>
       <c r="H295" t="n">
-        <v>0.000433</v>
+        <v>0.000399</v>
       </c>
       <c r="I295" t="n">
-        <v>0.00238</v>
+        <v>0.00219</v>
       </c>
     </row>
     <row r="296">
@@ -15039,16 +15039,16 @@
         <v>9</v>
       </c>
       <c r="F298" t="n">
-        <v>0.603</v>
+        <v>0.608</v>
       </c>
       <c r="G298" t="n">
-        <v>0.73</v>
+        <v>0.744</v>
       </c>
       <c r="H298" t="n">
-        <v>0.0447</v>
+        <v>0.0303</v>
       </c>
       <c r="I298" t="n">
-        <v>0.0702</v>
+        <v>0.0476</v>
       </c>
     </row>
     <row r="299">
@@ -15483,16 +15483,16 @@
         <v>5</v>
       </c>
       <c r="F310" t="n">
-        <v>0.851</v>
+        <v>0.856</v>
       </c>
       <c r="G310" t="n">
-        <v>0.857</v>
+        <v>0.862</v>
       </c>
       <c r="H310" t="n">
-        <v>0.883</v>
+        <v>0.881</v>
       </c>
       <c r="I310" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="311">
@@ -15520,16 +15520,16 @@
         <v>6</v>
       </c>
       <c r="F311" t="n">
-        <v>0.803</v>
+        <v>0.821</v>
       </c>
       <c r="G311" t="n">
-        <v>0.922</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H311" t="n">
-        <v>0.00202</v>
+        <v>0.00212</v>
       </c>
       <c r="I311" t="n">
-        <v>0.0222</v>
+        <v>0.0233</v>
       </c>
     </row>
     <row r="312">
@@ -15631,16 +15631,16 @@
         <v>9</v>
       </c>
       <c r="F314" t="n">
-        <v>0.749</v>
+        <v>0.752</v>
       </c>
       <c r="G314" t="n">
-        <v>0.825</v>
+        <v>0.834</v>
       </c>
       <c r="H314" t="n">
-        <v>0.058</v>
+        <v>0.0411</v>
       </c>
       <c r="I314" t="n">
-        <v>0.0798</v>
+        <v>0.0646</v>
       </c>
     </row>
     <row r="315">
@@ -16075,10 +16075,10 @@
         <v>5</v>
       </c>
       <c r="F326" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="G326" t="n">
-        <v>0.827</v>
+        <v>0.833</v>
       </c>
       <c r="H326" t="n">
         <v>1</v>
@@ -16112,16 +16112,16 @@
         <v>6</v>
       </c>
       <c r="F327" t="n">
-        <v>0.793</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G327" t="n">
-        <v>0.867</v>
+        <v>0.88</v>
       </c>
       <c r="H327" t="n">
-        <v>0.124</v>
+        <v>0.149</v>
       </c>
       <c r="I327" t="n">
-        <v>0.238</v>
+        <v>0.328</v>
       </c>
     </row>
     <row r="328">
@@ -16223,16 +16223,16 @@
         <v>9</v>
       </c>
       <c r="F330" t="n">
-        <v>0.66</v>
+        <v>0.667</v>
       </c>
       <c r="G330" t="n">
-        <v>0.773</v>
+        <v>0.787</v>
       </c>
       <c r="H330" t="n">
-        <v>0.04</v>
+        <v>0.0273</v>
       </c>
       <c r="I330" t="n">
-        <v>0.11</v>
+        <v>0.0751</v>
       </c>
     </row>
     <row r="331">
@@ -16704,16 +16704,16 @@
         <v>6</v>
       </c>
       <c r="F343" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="G343" t="n">
         <v>0.883</v>
       </c>
       <c r="H343" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="I343" t="n">
-        <v>0.441</v>
+        <v>0.425</v>
       </c>
     </row>
     <row r="344">
@@ -16821,10 +16821,10 @@
         <v>0.96</v>
       </c>
       <c r="H346" t="n">
-        <v>0.389</v>
+        <v>0.391</v>
       </c>
       <c r="I346" t="n">
-        <v>0.535</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="347">
@@ -17259,13 +17259,13 @@
         <v>5</v>
       </c>
       <c r="F358" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G358" t="n">
-        <v>0.792</v>
+        <v>0.8</v>
       </c>
       <c r="H358" t="n">
-        <v>0.735</v>
+        <v>0.731</v>
       </c>
       <c r="I358" t="n">
         <v>1</v>
@@ -17296,16 +17296,16 @@
         <v>6</v>
       </c>
       <c r="F359" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="G359" t="n">
-        <v>0.902</v>
+        <v>0.922</v>
       </c>
       <c r="H359" t="n">
-        <v>0.000433</v>
+        <v>0.000399</v>
       </c>
       <c r="I359" t="n">
-        <v>0.00238</v>
+        <v>0.00219</v>
       </c>
     </row>
     <row r="360">
@@ -17407,16 +17407,16 @@
         <v>9</v>
       </c>
       <c r="F362" t="n">
-        <v>0.603</v>
+        <v>0.608</v>
       </c>
       <c r="G362" t="n">
-        <v>0.762</v>
+        <v>0.776</v>
       </c>
       <c r="H362" t="n">
-        <v>0.00991</v>
+        <v>0.00596</v>
       </c>
       <c r="I362" t="n">
-        <v>0.0182</v>
+        <v>0.0131</v>
       </c>
     </row>
     <row r="363">
@@ -17851,16 +17851,16 @@
         <v>5</v>
       </c>
       <c r="F374" t="n">
-        <v>0.851</v>
+        <v>0.856</v>
       </c>
       <c r="G374" t="n">
-        <v>0.86</v>
+        <v>0.865</v>
       </c>
       <c r="H374" t="n">
-        <v>0.882</v>
+        <v>0.88</v>
       </c>
       <c r="I374" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="375">
@@ -17888,16 +17888,16 @@
         <v>6</v>
       </c>
       <c r="F375" t="n">
-        <v>0.803</v>
+        <v>0.821</v>
       </c>
       <c r="G375" t="n">
-        <v>0.892</v>
+        <v>0.902</v>
       </c>
       <c r="H375" t="n">
-        <v>0.0225</v>
+        <v>0.0379</v>
       </c>
       <c r="I375" t="n">
-        <v>0.0495</v>
+        <v>0.0834</v>
       </c>
     </row>
     <row r="376">
@@ -17999,16 +17999,16 @@
         <v>9</v>
       </c>
       <c r="F378" t="n">
-        <v>0.749</v>
+        <v>0.752</v>
       </c>
       <c r="G378" t="n">
-        <v>0.85</v>
+        <v>0.858</v>
       </c>
       <c r="H378" t="n">
-        <v>0.0107</v>
+        <v>0.00665</v>
       </c>
       <c r="I378" t="n">
-        <v>0.0294</v>
+        <v>0.0183</v>
       </c>
     </row>
     <row r="379">
@@ -18443,13 +18443,13 @@
         <v>5</v>
       </c>
       <c r="F390" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G390" t="n">
-        <v>0.827</v>
+        <v>0.833</v>
       </c>
       <c r="H390" t="n">
-        <v>0.766</v>
+        <v>0.762</v>
       </c>
       <c r="I390" t="n">
         <v>1</v>
@@ -18480,16 +18480,16 @@
         <v>6</v>
       </c>
       <c r="F391" t="n">
-        <v>0.787</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G391" t="n">
         <v>0.853</v>
       </c>
       <c r="H391" t="n">
-        <v>0.176</v>
+        <v>0.357</v>
       </c>
       <c r="I391" t="n">
-        <v>0.242</v>
+        <v>0.393</v>
       </c>
     </row>
     <row r="392">
@@ -18591,16 +18591,16 @@
         <v>9</v>
       </c>
       <c r="F394" t="n">
-        <v>0.66</v>
+        <v>0.667</v>
       </c>
       <c r="G394" t="n">
-        <v>0.753</v>
+        <v>0.76</v>
       </c>
       <c r="H394" t="n">
-        <v>0.099</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="I394" t="n">
-        <v>0.203</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="395">
@@ -19072,16 +19072,16 @@
         <v>6</v>
       </c>
       <c r="F407" t="n">
-        <v>0.875</v>
+        <v>0.877</v>
       </c>
       <c r="G407" t="n">
-        <v>0.898</v>
+        <v>0.886</v>
       </c>
       <c r="H407" t="n">
-        <v>0.8080000000000001</v>
+        <v>1</v>
       </c>
       <c r="I407" t="n">
-        <v>0.988</v>
+        <v>1</v>
       </c>
     </row>
     <row r="408">
@@ -19192,7 +19192,7 @@
         <v>0.238</v>
       </c>
       <c r="I410" t="n">
-        <v>0.535</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="411">
@@ -19627,13 +19627,13 @@
         <v>5</v>
       </c>
       <c r="F422" t="n">
-        <v>0.743</v>
+        <v>0.75</v>
       </c>
       <c r="G422" t="n">
-        <v>0.802</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H422" t="n">
-        <v>0.402</v>
+        <v>0.394</v>
       </c>
       <c r="I422" t="n">
         <v>1</v>
@@ -19664,16 +19664,16 @@
         <v>6</v>
       </c>
       <c r="F423" t="n">
-        <v>0.761</v>
+        <v>0.789</v>
       </c>
       <c r="G423" t="n">
-        <v>0.859</v>
+        <v>0.867</v>
       </c>
       <c r="H423" t="n">
-        <v>0.132</v>
+        <v>0.236</v>
       </c>
       <c r="I423" t="n">
-        <v>0.145</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="424">
@@ -19775,16 +19775,16 @@
         <v>9</v>
       </c>
       <c r="F426" t="n">
-        <v>0.619</v>
+        <v>0.624</v>
       </c>
       <c r="G426" t="n">
-        <v>0.778</v>
+        <v>0.784</v>
       </c>
       <c r="H426" t="n">
-        <v>0.008880000000000001</v>
+        <v>0.008240000000000001</v>
       </c>
       <c r="I426" t="n">
-        <v>0.0182</v>
+        <v>0.0151</v>
       </c>
     </row>
     <row r="427">
@@ -20219,16 +20219,16 @@
         <v>5</v>
       </c>
       <c r="F438" t="n">
-        <v>0.838</v>
+        <v>0.843</v>
       </c>
       <c r="G438" t="n">
-        <v>0.862</v>
+        <v>0.866</v>
       </c>
       <c r="H438" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.555</v>
       </c>
       <c r="I438" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="439">
@@ -20256,16 +20256,16 @@
         <v>6</v>
       </c>
       <c r="F439" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G439" t="n">
-        <v>0.878</v>
+        <v>0.876</v>
       </c>
       <c r="H439" t="n">
-        <v>0.105</v>
+        <v>0.23</v>
       </c>
       <c r="I439" t="n">
-        <v>0.132</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="440">
@@ -20367,16 +20367,16 @@
         <v>9</v>
       </c>
       <c r="F442" t="n">
-        <v>0.754</v>
+        <v>0.757</v>
       </c>
       <c r="G442" t="n">
-        <v>0.841</v>
+        <v>0.845</v>
       </c>
       <c r="H442" t="n">
-        <v>0.0236</v>
+        <v>0.0225</v>
       </c>
       <c r="I442" t="n">
-        <v>0.0519</v>
+        <v>0.0413</v>
       </c>
     </row>
     <row r="443">
@@ -20811,13 +20811,13 @@
         <v>5</v>
       </c>
       <c r="F454" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G454" t="n">
-        <v>0.8</v>
+        <v>0.793</v>
       </c>
       <c r="H454" t="n">
-        <v>1</v>
+        <v>0.772</v>
       </c>
       <c r="I454" t="n">
         <v>1</v>
@@ -20848,16 +20848,16 @@
         <v>6</v>
       </c>
       <c r="F455" t="n">
-        <v>0.787</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G455" t="n">
-        <v>0.847</v>
+        <v>0.853</v>
       </c>
       <c r="H455" t="n">
-        <v>0.232</v>
+        <v>0.357</v>
       </c>
       <c r="I455" t="n">
-        <v>0.255</v>
+        <v>0.393</v>
       </c>
     </row>
     <row r="456">
@@ -20959,16 +20959,16 @@
         <v>9</v>
       </c>
       <c r="F458" t="n">
-        <v>0.66</v>
+        <v>0.667</v>
       </c>
       <c r="G458" t="n">
-        <v>0.78</v>
+        <v>0.793</v>
       </c>
       <c r="H458" t="n">
-        <v>0.0285</v>
+        <v>0.0189</v>
       </c>
       <c r="I458" t="n">
-        <v>0.104</v>
+        <v>0.0693</v>
       </c>
     </row>
     <row r="459">
@@ -21042,7 +21042,7 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="I460" t="n">
-        <v>0.865</v>
+        <v>0.837</v>
       </c>
     </row>
     <row r="461">
@@ -21406,13 +21406,13 @@
         <v>0.962</v>
       </c>
       <c r="G470" t="n">
-        <v>0.899</v>
+        <v>0.888</v>
       </c>
       <c r="H470" t="n">
-        <v>0.142</v>
+        <v>0.0888</v>
       </c>
       <c r="I470" t="n">
-        <v>0.521</v>
+        <v>0.326</v>
       </c>
     </row>
     <row r="471">
@@ -21440,13 +21440,13 @@
         <v>6</v>
       </c>
       <c r="F471" t="n">
-        <v>0.875</v>
+        <v>0.877</v>
       </c>
       <c r="G471" t="n">
-        <v>0.863</v>
+        <v>0.854</v>
       </c>
       <c r="H471" t="n">
-        <v>1</v>
+        <v>0.826</v>
       </c>
       <c r="I471" t="n">
         <v>1</v>
@@ -21557,10 +21557,10 @@
         <v>0.927</v>
       </c>
       <c r="H474" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="I474" t="n">
-        <v>0.535</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="475">
@@ -21995,13 +21995,13 @@
         <v>5</v>
       </c>
       <c r="F486" t="n">
-        <v>0.743</v>
+        <v>0.75</v>
       </c>
       <c r="G486" t="n">
-        <v>0.792</v>
+        <v>0.79</v>
       </c>
       <c r="H486" t="n">
-        <v>0.506</v>
+        <v>0.615</v>
       </c>
       <c r="I486" t="n">
         <v>1</v>
@@ -22032,16 +22032,16 @@
         <v>6</v>
       </c>
       <c r="F487" t="n">
-        <v>0.761</v>
+        <v>0.789</v>
       </c>
       <c r="G487" t="n">
-        <v>0.891</v>
+        <v>0.911</v>
       </c>
       <c r="H487" t="n">
-        <v>0.0313</v>
+        <v>0.0354</v>
       </c>
       <c r="I487" t="n">
-        <v>0.0492</v>
+        <v>0.0556</v>
       </c>
     </row>
     <row r="488">
@@ -22143,16 +22143,16 @@
         <v>9</v>
       </c>
       <c r="F490" t="n">
-        <v>0.619</v>
+        <v>0.624</v>
       </c>
       <c r="G490" t="n">
-        <v>0.802</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H490" t="n">
-        <v>0.00213</v>
+        <v>0.00111</v>
       </c>
       <c r="I490" t="n">
-        <v>0.00781</v>
+        <v>0.00407</v>
       </c>
     </row>
     <row r="491">
@@ -22587,16 +22587,16 @@
         <v>5</v>
       </c>
       <c r="F502" t="n">
-        <v>0.838</v>
+        <v>0.843</v>
       </c>
       <c r="G502" t="n">
-        <v>0.842</v>
+        <v>0.836</v>
       </c>
       <c r="H502" t="n">
-        <v>1</v>
+        <v>0.888</v>
       </c>
       <c r="I502" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="503">
@@ -22624,16 +22624,16 @@
         <v>6</v>
       </c>
       <c r="F503" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G503" t="n">
-        <v>0.877</v>
+        <v>0.882</v>
       </c>
       <c r="H503" t="n">
-        <v>0.108</v>
+        <v>0.176</v>
       </c>
       <c r="I503" t="n">
-        <v>0.132</v>
+        <v>0.242</v>
       </c>
     </row>
     <row r="504">
@@ -22735,16 +22735,16 @@
         <v>9</v>
       </c>
       <c r="F506" t="n">
-        <v>0.754</v>
+        <v>0.757</v>
       </c>
       <c r="G506" t="n">
-        <v>0.86</v>
+        <v>0.868</v>
       </c>
       <c r="H506" t="n">
-        <v>0.00518</v>
+        <v>0.00306</v>
       </c>
       <c r="I506" t="n">
-        <v>0.019</v>
+        <v>0.0112</v>
       </c>
     </row>
     <row r="507">
@@ -23179,13 +23179,13 @@
         <v>5</v>
       </c>
       <c r="F518" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G518" t="n">
-        <v>0.767</v>
+        <v>0.773</v>
       </c>
       <c r="H518" t="n">
-        <v>0.481</v>
+        <v>0.476</v>
       </c>
       <c r="I518" t="n">
         <v>1</v>
@@ -23216,16 +23216,16 @@
         <v>6</v>
       </c>
       <c r="F519" t="n">
-        <v>0.787</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G519" t="n">
-        <v>0.86</v>
+        <v>0.867</v>
       </c>
       <c r="H519" t="n">
-        <v>0.13</v>
+        <v>0.211</v>
       </c>
       <c r="I519" t="n">
-        <v>0.238</v>
+        <v>0.332</v>
       </c>
     </row>
     <row r="520">
@@ -23327,16 +23327,16 @@
         <v>9</v>
       </c>
       <c r="F522" t="n">
-        <v>0.66</v>
+        <v>0.667</v>
       </c>
       <c r="G522" t="n">
-        <v>0.78</v>
+        <v>0.793</v>
       </c>
       <c r="H522" t="n">
-        <v>0.0285</v>
+        <v>0.0189</v>
       </c>
       <c r="I522" t="n">
-        <v>0.104</v>
+        <v>0.0693</v>
       </c>
     </row>
     <row r="523">
@@ -23780,7 +23780,7 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I534" t="n">
-        <v>0.488</v>
+        <v>0.326</v>
       </c>
     </row>
     <row r="535">
@@ -23808,16 +23808,16 @@
         <v>6</v>
       </c>
       <c r="F535" t="n">
-        <v>0.875</v>
+        <v>0.877</v>
       </c>
       <c r="G535" t="n">
-        <v>0.899</v>
+        <v>0.889</v>
       </c>
       <c r="H535" t="n">
-        <v>0.636</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="I535" t="n">
-        <v>0.961</v>
+        <v>1</v>
       </c>
     </row>
     <row r="536">
@@ -23925,10 +23925,10 @@
         <v>0.927</v>
       </c>
       <c r="H538" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="I538" t="n">
-        <v>0.535</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="539">
@@ -24363,10 +24363,10 @@
         <v>5</v>
       </c>
       <c r="F550" t="n">
-        <v>0.743</v>
+        <v>0.75</v>
       </c>
       <c r="G550" t="n">
-        <v>0.752</v>
+        <v>0.76</v>
       </c>
       <c r="H550" t="n">
         <v>1</v>
@@ -24400,16 +24400,16 @@
         <v>6</v>
       </c>
       <c r="F551" t="n">
-        <v>0.761</v>
+        <v>0.789</v>
       </c>
       <c r="G551" t="n">
-        <v>0.87</v>
+        <v>0.889</v>
       </c>
       <c r="H551" t="n">
-        <v>0.0864</v>
+        <v>0.104</v>
       </c>
       <c r="I551" t="n">
-        <v>0.119</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="552">
@@ -24511,16 +24511,16 @@
         <v>9</v>
       </c>
       <c r="F554" t="n">
-        <v>0.619</v>
+        <v>0.624</v>
       </c>
       <c r="G554" t="n">
-        <v>0.802</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H554" t="n">
-        <v>0.00213</v>
+        <v>0.00111</v>
       </c>
       <c r="I554" t="n">
-        <v>0.00781</v>
+        <v>0.00407</v>
       </c>
     </row>
     <row r="555">
@@ -24955,16 +24955,16 @@
         <v>5</v>
       </c>
       <c r="F566" t="n">
-        <v>0.838</v>
+        <v>0.843</v>
       </c>
       <c r="G566" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H566" t="n">
-        <v>0.583</v>
+        <v>0.578</v>
       </c>
       <c r="I566" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="567">
@@ -24992,16 +24992,16 @@
         <v>6</v>
       </c>
       <c r="F567" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G567" t="n">
-        <v>0.884</v>
+        <v>0.889</v>
       </c>
       <c r="H567" t="n">
-        <v>0.0743</v>
+        <v>0.125</v>
       </c>
       <c r="I567" t="n">
-        <v>0.117</v>
+        <v>0.196</v>
       </c>
     </row>
     <row r="568">
@@ -25103,16 +25103,16 @@
         <v>9</v>
       </c>
       <c r="F570" t="n">
-        <v>0.754</v>
+        <v>0.757</v>
       </c>
       <c r="G570" t="n">
-        <v>0.86</v>
+        <v>0.868</v>
       </c>
       <c r="H570" t="n">
-        <v>0.00518</v>
+        <v>0.00306</v>
       </c>
       <c r="I570" t="n">
-        <v>0.019</v>
+        <v>0.0112</v>
       </c>
     </row>
     <row r="571">
@@ -25547,13 +25547,13 @@
         <v>5</v>
       </c>
       <c r="F582" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G582" t="n">
-        <v>0.787</v>
+        <v>0.793</v>
       </c>
       <c r="H582" t="n">
-        <v>0.774</v>
+        <v>0.772</v>
       </c>
       <c r="I582" t="n">
         <v>1</v>
@@ -25584,16 +25584,16 @@
         <v>6</v>
       </c>
       <c r="F583" t="n">
-        <v>0.787</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G583" t="n">
-        <v>0.84</v>
+        <v>0.847</v>
       </c>
       <c r="H583" t="n">
-        <v>0.3</v>
+        <v>0.446</v>
       </c>
       <c r="I583" t="n">
-        <v>0.3</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="584">
@@ -25695,16 +25695,16 @@
         <v>9</v>
       </c>
       <c r="F586" t="n">
-        <v>0.66</v>
+        <v>0.667</v>
       </c>
       <c r="G586" t="n">
-        <v>0.8</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H586" t="n">
-        <v>0.00906</v>
+        <v>0.00551</v>
       </c>
       <c r="I586" t="n">
-        <v>0.0997</v>
+        <v>0.0606</v>
       </c>
     </row>
     <row r="587">
@@ -26148,7 +26148,7 @@
         <v>0.0888</v>
       </c>
       <c r="I598" t="n">
-        <v>0.488</v>
+        <v>0.326</v>
       </c>
     </row>
     <row r="599">
@@ -26176,10 +26176,10 @@
         <v>6</v>
       </c>
       <c r="F599" t="n">
-        <v>0.875</v>
+        <v>0.877</v>
       </c>
       <c r="G599" t="n">
-        <v>0.878</v>
+        <v>0.868</v>
       </c>
       <c r="H599" t="n">
         <v>1</v>
@@ -26293,10 +26293,10 @@
         <v>0.929</v>
       </c>
       <c r="H602" t="n">
-        <v>0.363</v>
+        <v>0.365</v>
       </c>
       <c r="I602" t="n">
-        <v>0.535</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="603">
@@ -26731,13 +26731,13 @@
         <v>5</v>
       </c>
       <c r="F614" t="n">
-        <v>0.743</v>
+        <v>0.75</v>
       </c>
       <c r="G614" t="n">
-        <v>0.782</v>
+        <v>0.79</v>
       </c>
       <c r="H614" t="n">
-        <v>0.62</v>
+        <v>0.615</v>
       </c>
       <c r="I614" t="n">
         <v>1</v>
@@ -26768,16 +26768,16 @@
         <v>6</v>
       </c>
       <c r="F615" t="n">
-        <v>0.761</v>
+        <v>0.789</v>
       </c>
       <c r="G615" t="n">
-        <v>0.859</v>
+        <v>0.878</v>
       </c>
       <c r="H615" t="n">
-        <v>0.132</v>
+        <v>0.161</v>
       </c>
       <c r="I615" t="n">
-        <v>0.145</v>
+        <v>0.197</v>
       </c>
     </row>
     <row r="616">
@@ -26879,16 +26879,16 @@
         <v>9</v>
       </c>
       <c r="F618" t="n">
-        <v>0.619</v>
+        <v>0.624</v>
       </c>
       <c r="G618" t="n">
-        <v>0.825</v>
+        <v>0.84</v>
       </c>
       <c r="H618" t="n">
-        <v>0.000395</v>
+        <v>0.000178</v>
       </c>
       <c r="I618" t="n">
-        <v>0.00434</v>
+        <v>0.00196</v>
       </c>
     </row>
     <row r="619">
@@ -27323,16 +27323,16 @@
         <v>5</v>
       </c>
       <c r="F630" t="n">
-        <v>0.838</v>
+        <v>0.843</v>
       </c>
       <c r="G630" t="n">
-        <v>0.832</v>
+        <v>0.836</v>
       </c>
       <c r="H630" t="n">
-        <v>0.889</v>
+        <v>0.888</v>
       </c>
       <c r="I630" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="631">
@@ -27360,16 +27360,16 @@
         <v>6</v>
       </c>
       <c r="F631" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G631" t="n">
-        <v>0.868</v>
+        <v>0.873</v>
       </c>
       <c r="H631" t="n">
-        <v>0.19</v>
+        <v>0.294</v>
       </c>
       <c r="I631" t="n">
-        <v>0.19</v>
+        <v>0.294</v>
       </c>
     </row>
     <row r="632">
@@ -27471,16 +27471,16 @@
         <v>9</v>
       </c>
       <c r="F634" t="n">
-        <v>0.754</v>
+        <v>0.757</v>
       </c>
       <c r="G634" t="n">
-        <v>0.874</v>
+        <v>0.882</v>
       </c>
       <c r="H634" t="n">
-        <v>0.00129</v>
+        <v>0.000684</v>
       </c>
       <c r="I634" t="n">
-        <v>0.0142</v>
+        <v>0.00752</v>
       </c>
     </row>
     <row r="635">
@@ -27915,13 +27915,13 @@
         <v>5</v>
       </c>
       <c r="F646" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G646" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="H646" t="n">
-        <v>0.885</v>
+        <v>0.884</v>
       </c>
       <c r="I646" t="n">
         <v>1</v>
@@ -27952,16 +27952,16 @@
         <v>6</v>
       </c>
       <c r="F647" t="n">
-        <v>0.787</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G647" t="n">
-        <v>0.853</v>
+        <v>0.867</v>
       </c>
       <c r="H647" t="n">
-        <v>0.176</v>
+        <v>0.211</v>
       </c>
       <c r="I647" t="n">
-        <v>0.242</v>
+        <v>0.332</v>
       </c>
     </row>
     <row r="648">
@@ -28063,16 +28063,16 @@
         <v>9</v>
       </c>
       <c r="F650" t="n">
-        <v>0.66</v>
+        <v>0.667</v>
       </c>
       <c r="G650" t="n">
-        <v>0.7</v>
+        <v>0.707</v>
       </c>
       <c r="H650" t="n">
-        <v>0.536</v>
+        <v>0.534</v>
       </c>
       <c r="I650" t="n">
-        <v>0.59</v>
+        <v>0.587</v>
       </c>
     </row>
     <row r="651">
@@ -28140,13 +28140,13 @@
         <v>0.773</v>
       </c>
       <c r="G652" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="H652" t="n">
-        <v>0.779</v>
+        <v>0.673</v>
       </c>
       <c r="I652" t="n">
-        <v>0.865</v>
+        <v>0.837</v>
       </c>
     </row>
     <row r="653">
@@ -28544,16 +28544,16 @@
         <v>6</v>
       </c>
       <c r="F663" t="n">
-        <v>0.875</v>
+        <v>0.877</v>
       </c>
       <c r="G663" t="n">
         <v>0.961</v>
       </c>
       <c r="H663" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="I663" t="n">
-        <v>0.441</v>
+        <v>0.425</v>
       </c>
     </row>
     <row r="664">
@@ -28664,7 +28664,7 @@
         <v>0.364</v>
       </c>
       <c r="I666" t="n">
-        <v>0.535</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="667">
@@ -28732,13 +28732,13 @@
         <v>0.863</v>
       </c>
       <c r="G668" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="H668" t="n">
-        <v>0.038</v>
+        <v>0.0378</v>
       </c>
       <c r="I668" t="n">
-        <v>0.418</v>
+        <v>0.416</v>
       </c>
     </row>
     <row r="669">
@@ -29099,13 +29099,13 @@
         <v>5</v>
       </c>
       <c r="F678" t="n">
-        <v>0.743</v>
+        <v>0.75</v>
       </c>
       <c r="G678" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="H678" t="n">
-        <v>0.532</v>
+        <v>0.527</v>
       </c>
       <c r="I678" t="n">
         <v>1</v>
@@ -29136,16 +29136,16 @@
         <v>6</v>
       </c>
       <c r="F679" t="n">
-        <v>0.761</v>
+        <v>0.789</v>
       </c>
       <c r="G679" t="n">
-        <v>0.793</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H679" t="n">
-        <v>0.723</v>
+        <v>0.852</v>
       </c>
       <c r="I679" t="n">
-        <v>0.723</v>
+        <v>0.852</v>
       </c>
     </row>
     <row r="680">
@@ -29247,16 +29247,16 @@
         <v>9</v>
       </c>
       <c r="F682" t="n">
-        <v>0.619</v>
+        <v>0.624</v>
       </c>
       <c r="G682" t="n">
-        <v>0.651</v>
+        <v>0.656</v>
       </c>
       <c r="H682" t="n">
-        <v>0.695</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="I682" t="n">
-        <v>0.764</v>
+        <v>0.762</v>
       </c>
     </row>
     <row r="683">
@@ -29324,13 +29324,13 @@
         <v>0.75</v>
       </c>
       <c r="G684" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="H684" t="n">
-        <v>0.413</v>
+        <v>0.51</v>
       </c>
       <c r="I684" t="n">
-        <v>0.649</v>
+        <v>0.701</v>
       </c>
     </row>
     <row r="685">
@@ -29691,16 +29691,16 @@
         <v>5</v>
       </c>
       <c r="F694" t="n">
-        <v>0.838</v>
+        <v>0.843</v>
       </c>
       <c r="G694" t="n">
-        <v>0.819</v>
+        <v>0.824</v>
       </c>
       <c r="H694" t="n">
-        <v>0.672</v>
+        <v>0.668</v>
       </c>
       <c r="I694" t="n">
-        <v>1</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="695">
@@ -29728,16 +29728,16 @@
         <v>6</v>
       </c>
       <c r="F695" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G695" t="n">
-        <v>0.869</v>
+        <v>0.88</v>
       </c>
       <c r="H695" t="n">
-        <v>0.183</v>
+        <v>0.219</v>
       </c>
       <c r="I695" t="n">
-        <v>0.19</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="696">
@@ -29839,16 +29839,16 @@
         <v>9</v>
       </c>
       <c r="F698" t="n">
-        <v>0.754</v>
+        <v>0.757</v>
       </c>
       <c r="G698" t="n">
-        <v>0.785</v>
+        <v>0.788</v>
       </c>
       <c r="H698" t="n">
-        <v>0.486</v>
+        <v>0.483</v>
       </c>
       <c r="I698" t="n">
-        <v>0.535</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="699">
@@ -29916,13 +29916,13 @@
         <v>0.802</v>
       </c>
       <c r="G700" t="n">
-        <v>0.803</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H700" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="I700" t="n">
-        <v>1</v>
+        <v>0.979</v>
       </c>
     </row>
     <row r="701">

--- a/eval/learning-curve/results/statistical_tests_full150.xlsx
+++ b/eval/learning-curve/results/statistical_tests_full150.xlsx
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.12</v>
+        <v>0.117</v>
       </c>
       <c r="F2" t="n">
         <v>0.837</v>
@@ -512,13 +512,13 @@
         <v>0.863</v>
       </c>
       <c r="H2" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="I2" t="n">
         <v>0.102</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>0.863</v>
       </c>
       <c r="H3" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="I3" t="n">
         <v>0.102</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.311</v>
+        <v>0.303</v>
       </c>
       <c r="F4" t="n">
         <v>0.837</v>
@@ -592,13 +592,13 @@
         <v>0.854</v>
       </c>
       <c r="H4" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="I4" t="n">
         <v>0.08690000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.38875</v>
+        <v>0.37875</v>
       </c>
     </row>
     <row r="5">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="F5" t="n">
         <v>0.837</v>
@@ -632,13 +632,13 @@
         <v>0.854</v>
       </c>
       <c r="H5" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="I5" t="n">
         <v>0.08690000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="6">
@@ -663,22 +663,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.397</v>
+        <v>0.385</v>
       </c>
       <c r="F6" t="n">
         <v>0.837</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="I6" t="n">
         <v>0.167</v>
       </c>
       <c r="J6" t="n">
-        <v>0.397</v>
+        <v>0.385</v>
       </c>
     </row>
     <row r="7">
@@ -703,22 +703,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.66</v>
+        <v>0.638</v>
       </c>
       <c r="F7" t="n">
         <v>0.837</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="I7" t="n">
         <v>0.167</v>
       </c>
       <c r="J7" t="n">
-        <v>0.66</v>
+        <v>0.638</v>
       </c>
     </row>
     <row r="8">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.0771</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="F8" t="n">
         <v>0.837</v>
@@ -752,13 +752,13 @@
         <v>0.865</v>
       </c>
       <c r="H8" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="I8" t="n">
         <v>0.08210000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.19275</v>
+        <v>0.18725</v>
       </c>
     </row>
     <row r="9">
@@ -792,7 +792,7 @@
         <v>0.865</v>
       </c>
       <c r="H9" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="I9" t="n">
         <v>0.08210000000000001</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.0009790000000000001</v>
+        <v>0.001</v>
       </c>
       <c r="F10" t="n">
         <v>0.837</v>
@@ -832,13 +832,13 @@
         <v>0.903</v>
       </c>
       <c r="H10" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0697</v>
+        <v>0.0706</v>
       </c>
       <c r="J10" t="n">
-        <v>0.004895</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="11">
@@ -872,10 +872,10 @@
         <v>0.903</v>
       </c>
       <c r="H11" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0697</v>
+        <v>0.0706</v>
       </c>
       <c r="J11" t="n">
         <v>0.007299999999999999</v>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.0104</v>
+        <v>0.01</v>
       </c>
       <c r="F12" t="n">
         <v>0.837</v>
@@ -912,13 +912,13 @@
         <v>0.88</v>
       </c>
       <c r="H12" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0828</v>
+        <v>0.0833</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0104</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="13">
@@ -952,10 +952,10 @@
         <v>0.88</v>
       </c>
       <c r="H13" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0828</v>
+        <v>0.0833</v>
       </c>
       <c r="J13" t="n">
         <v>0.0243</v>
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.0334</v>
+        <v>0.0318</v>
       </c>
       <c r="F14" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="G14" t="n">
         <v>0.824</v>
@@ -998,7 +998,7 @@
         <v>0.165</v>
       </c>
       <c r="J14" t="n">
-        <v>0.08349999999999999</v>
+        <v>0.0795</v>
       </c>
     </row>
     <row r="15">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.0307</v>
+        <v>0.0285</v>
       </c>
       <c r="F15" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="G15" t="n">
         <v>0.824</v>
@@ -1038,7 +1038,7 @@
         <v>0.165</v>
       </c>
       <c r="J15" t="n">
-        <v>0.07675</v>
+        <v>0.07125000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.206</v>
+        <v>0.209</v>
       </c>
       <c r="F16" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>0.154</v>
@@ -1078,7 +1078,7 @@
         <v>0.175</v>
       </c>
       <c r="J16" t="n">
-        <v>0.305</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="17">
@@ -1106,10 +1106,10 @@
         <v>0.214</v>
       </c>
       <c r="F17" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H17" t="n">
         <v>0.154</v>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.244</v>
+        <v>0.248</v>
       </c>
       <c r="F18" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H18" t="n">
         <v>0.154</v>
@@ -1158,7 +1158,7 @@
         <v>0.175</v>
       </c>
       <c r="J18" t="n">
-        <v>0.305</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="19">
@@ -1186,10 +1186,10 @@
         <v>0.272</v>
       </c>
       <c r="F19" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H19" t="n">
         <v>0.154</v>
@@ -1223,13 +1223,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.374</v>
+        <v>0.381</v>
       </c>
       <c r="F20" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H20" t="n">
         <v>0.154</v>
@@ -1238,7 +1238,7 @@
         <v>0.19</v>
       </c>
       <c r="J20" t="n">
-        <v>0.374</v>
+        <v>0.381</v>
       </c>
     </row>
     <row r="21">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.352</v>
+        <v>0.365</v>
       </c>
       <c r="F21" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H21" t="n">
         <v>0.154</v>
@@ -1278,7 +1278,7 @@
         <v>0.19</v>
       </c>
       <c r="J21" t="n">
-        <v>0.352</v>
+        <v>0.365</v>
       </c>
     </row>
     <row r="22">
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.0142</v>
+        <v>0.0136</v>
       </c>
       <c r="F22" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="G22" t="n">
         <v>0.853</v>
@@ -1318,7 +1318,7 @@
         <v>0.0919</v>
       </c>
       <c r="J22" t="n">
-        <v>0.07100000000000001</v>
+        <v>0.06799999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1346,7 +1346,7 @@
         <v>0.00188</v>
       </c>
       <c r="F23" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="G23" t="n">
         <v>0.853</v>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.156</v>
+        <v>0.155</v>
       </c>
       <c r="F28" t="n">
         <v>0.864</v>
@@ -1555,10 +1555,10 @@
         <v>0.163</v>
       </c>
       <c r="I28" t="n">
-        <v>0.185</v>
+        <v>0.184</v>
       </c>
       <c r="J28" t="n">
-        <v>0.39</v>
+        <v>0.3875</v>
       </c>
     </row>
     <row r="29">
@@ -1595,7 +1595,7 @@
         <v>0.163</v>
       </c>
       <c r="I29" t="n">
-        <v>0.185</v>
+        <v>0.184</v>
       </c>
       <c r="J29" t="n">
         <v>0.24</v>
@@ -1718,7 +1718,7 @@
         <v>0.0584</v>
       </c>
       <c r="J32" t="n">
-        <v>0.39</v>
+        <v>0.3875</v>
       </c>
     </row>
     <row r="33">
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.461</v>
+        <v>0.455</v>
       </c>
       <c r="F36" t="n">
         <v>0.793</v>
@@ -1878,7 +1878,7 @@
         <v>0.195</v>
       </c>
       <c r="J36" t="n">
-        <v>0.946</v>
+        <v>0.9480000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.946</v>
+        <v>0.948</v>
       </c>
       <c r="F38" t="n">
         <v>0.793</v>
@@ -1958,7 +1958,7 @@
         <v>0.182</v>
       </c>
       <c r="J38" t="n">
-        <v>0.946</v>
+        <v>0.9480000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
       <c r="F40" t="n">
         <v>0.793</v>
@@ -2038,7 +2038,7 @@
         <v>0.188</v>
       </c>
       <c r="J40" t="n">
-        <v>0.946</v>
+        <v>0.9480000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.761</v>
+        <v>0.763</v>
       </c>
       <c r="F42" t="n">
         <v>0.793</v>
@@ -2115,10 +2115,10 @@
         <v>0.205</v>
       </c>
       <c r="I42" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="J42" t="n">
-        <v>0.946</v>
+        <v>0.9480000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -2155,7 +2155,7 @@
         <v>0.205</v>
       </c>
       <c r="I43" t="n">
-        <v>0.195</v>
+        <v>0.194</v>
       </c>
       <c r="J43" t="n">
         <v>0.669</v>
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.0009</v>
+        <v>0.000892</v>
       </c>
       <c r="F44" t="n">
         <v>0.793</v>
@@ -2198,7 +2198,7 @@
         <v>0.0954</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0045</v>
+        <v>0.00446</v>
       </c>
     </row>
     <row r="45">
@@ -2263,7 +2263,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.274</v>
+        <v>0.268</v>
       </c>
       <c r="F46" t="n">
         <v>0.765</v>
@@ -2278,7 +2278,7 @@
         <v>0.186</v>
       </c>
       <c r="J46" t="n">
-        <v>0.4566666666666667</v>
+        <v>0.4466666666666667</v>
       </c>
     </row>
     <row r="47">
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.612</v>
+        <v>0.599</v>
       </c>
       <c r="F48" t="n">
         <v>0.765</v>
@@ -2358,7 +2358,7 @@
         <v>0.15</v>
       </c>
       <c r="J48" t="n">
-        <v>0.612</v>
+        <v>0.599</v>
       </c>
     </row>
     <row r="49">
@@ -2423,13 +2423,13 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.445</v>
+        <v>0.452</v>
       </c>
       <c r="F50" t="n">
         <v>0.765</v>
       </c>
       <c r="G50" t="n">
-        <v>0.789</v>
+        <v>0.788</v>
       </c>
       <c r="H50" t="n">
         <v>0.165</v>
@@ -2438,7 +2438,7 @@
         <v>0.148</v>
       </c>
       <c r="J50" t="n">
-        <v>0.55625</v>
+        <v>0.5650000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2469,7 +2469,7 @@
         <v>0.765</v>
       </c>
       <c r="G51" t="n">
-        <v>0.789</v>
+        <v>0.788</v>
       </c>
       <c r="H51" t="n">
         <v>0.165</v>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.136</v>
+        <v>0.134</v>
       </c>
       <c r="F52" t="n">
         <v>0.765</v>
@@ -2518,7 +2518,7 @@
         <v>0.143</v>
       </c>
       <c r="J52" t="n">
-        <v>0.34</v>
+        <v>0.335</v>
       </c>
     </row>
     <row r="53">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.00993</v>
+        <v>0.0102</v>
       </c>
       <c r="F54" t="n">
         <v>0.765</v>
@@ -2598,7 +2598,7 @@
         <v>0.137</v>
       </c>
       <c r="J54" t="n">
-        <v>0.04965</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="55">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.112</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="F57" t="n">
         <v>0.765</v>
@@ -2718,7 +2718,7 @@
         <v>0.185</v>
       </c>
       <c r="J57" t="n">
-        <v>0.112</v>
+        <v>0.09950000000000001</v>
       </c>
     </row>
     <row r="58">
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.0216</v>
+        <v>0.0206</v>
       </c>
       <c r="F58" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G58" t="n">
         <v>0.8070000000000001</v>
@@ -2758,7 +2758,7 @@
         <v>0.181</v>
       </c>
       <c r="J58" t="n">
-        <v>0.027</v>
+        <v>0.02575</v>
       </c>
     </row>
     <row r="59">
@@ -2786,7 +2786,7 @@
         <v>0.0303</v>
       </c>
       <c r="F59" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G59" t="n">
         <v>0.8070000000000001</v>
@@ -2823,13 +2823,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.00441</v>
+        <v>0.00429</v>
       </c>
       <c r="F60" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G60" t="n">
-        <v>0.82</v>
+        <v>0.819</v>
       </c>
       <c r="H60" t="n">
         <v>0.185</v>
@@ -2838,7 +2838,7 @@
         <v>0.16</v>
       </c>
       <c r="J60" t="n">
-        <v>0.02205</v>
+        <v>0.02145</v>
       </c>
     </row>
     <row r="61">
@@ -2866,10 +2866,10 @@
         <v>0.00521</v>
       </c>
       <c r="F61" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G61" t="n">
-        <v>0.82</v>
+        <v>0.819</v>
       </c>
       <c r="H61" t="n">
         <v>0.185</v>
@@ -2903,22 +2903,22 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.017</v>
+        <v>0.0168</v>
       </c>
       <c r="F62" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G62" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H62" t="n">
         <v>0.185</v>
       </c>
       <c r="I62" t="n">
-        <v>0.156</v>
+        <v>0.155</v>
       </c>
       <c r="J62" t="n">
-        <v>0.027</v>
+        <v>0.02575</v>
       </c>
     </row>
     <row r="63">
@@ -2946,16 +2946,16 @@
         <v>0.0199</v>
       </c>
       <c r="F63" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G63" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H63" t="n">
         <v>0.185</v>
       </c>
       <c r="I63" t="n">
-        <v>0.156</v>
+        <v>0.155</v>
       </c>
       <c r="J63" t="n">
         <v>0.03316666666666667</v>
@@ -2983,13 +2983,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.0124</v>
+        <v>0.0122</v>
       </c>
       <c r="F64" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G64" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H64" t="n">
         <v>0.185</v>
@@ -2998,7 +2998,7 @@
         <v>0.162</v>
       </c>
       <c r="J64" t="n">
-        <v>0.027</v>
+        <v>0.02575</v>
       </c>
     </row>
     <row r="65">
@@ -3026,10 +3026,10 @@
         <v>0.00763</v>
       </c>
       <c r="F65" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G65" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H65" t="n">
         <v>0.185</v>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.109</v>
+        <v>0.115</v>
       </c>
       <c r="F66" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G66" t="n">
         <v>0.706</v>
@@ -3078,7 +3078,7 @@
         <v>0.164</v>
       </c>
       <c r="J66" t="n">
-        <v>0.109</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="67">
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.14</v>
+        <v>0.156</v>
       </c>
       <c r="F67" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G67" t="n">
         <v>0.706</v>
@@ -3118,7 +3118,7 @@
         <v>0.164</v>
       </c>
       <c r="J67" t="n">
-        <v>0.14</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="68">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.571</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="F68" t="n">
         <v>0.798</v>
@@ -3158,7 +3158,7 @@
         <v>0.139</v>
       </c>
       <c r="J68" t="n">
-        <v>0.7887500000000001</v>
+        <v>0.7787500000000001</v>
       </c>
     </row>
     <row r="69">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.88</v>
+        <v>0.867</v>
       </c>
       <c r="F70" t="n">
         <v>0.798</v>
@@ -3238,7 +3238,7 @@
         <v>0.116</v>
       </c>
       <c r="J70" t="n">
-        <v>0.8800000000000001</v>
+        <v>0.867</v>
       </c>
     </row>
     <row r="71">
@@ -3303,13 +3303,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.631</v>
+        <v>0.623</v>
       </c>
       <c r="F72" t="n">
         <v>0.798</v>
       </c>
       <c r="G72" t="n">
-        <v>0.787</v>
+        <v>0.786</v>
       </c>
       <c r="H72" t="n">
         <v>0.132</v>
@@ -3318,7 +3318,7 @@
         <v>0.152</v>
       </c>
       <c r="J72" t="n">
-        <v>0.7887500000000001</v>
+        <v>0.7787500000000001</v>
       </c>
     </row>
     <row r="73">
@@ -3343,13 +3343,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.609</v>
+        <v>0.65</v>
       </c>
       <c r="F73" t="n">
         <v>0.798</v>
       </c>
       <c r="G73" t="n">
-        <v>0.787</v>
+        <v>0.786</v>
       </c>
       <c r="H73" t="n">
         <v>0.132</v>
@@ -3358,7 +3358,7 @@
         <v>0.152</v>
       </c>
       <c r="J73" t="n">
-        <v>0.76125</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="74">
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.368</v>
+        <v>0.36</v>
       </c>
       <c r="F74" t="n">
         <v>0.798</v>
@@ -3398,7 +3398,7 @@
         <v>0.107</v>
       </c>
       <c r="J74" t="n">
-        <v>0.7887500000000001</v>
+        <v>0.7787500000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.00321</v>
+        <v>0.00322</v>
       </c>
       <c r="F76" t="n">
         <v>0.798</v>
@@ -3475,10 +3475,10 @@
         <v>0.132</v>
       </c>
       <c r="I76" t="n">
-        <v>0.092</v>
+        <v>0.0921</v>
       </c>
       <c r="J76" t="n">
-        <v>0.01605</v>
+        <v>0.0161</v>
       </c>
     </row>
     <row r="77">
@@ -3515,7 +3515,7 @@
         <v>0.132</v>
       </c>
       <c r="I77" t="n">
-        <v>0.092</v>
+        <v>0.0921</v>
       </c>
       <c r="J77" t="n">
         <v>0.0143</v>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.195</v>
+        <v>0.193</v>
       </c>
       <c r="F78" t="n">
         <v>0.798</v>
@@ -3558,7 +3558,7 @@
         <v>0.15</v>
       </c>
       <c r="J78" t="n">
-        <v>0.195</v>
+        <v>0.193</v>
       </c>
     </row>
     <row r="79">
@@ -3623,22 +3623,22 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.0157</v>
+        <v>0.0148</v>
       </c>
       <c r="F80" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G80" t="n">
         <v>0.789</v>
       </c>
       <c r="H80" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="I80" t="n">
         <v>0.181</v>
       </c>
       <c r="J80" t="n">
-        <v>0.03924999999999999</v>
+        <v>0.03700000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -3666,13 +3666,13 @@
         <v>0.011</v>
       </c>
       <c r="F81" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G81" t="n">
         <v>0.789</v>
       </c>
       <c r="H81" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="I81" t="n">
         <v>0.181</v>
@@ -3706,16 +3706,16 @@
         <v>0.0273</v>
       </c>
       <c r="F82" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G82" t="n">
         <v>0.792</v>
       </c>
       <c r="H82" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="I82" t="n">
-        <v>0.16</v>
+        <v>0.159</v>
       </c>
       <c r="J82" t="n">
         <v>0.04550000000000001</v>
@@ -3746,16 +3746,16 @@
         <v>0.0507</v>
       </c>
       <c r="F83" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G83" t="n">
         <v>0.792</v>
       </c>
       <c r="H83" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="I83" t="n">
-        <v>0.16</v>
+        <v>0.159</v>
       </c>
       <c r="J83" t="n">
         <v>0.05769999999999999</v>
@@ -3783,22 +3783,22 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.0409</v>
+        <v>0.041</v>
       </c>
       <c r="F84" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G84" t="n">
-        <v>0.789</v>
+        <v>0.788</v>
       </c>
       <c r="H84" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="I84" t="n">
         <v>0.161</v>
       </c>
       <c r="J84" t="n">
-        <v>0.0458</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="85">
@@ -3826,13 +3826,13 @@
         <v>0.0577</v>
       </c>
       <c r="F85" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G85" t="n">
-        <v>0.789</v>
+        <v>0.788</v>
       </c>
       <c r="H85" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="I85" t="n">
         <v>0.161</v>
@@ -3863,22 +3863,22 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.0458</v>
+        <v>0.046</v>
       </c>
       <c r="F86" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G86" t="n">
         <v>0.793</v>
       </c>
       <c r="H86" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="I86" t="n">
         <v>0.169</v>
       </c>
       <c r="J86" t="n">
-        <v>0.0458</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="87">
@@ -3906,13 +3906,13 @@
         <v>0.0577</v>
       </c>
       <c r="F87" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G87" t="n">
         <v>0.793</v>
       </c>
       <c r="H87" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="I87" t="n">
         <v>0.169</v>
@@ -3943,22 +3943,22 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.0141</v>
+        <v>0.0134</v>
       </c>
       <c r="F88" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G88" t="n">
         <v>0.791</v>
       </c>
       <c r="H88" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="I88" t="n">
         <v>0.137</v>
       </c>
       <c r="J88" t="n">
-        <v>0.03924999999999999</v>
+        <v>0.03700000000000001</v>
       </c>
     </row>
     <row r="89">
@@ -3986,13 +3986,13 @@
         <v>0.0076</v>
       </c>
       <c r="F89" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G89" t="n">
         <v>0.791</v>
       </c>
       <c r="H89" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="I89" t="n">
         <v>0.137</v>
@@ -4272,16 +4272,16 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>0.893</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0717</v>
+        <v>0.0515</v>
       </c>
       <c r="I7" t="n">
-        <v>0.289</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="8">
@@ -4864,16 +4864,16 @@
         <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
       <c r="G23" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>0.466</v>
+        <v>0.469</v>
       </c>
       <c r="I23" t="n">
-        <v>0.854</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="24">
@@ -5456,16 +5456,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.711</v>
+        <v>0.7</v>
       </c>
       <c r="G39" t="n">
         <v>0.878</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0092</v>
+        <v>0.00568</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0202</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="40">
@@ -6048,16 +6048,16 @@
         <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>0.821</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G55" t="n">
         <v>0.908</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0231</v>
+        <v>0.0155</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0834</v>
+        <v>0.0484</v>
       </c>
     </row>
     <row r="56">
@@ -6640,16 +6640,16 @@
         <v>6</v>
       </c>
       <c r="F71" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G71" t="n">
         <v>0.887</v>
       </c>
       <c r="H71" t="n">
-        <v>0.105</v>
+        <v>0.0771</v>
       </c>
       <c r="I71" t="n">
-        <v>0.289</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="72">
@@ -7232,16 +7232,16 @@
         <v>6</v>
       </c>
       <c r="F87" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
       <c r="G87" t="n">
         <v>0.91</v>
       </c>
       <c r="H87" t="n">
-        <v>0.191</v>
+        <v>0.192</v>
       </c>
       <c r="I87" t="n">
-        <v>0.525</v>
+        <v>0.528</v>
       </c>
     </row>
     <row r="88">
@@ -7824,16 +7824,16 @@
         <v>6</v>
       </c>
       <c r="F103" t="n">
-        <v>0.711</v>
+        <v>0.7</v>
       </c>
       <c r="G103" t="n">
         <v>0.9</v>
       </c>
       <c r="H103" t="n">
-        <v>0.00225</v>
+        <v>0.00131</v>
       </c>
       <c r="I103" t="n">
-        <v>0.00825</v>
+        <v>0.0048</v>
       </c>
     </row>
     <row r="104">
@@ -8416,16 +8416,16 @@
         <v>6</v>
       </c>
       <c r="F119" t="n">
-        <v>0.821</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G119" t="n">
         <v>0.905</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0254</v>
+        <v>0.017</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0834</v>
+        <v>0.0484</v>
       </c>
     </row>
     <row r="120">
@@ -9008,16 +9008,16 @@
         <v>6</v>
       </c>
       <c r="F135" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G135" t="n">
-        <v>0.86</v>
+        <v>0.853</v>
       </c>
       <c r="H135" t="n">
-        <v>0.349</v>
+        <v>0.357</v>
       </c>
       <c r="I135" t="n">
-        <v>0.393</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="136">
@@ -9122,13 +9122,13 @@
         <v>0.667</v>
       </c>
       <c r="G138" t="n">
-        <v>0.76</v>
+        <v>0.753</v>
       </c>
       <c r="H138" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.127</v>
       </c>
       <c r="I138" t="n">
-        <v>0.175</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="139">
@@ -9600,10 +9600,10 @@
         <v>6</v>
       </c>
       <c r="F151" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
       <c r="G151" t="n">
-        <v>0.897</v>
+        <v>0.895</v>
       </c>
       <c r="H151" t="n">
         <v>0.116</v>
@@ -9714,13 +9714,13 @@
         <v>0.987</v>
       </c>
       <c r="G154" t="n">
-        <v>0.924</v>
+        <v>0.923</v>
       </c>
       <c r="H154" t="n">
-        <v>0.0809</v>
+        <v>0.0805</v>
       </c>
       <c r="I154" t="n">
-        <v>0.538</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="155">
@@ -10192,16 +10192,16 @@
         <v>6</v>
       </c>
       <c r="F167" t="n">
-        <v>0.711</v>
+        <v>0.7</v>
       </c>
       <c r="G167" t="n">
-        <v>0.867</v>
+        <v>0.856</v>
       </c>
       <c r="H167" t="n">
-        <v>0.0168</v>
+        <v>0.0191</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0308</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="168">
@@ -10306,13 +10306,13 @@
         <v>0.608</v>
       </c>
       <c r="G170" t="n">
-        <v>0.776</v>
+        <v>0.768</v>
       </c>
       <c r="H170" t="n">
-        <v>0.00596</v>
+        <v>0.00927</v>
       </c>
       <c r="I170" t="n">
-        <v>0.0131</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="171">
@@ -10784,16 +10784,16 @@
         <v>6</v>
       </c>
       <c r="F183" t="n">
-        <v>0.821</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G183" t="n">
-        <v>0.881</v>
+        <v>0.875</v>
       </c>
       <c r="H183" t="n">
-        <v>0.124</v>
+        <v>0.129</v>
       </c>
       <c r="I183" t="n">
-        <v>0.196</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="184">
@@ -10898,13 +10898,13 @@
         <v>0.752</v>
       </c>
       <c r="G186" t="n">
-        <v>0.843</v>
+        <v>0.838</v>
       </c>
       <c r="H186" t="n">
-        <v>0.0216</v>
+        <v>0.0304</v>
       </c>
       <c r="I186" t="n">
-        <v>0.0413</v>
+        <v>0.0557</v>
       </c>
     </row>
     <row r="187">
@@ -11376,16 +11376,16 @@
         <v>6</v>
       </c>
       <c r="F199" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G199" t="n">
         <v>0.887</v>
       </c>
       <c r="H199" t="n">
-        <v>0.105</v>
+        <v>0.0771</v>
       </c>
       <c r="I199" t="n">
-        <v>0.289</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="200">
@@ -11496,7 +11496,7 @@
         <v>0.127</v>
       </c>
       <c r="I202" t="n">
-        <v>0.175</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="203">
@@ -11968,16 +11968,16 @@
         <v>6</v>
       </c>
       <c r="F215" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
       <c r="G215" t="n">
         <v>0.92</v>
       </c>
       <c r="H215" t="n">
-        <v>0.301</v>
+        <v>0.302</v>
       </c>
       <c r="I215" t="n">
-        <v>0.662</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="216">
@@ -12560,16 +12560,16 @@
         <v>6</v>
       </c>
       <c r="F231" t="n">
-        <v>0.711</v>
+        <v>0.7</v>
       </c>
       <c r="G231" t="n">
         <v>0.889</v>
       </c>
       <c r="H231" t="n">
-        <v>0.00472</v>
+        <v>0.00282</v>
       </c>
       <c r="I231" t="n">
-        <v>0.013</v>
+        <v>0.00775</v>
       </c>
     </row>
     <row r="232">
@@ -13152,16 +13152,16 @@
         <v>6</v>
       </c>
       <c r="F247" t="n">
-        <v>0.821</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G247" t="n">
         <v>0.904</v>
       </c>
       <c r="H247" t="n">
-        <v>0.036</v>
+        <v>0.0176</v>
       </c>
       <c r="I247" t="n">
-        <v>0.0834</v>
+        <v>0.0484</v>
       </c>
     </row>
     <row r="248">
@@ -13272,7 +13272,7 @@
         <v>0.0548</v>
       </c>
       <c r="I250" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="251">
@@ -13744,16 +13744,16 @@
         <v>6</v>
       </c>
       <c r="F263" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G263" t="n">
         <v>0.92</v>
       </c>
       <c r="H263" t="n">
-        <v>0.0102</v>
+        <v>0.0066</v>
       </c>
       <c r="I263" t="n">
-        <v>0.112</v>
+        <v>0.0726</v>
       </c>
     </row>
     <row r="264">
@@ -13858,13 +13858,13 @@
         <v>0.667</v>
       </c>
       <c r="G266" t="n">
-        <v>0.753</v>
+        <v>0.747</v>
       </c>
       <c r="H266" t="n">
-        <v>0.127</v>
+        <v>0.163</v>
       </c>
       <c r="I266" t="n">
-        <v>0.175</v>
+        <v>0.224</v>
       </c>
     </row>
     <row r="267">
@@ -14336,7 +14336,7 @@
         <v>6</v>
       </c>
       <c r="F279" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
       <c r="G279" t="n">
         <v>0.9429999999999999</v>
@@ -14450,13 +14450,13 @@
         <v>0.987</v>
       </c>
       <c r="G282" t="n">
-        <v>0.949</v>
+        <v>0.948</v>
       </c>
       <c r="H282" t="n">
-        <v>0.231</v>
+        <v>0.229</v>
       </c>
       <c r="I282" t="n">
-        <v>0.538</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="283">
@@ -14928,16 +14928,16 @@
         <v>6</v>
       </c>
       <c r="F295" t="n">
-        <v>0.711</v>
+        <v>0.7</v>
       </c>
       <c r="G295" t="n">
         <v>0.922</v>
       </c>
       <c r="H295" t="n">
-        <v>0.000399</v>
+        <v>0.000217</v>
       </c>
       <c r="I295" t="n">
-        <v>0.00219</v>
+        <v>0.00119</v>
       </c>
     </row>
     <row r="296">
@@ -15042,13 +15042,13 @@
         <v>0.608</v>
       </c>
       <c r="G298" t="n">
-        <v>0.744</v>
+        <v>0.736</v>
       </c>
       <c r="H298" t="n">
-        <v>0.0303</v>
+        <v>0.043</v>
       </c>
       <c r="I298" t="n">
-        <v>0.0476</v>
+        <v>0.06759999999999999</v>
       </c>
     </row>
     <row r="299">
@@ -15520,16 +15520,16 @@
         <v>6</v>
       </c>
       <c r="F311" t="n">
-        <v>0.821</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G311" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="H311" t="n">
-        <v>0.00212</v>
+        <v>0.00128</v>
       </c>
       <c r="I311" t="n">
-        <v>0.0233</v>
+        <v>0.0141</v>
       </c>
     </row>
     <row r="312">
@@ -15634,13 +15634,13 @@
         <v>0.752</v>
       </c>
       <c r="G314" t="n">
-        <v>0.834</v>
+        <v>0.829</v>
       </c>
       <c r="H314" t="n">
-        <v>0.0411</v>
+        <v>0.056</v>
       </c>
       <c r="I314" t="n">
-        <v>0.0646</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="315">
@@ -16112,16 +16112,16 @@
         <v>6</v>
       </c>
       <c r="F327" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G327" t="n">
         <v>0.88</v>
       </c>
       <c r="H327" t="n">
-        <v>0.149</v>
+        <v>0.112</v>
       </c>
       <c r="I327" t="n">
-        <v>0.328</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="328">
@@ -16226,13 +16226,13 @@
         <v>0.667</v>
       </c>
       <c r="G330" t="n">
-        <v>0.787</v>
+        <v>0.78</v>
       </c>
       <c r="H330" t="n">
-        <v>0.0273</v>
+        <v>0.0386</v>
       </c>
       <c r="I330" t="n">
-        <v>0.0751</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="331">
@@ -16704,13 +16704,13 @@
         <v>6</v>
       </c>
       <c r="F343" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
       <c r="G343" t="n">
         <v>0.883</v>
       </c>
       <c r="H343" t="n">
-        <v>0.075</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="I343" t="n">
         <v>0.425</v>
@@ -16821,10 +16821,10 @@
         <v>0.96</v>
       </c>
       <c r="H346" t="n">
-        <v>0.391</v>
+        <v>0.389</v>
       </c>
       <c r="I346" t="n">
-        <v>0.538</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="347">
@@ -17296,16 +17296,16 @@
         <v>6</v>
       </c>
       <c r="F359" t="n">
-        <v>0.711</v>
+        <v>0.7</v>
       </c>
       <c r="G359" t="n">
         <v>0.922</v>
       </c>
       <c r="H359" t="n">
-        <v>0.000399</v>
+        <v>0.000217</v>
       </c>
       <c r="I359" t="n">
-        <v>0.00219</v>
+        <v>0.00119</v>
       </c>
     </row>
     <row r="360">
@@ -17410,13 +17410,13 @@
         <v>0.608</v>
       </c>
       <c r="G362" t="n">
-        <v>0.776</v>
+        <v>0.768</v>
       </c>
       <c r="H362" t="n">
-        <v>0.00596</v>
+        <v>0.00927</v>
       </c>
       <c r="I362" t="n">
-        <v>0.0131</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="363">
@@ -17888,16 +17888,16 @@
         <v>6</v>
       </c>
       <c r="F375" t="n">
-        <v>0.821</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G375" t="n">
         <v>0.902</v>
       </c>
       <c r="H375" t="n">
-        <v>0.0379</v>
+        <v>0.0264</v>
       </c>
       <c r="I375" t="n">
-        <v>0.0834</v>
+        <v>0.0581</v>
       </c>
     </row>
     <row r="376">
@@ -18002,13 +18002,13 @@
         <v>0.752</v>
       </c>
       <c r="G378" t="n">
-        <v>0.858</v>
+        <v>0.853</v>
       </c>
       <c r="H378" t="n">
-        <v>0.00665</v>
+        <v>0.01</v>
       </c>
       <c r="I378" t="n">
-        <v>0.0183</v>
+        <v>0.0275</v>
       </c>
     </row>
     <row r="379">
@@ -18480,13 +18480,13 @@
         <v>6</v>
       </c>
       <c r="F391" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="G391" t="n">
         <v>0.853</v>
       </c>
       <c r="H391" t="n">
-        <v>0.357</v>
+        <v>0.286</v>
       </c>
       <c r="I391" t="n">
         <v>0.393</v>
@@ -18600,7 +18600,7 @@
         <v>0.09669999999999999</v>
       </c>
       <c r="I394" t="n">
-        <v>0.175</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="395">
@@ -19072,7 +19072,7 @@
         <v>6</v>
       </c>
       <c r="F407" t="n">
-        <v>0.877</v>
+        <v>0.875</v>
       </c>
       <c r="G407" t="n">
         <v>0.886</v>
@@ -19192,7 +19192,7 @@
         <v>0.238</v>
       </c>
       <c r="I410" t="n">
-        <v>0.538</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="411">
@@ -19664,16 +19664,16 @@
         <v>6</v>
       </c>
       <c r="F423" t="n">
-        <v>0.789</v>
+        <v>0.778</v>
       </c>
       <c r="G423" t="n">
         <v>0.867</v>
       </c>
       <c r="H423" t="n">
-        <v>0.236</v>
+        <v>0.172</v>
       </c>
       <c r="I423" t="n">
-        <v>0.26</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="424">
@@ -19784,7 +19784,7 @@
         <v>0.008240000000000001</v>
       </c>
       <c r="I426" t="n">
-        <v>0.0151</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="427">
@@ -20256,16 +20256,16 @@
         <v>6</v>
       </c>
       <c r="F439" t="n">
-        <v>0.83</v>
+        <v>0.824</v>
       </c>
       <c r="G439" t="n">
         <v>0.876</v>
       </c>
       <c r="H439" t="n">
-        <v>0.23</v>
+        <v>0.179</v>
       </c>
       <c r="I439" t="n">
-        <v>0.253</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="440">
@@ -20376,7 +20376,7 @@
         <v>0.0225</v>
       </c>
       <c r="I442" t="n">
-        <v>0.0413</v>
+        <v>0.0495</v>
       </c>
     </row>
     <row r="443">
@@ -20848,16 +20848,16 @@
         <v>6</v>
       </c>
       <c r="F455" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="G455" t="n">
-        <v>0.853</v>
+        <v>0.847</v>
       </c>
       <c r="H455" t="n">
-        <v>0.357</v>
+        <v>0.364</v>
       </c>
       <c r="I455" t="n">
-        <v>0.393</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="456">
@@ -20962,13 +20962,13 @@
         <v>0.667</v>
       </c>
       <c r="G458" t="n">
-        <v>0.793</v>
+        <v>0.787</v>
       </c>
       <c r="H458" t="n">
-        <v>0.0189</v>
+        <v>0.0273</v>
       </c>
       <c r="I458" t="n">
-        <v>0.0693</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="459">
@@ -21440,10 +21440,10 @@
         <v>6</v>
       </c>
       <c r="F471" t="n">
-        <v>0.877</v>
+        <v>0.875</v>
       </c>
       <c r="G471" t="n">
-        <v>0.854</v>
+        <v>0.853</v>
       </c>
       <c r="H471" t="n">
         <v>0.826</v>
@@ -21557,10 +21557,10 @@
         <v>0.927</v>
       </c>
       <c r="H474" t="n">
-        <v>0.36</v>
+        <v>0.359</v>
       </c>
       <c r="I474" t="n">
-        <v>0.538</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="475">
@@ -22032,16 +22032,16 @@
         <v>6</v>
       </c>
       <c r="F487" t="n">
-        <v>0.789</v>
+        <v>0.778</v>
       </c>
       <c r="G487" t="n">
-        <v>0.911</v>
+        <v>0.9</v>
       </c>
       <c r="H487" t="n">
-        <v>0.0354</v>
+        <v>0.0413</v>
       </c>
       <c r="I487" t="n">
-        <v>0.0556</v>
+        <v>0.0649</v>
       </c>
     </row>
     <row r="488">
@@ -22146,13 +22146,13 @@
         <v>0.624</v>
       </c>
       <c r="G490" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H490" t="n">
-        <v>0.00111</v>
+        <v>0.00192</v>
       </c>
       <c r="I490" t="n">
-        <v>0.00407</v>
+        <v>0.00704</v>
       </c>
     </row>
     <row r="491">
@@ -22624,16 +22624,16 @@
         <v>6</v>
       </c>
       <c r="F503" t="n">
-        <v>0.83</v>
+        <v>0.824</v>
       </c>
       <c r="G503" t="n">
-        <v>0.882</v>
+        <v>0.876</v>
       </c>
       <c r="H503" t="n">
-        <v>0.176</v>
+        <v>0.182</v>
       </c>
       <c r="I503" t="n">
-        <v>0.242</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="504">
@@ -22738,13 +22738,13 @@
         <v>0.757</v>
       </c>
       <c r="G506" t="n">
-        <v>0.868</v>
+        <v>0.863</v>
       </c>
       <c r="H506" t="n">
-        <v>0.00306</v>
+        <v>0.0048</v>
       </c>
       <c r="I506" t="n">
-        <v>0.0112</v>
+        <v>0.0176</v>
       </c>
     </row>
     <row r="507">
@@ -23216,16 +23216,16 @@
         <v>6</v>
       </c>
       <c r="F519" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="G519" t="n">
-        <v>0.867</v>
+        <v>0.86</v>
       </c>
       <c r="H519" t="n">
-        <v>0.211</v>
+        <v>0.219</v>
       </c>
       <c r="I519" t="n">
-        <v>0.332</v>
+        <v>0.344</v>
       </c>
     </row>
     <row r="520">
@@ -23330,13 +23330,13 @@
         <v>0.667</v>
       </c>
       <c r="G522" t="n">
-        <v>0.793</v>
+        <v>0.787</v>
       </c>
       <c r="H522" t="n">
-        <v>0.0189</v>
+        <v>0.0273</v>
       </c>
       <c r="I522" t="n">
-        <v>0.0693</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="523">
@@ -23808,10 +23808,10 @@
         <v>6</v>
       </c>
       <c r="F535" t="n">
-        <v>0.877</v>
+        <v>0.875</v>
       </c>
       <c r="G535" t="n">
-        <v>0.889</v>
+        <v>0.888</v>
       </c>
       <c r="H535" t="n">
         <v>0.8159999999999999</v>
@@ -23925,10 +23925,10 @@
         <v>0.927</v>
       </c>
       <c r="H538" t="n">
-        <v>0.36</v>
+        <v>0.359</v>
       </c>
       <c r="I538" t="n">
-        <v>0.538</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="539">
@@ -24400,16 +24400,16 @@
         <v>6</v>
       </c>
       <c r="F551" t="n">
-        <v>0.789</v>
+        <v>0.778</v>
       </c>
       <c r="G551" t="n">
-        <v>0.889</v>
+        <v>0.878</v>
       </c>
       <c r="H551" t="n">
-        <v>0.104</v>
+        <v>0.113</v>
       </c>
       <c r="I551" t="n">
-        <v>0.143</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="552">
@@ -24514,13 +24514,13 @@
         <v>0.624</v>
       </c>
       <c r="G554" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H554" t="n">
-        <v>0.00111</v>
+        <v>0.00192</v>
       </c>
       <c r="I554" t="n">
-        <v>0.00407</v>
+        <v>0.00704</v>
       </c>
     </row>
     <row r="555">
@@ -24992,16 +24992,16 @@
         <v>6</v>
       </c>
       <c r="F567" t="n">
-        <v>0.83</v>
+        <v>0.824</v>
       </c>
       <c r="G567" t="n">
-        <v>0.889</v>
+        <v>0.883</v>
       </c>
       <c r="H567" t="n">
-        <v>0.125</v>
+        <v>0.131</v>
       </c>
       <c r="I567" t="n">
-        <v>0.196</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="568">
@@ -25106,13 +25106,13 @@
         <v>0.757</v>
       </c>
       <c r="G570" t="n">
-        <v>0.868</v>
+        <v>0.863</v>
       </c>
       <c r="H570" t="n">
-        <v>0.00306</v>
+        <v>0.0048</v>
       </c>
       <c r="I570" t="n">
-        <v>0.0112</v>
+        <v>0.0176</v>
       </c>
     </row>
     <row r="571">
@@ -25584,16 +25584,16 @@
         <v>6</v>
       </c>
       <c r="F583" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="G583" t="n">
-        <v>0.847</v>
+        <v>0.84</v>
       </c>
       <c r="H583" t="n">
-        <v>0.446</v>
+        <v>0.453</v>
       </c>
       <c r="I583" t="n">
-        <v>0.446</v>
+        <v>0.453</v>
       </c>
     </row>
     <row r="584">
@@ -25698,13 +25698,13 @@
         <v>0.667</v>
       </c>
       <c r="G586" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H586" t="n">
-        <v>0.00551</v>
+        <v>0.00851</v>
       </c>
       <c r="I586" t="n">
-        <v>0.0606</v>
+        <v>0.0936</v>
       </c>
     </row>
     <row r="587">
@@ -26176,10 +26176,10 @@
         <v>6</v>
       </c>
       <c r="F599" t="n">
-        <v>0.877</v>
+        <v>0.875</v>
       </c>
       <c r="G599" t="n">
-        <v>0.868</v>
+        <v>0.867</v>
       </c>
       <c r="H599" t="n">
         <v>1</v>
@@ -26293,10 +26293,10 @@
         <v>0.929</v>
       </c>
       <c r="H602" t="n">
-        <v>0.365</v>
+        <v>0.363</v>
       </c>
       <c r="I602" t="n">
-        <v>0.538</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="603">
@@ -26768,16 +26768,16 @@
         <v>6</v>
       </c>
       <c r="F615" t="n">
-        <v>0.789</v>
+        <v>0.778</v>
       </c>
       <c r="G615" t="n">
-        <v>0.878</v>
+        <v>0.867</v>
       </c>
       <c r="H615" t="n">
-        <v>0.161</v>
+        <v>0.172</v>
       </c>
       <c r="I615" t="n">
-        <v>0.197</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="616">
@@ -26882,13 +26882,13 @@
         <v>0.624</v>
       </c>
       <c r="G618" t="n">
-        <v>0.84</v>
+        <v>0.832</v>
       </c>
       <c r="H618" t="n">
-        <v>0.000178</v>
+        <v>0.00034</v>
       </c>
       <c r="I618" t="n">
-        <v>0.00196</v>
+        <v>0.00374</v>
       </c>
     </row>
     <row r="619">
@@ -27360,16 +27360,16 @@
         <v>6</v>
       </c>
       <c r="F631" t="n">
-        <v>0.83</v>
+        <v>0.824</v>
       </c>
       <c r="G631" t="n">
-        <v>0.873</v>
+        <v>0.867</v>
       </c>
       <c r="H631" t="n">
-        <v>0.294</v>
+        <v>0.301</v>
       </c>
       <c r="I631" t="n">
-        <v>0.294</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="632">
@@ -27474,13 +27474,13 @@
         <v>0.757</v>
       </c>
       <c r="G634" t="n">
-        <v>0.882</v>
+        <v>0.878</v>
       </c>
       <c r="H634" t="n">
-        <v>0.000684</v>
+        <v>0.00116</v>
       </c>
       <c r="I634" t="n">
-        <v>0.00752</v>
+        <v>0.0128</v>
       </c>
     </row>
     <row r="635">
@@ -27952,16 +27952,16 @@
         <v>6</v>
       </c>
       <c r="F647" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="G647" t="n">
         <v>0.867</v>
       </c>
       <c r="H647" t="n">
-        <v>0.211</v>
+        <v>0.163</v>
       </c>
       <c r="I647" t="n">
-        <v>0.332</v>
+        <v>0.299</v>
       </c>
     </row>
     <row r="648">
@@ -28544,13 +28544,13 @@
         <v>6</v>
       </c>
       <c r="F663" t="n">
-        <v>0.877</v>
+        <v>0.875</v>
       </c>
       <c r="G663" t="n">
         <v>0.961</v>
       </c>
       <c r="H663" t="n">
-        <v>0.081</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="I663" t="n">
         <v>0.425</v>
@@ -28664,7 +28664,7 @@
         <v>0.364</v>
       </c>
       <c r="I666" t="n">
-        <v>0.538</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="667">
@@ -29136,16 +29136,16 @@
         <v>6</v>
       </c>
       <c r="F679" t="n">
-        <v>0.789</v>
+        <v>0.778</v>
       </c>
       <c r="G679" t="n">
         <v>0.8110000000000001</v>
       </c>
       <c r="H679" t="n">
-        <v>0.852</v>
+        <v>0.713</v>
       </c>
       <c r="I679" t="n">
-        <v>0.852</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="680">
@@ -29728,16 +29728,16 @@
         <v>6</v>
       </c>
       <c r="F695" t="n">
-        <v>0.83</v>
+        <v>0.824</v>
       </c>
       <c r="G695" t="n">
         <v>0.88</v>
       </c>
       <c r="H695" t="n">
-        <v>0.219</v>
+        <v>0.169</v>
       </c>
       <c r="I695" t="n">
-        <v>0.253</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="696">
